--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC1CFC4-09F7-47F6-9762-260789816461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CFCFCBB-9B25-4787-A016-36A774B55212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{620F2FE1-F503-4B49-BC57-CF5362249F55}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32651B99-BD7A-4965-A433-19B9A34D9B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C637227-1A6A-4661-AABC-91BCCD4F390E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AA43A1BD-2EBC-4E6B-A8C0-B06F38CB813E}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A920312E-E1EC-41E0-BA63-71AD203645D7}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -4510,7 +4510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B58B86-13CC-4B56-BCB8-3994B39D6CEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C027D2E-1035-4ECD-AF9F-77E6C835F9D2}">
   <dimension ref="A1:G742"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC35C15E-CEF6-4CD9-874B-301CA3196F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6025169-11E7-424F-BDE5-C5E0874C5066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{43C0AF68-44A9-44DD-B3B4-D244A6EA0A61}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{386BEF06-9D30-4982-9932-AAD1C352A85A}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -4468,7 +4468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26AA8AD9-1316-498E-AEC1-3BB3967F5A69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C499A68-4AD1-4B16-A9E9-40FD10C7A706}">
   <dimension ref="A1:G716"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9B00869-D7CD-423B-8EF5-23795223A936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96A93E01-970B-4B4E-964D-2AD29C567736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25410" yWindow="6480" windowWidth="15000" windowHeight="6195" xr2:uid="{E99A6CCA-CE04-4722-A80F-5503590B21CF}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3B9961F0-C022-4287-8185-2B974A59C10C}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3122" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3172" uniqueCount="1201">
   <si>
     <t>0001</t>
   </si>
@@ -1201,6 +1201,9 @@
     <t xml:space="preserve">  216003</t>
   </si>
   <si>
+    <t xml:space="preserve">  216005</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216007</t>
   </si>
   <si>
@@ -3286,6 +3289,60 @@
     <t>GUIDOLI FLORIO S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  216671</t>
+  </si>
+  <si>
+    <t>AA05</t>
+  </si>
+  <si>
+    <t>SANITARIOS ALVAREZ SOC. LEY 19550 CAP. I SECCION I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216675</t>
+  </si>
+  <si>
+    <t>DS15</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216677</t>
+  </si>
+  <si>
+    <t>LP11</t>
+  </si>
+  <si>
+    <t>SANITARIOS LA PRIMERA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216678</t>
+  </si>
+  <si>
+    <t>DA11</t>
+  </si>
+  <si>
+    <t>DAFYS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216684</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -3298,12 +3355,6 @@
     <t xml:space="preserve">     128</t>
   </si>
   <si>
-    <t>AA05</t>
-  </si>
-  <si>
-    <t>SANITARIOS ALVAREZ SOC. LEY 19550 CAP. I SECCION I</t>
-  </si>
-  <si>
     <t>0008</t>
   </si>
   <si>
@@ -3493,13 +3544,10 @@
     <t xml:space="preserve">    2604</t>
   </si>
   <si>
-    <t xml:space="preserve">    2610</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2656</t>
+    <t xml:space="preserve">    2661</t>
   </si>
   <si>
     <t>9999</t>
@@ -4024,31 +4072,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A865FBD-990D-4E8B-ACFE-BBD73A11E51C}">
-  <dimension ref="A1:G624"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29194AA0-4A08-4735-8B1E-C9FE8AD975BB}">
+  <dimension ref="A1:G634"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>1178</v>
+        <v>1194</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1179</v>
+        <v>1195</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1180</v>
+        <v>1196</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1181</v>
+        <v>1197</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1182</v>
+        <v>1198</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1183</v>
+        <v>1199</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1184</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6980,7 +7028,7 @@
         <v>302</v>
       </c>
       <c r="C129" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D129" t="s">
         <v>303</v>
@@ -8248,16 +8296,16 @@
         <v>80</v>
       </c>
       <c r="D184" t="s">
-        <v>394</v>
+        <v>31</v>
       </c>
       <c r="E184" t="s">
-        <v>395</v>
+        <v>32</v>
       </c>
       <c r="F184" s="1">
         <v>46283</v>
       </c>
       <c r="G184" s="1">
-        <v>46283</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -8265,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
+        <v>394</v>
+      </c>
+      <c r="C185" t="s">
+        <v>80</v>
+      </c>
+      <c r="D185" t="s">
+        <v>395</v>
+      </c>
+      <c r="E185" t="s">
         <v>396</v>
-      </c>
-      <c r="C185" t="s">
-        <v>80</v>
-      </c>
-      <c r="D185" t="s">
-        <v>394</v>
-      </c>
-      <c r="E185" t="s">
-        <v>395</v>
       </c>
       <c r="F185" s="1">
         <v>46283</v>
@@ -8294,16 +8342,16 @@
         <v>80</v>
       </c>
       <c r="D186" t="s">
-        <v>249</v>
+        <v>395</v>
       </c>
       <c r="E186" t="s">
-        <v>250</v>
+        <v>396</v>
       </c>
       <c r="F186" s="1">
         <v>46283</v>
       </c>
       <c r="G186" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
@@ -8317,16 +8365,16 @@
         <v>80</v>
       </c>
       <c r="D187" t="s">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="E187" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="F187" s="1">
         <v>46283</v>
       </c>
       <c r="G187" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -8337,19 +8385,19 @@
         <v>399</v>
       </c>
       <c r="C188" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D188" t="s">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="E188" t="s">
-        <v>401</v>
+        <v>38</v>
       </c>
       <c r="F188" s="1">
         <v>46283</v>
       </c>
       <c r="G188" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
@@ -8357,22 +8405,22 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
+        <v>400</v>
+      </c>
+      <c r="C189" t="s">
+        <v>2</v>
+      </c>
+      <c r="D189" t="s">
+        <v>401</v>
+      </c>
+      <c r="E189" t="s">
         <v>402</v>
-      </c>
-      <c r="C189" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>403</v>
-      </c>
-      <c r="E189" t="s">
-        <v>404</v>
       </c>
       <c r="F189" s="1">
         <v>46283</v>
       </c>
       <c r="G189" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -8380,22 +8428,22 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
+        <v>403</v>
+      </c>
+      <c r="C190" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
+        <v>404</v>
+      </c>
+      <c r="E190" t="s">
         <v>405</v>
-      </c>
-      <c r="C190" t="s">
-        <v>80</v>
-      </c>
-      <c r="D190" t="s">
-        <v>406</v>
-      </c>
-      <c r="E190" t="s">
-        <v>407</v>
       </c>
       <c r="F190" s="1">
         <v>46283</v>
       </c>
       <c r="G190" s="1">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -8403,16 +8451,16 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
+        <v>406</v>
+      </c>
+      <c r="C191" t="s">
+        <v>80</v>
+      </c>
+      <c r="D191" t="s">
+        <v>407</v>
+      </c>
+      <c r="E191" t="s">
         <v>408</v>
-      </c>
-      <c r="C191" t="s">
-        <v>80</v>
-      </c>
-      <c r="D191" t="s">
-        <v>409</v>
-      </c>
-      <c r="E191" t="s">
-        <v>410</v>
       </c>
       <c r="F191" s="1">
         <v>46283</v>
@@ -8426,22 +8474,22 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
+        <v>409</v>
+      </c>
+      <c r="C192" t="s">
+        <v>80</v>
+      </c>
+      <c r="D192" t="s">
+        <v>410</v>
+      </c>
+      <c r="E192" t="s">
         <v>411</v>
-      </c>
-      <c r="C192" t="s">
-        <v>2</v>
-      </c>
-      <c r="D192" t="s">
-        <v>143</v>
-      </c>
-      <c r="E192" t="s">
-        <v>144</v>
       </c>
       <c r="F192" s="1">
         <v>46283</v>
       </c>
       <c r="G192" s="1">
-        <v>46283</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
@@ -8452,19 +8500,19 @@
         <v>412</v>
       </c>
       <c r="C193" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D193" t="s">
-        <v>403</v>
+        <v>143</v>
       </c>
       <c r="E193" t="s">
-        <v>404</v>
+        <v>144</v>
       </c>
       <c r="F193" s="1">
         <v>46283</v>
       </c>
       <c r="G193" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
@@ -8475,19 +8523,19 @@
         <v>413</v>
       </c>
       <c r="C194" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D194" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E194" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="F194" s="1">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="G194" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
@@ -8495,22 +8543,22 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
+        <v>414</v>
+      </c>
+      <c r="C195" t="s">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>415</v>
+      </c>
+      <c r="E195" t="s">
         <v>416</v>
-      </c>
-      <c r="C195" t="s">
-        <v>80</v>
-      </c>
-      <c r="D195" t="s">
-        <v>152</v>
-      </c>
-      <c r="E195" t="s">
-        <v>153</v>
       </c>
       <c r="F195" s="1">
         <v>46284</v>
       </c>
       <c r="G195" s="1">
-        <v>46294</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -8521,19 +8569,19 @@
         <v>417</v>
       </c>
       <c r="C196" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D196" t="s">
-        <v>418</v>
+        <v>152</v>
       </c>
       <c r="E196" t="s">
-        <v>419</v>
+        <v>153</v>
       </c>
       <c r="F196" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="G196" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -8541,22 +8589,22 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
+        <v>418</v>
+      </c>
+      <c r="C197" t="s">
+        <v>2</v>
+      </c>
+      <c r="D197" t="s">
+        <v>419</v>
+      </c>
+      <c r="E197" t="s">
         <v>420</v>
-      </c>
-      <c r="C197" t="s">
-        <v>80</v>
-      </c>
-      <c r="D197" t="s">
-        <v>421</v>
-      </c>
-      <c r="E197" t="s">
-        <v>422</v>
       </c>
       <c r="F197" s="1">
         <v>46286</v>
       </c>
       <c r="G197" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -8564,16 +8612,16 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
+        <v>421</v>
+      </c>
+      <c r="C198" t="s">
+        <v>80</v>
+      </c>
+      <c r="D198" t="s">
+        <v>422</v>
+      </c>
+      <c r="E198" t="s">
         <v>423</v>
-      </c>
-      <c r="C198" t="s">
-        <v>80</v>
-      </c>
-      <c r="D198" t="s">
-        <v>300</v>
-      </c>
-      <c r="E198" t="s">
-        <v>301</v>
       </c>
       <c r="F198" s="1">
         <v>46286</v>
@@ -8593,10 +8641,10 @@
         <v>80</v>
       </c>
       <c r="D199" t="s">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="E199" t="s">
-        <v>426</v>
+        <v>301</v>
       </c>
       <c r="F199" s="1">
         <v>46286</v>
@@ -8610,16 +8658,16 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
+        <v>425</v>
+      </c>
+      <c r="C200" t="s">
+        <v>80</v>
+      </c>
+      <c r="D200" t="s">
+        <v>426</v>
+      </c>
+      <c r="E200" t="s">
         <v>427</v>
-      </c>
-      <c r="C200" t="s">
-        <v>80</v>
-      </c>
-      <c r="D200" t="s">
-        <v>16</v>
-      </c>
-      <c r="E200" t="s">
-        <v>17</v>
       </c>
       <c r="F200" s="1">
         <v>46286</v>
@@ -8662,10 +8710,10 @@
         <v>80</v>
       </c>
       <c r="D202" t="s">
-        <v>430</v>
+        <v>16</v>
       </c>
       <c r="E202" t="s">
-        <v>431</v>
+        <v>17</v>
       </c>
       <c r="F202" s="1">
         <v>46286</v>
@@ -8679,22 +8727,22 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
+        <v>430</v>
+      </c>
+      <c r="C203" t="s">
+        <v>80</v>
+      </c>
+      <c r="D203" t="s">
+        <v>431</v>
+      </c>
+      <c r="E203" t="s">
         <v>432</v>
-      </c>
-      <c r="C203" t="s">
-        <v>80</v>
-      </c>
-      <c r="D203" t="s">
-        <v>433</v>
-      </c>
-      <c r="E203" t="s">
-        <v>434</v>
       </c>
       <c r="F203" s="1">
         <v>46286</v>
       </c>
       <c r="G203" s="1">
-        <v>46293</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -8702,22 +8750,22 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
+        <v>433</v>
+      </c>
+      <c r="C204" t="s">
+        <v>80</v>
+      </c>
+      <c r="D204" t="s">
+        <v>434</v>
+      </c>
+      <c r="E204" t="s">
         <v>435</v>
-      </c>
-      <c r="C204" t="s">
-        <v>80</v>
-      </c>
-      <c r="D204" t="s">
-        <v>223</v>
-      </c>
-      <c r="E204" t="s">
-        <v>224</v>
       </c>
       <c r="F204" s="1">
         <v>46286</v>
       </c>
       <c r="G204" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -8731,16 +8779,16 @@
         <v>80</v>
       </c>
       <c r="D205" t="s">
-        <v>437</v>
+        <v>223</v>
       </c>
       <c r="E205" t="s">
-        <v>438</v>
+        <v>224</v>
       </c>
       <c r="F205" s="1">
         <v>46286</v>
       </c>
       <c r="G205" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -8748,22 +8796,22 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
+        <v>437</v>
+      </c>
+      <c r="C206" t="s">
+        <v>80</v>
+      </c>
+      <c r="D206" t="s">
+        <v>438</v>
+      </c>
+      <c r="E206" t="s">
         <v>439</v>
-      </c>
-      <c r="C206" t="s">
-        <v>80</v>
-      </c>
-      <c r="D206" t="s">
-        <v>440</v>
-      </c>
-      <c r="E206" t="s">
-        <v>441</v>
       </c>
       <c r="F206" s="1">
         <v>46286</v>
       </c>
       <c r="G206" s="1">
-        <v>46286</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -8771,16 +8819,16 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
+        <v>440</v>
+      </c>
+      <c r="C207" t="s">
+        <v>80</v>
+      </c>
+      <c r="D207" t="s">
+        <v>441</v>
+      </c>
+      <c r="E207" t="s">
         <v>442</v>
-      </c>
-      <c r="C207" t="s">
-        <v>80</v>
-      </c>
-      <c r="D207" t="s">
-        <v>443</v>
-      </c>
-      <c r="E207" t="s">
-        <v>444</v>
       </c>
       <c r="F207" s="1">
         <v>46286</v>
@@ -8794,16 +8842,16 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
+        <v>443</v>
+      </c>
+      <c r="C208" t="s">
+        <v>80</v>
+      </c>
+      <c r="D208" t="s">
+        <v>444</v>
+      </c>
+      <c r="E208" t="s">
         <v>445</v>
-      </c>
-      <c r="C208" t="s">
-        <v>80</v>
-      </c>
-      <c r="D208" t="s">
-        <v>446</v>
-      </c>
-      <c r="E208" t="s">
-        <v>447</v>
       </c>
       <c r="F208" s="1">
         <v>46286</v>
@@ -8817,16 +8865,16 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
+        <v>446</v>
+      </c>
+      <c r="C209" t="s">
+        <v>80</v>
+      </c>
+      <c r="D209" t="s">
+        <v>447</v>
+      </c>
+      <c r="E209" t="s">
         <v>448</v>
-      </c>
-      <c r="C209" t="s">
-        <v>80</v>
-      </c>
-      <c r="D209" t="s">
-        <v>449</v>
-      </c>
-      <c r="E209" t="s">
-        <v>450</v>
       </c>
       <c r="F209" s="1">
         <v>46286</v>
@@ -8840,16 +8888,16 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
+        <v>449</v>
+      </c>
+      <c r="C210" t="s">
+        <v>80</v>
+      </c>
+      <c r="D210" t="s">
+        <v>450</v>
+      </c>
+      <c r="E210" t="s">
         <v>451</v>
-      </c>
-      <c r="C210" t="s">
-        <v>80</v>
-      </c>
-      <c r="D210" t="s">
-        <v>16</v>
-      </c>
-      <c r="E210" t="s">
-        <v>17</v>
       </c>
       <c r="F210" s="1">
         <v>46286</v>
@@ -8869,10 +8917,10 @@
         <v>80</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>16</v>
       </c>
       <c r="E211" t="s">
-        <v>454</v>
+        <v>17</v>
       </c>
       <c r="F211" s="1">
         <v>46286</v>
@@ -8886,16 +8934,16 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
+        <v>453</v>
+      </c>
+      <c r="C212" t="s">
+        <v>80</v>
+      </c>
+      <c r="D212" t="s">
+        <v>454</v>
+      </c>
+      <c r="E212" t="s">
         <v>455</v>
-      </c>
-      <c r="C212" t="s">
-        <v>80</v>
-      </c>
-      <c r="D212" t="s">
-        <v>456</v>
-      </c>
-      <c r="E212" t="s">
-        <v>457</v>
       </c>
       <c r="F212" s="1">
         <v>46286</v>
@@ -8909,16 +8957,16 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
+        <v>456</v>
+      </c>
+      <c r="C213" t="s">
+        <v>80</v>
+      </c>
+      <c r="D213" t="s">
+        <v>457</v>
+      </c>
+      <c r="E213" t="s">
         <v>458</v>
-      </c>
-      <c r="C213" t="s">
-        <v>80</v>
-      </c>
-      <c r="D213" t="s">
-        <v>456</v>
-      </c>
-      <c r="E213" t="s">
-        <v>457</v>
       </c>
       <c r="F213" s="1">
         <v>46286</v>
@@ -8938,10 +8986,10 @@
         <v>80</v>
       </c>
       <c r="D214" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E214" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F214" s="1">
         <v>46286</v>
@@ -8955,16 +9003,16 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
+        <v>460</v>
+      </c>
+      <c r="C215" t="s">
+        <v>80</v>
+      </c>
+      <c r="D215" t="s">
+        <v>461</v>
+      </c>
+      <c r="E215" t="s">
         <v>462</v>
-      </c>
-      <c r="C215" t="s">
-        <v>80</v>
-      </c>
-      <c r="D215" t="s">
-        <v>16</v>
-      </c>
-      <c r="E215" t="s">
-        <v>17</v>
       </c>
       <c r="F215" s="1">
         <v>46286</v>
@@ -8984,10 +9032,10 @@
         <v>80</v>
       </c>
       <c r="D216" t="s">
-        <v>464</v>
+        <v>16</v>
       </c>
       <c r="E216" t="s">
-        <v>465</v>
+        <v>17</v>
       </c>
       <c r="F216" s="1">
         <v>46286</v>
@@ -9001,16 +9049,16 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
+        <v>464</v>
+      </c>
+      <c r="C217" t="s">
+        <v>80</v>
+      </c>
+      <c r="D217" t="s">
+        <v>465</v>
+      </c>
+      <c r="E217" t="s">
         <v>466</v>
-      </c>
-      <c r="C217" t="s">
-        <v>80</v>
-      </c>
-      <c r="D217" t="s">
-        <v>464</v>
-      </c>
-      <c r="E217" t="s">
-        <v>465</v>
       </c>
       <c r="F217" s="1">
         <v>46286</v>
@@ -9030,10 +9078,10 @@
         <v>80</v>
       </c>
       <c r="D218" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E218" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F218" s="1">
         <v>46286</v>
@@ -9053,10 +9101,10 @@
         <v>80</v>
       </c>
       <c r="D219" t="s">
-        <v>37</v>
+        <v>465</v>
       </c>
       <c r="E219" t="s">
-        <v>38</v>
+        <v>466</v>
       </c>
       <c r="F219" s="1">
         <v>46286</v>
@@ -9214,10 +9262,10 @@
         <v>80</v>
       </c>
       <c r="D226" t="s">
-        <v>476</v>
+        <v>37</v>
       </c>
       <c r="E226" t="s">
-        <v>477</v>
+        <v>38</v>
       </c>
       <c r="F226" s="1">
         <v>46286</v>
@@ -9231,16 +9279,16 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
+        <v>476</v>
+      </c>
+      <c r="C227" t="s">
+        <v>80</v>
+      </c>
+      <c r="D227" t="s">
+        <v>477</v>
+      </c>
+      <c r="E227" t="s">
         <v>478</v>
-      </c>
-      <c r="C227" t="s">
-        <v>80</v>
-      </c>
-      <c r="D227" t="s">
-        <v>267</v>
-      </c>
-      <c r="E227" t="s">
-        <v>268</v>
       </c>
       <c r="F227" s="1">
         <v>46286</v>
@@ -9303,13 +9351,13 @@
         <v>481</v>
       </c>
       <c r="C230" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D230" t="s">
-        <v>482</v>
+        <v>267</v>
       </c>
       <c r="E230" t="s">
-        <v>483</v>
+        <v>268</v>
       </c>
       <c r="F230" s="1">
         <v>46286</v>
@@ -9323,22 +9371,22 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
+        <v>482</v>
+      </c>
+      <c r="C231" t="s">
+        <v>2</v>
+      </c>
+      <c r="D231" t="s">
+        <v>483</v>
+      </c>
+      <c r="E231" t="s">
         <v>484</v>
-      </c>
-      <c r="C231" t="s">
-        <v>80</v>
-      </c>
-      <c r="D231" t="s">
-        <v>182</v>
-      </c>
-      <c r="E231" t="s">
-        <v>183</v>
       </c>
       <c r="F231" s="1">
         <v>46286</v>
       </c>
       <c r="G231" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -9352,10 +9400,10 @@
         <v>80</v>
       </c>
       <c r="D232" t="s">
-        <v>486</v>
+        <v>182</v>
       </c>
       <c r="E232" t="s">
-        <v>487</v>
+        <v>183</v>
       </c>
       <c r="F232" s="1">
         <v>46286</v>
@@ -9369,22 +9417,22 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
+        <v>486</v>
+      </c>
+      <c r="C233" t="s">
+        <v>80</v>
+      </c>
+      <c r="D233" t="s">
+        <v>487</v>
+      </c>
+      <c r="E233" t="s">
         <v>488</v>
-      </c>
-      <c r="C233" t="s">
-        <v>80</v>
-      </c>
-      <c r="D233" t="s">
-        <v>16</v>
-      </c>
-      <c r="E233" t="s">
-        <v>17</v>
       </c>
       <c r="F233" s="1">
         <v>46286</v>
       </c>
       <c r="G233" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -9398,10 +9446,10 @@
         <v>80</v>
       </c>
       <c r="D234" t="s">
-        <v>490</v>
+        <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>491</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1">
         <v>46286</v>
@@ -9415,22 +9463,22 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>490</v>
+      </c>
+      <c r="C235" t="s">
+        <v>80</v>
+      </c>
+      <c r="D235" t="s">
+        <v>491</v>
+      </c>
+      <c r="E235" t="s">
         <v>492</v>
-      </c>
-      <c r="C235" t="s">
-        <v>80</v>
-      </c>
-      <c r="D235" t="s">
-        <v>493</v>
-      </c>
-      <c r="E235" t="s">
-        <v>494</v>
       </c>
       <c r="F235" s="1">
         <v>46286</v>
       </c>
       <c r="G235" s="1">
-        <v>46287</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -9438,22 +9486,22 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
+        <v>493</v>
+      </c>
+      <c r="C236" t="s">
+        <v>80</v>
+      </c>
+      <c r="D236" t="s">
+        <v>494</v>
+      </c>
+      <c r="E236" t="s">
         <v>495</v>
-      </c>
-      <c r="C236" t="s">
-        <v>80</v>
-      </c>
-      <c r="D236" t="s">
-        <v>496</v>
-      </c>
-      <c r="E236" t="s">
-        <v>497</v>
       </c>
       <c r="F236" s="1">
         <v>46286</v>
       </c>
       <c r="G236" s="1">
-        <v>46294</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -9461,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
+        <v>496</v>
+      </c>
+      <c r="C237" t="s">
+        <v>80</v>
+      </c>
+      <c r="D237" t="s">
+        <v>497</v>
+      </c>
+      <c r="E237" t="s">
         <v>498</v>
-      </c>
-      <c r="C237" t="s">
-        <v>80</v>
-      </c>
-      <c r="D237" t="s">
-        <v>499</v>
-      </c>
-      <c r="E237" t="s">
-        <v>500</v>
       </c>
       <c r="F237" s="1">
         <v>46286</v>
       </c>
       <c r="G237" s="1">
-        <v>46287</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -9484,22 +9532,22 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
+        <v>499</v>
+      </c>
+      <c r="C238" t="s">
+        <v>80</v>
+      </c>
+      <c r="D238" t="s">
+        <v>500</v>
+      </c>
+      <c r="E238" t="s">
         <v>501</v>
       </c>
-      <c r="C238" t="s">
-        <v>2</v>
-      </c>
-      <c r="D238" t="s">
-        <v>84</v>
-      </c>
-      <c r="E238" t="s">
-        <v>85</v>
-      </c>
       <c r="F238" s="1">
+        <v>46286</v>
+      </c>
+      <c r="G238" s="1">
         <v>46287</v>
-      </c>
-      <c r="G238" s="1">
-        <v>46290</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -9513,16 +9561,16 @@
         <v>2</v>
       </c>
       <c r="D239" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="E239" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="F239" s="1">
         <v>46287</v>
       </c>
       <c r="G239" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -9533,7 +9581,7 @@
         <v>503</v>
       </c>
       <c r="C240" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D240" t="s">
         <v>37</v>
@@ -9559,10 +9607,10 @@
         <v>80</v>
       </c>
       <c r="D241" t="s">
-        <v>430</v>
+        <v>37</v>
       </c>
       <c r="E241" t="s">
-        <v>431</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1">
         <v>46287</v>
@@ -9579,13 +9627,13 @@
         <v>505</v>
       </c>
       <c r="C242" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>431</v>
       </c>
       <c r="E242" t="s">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="F242" s="1">
         <v>46287</v>
@@ -9599,16 +9647,16 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
+        <v>506</v>
+      </c>
+      <c r="C243" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" t="s">
+        <v>507</v>
+      </c>
+      <c r="E243" t="s">
         <v>508</v>
-      </c>
-      <c r="C243" t="s">
-        <v>80</v>
-      </c>
-      <c r="D243" t="s">
-        <v>509</v>
-      </c>
-      <c r="E243" t="s">
-        <v>510</v>
       </c>
       <c r="F243" s="1">
         <v>46287</v>
@@ -9622,16 +9670,16 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
+        <v>509</v>
+      </c>
+      <c r="C244" t="s">
+        <v>80</v>
+      </c>
+      <c r="D244" t="s">
+        <v>510</v>
+      </c>
+      <c r="E244" t="s">
         <v>511</v>
-      </c>
-      <c r="C244" t="s">
-        <v>80</v>
-      </c>
-      <c r="D244" t="s">
-        <v>509</v>
-      </c>
-      <c r="E244" t="s">
-        <v>510</v>
       </c>
       <c r="F244" s="1">
         <v>46287</v>
@@ -9651,10 +9699,10 @@
         <v>80</v>
       </c>
       <c r="D245" t="s">
-        <v>28</v>
+        <v>510</v>
       </c>
       <c r="E245" t="s">
-        <v>29</v>
+        <v>511</v>
       </c>
       <c r="F245" s="1">
         <v>46287</v>
@@ -9674,10 +9722,10 @@
         <v>80</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c r="E246" t="s">
-        <v>515</v>
+        <v>29</v>
       </c>
       <c r="F246" s="1">
         <v>46287</v>
@@ -9691,16 +9739,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
+        <v>514</v>
+      </c>
+      <c r="C247" t="s">
+        <v>80</v>
+      </c>
+      <c r="D247" t="s">
+        <v>515</v>
+      </c>
+      <c r="E247" t="s">
         <v>516</v>
-      </c>
-      <c r="C247" t="s">
-        <v>80</v>
-      </c>
-      <c r="D247" t="s">
-        <v>517</v>
-      </c>
-      <c r="E247" t="s">
-        <v>518</v>
       </c>
       <c r="F247" s="1">
         <v>46287</v>
@@ -9714,16 +9762,16 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
+        <v>517</v>
+      </c>
+      <c r="C248" t="s">
+        <v>80</v>
+      </c>
+      <c r="D248" t="s">
+        <v>518</v>
+      </c>
+      <c r="E248" t="s">
         <v>519</v>
-      </c>
-      <c r="C248" t="s">
-        <v>80</v>
-      </c>
-      <c r="D248" t="s">
-        <v>520</v>
-      </c>
-      <c r="E248" t="s">
-        <v>521</v>
       </c>
       <c r="F248" s="1">
         <v>46287</v>
@@ -9737,16 +9785,16 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
+        <v>520</v>
+      </c>
+      <c r="C249" t="s">
+        <v>80</v>
+      </c>
+      <c r="D249" t="s">
+        <v>521</v>
+      </c>
+      <c r="E249" t="s">
         <v>522</v>
-      </c>
-      <c r="C249" t="s">
-        <v>80</v>
-      </c>
-      <c r="D249" t="s">
-        <v>523</v>
-      </c>
-      <c r="E249" t="s">
-        <v>524</v>
       </c>
       <c r="F249" s="1">
         <v>46287</v>
@@ -9760,16 +9808,16 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
+        <v>523</v>
+      </c>
+      <c r="C250" t="s">
+        <v>80</v>
+      </c>
+      <c r="D250" t="s">
+        <v>524</v>
+      </c>
+      <c r="E250" t="s">
         <v>525</v>
-      </c>
-      <c r="C250" t="s">
-        <v>80</v>
-      </c>
-      <c r="D250" t="s">
-        <v>526</v>
-      </c>
-      <c r="E250" t="s">
-        <v>527</v>
       </c>
       <c r="F250" s="1">
         <v>46287</v>
@@ -9783,22 +9831,22 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
+        <v>526</v>
+      </c>
+      <c r="C251" t="s">
+        <v>80</v>
+      </c>
+      <c r="D251" t="s">
+        <v>527</v>
+      </c>
+      <c r="E251" t="s">
         <v>528</v>
-      </c>
-      <c r="C251" t="s">
-        <v>80</v>
-      </c>
-      <c r="D251" t="s">
-        <v>3</v>
-      </c>
-      <c r="E251" t="s">
-        <v>4</v>
       </c>
       <c r="F251" s="1">
         <v>46287</v>
       </c>
       <c r="G251" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -9812,16 +9860,16 @@
         <v>80</v>
       </c>
       <c r="D252" t="s">
-        <v>530</v>
+        <v>3</v>
       </c>
       <c r="E252" t="s">
-        <v>531</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1">
         <v>46287</v>
       </c>
       <c r="G252" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -9829,22 +9877,22 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
+        <v>530</v>
+      </c>
+      <c r="C253" t="s">
+        <v>80</v>
+      </c>
+      <c r="D253" t="s">
+        <v>531</v>
+      </c>
+      <c r="E253" t="s">
         <v>532</v>
-      </c>
-      <c r="C253" t="s">
-        <v>80</v>
-      </c>
-      <c r="D253" t="s">
-        <v>13</v>
-      </c>
-      <c r="E253" t="s">
-        <v>14</v>
       </c>
       <c r="F253" s="1">
         <v>46287</v>
       </c>
       <c r="G253" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -9858,16 +9906,16 @@
         <v>80</v>
       </c>
       <c r="D254" t="s">
-        <v>394</v>
+        <v>13</v>
       </c>
       <c r="E254" t="s">
-        <v>395</v>
+        <v>14</v>
       </c>
       <c r="F254" s="1">
         <v>46287</v>
       </c>
       <c r="G254" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -9881,10 +9929,10 @@
         <v>80</v>
       </c>
       <c r="D255" t="s">
-        <v>16</v>
+        <v>395</v>
       </c>
       <c r="E255" t="s">
-        <v>17</v>
+        <v>396</v>
       </c>
       <c r="F255" s="1">
         <v>46287</v>
@@ -9950,10 +9998,10 @@
         <v>80</v>
       </c>
       <c r="D258" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1">
         <v>46287</v>
@@ -9973,10 +10021,10 @@
         <v>80</v>
       </c>
       <c r="D259" t="s">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="E259" t="s">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="F259" s="1">
         <v>46287</v>
@@ -9993,19 +10041,19 @@
         <v>539</v>
       </c>
       <c r="C260" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D260" t="s">
-        <v>540</v>
+        <v>74</v>
       </c>
       <c r="E260" t="s">
-        <v>541</v>
+        <v>75</v>
       </c>
       <c r="F260" s="1">
         <v>46287</v>
       </c>
       <c r="G260" s="1">
-        <v>46294</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
@@ -10013,22 +10061,22 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
+        <v>540</v>
+      </c>
+      <c r="C261" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" t="s">
+        <v>541</v>
+      </c>
+      <c r="E261" t="s">
         <v>542</v>
-      </c>
-      <c r="C261" t="s">
-        <v>80</v>
-      </c>
-      <c r="D261" t="s">
-        <v>98</v>
-      </c>
-      <c r="E261" t="s">
-        <v>99</v>
       </c>
       <c r="F261" s="1">
         <v>46287</v>
       </c>
       <c r="G261" s="1">
-        <v>46287</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
@@ -10042,10 +10090,10 @@
         <v>80</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F262" s="1">
         <v>46287</v>
@@ -10065,10 +10113,10 @@
         <v>80</v>
       </c>
       <c r="D263" t="s">
-        <v>545</v>
+        <v>16</v>
       </c>
       <c r="E263" t="s">
-        <v>546</v>
+        <v>17</v>
       </c>
       <c r="F263" s="1">
         <v>46287</v>
@@ -10082,16 +10130,16 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
+        <v>545</v>
+      </c>
+      <c r="C264" t="s">
+        <v>80</v>
+      </c>
+      <c r="D264" t="s">
+        <v>546</v>
+      </c>
+      <c r="E264" t="s">
         <v>547</v>
-      </c>
-      <c r="C264" t="s">
-        <v>80</v>
-      </c>
-      <c r="D264" t="s">
-        <v>548</v>
-      </c>
-      <c r="E264" t="s">
-        <v>549</v>
       </c>
       <c r="F264" s="1">
         <v>46287</v>
@@ -10105,16 +10153,16 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
+        <v>548</v>
+      </c>
+      <c r="C265" t="s">
+        <v>80</v>
+      </c>
+      <c r="D265" t="s">
+        <v>549</v>
+      </c>
+      <c r="E265" t="s">
         <v>550</v>
-      </c>
-      <c r="C265" t="s">
-        <v>80</v>
-      </c>
-      <c r="D265" t="s">
-        <v>551</v>
-      </c>
-      <c r="E265" t="s">
-        <v>552</v>
       </c>
       <c r="F265" s="1">
         <v>46287</v>
@@ -10128,22 +10176,22 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
+        <v>551</v>
+      </c>
+      <c r="C266" t="s">
+        <v>80</v>
+      </c>
+      <c r="D266" t="s">
+        <v>552</v>
+      </c>
+      <c r="E266" t="s">
         <v>553</v>
-      </c>
-      <c r="C266" t="s">
-        <v>80</v>
-      </c>
-      <c r="D266" t="s">
-        <v>554</v>
-      </c>
-      <c r="E266" t="s">
-        <v>555</v>
       </c>
       <c r="F266" s="1">
         <v>46287</v>
       </c>
       <c r="G266" s="1">
-        <v>46294</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
@@ -10151,22 +10199,22 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>554</v>
+      </c>
+      <c r="C267" t="s">
+        <v>80</v>
+      </c>
+      <c r="D267" t="s">
+        <v>555</v>
+      </c>
+      <c r="E267" t="s">
         <v>556</v>
-      </c>
-      <c r="C267" t="s">
-        <v>80</v>
-      </c>
-      <c r="D267" t="s">
-        <v>37</v>
-      </c>
-      <c r="E267" t="s">
-        <v>38</v>
       </c>
       <c r="F267" s="1">
         <v>46287</v>
       </c>
       <c r="G267" s="1">
-        <v>46287</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
@@ -10180,10 +10228,10 @@
         <v>80</v>
       </c>
       <c r="D268" t="s">
-        <v>558</v>
+        <v>37</v>
       </c>
       <c r="E268" t="s">
-        <v>559</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1">
         <v>46287</v>
@@ -10197,22 +10245,22 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
+        <v>558</v>
+      </c>
+      <c r="C269" t="s">
+        <v>80</v>
+      </c>
+      <c r="D269" t="s">
+        <v>559</v>
+      </c>
+      <c r="E269" t="s">
         <v>560</v>
-      </c>
-      <c r="C269" t="s">
-        <v>80</v>
-      </c>
-      <c r="D269" t="s">
-        <v>561</v>
-      </c>
-      <c r="E269" t="s">
-        <v>562</v>
       </c>
       <c r="F269" s="1">
         <v>46287</v>
       </c>
       <c r="G269" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
@@ -10220,22 +10268,22 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
+        <v>561</v>
+      </c>
+      <c r="C270" t="s">
+        <v>80</v>
+      </c>
+      <c r="D270" t="s">
+        <v>562</v>
+      </c>
+      <c r="E270" t="s">
         <v>563</v>
-      </c>
-      <c r="C270" t="s">
-        <v>80</v>
-      </c>
-      <c r="D270" t="s">
-        <v>564</v>
-      </c>
-      <c r="E270" t="s">
-        <v>565</v>
       </c>
       <c r="F270" s="1">
         <v>46287</v>
       </c>
       <c r="G270" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -10243,22 +10291,22 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
+        <v>564</v>
+      </c>
+      <c r="C271" t="s">
+        <v>80</v>
+      </c>
+      <c r="D271" t="s">
+        <v>565</v>
+      </c>
+      <c r="E271" t="s">
         <v>566</v>
-      </c>
-      <c r="C271" t="s">
-        <v>80</v>
-      </c>
-      <c r="D271" t="s">
-        <v>567</v>
-      </c>
-      <c r="E271" t="s">
-        <v>568</v>
       </c>
       <c r="F271" s="1">
         <v>46287</v>
       </c>
       <c r="G271" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
@@ -10266,16 +10314,16 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
+        <v>567</v>
+      </c>
+      <c r="C272" t="s">
+        <v>80</v>
+      </c>
+      <c r="D272" t="s">
+        <v>568</v>
+      </c>
+      <c r="E272" t="s">
         <v>569</v>
-      </c>
-      <c r="C272" t="s">
-        <v>80</v>
-      </c>
-      <c r="D272" t="s">
-        <v>185</v>
-      </c>
-      <c r="E272" t="s">
-        <v>186</v>
       </c>
       <c r="F272" s="1">
         <v>46287</v>
@@ -10295,16 +10343,16 @@
         <v>80</v>
       </c>
       <c r="D273" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="E273" t="s">
-        <v>279</v>
+        <v>186</v>
       </c>
       <c r="F273" s="1">
         <v>46287</v>
       </c>
       <c r="G273" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
@@ -10318,10 +10366,10 @@
         <v>80</v>
       </c>
       <c r="D274" t="s">
-        <v>572</v>
+        <v>278</v>
       </c>
       <c r="E274" t="s">
-        <v>573</v>
+        <v>279</v>
       </c>
       <c r="F274" s="1">
         <v>46287</v>
@@ -10335,22 +10383,22 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
+        <v>572</v>
+      </c>
+      <c r="C275" t="s">
+        <v>80</v>
+      </c>
+      <c r="D275" t="s">
+        <v>573</v>
+      </c>
+      <c r="E275" t="s">
         <v>574</v>
-      </c>
-      <c r="C275" t="s">
-        <v>80</v>
-      </c>
-      <c r="D275" t="s">
-        <v>575</v>
-      </c>
-      <c r="E275" t="s">
-        <v>576</v>
       </c>
       <c r="F275" s="1">
         <v>46287</v>
       </c>
       <c r="G275" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
@@ -10358,22 +10406,22 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
+        <v>575</v>
+      </c>
+      <c r="C276" t="s">
+        <v>80</v>
+      </c>
+      <c r="D276" t="s">
+        <v>576</v>
+      </c>
+      <c r="E276" t="s">
         <v>577</v>
-      </c>
-      <c r="C276" t="s">
-        <v>80</v>
-      </c>
-      <c r="D276" t="s">
-        <v>578</v>
-      </c>
-      <c r="E276" t="s">
-        <v>579</v>
       </c>
       <c r="F276" s="1">
         <v>46287</v>
       </c>
       <c r="G276" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.2">
@@ -10381,16 +10429,16 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
+        <v>578</v>
+      </c>
+      <c r="C277" t="s">
+        <v>80</v>
+      </c>
+      <c r="D277" t="s">
+        <v>579</v>
+      </c>
+      <c r="E277" t="s">
         <v>580</v>
-      </c>
-      <c r="C277" t="s">
-        <v>80</v>
-      </c>
-      <c r="D277" t="s">
-        <v>581</v>
-      </c>
-      <c r="E277" t="s">
-        <v>582</v>
       </c>
       <c r="F277" s="1">
         <v>46287</v>
@@ -10404,16 +10452,16 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
+        <v>581</v>
+      </c>
+      <c r="C278" t="s">
+        <v>80</v>
+      </c>
+      <c r="D278" t="s">
+        <v>582</v>
+      </c>
+      <c r="E278" t="s">
         <v>583</v>
-      </c>
-      <c r="C278" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" t="s">
-        <v>584</v>
-      </c>
-      <c r="E278" t="s">
-        <v>585</v>
       </c>
       <c r="F278" s="1">
         <v>46287</v>
@@ -10427,16 +10475,16 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
+        <v>584</v>
+      </c>
+      <c r="C279" t="s">
+        <v>80</v>
+      </c>
+      <c r="D279" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" t="s">
         <v>586</v>
-      </c>
-      <c r="C279" t="s">
-        <v>80</v>
-      </c>
-      <c r="D279" t="s">
-        <v>584</v>
-      </c>
-      <c r="E279" t="s">
-        <v>585</v>
       </c>
       <c r="F279" s="1">
         <v>46287</v>
@@ -10456,10 +10504,10 @@
         <v>80</v>
       </c>
       <c r="D280" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E280" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F280" s="1">
         <v>46287</v>
@@ -10473,19 +10521,19 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
+        <v>588</v>
+      </c>
+      <c r="C281" t="s">
+        <v>80</v>
+      </c>
+      <c r="D281" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" t="s">
         <v>590</v>
       </c>
-      <c r="C281" t="s">
-        <v>2</v>
-      </c>
-      <c r="D281" t="s">
-        <v>87</v>
-      </c>
-      <c r="E281" t="s">
-        <v>88</v>
-      </c>
       <c r="F281" s="1">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="G281" s="1">
         <v>46288</v>
@@ -10499,13 +10547,13 @@
         <v>591</v>
       </c>
       <c r="C282" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D282" t="s">
-        <v>176</v>
+        <v>87</v>
       </c>
       <c r="E282" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="F282" s="1">
         <v>46288</v>
@@ -10525,10 +10573,10 @@
         <v>80</v>
       </c>
       <c r="D283" t="s">
-        <v>593</v>
+        <v>176</v>
       </c>
       <c r="E283" t="s">
-        <v>594</v>
+        <v>177</v>
       </c>
       <c r="F283" s="1">
         <v>46288</v>
@@ -10542,16 +10590,16 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>593</v>
+      </c>
+      <c r="C284" t="s">
+        <v>80</v>
+      </c>
+      <c r="D284" t="s">
+        <v>594</v>
+      </c>
+      <c r="E284" t="s">
         <v>595</v>
-      </c>
-      <c r="C284" t="s">
-        <v>2</v>
-      </c>
-      <c r="D284" t="s">
-        <v>87</v>
-      </c>
-      <c r="E284" t="s">
-        <v>88</v>
       </c>
       <c r="F284" s="1">
         <v>46288</v>
@@ -10568,13 +10616,13 @@
         <v>596</v>
       </c>
       <c r="C285" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D285" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="E285" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F285" s="1">
         <v>46288</v>
@@ -10594,10 +10642,10 @@
         <v>80</v>
       </c>
       <c r="D286" t="s">
-        <v>598</v>
+        <v>37</v>
       </c>
       <c r="E286" t="s">
-        <v>599</v>
+        <v>38</v>
       </c>
       <c r="F286" s="1">
         <v>46288</v>
@@ -10611,16 +10659,16 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
+        <v>598</v>
+      </c>
+      <c r="C287" t="s">
+        <v>80</v>
+      </c>
+      <c r="D287" t="s">
+        <v>599</v>
+      </c>
+      <c r="E287" t="s">
         <v>600</v>
-      </c>
-      <c r="C287" t="s">
-        <v>2</v>
-      </c>
-      <c r="D287" t="s">
-        <v>37</v>
-      </c>
-      <c r="E287" t="s">
-        <v>38</v>
       </c>
       <c r="F287" s="1">
         <v>46288</v>
@@ -10637,19 +10685,19 @@
         <v>601</v>
       </c>
       <c r="C288" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D288" t="s">
-        <v>602</v>
+        <v>37</v>
       </c>
       <c r="E288" t="s">
-        <v>603</v>
+        <v>38</v>
       </c>
       <c r="F288" s="1">
         <v>46288</v>
       </c>
       <c r="G288" s="1">
-        <v>46290</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
@@ -10657,22 +10705,22 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
+        <v>602</v>
+      </c>
+      <c r="C289" t="s">
+        <v>80</v>
+      </c>
+      <c r="D289" t="s">
+        <v>603</v>
+      </c>
+      <c r="E289" t="s">
         <v>604</v>
-      </c>
-      <c r="C289" t="s">
-        <v>80</v>
-      </c>
-      <c r="D289" t="s">
-        <v>605</v>
-      </c>
-      <c r="E289" t="s">
-        <v>606</v>
       </c>
       <c r="F289" s="1">
         <v>46288</v>
       </c>
       <c r="G289" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.2">
@@ -10680,16 +10728,16 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
+        <v>605</v>
+      </c>
+      <c r="C290" t="s">
+        <v>80</v>
+      </c>
+      <c r="D290" t="s">
+        <v>606</v>
+      </c>
+      <c r="E290" t="s">
         <v>607</v>
-      </c>
-      <c r="C290" t="s">
-        <v>80</v>
-      </c>
-      <c r="D290" t="s">
-        <v>16</v>
-      </c>
-      <c r="E290" t="s">
-        <v>17</v>
       </c>
       <c r="F290" s="1">
         <v>46288</v>
@@ -10709,16 +10757,16 @@
         <v>80</v>
       </c>
       <c r="D291" t="s">
-        <v>609</v>
+        <v>16</v>
       </c>
       <c r="E291" t="s">
-        <v>610</v>
+        <v>17</v>
       </c>
       <c r="F291" s="1">
         <v>46288</v>
       </c>
       <c r="G291" s="1">
-        <v>46294</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -10726,22 +10774,22 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
+        <v>609</v>
+      </c>
+      <c r="C292" t="s">
+        <v>80</v>
+      </c>
+      <c r="D292" t="s">
+        <v>610</v>
+      </c>
+      <c r="E292" t="s">
         <v>611</v>
-      </c>
-      <c r="C292" t="s">
-        <v>80</v>
-      </c>
-      <c r="D292" t="s">
-        <v>612</v>
-      </c>
-      <c r="E292" t="s">
-        <v>613</v>
       </c>
       <c r="F292" s="1">
         <v>46288</v>
       </c>
       <c r="G292" s="1">
-        <v>46288</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -10749,16 +10797,16 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
+        <v>612</v>
+      </c>
+      <c r="C293" t="s">
+        <v>80</v>
+      </c>
+      <c r="D293" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" t="s">
         <v>614</v>
-      </c>
-      <c r="C293" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" t="s">
-        <v>615</v>
-      </c>
-      <c r="E293" t="s">
-        <v>616</v>
       </c>
       <c r="F293" s="1">
         <v>46288</v>
@@ -10772,16 +10820,16 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
+        <v>615</v>
+      </c>
+      <c r="C294" t="s">
+        <v>80</v>
+      </c>
+      <c r="D294" t="s">
+        <v>616</v>
+      </c>
+      <c r="E294" t="s">
         <v>617</v>
-      </c>
-      <c r="C294" t="s">
-        <v>80</v>
-      </c>
-      <c r="D294" t="s">
-        <v>618</v>
-      </c>
-      <c r="E294" t="s">
-        <v>619</v>
       </c>
       <c r="F294" s="1">
         <v>46288</v>
@@ -10795,16 +10843,16 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
+        <v>618</v>
+      </c>
+      <c r="C295" t="s">
+        <v>80</v>
+      </c>
+      <c r="D295" t="s">
+        <v>619</v>
+      </c>
+      <c r="E295" t="s">
         <v>620</v>
-      </c>
-      <c r="C295" t="s">
-        <v>80</v>
-      </c>
-      <c r="D295" t="s">
-        <v>618</v>
-      </c>
-      <c r="E295" t="s">
-        <v>619</v>
       </c>
       <c r="F295" s="1">
         <v>46288</v>
@@ -10824,16 +10872,16 @@
         <v>80</v>
       </c>
       <c r="D296" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E296" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F296" s="1">
         <v>46288</v>
       </c>
       <c r="G296" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -10841,22 +10889,22 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
+        <v>622</v>
+      </c>
+      <c r="C297" t="s">
+        <v>80</v>
+      </c>
+      <c r="D297" t="s">
+        <v>623</v>
+      </c>
+      <c r="E297" t="s">
         <v>624</v>
-      </c>
-      <c r="C297" t="s">
-        <v>80</v>
-      </c>
-      <c r="D297" t="s">
-        <v>625</v>
-      </c>
-      <c r="E297" t="s">
-        <v>626</v>
       </c>
       <c r="F297" s="1">
         <v>46288</v>
       </c>
       <c r="G297" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -10864,16 +10912,16 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
+        <v>625</v>
+      </c>
+      <c r="C298" t="s">
+        <v>80</v>
+      </c>
+      <c r="D298" t="s">
+        <v>626</v>
+      </c>
+      <c r="E298" t="s">
         <v>627</v>
-      </c>
-      <c r="C298" t="s">
-        <v>80</v>
-      </c>
-      <c r="D298" t="s">
-        <v>443</v>
-      </c>
-      <c r="E298" t="s">
-        <v>444</v>
       </c>
       <c r="F298" s="1">
         <v>46288</v>
@@ -10893,10 +10941,10 @@
         <v>80</v>
       </c>
       <c r="D299" t="s">
-        <v>629</v>
+        <v>444</v>
       </c>
       <c r="E299" t="s">
-        <v>630</v>
+        <v>445</v>
       </c>
       <c r="F299" s="1">
         <v>46288</v>
@@ -10910,16 +10958,16 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
+        <v>629</v>
+      </c>
+      <c r="C300" t="s">
+        <v>80</v>
+      </c>
+      <c r="D300" t="s">
+        <v>630</v>
+      </c>
+      <c r="E300" t="s">
         <v>631</v>
-      </c>
-      <c r="C300" t="s">
-        <v>80</v>
-      </c>
-      <c r="D300" t="s">
-        <v>629</v>
-      </c>
-      <c r="E300" t="s">
-        <v>630</v>
       </c>
       <c r="F300" s="1">
         <v>46288</v>
@@ -10939,16 +10987,16 @@
         <v>80</v>
       </c>
       <c r="D301" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E301" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F301" s="1">
         <v>46288</v>
       </c>
       <c r="G301" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
@@ -10962,16 +11010,16 @@
         <v>80</v>
       </c>
       <c r="D302" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E302" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="F302" s="1">
         <v>46288</v>
       </c>
       <c r="G302" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -10979,16 +11027,16 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
+        <v>634</v>
+      </c>
+      <c r="C303" t="s">
+        <v>80</v>
+      </c>
+      <c r="D303" t="s">
+        <v>635</v>
+      </c>
+      <c r="E303" t="s">
         <v>636</v>
-      </c>
-      <c r="C303" t="s">
-        <v>80</v>
-      </c>
-      <c r="D303" t="s">
-        <v>98</v>
-      </c>
-      <c r="E303" t="s">
-        <v>99</v>
       </c>
       <c r="F303" s="1">
         <v>46288</v>
@@ -11008,10 +11056,10 @@
         <v>80</v>
       </c>
       <c r="D304" t="s">
-        <v>638</v>
+        <v>98</v>
       </c>
       <c r="E304" t="s">
-        <v>639</v>
+        <v>99</v>
       </c>
       <c r="F304" s="1">
         <v>46288</v>
@@ -11025,22 +11073,22 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
+        <v>638</v>
+      </c>
+      <c r="C305" t="s">
+        <v>80</v>
+      </c>
+      <c r="D305" t="s">
+        <v>639</v>
+      </c>
+      <c r="E305" t="s">
         <v>640</v>
-      </c>
-      <c r="C305" t="s">
-        <v>2</v>
-      </c>
-      <c r="D305" t="s">
-        <v>223</v>
-      </c>
-      <c r="E305" t="s">
-        <v>224</v>
       </c>
       <c r="F305" s="1">
         <v>46288</v>
       </c>
       <c r="G305" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -11051,19 +11099,19 @@
         <v>641</v>
       </c>
       <c r="C306" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D306" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="E306" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="F306" s="1">
         <v>46288</v>
       </c>
       <c r="G306" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -11077,16 +11125,16 @@
         <v>80</v>
       </c>
       <c r="D307" t="s">
-        <v>643</v>
+        <v>278</v>
       </c>
       <c r="E307" t="s">
-        <v>644</v>
+        <v>279</v>
       </c>
       <c r="F307" s="1">
         <v>46288</v>
       </c>
       <c r="G307" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
@@ -11094,22 +11142,22 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
+        <v>643</v>
+      </c>
+      <c r="C308" t="s">
+        <v>80</v>
+      </c>
+      <c r="D308" t="s">
+        <v>644</v>
+      </c>
+      <c r="E308" t="s">
         <v>645</v>
-      </c>
-      <c r="C308" t="s">
-        <v>80</v>
-      </c>
-      <c r="D308" t="s">
-        <v>93</v>
-      </c>
-      <c r="E308" t="s">
-        <v>94</v>
       </c>
       <c r="F308" s="1">
         <v>46288</v>
       </c>
       <c r="G308" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -11123,16 +11171,16 @@
         <v>80</v>
       </c>
       <c r="D309" t="s">
-        <v>605</v>
+        <v>93</v>
       </c>
       <c r="E309" t="s">
-        <v>606</v>
+        <v>94</v>
       </c>
       <c r="F309" s="1">
         <v>46288</v>
       </c>
       <c r="G309" s="1">
-        <v>46288</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
@@ -11146,10 +11194,10 @@
         <v>80</v>
       </c>
       <c r="D310" t="s">
-        <v>506</v>
+        <v>606</v>
       </c>
       <c r="E310" t="s">
-        <v>507</v>
+        <v>607</v>
       </c>
       <c r="F310" s="1">
         <v>46288</v>
@@ -11169,10 +11217,10 @@
         <v>80</v>
       </c>
       <c r="D311" t="s">
-        <v>649</v>
+        <v>507</v>
       </c>
       <c r="E311" t="s">
-        <v>650</v>
+        <v>508</v>
       </c>
       <c r="F311" s="1">
         <v>46288</v>
@@ -11186,16 +11234,16 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
+        <v>649</v>
+      </c>
+      <c r="C312" t="s">
+        <v>80</v>
+      </c>
+      <c r="D312" t="s">
+        <v>650</v>
+      </c>
+      <c r="E312" t="s">
         <v>651</v>
-      </c>
-      <c r="C312" t="s">
-        <v>80</v>
-      </c>
-      <c r="D312" t="s">
-        <v>652</v>
-      </c>
-      <c r="E312" t="s">
-        <v>653</v>
       </c>
       <c r="F312" s="1">
         <v>46288</v>
@@ -11209,16 +11257,16 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
+        <v>652</v>
+      </c>
+      <c r="C313" t="s">
+        <v>80</v>
+      </c>
+      <c r="D313" t="s">
+        <v>653</v>
+      </c>
+      <c r="E313" t="s">
         <v>654</v>
-      </c>
-      <c r="C313" t="s">
-        <v>80</v>
-      </c>
-      <c r="D313" t="s">
-        <v>655</v>
-      </c>
-      <c r="E313" t="s">
-        <v>656</v>
       </c>
       <c r="F313" s="1">
         <v>46288</v>
@@ -11232,16 +11280,16 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
+        <v>655</v>
+      </c>
+      <c r="C314" t="s">
+        <v>80</v>
+      </c>
+      <c r="D314" t="s">
+        <v>656</v>
+      </c>
+      <c r="E314" t="s">
         <v>657</v>
-      </c>
-      <c r="C314" t="s">
-        <v>80</v>
-      </c>
-      <c r="D314" t="s">
-        <v>655</v>
-      </c>
-      <c r="E314" t="s">
-        <v>656</v>
       </c>
       <c r="F314" s="1">
         <v>46288</v>
@@ -11261,10 +11309,10 @@
         <v>80</v>
       </c>
       <c r="D315" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="E315" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="F315" s="1">
         <v>46288</v>
@@ -11284,16 +11332,16 @@
         <v>80</v>
       </c>
       <c r="D316" t="s">
-        <v>140</v>
+        <v>650</v>
       </c>
       <c r="E316" t="s">
-        <v>141</v>
+        <v>651</v>
       </c>
       <c r="F316" s="1">
         <v>46288</v>
       </c>
       <c r="G316" s="1">
-        <v>46290</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -11307,16 +11355,16 @@
         <v>80</v>
       </c>
       <c r="D317" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="E317" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="F317" s="1">
         <v>46288</v>
       </c>
       <c r="G317" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -11330,10 +11378,10 @@
         <v>80</v>
       </c>
       <c r="D318" t="s">
-        <v>662</v>
+        <v>16</v>
       </c>
       <c r="E318" t="s">
-        <v>663</v>
+        <v>17</v>
       </c>
       <c r="F318" s="1">
         <v>46288</v>
@@ -11347,16 +11395,16 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
+        <v>662</v>
+      </c>
+      <c r="C319" t="s">
+        <v>80</v>
+      </c>
+      <c r="D319" t="s">
+        <v>663</v>
+      </c>
+      <c r="E319" t="s">
         <v>664</v>
-      </c>
-      <c r="C319" t="s">
-        <v>80</v>
-      </c>
-      <c r="D319" t="s">
-        <v>665</v>
-      </c>
-      <c r="E319" t="s">
-        <v>666</v>
       </c>
       <c r="F319" s="1">
         <v>46288</v>
@@ -11370,16 +11418,16 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>665</v>
+      </c>
+      <c r="C320" t="s">
+        <v>80</v>
+      </c>
+      <c r="D320" t="s">
+        <v>666</v>
+      </c>
+      <c r="E320" t="s">
         <v>667</v>
-      </c>
-      <c r="C320" t="s">
-        <v>80</v>
-      </c>
-      <c r="D320" t="s">
-        <v>37</v>
-      </c>
-      <c r="E320" t="s">
-        <v>38</v>
       </c>
       <c r="F320" s="1">
         <v>46288</v>
@@ -11537,16 +11585,16 @@
         <v>80</v>
       </c>
       <c r="D327" t="s">
-        <v>523</v>
+        <v>37</v>
       </c>
       <c r="E327" t="s">
-        <v>524</v>
+        <v>38</v>
       </c>
       <c r="F327" s="1">
         <v>46288</v>
       </c>
       <c r="G327" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -11560,16 +11608,16 @@
         <v>80</v>
       </c>
       <c r="D328" t="s">
-        <v>37</v>
+        <v>524</v>
       </c>
       <c r="E328" t="s">
-        <v>38</v>
+        <v>525</v>
       </c>
       <c r="F328" s="1">
         <v>46288</v>
       </c>
       <c r="G328" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -11583,16 +11631,16 @@
         <v>80</v>
       </c>
       <c r="D329" t="s">
-        <v>638</v>
+        <v>37</v>
       </c>
       <c r="E329" t="s">
-        <v>639</v>
+        <v>38</v>
       </c>
       <c r="F329" s="1">
         <v>46288</v>
       </c>
       <c r="G329" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
@@ -11606,10 +11654,10 @@
         <v>80</v>
       </c>
       <c r="D330" t="s">
-        <v>258</v>
+        <v>639</v>
       </c>
       <c r="E330" t="s">
-        <v>259</v>
+        <v>640</v>
       </c>
       <c r="F330" s="1">
         <v>46288</v>
@@ -11629,16 +11677,16 @@
         <v>80</v>
       </c>
       <c r="D331" t="s">
-        <v>679</v>
+        <v>258</v>
       </c>
       <c r="E331" t="s">
-        <v>680</v>
+        <v>259</v>
       </c>
       <c r="F331" s="1">
         <v>46288</v>
       </c>
       <c r="G331" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
@@ -11646,19 +11694,19 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
+        <v>679</v>
+      </c>
+      <c r="C332" t="s">
+        <v>80</v>
+      </c>
+      <c r="D332" t="s">
+        <v>680</v>
+      </c>
+      <c r="E332" t="s">
         <v>681</v>
       </c>
-      <c r="C332" t="s">
-        <v>80</v>
-      </c>
-      <c r="D332" t="s">
-        <v>682</v>
-      </c>
-      <c r="E332" t="s">
-        <v>683</v>
-      </c>
       <c r="F332" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="G332" s="1">
         <v>46294</v>
@@ -11669,22 +11717,22 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
+        <v>682</v>
+      </c>
+      <c r="C333" t="s">
+        <v>80</v>
+      </c>
+      <c r="D333" t="s">
+        <v>683</v>
+      </c>
+      <c r="E333" t="s">
         <v>684</v>
-      </c>
-      <c r="C333" t="s">
-        <v>80</v>
-      </c>
-      <c r="D333" t="s">
-        <v>685</v>
-      </c>
-      <c r="E333" t="s">
-        <v>686</v>
       </c>
       <c r="F333" s="1">
         <v>46289</v>
       </c>
       <c r="G333" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -11692,22 +11740,22 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
+        <v>685</v>
+      </c>
+      <c r="C334" t="s">
+        <v>80</v>
+      </c>
+      <c r="D334" t="s">
+        <v>686</v>
+      </c>
+      <c r="E334" t="s">
         <v>687</v>
-      </c>
-      <c r="C334" t="s">
-        <v>80</v>
-      </c>
-      <c r="D334" t="s">
-        <v>688</v>
-      </c>
-      <c r="E334" t="s">
-        <v>689</v>
       </c>
       <c r="F334" s="1">
         <v>46289</v>
       </c>
       <c r="G334" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -11715,16 +11763,16 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
+        <v>688</v>
+      </c>
+      <c r="C335" t="s">
+        <v>80</v>
+      </c>
+      <c r="D335" t="s">
+        <v>689</v>
+      </c>
+      <c r="E335" t="s">
         <v>690</v>
-      </c>
-      <c r="C335" t="s">
-        <v>80</v>
-      </c>
-      <c r="D335" t="s">
-        <v>691</v>
-      </c>
-      <c r="E335" t="s">
-        <v>692</v>
       </c>
       <c r="F335" s="1">
         <v>46289</v>
@@ -11738,16 +11786,16 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
+        <v>691</v>
+      </c>
+      <c r="C336" t="s">
+        <v>80</v>
+      </c>
+      <c r="D336" t="s">
+        <v>692</v>
+      </c>
+      <c r="E336" t="s">
         <v>693</v>
-      </c>
-      <c r="C336" t="s">
-        <v>80</v>
-      </c>
-      <c r="D336" t="s">
-        <v>694</v>
-      </c>
-      <c r="E336" t="s">
-        <v>695</v>
       </c>
       <c r="F336" s="1">
         <v>46289</v>
@@ -11761,16 +11809,16 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
+        <v>694</v>
+      </c>
+      <c r="C337" t="s">
+        <v>80</v>
+      </c>
+      <c r="D337" t="s">
+        <v>695</v>
+      </c>
+      <c r="E337" t="s">
         <v>696</v>
-      </c>
-      <c r="C337" t="s">
-        <v>80</v>
-      </c>
-      <c r="D337" t="s">
-        <v>561</v>
-      </c>
-      <c r="E337" t="s">
-        <v>562</v>
       </c>
       <c r="F337" s="1">
         <v>46289</v>
@@ -11790,10 +11838,10 @@
         <v>80</v>
       </c>
       <c r="D338" t="s">
-        <v>698</v>
+        <v>562</v>
       </c>
       <c r="E338" t="s">
-        <v>699</v>
+        <v>563</v>
       </c>
       <c r="F338" s="1">
         <v>46289</v>
@@ -11807,16 +11855,16 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
+        <v>698</v>
+      </c>
+      <c r="C339" t="s">
+        <v>80</v>
+      </c>
+      <c r="D339" t="s">
+        <v>699</v>
+      </c>
+      <c r="E339" t="s">
         <v>700</v>
-      </c>
-      <c r="C339" t="s">
-        <v>80</v>
-      </c>
-      <c r="D339" t="s">
-        <v>701</v>
-      </c>
-      <c r="E339" t="s">
-        <v>702</v>
       </c>
       <c r="F339" s="1">
         <v>46289</v>
@@ -11830,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
+        <v>701</v>
+      </c>
+      <c r="C340" t="s">
+        <v>2</v>
+      </c>
+      <c r="D340" t="s">
+        <v>702</v>
+      </c>
+      <c r="E340" t="s">
         <v>703</v>
-      </c>
-      <c r="C340" t="s">
-        <v>80</v>
-      </c>
-      <c r="D340" t="s">
-        <v>701</v>
-      </c>
-      <c r="E340" t="s">
-        <v>702</v>
       </c>
       <c r="F340" s="1">
         <v>46289</v>
@@ -11856,19 +11904,19 @@
         <v>704</v>
       </c>
       <c r="C341" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D341" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E341" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F341" s="1">
         <v>46289</v>
       </c>
       <c r="G341" s="1">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -11876,22 +11924,22 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
+        <v>705</v>
+      </c>
+      <c r="C342" t="s">
+        <v>80</v>
+      </c>
+      <c r="D342" t="s">
+        <v>706</v>
+      </c>
+      <c r="E342" t="s">
         <v>707</v>
-      </c>
-      <c r="C342" t="s">
-        <v>80</v>
-      </c>
-      <c r="D342" t="s">
-        <v>41</v>
-      </c>
-      <c r="E342" t="s">
-        <v>42</v>
       </c>
       <c r="F342" s="1">
         <v>46289</v>
       </c>
       <c r="G342" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -11905,10 +11953,10 @@
         <v>80</v>
       </c>
       <c r="D343" t="s">
-        <v>709</v>
+        <v>41</v>
       </c>
       <c r="E343" t="s">
-        <v>710</v>
+        <v>42</v>
       </c>
       <c r="F343" s="1">
         <v>46289</v>
@@ -11922,22 +11970,22 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
+        <v>709</v>
+      </c>
+      <c r="C344" t="s">
+        <v>80</v>
+      </c>
+      <c r="D344" t="s">
+        <v>710</v>
+      </c>
+      <c r="E344" t="s">
         <v>711</v>
-      </c>
-      <c r="C344" t="s">
-        <v>80</v>
-      </c>
-      <c r="D344" t="s">
-        <v>712</v>
-      </c>
-      <c r="E344" t="s">
-        <v>713</v>
       </c>
       <c r="F344" s="1">
         <v>46289</v>
       </c>
       <c r="G344" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
@@ -11945,22 +11993,22 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
+        <v>712</v>
+      </c>
+      <c r="C345" t="s">
+        <v>80</v>
+      </c>
+      <c r="D345" t="s">
+        <v>713</v>
+      </c>
+      <c r="E345" t="s">
         <v>714</v>
-      </c>
-      <c r="C345" t="s">
-        <v>80</v>
-      </c>
-      <c r="D345" t="s">
-        <v>182</v>
-      </c>
-      <c r="E345" t="s">
-        <v>183</v>
       </c>
       <c r="F345" s="1">
         <v>46289</v>
       </c>
       <c r="G345" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
@@ -11974,10 +12022,10 @@
         <v>80</v>
       </c>
       <c r="D346" t="s">
-        <v>615</v>
+        <v>182</v>
       </c>
       <c r="E346" t="s">
-        <v>616</v>
+        <v>183</v>
       </c>
       <c r="F346" s="1">
         <v>46289</v>
@@ -11997,10 +12045,10 @@
         <v>80</v>
       </c>
       <c r="D347" t="s">
-        <v>717</v>
+        <v>616</v>
       </c>
       <c r="E347" t="s">
-        <v>718</v>
+        <v>617</v>
       </c>
       <c r="F347" s="1">
         <v>46289</v>
@@ -12014,16 +12062,16 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
+        <v>717</v>
+      </c>
+      <c r="C348" t="s">
+        <v>80</v>
+      </c>
+      <c r="D348" t="s">
+        <v>718</v>
+      </c>
+      <c r="E348" t="s">
         <v>719</v>
-      </c>
-      <c r="C348" t="s">
-        <v>80</v>
-      </c>
-      <c r="D348" t="s">
-        <v>720</v>
-      </c>
-      <c r="E348" t="s">
-        <v>721</v>
       </c>
       <c r="F348" s="1">
         <v>46289</v>
@@ -12037,16 +12085,16 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
+        <v>720</v>
+      </c>
+      <c r="C349" t="s">
+        <v>80</v>
+      </c>
+      <c r="D349" t="s">
+        <v>721</v>
+      </c>
+      <c r="E349" t="s">
         <v>722</v>
-      </c>
-      <c r="C349" t="s">
-        <v>80</v>
-      </c>
-      <c r="D349" t="s">
-        <v>723</v>
-      </c>
-      <c r="E349" t="s">
-        <v>724</v>
       </c>
       <c r="F349" s="1">
         <v>46289</v>
@@ -12060,16 +12108,16 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
+        <v>723</v>
+      </c>
+      <c r="C350" t="s">
+        <v>80</v>
+      </c>
+      <c r="D350" t="s">
+        <v>724</v>
+      </c>
+      <c r="E350" t="s">
         <v>725</v>
-      </c>
-      <c r="C350" t="s">
-        <v>80</v>
-      </c>
-      <c r="D350" t="s">
-        <v>323</v>
-      </c>
-      <c r="E350" t="s">
-        <v>324</v>
       </c>
       <c r="F350" s="1">
         <v>46289</v>
@@ -12089,10 +12137,10 @@
         <v>80</v>
       </c>
       <c r="D351" t="s">
-        <v>727</v>
+        <v>323</v>
       </c>
       <c r="E351" t="s">
-        <v>728</v>
+        <v>324</v>
       </c>
       <c r="F351" s="1">
         <v>46289</v>
@@ -12106,16 +12154,16 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
+        <v>727</v>
+      </c>
+      <c r="C352" t="s">
+        <v>80</v>
+      </c>
+      <c r="D352" t="s">
+        <v>728</v>
+      </c>
+      <c r="E352" t="s">
         <v>729</v>
-      </c>
-      <c r="C352" t="s">
-        <v>80</v>
-      </c>
-      <c r="D352" t="s">
-        <v>267</v>
-      </c>
-      <c r="E352" t="s">
-        <v>268</v>
       </c>
       <c r="F352" s="1">
         <v>46289</v>
@@ -12135,10 +12183,10 @@
         <v>80</v>
       </c>
       <c r="D353" t="s">
-        <v>731</v>
+        <v>267</v>
       </c>
       <c r="E353" t="s">
-        <v>732</v>
+        <v>268</v>
       </c>
       <c r="F353" s="1">
         <v>46289</v>
@@ -12152,16 +12200,16 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
+        <v>731</v>
+      </c>
+      <c r="C354" t="s">
+        <v>80</v>
+      </c>
+      <c r="D354" t="s">
+        <v>732</v>
+      </c>
+      <c r="E354" t="s">
         <v>733</v>
-      </c>
-      <c r="C354" t="s">
-        <v>80</v>
-      </c>
-      <c r="D354" t="s">
-        <v>41</v>
-      </c>
-      <c r="E354" t="s">
-        <v>42</v>
       </c>
       <c r="F354" s="1">
         <v>46289</v>
@@ -12181,10 +12229,10 @@
         <v>80</v>
       </c>
       <c r="D355" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E355" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F355" s="1">
         <v>46289</v>
@@ -12204,10 +12252,10 @@
         <v>80</v>
       </c>
       <c r="D356" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E356" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F356" s="1">
         <v>46289</v>
@@ -12227,16 +12275,16 @@
         <v>80</v>
       </c>
       <c r="D357" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="E357" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="F357" s="1">
         <v>46289</v>
       </c>
       <c r="G357" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
@@ -12250,16 +12298,16 @@
         <v>80</v>
       </c>
       <c r="D358" t="s">
-        <v>738</v>
+        <v>192</v>
       </c>
       <c r="E358" t="s">
-        <v>739</v>
+        <v>193</v>
       </c>
       <c r="F358" s="1">
         <v>46289</v>
       </c>
       <c r="G358" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
@@ -12267,16 +12315,16 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
+        <v>738</v>
+      </c>
+      <c r="C359" t="s">
+        <v>80</v>
+      </c>
+      <c r="D359" t="s">
+        <v>739</v>
+      </c>
+      <c r="E359" t="s">
         <v>740</v>
-      </c>
-      <c r="C359" t="s">
-        <v>80</v>
-      </c>
-      <c r="D359" t="s">
-        <v>738</v>
-      </c>
-      <c r="E359" t="s">
-        <v>739</v>
       </c>
       <c r="F359" s="1">
         <v>46289</v>
@@ -12296,10 +12344,10 @@
         <v>80</v>
       </c>
       <c r="D360" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E360" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F360" s="1">
         <v>46289</v>
@@ -12319,10 +12367,10 @@
         <v>80</v>
       </c>
       <c r="D361" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="E361" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="F361" s="1">
         <v>46289</v>
@@ -12336,16 +12384,16 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
+        <v>743</v>
+      </c>
+      <c r="C362" t="s">
+        <v>80</v>
+      </c>
+      <c r="D362" t="s">
+        <v>744</v>
+      </c>
+      <c r="E362" t="s">
         <v>745</v>
-      </c>
-      <c r="C362" t="s">
-        <v>80</v>
-      </c>
-      <c r="D362" t="s">
-        <v>239</v>
-      </c>
-      <c r="E362" t="s">
-        <v>240</v>
       </c>
       <c r="F362" s="1">
         <v>46289</v>
@@ -12388,10 +12436,10 @@
         <v>80</v>
       </c>
       <c r="D364" t="s">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="E364" t="s">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="F364" s="1">
         <v>46289</v>
@@ -12411,10 +12459,10 @@
         <v>80</v>
       </c>
       <c r="D365" t="s">
-        <v>749</v>
+        <v>313</v>
       </c>
       <c r="E365" t="s">
-        <v>750</v>
+        <v>314</v>
       </c>
       <c r="F365" s="1">
         <v>46289</v>
@@ -12428,16 +12476,16 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
+        <v>749</v>
+      </c>
+      <c r="C366" t="s">
+        <v>80</v>
+      </c>
+      <c r="D366" t="s">
+        <v>750</v>
+      </c>
+      <c r="E366" t="s">
         <v>751</v>
-      </c>
-      <c r="C366" t="s">
-        <v>80</v>
-      </c>
-      <c r="D366" t="s">
-        <v>143</v>
-      </c>
-      <c r="E366" t="s">
-        <v>144</v>
       </c>
       <c r="F366" s="1">
         <v>46289</v>
@@ -12457,10 +12505,10 @@
         <v>80</v>
       </c>
       <c r="D367" t="s">
-        <v>561</v>
+        <v>143</v>
       </c>
       <c r="E367" t="s">
-        <v>562</v>
+        <v>144</v>
       </c>
       <c r="F367" s="1">
         <v>46289</v>
@@ -12480,16 +12528,16 @@
         <v>80</v>
       </c>
       <c r="D368" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="E368" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="F368" s="1">
         <v>46289</v>
       </c>
       <c r="G368" s="1">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.2">
@@ -12503,10 +12551,10 @@
         <v>80</v>
       </c>
       <c r="D369" t="s">
-        <v>421</v>
+        <v>585</v>
       </c>
       <c r="E369" t="s">
-        <v>422</v>
+        <v>586</v>
       </c>
       <c r="F369" s="1">
         <v>46289</v>
@@ -12526,10 +12574,10 @@
         <v>80</v>
       </c>
       <c r="D370" t="s">
-        <v>303</v>
+        <v>422</v>
       </c>
       <c r="E370" t="s">
-        <v>304</v>
+        <v>423</v>
       </c>
       <c r="F370" s="1">
         <v>46289</v>
@@ -12546,7 +12594,7 @@
         <v>756</v>
       </c>
       <c r="C371" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D371" t="s">
         <v>303</v>
@@ -12569,19 +12617,19 @@
         <v>757</v>
       </c>
       <c r="C372" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D372" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="E372" t="s">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="F372" s="1">
         <v>46289</v>
       </c>
       <c r="G372" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
@@ -12595,16 +12643,16 @@
         <v>80</v>
       </c>
       <c r="D373" t="s">
-        <v>759</v>
+        <v>77</v>
       </c>
       <c r="E373" t="s">
-        <v>760</v>
+        <v>78</v>
       </c>
       <c r="F373" s="1">
         <v>46289</v>
       </c>
       <c r="G373" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.2">
@@ -12612,16 +12660,16 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
+        <v>759</v>
+      </c>
+      <c r="C374" t="s">
+        <v>80</v>
+      </c>
+      <c r="D374" t="s">
+        <v>760</v>
+      </c>
+      <c r="E374" t="s">
         <v>761</v>
-      </c>
-      <c r="C374" t="s">
-        <v>80</v>
-      </c>
-      <c r="D374" t="s">
-        <v>762</v>
-      </c>
-      <c r="E374" t="s">
-        <v>763</v>
       </c>
       <c r="F374" s="1">
         <v>46289</v>
@@ -12635,16 +12683,16 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
+        <v>762</v>
+      </c>
+      <c r="C375" t="s">
+        <v>80</v>
+      </c>
+      <c r="D375" t="s">
+        <v>763</v>
+      </c>
+      <c r="E375" t="s">
         <v>764</v>
-      </c>
-      <c r="C375" t="s">
-        <v>80</v>
-      </c>
-      <c r="D375" t="s">
-        <v>765</v>
-      </c>
-      <c r="E375" t="s">
-        <v>766</v>
       </c>
       <c r="F375" s="1">
         <v>46289</v>
@@ -12658,22 +12706,22 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
+        <v>765</v>
+      </c>
+      <c r="C376" t="s">
+        <v>96</v>
+      </c>
+      <c r="D376" t="s">
+        <v>766</v>
+      </c>
+      <c r="E376" t="s">
         <v>767</v>
-      </c>
-      <c r="C376" t="s">
-        <v>80</v>
-      </c>
-      <c r="D376" t="s">
-        <v>768</v>
-      </c>
-      <c r="E376" t="s">
-        <v>769</v>
       </c>
       <c r="F376" s="1">
         <v>46289</v>
       </c>
       <c r="G376" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.2">
@@ -12681,19 +12729,19 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
+        <v>768</v>
+      </c>
+      <c r="C377" t="s">
+        <v>80</v>
+      </c>
+      <c r="D377" t="s">
+        <v>769</v>
+      </c>
+      <c r="E377" t="s">
         <v>770</v>
       </c>
-      <c r="C377" t="s">
-        <v>80</v>
-      </c>
-      <c r="D377" t="s">
-        <v>771</v>
-      </c>
-      <c r="E377" t="s">
-        <v>772</v>
-      </c>
       <c r="F377" s="1">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="G377" s="1">
         <v>46294</v>
@@ -12704,22 +12752,22 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
+        <v>771</v>
+      </c>
+      <c r="C378" t="s">
+        <v>80</v>
+      </c>
+      <c r="D378" t="s">
+        <v>772</v>
+      </c>
+      <c r="E378" t="s">
         <v>773</v>
-      </c>
-      <c r="C378" t="s">
-        <v>80</v>
-      </c>
-      <c r="D378" t="s">
-        <v>774</v>
-      </c>
-      <c r="E378" t="s">
-        <v>775</v>
       </c>
       <c r="F378" s="1">
         <v>46290</v>
       </c>
       <c r="G378" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.2">
@@ -12727,16 +12775,16 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
+        <v>774</v>
+      </c>
+      <c r="C379" t="s">
+        <v>80</v>
+      </c>
+      <c r="D379" t="s">
+        <v>775</v>
+      </c>
+      <c r="E379" t="s">
         <v>776</v>
-      </c>
-      <c r="C379" t="s">
-        <v>80</v>
-      </c>
-      <c r="D379" t="s">
-        <v>37</v>
-      </c>
-      <c r="E379" t="s">
-        <v>38</v>
       </c>
       <c r="F379" s="1">
         <v>46290</v>
@@ -12779,16 +12827,16 @@
         <v>80</v>
       </c>
       <c r="D381" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E381" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="F381" s="1">
         <v>46290</v>
       </c>
       <c r="G381" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.2">
@@ -12802,16 +12850,16 @@
         <v>80</v>
       </c>
       <c r="D382" t="s">
-        <v>780</v>
+        <v>77</v>
       </c>
       <c r="E382" t="s">
-        <v>781</v>
+        <v>78</v>
       </c>
       <c r="F382" s="1">
         <v>46290</v>
       </c>
       <c r="G382" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.2">
@@ -12819,16 +12867,16 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
+        <v>780</v>
+      </c>
+      <c r="C383" t="s">
+        <v>80</v>
+      </c>
+      <c r="D383" t="s">
+        <v>781</v>
+      </c>
+      <c r="E383" t="s">
         <v>782</v>
-      </c>
-      <c r="C383" t="s">
-        <v>80</v>
-      </c>
-      <c r="D383" t="s">
-        <v>605</v>
-      </c>
-      <c r="E383" t="s">
-        <v>606</v>
       </c>
       <c r="F383" s="1">
         <v>46290</v>
@@ -12848,16 +12896,16 @@
         <v>80</v>
       </c>
       <c r="D384" t="s">
-        <v>77</v>
+        <v>606</v>
       </c>
       <c r="E384" t="s">
-        <v>78</v>
+        <v>607</v>
       </c>
       <c r="F384" s="1">
         <v>46290</v>
       </c>
       <c r="G384" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.2">
@@ -12871,16 +12919,16 @@
         <v>80</v>
       </c>
       <c r="D385" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E385" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="F385" s="1">
         <v>46290</v>
       </c>
       <c r="G385" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.2">
@@ -12917,10 +12965,10 @@
         <v>80</v>
       </c>
       <c r="D387" t="s">
-        <v>787</v>
+        <v>37</v>
       </c>
       <c r="E387" t="s">
-        <v>788</v>
+        <v>38</v>
       </c>
       <c r="F387" s="1">
         <v>46290</v>
@@ -12934,16 +12982,16 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
+        <v>787</v>
+      </c>
+      <c r="C388" t="s">
+        <v>80</v>
+      </c>
+      <c r="D388" t="s">
+        <v>788</v>
+      </c>
+      <c r="E388" t="s">
         <v>789</v>
-      </c>
-      <c r="C388" t="s">
-        <v>80</v>
-      </c>
-      <c r="D388" t="s">
-        <v>48</v>
-      </c>
-      <c r="E388" t="s">
-        <v>49</v>
       </c>
       <c r="F388" s="1">
         <v>46290</v>
@@ -12963,10 +13011,10 @@
         <v>80</v>
       </c>
       <c r="D389" t="s">
-        <v>791</v>
+        <v>48</v>
       </c>
       <c r="E389" t="s">
-        <v>792</v>
+        <v>49</v>
       </c>
       <c r="F389" s="1">
         <v>46290</v>
@@ -12980,16 +13028,16 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
+        <v>791</v>
+      </c>
+      <c r="C390" t="s">
+        <v>80</v>
+      </c>
+      <c r="D390" t="s">
+        <v>792</v>
+      </c>
+      <c r="E390" t="s">
         <v>793</v>
-      </c>
-      <c r="C390" t="s">
-        <v>80</v>
-      </c>
-      <c r="D390" t="s">
-        <v>794</v>
-      </c>
-      <c r="E390" t="s">
-        <v>795</v>
       </c>
       <c r="F390" s="1">
         <v>46290</v>
@@ -13003,16 +13051,16 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
+        <v>794</v>
+      </c>
+      <c r="C391" t="s">
+        <v>80</v>
+      </c>
+      <c r="D391" t="s">
+        <v>795</v>
+      </c>
+      <c r="E391" t="s">
         <v>796</v>
-      </c>
-      <c r="C391" t="s">
-        <v>80</v>
-      </c>
-      <c r="D391" t="s">
-        <v>643</v>
-      </c>
-      <c r="E391" t="s">
-        <v>644</v>
       </c>
       <c r="F391" s="1">
         <v>46290</v>
@@ -13032,10 +13080,10 @@
         <v>80</v>
       </c>
       <c r="D392" t="s">
-        <v>514</v>
+        <v>644</v>
       </c>
       <c r="E392" t="s">
-        <v>515</v>
+        <v>645</v>
       </c>
       <c r="F392" s="1">
         <v>46290</v>
@@ -13055,10 +13103,10 @@
         <v>80</v>
       </c>
       <c r="D393" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="E393" t="s">
-        <v>144</v>
+        <v>516</v>
       </c>
       <c r="F393" s="1">
         <v>46290</v>
@@ -13078,10 +13126,10 @@
         <v>80</v>
       </c>
       <c r="D394" t="s">
-        <v>612</v>
+        <v>143</v>
       </c>
       <c r="E394" t="s">
-        <v>613</v>
+        <v>144</v>
       </c>
       <c r="F394" s="1">
         <v>46290</v>
@@ -13101,10 +13149,10 @@
         <v>80</v>
       </c>
       <c r="D395" t="s">
-        <v>307</v>
+        <v>613</v>
       </c>
       <c r="E395" t="s">
-        <v>308</v>
+        <v>614</v>
       </c>
       <c r="F395" s="1">
         <v>46290</v>
@@ -13121,13 +13169,13 @@
         <v>801</v>
       </c>
       <c r="C396" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D396" t="s">
-        <v>93</v>
+        <v>307</v>
       </c>
       <c r="E396" t="s">
-        <v>94</v>
+        <v>308</v>
       </c>
       <c r="F396" s="1">
         <v>46290</v>
@@ -13147,10 +13195,10 @@
         <v>80</v>
       </c>
       <c r="D397" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E397" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F397" s="1">
         <v>46290</v>
@@ -13170,16 +13218,16 @@
         <v>80</v>
       </c>
       <c r="D398" t="s">
-        <v>804</v>
+        <v>48</v>
       </c>
       <c r="E398" t="s">
-        <v>805</v>
+        <v>49</v>
       </c>
       <c r="F398" s="1">
         <v>46290</v>
       </c>
       <c r="G398" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.2">
@@ -13187,22 +13235,22 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
+        <v>804</v>
+      </c>
+      <c r="C399" t="s">
+        <v>80</v>
+      </c>
+      <c r="D399" t="s">
+        <v>805</v>
+      </c>
+      <c r="E399" t="s">
         <v>806</v>
-      </c>
-      <c r="C399" t="s">
-        <v>80</v>
-      </c>
-      <c r="D399" t="s">
-        <v>807</v>
-      </c>
-      <c r="E399" t="s">
-        <v>808</v>
       </c>
       <c r="F399" s="1">
         <v>46290</v>
       </c>
       <c r="G399" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.2">
@@ -13210,16 +13258,16 @@
         <v>0</v>
       </c>
       <c r="B400" t="s">
+        <v>807</v>
+      </c>
+      <c r="C400" t="s">
+        <v>80</v>
+      </c>
+      <c r="D400" t="s">
+        <v>808</v>
+      </c>
+      <c r="E400" t="s">
         <v>809</v>
-      </c>
-      <c r="C400" t="s">
-        <v>80</v>
-      </c>
-      <c r="D400" t="s">
-        <v>810</v>
-      </c>
-      <c r="E400" t="s">
-        <v>811</v>
       </c>
       <c r="F400" s="1">
         <v>46290</v>
@@ -13233,22 +13281,22 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
+        <v>810</v>
+      </c>
+      <c r="C401" t="s">
+        <v>80</v>
+      </c>
+      <c r="D401" t="s">
+        <v>811</v>
+      </c>
+      <c r="E401" t="s">
         <v>812</v>
-      </c>
-      <c r="C401" t="s">
-        <v>80</v>
-      </c>
-      <c r="D401" t="s">
-        <v>813</v>
-      </c>
-      <c r="E401" t="s">
-        <v>814</v>
       </c>
       <c r="F401" s="1">
         <v>46290</v>
       </c>
       <c r="G401" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
@@ -13256,22 +13304,22 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
+        <v>813</v>
+      </c>
+      <c r="C402" t="s">
+        <v>80</v>
+      </c>
+      <c r="D402" t="s">
+        <v>814</v>
+      </c>
+      <c r="E402" t="s">
         <v>815</v>
-      </c>
-      <c r="C402" t="s">
-        <v>2</v>
-      </c>
-      <c r="D402" t="s">
-        <v>77</v>
-      </c>
-      <c r="E402" t="s">
-        <v>78</v>
       </c>
       <c r="F402" s="1">
         <v>46290</v>
       </c>
       <c r="G402" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
@@ -13282,19 +13330,19 @@
         <v>816</v>
       </c>
       <c r="C403" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="E403" t="s">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="F403" s="1">
         <v>46290</v>
       </c>
       <c r="G403" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
@@ -13308,16 +13356,16 @@
         <v>80</v>
       </c>
       <c r="D404" t="s">
-        <v>818</v>
+        <v>293</v>
       </c>
       <c r="E404" t="s">
-        <v>819</v>
+        <v>294</v>
       </c>
       <c r="F404" s="1">
         <v>46290</v>
       </c>
       <c r="G404" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
@@ -13325,22 +13373,22 @@
         <v>0</v>
       </c>
       <c r="B405" t="s">
+        <v>818</v>
+      </c>
+      <c r="C405" t="s">
+        <v>80</v>
+      </c>
+      <c r="D405" t="s">
+        <v>819</v>
+      </c>
+      <c r="E405" t="s">
         <v>820</v>
-      </c>
-      <c r="C405" t="s">
-        <v>80</v>
-      </c>
-      <c r="D405" t="s">
-        <v>821</v>
-      </c>
-      <c r="E405" t="s">
-        <v>822</v>
       </c>
       <c r="F405" s="1">
         <v>46290</v>
       </c>
       <c r="G405" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
@@ -13348,22 +13396,22 @@
         <v>0</v>
       </c>
       <c r="B406" t="s">
+        <v>821</v>
+      </c>
+      <c r="C406" t="s">
+        <v>80</v>
+      </c>
+      <c r="D406" t="s">
+        <v>822</v>
+      </c>
+      <c r="E406" t="s">
         <v>823</v>
-      </c>
-      <c r="C406" t="s">
-        <v>80</v>
-      </c>
-      <c r="D406" t="s">
-        <v>824</v>
-      </c>
-      <c r="E406" t="s">
-        <v>825</v>
       </c>
       <c r="F406" s="1">
         <v>46290</v>
       </c>
       <c r="G406" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
@@ -13371,16 +13419,16 @@
         <v>0</v>
       </c>
       <c r="B407" t="s">
+        <v>824</v>
+      </c>
+      <c r="C407" t="s">
+        <v>80</v>
+      </c>
+      <c r="D407" t="s">
+        <v>825</v>
+      </c>
+      <c r="E407" t="s">
         <v>826</v>
-      </c>
-      <c r="C407" t="s">
-        <v>80</v>
-      </c>
-      <c r="D407" t="s">
-        <v>824</v>
-      </c>
-      <c r="E407" t="s">
-        <v>825</v>
       </c>
       <c r="F407" s="1">
         <v>46290</v>
@@ -13400,10 +13448,10 @@
         <v>80</v>
       </c>
       <c r="D408" t="s">
-        <v>226</v>
+        <v>825</v>
       </c>
       <c r="E408" t="s">
-        <v>227</v>
+        <v>826</v>
       </c>
       <c r="F408" s="1">
         <v>46290</v>
@@ -13423,10 +13471,10 @@
         <v>80</v>
       </c>
       <c r="D409" t="s">
-        <v>824</v>
+        <v>226</v>
       </c>
       <c r="E409" t="s">
-        <v>825</v>
+        <v>227</v>
       </c>
       <c r="F409" s="1">
         <v>46290</v>
@@ -13446,10 +13494,10 @@
         <v>80</v>
       </c>
       <c r="D410" t="s">
-        <v>182</v>
+        <v>825</v>
       </c>
       <c r="E410" t="s">
-        <v>183</v>
+        <v>826</v>
       </c>
       <c r="F410" s="1">
         <v>46290</v>
@@ -13469,10 +13517,10 @@
         <v>80</v>
       </c>
       <c r="D411" t="s">
-        <v>831</v>
+        <v>182</v>
       </c>
       <c r="E411" t="s">
-        <v>832</v>
+        <v>183</v>
       </c>
       <c r="F411" s="1">
         <v>46290</v>
@@ -13486,16 +13534,16 @@
         <v>0</v>
       </c>
       <c r="B412" t="s">
+        <v>831</v>
+      </c>
+      <c r="C412" t="s">
+        <v>80</v>
+      </c>
+      <c r="D412" t="s">
+        <v>832</v>
+      </c>
+      <c r="E412" t="s">
         <v>833</v>
-      </c>
-      <c r="C412" t="s">
-        <v>80</v>
-      </c>
-      <c r="D412" t="s">
-        <v>612</v>
-      </c>
-      <c r="E412" t="s">
-        <v>613</v>
       </c>
       <c r="F412" s="1">
         <v>46290</v>
@@ -13515,10 +13563,10 @@
         <v>80</v>
       </c>
       <c r="D413" t="s">
-        <v>48</v>
+        <v>613</v>
       </c>
       <c r="E413" t="s">
-        <v>49</v>
+        <v>614</v>
       </c>
       <c r="F413" s="1">
         <v>46290</v>
@@ -13538,10 +13586,10 @@
         <v>80</v>
       </c>
       <c r="D414" t="s">
-        <v>836</v>
+        <v>48</v>
       </c>
       <c r="E414" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="F414" s="1">
         <v>46290</v>
@@ -13555,16 +13603,16 @@
         <v>0</v>
       </c>
       <c r="B415" t="s">
+        <v>836</v>
+      </c>
+      <c r="C415" t="s">
+        <v>80</v>
+      </c>
+      <c r="D415" t="s">
+        <v>837</v>
+      </c>
+      <c r="E415" t="s">
         <v>838</v>
-      </c>
-      <c r="C415" t="s">
-        <v>80</v>
-      </c>
-      <c r="D415" t="s">
-        <v>839</v>
-      </c>
-      <c r="E415" t="s">
-        <v>840</v>
       </c>
       <c r="F415" s="1">
         <v>46290</v>
@@ -13578,16 +13626,16 @@
         <v>0</v>
       </c>
       <c r="B416" t="s">
+        <v>839</v>
+      </c>
+      <c r="C416" t="s">
+        <v>80</v>
+      </c>
+      <c r="D416" t="s">
+        <v>840</v>
+      </c>
+      <c r="E416" t="s">
         <v>841</v>
-      </c>
-      <c r="C416" t="s">
-        <v>80</v>
-      </c>
-      <c r="D416" t="s">
-        <v>842</v>
-      </c>
-      <c r="E416" t="s">
-        <v>843</v>
       </c>
       <c r="F416" s="1">
         <v>46290</v>
@@ -13601,16 +13649,16 @@
         <v>0</v>
       </c>
       <c r="B417" t="s">
+        <v>842</v>
+      </c>
+      <c r="C417" t="s">
+        <v>80</v>
+      </c>
+      <c r="D417" t="s">
+        <v>843</v>
+      </c>
+      <c r="E417" t="s">
         <v>844</v>
-      </c>
-      <c r="C417" t="s">
-        <v>80</v>
-      </c>
-      <c r="D417" t="s">
-        <v>845</v>
-      </c>
-      <c r="E417" t="s">
-        <v>846</v>
       </c>
       <c r="F417" s="1">
         <v>46290</v>
@@ -13624,16 +13672,16 @@
         <v>0</v>
       </c>
       <c r="B418" t="s">
+        <v>845</v>
+      </c>
+      <c r="C418" t="s">
+        <v>80</v>
+      </c>
+      <c r="D418" t="s">
+        <v>846</v>
+      </c>
+      <c r="E418" t="s">
         <v>847</v>
-      </c>
-      <c r="C418" t="s">
-        <v>80</v>
-      </c>
-      <c r="D418" t="s">
-        <v>226</v>
-      </c>
-      <c r="E418" t="s">
-        <v>227</v>
       </c>
       <c r="F418" s="1">
         <v>46290</v>
@@ -13653,10 +13701,10 @@
         <v>80</v>
       </c>
       <c r="D419" t="s">
-        <v>849</v>
+        <v>226</v>
       </c>
       <c r="E419" t="s">
-        <v>850</v>
+        <v>227</v>
       </c>
       <c r="F419" s="1">
         <v>46290</v>
@@ -13670,16 +13718,16 @@
         <v>0</v>
       </c>
       <c r="B420" t="s">
+        <v>849</v>
+      </c>
+      <c r="C420" t="s">
+        <v>80</v>
+      </c>
+      <c r="D420" t="s">
+        <v>850</v>
+      </c>
+      <c r="E420" t="s">
         <v>851</v>
-      </c>
-      <c r="C420" t="s">
-        <v>80</v>
-      </c>
-      <c r="D420" t="s">
-        <v>852</v>
-      </c>
-      <c r="E420" t="s">
-        <v>853</v>
       </c>
       <c r="F420" s="1">
         <v>46290</v>
@@ -13693,16 +13741,16 @@
         <v>0</v>
       </c>
       <c r="B421" t="s">
+        <v>852</v>
+      </c>
+      <c r="C421" t="s">
+        <v>80</v>
+      </c>
+      <c r="D421" t="s">
+        <v>853</v>
+      </c>
+      <c r="E421" t="s">
         <v>854</v>
-      </c>
-      <c r="C421" t="s">
-        <v>80</v>
-      </c>
-      <c r="D421" t="s">
-        <v>855</v>
-      </c>
-      <c r="E421" t="s">
-        <v>856</v>
       </c>
       <c r="F421" s="1">
         <v>46290</v>
@@ -13716,16 +13764,16 @@
         <v>0</v>
       </c>
       <c r="B422" t="s">
+        <v>855</v>
+      </c>
+      <c r="C422" t="s">
+        <v>80</v>
+      </c>
+      <c r="D422" t="s">
+        <v>856</v>
+      </c>
+      <c r="E422" t="s">
         <v>857</v>
-      </c>
-      <c r="C422" t="s">
-        <v>80</v>
-      </c>
-      <c r="D422" t="s">
-        <v>278</v>
-      </c>
-      <c r="E422" t="s">
-        <v>279</v>
       </c>
       <c r="F422" s="1">
         <v>46290</v>
@@ -13745,10 +13793,10 @@
         <v>80</v>
       </c>
       <c r="D423" t="s">
-        <v>345</v>
+        <v>278</v>
       </c>
       <c r="E423" t="s">
-        <v>346</v>
+        <v>279</v>
       </c>
       <c r="F423" s="1">
         <v>46290</v>
@@ -13768,10 +13816,10 @@
         <v>80</v>
       </c>
       <c r="D424" t="s">
-        <v>765</v>
+        <v>345</v>
       </c>
       <c r="E424" t="s">
-        <v>766</v>
+        <v>346</v>
       </c>
       <c r="F424" s="1">
         <v>46290</v>
@@ -13788,13 +13836,13 @@
         <v>860</v>
       </c>
       <c r="C425" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D425" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E425" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F425" s="1">
         <v>46290</v>
@@ -13811,13 +13859,13 @@
         <v>861</v>
       </c>
       <c r="C426" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D426" t="s">
-        <v>862</v>
+        <v>766</v>
       </c>
       <c r="E426" t="s">
-        <v>863</v>
+        <v>767</v>
       </c>
       <c r="F426" s="1">
         <v>46290</v>
@@ -13831,16 +13879,16 @@
         <v>0</v>
       </c>
       <c r="B427" t="s">
+        <v>862</v>
+      </c>
+      <c r="C427" t="s">
+        <v>80</v>
+      </c>
+      <c r="D427" t="s">
+        <v>863</v>
+      </c>
+      <c r="E427" t="s">
         <v>864</v>
-      </c>
-      <c r="C427" t="s">
-        <v>80</v>
-      </c>
-      <c r="D427" t="s">
-        <v>182</v>
-      </c>
-      <c r="E427" t="s">
-        <v>183</v>
       </c>
       <c r="F427" s="1">
         <v>46290</v>
@@ -13860,10 +13908,10 @@
         <v>80</v>
       </c>
       <c r="D428" t="s">
-        <v>382</v>
+        <v>182</v>
       </c>
       <c r="E428" t="s">
-        <v>383</v>
+        <v>183</v>
       </c>
       <c r="F428" s="1">
         <v>46290</v>
@@ -13883,10 +13931,10 @@
         <v>80</v>
       </c>
       <c r="D429" t="s">
-        <v>486</v>
+        <v>382</v>
       </c>
       <c r="E429" t="s">
-        <v>487</v>
+        <v>383</v>
       </c>
       <c r="F429" s="1">
         <v>46290</v>
@@ -13906,10 +13954,10 @@
         <v>80</v>
       </c>
       <c r="D430" t="s">
-        <v>868</v>
+        <v>487</v>
       </c>
       <c r="E430" t="s">
-        <v>869</v>
+        <v>488</v>
       </c>
       <c r="F430" s="1">
         <v>46290</v>
@@ -13923,22 +13971,22 @@
         <v>0</v>
       </c>
       <c r="B431" t="s">
+        <v>868</v>
+      </c>
+      <c r="C431" t="s">
+        <v>80</v>
+      </c>
+      <c r="D431" t="s">
+        <v>869</v>
+      </c>
+      <c r="E431" t="s">
         <v>870</v>
       </c>
-      <c r="C431" t="s">
-        <v>80</v>
-      </c>
-      <c r="D431" t="s">
-        <v>871</v>
-      </c>
-      <c r="E431" t="s">
-        <v>872</v>
-      </c>
       <c r="F431" s="1">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="G431" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
@@ -13946,16 +13994,16 @@
         <v>0</v>
       </c>
       <c r="B432" t="s">
+        <v>871</v>
+      </c>
+      <c r="C432" t="s">
+        <v>80</v>
+      </c>
+      <c r="D432" t="s">
+        <v>872</v>
+      </c>
+      <c r="E432" t="s">
         <v>873</v>
-      </c>
-      <c r="C432" t="s">
-        <v>80</v>
-      </c>
-      <c r="D432" t="s">
-        <v>874</v>
-      </c>
-      <c r="E432" t="s">
-        <v>875</v>
       </c>
       <c r="F432" s="1">
         <v>46291</v>
@@ -13969,16 +14017,16 @@
         <v>0</v>
       </c>
       <c r="B433" t="s">
+        <v>874</v>
+      </c>
+      <c r="C433" t="s">
+        <v>80</v>
+      </c>
+      <c r="D433" t="s">
+        <v>875</v>
+      </c>
+      <c r="E433" t="s">
         <v>876</v>
-      </c>
-      <c r="C433" t="s">
-        <v>80</v>
-      </c>
-      <c r="D433" t="s">
-        <v>877</v>
-      </c>
-      <c r="E433" t="s">
-        <v>878</v>
       </c>
       <c r="F433" s="1">
         <v>46291</v>
@@ -13992,16 +14040,16 @@
         <v>0</v>
       </c>
       <c r="B434" t="s">
+        <v>877</v>
+      </c>
+      <c r="C434" t="s">
+        <v>80</v>
+      </c>
+      <c r="D434" t="s">
+        <v>878</v>
+      </c>
+      <c r="E434" t="s">
         <v>879</v>
-      </c>
-      <c r="C434" t="s">
-        <v>80</v>
-      </c>
-      <c r="D434" t="s">
-        <v>81</v>
-      </c>
-      <c r="E434" t="s">
-        <v>82</v>
       </c>
       <c r="F434" s="1">
         <v>46291</v>
@@ -14021,10 +14069,10 @@
         <v>80</v>
       </c>
       <c r="D435" t="s">
-        <v>881</v>
+        <v>81</v>
       </c>
       <c r="E435" t="s">
-        <v>882</v>
+        <v>82</v>
       </c>
       <c r="F435" s="1">
         <v>46291</v>
@@ -14038,19 +14086,19 @@
         <v>0</v>
       </c>
       <c r="B436" t="s">
+        <v>881</v>
+      </c>
+      <c r="C436" t="s">
+        <v>80</v>
+      </c>
+      <c r="D436" t="s">
+        <v>882</v>
+      </c>
+      <c r="E436" t="s">
         <v>883</v>
       </c>
-      <c r="C436" t="s">
-        <v>80</v>
-      </c>
-      <c r="D436" t="s">
-        <v>341</v>
-      </c>
-      <c r="E436" t="s">
-        <v>342</v>
-      </c>
       <c r="F436" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G436" s="1">
         <v>46293</v>
@@ -14067,10 +14115,10 @@
         <v>80</v>
       </c>
       <c r="D437" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="E437" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F437" s="1">
         <v>46293</v>
@@ -14113,10 +14161,10 @@
         <v>80</v>
       </c>
       <c r="D439" t="s">
-        <v>852</v>
+        <v>300</v>
       </c>
       <c r="E439" t="s">
-        <v>853</v>
+        <v>301</v>
       </c>
       <c r="F439" s="1">
         <v>46293</v>
@@ -14136,10 +14184,10 @@
         <v>80</v>
       </c>
       <c r="D440" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
       <c r="E440" t="s">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="F440" s="1">
         <v>46293</v>
@@ -14159,10 +14207,10 @@
         <v>80</v>
       </c>
       <c r="D441" t="s">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="E441" t="s">
-        <v>805</v>
+        <v>833</v>
       </c>
       <c r="F441" s="1">
         <v>46293</v>
@@ -14182,10 +14230,10 @@
         <v>80</v>
       </c>
       <c r="D442" t="s">
-        <v>81</v>
+        <v>805</v>
       </c>
       <c r="E442" t="s">
-        <v>82</v>
+        <v>806</v>
       </c>
       <c r="F442" s="1">
         <v>46293</v>
@@ -14205,10 +14253,10 @@
         <v>80</v>
       </c>
       <c r="D443" t="s">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="E443" t="s">
-        <v>892</v>
+        <v>82</v>
       </c>
       <c r="F443" s="1">
         <v>46293</v>
@@ -14222,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="B444" t="s">
+        <v>891</v>
+      </c>
+      <c r="C444" t="s">
+        <v>80</v>
+      </c>
+      <c r="D444" t="s">
+        <v>892</v>
+      </c>
+      <c r="E444" t="s">
         <v>893</v>
-      </c>
-      <c r="C444" t="s">
-        <v>80</v>
-      </c>
-      <c r="D444" t="s">
-        <v>19</v>
-      </c>
-      <c r="E444" t="s">
-        <v>20</v>
       </c>
       <c r="F444" s="1">
         <v>46293</v>
@@ -14251,10 +14299,10 @@
         <v>80</v>
       </c>
       <c r="D445" t="s">
-        <v>895</v>
+        <v>19</v>
       </c>
       <c r="E445" t="s">
-        <v>896</v>
+        <v>20</v>
       </c>
       <c r="F445" s="1">
         <v>46293</v>
@@ -14268,16 +14316,16 @@
         <v>0</v>
       </c>
       <c r="B446" t="s">
+        <v>895</v>
+      </c>
+      <c r="C446" t="s">
+        <v>80</v>
+      </c>
+      <c r="D446" t="s">
+        <v>896</v>
+      </c>
+      <c r="E446" t="s">
         <v>897</v>
-      </c>
-      <c r="C446" t="s">
-        <v>80</v>
-      </c>
-      <c r="D446" t="s">
-        <v>371</v>
-      </c>
-      <c r="E446" t="s">
-        <v>372</v>
       </c>
       <c r="F446" s="1">
         <v>46293</v>
@@ -14297,10 +14345,10 @@
         <v>80</v>
       </c>
       <c r="D447" t="s">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="E447" t="s">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="F447" s="1">
         <v>46293</v>
@@ -14320,10 +14368,10 @@
         <v>80</v>
       </c>
       <c r="D448" t="s">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="E448" t="s">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="F448" s="1">
         <v>46293</v>
@@ -14343,10 +14391,10 @@
         <v>80</v>
       </c>
       <c r="D449" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="E449" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="F449" s="1">
         <v>46293</v>
@@ -14375,7 +14423,7 @@
         <v>46293</v>
       </c>
       <c r="G450" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
@@ -14389,16 +14437,16 @@
         <v>80</v>
       </c>
       <c r="D451" t="s">
-        <v>903</v>
+        <v>212</v>
       </c>
       <c r="E451" t="s">
-        <v>904</v>
+        <v>213</v>
       </c>
       <c r="F451" s="1">
         <v>46293</v>
       </c>
       <c r="G451" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
@@ -14406,16 +14454,16 @@
         <v>0</v>
       </c>
       <c r="B452" t="s">
+        <v>903</v>
+      </c>
+      <c r="C452" t="s">
+        <v>80</v>
+      </c>
+      <c r="D452" t="s">
+        <v>904</v>
+      </c>
+      <c r="E452" t="s">
         <v>905</v>
-      </c>
-      <c r="C452" t="s">
-        <v>80</v>
-      </c>
-      <c r="D452" t="s">
-        <v>906</v>
-      </c>
-      <c r="E452" t="s">
-        <v>907</v>
       </c>
       <c r="F452" s="1">
         <v>46293</v>
@@ -14429,16 +14477,16 @@
         <v>0</v>
       </c>
       <c r="B453" t="s">
+        <v>906</v>
+      </c>
+      <c r="C453" t="s">
+        <v>80</v>
+      </c>
+      <c r="D453" t="s">
+        <v>907</v>
+      </c>
+      <c r="E453" t="s">
         <v>908</v>
-      </c>
-      <c r="C453" t="s">
-        <v>80</v>
-      </c>
-      <c r="D453" t="s">
-        <v>909</v>
-      </c>
-      <c r="E453" t="s">
-        <v>910</v>
       </c>
       <c r="F453" s="1">
         <v>46293</v>
@@ -14452,16 +14500,16 @@
         <v>0</v>
       </c>
       <c r="B454" t="s">
+        <v>909</v>
+      </c>
+      <c r="C454" t="s">
+        <v>80</v>
+      </c>
+      <c r="D454" t="s">
+        <v>910</v>
+      </c>
+      <c r="E454" t="s">
         <v>911</v>
-      </c>
-      <c r="C454" t="s">
-        <v>80</v>
-      </c>
-      <c r="D454" t="s">
-        <v>912</v>
-      </c>
-      <c r="E454" t="s">
-        <v>913</v>
       </c>
       <c r="F454" s="1">
         <v>46293</v>
@@ -14475,16 +14523,16 @@
         <v>0</v>
       </c>
       <c r="B455" t="s">
+        <v>912</v>
+      </c>
+      <c r="C455" t="s">
+        <v>80</v>
+      </c>
+      <c r="D455" t="s">
+        <v>913</v>
+      </c>
+      <c r="E455" t="s">
         <v>914</v>
-      </c>
-      <c r="C455" t="s">
-        <v>80</v>
-      </c>
-      <c r="D455" t="s">
-        <v>48</v>
-      </c>
-      <c r="E455" t="s">
-        <v>49</v>
       </c>
       <c r="F455" s="1">
         <v>46293</v>
@@ -14504,10 +14552,10 @@
         <v>80</v>
       </c>
       <c r="D456" t="s">
-        <v>916</v>
+        <v>48</v>
       </c>
       <c r="E456" t="s">
-        <v>917</v>
+        <v>49</v>
       </c>
       <c r="F456" s="1">
         <v>46293</v>
@@ -14521,16 +14569,16 @@
         <v>0</v>
       </c>
       <c r="B457" t="s">
+        <v>916</v>
+      </c>
+      <c r="C457" t="s">
+        <v>80</v>
+      </c>
+      <c r="D457" t="s">
+        <v>917</v>
+      </c>
+      <c r="E457" t="s">
         <v>918</v>
-      </c>
-      <c r="C457" t="s">
-        <v>80</v>
-      </c>
-      <c r="D457" t="s">
-        <v>919</v>
-      </c>
-      <c r="E457" t="s">
-        <v>920</v>
       </c>
       <c r="F457" s="1">
         <v>46293</v>
@@ -14544,16 +14592,16 @@
         <v>0</v>
       </c>
       <c r="B458" t="s">
+        <v>919</v>
+      </c>
+      <c r="C458" t="s">
+        <v>80</v>
+      </c>
+      <c r="D458" t="s">
+        <v>920</v>
+      </c>
+      <c r="E458" t="s">
         <v>921</v>
-      </c>
-      <c r="C458" t="s">
-        <v>80</v>
-      </c>
-      <c r="D458" t="s">
-        <v>685</v>
-      </c>
-      <c r="E458" t="s">
-        <v>686</v>
       </c>
       <c r="F458" s="1">
         <v>46293</v>
@@ -14573,10 +14621,10 @@
         <v>80</v>
       </c>
       <c r="D459" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="E459" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="F459" s="1">
         <v>46293</v>
@@ -14596,10 +14644,10 @@
         <v>80</v>
       </c>
       <c r="D460" t="s">
-        <v>924</v>
+        <v>699</v>
       </c>
       <c r="E460" t="s">
-        <v>925</v>
+        <v>700</v>
       </c>
       <c r="F460" s="1">
         <v>46293</v>
@@ -14613,16 +14661,16 @@
         <v>0</v>
       </c>
       <c r="B461" t="s">
+        <v>924</v>
+      </c>
+      <c r="C461" t="s">
+        <v>80</v>
+      </c>
+      <c r="D461" t="s">
+        <v>925</v>
+      </c>
+      <c r="E461" t="s">
         <v>926</v>
-      </c>
-      <c r="C461" t="s">
-        <v>80</v>
-      </c>
-      <c r="D461" t="s">
-        <v>924</v>
-      </c>
-      <c r="E461" t="s">
-        <v>925</v>
       </c>
       <c r="F461" s="1">
         <v>46293</v>
@@ -14642,10 +14690,10 @@
         <v>80</v>
       </c>
       <c r="D462" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="E462" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="F462" s="1">
         <v>46293</v>
@@ -14659,16 +14707,16 @@
         <v>0</v>
       </c>
       <c r="B463" t="s">
+        <v>928</v>
+      </c>
+      <c r="C463" t="s">
+        <v>80</v>
+      </c>
+      <c r="D463" t="s">
+        <v>929</v>
+      </c>
+      <c r="E463" t="s">
         <v>930</v>
-      </c>
-      <c r="C463" t="s">
-        <v>80</v>
-      </c>
-      <c r="D463" t="s">
-        <v>172</v>
-      </c>
-      <c r="E463" t="s">
-        <v>173</v>
       </c>
       <c r="F463" s="1">
         <v>46293</v>
@@ -14688,10 +14736,10 @@
         <v>80</v>
       </c>
       <c r="D464" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="E464" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="F464" s="1">
         <v>46293</v>
@@ -14711,10 +14759,10 @@
         <v>80</v>
       </c>
       <c r="D465" t="s">
-        <v>933</v>
+        <v>212</v>
       </c>
       <c r="E465" t="s">
-        <v>934</v>
+        <v>213</v>
       </c>
       <c r="F465" s="1">
         <v>46293</v>
@@ -14728,16 +14776,16 @@
         <v>0</v>
       </c>
       <c r="B466" t="s">
+        <v>933</v>
+      </c>
+      <c r="C466" t="s">
+        <v>80</v>
+      </c>
+      <c r="D466" t="s">
+        <v>934</v>
+      </c>
+      <c r="E466" t="s">
         <v>935</v>
-      </c>
-      <c r="C466" t="s">
-        <v>80</v>
-      </c>
-      <c r="D466" t="s">
-        <v>200</v>
-      </c>
-      <c r="E466" t="s">
-        <v>201</v>
       </c>
       <c r="F466" s="1">
         <v>46293</v>
@@ -14757,10 +14805,10 @@
         <v>80</v>
       </c>
       <c r="D467" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="E467" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="F467" s="1">
         <v>46293</v>
@@ -14780,10 +14828,10 @@
         <v>80</v>
       </c>
       <c r="D468" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="E468" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="F468" s="1">
         <v>46293</v>
@@ -14803,10 +14851,10 @@
         <v>80</v>
       </c>
       <c r="D469" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E469" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F469" s="1">
         <v>46293</v>
@@ -14849,10 +14897,10 @@
         <v>80</v>
       </c>
       <c r="D471" t="s">
-        <v>179</v>
+        <v>16</v>
       </c>
       <c r="E471" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="F471" s="1">
         <v>46293</v>
@@ -14872,10 +14920,10 @@
         <v>80</v>
       </c>
       <c r="D472" t="s">
-        <v>629</v>
+        <v>179</v>
       </c>
       <c r="E472" t="s">
-        <v>630</v>
+        <v>180</v>
       </c>
       <c r="F472" s="1">
         <v>46293</v>
@@ -14895,10 +14943,10 @@
         <v>80</v>
       </c>
       <c r="D473" t="s">
-        <v>16</v>
+        <v>630</v>
       </c>
       <c r="E473" t="s">
-        <v>17</v>
+        <v>631</v>
       </c>
       <c r="F473" s="1">
         <v>46293</v>
@@ -14918,10 +14966,10 @@
         <v>80</v>
       </c>
       <c r="D474" t="s">
-        <v>944</v>
+        <v>16</v>
       </c>
       <c r="E474" t="s">
-        <v>945</v>
+        <v>17</v>
       </c>
       <c r="F474" s="1">
         <v>46293</v>
@@ -14935,16 +14983,16 @@
         <v>0</v>
       </c>
       <c r="B475" t="s">
+        <v>944</v>
+      </c>
+      <c r="C475" t="s">
+        <v>80</v>
+      </c>
+      <c r="D475" t="s">
+        <v>945</v>
+      </c>
+      <c r="E475" t="s">
         <v>946</v>
-      </c>
-      <c r="C475" t="s">
-        <v>80</v>
-      </c>
-      <c r="D475" t="s">
-        <v>947</v>
-      </c>
-      <c r="E475" t="s">
-        <v>948</v>
       </c>
       <c r="F475" s="1">
         <v>46293</v>
@@ -14958,16 +15006,16 @@
         <v>0</v>
       </c>
       <c r="B476" t="s">
+        <v>947</v>
+      </c>
+      <c r="C476" t="s">
+        <v>80</v>
+      </c>
+      <c r="D476" t="s">
+        <v>948</v>
+      </c>
+      <c r="E476" t="s">
         <v>949</v>
-      </c>
-      <c r="C476" t="s">
-        <v>80</v>
-      </c>
-      <c r="D476" t="s">
-        <v>172</v>
-      </c>
-      <c r="E476" t="s">
-        <v>173</v>
       </c>
       <c r="F476" s="1">
         <v>46293</v>
@@ -15010,10 +15058,10 @@
         <v>80</v>
       </c>
       <c r="D478" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="E478" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="F478" s="1">
         <v>46293</v>
@@ -15033,10 +15081,10 @@
         <v>80</v>
       </c>
       <c r="D479" t="s">
-        <v>712</v>
+        <v>223</v>
       </c>
       <c r="E479" t="s">
-        <v>713</v>
+        <v>224</v>
       </c>
       <c r="F479" s="1">
         <v>46293</v>
@@ -15056,10 +15104,10 @@
         <v>80</v>
       </c>
       <c r="D480" t="s">
-        <v>16</v>
+        <v>713</v>
       </c>
       <c r="E480" t="s">
-        <v>17</v>
+        <v>714</v>
       </c>
       <c r="F480" s="1">
         <v>46293</v>
@@ -15079,10 +15127,10 @@
         <v>80</v>
       </c>
       <c r="D481" t="s">
-        <v>403</v>
+        <v>16</v>
       </c>
       <c r="E481" t="s">
-        <v>404</v>
+        <v>17</v>
       </c>
       <c r="F481" s="1">
         <v>46293</v>
@@ -15102,10 +15150,10 @@
         <v>80</v>
       </c>
       <c r="D482" t="s">
-        <v>712</v>
+        <v>404</v>
       </c>
       <c r="E482" t="s">
-        <v>713</v>
+        <v>405</v>
       </c>
       <c r="F482" s="1">
         <v>46293</v>
@@ -15125,10 +15173,10 @@
         <v>80</v>
       </c>
       <c r="D483" t="s">
-        <v>957</v>
+        <v>713</v>
       </c>
       <c r="E483" t="s">
-        <v>958</v>
+        <v>714</v>
       </c>
       <c r="F483" s="1">
         <v>46293</v>
@@ -15142,16 +15190,16 @@
         <v>0</v>
       </c>
       <c r="B484" t="s">
+        <v>957</v>
+      </c>
+      <c r="C484" t="s">
+        <v>80</v>
+      </c>
+      <c r="D484" t="s">
+        <v>958</v>
+      </c>
+      <c r="E484" t="s">
         <v>959</v>
-      </c>
-      <c r="C484" t="s">
-        <v>80</v>
-      </c>
-      <c r="D484" t="s">
-        <v>685</v>
-      </c>
-      <c r="E484" t="s">
-        <v>686</v>
       </c>
       <c r="F484" s="1">
         <v>46293</v>
@@ -15171,10 +15219,10 @@
         <v>80</v>
       </c>
       <c r="D485" t="s">
-        <v>961</v>
+        <v>686</v>
       </c>
       <c r="E485" t="s">
-        <v>962</v>
+        <v>687</v>
       </c>
       <c r="F485" s="1">
         <v>46293</v>
@@ -15188,16 +15236,16 @@
         <v>0</v>
       </c>
       <c r="B486" t="s">
+        <v>961</v>
+      </c>
+      <c r="C486" t="s">
+        <v>80</v>
+      </c>
+      <c r="D486" t="s">
+        <v>962</v>
+      </c>
+      <c r="E486" t="s">
         <v>963</v>
-      </c>
-      <c r="C486" t="s">
-        <v>80</v>
-      </c>
-      <c r="D486" t="s">
-        <v>81</v>
-      </c>
-      <c r="E486" t="s">
-        <v>82</v>
       </c>
       <c r="F486" s="1">
         <v>46293</v>
@@ -15217,10 +15265,10 @@
         <v>80</v>
       </c>
       <c r="D487" t="s">
-        <v>965</v>
+        <v>81</v>
       </c>
       <c r="E487" t="s">
-        <v>966</v>
+        <v>82</v>
       </c>
       <c r="F487" s="1">
         <v>46293</v>
@@ -15234,16 +15282,16 @@
         <v>0</v>
       </c>
       <c r="B488" t="s">
+        <v>965</v>
+      </c>
+      <c r="C488" t="s">
+        <v>80</v>
+      </c>
+      <c r="D488" t="s">
+        <v>966</v>
+      </c>
+      <c r="E488" t="s">
         <v>967</v>
-      </c>
-      <c r="C488" t="s">
-        <v>80</v>
-      </c>
-      <c r="D488" t="s">
-        <v>968</v>
-      </c>
-      <c r="E488" t="s">
-        <v>969</v>
       </c>
       <c r="F488" s="1">
         <v>46293</v>
@@ -15257,16 +15305,16 @@
         <v>0</v>
       </c>
       <c r="B489" t="s">
+        <v>968</v>
+      </c>
+      <c r="C489" t="s">
+        <v>80</v>
+      </c>
+      <c r="D489" t="s">
+        <v>969</v>
+      </c>
+      <c r="E489" t="s">
         <v>970</v>
-      </c>
-      <c r="C489" t="s">
-        <v>80</v>
-      </c>
-      <c r="D489" t="s">
-        <v>968</v>
-      </c>
-      <c r="E489" t="s">
-        <v>969</v>
       </c>
       <c r="F489" s="1">
         <v>46293</v>
@@ -15286,16 +15334,16 @@
         <v>80</v>
       </c>
       <c r="D490" t="s">
-        <v>258</v>
+        <v>969</v>
       </c>
       <c r="E490" t="s">
-        <v>259</v>
+        <v>970</v>
       </c>
       <c r="F490" s="1">
         <v>46293</v>
       </c>
       <c r="G490" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.2">
@@ -15309,13 +15357,13 @@
         <v>80</v>
       </c>
       <c r="D491" t="s">
-        <v>973</v>
+        <v>258</v>
       </c>
       <c r="E491" t="s">
-        <v>974</v>
+        <v>259</v>
       </c>
       <c r="F491" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="G491" s="1">
         <v>46294</v>
@@ -15326,16 +15374,16 @@
         <v>0</v>
       </c>
       <c r="B492" t="s">
+        <v>973</v>
+      </c>
+      <c r="C492" t="s">
+        <v>80</v>
+      </c>
+      <c r="D492" t="s">
+        <v>974</v>
+      </c>
+      <c r="E492" t="s">
         <v>975</v>
-      </c>
-      <c r="C492" t="s">
-        <v>80</v>
-      </c>
-      <c r="D492" t="s">
-        <v>16</v>
-      </c>
-      <c r="E492" t="s">
-        <v>17</v>
       </c>
       <c r="F492" s="1">
         <v>46294</v>
@@ -15355,10 +15403,10 @@
         <v>80</v>
       </c>
       <c r="D493" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E493" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F493" s="1">
         <v>46294</v>
@@ -15470,10 +15518,10 @@
         <v>80</v>
       </c>
       <c r="D498" t="s">
-        <v>982</v>
+        <v>37</v>
       </c>
       <c r="E498" t="s">
-        <v>983</v>
+        <v>38</v>
       </c>
       <c r="F498" s="1">
         <v>46294</v>
@@ -15487,16 +15535,16 @@
         <v>0</v>
       </c>
       <c r="B499" t="s">
+        <v>982</v>
+      </c>
+      <c r="C499" t="s">
+        <v>80</v>
+      </c>
+      <c r="D499" t="s">
+        <v>983</v>
+      </c>
+      <c r="E499" t="s">
         <v>984</v>
-      </c>
-      <c r="C499" t="s">
-        <v>80</v>
-      </c>
-      <c r="D499" t="s">
-        <v>87</v>
-      </c>
-      <c r="E499" t="s">
-        <v>88</v>
       </c>
       <c r="F499" s="1">
         <v>46294</v>
@@ -15654,10 +15702,10 @@
         <v>80</v>
       </c>
       <c r="D506" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="E506" t="s">
-        <v>805</v>
+        <v>88</v>
       </c>
       <c r="F506" s="1">
         <v>46294</v>
@@ -15677,10 +15725,10 @@
         <v>80</v>
       </c>
       <c r="D507" t="s">
-        <v>993</v>
+        <v>805</v>
       </c>
       <c r="E507" t="s">
-        <v>994</v>
+        <v>806</v>
       </c>
       <c r="F507" s="1">
         <v>46294</v>
@@ -15694,16 +15742,16 @@
         <v>0</v>
       </c>
       <c r="B508" t="s">
+        <v>993</v>
+      </c>
+      <c r="C508" t="s">
+        <v>80</v>
+      </c>
+      <c r="D508" t="s">
+        <v>994</v>
+      </c>
+      <c r="E508" t="s">
         <v>995</v>
-      </c>
-      <c r="C508" t="s">
-        <v>80</v>
-      </c>
-      <c r="D508" t="s">
-        <v>996</v>
-      </c>
-      <c r="E508" t="s">
-        <v>997</v>
       </c>
       <c r="F508" s="1">
         <v>46294</v>
@@ -15717,16 +15765,16 @@
         <v>0</v>
       </c>
       <c r="B509" t="s">
+        <v>996</v>
+      </c>
+      <c r="C509" t="s">
+        <v>80</v>
+      </c>
+      <c r="D509" t="s">
+        <v>997</v>
+      </c>
+      <c r="E509" t="s">
         <v>998</v>
-      </c>
-      <c r="C509" t="s">
-        <v>80</v>
-      </c>
-      <c r="D509" t="s">
-        <v>48</v>
-      </c>
-      <c r="E509" t="s">
-        <v>49</v>
       </c>
       <c r="F509" s="1">
         <v>46294</v>
@@ -15746,10 +15794,10 @@
         <v>80</v>
       </c>
       <c r="D510" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="E510" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="F510" s="1">
         <v>46294</v>
@@ -15769,10 +15817,10 @@
         <v>80</v>
       </c>
       <c r="D511" t="s">
-        <v>1001</v>
+        <v>143</v>
       </c>
       <c r="E511" t="s">
-        <v>1002</v>
+        <v>144</v>
       </c>
       <c r="F511" s="1">
         <v>46294</v>
@@ -15786,16 +15834,16 @@
         <v>0</v>
       </c>
       <c r="B512" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C512" t="s">
+        <v>80</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E512" t="s">
         <v>1003</v>
-      </c>
-      <c r="C512" t="s">
-        <v>80</v>
-      </c>
-      <c r="D512" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1005</v>
       </c>
       <c r="F512" s="1">
         <v>46294</v>
@@ -15809,16 +15857,16 @@
         <v>0</v>
       </c>
       <c r="B513" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C513" t="s">
+        <v>80</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E513" t="s">
         <v>1006</v>
-      </c>
-      <c r="C513" t="s">
-        <v>80</v>
-      </c>
-      <c r="D513" t="s">
-        <v>48</v>
-      </c>
-      <c r="E513" t="s">
-        <v>49</v>
       </c>
       <c r="F513" s="1">
         <v>46294</v>
@@ -15838,10 +15886,10 @@
         <v>80</v>
       </c>
       <c r="D514" t="s">
-        <v>1008</v>
+        <v>48</v>
       </c>
       <c r="E514" t="s">
-        <v>1009</v>
+        <v>49</v>
       </c>
       <c r="F514" s="1">
         <v>46294</v>
@@ -15855,16 +15903,16 @@
         <v>0</v>
       </c>
       <c r="B515" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C515" t="s">
+        <v>2</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E515" t="s">
         <v>1010</v>
-      </c>
-      <c r="C515" t="s">
-        <v>80</v>
-      </c>
-      <c r="D515" t="s">
-        <v>698</v>
-      </c>
-      <c r="E515" t="s">
-        <v>699</v>
       </c>
       <c r="F515" s="1">
         <v>46294</v>
@@ -15884,10 +15932,10 @@
         <v>80</v>
       </c>
       <c r="D516" t="s">
-        <v>1012</v>
+        <v>699</v>
       </c>
       <c r="E516" t="s">
-        <v>1013</v>
+        <v>700</v>
       </c>
       <c r="F516" s="1">
         <v>46294</v>
@@ -15901,16 +15949,16 @@
         <v>0</v>
       </c>
       <c r="B517" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C517" t="s">
+        <v>80</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E517" t="s">
         <v>1014</v>
-      </c>
-      <c r="C517" t="s">
-        <v>80</v>
-      </c>
-      <c r="D517" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E517" t="s">
-        <v>1016</v>
       </c>
       <c r="F517" s="1">
         <v>46294</v>
@@ -15924,16 +15972,16 @@
         <v>0</v>
       </c>
       <c r="B518" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C518" t="s">
+        <v>80</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E518" t="s">
         <v>1017</v>
-      </c>
-      <c r="C518" t="s">
-        <v>80</v>
-      </c>
-      <c r="D518" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E518" t="s">
-        <v>1019</v>
       </c>
       <c r="F518" s="1">
         <v>46294</v>
@@ -15947,16 +15995,16 @@
         <v>0</v>
       </c>
       <c r="B519" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C519" t="s">
+        <v>80</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E519" t="s">
         <v>1020</v>
-      </c>
-      <c r="C519" t="s">
-        <v>80</v>
-      </c>
-      <c r="D519" t="s">
-        <v>182</v>
-      </c>
-      <c r="E519" t="s">
-        <v>183</v>
       </c>
       <c r="F519" s="1">
         <v>46294</v>
@@ -15976,10 +16024,10 @@
         <v>80</v>
       </c>
       <c r="D520" t="s">
-        <v>1022</v>
+        <v>182</v>
       </c>
       <c r="E520" t="s">
-        <v>1023</v>
+        <v>183</v>
       </c>
       <c r="F520" s="1">
         <v>46294</v>
@@ -15993,16 +16041,16 @@
         <v>0</v>
       </c>
       <c r="B521" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C521" t="s">
+        <v>80</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E521" t="s">
         <v>1024</v>
-      </c>
-      <c r="C521" t="s">
-        <v>80</v>
-      </c>
-      <c r="D521" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1026</v>
       </c>
       <c r="F521" s="1">
         <v>46294</v>
@@ -16016,16 +16064,16 @@
         <v>0</v>
       </c>
       <c r="B522" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C522" t="s">
+        <v>80</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E522" t="s">
         <v>1027</v>
-      </c>
-      <c r="C522" t="s">
-        <v>80</v>
-      </c>
-      <c r="D522" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E522" t="s">
-        <v>1026</v>
       </c>
       <c r="F522" s="1">
         <v>46294</v>
@@ -16045,10 +16093,10 @@
         <v>80</v>
       </c>
       <c r="D523" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E523" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F523" s="1">
         <v>46294</v>
@@ -16062,16 +16110,16 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C524" t="s">
+        <v>80</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E524" t="s">
         <v>1031</v>
-      </c>
-      <c r="C524" t="s">
-        <v>80</v>
-      </c>
-      <c r="D524" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E524" t="s">
-        <v>1033</v>
       </c>
       <c r="F524" s="1">
         <v>46294</v>
@@ -16085,16 +16133,16 @@
         <v>0</v>
       </c>
       <c r="B525" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C525" t="s">
+        <v>80</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E525" t="s">
         <v>1034</v>
-      </c>
-      <c r="C525" t="s">
-        <v>80</v>
-      </c>
-      <c r="D525" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E525" t="s">
-        <v>1036</v>
       </c>
       <c r="F525" s="1">
         <v>46294</v>
@@ -16108,16 +16156,16 @@
         <v>0</v>
       </c>
       <c r="B526" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C526" t="s">
+        <v>80</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E526" t="s">
         <v>1037</v>
-      </c>
-      <c r="C526" t="s">
-        <v>80</v>
-      </c>
-      <c r="D526" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E526" t="s">
-        <v>1039</v>
       </c>
       <c r="F526" s="1">
         <v>46294</v>
@@ -16131,16 +16179,16 @@
         <v>0</v>
       </c>
       <c r="B527" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C527" t="s">
+        <v>80</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E527" t="s">
         <v>1040</v>
-      </c>
-      <c r="C527" t="s">
-        <v>80</v>
-      </c>
-      <c r="D527" t="s">
-        <v>77</v>
-      </c>
-      <c r="E527" t="s">
-        <v>78</v>
       </c>
       <c r="F527" s="1">
         <v>46294</v>
@@ -16183,10 +16231,10 @@
         <v>80</v>
       </c>
       <c r="D529" t="s">
-        <v>1043</v>
+        <v>77</v>
       </c>
       <c r="E529" t="s">
-        <v>1044</v>
+        <v>78</v>
       </c>
       <c r="F529" s="1">
         <v>46294</v>
@@ -16200,16 +16248,16 @@
         <v>0</v>
       </c>
       <c r="B530" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C530" t="s">
+        <v>80</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E530" t="s">
         <v>1045</v>
-      </c>
-      <c r="C530" t="s">
-        <v>80</v>
-      </c>
-      <c r="D530" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E530" t="s">
-        <v>1044</v>
       </c>
       <c r="F530" s="1">
         <v>46294</v>
@@ -16229,10 +16277,10 @@
         <v>80</v>
       </c>
       <c r="D531" t="s">
-        <v>93</v>
+        <v>1044</v>
       </c>
       <c r="E531" t="s">
-        <v>94</v>
+        <v>1045</v>
       </c>
       <c r="F531" s="1">
         <v>46294</v>
@@ -16252,10 +16300,10 @@
         <v>80</v>
       </c>
       <c r="D532" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E532" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F532" s="1">
         <v>46294</v>
@@ -16275,10 +16323,10 @@
         <v>80</v>
       </c>
       <c r="D533" t="s">
-        <v>1049</v>
+        <v>48</v>
       </c>
       <c r="E533" t="s">
-        <v>1050</v>
+        <v>49</v>
       </c>
       <c r="F533" s="1">
         <v>46294</v>
@@ -16292,16 +16340,16 @@
         <v>0</v>
       </c>
       <c r="B534" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C534" t="s">
+        <v>80</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E534" t="s">
         <v>1051</v>
-      </c>
-      <c r="C534" t="s">
-        <v>80</v>
-      </c>
-      <c r="D534" t="s">
-        <v>278</v>
-      </c>
-      <c r="E534" t="s">
-        <v>279</v>
       </c>
       <c r="F534" s="1">
         <v>46294</v>
@@ -16321,10 +16369,10 @@
         <v>80</v>
       </c>
       <c r="D535" t="s">
-        <v>1053</v>
+        <v>278</v>
       </c>
       <c r="E535" t="s">
-        <v>1054</v>
+        <v>279</v>
       </c>
       <c r="F535" s="1">
         <v>46294</v>
@@ -16338,16 +16386,16 @@
         <v>0</v>
       </c>
       <c r="B536" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C536" t="s">
+        <v>80</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E536" t="s">
         <v>1055</v>
-      </c>
-      <c r="C536" t="s">
-        <v>80</v>
-      </c>
-      <c r="D536" t="s">
-        <v>506</v>
-      </c>
-      <c r="E536" t="s">
-        <v>507</v>
       </c>
       <c r="F536" s="1">
         <v>46294</v>
@@ -16367,10 +16415,10 @@
         <v>80</v>
       </c>
       <c r="D537" t="s">
-        <v>968</v>
+        <v>507</v>
       </c>
       <c r="E537" t="s">
-        <v>969</v>
+        <v>508</v>
       </c>
       <c r="F537" s="1">
         <v>46294</v>
@@ -16390,10 +16438,10 @@
         <v>80</v>
       </c>
       <c r="D538" t="s">
-        <v>48</v>
+        <v>969</v>
       </c>
       <c r="E538" t="s">
-        <v>49</v>
+        <v>970</v>
       </c>
       <c r="F538" s="1">
         <v>46294</v>
@@ -16413,10 +16461,10 @@
         <v>80</v>
       </c>
       <c r="D539" t="s">
-        <v>1035</v>
+        <v>48</v>
       </c>
       <c r="E539" t="s">
-        <v>1036</v>
+        <v>49</v>
       </c>
       <c r="F539" s="1">
         <v>46294</v>
@@ -16436,10 +16484,10 @@
         <v>80</v>
       </c>
       <c r="D540" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E540" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F540" s="1">
         <v>46294</v>
@@ -16459,10 +16507,10 @@
         <v>80</v>
       </c>
       <c r="D541" t="s">
-        <v>968</v>
+        <v>1036</v>
       </c>
       <c r="E541" t="s">
-        <v>969</v>
+        <v>1037</v>
       </c>
       <c r="F541" s="1">
         <v>46294</v>
@@ -16482,10 +16530,10 @@
         <v>80</v>
       </c>
       <c r="D542" t="s">
-        <v>1062</v>
+        <v>969</v>
       </c>
       <c r="E542" t="s">
-        <v>1063</v>
+        <v>970</v>
       </c>
       <c r="F542" s="1">
         <v>46294</v>
@@ -16499,16 +16547,16 @@
         <v>0</v>
       </c>
       <c r="B543" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C543" t="s">
+        <v>80</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E543" t="s">
         <v>1064</v>
-      </c>
-      <c r="C543" t="s">
-        <v>80</v>
-      </c>
-      <c r="D543" t="s">
-        <v>16</v>
-      </c>
-      <c r="E543" t="s">
-        <v>17</v>
       </c>
       <c r="F543" s="1">
         <v>46294</v>
@@ -16528,10 +16576,10 @@
         <v>80</v>
       </c>
       <c r="D544" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="E544" t="s">
-        <v>285</v>
+        <v>17</v>
       </c>
       <c r="F544" s="1">
         <v>46294</v>
@@ -16574,10 +16622,10 @@
         <v>80</v>
       </c>
       <c r="D546" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="E546" t="s">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="F546" s="1">
         <v>46294</v>
@@ -16597,10 +16645,10 @@
         <v>80</v>
       </c>
       <c r="D547" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="E547" t="s">
-        <v>285</v>
+        <v>17</v>
       </c>
       <c r="F547" s="1">
         <v>46294</v>
@@ -16643,10 +16691,10 @@
         <v>80</v>
       </c>
       <c r="D549" t="s">
-        <v>652</v>
+        <v>284</v>
       </c>
       <c r="E549" t="s">
-        <v>653</v>
+        <v>285</v>
       </c>
       <c r="F549" s="1">
         <v>46294</v>
@@ -16666,10 +16714,10 @@
         <v>80</v>
       </c>
       <c r="D550" t="s">
-        <v>1072</v>
+        <v>653</v>
       </c>
       <c r="E550" t="s">
-        <v>1073</v>
+        <v>654</v>
       </c>
       <c r="F550" s="1">
         <v>46294</v>
@@ -16683,16 +16731,16 @@
         <v>0</v>
       </c>
       <c r="B551" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C551" t="s">
+        <v>80</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E551" t="s">
         <v>1074</v>
-      </c>
-      <c r="C551" t="s">
-        <v>80</v>
-      </c>
-      <c r="D551" t="s">
-        <v>155</v>
-      </c>
-      <c r="E551" t="s">
-        <v>156</v>
       </c>
       <c r="F551" s="1">
         <v>46294</v>
@@ -16712,10 +16760,10 @@
         <v>80</v>
       </c>
       <c r="D552" t="s">
-        <v>1076</v>
+        <v>155</v>
       </c>
       <c r="E552" t="s">
-        <v>1077</v>
+        <v>156</v>
       </c>
       <c r="F552" s="1">
         <v>46294</v>
@@ -16729,16 +16777,16 @@
         <v>0</v>
       </c>
       <c r="B553" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C553" t="s">
+        <v>80</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E553" t="s">
         <v>1078</v>
-      </c>
-      <c r="C553" t="s">
-        <v>80</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E553" t="s">
-        <v>1080</v>
       </c>
       <c r="F553" s="1">
         <v>46294</v>
@@ -16752,16 +16800,16 @@
         <v>0</v>
       </c>
       <c r="B554" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C554" t="s">
+        <v>80</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E554" t="s">
         <v>1081</v>
-      </c>
-      <c r="C554" t="s">
-        <v>80</v>
-      </c>
-      <c r="D554" t="s">
-        <v>16</v>
-      </c>
-      <c r="E554" t="s">
-        <v>17</v>
       </c>
       <c r="F554" s="1">
         <v>46294</v>
@@ -16781,10 +16829,10 @@
         <v>80</v>
       </c>
       <c r="D555" t="s">
-        <v>1083</v>
+        <v>16</v>
       </c>
       <c r="E555" t="s">
-        <v>1084</v>
+        <v>17</v>
       </c>
       <c r="F555" s="1">
         <v>46294</v>
@@ -16798,16 +16846,16 @@
         <v>0</v>
       </c>
       <c r="B556" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C556" t="s">
+        <v>80</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E556" t="s">
         <v>1085</v>
-      </c>
-      <c r="C556" t="s">
-        <v>80</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E556" t="s">
-        <v>1087</v>
       </c>
       <c r="F556" s="1">
         <v>46294</v>
@@ -16818,979 +16866,979 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
+        <v>0</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C557" t="s">
+        <v>80</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E557" t="s">
         <v>1088</v>
       </c>
-      <c r="B557" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C557" t="s">
-        <v>2</v>
-      </c>
-      <c r="D557" t="s">
-        <v>200</v>
-      </c>
-      <c r="E557" t="s">
-        <v>201</v>
-      </c>
       <c r="F557" s="1">
-        <v>46148</v>
+        <v>46294</v>
       </c>
       <c r="G557" s="1">
-        <v>46149</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="B558" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C558" t="s">
+        <v>80</v>
+      </c>
+      <c r="D558" t="s">
         <v>1090</v>
       </c>
-      <c r="C558" t="s">
-        <v>2</v>
-      </c>
-      <c r="D558" t="s">
-        <v>112</v>
-      </c>
       <c r="E558" t="s">
-        <v>113</v>
+        <v>1091</v>
       </c>
       <c r="F558" s="1">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="G558" s="1">
-        <v>46268</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C559" t="s">
         <v>80</v>
       </c>
       <c r="D559" t="s">
-        <v>1092</v>
+        <v>699</v>
       </c>
       <c r="E559" t="s">
-        <v>1093</v>
+        <v>700</v>
       </c>
       <c r="F559" s="1">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="G559" s="1">
-        <v>46288</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>0</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C560" t="s">
+        <v>80</v>
+      </c>
+      <c r="D560" t="s">
         <v>1094</v>
       </c>
-      <c r="B560" t="s">
+      <c r="E560" t="s">
         <v>1095</v>
       </c>
-      <c r="C560" t="s">
-        <v>6</v>
-      </c>
-      <c r="D560" t="s">
-        <v>41</v>
-      </c>
-      <c r="E560" t="s">
-        <v>42</v>
-      </c>
       <c r="F560" s="1">
-        <v>46133</v>
+        <v>46294</v>
       </c>
       <c r="G560" s="1">
-        <v>46134</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B561" t="s">
         <v>1096</v>
       </c>
       <c r="C561" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D561" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="E561" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="F561" s="1">
-        <v>46134</v>
+        <v>46294</v>
       </c>
       <c r="G561" s="1">
-        <v>46134</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B562" t="s">
         <v>1097</v>
       </c>
       <c r="C562" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D562" t="s">
-        <v>19</v>
+        <v>1098</v>
       </c>
       <c r="E562" t="s">
-        <v>20</v>
+        <v>1099</v>
       </c>
       <c r="F562" s="1">
-        <v>46156</v>
+        <v>46294</v>
       </c>
       <c r="G562" s="1">
-        <v>46156</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C563" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D563" t="s">
-        <v>891</v>
+        <v>1101</v>
       </c>
       <c r="E563" t="s">
-        <v>892</v>
+        <v>1102</v>
       </c>
       <c r="F563" s="1">
-        <v>46195</v>
+        <v>46295</v>
       </c>
       <c r="G563" s="1">
-        <v>46195</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C564" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D564" t="s">
-        <v>1100</v>
+        <v>37</v>
       </c>
       <c r="E564" t="s">
-        <v>1101</v>
+        <v>38</v>
       </c>
       <c r="F564" s="1">
-        <v>46209</v>
+        <v>46295</v>
       </c>
       <c r="G564" s="1">
-        <v>46218</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C565" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D565" t="s">
-        <v>1103</v>
+        <v>37</v>
       </c>
       <c r="E565" t="s">
-        <v>1104</v>
+        <v>38</v>
       </c>
       <c r="F565" s="1">
-        <v>46213</v>
+        <v>46295</v>
       </c>
       <c r="G565" s="1">
-        <v>46213</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B566" t="s">
         <v>1105</v>
       </c>
       <c r="C566" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D566" t="s">
-        <v>1106</v>
+        <v>77</v>
       </c>
       <c r="E566" t="s">
-        <v>1107</v>
+        <v>78</v>
       </c>
       <c r="F566" s="1">
-        <v>46213</v>
+        <v>46295</v>
       </c>
       <c r="G566" s="1">
-        <v>46216</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C567" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D567" t="s">
-        <v>891</v>
+        <v>278</v>
       </c>
       <c r="E567" t="s">
-        <v>892</v>
+        <v>279</v>
       </c>
       <c r="F567" s="1">
-        <v>46223</v>
+        <v>46295</v>
       </c>
       <c r="G567" s="1">
-        <v>46223</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B568" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C568" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D568" t="s">
-        <v>1106</v>
+        <v>200</v>
       </c>
       <c r="E568" t="s">
-        <v>1107</v>
+        <v>201</v>
       </c>
       <c r="F568" s="1">
-        <v>46224</v>
+        <v>46148</v>
       </c>
       <c r="G568" s="1">
-        <v>46224</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B569" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C569" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D569" t="s">
-        <v>1004</v>
+        <v>112</v>
       </c>
       <c r="E569" t="s">
-        <v>1005</v>
+        <v>113</v>
       </c>
       <c r="F569" s="1">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="G569" s="1">
-        <v>46253</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B570" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C570" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D570" t="s">
-        <v>212</v>
+        <v>1090</v>
       </c>
       <c r="E570" t="s">
-        <v>213</v>
+        <v>1091</v>
       </c>
       <c r="F570" s="1">
-        <v>46273</v>
+        <v>46288</v>
       </c>
       <c r="G570" s="1">
-        <v>46274</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B571" t="s">
         <v>1112</v>
       </c>
       <c r="C571" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D571" t="s">
-        <v>1113</v>
+        <v>41</v>
       </c>
       <c r="E571" t="s">
-        <v>1114</v>
+        <v>42</v>
       </c>
       <c r="F571" s="1">
-        <v>46274</v>
+        <v>46133</v>
       </c>
       <c r="G571" s="1">
-        <v>46283</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B572" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C572" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D572" t="s">
-        <v>1106</v>
+        <v>41</v>
       </c>
       <c r="E572" t="s">
-        <v>1107</v>
+        <v>42</v>
       </c>
       <c r="F572" s="1">
-        <v>46276</v>
+        <v>46134</v>
       </c>
       <c r="G572" s="1">
-        <v>46289</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B573" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C573" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D573" t="s">
-        <v>414</v>
+        <v>19</v>
       </c>
       <c r="E573" t="s">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="F573" s="1">
-        <v>46284</v>
+        <v>46156</v>
       </c>
       <c r="G573" s="1">
-        <v>46286</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B574" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C574" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D574" t="s">
-        <v>1106</v>
+        <v>892</v>
       </c>
       <c r="E574" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
       <c r="F574" s="1">
-        <v>46289</v>
+        <v>46195</v>
       </c>
       <c r="G574" s="1">
-        <v>46289</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B575" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C575" t="s">
+        <v>96</v>
+      </c>
+      <c r="D575" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E575" t="s">
         <v>1118</v>
       </c>
-      <c r="C575" t="s">
-        <v>80</v>
-      </c>
-      <c r="D575" t="s">
-        <v>41</v>
-      </c>
-      <c r="E575" t="s">
-        <v>42</v>
-      </c>
       <c r="F575" s="1">
-        <v>46289</v>
+        <v>46209</v>
       </c>
       <c r="G575" s="1">
-        <v>46289</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B576" t="s">
         <v>1119</v>
       </c>
       <c r="C576" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D576" t="s">
-        <v>41</v>
+        <v>1120</v>
       </c>
       <c r="E576" t="s">
-        <v>42</v>
+        <v>1121</v>
       </c>
       <c r="F576" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
       <c r="G576" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B577" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C577" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D577" t="s">
-        <v>1100</v>
+        <v>1123</v>
       </c>
       <c r="E577" t="s">
-        <v>1101</v>
+        <v>1124</v>
       </c>
       <c r="F577" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
       <c r="G577" s="1">
-        <v>46289</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B578" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="C578" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D578" t="s">
-        <v>1100</v>
+        <v>892</v>
       </c>
       <c r="E578" t="s">
-        <v>1101</v>
+        <v>893</v>
       </c>
       <c r="F578" s="1">
-        <v>46290</v>
+        <v>46223</v>
       </c>
       <c r="G578" s="1">
-        <v>46290</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B579" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C579" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D579" t="s">
-        <v>341</v>
+        <v>1123</v>
       </c>
       <c r="E579" t="s">
-        <v>342</v>
+        <v>1124</v>
       </c>
       <c r="F579" s="1">
-        <v>46293</v>
+        <v>46224</v>
       </c>
       <c r="G579" s="1">
-        <v>46293</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B580" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C580" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D580" t="s">
-        <v>891</v>
+        <v>1005</v>
       </c>
       <c r="E580" t="s">
-        <v>892</v>
+        <v>1006</v>
       </c>
       <c r="F580" s="1">
-        <v>46293</v>
+        <v>46253</v>
       </c>
       <c r="G580" s="1">
-        <v>46293</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B581" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C581" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D581" t="s">
-        <v>891</v>
+        <v>212</v>
       </c>
       <c r="E581" t="s">
-        <v>892</v>
+        <v>213</v>
       </c>
       <c r="F581" s="1">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="G581" s="1">
-        <v>46293</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B582" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="C582" t="s">
         <v>80</v>
       </c>
       <c r="D582" t="s">
-        <v>212</v>
+        <v>1130</v>
       </c>
       <c r="E582" t="s">
-        <v>213</v>
+        <v>1131</v>
       </c>
       <c r="F582" s="1">
-        <v>46293</v>
+        <v>46274</v>
       </c>
       <c r="G582" s="1">
-        <v>46293</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B583" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="C583" t="s">
         <v>80</v>
       </c>
       <c r="D583" t="s">
-        <v>1004</v>
+        <v>1123</v>
       </c>
       <c r="E583" t="s">
-        <v>1005</v>
+        <v>1124</v>
       </c>
       <c r="F583" s="1">
-        <v>46294</v>
+        <v>46276</v>
       </c>
       <c r="G583" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B584" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="C584" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D584" t="s">
-        <v>968</v>
+        <v>415</v>
       </c>
       <c r="E584" t="s">
-        <v>969</v>
+        <v>416</v>
       </c>
       <c r="F584" s="1">
-        <v>46294</v>
+        <v>46284</v>
       </c>
       <c r="G584" s="1">
-        <v>46294</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B585" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C585" t="s">
         <v>80</v>
       </c>
       <c r="D585" t="s">
-        <v>1106</v>
+        <v>1123</v>
       </c>
       <c r="E585" t="s">
-        <v>1107</v>
+        <v>1124</v>
       </c>
       <c r="F585" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="G585" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="B586" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="C586" t="s">
         <v>80</v>
       </c>
       <c r="D586" t="s">
-        <v>1106</v>
+        <v>41</v>
       </c>
       <c r="E586" t="s">
-        <v>1107</v>
+        <v>42</v>
       </c>
       <c r="F586" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="G586" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B587" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="C587" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D587" t="s">
-        <v>1132</v>
+        <v>41</v>
       </c>
       <c r="E587" t="s">
-        <v>1133</v>
+        <v>42</v>
       </c>
       <c r="F587" s="1">
-        <v>46063</v>
+        <v>46289</v>
       </c>
       <c r="G587" s="1">
-        <v>46064</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B588" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C588" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D588" t="s">
-        <v>57</v>
+        <v>1117</v>
       </c>
       <c r="E588" t="s">
-        <v>58</v>
+        <v>1118</v>
       </c>
       <c r="F588" s="1">
-        <v>46113</v>
+        <v>46289</v>
       </c>
       <c r="G588" s="1">
-        <v>46125</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B589" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="C589" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D589" t="s">
-        <v>57</v>
+        <v>1117</v>
       </c>
       <c r="E589" t="s">
-        <v>58</v>
+        <v>1118</v>
       </c>
       <c r="F589" s="1">
-        <v>46125</v>
+        <v>46290</v>
       </c>
       <c r="G589" s="1">
-        <v>46125</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B590" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C590" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D590" t="s">
-        <v>57</v>
+        <v>341</v>
       </c>
       <c r="E590" t="s">
-        <v>58</v>
+        <v>342</v>
       </c>
       <c r="F590" s="1">
-        <v>46126</v>
+        <v>46293</v>
       </c>
       <c r="G590" s="1">
-        <v>46126</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B591" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="C591" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D591" t="s">
-        <v>57</v>
+        <v>892</v>
       </c>
       <c r="E591" t="s">
-        <v>58</v>
+        <v>893</v>
       </c>
       <c r="F591" s="1">
-        <v>46126</v>
+        <v>46293</v>
       </c>
       <c r="G591" s="1">
-        <v>46126</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B592" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C592" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D592" t="s">
-        <v>57</v>
+        <v>892</v>
       </c>
       <c r="E592" t="s">
-        <v>58</v>
+        <v>893</v>
       </c>
       <c r="F592" s="1">
-        <v>46128</v>
+        <v>46293</v>
       </c>
       <c r="G592" s="1">
-        <v>46128</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B593" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="C593" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D593" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="E593" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="F593" s="1">
-        <v>46132</v>
+        <v>46293</v>
       </c>
       <c r="G593" s="1">
-        <v>46132</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B594" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C594" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D594" t="s">
-        <v>57</v>
+        <v>1005</v>
       </c>
       <c r="E594" t="s">
-        <v>58</v>
+        <v>1006</v>
       </c>
       <c r="F594" s="1">
-        <v>46161</v>
+        <v>46294</v>
       </c>
       <c r="G594" s="1">
-        <v>46161</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B595" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="C595" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D595" t="s">
-        <v>57</v>
+        <v>969</v>
       </c>
       <c r="E595" t="s">
-        <v>58</v>
+        <v>970</v>
       </c>
       <c r="F595" s="1">
-        <v>46174</v>
+        <v>46294</v>
       </c>
       <c r="G595" s="1">
-        <v>46174</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B596" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C596" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D596" t="s">
-        <v>57</v>
+        <v>1123</v>
       </c>
       <c r="E596" t="s">
-        <v>58</v>
+        <v>1124</v>
       </c>
       <c r="F596" s="1">
-        <v>46174</v>
+        <v>46294</v>
       </c>
       <c r="G596" s="1">
-        <v>46174</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="B597" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="C597" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D597" t="s">
-        <v>57</v>
+        <v>1123</v>
       </c>
       <c r="E597" t="s">
-        <v>58</v>
+        <v>1124</v>
       </c>
       <c r="F597" s="1">
-        <v>46195</v>
+        <v>46294</v>
       </c>
       <c r="G597" s="1">
-        <v>46252</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B598" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C598" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D598" t="s">
-        <v>57</v>
+        <v>1149</v>
       </c>
       <c r="E598" t="s">
-        <v>58</v>
+        <v>1150</v>
       </c>
       <c r="F598" s="1">
-        <v>46210</v>
+        <v>46063</v>
       </c>
       <c r="G598" s="1">
-        <v>46210</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B599" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C599" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D599" t="s">
         <v>57</v>
@@ -17799,21 +17847,21 @@
         <v>58</v>
       </c>
       <c r="F599" s="1">
-        <v>46213</v>
+        <v>46113</v>
       </c>
       <c r="G599" s="1">
-        <v>46213</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B600" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C600" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D600" t="s">
         <v>57</v>
@@ -17822,44 +17870,44 @@
         <v>58</v>
       </c>
       <c r="F600" s="1">
-        <v>46218</v>
+        <v>46125</v>
       </c>
       <c r="G600" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B601" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="C601" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D601" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E601" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F601" s="1">
-        <v>46226</v>
+        <v>46126</v>
       </c>
       <c r="G601" s="1">
-        <v>46226</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B602" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="C602" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D602" t="s">
         <v>57</v>
@@ -17868,21 +17916,21 @@
         <v>58</v>
       </c>
       <c r="F602" s="1">
-        <v>46227</v>
+        <v>46126</v>
       </c>
       <c r="G602" s="1">
-        <v>46252</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B603" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="C603" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D603" t="s">
         <v>57</v>
@@ -17891,18 +17939,18 @@
         <v>58</v>
       </c>
       <c r="F603" s="1">
-        <v>46227</v>
+        <v>46128</v>
       </c>
       <c r="G603" s="1">
-        <v>46252</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B604" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="C604" t="s">
         <v>6</v>
@@ -17914,44 +17962,44 @@
         <v>58</v>
       </c>
       <c r="F604" s="1">
-        <v>46227</v>
+        <v>46132</v>
       </c>
       <c r="G604" s="1">
-        <v>46228</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B605" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C605" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D605" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E605" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F605" s="1">
-        <v>46230</v>
+        <v>46161</v>
       </c>
       <c r="G605" s="1">
-        <v>46252</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B606" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="C606" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D606" t="s">
         <v>57</v>
@@ -17960,21 +18008,21 @@
         <v>58</v>
       </c>
       <c r="F606" s="1">
-        <v>46231</v>
+        <v>46174</v>
       </c>
       <c r="G606" s="1">
-        <v>46231</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B607" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="C607" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D607" t="s">
         <v>57</v>
@@ -17983,21 +18031,21 @@
         <v>58</v>
       </c>
       <c r="F607" s="1">
-        <v>46254</v>
+        <v>46174</v>
       </c>
       <c r="G607" s="1">
-        <v>46254</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B608" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="C608" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D608" t="s">
         <v>57</v>
@@ -18006,18 +18054,18 @@
         <v>58</v>
       </c>
       <c r="F608" s="1">
-        <v>46255</v>
+        <v>46195</v>
       </c>
       <c r="G608" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B609" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="C609" t="s">
         <v>6</v>
@@ -18029,21 +18077,21 @@
         <v>58</v>
       </c>
       <c r="F609" s="1">
-        <v>46260</v>
+        <v>46210</v>
       </c>
       <c r="G609" s="1">
-        <v>46260</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B610" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C610" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D610" t="s">
         <v>57</v>
@@ -18052,21 +18100,21 @@
         <v>58</v>
       </c>
       <c r="F610" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
       <c r="G610" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B611" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="C611" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D611" t="s">
         <v>57</v>
@@ -18075,41 +18123,41 @@
         <v>58</v>
       </c>
       <c r="F611" s="1">
-        <v>46289</v>
+        <v>46218</v>
       </c>
       <c r="G611" s="1">
-        <v>46294</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B612" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="C612" t="s">
         <v>6</v>
       </c>
       <c r="D612" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E612" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F612" s="1">
-        <v>46294</v>
+        <v>46226</v>
       </c>
       <c r="G612" s="1">
-        <v>46294</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>1130</v>
+        <v>1147</v>
       </c>
       <c r="B613" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="C613" t="s">
         <v>80</v>
@@ -18121,142 +18169,142 @@
         <v>58</v>
       </c>
       <c r="F613" s="1">
-        <v>46294</v>
+        <v>46227</v>
       </c>
       <c r="G613" s="1">
-        <v>46294</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B614" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="C614" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D614" t="s">
-        <v>1162</v>
+        <v>57</v>
       </c>
       <c r="E614" t="s">
-        <v>1163</v>
+        <v>58</v>
       </c>
       <c r="F614" s="1">
-        <v>46157</v>
+        <v>46227</v>
       </c>
       <c r="G614" s="1">
-        <v>46157</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B615" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C615" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D615" t="s">
-        <v>1165</v>
+        <v>57</v>
       </c>
       <c r="E615" t="s">
-        <v>1166</v>
+        <v>58</v>
       </c>
       <c r="F615" s="1">
-        <v>46168</v>
+        <v>46227</v>
       </c>
       <c r="G615" s="1">
-        <v>46170</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B616" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C616" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D616" t="s">
-        <v>1162</v>
+        <v>77</v>
       </c>
       <c r="E616" t="s">
-        <v>1163</v>
+        <v>78</v>
       </c>
       <c r="F616" s="1">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="G616" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B617" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C617" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D617" t="s">
-        <v>1162</v>
+        <v>57</v>
       </c>
       <c r="E617" t="s">
-        <v>1163</v>
+        <v>58</v>
       </c>
       <c r="F617" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="G617" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B618" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C618" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D618" t="s">
-        <v>1170</v>
+        <v>57</v>
       </c>
       <c r="E618" t="s">
-        <v>1171</v>
+        <v>58</v>
       </c>
       <c r="F618" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="G618" s="1">
-        <v>46247</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B619" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C619" t="s">
         <v>2</v>
       </c>
       <c r="D619" t="s">
-        <v>1162</v>
+        <v>57</v>
       </c>
       <c r="E619" t="s">
-        <v>1163</v>
+        <v>58</v>
       </c>
       <c r="F619" s="1">
         <v>46255</v>
@@ -18267,116 +18315,346 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B620" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C620" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D620" t="s">
-        <v>1162</v>
+        <v>57</v>
       </c>
       <c r="E620" t="s">
-        <v>1163</v>
+        <v>58</v>
       </c>
       <c r="F620" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="G620" s="1">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B621" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C621" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D621" t="s">
-        <v>1162</v>
+        <v>57</v>
       </c>
       <c r="E621" t="s">
-        <v>1163</v>
+        <v>58</v>
       </c>
       <c r="F621" s="1">
-        <v>46262</v>
+        <v>46289</v>
       </c>
       <c r="G621" s="1">
-        <v>46265</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B622" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C622" t="s">
         <v>6</v>
       </c>
       <c r="D622" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E622" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F622" s="1">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="G622" s="1">
-        <v>46283</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B623" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C623" t="s">
         <v>80</v>
       </c>
       <c r="D623" t="s">
-        <v>924</v>
+        <v>57</v>
       </c>
       <c r="E623" t="s">
-        <v>925</v>
+        <v>58</v>
       </c>
       <c r="F623" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="G623" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="B624" t="s">
         <v>1177</v>
       </c>
       <c r="C624" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D624" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E624" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F624" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G624" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A625" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C625" t="s">
+        <v>2</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F625" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G625" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A626" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C626" t="s">
+        <v>2</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E626" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F626" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G626" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A627" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C627" t="s">
+        <v>2</v>
+      </c>
+      <c r="D627" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E627" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F627" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G627" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A628" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C628" t="s">
+        <v>2</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E628" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F628" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G628" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A629" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C629" t="s">
+        <v>2</v>
+      </c>
+      <c r="D629" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E629" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F629" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G629" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A630" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C630" t="s">
+        <v>2</v>
+      </c>
+      <c r="D630" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E630" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F630" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G630" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A631" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C631" t="s">
+        <v>2</v>
+      </c>
+      <c r="D631" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E631" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F631" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G631" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A632" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C632" t="s">
+        <v>6</v>
+      </c>
+      <c r="D632" t="s">
+        <v>13</v>
+      </c>
+      <c r="E632" t="s">
+        <v>14</v>
+      </c>
+      <c r="F632" s="1">
+        <v>46281</v>
+      </c>
+      <c r="G632" s="1">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A633" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C633" t="s">
+        <v>80</v>
+      </c>
+      <c r="D633" t="s">
+        <v>925</v>
+      </c>
+      <c r="E633" t="s">
+        <v>926</v>
+      </c>
+      <c r="F633" s="1">
+        <v>46286</v>
+      </c>
+      <c r="G633" s="1">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A634" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C634" t="s">
+        <v>80</v>
+      </c>
+      <c r="D634" t="s">
         <v>98</v>
       </c>
-      <c r="E624" t="s">
+      <c r="E634" t="s">
         <v>99</v>
       </c>
-      <c r="F624" s="1">
+      <c r="F634" s="1">
         <v>46289</v>
       </c>
-      <c r="G624" s="1">
+      <c r="G634" s="1">
         <v>46290</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB124B78-91C8-45CE-8A9B-E5A31D937093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59A825F2-9151-4107-AA5E-81FF6269FF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{10659DCE-AFA0-42E0-A2F0-BEF5F2A0F442}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{59BFD859-169D-4D95-8EF9-465B517AD1D0}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3037" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="1187">
   <si>
     <t>0001</t>
   </si>
@@ -3223,6 +3223,9 @@
     <t xml:space="preserve">  216822</t>
   </si>
   <si>
+    <t xml:space="preserve">  216823</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216824</t>
   </si>
   <si>
@@ -3244,6 +3247,90 @@
     <t xml:space="preserve">  216828</t>
   </si>
   <si>
+    <t xml:space="preserve">  216830</t>
+  </si>
+  <si>
+    <t>VC09</t>
+  </si>
+  <si>
+    <t>VICENTELLI CARLOS ROBERTO - CASA DIVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216848</t>
+  </si>
+  <si>
+    <t>MF13</t>
+  </si>
+  <si>
+    <t>MAS FERRETERIAS S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216849</t>
+  </si>
+  <si>
+    <t>HC03</t>
+  </si>
+  <si>
+    <t>HIJOS DE RAFAEL CONTI S.A. - CONTI MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216850</t>
+  </si>
+  <si>
+    <t>GL08</t>
+  </si>
+  <si>
+    <t>GUTIERREZ LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  216851</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -3310,9 +3397,6 @@
     <t xml:space="preserve">    2959</t>
   </si>
   <si>
-    <t xml:space="preserve">    2974</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2977</t>
   </si>
   <si>
@@ -3325,13 +3409,7 @@
     <t xml:space="preserve">    2992</t>
   </si>
   <si>
-    <t xml:space="preserve">    2994</t>
-  </si>
-  <si>
-    <t>PA01</t>
-  </si>
-  <si>
-    <t>VARIOS</t>
+    <t xml:space="preserve">    2996</t>
   </si>
   <si>
     <t>4444</t>
@@ -3418,10 +3496,13 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2675</t>
+    <t xml:space="preserve">    2686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2689</t>
   </si>
   <si>
     <t>9999</t>
@@ -3949,31 +4030,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C06B3F2-EB6E-462E-BBD0-666D451C5748}">
-  <dimension ref="A1:G607"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DDFE0BE-7CA2-47A9-9B7D-D36B993F240A}">
+  <dimension ref="A1:G628"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1159</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -5847,7 +5928,7 @@
         <v>206</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D83" t="s">
         <v>37</v>
@@ -5985,7 +6066,7 @@
         <v>220</v>
       </c>
       <c r="C89" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D89" t="s">
         <v>37</v>
@@ -6238,7 +6319,7 @@
         <v>241</v>
       </c>
       <c r="C100" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D100" t="s">
         <v>37</v>
@@ -6284,7 +6365,7 @@
         <v>243</v>
       </c>
       <c r="C102" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
@@ -6491,7 +6572,7 @@
         <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D111" t="s">
         <v>140</v>
@@ -6652,7 +6733,7 @@
         <v>281</v>
       </c>
       <c r="C118" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D118" t="s">
         <v>140</v>
@@ -6721,7 +6802,7 @@
         <v>288</v>
       </c>
       <c r="C121" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
         <v>289</v>
@@ -6836,7 +6917,7 @@
         <v>297</v>
       </c>
       <c r="C126" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D126" t="s">
         <v>298</v>
@@ -6859,7 +6940,7 @@
         <v>300</v>
       </c>
       <c r="C127" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D127" t="s">
         <v>140</v>
@@ -6882,7 +6963,7 @@
         <v>301</v>
       </c>
       <c r="C128" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D128" t="s">
         <v>140</v>
@@ -7503,7 +7584,7 @@
         <v>340</v>
       </c>
       <c r="C155" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D155" t="s">
         <v>37</v>
@@ -7572,7 +7653,7 @@
         <v>347</v>
       </c>
       <c r="C158" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
         <v>348</v>
@@ -7710,7 +7791,7 @@
         <v>361</v>
       </c>
       <c r="C164" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D164" t="s">
         <v>16</v>
@@ -7756,7 +7837,7 @@
         <v>365</v>
       </c>
       <c r="C166" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
         <v>223</v>
@@ -8193,7 +8274,7 @@
         <v>400</v>
       </c>
       <c r="C185" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D185" t="s">
         <v>37</v>
@@ -8699,7 +8780,7 @@
         <v>452</v>
       </c>
       <c r="C207" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D207" t="s">
         <v>185</v>
@@ -8860,7 +8941,7 @@
         <v>469</v>
       </c>
       <c r="C214" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D214" t="s">
         <v>470</v>
@@ -8952,7 +9033,7 @@
         <v>477</v>
       </c>
       <c r="C218" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D218" t="s">
         <v>37</v>
@@ -9343,7 +9424,7 @@
         <v>516</v>
       </c>
       <c r="C235" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D235" t="s">
         <v>517</v>
@@ -9527,7 +9608,7 @@
         <v>532</v>
       </c>
       <c r="C243" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D243" t="s">
         <v>140</v>
@@ -9803,7 +9884,7 @@
         <v>548</v>
       </c>
       <c r="C255" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D255" t="s">
         <v>37</v>
@@ -10148,7 +10229,7 @@
         <v>585</v>
       </c>
       <c r="C270" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D270" t="s">
         <v>586</v>
@@ -10240,7 +10321,7 @@
         <v>593</v>
       </c>
       <c r="C274" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D274" t="s">
         <v>48</v>
@@ -10378,7 +10459,7 @@
         <v>603</v>
       </c>
       <c r="C280" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D280" t="s">
         <v>604</v>
@@ -10401,7 +10482,7 @@
         <v>606</v>
       </c>
       <c r="C281" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D281" t="s">
         <v>604</v>
@@ -10424,7 +10505,7 @@
         <v>607</v>
       </c>
       <c r="C282" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D282" t="s">
         <v>608</v>
@@ -10516,7 +10597,7 @@
         <v>615</v>
       </c>
       <c r="C286" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D286" t="s">
         <v>616</v>
@@ -10608,7 +10689,7 @@
         <v>627</v>
       </c>
       <c r="C290" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D290" t="s">
         <v>37</v>
@@ -10631,7 +10712,7 @@
         <v>628</v>
       </c>
       <c r="C291" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D291" t="s">
         <v>37</v>
@@ -10838,7 +10919,7 @@
         <v>641</v>
       </c>
       <c r="C300" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D300" t="s">
         <v>642</v>
@@ -10861,7 +10942,7 @@
         <v>644</v>
       </c>
       <c r="C301" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D301" t="s">
         <v>517</v>
@@ -11275,7 +11356,7 @@
         <v>690</v>
       </c>
       <c r="C319" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D319" t="s">
         <v>691</v>
@@ -11321,7 +11402,7 @@
         <v>696</v>
       </c>
       <c r="C321" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D321" t="s">
         <v>81</v>
@@ -11620,7 +11701,7 @@
         <v>711</v>
       </c>
       <c r="C334" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D334" t="s">
         <v>712</v>
@@ -11643,7 +11724,7 @@
         <v>714</v>
       </c>
       <c r="C335" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D335" t="s">
         <v>715</v>
@@ -11758,7 +11839,7 @@
         <v>727</v>
       </c>
       <c r="C340" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D340" t="s">
         <v>172</v>
@@ -11804,7 +11885,7 @@
         <v>731</v>
       </c>
       <c r="C342" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D342" t="s">
         <v>200</v>
@@ -11896,7 +11977,7 @@
         <v>735</v>
       </c>
       <c r="C346" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D346" t="s">
         <v>179</v>
@@ -11942,7 +12023,7 @@
         <v>737</v>
       </c>
       <c r="C348" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D348" t="s">
         <v>16</v>
@@ -11988,7 +12069,7 @@
         <v>741</v>
       </c>
       <c r="C350" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D350" t="s">
         <v>172</v>
@@ -12011,7 +12092,7 @@
         <v>742</v>
       </c>
       <c r="C351" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D351" t="s">
         <v>172</v>
@@ -12034,7 +12115,7 @@
         <v>743</v>
       </c>
       <c r="C352" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D352" t="s">
         <v>223</v>
@@ -12195,7 +12276,7 @@
         <v>754</v>
       </c>
       <c r="C359" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D359" t="s">
         <v>81</v>
@@ -12287,7 +12368,7 @@
         <v>760</v>
       </c>
       <c r="C363" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D363" t="s">
         <v>761</v>
@@ -12402,7 +12483,7 @@
         <v>767</v>
       </c>
       <c r="C368" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D368" t="s">
         <v>37</v>
@@ -12471,7 +12552,7 @@
         <v>772</v>
       </c>
       <c r="C371" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D371" t="s">
         <v>87</v>
@@ -12517,7 +12598,7 @@
         <v>774</v>
       </c>
       <c r="C373" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D373" t="s">
         <v>87</v>
@@ -12563,7 +12644,7 @@
         <v>776</v>
       </c>
       <c r="C375" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D375" t="s">
         <v>87</v>
@@ -13368,7 +13449,7 @@
         <v>839</v>
       </c>
       <c r="C410" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D410" t="s">
         <v>840</v>
@@ -13414,7 +13495,7 @@
         <v>843</v>
       </c>
       <c r="C412" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D412" t="s">
         <v>844</v>
@@ -13552,7 +13633,7 @@
         <v>859</v>
       </c>
       <c r="C418" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D418" t="s">
         <v>185</v>
@@ -13667,7 +13748,7 @@
         <v>868</v>
       </c>
       <c r="C423" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D423" t="s">
         <v>869</v>
@@ -13736,7 +13817,7 @@
         <v>875</v>
       </c>
       <c r="C426" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D426" t="s">
         <v>876</v>
@@ -13782,7 +13863,7 @@
         <v>879</v>
       </c>
       <c r="C428" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D428" t="s">
         <v>16</v>
@@ -14265,7 +14346,7 @@
         <v>916</v>
       </c>
       <c r="C449" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D449" t="s">
         <v>185</v>
@@ -14334,7 +14415,7 @@
         <v>921</v>
       </c>
       <c r="C452" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D452" t="s">
         <v>922</v>
@@ -14380,7 +14461,7 @@
         <v>927</v>
       </c>
       <c r="C454" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D454" t="s">
         <v>470</v>
@@ -14449,7 +14530,7 @@
         <v>934</v>
       </c>
       <c r="C457" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D457" t="s">
         <v>935</v>
@@ -14495,7 +14576,7 @@
         <v>938</v>
       </c>
       <c r="C459" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D459" t="s">
         <v>939</v>
@@ -14518,7 +14599,7 @@
         <v>941</v>
       </c>
       <c r="C460" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D460" t="s">
         <v>942</v>
@@ -14541,7 +14622,7 @@
         <v>944</v>
       </c>
       <c r="C461" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D461" t="s">
         <v>945</v>
@@ -14564,7 +14645,7 @@
         <v>947</v>
       </c>
       <c r="C462" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D462" t="s">
         <v>948</v>
@@ -14587,7 +14668,7 @@
         <v>950</v>
       </c>
       <c r="C463" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D463" t="s">
         <v>655</v>
@@ -14633,7 +14714,7 @@
         <v>952</v>
       </c>
       <c r="C465" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D465" t="s">
         <v>953</v>
@@ -14656,7 +14737,7 @@
         <v>955</v>
       </c>
       <c r="C466" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D466" t="s">
         <v>945</v>
@@ -14702,7 +14783,7 @@
         <v>957</v>
       </c>
       <c r="C468" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D468" t="s">
         <v>140</v>
@@ -14771,7 +14852,7 @@
         <v>960</v>
       </c>
       <c r="C471" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D471" t="s">
         <v>140</v>
@@ -14794,7 +14875,7 @@
         <v>961</v>
       </c>
       <c r="C472" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D472" t="s">
         <v>140</v>
@@ -14817,7 +14898,7 @@
         <v>962</v>
       </c>
       <c r="C473" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D473" t="s">
         <v>608</v>
@@ -14840,7 +14921,7 @@
         <v>963</v>
       </c>
       <c r="C474" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D474" t="s">
         <v>608</v>
@@ -14863,7 +14944,7 @@
         <v>964</v>
       </c>
       <c r="C475" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D475" t="s">
         <v>608</v>
@@ -14886,7 +14967,7 @@
         <v>965</v>
       </c>
       <c r="C476" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D476" t="s">
         <v>608</v>
@@ -14909,7 +14990,7 @@
         <v>966</v>
       </c>
       <c r="C477" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D477" t="s">
         <v>967</v>
@@ -15208,7 +15289,7 @@
         <v>983</v>
       </c>
       <c r="C490" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D490" t="s">
         <v>45</v>
@@ -15231,7 +15312,7 @@
         <v>984</v>
       </c>
       <c r="C491" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D491" t="s">
         <v>45</v>
@@ -16220,7 +16301,7 @@
         <v>1045</v>
       </c>
       <c r="C534" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D534" t="s">
         <v>608</v>
@@ -16499,16 +16580,16 @@
         <v>80</v>
       </c>
       <c r="D546" t="s">
-        <v>918</v>
+        <v>608</v>
       </c>
       <c r="E546" t="s">
-        <v>919</v>
+        <v>609</v>
       </c>
       <c r="F546" s="1">
         <v>46296</v>
       </c>
       <c r="G546" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.2">
@@ -16522,10 +16603,10 @@
         <v>80</v>
       </c>
       <c r="D547" t="s">
-        <v>847</v>
+        <v>918</v>
       </c>
       <c r="E547" t="s">
-        <v>848</v>
+        <v>919</v>
       </c>
       <c r="F547" s="1">
         <v>46296</v>
@@ -16568,10 +16649,10 @@
         <v>80</v>
       </c>
       <c r="D549" t="s">
-        <v>1071</v>
+        <v>847</v>
       </c>
       <c r="E549" t="s">
-        <v>1072</v>
+        <v>848</v>
       </c>
       <c r="F549" s="1">
         <v>46296</v>
@@ -16585,16 +16666,16 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C550" t="s">
+        <v>80</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E550" t="s">
         <v>1073</v>
-      </c>
-      <c r="C550" t="s">
-        <v>80</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1072</v>
       </c>
       <c r="F550" s="1">
         <v>46296</v>
@@ -16605,122 +16686,122 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
+        <v>0</v>
+      </c>
+      <c r="B551" t="s">
         <v>1074</v>
       </c>
-      <c r="B551" t="s">
-        <v>1075</v>
-      </c>
       <c r="C551" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D551" t="s">
-        <v>200</v>
+        <v>1072</v>
       </c>
       <c r="E551" t="s">
-        <v>201</v>
+        <v>1073</v>
       </c>
       <c r="F551" s="1">
-        <v>46148</v>
+        <v>46296</v>
       </c>
       <c r="G551" s="1">
-        <v>46149</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="B552" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C552" t="s">
+        <v>80</v>
+      </c>
+      <c r="D552" t="s">
         <v>1076</v>
       </c>
-      <c r="C552" t="s">
-        <v>2</v>
-      </c>
-      <c r="D552" t="s">
-        <v>112</v>
-      </c>
       <c r="E552" t="s">
-        <v>113</v>
+        <v>1077</v>
       </c>
       <c r="F552" s="1">
-        <v>46268</v>
+        <v>46296</v>
       </c>
       <c r="G552" s="1">
-        <v>46268</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B553" t="s">
         <v>1078</v>
       </c>
       <c r="C553" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D553" t="s">
-        <v>41</v>
+        <v>761</v>
       </c>
       <c r="E553" t="s">
-        <v>42</v>
+        <v>762</v>
       </c>
       <c r="F553" s="1">
-        <v>46133</v>
+        <v>46296</v>
       </c>
       <c r="G553" s="1">
-        <v>46134</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B554" t="s">
         <v>1079</v>
       </c>
       <c r="C554" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D554" t="s">
-        <v>41</v>
+        <v>1061</v>
       </c>
       <c r="E554" t="s">
-        <v>42</v>
+        <v>1062</v>
       </c>
       <c r="F554" s="1">
-        <v>46134</v>
+        <v>46296</v>
       </c>
       <c r="G554" s="1">
-        <v>46134</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B555" t="s">
         <v>1080</v>
       </c>
       <c r="C555" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D555" t="s">
-        <v>19</v>
+        <v>1022</v>
       </c>
       <c r="E555" t="s">
-        <v>20</v>
+        <v>1023</v>
       </c>
       <c r="F555" s="1">
-        <v>46156</v>
+        <v>46296</v>
       </c>
       <c r="G555" s="1">
-        <v>46156</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B556" t="s">
         <v>1081</v>
@@ -16729,832 +16810,832 @@
         <v>80</v>
       </c>
       <c r="D556" t="s">
-        <v>1001</v>
+        <v>146</v>
       </c>
       <c r="E556" t="s">
-        <v>1002</v>
+        <v>147</v>
       </c>
       <c r="F556" s="1">
-        <v>46195</v>
+        <v>46296</v>
       </c>
       <c r="G556" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B557" t="s">
         <v>1082</v>
       </c>
       <c r="C557" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D557" t="s">
-        <v>1083</v>
+        <v>304</v>
       </c>
       <c r="E557" t="s">
-        <v>1084</v>
+        <v>305</v>
       </c>
       <c r="F557" s="1">
-        <v>46209</v>
+        <v>46297</v>
       </c>
       <c r="G557" s="1">
-        <v>46218</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C558" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D558" t="s">
-        <v>939</v>
+        <v>807</v>
       </c>
       <c r="E558" t="s">
-        <v>940</v>
+        <v>808</v>
       </c>
       <c r="F558" s="1">
-        <v>46213</v>
+        <v>46297</v>
       </c>
       <c r="G558" s="1">
-        <v>46213</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C559" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D559" t="s">
-        <v>1087</v>
+        <v>460</v>
       </c>
       <c r="E559" t="s">
-        <v>1088</v>
+        <v>461</v>
       </c>
       <c r="F559" s="1">
-        <v>46213</v>
+        <v>46297</v>
       </c>
       <c r="G559" s="1">
-        <v>46216</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C560" t="s">
         <v>80</v>
       </c>
       <c r="D560" t="s">
-        <v>1001</v>
+        <v>25</v>
       </c>
       <c r="E560" t="s">
-        <v>1002</v>
+        <v>26</v>
       </c>
       <c r="F560" s="1">
-        <v>46223</v>
+        <v>46297</v>
       </c>
       <c r="G560" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C561" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D561" t="s">
-        <v>1087</v>
+        <v>37</v>
       </c>
       <c r="E561" t="s">
-        <v>1088</v>
+        <v>38</v>
       </c>
       <c r="F561" s="1">
-        <v>46224</v>
+        <v>46297</v>
       </c>
       <c r="G561" s="1">
-        <v>46224</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C562" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D562" t="s">
-        <v>1092</v>
+        <v>37</v>
       </c>
       <c r="E562" t="s">
-        <v>1093</v>
+        <v>38</v>
       </c>
       <c r="F562" s="1">
-        <v>46253</v>
+        <v>46297</v>
       </c>
       <c r="G562" s="1">
-        <v>46253</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="C563" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D563" t="s">
-        <v>212</v>
+        <v>492</v>
       </c>
       <c r="E563" t="s">
-        <v>213</v>
+        <v>493</v>
       </c>
       <c r="F563" s="1">
-        <v>46273</v>
+        <v>46297</v>
       </c>
       <c r="G563" s="1">
-        <v>46274</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="C564" t="s">
         <v>80</v>
       </c>
       <c r="D564" t="s">
-        <v>354</v>
+        <v>492</v>
       </c>
       <c r="E564" t="s">
-        <v>355</v>
+        <v>493</v>
       </c>
       <c r="F564" s="1">
-        <v>46284</v>
+        <v>46297</v>
       </c>
       <c r="G564" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="C565" t="s">
         <v>80</v>
       </c>
       <c r="D565" t="s">
-        <v>1087</v>
+        <v>143</v>
       </c>
       <c r="E565" t="s">
-        <v>1088</v>
+        <v>144</v>
       </c>
       <c r="F565" s="1">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="G565" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="C566" t="s">
         <v>80</v>
       </c>
       <c r="D566" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="E566" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="F566" s="1">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="G566" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="C567" t="s">
         <v>80</v>
       </c>
       <c r="D567" t="s">
-        <v>304</v>
+        <v>48</v>
       </c>
       <c r="E567" t="s">
-        <v>305</v>
+        <v>49</v>
       </c>
       <c r="F567" s="1">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G567" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B568" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="C568" t="s">
         <v>80</v>
       </c>
       <c r="D568" t="s">
-        <v>756</v>
+        <v>1094</v>
       </c>
       <c r="E568" t="s">
-        <v>757</v>
+        <v>1095</v>
       </c>
       <c r="F568" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="G568" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C569" t="s">
         <v>80</v>
       </c>
       <c r="D569" t="s">
-        <v>1083</v>
+        <v>1097</v>
       </c>
       <c r="E569" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="F569" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G569" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="B570" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C570" t="s">
+        <v>80</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E570" t="s">
         <v>1101</v>
       </c>
-      <c r="C570" t="s">
-        <v>80</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E570" t="s">
-        <v>1103</v>
-      </c>
       <c r="F570" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="G570" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="B571" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C571" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D571" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="E571" t="s">
-        <v>1107</v>
+        <v>17</v>
       </c>
       <c r="F571" s="1">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="G571" s="1">
-        <v>46064</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B572" t="s">
         <v>1104</v>
       </c>
-      <c r="B572" t="s">
-        <v>1108</v>
-      </c>
       <c r="C572" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D572" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="E572" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="F572" s="1">
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="G572" s="1">
-        <v>46125</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B573" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C573" t="s">
         <v>2</v>
       </c>
       <c r="D573" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E573" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="F573" s="1">
-        <v>46125</v>
+        <v>46268</v>
       </c>
       <c r="G573" s="1">
-        <v>46125</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B574" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="C574" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D574" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E574" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F574" s="1">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="G574" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B575" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C575" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D575" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E575" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F575" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="G575" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B576" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C576" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D576" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E576" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F576" s="1">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="G576" s="1">
-        <v>46128</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B577" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C577" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D577" t="s">
-        <v>57</v>
+        <v>1001</v>
       </c>
       <c r="E577" t="s">
-        <v>58</v>
+        <v>1002</v>
       </c>
       <c r="F577" s="1">
-        <v>46132</v>
+        <v>46195</v>
       </c>
       <c r="G577" s="1">
-        <v>46132</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B578" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C578" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="D578" t="s">
-        <v>57</v>
+        <v>1112</v>
       </c>
       <c r="E578" t="s">
-        <v>58</v>
+        <v>1113</v>
       </c>
       <c r="F578" s="1">
-        <v>46161</v>
+        <v>46209</v>
       </c>
       <c r="G578" s="1">
-        <v>46161</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B579" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C579" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D579" t="s">
-        <v>57</v>
+        <v>939</v>
       </c>
       <c r="E579" t="s">
-        <v>58</v>
+        <v>940</v>
       </c>
       <c r="F579" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
       <c r="G579" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B580" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C580" t="s">
+        <v>96</v>
+      </c>
+      <c r="D580" t="s">
         <v>1116</v>
       </c>
-      <c r="C580" t="s">
-        <v>2</v>
-      </c>
-      <c r="D580" t="s">
-        <v>57</v>
-      </c>
       <c r="E580" t="s">
-        <v>58</v>
+        <v>1117</v>
       </c>
       <c r="F580" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
       <c r="G580" s="1">
-        <v>46174</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B581" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C581" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D581" t="s">
-        <v>57</v>
+        <v>1001</v>
       </c>
       <c r="E581" t="s">
-        <v>58</v>
+        <v>1002</v>
       </c>
       <c r="F581" s="1">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="G581" s="1">
-        <v>46252</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B582" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C582" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D582" t="s">
-        <v>57</v>
+        <v>1116</v>
       </c>
       <c r="E582" t="s">
-        <v>58</v>
+        <v>1117</v>
       </c>
       <c r="F582" s="1">
-        <v>46210</v>
+        <v>46224</v>
       </c>
       <c r="G582" s="1">
-        <v>46210</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B583" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C583" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D583" t="s">
-        <v>57</v>
+        <v>1121</v>
       </c>
       <c r="E583" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="F583" s="1">
-        <v>46213</v>
+        <v>46253</v>
       </c>
       <c r="G583" s="1">
-        <v>46213</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B584" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C584" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D584" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="E584" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="F584" s="1">
-        <v>46218</v>
+        <v>46273</v>
       </c>
       <c r="G584" s="1">
-        <v>46252</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B585" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C585" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D585" t="s">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="E585" t="s">
-        <v>78</v>
+        <v>355</v>
       </c>
       <c r="F585" s="1">
-        <v>46226</v>
+        <v>46284</v>
       </c>
       <c r="G585" s="1">
-        <v>46226</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B586" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C586" t="s">
         <v>80</v>
       </c>
       <c r="D586" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E586" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F586" s="1">
-        <v>46227</v>
+        <v>46289</v>
       </c>
       <c r="G586" s="1">
-        <v>46252</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B587" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="C587" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D587" t="s">
-        <v>57</v>
+        <v>304</v>
       </c>
       <c r="E587" t="s">
-        <v>58</v>
+        <v>305</v>
       </c>
       <c r="F587" s="1">
-        <v>46227</v>
+        <v>46293</v>
       </c>
       <c r="G587" s="1">
-        <v>46252</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B588" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C588" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D588" t="s">
-        <v>57</v>
+        <v>756</v>
       </c>
       <c r="E588" t="s">
-        <v>58</v>
+        <v>757</v>
       </c>
       <c r="F588" s="1">
-        <v>46227</v>
+        <v>46294</v>
       </c>
       <c r="G588" s="1">
-        <v>46228</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B589" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C589" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D589" t="s">
-        <v>77</v>
+        <v>1112</v>
       </c>
       <c r="E589" t="s">
-        <v>78</v>
+        <v>1113</v>
       </c>
       <c r="F589" s="1">
-        <v>46230</v>
+        <v>46295</v>
       </c>
       <c r="G589" s="1">
-        <v>46252</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B590" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C590" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D590" t="s">
-        <v>57</v>
+        <v>1112</v>
       </c>
       <c r="E590" t="s">
-        <v>58</v>
+        <v>1113</v>
       </c>
       <c r="F590" s="1">
-        <v>46231</v>
+        <v>46297</v>
       </c>
       <c r="G590" s="1">
-        <v>46231</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B591" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="C591" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D591" t="s">
-        <v>57</v>
+        <v>1132</v>
       </c>
       <c r="E591" t="s">
-        <v>58</v>
+        <v>1133</v>
       </c>
       <c r="F591" s="1">
-        <v>46254</v>
+        <v>46063</v>
       </c>
       <c r="G591" s="1">
-        <v>46254</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B592" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C592" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D592" t="s">
         <v>57</v>
@@ -17563,21 +17644,21 @@
         <v>58</v>
       </c>
       <c r="F592" s="1">
-        <v>46255</v>
+        <v>46113</v>
       </c>
       <c r="G592" s="1">
-        <v>46255</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B593" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="C593" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D593" t="s">
         <v>57</v>
@@ -17586,21 +17667,21 @@
         <v>58</v>
       </c>
       <c r="F593" s="1">
-        <v>46260</v>
+        <v>46125</v>
       </c>
       <c r="G593" s="1">
-        <v>46260</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B594" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="C594" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D594" t="s">
         <v>57</v>
@@ -17609,21 +17690,21 @@
         <v>58</v>
       </c>
       <c r="F594" s="1">
-        <v>46289</v>
+        <v>46126</v>
       </c>
       <c r="G594" s="1">
-        <v>46289</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B595" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="C595" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D595" t="s">
         <v>57</v>
@@ -17632,21 +17713,21 @@
         <v>58</v>
       </c>
       <c r="F595" s="1">
-        <v>46294</v>
+        <v>46126</v>
       </c>
       <c r="G595" s="1">
-        <v>46294</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B596" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="C596" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D596" t="s">
         <v>57</v>
@@ -17655,21 +17736,21 @@
         <v>58</v>
       </c>
       <c r="F596" s="1">
-        <v>46296</v>
+        <v>46128</v>
       </c>
       <c r="G596" s="1">
-        <v>46296</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>1104</v>
+        <v>1130</v>
       </c>
       <c r="B597" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="C597" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D597" t="s">
         <v>57</v>
@@ -17678,239 +17759,722 @@
         <v>58</v>
       </c>
       <c r="F597" s="1">
-        <v>46296</v>
+        <v>46132</v>
       </c>
       <c r="G597" s="1">
-        <v>46296</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B598" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="C598" t="s">
         <v>2</v>
       </c>
       <c r="D598" t="s">
-        <v>1136</v>
+        <v>57</v>
       </c>
       <c r="E598" t="s">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="F598" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="G598" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B599" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C599" t="s">
         <v>2</v>
       </c>
       <c r="D599" t="s">
-        <v>1139</v>
+        <v>57</v>
       </c>
       <c r="E599" t="s">
-        <v>1140</v>
+        <v>58</v>
       </c>
       <c r="F599" s="1">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="G599" s="1">
-        <v>46170</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B600" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C600" t="s">
         <v>2</v>
       </c>
       <c r="D600" t="s">
-        <v>1136</v>
+        <v>57</v>
       </c>
       <c r="E600" t="s">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="F600" s="1">
-        <v>46244</v>
+        <v>46174</v>
       </c>
       <c r="G600" s="1">
-        <v>46244</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B601" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C601" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D601" t="s">
-        <v>1136</v>
+        <v>57</v>
       </c>
       <c r="E601" t="s">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="F601" s="1">
-        <v>46247</v>
+        <v>46195</v>
       </c>
       <c r="G601" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B602" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C602" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D602" t="s">
-        <v>1144</v>
+        <v>57</v>
       </c>
       <c r="E602" t="s">
-        <v>1145</v>
+        <v>58</v>
       </c>
       <c r="F602" s="1">
-        <v>46247</v>
+        <v>46210</v>
       </c>
       <c r="G602" s="1">
-        <v>46247</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B603" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C603" t="s">
         <v>2</v>
       </c>
       <c r="D603" t="s">
-        <v>1136</v>
+        <v>57</v>
       </c>
       <c r="E603" t="s">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="F603" s="1">
-        <v>46255</v>
+        <v>46213</v>
       </c>
       <c r="G603" s="1">
-        <v>46255</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B604" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C604" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D604" t="s">
-        <v>1136</v>
+        <v>57</v>
       </c>
       <c r="E604" t="s">
-        <v>1137</v>
+        <v>58</v>
       </c>
       <c r="F604" s="1">
-        <v>46258</v>
+        <v>46218</v>
       </c>
       <c r="G604" s="1">
-        <v>46258</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B605" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C605" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D605" t="s">
-        <v>1136</v>
+        <v>77</v>
       </c>
       <c r="E605" t="s">
-        <v>1137</v>
+        <v>78</v>
       </c>
       <c r="F605" s="1">
-        <v>46262</v>
+        <v>46226</v>
       </c>
       <c r="G605" s="1">
-        <v>46265</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B606" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C606" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D606" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E606" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F606" s="1">
-        <v>46281</v>
+        <v>46227</v>
       </c>
       <c r="G606" s="1">
-        <v>46283</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B607" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C607" t="s">
+        <v>6</v>
+      </c>
+      <c r="D607" t="s">
+        <v>57</v>
+      </c>
+      <c r="E607" t="s">
+        <v>58</v>
+      </c>
+      <c r="F607" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G607" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B608" t="s">
         <v>1150</v>
       </c>
-      <c r="C607" t="s">
-        <v>80</v>
-      </c>
-      <c r="D607" t="s">
+      <c r="C608" t="s">
+        <v>6</v>
+      </c>
+      <c r="D608" t="s">
+        <v>57</v>
+      </c>
+      <c r="E608" t="s">
+        <v>58</v>
+      </c>
+      <c r="F608" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G608" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A609" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B609" t="s">
         <v>1151</v>
       </c>
-      <c r="E607" t="s">
+      <c r="C609" t="s">
+        <v>6</v>
+      </c>
+      <c r="D609" t="s">
+        <v>77</v>
+      </c>
+      <c r="E609" t="s">
+        <v>78</v>
+      </c>
+      <c r="F609" s="1">
+        <v>46230</v>
+      </c>
+      <c r="G609" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B610" t="s">
         <v>1152</v>
       </c>
-      <c r="F607" s="1">
+      <c r="C610" t="s">
+        <v>6</v>
+      </c>
+      <c r="D610" t="s">
+        <v>57</v>
+      </c>
+      <c r="E610" t="s">
+        <v>58</v>
+      </c>
+      <c r="F610" s="1">
+        <v>46231</v>
+      </c>
+      <c r="G610" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C611" t="s">
+        <v>6</v>
+      </c>
+      <c r="D611" t="s">
+        <v>57</v>
+      </c>
+      <c r="E611" t="s">
+        <v>58</v>
+      </c>
+      <c r="F611" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G611" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A612" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C612" t="s">
+        <v>2</v>
+      </c>
+      <c r="D612" t="s">
+        <v>57</v>
+      </c>
+      <c r="E612" t="s">
+        <v>58</v>
+      </c>
+      <c r="F612" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G612" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A613" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C613" t="s">
+        <v>6</v>
+      </c>
+      <c r="D613" t="s">
+        <v>57</v>
+      </c>
+      <c r="E613" t="s">
+        <v>58</v>
+      </c>
+      <c r="F613" s="1">
+        <v>46260</v>
+      </c>
+      <c r="G613" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A614" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C614" t="s">
+        <v>6</v>
+      </c>
+      <c r="D614" t="s">
+        <v>57</v>
+      </c>
+      <c r="E614" t="s">
+        <v>58</v>
+      </c>
+      <c r="F614" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G614" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C615" t="s">
+        <v>6</v>
+      </c>
+      <c r="D615" t="s">
+        <v>57</v>
+      </c>
+      <c r="E615" t="s">
+        <v>58</v>
+      </c>
+      <c r="F615" s="1">
+        <v>46294</v>
+      </c>
+      <c r="G615" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A616" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C616" t="s">
+        <v>80</v>
+      </c>
+      <c r="D616" t="s">
+        <v>57</v>
+      </c>
+      <c r="E616" t="s">
+        <v>58</v>
+      </c>
+      <c r="F616" s="1">
+        <v>46297</v>
+      </c>
+      <c r="G616" s="1">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C617" t="s">
+        <v>80</v>
+      </c>
+      <c r="D617" t="s">
+        <v>57</v>
+      </c>
+      <c r="E617" t="s">
+        <v>58</v>
+      </c>
+      <c r="F617" s="1">
+        <v>46297</v>
+      </c>
+      <c r="G617" s="1">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A618" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C618" t="s">
+        <v>80</v>
+      </c>
+      <c r="D618" t="s">
+        <v>57</v>
+      </c>
+      <c r="E618" t="s">
+        <v>58</v>
+      </c>
+      <c r="F618" s="1">
+        <v>46297</v>
+      </c>
+      <c r="G618" s="1">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A619" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C619" t="s">
+        <v>2</v>
+      </c>
+      <c r="D619" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E619" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F619" s="1">
+        <v>46157</v>
+      </c>
+      <c r="G619" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C620" t="s">
+        <v>2</v>
+      </c>
+      <c r="D620" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E620" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F620" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G620" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C621" t="s">
+        <v>2</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E621" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F621" s="1">
+        <v>46244</v>
+      </c>
+      <c r="G621" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A622" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C622" t="s">
+        <v>2</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E622" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F622" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G622" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C623" t="s">
+        <v>2</v>
+      </c>
+      <c r="D623" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E623" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F623" s="1">
+        <v>46247</v>
+      </c>
+      <c r="G623" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A624" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C624" t="s">
+        <v>2</v>
+      </c>
+      <c r="D624" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E624" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F624" s="1">
+        <v>46255</v>
+      </c>
+      <c r="G624" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A625" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C625" t="s">
+        <v>2</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F625" s="1">
+        <v>46258</v>
+      </c>
+      <c r="G625" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A626" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C626" t="s">
+        <v>2</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E626" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F626" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G626" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A627" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C627" t="s">
+        <v>6</v>
+      </c>
+      <c r="D627" t="s">
+        <v>13</v>
+      </c>
+      <c r="E627" t="s">
+        <v>14</v>
+      </c>
+      <c r="F627" s="1">
+        <v>46281</v>
+      </c>
+      <c r="G627" s="1">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A628" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C628" t="s">
+        <v>80</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E628" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F628" s="1">
         <v>46296</v>
       </c>
-      <c r="G607" s="1">
+      <c r="G628" s="1">
         <v>46296</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D2DE02-734B-41C8-8A01-ECD818F10DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DB71B2E-2DDA-48DC-83A1-A73DE924BB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3F782A1E-2DE1-4C43-A05B-9504CDFDF93D}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F6ABC71F-A7F9-4D66-AD6E-1BB0243FA047}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1133">
   <si>
     <t>0001</t>
   </si>
@@ -3226,13 +3226,7 @@
     <t xml:space="preserve">    2912</t>
   </si>
   <si>
-    <t xml:space="preserve">    2959</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2984</t>
   </si>
   <si>
     <t xml:space="preserve">    2989</t>
@@ -3874,31 +3868,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EBB095-BFE9-4105-AD13-1A86A742EC8E}">
-  <dimension ref="A1:G596"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D936D12B-A57F-41E8-914C-0CDC702B4F18}">
+  <dimension ref="A1:G594"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>1132</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6232,7 +6226,7 @@
         <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D103" t="s">
         <v>247</v>
@@ -6301,7 +6295,7 @@
         <v>253</v>
       </c>
       <c r="C106" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D106" t="s">
         <v>254</v>
@@ -6439,7 +6433,7 @@
         <v>269</v>
       </c>
       <c r="C112" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D112" t="s">
         <v>37</v>
@@ -6508,7 +6502,7 @@
         <v>274</v>
       </c>
       <c r="C115" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D115" t="s">
         <v>37</v>
@@ -6646,7 +6640,7 @@
         <v>286</v>
       </c>
       <c r="C121" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
         <v>37</v>
@@ -6692,7 +6686,7 @@
         <v>288</v>
       </c>
       <c r="C123" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
         <v>37</v>
@@ -6715,7 +6709,7 @@
         <v>289</v>
       </c>
       <c r="C124" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D124" t="s">
         <v>37</v>
@@ -6738,7 +6732,7 @@
         <v>290</v>
       </c>
       <c r="C125" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D125" t="s">
         <v>37</v>
@@ -6807,7 +6801,7 @@
         <v>293</v>
       </c>
       <c r="C128" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
         <v>37</v>
@@ -6853,7 +6847,7 @@
         <v>295</v>
       </c>
       <c r="C130" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D130" t="s">
         <v>37</v>
@@ -6968,7 +6962,7 @@
         <v>304</v>
       </c>
       <c r="C135" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D135" t="s">
         <v>305</v>
@@ -7175,7 +7169,7 @@
         <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D144" t="s">
         <v>322</v>
@@ -8279,7 +8273,7 @@
         <v>429</v>
       </c>
       <c r="C192" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
         <v>427</v>
@@ -8486,7 +8480,7 @@
         <v>446</v>
       </c>
       <c r="C201" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D201" t="s">
         <v>447</v>
@@ -8601,7 +8595,7 @@
         <v>461</v>
       </c>
       <c r="C206" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D206" t="s">
         <v>462</v>
@@ -8624,7 +8618,7 @@
         <v>464</v>
       </c>
       <c r="C207" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D207" t="s">
         <v>462</v>
@@ -8647,7 +8641,7 @@
         <v>465</v>
       </c>
       <c r="C208" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D208" t="s">
         <v>462</v>
@@ -9475,7 +9469,7 @@
         <v>535</v>
       </c>
       <c r="C244" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D244" t="s">
         <v>536</v>
@@ -10694,7 +10688,7 @@
         <v>642</v>
       </c>
       <c r="C297" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D297" t="s">
         <v>462</v>
@@ -10970,7 +10964,7 @@
         <v>662</v>
       </c>
       <c r="C309" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D309" t="s">
         <v>37</v>
@@ -11039,7 +11033,7 @@
         <v>665</v>
       </c>
       <c r="C312" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D312" t="s">
         <v>37</v>
@@ -11982,7 +11976,7 @@
         <v>738</v>
       </c>
       <c r="C353" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D353" t="s">
         <v>322</v>
@@ -12051,7 +12045,7 @@
         <v>745</v>
       </c>
       <c r="C356" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D356" t="s">
         <v>746</v>
@@ -12235,7 +12229,7 @@
         <v>759</v>
       </c>
       <c r="C364" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D364" t="s">
         <v>760</v>
@@ -12373,7 +12367,7 @@
         <v>769</v>
       </c>
       <c r="C370" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D370" t="s">
         <v>770</v>
@@ -12396,7 +12390,7 @@
         <v>772</v>
       </c>
       <c r="C371" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D371" t="s">
         <v>773</v>
@@ -12419,7 +12413,7 @@
         <v>775</v>
       </c>
       <c r="C372" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D372" t="s">
         <v>773</v>
@@ -12488,7 +12482,7 @@
         <v>780</v>
       </c>
       <c r="C375" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D375" t="s">
         <v>322</v>
@@ -12511,7 +12505,7 @@
         <v>781</v>
       </c>
       <c r="C376" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D376" t="s">
         <v>782</v>
@@ -12603,7 +12597,7 @@
         <v>789</v>
       </c>
       <c r="C380" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D380" t="s">
         <v>254</v>
@@ -12718,7 +12712,7 @@
         <v>800</v>
       </c>
       <c r="C385" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D385" t="s">
         <v>68</v>
@@ -12741,7 +12735,7 @@
         <v>801</v>
       </c>
       <c r="C386" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D386" t="s">
         <v>19</v>
@@ -13247,7 +13241,7 @@
         <v>829</v>
       </c>
       <c r="C408" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D408" t="s">
         <v>81</v>
@@ -13316,7 +13310,7 @@
         <v>832</v>
       </c>
       <c r="C411" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D411" t="s">
         <v>37</v>
@@ -13546,7 +13540,7 @@
         <v>848</v>
       </c>
       <c r="C421" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -13845,7 +13839,7 @@
         <v>867</v>
       </c>
       <c r="C434" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D434" t="s">
         <v>19</v>
@@ -13914,7 +13908,7 @@
         <v>870</v>
       </c>
       <c r="C437" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D437" t="s">
         <v>68</v>
@@ -14052,7 +14046,7 @@
         <v>884</v>
       </c>
       <c r="C443" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D443" t="s">
         <v>885</v>
@@ -14075,7 +14069,7 @@
         <v>887</v>
       </c>
       <c r="C444" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D444" t="s">
         <v>885</v>
@@ -14121,7 +14115,7 @@
         <v>891</v>
       </c>
       <c r="C446" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D446" t="s">
         <v>140</v>
@@ -16493,13 +16487,13 @@
         <v>80</v>
       </c>
       <c r="D549" t="s">
-        <v>322</v>
+        <v>41</v>
       </c>
       <c r="E549" t="s">
-        <v>323</v>
+        <v>42</v>
       </c>
       <c r="F549" s="1">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="G549" s="1">
         <v>46296</v>
@@ -16516,16 +16510,16 @@
         <v>80</v>
       </c>
       <c r="D550" t="s">
-        <v>41</v>
+        <v>657</v>
       </c>
       <c r="E550" t="s">
-        <v>42</v>
+        <v>658</v>
       </c>
       <c r="F550" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="G550" s="1">
-        <v>46296</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.2">
@@ -16539,16 +16533,16 @@
         <v>80</v>
       </c>
       <c r="D551" t="s">
-        <v>276</v>
+        <v>1055</v>
       </c>
       <c r="E551" t="s">
-        <v>277</v>
+        <v>1056</v>
       </c>
       <c r="F551" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="G551" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.2">
@@ -16562,16 +16556,16 @@
         <v>80</v>
       </c>
       <c r="D552" t="s">
-        <v>657</v>
+        <v>133</v>
       </c>
       <c r="E552" t="s">
-        <v>658</v>
+        <v>134</v>
       </c>
       <c r="F552" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="G552" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.2">
@@ -16591,10 +16585,10 @@
         <v>1056</v>
       </c>
       <c r="F553" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G553" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.2">
@@ -16608,10 +16602,10 @@
         <v>80</v>
       </c>
       <c r="D554" t="s">
-        <v>133</v>
+        <v>1045</v>
       </c>
       <c r="E554" t="s">
-        <v>134</v>
+        <v>1046</v>
       </c>
       <c r="F554" s="1">
         <v>46297</v>
@@ -16622,82 +16616,82 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1050</v>
+        <v>1074</v>
       </c>
       <c r="B555" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C555" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D555" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="E555" t="s">
-        <v>1056</v>
+        <v>1077</v>
       </c>
       <c r="F555" s="1">
-        <v>46297</v>
+        <v>46063</v>
       </c>
       <c r="G555" s="1">
-        <v>46297</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1050</v>
+        <v>1074</v>
       </c>
       <c r="B556" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C556" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D556" t="s">
-        <v>1045</v>
+        <v>57</v>
       </c>
       <c r="E556" t="s">
-        <v>1046</v>
+        <v>58</v>
       </c>
       <c r="F556" s="1">
-        <v>46297</v>
+        <v>46113</v>
       </c>
       <c r="G556" s="1">
-        <v>46297</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B557" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C557" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="D557" t="s">
-        <v>1078</v>
+        <v>57</v>
       </c>
       <c r="E557" t="s">
-        <v>1079</v>
+        <v>58</v>
       </c>
       <c r="F557" s="1">
-        <v>46063</v>
+        <v>46125</v>
       </c>
       <c r="G557" s="1">
-        <v>46064</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B558" t="s">
         <v>1080</v>
       </c>
       <c r="C558" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D558" t="s">
         <v>57</v>
@@ -16706,15 +16700,15 @@
         <v>58</v>
       </c>
       <c r="F558" s="1">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="G558" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B559" t="s">
         <v>1081</v>
@@ -16729,15 +16723,15 @@
         <v>58</v>
       </c>
       <c r="F559" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="G559" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B560" t="s">
         <v>1082</v>
@@ -16752,21 +16746,21 @@
         <v>58</v>
       </c>
       <c r="F560" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="G560" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B561" t="s">
         <v>1083</v>
       </c>
       <c r="C561" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D561" t="s">
         <v>57</v>
@@ -16775,15 +16769,15 @@
         <v>58</v>
       </c>
       <c r="F561" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G561" s="1">
-        <v>46126</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B562" t="s">
         <v>1084</v>
@@ -16798,21 +16792,21 @@
         <v>58</v>
       </c>
       <c r="F562" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
       <c r="G562" s="1">
-        <v>46128</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B563" t="s">
         <v>1085</v>
       </c>
       <c r="C563" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D563" t="s">
         <v>57</v>
@@ -16821,15 +16815,15 @@
         <v>58</v>
       </c>
       <c r="F563" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
       <c r="G563" s="1">
-        <v>46132</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B564" t="s">
         <v>1086</v>
@@ -16844,21 +16838,21 @@
         <v>58</v>
       </c>
       <c r="F564" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="G564" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B565" t="s">
         <v>1087</v>
       </c>
       <c r="C565" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D565" t="s">
         <v>57</v>
@@ -16867,21 +16861,21 @@
         <v>58</v>
       </c>
       <c r="F565" s="1">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="G565" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B566" t="s">
         <v>1088</v>
       </c>
       <c r="C566" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D566" t="s">
         <v>57</v>
@@ -16890,21 +16884,21 @@
         <v>58</v>
       </c>
       <c r="F566" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
       <c r="G566" s="1">
-        <v>46174</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B567" t="s">
         <v>1089</v>
       </c>
       <c r="C567" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D567" t="s">
         <v>57</v>
@@ -16913,15 +16907,15 @@
         <v>58</v>
       </c>
       <c r="F567" s="1">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="G567" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B568" t="s">
         <v>1090</v>
@@ -16936,44 +16930,44 @@
         <v>58</v>
       </c>
       <c r="F568" s="1">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="G568" s="1">
-        <v>46210</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B569" t="s">
         <v>1091</v>
       </c>
       <c r="C569" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D569" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E569" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F569" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
       <c r="G569" s="1">
-        <v>46213</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B570" t="s">
         <v>1092</v>
       </c>
       <c r="C570" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D570" t="s">
         <v>57</v>
@@ -16982,7 +16976,7 @@
         <v>58</v>
       </c>
       <c r="F570" s="1">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="G570" s="1">
         <v>46252</v>
@@ -16990,7 +16984,7 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B571" t="s">
         <v>1093</v>
@@ -16999,27 +16993,27 @@
         <v>6</v>
       </c>
       <c r="D571" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E571" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F571" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="G571" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B572" t="s">
         <v>1094</v>
       </c>
       <c r="C572" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D572" t="s">
         <v>57</v>
@@ -17031,12 +17025,12 @@
         <v>46227</v>
       </c>
       <c r="G572" s="1">
-        <v>46252</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B573" t="s">
         <v>1095</v>
@@ -17045,13 +17039,13 @@
         <v>6</v>
       </c>
       <c r="D573" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E573" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F573" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="G573" s="1">
         <v>46252</v>
@@ -17059,7 +17053,7 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B574" t="s">
         <v>1096</v>
@@ -17074,15 +17068,15 @@
         <v>58</v>
       </c>
       <c r="F574" s="1">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="G574" s="1">
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B575" t="s">
         <v>1097</v>
@@ -17091,27 +17085,27 @@
         <v>6</v>
       </c>
       <c r="D575" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E575" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F575" s="1">
-        <v>46230</v>
+        <v>46254</v>
       </c>
       <c r="G575" s="1">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B576" t="s">
         <v>1098</v>
       </c>
       <c r="C576" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D576" t="s">
         <v>57</v>
@@ -17120,15 +17114,15 @@
         <v>58</v>
       </c>
       <c r="F576" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
       <c r="G576" s="1">
-        <v>46231</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B577" t="s">
         <v>1099</v>
@@ -17143,21 +17137,21 @@
         <v>58</v>
       </c>
       <c r="F577" s="1">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="G577" s="1">
-        <v>46254</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B578" t="s">
         <v>1100</v>
       </c>
       <c r="C578" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D578" t="s">
         <v>57</v>
@@ -17166,15 +17160,15 @@
         <v>58</v>
       </c>
       <c r="F578" s="1">
-        <v>46255</v>
+        <v>46289</v>
       </c>
       <c r="G578" s="1">
-        <v>46255</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B579" t="s">
         <v>1101</v>
@@ -17189,21 +17183,21 @@
         <v>58</v>
       </c>
       <c r="F579" s="1">
-        <v>46260</v>
+        <v>46294</v>
       </c>
       <c r="G579" s="1">
-        <v>46260</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B580" t="s">
         <v>1102</v>
       </c>
       <c r="C580" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D580" t="s">
         <v>57</v>
@@ -17212,21 +17206,21 @@
         <v>58</v>
       </c>
       <c r="F580" s="1">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="G580" s="1">
-        <v>46289</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B581" t="s">
         <v>1103</v>
       </c>
       <c r="C581" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D581" t="s">
         <v>57</v>
@@ -17235,15 +17229,15 @@
         <v>58</v>
       </c>
       <c r="F581" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="G581" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B582" t="s">
         <v>1104</v>
@@ -17266,7 +17260,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B583" t="s">
         <v>1105</v>
@@ -17289,99 +17283,99 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1076</v>
+        <v>1106</v>
       </c>
       <c r="B584" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C584" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D584" t="s">
-        <v>57</v>
+        <v>1108</v>
       </c>
       <c r="E584" t="s">
-        <v>58</v>
+        <v>1109</v>
       </c>
       <c r="F584" s="1">
-        <v>46297</v>
+        <v>46157</v>
       </c>
       <c r="G584" s="1">
-        <v>46297</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1076</v>
+        <v>1106</v>
       </c>
       <c r="B585" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C585" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D585" t="s">
-        <v>57</v>
+        <v>1111</v>
       </c>
       <c r="E585" t="s">
-        <v>58</v>
+        <v>1112</v>
       </c>
       <c r="F585" s="1">
-        <v>46297</v>
+        <v>46168</v>
       </c>
       <c r="G585" s="1">
-        <v>46297</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B586" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C586" t="s">
         <v>2</v>
       </c>
       <c r="D586" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E586" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F586" s="1">
-        <v>46157</v>
+        <v>46218</v>
       </c>
       <c r="G586" s="1">
-        <v>46157</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B587" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C587" t="s">
         <v>2</v>
       </c>
       <c r="D587" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="E587" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="F587" s="1">
-        <v>46168</v>
+        <v>46244</v>
       </c>
       <c r="G587" s="1">
-        <v>46170</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B588" t="s">
         <v>1115</v>
@@ -17390,21 +17384,21 @@
         <v>2</v>
       </c>
       <c r="D588" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E588" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F588" s="1">
-        <v>46218</v>
+        <v>46247</v>
       </c>
       <c r="G588" s="1">
-        <v>46218</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B589" t="s">
         <v>1116</v>
@@ -17413,67 +17407,67 @@
         <v>2</v>
       </c>
       <c r="D589" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="E589" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="F589" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="G589" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B590" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C590" t="s">
         <v>2</v>
       </c>
       <c r="D590" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E590" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F590" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="G590" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B591" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C591" t="s">
         <v>2</v>
       </c>
       <c r="D591" t="s">
-        <v>1119</v>
+        <v>1108</v>
       </c>
       <c r="E591" t="s">
-        <v>1120</v>
+        <v>1109</v>
       </c>
       <c r="F591" s="1">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="G591" s="1">
-        <v>46247</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B592" t="s">
         <v>1121</v>
@@ -17482,107 +17476,61 @@
         <v>2</v>
       </c>
       <c r="D592" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E592" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F592" s="1">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="G592" s="1">
-        <v>46255</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B593" t="s">
         <v>1122</v>
       </c>
       <c r="C593" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D593" t="s">
-        <v>1110</v>
+        <v>13</v>
       </c>
       <c r="E593" t="s">
-        <v>1111</v>
+        <v>14</v>
       </c>
       <c r="F593" s="1">
-        <v>46258</v>
+        <v>46281</v>
       </c>
       <c r="G593" s="1">
-        <v>46258</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B594" t="s">
         <v>1123</v>
       </c>
       <c r="C594" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D594" t="s">
-        <v>1110</v>
+        <v>1124</v>
       </c>
       <c r="E594" t="s">
-        <v>1111</v>
+        <v>1125</v>
       </c>
       <c r="F594" s="1">
-        <v>46262</v>
+        <v>46296</v>
       </c>
       <c r="G594" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A595" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B595" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C595" t="s">
-        <v>6</v>
-      </c>
-      <c r="D595" t="s">
-        <v>13</v>
-      </c>
-      <c r="E595" t="s">
-        <v>14</v>
-      </c>
-      <c r="F595" s="1">
-        <v>46281</v>
-      </c>
-      <c r="G595" s="1">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A596" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B596" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C596" t="s">
-        <v>80</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E596" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F596" s="1">
-        <v>46296</v>
-      </c>
-      <c r="G596" s="1">
         <v>46296</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E881DEAA-F71C-4D68-9FEB-739812AF0C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FA92BC2-AC2D-449D-803C-1DD22BD3DBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{89B1FA2D-B3E7-4A06-8837-ED1EBFC83EED}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4A7C9FCC-8ACC-4C71-8143-3C4F66FF6395}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1127">
   <si>
     <t>0001</t>
   </si>
@@ -3047,6 +3047,36 @@
   </si>
   <si>
     <t xml:space="preserve">  217107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217109</t>
+  </si>
+  <si>
+    <t>LN02</t>
+  </si>
+  <si>
+    <t>LA NORIA REVESIMIENTOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217110</t>
+  </si>
+  <si>
+    <t>AB08</t>
+  </si>
+  <si>
+    <t>ABELSON S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217111</t>
+  </si>
+  <si>
+    <t>GI09</t>
+  </si>
+  <si>
+    <t>GRUPO INNOVARE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217112</t>
   </si>
   <si>
     <t>0004</t>
@@ -3820,34 +3850,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6827804E-F2A3-4D11-A68D-6506E0605E1F}">
-  <dimension ref="A1:H591"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3805E581-45E9-4BDB-9E62-FC6A01FC27C0}">
+  <dimension ref="A1:H595"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -15613,7 +15643,7 @@
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E454" t="s">
         <v>77</v>
@@ -17268,62 +17298,62 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
+        <v>0</v>
+      </c>
+      <c r="B518" t="s">
         <v>1009</v>
       </c>
-      <c r="B518" t="s">
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518" t="s">
+        <v>80</v>
+      </c>
+      <c r="E518" t="s">
         <v>1010</v>
       </c>
-      <c r="C518">
-        <v>1</v>
-      </c>
-      <c r="D518" t="s">
-        <v>2</v>
-      </c>
-      <c r="E518" t="s">
-        <v>200</v>
-      </c>
       <c r="F518" t="s">
-        <v>201</v>
+        <v>1011</v>
       </c>
       <c r="G518" s="1">
-        <v>46148</v>
+        <v>46301</v>
       </c>
       <c r="H518" s="1">
-        <v>46149</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="B519" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C519">
         <v>1</v>
       </c>
       <c r="D519" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E519" t="s">
-        <v>112</v>
+        <v>1013</v>
       </c>
       <c r="F519" t="s">
-        <v>113</v>
+        <v>1014</v>
       </c>
       <c r="G519" s="1">
-        <v>46268</v>
+        <v>46301</v>
       </c>
       <c r="H519" s="1">
-        <v>46268</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C520">
         <v>1</v>
@@ -17332,10 +17362,10 @@
         <v>80</v>
       </c>
       <c r="E520" t="s">
-        <v>741</v>
+        <v>1016</v>
       </c>
       <c r="F520" t="s">
-        <v>742</v>
+        <v>1017</v>
       </c>
       <c r="G520" s="1">
         <v>46301</v>
@@ -17346,10 +17376,10 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="B521" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C521">
         <v>1</v>
@@ -17358,10 +17388,10 @@
         <v>80</v>
       </c>
       <c r="E521" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F521" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="G521" s="1">
         <v>46301</v>
@@ -17372,140 +17402,140 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="B522" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C522">
         <v>1</v>
       </c>
       <c r="D522" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E522" t="s">
-        <v>741</v>
+        <v>200</v>
       </c>
       <c r="F522" t="s">
-        <v>742</v>
+        <v>201</v>
       </c>
       <c r="G522" s="1">
-        <v>46301</v>
+        <v>46148</v>
       </c>
       <c r="H522" s="1">
-        <v>46301</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B523" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C523">
         <v>1</v>
       </c>
       <c r="D523" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E523" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F523" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G523" s="1">
-        <v>46133</v>
+        <v>46268</v>
       </c>
       <c r="H523" s="1">
-        <v>46134</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B524" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C524">
         <v>1</v>
       </c>
       <c r="D524" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E524" t="s">
-        <v>41</v>
+        <v>741</v>
       </c>
       <c r="F524" t="s">
-        <v>42</v>
+        <v>742</v>
       </c>
       <c r="G524" s="1">
-        <v>46134</v>
+        <v>46301</v>
       </c>
       <c r="H524" s="1">
-        <v>46134</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B525" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C525">
         <v>1</v>
       </c>
       <c r="D525" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E525" t="s">
-        <v>19</v>
+        <v>1024</v>
       </c>
       <c r="F525" t="s">
-        <v>20</v>
+        <v>1025</v>
       </c>
       <c r="G525" s="1">
-        <v>46156</v>
+        <v>46301</v>
       </c>
       <c r="H525" s="1">
-        <v>46156</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B526" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="C526">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D526" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E526" t="s">
-        <v>1022</v>
+        <v>741</v>
       </c>
       <c r="F526" t="s">
-        <v>1023</v>
+        <v>742</v>
       </c>
       <c r="G526" s="1">
-        <v>46209</v>
+        <v>46301</v>
       </c>
       <c r="H526" s="1">
-        <v>46218</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B527" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C527">
         <v>1</v>
@@ -17514,47 +17544,47 @@
         <v>6</v>
       </c>
       <c r="E527" t="s">
-        <v>1025</v>
+        <v>41</v>
       </c>
       <c r="F527" t="s">
-        <v>1026</v>
+        <v>42</v>
       </c>
       <c r="G527" s="1">
-        <v>46213</v>
+        <v>46133</v>
       </c>
       <c r="H527" s="1">
-        <v>46213</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B528" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C528">
         <v>1</v>
       </c>
       <c r="D528" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="E528" t="s">
-        <v>1028</v>
+        <v>41</v>
       </c>
       <c r="F528" t="s">
-        <v>1029</v>
+        <v>42</v>
       </c>
       <c r="G528" s="1">
-        <v>46213</v>
+        <v>46134</v>
       </c>
       <c r="H528" s="1">
-        <v>46216</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B529" t="s">
         <v>1030</v>
@@ -17563,33 +17593,33 @@
         <v>1</v>
       </c>
       <c r="D529" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="E529" t="s">
-        <v>1028</v>
+        <v>19</v>
       </c>
       <c r="F529" t="s">
-        <v>1029</v>
+        <v>20</v>
       </c>
       <c r="G529" s="1">
-        <v>46224</v>
+        <v>46156</v>
       </c>
       <c r="H529" s="1">
-        <v>46224</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B530" t="s">
         <v>1031</v>
       </c>
       <c r="C530">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D530" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="E530" t="s">
         <v>1032</v>
@@ -17598,15 +17628,15 @@
         <v>1033</v>
       </c>
       <c r="G530" s="1">
-        <v>46253</v>
+        <v>46209</v>
       </c>
       <c r="H530" s="1">
-        <v>46253</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B531" t="s">
         <v>1034</v>
@@ -17615,157 +17645,157 @@
         <v>1</v>
       </c>
       <c r="D531" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E531" t="s">
-        <v>211</v>
+        <v>1035</v>
       </c>
       <c r="F531" t="s">
-        <v>212</v>
+        <v>1036</v>
       </c>
       <c r="G531" s="1">
-        <v>46273</v>
+        <v>46213</v>
       </c>
       <c r="H531" s="1">
-        <v>46274</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B532" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C532">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D532" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E532" t="s">
-        <v>41</v>
+        <v>1038</v>
       </c>
       <c r="F532" t="s">
-        <v>42</v>
+        <v>1039</v>
       </c>
       <c r="G532" s="1">
-        <v>46289</v>
+        <v>46213</v>
       </c>
       <c r="H532" s="1">
-        <v>46296</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B533" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C533">
         <v>1</v>
       </c>
       <c r="D533" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E533" t="s">
-        <v>1022</v>
+        <v>1038</v>
       </c>
       <c r="F533" t="s">
-        <v>1023</v>
+        <v>1039</v>
       </c>
       <c r="G533" s="1">
-        <v>46295</v>
+        <v>46224</v>
       </c>
       <c r="H533" s="1">
-        <v>46295</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B534" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="C534">
         <v>1</v>
       </c>
       <c r="D534" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E534" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="F534" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G534" s="1">
-        <v>46295</v>
+        <v>46253</v>
       </c>
       <c r="H534" s="1">
-        <v>46301</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B535" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C535">
         <v>1</v>
       </c>
       <c r="D535" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E535" t="s">
-        <v>1022</v>
+        <v>211</v>
       </c>
       <c r="F535" t="s">
-        <v>1023</v>
+        <v>212</v>
       </c>
       <c r="G535" s="1">
-        <v>46297</v>
+        <v>46273</v>
       </c>
       <c r="H535" s="1">
-        <v>46297</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B536" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="C536">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D536" t="s">
         <v>80</v>
       </c>
       <c r="E536" t="s">
-        <v>710</v>
+        <v>41</v>
       </c>
       <c r="F536" t="s">
-        <v>711</v>
+        <v>42</v>
       </c>
       <c r="G536" s="1">
-        <v>46297</v>
+        <v>46289</v>
       </c>
       <c r="H536" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B537" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C537">
         <v>1</v>
@@ -17774,24 +17804,24 @@
         <v>80</v>
       </c>
       <c r="E537" t="s">
-        <v>461</v>
+        <v>1032</v>
       </c>
       <c r="F537" t="s">
-        <v>462</v>
+        <v>1033</v>
       </c>
       <c r="G537" s="1">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="H537" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B538" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="C538">
         <v>1</v>
@@ -17800,24 +17830,24 @@
         <v>80</v>
       </c>
       <c r="E538" t="s">
-        <v>744</v>
+        <v>1048</v>
       </c>
       <c r="F538" t="s">
-        <v>745</v>
+        <v>1049</v>
       </c>
       <c r="G538" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="H538" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B539" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="C539">
         <v>1</v>
@@ -17826,24 +17856,24 @@
         <v>80</v>
       </c>
       <c r="E539" t="s">
-        <v>1045</v>
+        <v>1032</v>
       </c>
       <c r="F539" t="s">
-        <v>1046</v>
+        <v>1033</v>
       </c>
       <c r="G539" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H539" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B540" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C540">
         <v>1</v>
@@ -17852,24 +17882,24 @@
         <v>80</v>
       </c>
       <c r="E540" t="s">
-        <v>1045</v>
+        <v>710</v>
       </c>
       <c r="F540" t="s">
-        <v>1046</v>
+        <v>711</v>
       </c>
       <c r="G540" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H540" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B541" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C541">
         <v>1</v>
@@ -17878,13 +17908,13 @@
         <v>80</v>
       </c>
       <c r="E541" t="s">
-        <v>1022</v>
+        <v>461</v>
       </c>
       <c r="F541" t="s">
-        <v>1023</v>
+        <v>462</v>
       </c>
       <c r="G541" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H541" s="1">
         <v>46300</v>
@@ -17892,22 +17922,22 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B542" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C542">
         <v>1</v>
       </c>
       <c r="D542" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E542" t="s">
-        <v>221</v>
+        <v>744</v>
       </c>
       <c r="F542" t="s">
-        <v>222</v>
+        <v>745</v>
       </c>
       <c r="G542" s="1">
         <v>46300</v>
@@ -17918,10 +17948,10 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B543" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="C543">
         <v>1</v>
@@ -17930,10 +17960,10 @@
         <v>80</v>
       </c>
       <c r="E543" t="s">
-        <v>221</v>
+        <v>1055</v>
       </c>
       <c r="F543" t="s">
-        <v>222</v>
+        <v>1056</v>
       </c>
       <c r="G543" s="1">
         <v>46300</v>
@@ -17944,10 +17974,10 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B544" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C544">
         <v>1</v>
@@ -17956,24 +17986,24 @@
         <v>80</v>
       </c>
       <c r="E544" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="F544" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="G544" s="1">
         <v>46300</v>
       </c>
       <c r="H544" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B545" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="C545">
         <v>1</v>
@@ -17982,10 +18012,10 @@
         <v>80</v>
       </c>
       <c r="E545" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="F545" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="G545" s="1">
         <v>46300</v>
@@ -17996,22 +18026,22 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B546" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C546">
         <v>1</v>
       </c>
       <c r="D546" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E546" t="s">
-        <v>1028</v>
+        <v>221</v>
       </c>
       <c r="F546" t="s">
-        <v>1029</v>
+        <v>222</v>
       </c>
       <c r="G546" s="1">
         <v>46300</v>
@@ -18022,10 +18052,10 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B547" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="C547">
         <v>1</v>
@@ -18034,24 +18064,24 @@
         <v>80</v>
       </c>
       <c r="E547" t="s">
-        <v>744</v>
+        <v>221</v>
       </c>
       <c r="F547" t="s">
-        <v>745</v>
+        <v>222</v>
       </c>
       <c r="G547" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H547" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="B548" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="C548">
         <v>1</v>
@@ -18060,13 +18090,13 @@
         <v>80</v>
       </c>
       <c r="E548" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="F548" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="G548" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H548" s="1">
         <v>46301</v>
@@ -18074,146 +18104,146 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1056</v>
+        <v>1027</v>
       </c>
       <c r="B549" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="C549">
         <v>1</v>
       </c>
       <c r="D549" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E549" t="s">
-        <v>1058</v>
+        <v>1038</v>
       </c>
       <c r="F549" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="G549" s="1">
-        <v>46063</v>
+        <v>46300</v>
       </c>
       <c r="H549" s="1">
-        <v>46064</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1056</v>
+        <v>1027</v>
       </c>
       <c r="B550" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C550">
         <v>1</v>
       </c>
       <c r="D550" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E550" t="s">
-        <v>57</v>
+        <v>1038</v>
       </c>
       <c r="F550" t="s">
-        <v>58</v>
+        <v>1039</v>
       </c>
       <c r="G550" s="1">
-        <v>46113</v>
+        <v>46300</v>
       </c>
       <c r="H550" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1056</v>
+        <v>1027</v>
       </c>
       <c r="B551" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C551">
         <v>1</v>
       </c>
       <c r="D551" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E551" t="s">
-        <v>57</v>
+        <v>744</v>
       </c>
       <c r="F551" t="s">
-        <v>58</v>
+        <v>745</v>
       </c>
       <c r="G551" s="1">
-        <v>46125</v>
+        <v>46301</v>
       </c>
       <c r="H551" s="1">
-        <v>46125</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C552">
+        <v>1</v>
+      </c>
+      <c r="D552" t="s">
+        <v>80</v>
+      </c>
+      <c r="E552" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F552" t="s">
         <v>1056</v>
       </c>
-      <c r="B552" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C552">
-        <v>1</v>
-      </c>
-      <c r="D552" t="s">
-        <v>2</v>
-      </c>
-      <c r="E552" t="s">
-        <v>57</v>
-      </c>
-      <c r="F552" t="s">
-        <v>58</v>
-      </c>
       <c r="G552" s="1">
-        <v>46126</v>
+        <v>46301</v>
       </c>
       <c r="H552" s="1">
-        <v>46126</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B553" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C553">
         <v>1</v>
       </c>
       <c r="D553" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E553" t="s">
-        <v>57</v>
+        <v>1068</v>
       </c>
       <c r="F553" t="s">
-        <v>58</v>
+        <v>1069</v>
       </c>
       <c r="G553" s="1">
-        <v>46126</v>
+        <v>46063</v>
       </c>
       <c r="H553" s="1">
-        <v>46126</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B554" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C554">
         <v>1</v>
       </c>
       <c r="D554" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E554" t="s">
         <v>57</v>
@@ -18222,24 +18252,24 @@
         <v>58</v>
       </c>
       <c r="G554" s="1">
-        <v>46128</v>
+        <v>46113</v>
       </c>
       <c r="H554" s="1">
-        <v>46128</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B555" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C555">
         <v>1</v>
       </c>
       <c r="D555" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E555" t="s">
         <v>57</v>
@@ -18248,18 +18278,18 @@
         <v>58</v>
       </c>
       <c r="G555" s="1">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="H555" s="1">
-        <v>46132</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B556" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="C556">
         <v>1</v>
@@ -18274,18 +18304,18 @@
         <v>58</v>
       </c>
       <c r="G556" s="1">
-        <v>46161</v>
+        <v>46126</v>
       </c>
       <c r="H556" s="1">
-        <v>46161</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B557" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="C557">
         <v>1</v>
@@ -18300,18 +18330,18 @@
         <v>58</v>
       </c>
       <c r="G557" s="1">
-        <v>46174</v>
+        <v>46126</v>
       </c>
       <c r="H557" s="1">
-        <v>46174</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B558" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="C558">
         <v>1</v>
@@ -18326,18 +18356,18 @@
         <v>58</v>
       </c>
       <c r="G558" s="1">
-        <v>46174</v>
+        <v>46128</v>
       </c>
       <c r="H558" s="1">
-        <v>46174</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B559" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="C559">
         <v>1</v>
@@ -18352,24 +18382,24 @@
         <v>58</v>
       </c>
       <c r="G559" s="1">
-        <v>46195</v>
+        <v>46132</v>
       </c>
       <c r="H559" s="1">
-        <v>46252</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B560" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="C560">
         <v>1</v>
       </c>
       <c r="D560" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E560" t="s">
         <v>57</v>
@@ -18378,18 +18408,18 @@
         <v>58</v>
       </c>
       <c r="G560" s="1">
-        <v>46210</v>
+        <v>46161</v>
       </c>
       <c r="H560" s="1">
-        <v>46210</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B561" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="C561">
         <v>1</v>
@@ -18404,24 +18434,24 @@
         <v>58</v>
       </c>
       <c r="G561" s="1">
-        <v>46213</v>
+        <v>46174</v>
       </c>
       <c r="H561" s="1">
-        <v>46213</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B562" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="C562">
         <v>1</v>
       </c>
       <c r="D562" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E562" t="s">
         <v>57</v>
@@ -18430,18 +18460,18 @@
         <v>58</v>
       </c>
       <c r="G562" s="1">
-        <v>46218</v>
+        <v>46174</v>
       </c>
       <c r="H562" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B563" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C563">
         <v>1</v>
@@ -18450,30 +18480,30 @@
         <v>6</v>
       </c>
       <c r="E563" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F563" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G563" s="1">
-        <v>46226</v>
+        <v>46195</v>
       </c>
       <c r="H563" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B564" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="C564">
         <v>1</v>
       </c>
       <c r="D564" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E564" t="s">
         <v>57</v>
@@ -18482,24 +18512,24 @@
         <v>58</v>
       </c>
       <c r="G564" s="1">
-        <v>46227</v>
+        <v>46210</v>
       </c>
       <c r="H564" s="1">
-        <v>46252</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B565" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C565">
         <v>1</v>
       </c>
       <c r="D565" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E565" t="s">
         <v>57</v>
@@ -18508,18 +18538,18 @@
         <v>58</v>
       </c>
       <c r="G565" s="1">
-        <v>46227</v>
+        <v>46213</v>
       </c>
       <c r="H565" s="1">
-        <v>46252</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B566" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="C566">
         <v>1</v>
@@ -18534,18 +18564,18 @@
         <v>58</v>
       </c>
       <c r="G566" s="1">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="H566" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B567" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="C567">
         <v>1</v>
@@ -18560,24 +18590,24 @@
         <v>78</v>
       </c>
       <c r="G567" s="1">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="H567" s="1">
-        <v>46252</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B568" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="C568">
         <v>1</v>
       </c>
       <c r="D568" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E568" t="s">
         <v>57</v>
@@ -18586,18 +18616,18 @@
         <v>58</v>
       </c>
       <c r="G568" s="1">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="H568" s="1">
-        <v>46231</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B569" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C569">
         <v>1</v>
@@ -18612,24 +18642,24 @@
         <v>58</v>
       </c>
       <c r="G569" s="1">
-        <v>46254</v>
+        <v>46227</v>
       </c>
       <c r="H569" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B570" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="C570">
         <v>1</v>
       </c>
       <c r="D570" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E570" t="s">
         <v>57</v>
@@ -18638,18 +18668,18 @@
         <v>58</v>
       </c>
       <c r="G570" s="1">
-        <v>46255</v>
+        <v>46227</v>
       </c>
       <c r="H570" s="1">
-        <v>46255</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B571" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C571">
         <v>1</v>
@@ -18658,24 +18688,24 @@
         <v>6</v>
       </c>
       <c r="E571" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F571" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G571" s="1">
-        <v>46260</v>
+        <v>46230</v>
       </c>
       <c r="H571" s="1">
-        <v>46260</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B572" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C572">
         <v>1</v>
@@ -18690,18 +18720,18 @@
         <v>58</v>
       </c>
       <c r="G572" s="1">
-        <v>46289</v>
+        <v>46231</v>
       </c>
       <c r="H572" s="1">
-        <v>46289</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B573" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="C573">
         <v>1</v>
@@ -18716,24 +18746,24 @@
         <v>58</v>
       </c>
       <c r="G573" s="1">
-        <v>46294</v>
+        <v>46254</v>
       </c>
       <c r="H573" s="1">
-        <v>46294</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B574" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="C574">
         <v>1</v>
       </c>
       <c r="D574" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E574" t="s">
         <v>57</v>
@@ -18742,24 +18772,24 @@
         <v>58</v>
       </c>
       <c r="G574" s="1">
-        <v>46301</v>
+        <v>46255</v>
       </c>
       <c r="H574" s="1">
-        <v>46301</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B575" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C575">
         <v>1</v>
       </c>
       <c r="D575" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E575" t="s">
         <v>57</v>
@@ -18768,24 +18798,24 @@
         <v>58</v>
       </c>
       <c r="G575" s="1">
-        <v>46301</v>
+        <v>46260</v>
       </c>
       <c r="H575" s="1">
-        <v>46301</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B576" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C576">
         <v>1</v>
       </c>
       <c r="D576" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E576" t="s">
         <v>57</v>
@@ -18794,24 +18824,24 @@
         <v>58</v>
       </c>
       <c r="G576" s="1">
-        <v>46301</v>
+        <v>46289</v>
       </c>
       <c r="H576" s="1">
-        <v>46301</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B577" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="C577">
         <v>1</v>
       </c>
       <c r="D577" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>57</v>
@@ -18820,18 +18850,18 @@
         <v>58</v>
       </c>
       <c r="G577" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="H577" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B578" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C578">
         <v>1</v>
@@ -18854,10 +18884,10 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B579" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C579">
         <v>1</v>
@@ -18880,10 +18910,10 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B580" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="C580">
         <v>1</v>
@@ -18906,10 +18936,10 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="B581" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="C581">
         <v>1</v>
@@ -18932,114 +18962,114 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
       <c r="B582" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="C582">
         <v>1</v>
       </c>
       <c r="D582" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E582" t="s">
-        <v>1094</v>
+        <v>57</v>
       </c>
       <c r="F582" t="s">
-        <v>1095</v>
+        <v>58</v>
       </c>
       <c r="G582" s="1">
-        <v>46157</v>
+        <v>46301</v>
       </c>
       <c r="H582" s="1">
-        <v>46157</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
       <c r="B583" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="C583">
         <v>1</v>
       </c>
       <c r="D583" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E583" t="s">
-        <v>1097</v>
+        <v>57</v>
       </c>
       <c r="F583" t="s">
-        <v>1098</v>
+        <v>58</v>
       </c>
       <c r="G583" s="1">
-        <v>46168</v>
+        <v>46301</v>
       </c>
       <c r="H583" s="1">
-        <v>46170</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
       <c r="B584" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C584">
         <v>1</v>
       </c>
       <c r="D584" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E584" t="s">
-        <v>1094</v>
+        <v>57</v>
       </c>
       <c r="F584" t="s">
-        <v>1095</v>
+        <v>58</v>
       </c>
       <c r="G584" s="1">
-        <v>46218</v>
+        <v>46301</v>
       </c>
       <c r="H584" s="1">
-        <v>46218</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
       <c r="B585" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C585">
         <v>1</v>
       </c>
       <c r="D585" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E585" t="s">
-        <v>1094</v>
+        <v>57</v>
       </c>
       <c r="F585" t="s">
-        <v>1095</v>
+        <v>58</v>
       </c>
       <c r="G585" s="1">
-        <v>46244</v>
+        <v>46301</v>
       </c>
       <c r="H585" s="1">
-        <v>46244</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B586" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C586">
         <v>1</v>
@@ -19048,24 +19078,24 @@
         <v>2</v>
       </c>
       <c r="E586" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="F586" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G586" s="1">
-        <v>46247</v>
+        <v>46157</v>
       </c>
       <c r="H586" s="1">
-        <v>46247</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B587" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C587">
         <v>1</v>
@@ -19074,24 +19104,24 @@
         <v>2</v>
       </c>
       <c r="E587" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="F587" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="G587" s="1">
-        <v>46247</v>
+        <v>46168</v>
       </c>
       <c r="H587" s="1">
-        <v>46247</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B588" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C588">
         <v>1</v>
@@ -19100,24 +19130,24 @@
         <v>2</v>
       </c>
       <c r="E588" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="F588" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G588" s="1">
-        <v>46255</v>
+        <v>46218</v>
       </c>
       <c r="H588" s="1">
-        <v>46255</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B589" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C589">
         <v>1</v>
@@ -19126,24 +19156,24 @@
         <v>2</v>
       </c>
       <c r="E589" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="F589" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G589" s="1">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="H589" s="1">
-        <v>46258</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B590" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="C590">
         <v>1</v>
@@ -19152,41 +19182,145 @@
         <v>2</v>
       </c>
       <c r="E590" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="F590" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G590" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="H590" s="1">
-        <v>46265</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="B591" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C591">
         <v>1</v>
       </c>
       <c r="D591" t="s">
+        <v>2</v>
+      </c>
+      <c r="E591" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F591" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G591" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H591" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A592" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C592">
+        <v>1</v>
+      </c>
+      <c r="D592" t="s">
+        <v>2</v>
+      </c>
+      <c r="E592" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F592" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G592" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H592" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A593" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C593">
+        <v>1</v>
+      </c>
+      <c r="D593" t="s">
+        <v>2</v>
+      </c>
+      <c r="E593" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F593" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G593" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H593" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A594" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C594">
+        <v>1</v>
+      </c>
+      <c r="D594" t="s">
+        <v>2</v>
+      </c>
+      <c r="E594" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F594" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G594" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H594" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C595">
+        <v>1</v>
+      </c>
+      <c r="D595" t="s">
         <v>6</v>
       </c>
-      <c r="E591" t="s">
+      <c r="E595" t="s">
         <v>13</v>
       </c>
-      <c r="F591" t="s">
+      <c r="F595" t="s">
         <v>14</v>
       </c>
-      <c r="G591" s="1">
+      <c r="G595" s="1">
         <v>46281</v>
       </c>
-      <c r="H591" s="1">
+      <c r="H595" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FA92BC2-AC2D-449D-803C-1DD22BD3DBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04BF0C54-EF3F-4A51-A965-29271E3CDDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4A7C9FCC-8ACC-4C71-8143-3C4F66FF6395}"/>
+    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{48EEEAB2-6CCC-47EC-B8AB-014012AE06ED}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="1134">
   <si>
     <t>0001</t>
   </si>
@@ -994,9 +994,6 @@
     <t>ABASTECIMIENTOS PLASTICOS S.R.L. -ABAS PLAS</t>
   </si>
   <si>
-    <t xml:space="preserve">  216292</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216295</t>
   </si>
   <si>
@@ -1525,6 +1522,9 @@
     <t xml:space="preserve">  216689</t>
   </si>
   <si>
+    <t xml:space="preserve">  216692</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216695</t>
   </si>
   <si>
@@ -2107,6 +2107,9 @@
     <t>AQUA SANITARIOS TANDIL S. R. L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  216906</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216908</t>
   </si>
   <si>
@@ -3079,6 +3082,54 @@
     <t xml:space="preserve">  217112</t>
   </si>
   <si>
+    <t xml:space="preserve">  217113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217116</t>
+  </si>
+  <si>
+    <t>CC52</t>
+  </si>
+  <si>
+    <t>CHEN CHING MEI- SANITARIOS DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217117</t>
+  </si>
+  <si>
+    <t>CO42</t>
+  </si>
+  <si>
+    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217118</t>
+  </si>
+  <si>
+    <t>DM20</t>
+  </si>
+  <si>
+    <t>DECO MIRACEMA SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217119</t>
+  </si>
+  <si>
+    <t>BH09</t>
+  </si>
+  <si>
+    <t>BONOMI HERNAN ALBERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217120</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -3178,9 +3229,6 @@
     <t xml:space="preserve">    2997</t>
   </si>
   <si>
-    <t xml:space="preserve">    2998</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3000</t>
   </si>
   <si>
@@ -3196,9 +3244,6 @@
     <t xml:space="preserve">    3002</t>
   </si>
   <si>
-    <t xml:space="preserve">    3003</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3004</t>
   </si>
   <si>
@@ -3302,30 +3347,6 @@
   </si>
   <si>
     <t xml:space="preserve">    2644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2735</t>
   </si>
   <si>
     <t>9999</t>
@@ -3850,34 +3871,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3805E581-45E9-4BDB-9E62-FC6A01FC27C0}">
-  <dimension ref="A1:H595"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43366DD-0BD3-40F5-9CC0-9D66AE907CB0}">
+  <dimension ref="A1:H594"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5139,7 +5160,7 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E50" t="s">
         <v>124</v>
@@ -7401,13 +7422,13 @@
         <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E137" t="s">
-        <v>87</v>
+        <v>325</v>
       </c>
       <c r="F137" t="s">
-        <v>88</v>
+        <v>326</v>
       </c>
       <c r="G137" s="1">
         <v>46288</v>
@@ -7421,25 +7442,25 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F138" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G138" s="1">
         <v>46288</v>
       </c>
       <c r="H138" s="1">
-        <v>46288</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -7447,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" t="s">
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F139" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G139" s="1">
         <v>46288</v>
       </c>
       <c r="H139" s="1">
-        <v>46295</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -7473,25 +7494,25 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E140" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F140" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G140" s="1">
         <v>46288</v>
       </c>
       <c r="H140" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -7499,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7508,16 +7529,16 @@
         <v>80</v>
       </c>
       <c r="E141" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F141" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G141" s="1">
         <v>46288</v>
       </c>
       <c r="H141" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -7525,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7534,10 +7555,10 @@
         <v>80</v>
       </c>
       <c r="E142" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F142" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G142" s="1">
         <v>46288</v>
@@ -7551,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7560,10 +7581,10 @@
         <v>80</v>
       </c>
       <c r="E143" t="s">
-        <v>341</v>
+        <v>98</v>
       </c>
       <c r="F143" t="s">
-        <v>342</v>
+        <v>99</v>
       </c>
       <c r="G143" s="1">
         <v>46288</v>
@@ -7583,19 +7604,19 @@
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="F144" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="G144" s="1">
         <v>46288</v>
       </c>
       <c r="H144" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -7606,22 +7627,22 @@
         <v>344</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E145" t="s">
-        <v>221</v>
+        <v>93</v>
       </c>
       <c r="F145" t="s">
-        <v>222</v>
+        <v>94</v>
       </c>
       <c r="G145" s="1">
         <v>46288</v>
       </c>
       <c r="H145" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -7632,22 +7653,22 @@
         <v>345</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" t="s">
         <v>80</v>
       </c>
       <c r="E146" t="s">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c r="F146" t="s">
-        <v>94</v>
+        <v>347</v>
       </c>
       <c r="G146" s="1">
         <v>46288</v>
       </c>
       <c r="H146" s="1">
-        <v>46293</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -7655,19 +7676,19 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
+        <v>348</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>80</v>
+      </c>
+      <c r="E147" t="s">
         <v>346</v>
       </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>80</v>
-      </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>347</v>
-      </c>
-      <c r="F147" t="s">
-        <v>348</v>
       </c>
       <c r="G147" s="1">
         <v>46288</v>
@@ -7690,10 +7711,10 @@
         <v>80</v>
       </c>
       <c r="E148" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F148" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G148" s="1">
         <v>46288</v>
@@ -7707,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -7716,10 +7737,10 @@
         <v>80</v>
       </c>
       <c r="E149" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F149" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G149" s="1">
         <v>46288</v>
@@ -7733,19 +7754,19 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="F150" t="s">
-        <v>355</v>
+        <v>38</v>
       </c>
       <c r="G150" s="1">
         <v>46288</v>
@@ -7933,7 +7954,7 @@
         <v>46288</v>
       </c>
       <c r="H157" s="1">
-        <v>46288</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -7950,16 +7971,16 @@
         <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>37</v>
+        <v>364</v>
       </c>
       <c r="F158" t="s">
-        <v>38</v>
+        <v>365</v>
       </c>
       <c r="G158" s="1">
         <v>46288</v>
       </c>
       <c r="H158" s="1">
-        <v>46301</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -7967,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7976,13 +7997,13 @@
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F159" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G159" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H159" s="1">
         <v>46289</v>
@@ -7993,7 +8014,7 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8002,10 +8023,10 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F160" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G160" s="1">
         <v>46289</v>
@@ -8019,25 +8040,25 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D161" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E161" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F161" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G161" s="1">
         <v>46289</v>
       </c>
       <c r="H161" s="1">
-        <v>46289</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -8045,25 +8066,25 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F162" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G162" s="1">
         <v>46289</v>
       </c>
       <c r="H162" s="1">
-        <v>46301</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -8071,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8080,16 +8101,16 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F163" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G163" s="1">
         <v>46289</v>
       </c>
       <c r="H163" s="1">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -8097,25 +8118,25 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D164" t="s">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F164" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G164" s="1">
         <v>46289</v>
       </c>
       <c r="H164" s="1">
-        <v>46289</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -8123,25 +8144,25 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="s">
         <v>80</v>
       </c>
       <c r="E165" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F165" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G165" s="1">
         <v>46289</v>
       </c>
       <c r="H165" s="1">
-        <v>46300</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -8149,25 +8170,25 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
         <v>80</v>
       </c>
       <c r="E166" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F166" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G166" s="1">
         <v>46289</v>
       </c>
       <c r="H166" s="1">
-        <v>46296</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -8175,25 +8196,25 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C167">
         <v>2</v>
       </c>
       <c r="D167" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="F167" t="s">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="G167" s="1">
         <v>46289</v>
       </c>
       <c r="H167" s="1">
-        <v>46300</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -8204,16 +8225,16 @@
         <v>391</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168" t="s">
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="F168" t="s">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="G168" s="1">
         <v>46289</v>
@@ -8227,22 +8248,22 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
         <v>2</v>
       </c>
       <c r="E169" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F169" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G169" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H169" s="1">
         <v>46294</v>
@@ -8253,19 +8274,19 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C170">
         <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="F170" t="s">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="G170" s="1">
         <v>46290</v>
@@ -8282,7 +8303,7 @@
         <v>398</v>
       </c>
       <c r="C171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="s">
         <v>2</v>
@@ -8314,16 +8335,16 @@
         <v>80</v>
       </c>
       <c r="E172" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F172" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G172" s="1">
         <v>46290</v>
       </c>
       <c r="H172" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -8334,22 +8355,22 @@
         <v>400</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" t="s">
         <v>80</v>
       </c>
       <c r="E173" t="s">
-        <v>93</v>
+        <v>401</v>
       </c>
       <c r="F173" t="s">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="G173" s="1">
         <v>46290</v>
       </c>
       <c r="H173" s="1">
-        <v>46290</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -8357,25 +8378,25 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F174" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G174" s="1">
         <v>46290</v>
       </c>
       <c r="H174" s="1">
-        <v>46297</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -8383,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8392,10 +8413,10 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F175" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G175" s="1">
         <v>46290</v>
@@ -8409,19 +8430,19 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E176" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F176" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G176" s="1">
         <v>46290</v>
@@ -8435,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8444,16 +8465,16 @@
         <v>80</v>
       </c>
       <c r="E177" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="F177" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="G177" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H177" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -8467,13 +8488,13 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E178" t="s">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="F178" t="s">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="G178" s="1">
         <v>46293</v>
@@ -8493,13 +8514,13 @@
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="F179" t="s">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="G179" s="1">
         <v>46293</v>
@@ -8513,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8522,10 +8543,10 @@
         <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>416</v>
+        <v>16</v>
       </c>
       <c r="F180" t="s">
-        <v>417</v>
+        <v>17</v>
       </c>
       <c r="G180" s="1">
         <v>46293</v>
@@ -8568,22 +8589,22 @@
         <v>419</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E182" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="F182" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="G182" s="1">
         <v>46293</v>
       </c>
       <c r="H182" s="1">
-        <v>46293</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -8600,16 +8621,16 @@
         <v>80</v>
       </c>
       <c r="E183" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="F183" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="G183" s="1">
         <v>46293</v>
       </c>
       <c r="H183" s="1">
-        <v>46297</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -8620,22 +8641,22 @@
         <v>421</v>
       </c>
       <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184" t="s">
         <v>2</v>
       </c>
-      <c r="D184" t="s">
-        <v>80</v>
-      </c>
       <c r="E184" t="s">
-        <v>16</v>
+        <v>422</v>
       </c>
       <c r="F184" t="s">
-        <v>17</v>
+        <v>423</v>
       </c>
       <c r="G184" s="1">
         <v>46293</v>
       </c>
       <c r="H184" s="1">
-        <v>46301</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -8643,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8652,16 +8673,16 @@
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>423</v>
+        <v>37</v>
       </c>
       <c r="F185" t="s">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="G185" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H185" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -8704,10 +8725,10 @@
         <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="F187" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="G187" s="1">
         <v>46294</v>
@@ -8753,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E189" t="s">
         <v>87</v>
@@ -8782,10 +8803,10 @@
         <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>87</v>
+        <v>401</v>
       </c>
       <c r="F190" t="s">
-        <v>88</v>
+        <v>402</v>
       </c>
       <c r="G190" s="1">
         <v>46294</v>
@@ -8805,13 +8826,13 @@
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E191" t="s">
-        <v>402</v>
+        <v>143</v>
       </c>
       <c r="F191" t="s">
-        <v>403</v>
+        <v>144</v>
       </c>
       <c r="G191" s="1">
         <v>46294</v>
@@ -8834,10 +8855,10 @@
         <v>80</v>
       </c>
       <c r="E192" t="s">
-        <v>143</v>
+        <v>432</v>
       </c>
       <c r="F192" t="s">
-        <v>144</v>
+        <v>433</v>
       </c>
       <c r="G192" s="1">
         <v>46294</v>
@@ -8851,7 +8872,7 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -8860,10 +8881,10 @@
         <v>80</v>
       </c>
       <c r="E193" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F193" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G193" s="1">
         <v>46294</v>
@@ -8877,7 +8898,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -8886,10 +8907,10 @@
         <v>80</v>
       </c>
       <c r="E194" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F194" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G194" s="1">
         <v>46294</v>
@@ -8903,7 +8924,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -8912,10 +8933,10 @@
         <v>80</v>
       </c>
       <c r="E195" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F195" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G195" s="1">
         <v>46294</v>
@@ -8929,19 +8950,19 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
+        <v>443</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>80</v>
+      </c>
+      <c r="E196" t="s">
         <v>441</v>
       </c>
-      <c r="C196">
-        <v>1</v>
-      </c>
-      <c r="D196" t="s">
-        <v>80</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>442</v>
-      </c>
-      <c r="F196" t="s">
-        <v>443</v>
       </c>
       <c r="G196" s="1">
         <v>46294</v>
@@ -8964,10 +8985,10 @@
         <v>80</v>
       </c>
       <c r="E197" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F197" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G197" s="1">
         <v>46294</v>
@@ -8981,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -8990,10 +9011,10 @@
         <v>80</v>
       </c>
       <c r="E198" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F198" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G198" s="1">
         <v>46294</v>
@@ -9007,19 +9028,19 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F199" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G199" s="1">
         <v>46294</v>
@@ -9033,19 +9054,19 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>452</v>
+        <v>77</v>
       </c>
       <c r="F200" t="s">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="G200" s="1">
         <v>46294</v>
@@ -9091,13 +9112,13 @@
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E202" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F202" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G202" s="1">
         <v>46294</v>
@@ -9120,10 +9141,10 @@
         <v>80</v>
       </c>
       <c r="E203" t="s">
-        <v>93</v>
+        <v>457</v>
       </c>
       <c r="F203" t="s">
-        <v>94</v>
+        <v>458</v>
       </c>
       <c r="G203" s="1">
         <v>46294</v>
@@ -9137,19 +9158,19 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F204" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G204" s="1">
         <v>46294</v>
@@ -9163,19 +9184,19 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="F205" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="G205" s="1">
         <v>46294</v>
@@ -9195,13 +9216,13 @@
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
+        <v>451</v>
+      </c>
+      <c r="F206" t="s">
         <v>452</v>
-      </c>
-      <c r="F206" t="s">
-        <v>453</v>
       </c>
       <c r="G206" s="1">
         <v>46294</v>
@@ -9221,13 +9242,13 @@
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F207" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="G207" s="1">
         <v>46294</v>
@@ -9241,19 +9262,19 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E208" t="s">
-        <v>466</v>
+        <v>247</v>
       </c>
       <c r="F208" t="s">
-        <v>467</v>
+        <v>248</v>
       </c>
       <c r="G208" s="1">
         <v>46294</v>
@@ -9270,10 +9291,10 @@
         <v>468</v>
       </c>
       <c r="C209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D209" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E209" t="s">
         <v>247</v>
@@ -9285,7 +9306,7 @@
         <v>46294</v>
       </c>
       <c r="H209" s="1">
-        <v>46294</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -9296,22 +9317,22 @@
         <v>469</v>
       </c>
       <c r="C210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E210" t="s">
-        <v>247</v>
+        <v>470</v>
       </c>
       <c r="F210" t="s">
-        <v>248</v>
+        <v>471</v>
       </c>
       <c r="G210" s="1">
         <v>46294</v>
       </c>
       <c r="H210" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -9319,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -9328,10 +9349,10 @@
         <v>80</v>
       </c>
       <c r="E211" t="s">
-        <v>471</v>
+        <v>155</v>
       </c>
       <c r="F211" t="s">
-        <v>472</v>
+        <v>156</v>
       </c>
       <c r="G211" s="1">
         <v>46294</v>
@@ -9354,10 +9375,10 @@
         <v>80</v>
       </c>
       <c r="E212" t="s">
-        <v>155</v>
+        <v>474</v>
       </c>
       <c r="F212" t="s">
-        <v>156</v>
+        <v>475</v>
       </c>
       <c r="G212" s="1">
         <v>46294</v>
@@ -9371,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -9380,10 +9401,10 @@
         <v>80</v>
       </c>
       <c r="E213" t="s">
-        <v>475</v>
+        <v>16</v>
       </c>
       <c r="F213" t="s">
-        <v>476</v>
+        <v>17</v>
       </c>
       <c r="G213" s="1">
         <v>46294</v>
@@ -9406,10 +9427,10 @@
         <v>80</v>
       </c>
       <c r="E214" t="s">
-        <v>16</v>
+        <v>478</v>
       </c>
       <c r="F214" t="s">
-        <v>17</v>
+        <v>479</v>
       </c>
       <c r="G214" s="1">
         <v>46294</v>
@@ -9423,7 +9444,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -9432,16 +9453,16 @@
         <v>80</v>
       </c>
       <c r="E215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F215" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G215" s="1">
         <v>46294</v>
       </c>
       <c r="H215" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -9449,25 +9470,25 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D216" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G216" s="1">
         <v>46294</v>
       </c>
       <c r="H216" s="1">
-        <v>46295</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -9475,25 +9496,25 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C217">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217" t="s">
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F217" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G217" s="1">
         <v>46294</v>
       </c>
       <c r="H217" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -9501,25 +9522,25 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E218" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F218" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G218" s="1">
         <v>46294</v>
       </c>
       <c r="H218" s="1">
-        <v>46295</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -9527,25 +9548,25 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D219" t="s">
         <v>80</v>
       </c>
       <c r="E219" t="s">
-        <v>491</v>
+        <v>37</v>
       </c>
       <c r="F219" t="s">
-        <v>492</v>
+        <v>38</v>
       </c>
       <c r="G219" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H219" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -9585,13 +9606,13 @@
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F221" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="G221" s="1">
         <v>46295</v>
@@ -9611,13 +9632,13 @@
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E222" t="s">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="F222" t="s">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="G222" s="1">
         <v>46295</v>
@@ -9631,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -9640,10 +9661,10 @@
         <v>80</v>
       </c>
       <c r="E223" t="s">
-        <v>497</v>
+        <v>410</v>
       </c>
       <c r="F223" t="s">
-        <v>498</v>
+        <v>411</v>
       </c>
       <c r="G223" s="1">
         <v>46295</v>
@@ -9663,13 +9684,13 @@
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="F224" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="G224" s="1">
         <v>46295</v>
@@ -9692,16 +9713,16 @@
         <v>80</v>
       </c>
       <c r="E225" t="s">
-        <v>452</v>
+        <v>31</v>
       </c>
       <c r="F225" t="s">
-        <v>453</v>
+        <v>32</v>
       </c>
       <c r="G225" s="1">
         <v>46295</v>
       </c>
       <c r="H225" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -9718,10 +9739,10 @@
         <v>80</v>
       </c>
       <c r="E226" t="s">
+        <v>410</v>
+      </c>
+      <c r="F226" t="s">
         <v>411</v>
-      </c>
-      <c r="F226" t="s">
-        <v>412</v>
       </c>
       <c r="G226" s="1">
         <v>46295</v>
@@ -9744,10 +9765,10 @@
         <v>80</v>
       </c>
       <c r="E227" t="s">
+        <v>410</v>
+      </c>
+      <c r="F227" t="s">
         <v>411</v>
-      </c>
-      <c r="F227" t="s">
-        <v>412</v>
       </c>
       <c r="G227" s="1">
         <v>46295</v>
@@ -9793,13 +9814,13 @@
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E229" t="s">
+        <v>460</v>
+      </c>
+      <c r="F229" t="s">
         <v>461</v>
-      </c>
-      <c r="F229" t="s">
-        <v>462</v>
       </c>
       <c r="G229" s="1">
         <v>46295</v>
@@ -9871,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E232" t="s">
         <v>143</v>
@@ -9975,13 +9996,13 @@
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E236" t="s">
+        <v>395</v>
+      </c>
+      <c r="F236" t="s">
         <v>396</v>
-      </c>
-      <c r="F236" t="s">
-        <v>397</v>
       </c>
       <c r="G236" s="1">
         <v>46295</v>
@@ -10004,10 +10025,10 @@
         <v>80</v>
       </c>
       <c r="E237" t="s">
+        <v>353</v>
+      </c>
+      <c r="F237" t="s">
         <v>354</v>
-      </c>
-      <c r="F237" t="s">
-        <v>355</v>
       </c>
       <c r="G237" s="1">
         <v>46295</v>
@@ -10339,7 +10360,7 @@
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E250" t="s">
         <v>532</v>
@@ -10833,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E269" t="s">
         <v>565</v>
@@ -10859,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E270" t="s">
         <v>565</v>
@@ -10885,7 +10906,7 @@
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E271" t="s">
         <v>565</v>
@@ -11252,10 +11273,10 @@
         <v>80</v>
       </c>
       <c r="E285" t="s">
+        <v>478</v>
+      </c>
+      <c r="F285" t="s">
         <v>479</v>
-      </c>
-      <c r="F285" t="s">
-        <v>480</v>
       </c>
       <c r="G285" s="1">
         <v>46296</v>
@@ -11278,10 +11299,10 @@
         <v>80</v>
       </c>
       <c r="E286" t="s">
+        <v>478</v>
+      </c>
+      <c r="F286" t="s">
         <v>479</v>
-      </c>
-      <c r="F286" t="s">
-        <v>480</v>
       </c>
       <c r="G286" s="1">
         <v>46296</v>
@@ -11301,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E287" t="s">
         <v>599</v>
@@ -11327,7 +11348,7 @@
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E288" t="s">
         <v>565</v>
@@ -11405,13 +11426,13 @@
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E291" t="s">
+        <v>451</v>
+      </c>
+      <c r="F291" t="s">
         <v>452</v>
-      </c>
-      <c r="F291" t="s">
-        <v>453</v>
       </c>
       <c r="G291" s="1">
         <v>46297</v>
@@ -11457,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E293" t="s">
         <v>25</v>
@@ -11538,10 +11559,10 @@
         <v>80</v>
       </c>
       <c r="E296" t="s">
+        <v>331</v>
+      </c>
+      <c r="F296" t="s">
         <v>332</v>
-      </c>
-      <c r="F296" t="s">
-        <v>333</v>
       </c>
       <c r="G296" s="1">
         <v>46297</v>
@@ -11564,10 +11585,10 @@
         <v>80</v>
       </c>
       <c r="E297" t="s">
+        <v>331</v>
+      </c>
+      <c r="F297" t="s">
         <v>332</v>
-      </c>
-      <c r="F297" t="s">
-        <v>333</v>
       </c>
       <c r="G297" s="1">
         <v>46297</v>
@@ -12081,13 +12102,13 @@
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E317" t="s">
+        <v>451</v>
+      </c>
+      <c r="F317" t="s">
         <v>452</v>
-      </c>
-      <c r="F317" t="s">
-        <v>453</v>
       </c>
       <c r="G317" s="1">
         <v>46297</v>
@@ -12292,10 +12313,10 @@
         <v>80</v>
       </c>
       <c r="E325" t="s">
+        <v>401</v>
+      </c>
+      <c r="F325" t="s">
         <v>402</v>
-      </c>
-      <c r="F325" t="s">
-        <v>403</v>
       </c>
       <c r="G325" s="1">
         <v>46297</v>
@@ -12370,10 +12391,10 @@
         <v>80</v>
       </c>
       <c r="E328" t="s">
+        <v>481</v>
+      </c>
+      <c r="F328" t="s">
         <v>482</v>
-      </c>
-      <c r="F328" t="s">
-        <v>483</v>
       </c>
       <c r="G328" s="1">
         <v>46297</v>
@@ -12786,16 +12807,16 @@
         <v>80</v>
       </c>
       <c r="E344" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="F344" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="G344" s="1">
         <v>46297</v>
       </c>
       <c r="H344" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
@@ -12812,10 +12833,10 @@
         <v>80</v>
       </c>
       <c r="E345" t="s">
-        <v>697</v>
+        <v>272</v>
       </c>
       <c r="F345" t="s">
-        <v>698</v>
+        <v>273</v>
       </c>
       <c r="G345" s="1">
         <v>46297</v>
@@ -12829,19 +12850,19 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
+        <v>697</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+      <c r="D346" t="s">
+        <v>80</v>
+      </c>
+      <c r="E346" t="s">
+        <v>698</v>
+      </c>
+      <c r="F346" t="s">
         <v>699</v>
-      </c>
-      <c r="C346">
-        <v>1</v>
-      </c>
-      <c r="D346" t="s">
-        <v>80</v>
-      </c>
-      <c r="E346" t="s">
-        <v>700</v>
-      </c>
-      <c r="F346" t="s">
-        <v>701</v>
       </c>
       <c r="G346" s="1">
         <v>46297</v>
@@ -12855,19 +12876,19 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
+        <v>700</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347" t="s">
+        <v>80</v>
+      </c>
+      <c r="E347" t="s">
+        <v>701</v>
+      </c>
+      <c r="F347" t="s">
         <v>702</v>
-      </c>
-      <c r="C347">
-        <v>1</v>
-      </c>
-      <c r="D347" t="s">
-        <v>80</v>
-      </c>
-      <c r="E347" t="s">
-        <v>310</v>
-      </c>
-      <c r="F347" t="s">
-        <v>311</v>
       </c>
       <c r="G347" s="1">
         <v>46297</v>
@@ -12890,10 +12911,10 @@
         <v>80</v>
       </c>
       <c r="E348" t="s">
-        <v>704</v>
+        <v>310</v>
       </c>
       <c r="F348" t="s">
-        <v>705</v>
+        <v>311</v>
       </c>
       <c r="G348" s="1">
         <v>46297</v>
@@ -12907,19 +12928,19 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
+        <v>704</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+      <c r="D349" t="s">
+        <v>80</v>
+      </c>
+      <c r="E349" t="s">
+        <v>705</v>
+      </c>
+      <c r="F349" t="s">
         <v>706</v>
-      </c>
-      <c r="C349">
-        <v>1</v>
-      </c>
-      <c r="D349" t="s">
-        <v>2</v>
-      </c>
-      <c r="E349" t="s">
-        <v>707</v>
-      </c>
-      <c r="F349" t="s">
-        <v>708</v>
       </c>
       <c r="G349" s="1">
         <v>46297</v>
@@ -12933,19 +12954,19 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
+        <v>707</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="s">
+        <v>2</v>
+      </c>
+      <c r="E350" t="s">
+        <v>708</v>
+      </c>
+      <c r="F350" t="s">
         <v>709</v>
-      </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-      <c r="D350" t="s">
-        <v>80</v>
-      </c>
-      <c r="E350" t="s">
-        <v>710</v>
-      </c>
-      <c r="F350" t="s">
-        <v>711</v>
       </c>
       <c r="G350" s="1">
         <v>46297</v>
@@ -12959,25 +12980,25 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
+        <v>710</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351" t="s">
+        <v>80</v>
+      </c>
+      <c r="E351" t="s">
+        <v>711</v>
+      </c>
+      <c r="F351" t="s">
         <v>712</v>
-      </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
-      <c r="D351" t="s">
-        <v>80</v>
-      </c>
-      <c r="E351" t="s">
-        <v>710</v>
-      </c>
-      <c r="F351" t="s">
-        <v>711</v>
       </c>
       <c r="G351" s="1">
         <v>46297</v>
       </c>
       <c r="H351" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
@@ -12994,10 +13015,10 @@
         <v>80</v>
       </c>
       <c r="E352" t="s">
-        <v>423</v>
+        <v>711</v>
       </c>
       <c r="F352" t="s">
-        <v>424</v>
+        <v>712</v>
       </c>
       <c r="G352" s="1">
         <v>46297</v>
@@ -13020,10 +13041,10 @@
         <v>80</v>
       </c>
       <c r="E353" t="s">
-        <v>715</v>
+        <v>422</v>
       </c>
       <c r="F353" t="s">
-        <v>716</v>
+        <v>423</v>
       </c>
       <c r="G353" s="1">
         <v>46297</v>
@@ -13037,19 +13058,19 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
+        <v>715</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354" t="s">
+        <v>80</v>
+      </c>
+      <c r="E354" t="s">
+        <v>716</v>
+      </c>
+      <c r="F354" t="s">
         <v>717</v>
-      </c>
-      <c r="C354">
-        <v>1</v>
-      </c>
-      <c r="D354" t="s">
-        <v>80</v>
-      </c>
-      <c r="E354" t="s">
-        <v>718</v>
-      </c>
-      <c r="F354" t="s">
-        <v>719</v>
       </c>
       <c r="G354" s="1">
         <v>46297</v>
@@ -13063,19 +13084,19 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
+        <v>718</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355" t="s">
+        <v>80</v>
+      </c>
+      <c r="E355" t="s">
+        <v>719</v>
+      </c>
+      <c r="F355" t="s">
         <v>720</v>
-      </c>
-      <c r="C355">
-        <v>1</v>
-      </c>
-      <c r="D355" t="s">
-        <v>80</v>
-      </c>
-      <c r="E355" t="s">
-        <v>365</v>
-      </c>
-      <c r="F355" t="s">
-        <v>366</v>
       </c>
       <c r="G355" s="1">
         <v>46297</v>
@@ -13098,10 +13119,10 @@
         <v>80</v>
       </c>
       <c r="E356" t="s">
-        <v>722</v>
+        <v>364</v>
       </c>
       <c r="F356" t="s">
-        <v>723</v>
+        <v>365</v>
       </c>
       <c r="G356" s="1">
         <v>46297</v>
@@ -13115,19 +13136,19 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
+        <v>722</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>2</v>
+      </c>
+      <c r="E357" t="s">
+        <v>723</v>
+      </c>
+      <c r="F357" t="s">
         <v>724</v>
-      </c>
-      <c r="C357">
-        <v>1</v>
-      </c>
-      <c r="D357" t="s">
-        <v>80</v>
-      </c>
-      <c r="E357" t="s">
-        <v>461</v>
-      </c>
-      <c r="F357" t="s">
-        <v>462</v>
       </c>
       <c r="G357" s="1">
         <v>46297</v>
@@ -13147,13 +13168,13 @@
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>726</v>
+        <v>460</v>
       </c>
       <c r="F358" t="s">
-        <v>727</v>
+        <v>461</v>
       </c>
       <c r="G358" s="1">
         <v>46297</v>
@@ -13167,19 +13188,19 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
+        <v>726</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359" t="s">
+        <v>2</v>
+      </c>
+      <c r="E359" t="s">
+        <v>727</v>
+      </c>
+      <c r="F359" t="s">
         <v>728</v>
-      </c>
-      <c r="C359">
-        <v>1</v>
-      </c>
-      <c r="D359" t="s">
-        <v>80</v>
-      </c>
-      <c r="E359" t="s">
-        <v>726</v>
-      </c>
-      <c r="F359" t="s">
-        <v>727</v>
       </c>
       <c r="G359" s="1">
         <v>46297</v>
@@ -13199,16 +13220,16 @@
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E360" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F360" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="G360" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="H360" s="1">
         <v>46300</v>
@@ -13219,19 +13240,19 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
+        <v>730</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+      <c r="D361" t="s">
+        <v>80</v>
+      </c>
+      <c r="E361" t="s">
+        <v>731</v>
+      </c>
+      <c r="F361" t="s">
         <v>732</v>
-      </c>
-      <c r="C361">
-        <v>1</v>
-      </c>
-      <c r="D361" t="s">
-        <v>80</v>
-      </c>
-      <c r="E361" t="s">
-        <v>730</v>
-      </c>
-      <c r="F361" t="s">
-        <v>731</v>
       </c>
       <c r="G361" s="1">
         <v>46298</v>
@@ -13254,13 +13275,13 @@
         <v>80</v>
       </c>
       <c r="E362" t="s">
-        <v>396</v>
+        <v>731</v>
       </c>
       <c r="F362" t="s">
-        <v>397</v>
+        <v>732</v>
       </c>
       <c r="G362" s="1">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="H362" s="1">
         <v>46300</v>
@@ -13277,13 +13298,13 @@
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E363" t="s">
-        <v>735</v>
+        <v>395</v>
       </c>
       <c r="F363" t="s">
-        <v>736</v>
+        <v>396</v>
       </c>
       <c r="G363" s="1">
         <v>46300</v>
@@ -13297,19 +13318,19 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
+        <v>735</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+      <c r="D364" t="s">
+        <v>2</v>
+      </c>
+      <c r="E364" t="s">
+        <v>736</v>
+      </c>
+      <c r="F364" t="s">
         <v>737</v>
-      </c>
-      <c r="C364">
-        <v>1</v>
-      </c>
-      <c r="D364" t="s">
-        <v>80</v>
-      </c>
-      <c r="E364" t="s">
-        <v>738</v>
-      </c>
-      <c r="F364" t="s">
-        <v>739</v>
       </c>
       <c r="G364" s="1">
         <v>46300</v>
@@ -13323,19 +13344,19 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
+        <v>738</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+      <c r="D365" t="s">
+        <v>80</v>
+      </c>
+      <c r="E365" t="s">
+        <v>739</v>
+      </c>
+      <c r="F365" t="s">
         <v>740</v>
-      </c>
-      <c r="C365">
-        <v>1</v>
-      </c>
-      <c r="D365" t="s">
-        <v>80</v>
-      </c>
-      <c r="E365" t="s">
-        <v>741</v>
-      </c>
-      <c r="F365" t="s">
-        <v>742</v>
       </c>
       <c r="G365" s="1">
         <v>46300</v>
@@ -13349,19 +13370,19 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
+        <v>741</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+      <c r="D366" t="s">
+        <v>80</v>
+      </c>
+      <c r="E366" t="s">
+        <v>742</v>
+      </c>
+      <c r="F366" t="s">
         <v>743</v>
-      </c>
-      <c r="C366">
-        <v>1</v>
-      </c>
-      <c r="D366" t="s">
-        <v>80</v>
-      </c>
-      <c r="E366" t="s">
-        <v>744</v>
-      </c>
-      <c r="F366" t="s">
-        <v>745</v>
       </c>
       <c r="G366" s="1">
         <v>46300</v>
@@ -13375,19 +13396,19 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
+        <v>744</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+      <c r="D367" t="s">
+        <v>80</v>
+      </c>
+      <c r="E367" t="s">
+        <v>745</v>
+      </c>
+      <c r="F367" t="s">
         <v>746</v>
-      </c>
-      <c r="C367">
-        <v>1</v>
-      </c>
-      <c r="D367" t="s">
-        <v>80</v>
-      </c>
-      <c r="E367" t="s">
-        <v>684</v>
-      </c>
-      <c r="F367" t="s">
-        <v>685</v>
       </c>
       <c r="G367" s="1">
         <v>46300</v>
@@ -13410,10 +13431,10 @@
         <v>80</v>
       </c>
       <c r="E368" t="s">
-        <v>748</v>
+        <v>684</v>
       </c>
       <c r="F368" t="s">
-        <v>749</v>
+        <v>685</v>
       </c>
       <c r="G368" s="1">
         <v>46300</v>
@@ -13427,19 +13448,19 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
+        <v>748</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+      <c r="D369" t="s">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>749</v>
+      </c>
+      <c r="F369" t="s">
         <v>750</v>
-      </c>
-      <c r="C369">
-        <v>1</v>
-      </c>
-      <c r="D369" t="s">
-        <v>80</v>
-      </c>
-      <c r="E369" t="s">
-        <v>751</v>
-      </c>
-      <c r="F369" t="s">
-        <v>752</v>
       </c>
       <c r="G369" s="1">
         <v>46300</v>
@@ -13453,19 +13474,19 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
+        <v>751</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+      <c r="D370" t="s">
+        <v>80</v>
+      </c>
+      <c r="E370" t="s">
+        <v>752</v>
+      </c>
+      <c r="F370" t="s">
         <v>753</v>
-      </c>
-      <c r="C370">
-        <v>1</v>
-      </c>
-      <c r="D370" t="s">
-        <v>80</v>
-      </c>
-      <c r="E370" t="s">
-        <v>754</v>
-      </c>
-      <c r="F370" t="s">
-        <v>755</v>
       </c>
       <c r="G370" s="1">
         <v>46300</v>
@@ -13479,19 +13500,19 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
+        <v>754</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+      <c r="D371" t="s">
+        <v>80</v>
+      </c>
+      <c r="E371" t="s">
+        <v>755</v>
+      </c>
+      <c r="F371" t="s">
         <v>756</v>
-      </c>
-      <c r="C371">
-        <v>1</v>
-      </c>
-      <c r="D371" t="s">
-        <v>80</v>
-      </c>
-      <c r="E371" t="s">
-        <v>240</v>
-      </c>
-      <c r="F371" t="s">
-        <v>241</v>
       </c>
       <c r="G371" s="1">
         <v>46300</v>
@@ -13514,10 +13535,10 @@
         <v>80</v>
       </c>
       <c r="E372" t="s">
-        <v>758</v>
+        <v>240</v>
       </c>
       <c r="F372" t="s">
-        <v>759</v>
+        <v>241</v>
       </c>
       <c r="G372" s="1">
         <v>46300</v>
@@ -13531,19 +13552,19 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
+        <v>758</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+      <c r="D373" t="s">
+        <v>80</v>
+      </c>
+      <c r="E373" t="s">
+        <v>759</v>
+      </c>
+      <c r="F373" t="s">
         <v>760</v>
-      </c>
-      <c r="C373">
-        <v>1</v>
-      </c>
-      <c r="D373" t="s">
-        <v>80</v>
-      </c>
-      <c r="E373" t="s">
-        <v>758</v>
-      </c>
-      <c r="F373" t="s">
-        <v>759</v>
       </c>
       <c r="G373" s="1">
         <v>46300</v>
@@ -13566,10 +13587,10 @@
         <v>80</v>
       </c>
       <c r="E374" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F374" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G374" s="1">
         <v>46300</v>
@@ -13592,10 +13613,10 @@
         <v>80</v>
       </c>
       <c r="E375" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F375" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G375" s="1">
         <v>46300</v>
@@ -13618,10 +13639,10 @@
         <v>80</v>
       </c>
       <c r="E376" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F376" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G376" s="1">
         <v>46300</v>
@@ -13644,10 +13665,10 @@
         <v>80</v>
       </c>
       <c r="E377" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F377" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G377" s="1">
         <v>46300</v>
@@ -13670,10 +13691,10 @@
         <v>80</v>
       </c>
       <c r="E378" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F378" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G378" s="1">
         <v>46300</v>
@@ -13696,10 +13717,10 @@
         <v>80</v>
       </c>
       <c r="E379" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="F379" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="G379" s="1">
         <v>46300</v>
@@ -13713,19 +13734,19 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
+        <v>767</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380" t="s">
+        <v>80</v>
+      </c>
+      <c r="E380" t="s">
+        <v>768</v>
+      </c>
+      <c r="F380" t="s">
         <v>769</v>
-      </c>
-      <c r="C380">
-        <v>1</v>
-      </c>
-      <c r="D380" t="s">
-        <v>80</v>
-      </c>
-      <c r="E380" t="s">
-        <v>758</v>
-      </c>
-      <c r="F380" t="s">
-        <v>759</v>
       </c>
       <c r="G380" s="1">
         <v>46300</v>
@@ -13748,10 +13769,10 @@
         <v>80</v>
       </c>
       <c r="E381" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="F381" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="G381" s="1">
         <v>46300</v>
@@ -13765,19 +13786,19 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
+        <v>771</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+      <c r="D382" t="s">
+        <v>80</v>
+      </c>
+      <c r="E382" t="s">
+        <v>772</v>
+      </c>
+      <c r="F382" t="s">
         <v>773</v>
-      </c>
-      <c r="C382">
-        <v>1</v>
-      </c>
-      <c r="D382" t="s">
-        <v>80</v>
-      </c>
-      <c r="E382" t="s">
-        <v>204</v>
-      </c>
-      <c r="F382" t="s">
-        <v>205</v>
       </c>
       <c r="G382" s="1">
         <v>46300</v>
@@ -13800,10 +13821,10 @@
         <v>80</v>
       </c>
       <c r="E383" t="s">
-        <v>775</v>
+        <v>204</v>
       </c>
       <c r="F383" t="s">
-        <v>776</v>
+        <v>205</v>
       </c>
       <c r="G383" s="1">
         <v>46300</v>
@@ -13817,19 +13838,19 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
+        <v>775</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384" t="s">
+        <v>80</v>
+      </c>
+      <c r="E384" t="s">
+        <v>776</v>
+      </c>
+      <c r="F384" t="s">
         <v>777</v>
-      </c>
-      <c r="C384">
-        <v>1</v>
-      </c>
-      <c r="D384" t="s">
-        <v>80</v>
-      </c>
-      <c r="E384" t="s">
-        <v>143</v>
-      </c>
-      <c r="F384" t="s">
-        <v>144</v>
       </c>
       <c r="G384" s="1">
         <v>46300</v>
@@ -13849,13 +13870,13 @@
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E385" t="s">
-        <v>377</v>
+        <v>143</v>
       </c>
       <c r="F385" t="s">
-        <v>378</v>
+        <v>144</v>
       </c>
       <c r="G385" s="1">
         <v>46300</v>
@@ -13878,10 +13899,10 @@
         <v>80</v>
       </c>
       <c r="E386" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="F386" t="s">
-        <v>26</v>
+        <v>377</v>
       </c>
       <c r="G386" s="1">
         <v>46300</v>
@@ -13901,13 +13922,13 @@
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E387" t="s">
-        <v>396</v>
+        <v>25</v>
       </c>
       <c r="F387" t="s">
-        <v>397</v>
+        <v>26</v>
       </c>
       <c r="G387" s="1">
         <v>46300</v>
@@ -13927,13 +13948,13 @@
         <v>1</v>
       </c>
       <c r="D388" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E388" t="s">
-        <v>782</v>
+        <v>395</v>
       </c>
       <c r="F388" t="s">
-        <v>783</v>
+        <v>396</v>
       </c>
       <c r="G388" s="1">
         <v>46300</v>
@@ -13947,19 +13968,19 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
+        <v>782</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>2</v>
+      </c>
+      <c r="E389" t="s">
+        <v>783</v>
+      </c>
+      <c r="F389" t="s">
         <v>784</v>
-      </c>
-      <c r="C389">
-        <v>1</v>
-      </c>
-      <c r="D389" t="s">
-        <v>80</v>
-      </c>
-      <c r="E389" t="s">
-        <v>785</v>
-      </c>
-      <c r="F389" t="s">
-        <v>786</v>
       </c>
       <c r="G389" s="1">
         <v>46300</v>
@@ -13973,19 +13994,19 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
+        <v>785</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>80</v>
+      </c>
+      <c r="E390" t="s">
+        <v>786</v>
+      </c>
+      <c r="F390" t="s">
         <v>787</v>
-      </c>
-      <c r="C390">
-        <v>1</v>
-      </c>
-      <c r="D390" t="s">
-        <v>80</v>
-      </c>
-      <c r="E390" t="s">
-        <v>788</v>
-      </c>
-      <c r="F390" t="s">
-        <v>789</v>
       </c>
       <c r="G390" s="1">
         <v>46300</v>
@@ -13999,19 +14020,19 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
+        <v>788</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>80</v>
+      </c>
+      <c r="E391" t="s">
+        <v>789</v>
+      </c>
+      <c r="F391" t="s">
         <v>790</v>
-      </c>
-      <c r="C391">
-        <v>1</v>
-      </c>
-      <c r="D391" t="s">
-        <v>80</v>
-      </c>
-      <c r="E391" t="s">
-        <v>785</v>
-      </c>
-      <c r="F391" t="s">
-        <v>786</v>
       </c>
       <c r="G391" s="1">
         <v>46300</v>
@@ -14034,10 +14055,10 @@
         <v>80</v>
       </c>
       <c r="E392" t="s">
-        <v>306</v>
+        <v>786</v>
       </c>
       <c r="F392" t="s">
-        <v>307</v>
+        <v>787</v>
       </c>
       <c r="G392" s="1">
         <v>46300</v>
@@ -14060,10 +14081,10 @@
         <v>80</v>
       </c>
       <c r="E393" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="F393" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="G393" s="1">
         <v>46300</v>
@@ -14086,10 +14107,10 @@
         <v>80</v>
       </c>
       <c r="E394" t="s">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="F394" t="s">
-        <v>241</v>
+        <v>8</v>
       </c>
       <c r="G394" s="1">
         <v>46300</v>
@@ -14112,10 +14133,10 @@
         <v>80</v>
       </c>
       <c r="E395" t="s">
-        <v>98</v>
+        <v>240</v>
       </c>
       <c r="F395" t="s">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="G395" s="1">
         <v>46300</v>
@@ -14135,7 +14156,7 @@
         <v>1</v>
       </c>
       <c r="D396" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E396" t="s">
         <v>98</v>
@@ -14164,10 +14185,10 @@
         <v>80</v>
       </c>
       <c r="E397" t="s">
-        <v>565</v>
+        <v>98</v>
       </c>
       <c r="F397" t="s">
-        <v>566</v>
+        <v>99</v>
       </c>
       <c r="G397" s="1">
         <v>46300</v>
@@ -14187,13 +14208,13 @@
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E398" t="s">
-        <v>798</v>
+        <v>565</v>
       </c>
       <c r="F398" t="s">
-        <v>799</v>
+        <v>566</v>
       </c>
       <c r="G398" s="1">
         <v>46300</v>
@@ -14207,25 +14228,25 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
+        <v>798</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>80</v>
+      </c>
+      <c r="E399" t="s">
+        <v>799</v>
+      </c>
+      <c r="F399" t="s">
         <v>800</v>
       </c>
-      <c r="C399">
-        <v>1</v>
-      </c>
-      <c r="D399" t="s">
-        <v>80</v>
-      </c>
-      <c r="E399" t="s">
-        <v>200</v>
-      </c>
-      <c r="F399" t="s">
-        <v>201</v>
-      </c>
       <c r="G399" s="1">
         <v>46300</v>
       </c>
       <c r="H399" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
@@ -14242,16 +14263,16 @@
         <v>80</v>
       </c>
       <c r="E400" t="s">
-        <v>538</v>
+        <v>200</v>
       </c>
       <c r="F400" t="s">
-        <v>539</v>
+        <v>201</v>
       </c>
       <c r="G400" s="1">
         <v>46300</v>
       </c>
       <c r="H400" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
@@ -14294,10 +14315,10 @@
         <v>80</v>
       </c>
       <c r="E402" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F402" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G402" s="1">
         <v>46300</v>
@@ -14320,10 +14341,10 @@
         <v>80</v>
       </c>
       <c r="E403" t="s">
-        <v>805</v>
+        <v>541</v>
       </c>
       <c r="F403" t="s">
-        <v>806</v>
+        <v>542</v>
       </c>
       <c r="G403" s="1">
         <v>46300</v>
@@ -14337,19 +14358,19 @@
         <v>0</v>
       </c>
       <c r="B404" t="s">
+        <v>805</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>80</v>
+      </c>
+      <c r="E404" t="s">
+        <v>806</v>
+      </c>
+      <c r="F404" t="s">
         <v>807</v>
-      </c>
-      <c r="C404">
-        <v>1</v>
-      </c>
-      <c r="D404" t="s">
-        <v>80</v>
-      </c>
-      <c r="E404" t="s">
-        <v>37</v>
-      </c>
-      <c r="F404" t="s">
-        <v>38</v>
       </c>
       <c r="G404" s="1">
         <v>46300</v>
@@ -14372,10 +14393,10 @@
         <v>80</v>
       </c>
       <c r="E405" t="s">
-        <v>805</v>
+        <v>37</v>
       </c>
       <c r="F405" t="s">
-        <v>806</v>
+        <v>38</v>
       </c>
       <c r="G405" s="1">
         <v>46300</v>
@@ -14398,10 +14419,10 @@
         <v>80</v>
       </c>
       <c r="E406" t="s">
-        <v>726</v>
+        <v>806</v>
       </c>
       <c r="F406" t="s">
-        <v>727</v>
+        <v>807</v>
       </c>
       <c r="G406" s="1">
         <v>46300</v>
@@ -14421,13 +14442,13 @@
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E407" t="s">
-        <v>811</v>
+        <v>727</v>
       </c>
       <c r="F407" t="s">
-        <v>812</v>
+        <v>728</v>
       </c>
       <c r="G407" s="1">
         <v>46300</v>
@@ -14441,19 +14462,19 @@
         <v>0</v>
       </c>
       <c r="B408" t="s">
+        <v>811</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>80</v>
+      </c>
+      <c r="E408" t="s">
+        <v>812</v>
+      </c>
+      <c r="F408" t="s">
         <v>813</v>
-      </c>
-      <c r="C408">
-        <v>1</v>
-      </c>
-      <c r="D408" t="s">
-        <v>80</v>
-      </c>
-      <c r="E408" t="s">
-        <v>767</v>
-      </c>
-      <c r="F408" t="s">
-        <v>768</v>
       </c>
       <c r="G408" s="1">
         <v>46300</v>
@@ -14476,10 +14497,10 @@
         <v>80</v>
       </c>
       <c r="E409" t="s">
-        <v>726</v>
+        <v>768</v>
       </c>
       <c r="F409" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="G409" s="1">
         <v>46300</v>
@@ -14499,13 +14520,13 @@
         <v>1</v>
       </c>
       <c r="D410" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E410" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F410" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G410" s="1">
         <v>46300</v>
@@ -14525,13 +14546,13 @@
         <v>1</v>
       </c>
       <c r="D411" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E411" t="s">
-        <v>817</v>
+        <v>727</v>
       </c>
       <c r="F411" t="s">
-        <v>818</v>
+        <v>728</v>
       </c>
       <c r="G411" s="1">
         <v>46300</v>
@@ -14545,19 +14566,19 @@
         <v>0</v>
       </c>
       <c r="B412" t="s">
+        <v>817</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" t="s">
+        <v>80</v>
+      </c>
+      <c r="E412" t="s">
+        <v>818</v>
+      </c>
+      <c r="F412" t="s">
         <v>819</v>
-      </c>
-      <c r="C412">
-        <v>1</v>
-      </c>
-      <c r="D412" t="s">
-        <v>80</v>
-      </c>
-      <c r="E412" t="s">
-        <v>16</v>
-      </c>
-      <c r="F412" t="s">
-        <v>17</v>
       </c>
       <c r="G412" s="1">
         <v>46300</v>
@@ -14580,10 +14601,10 @@
         <v>80</v>
       </c>
       <c r="E413" t="s">
-        <v>581</v>
+        <v>16</v>
       </c>
       <c r="F413" t="s">
-        <v>582</v>
+        <v>17</v>
       </c>
       <c r="G413" s="1">
         <v>46300</v>
@@ -14606,10 +14627,10 @@
         <v>80</v>
       </c>
       <c r="E414" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F414" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G414" s="1">
         <v>46300</v>
@@ -14632,10 +14653,10 @@
         <v>80</v>
       </c>
       <c r="E415" t="s">
-        <v>230</v>
+        <v>578</v>
       </c>
       <c r="F415" t="s">
-        <v>231</v>
+        <v>579</v>
       </c>
       <c r="G415" s="1">
         <v>46300</v>
@@ -14658,10 +14679,10 @@
         <v>80</v>
       </c>
       <c r="E416" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="F416" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G416" s="1">
         <v>46300</v>
@@ -14684,10 +14705,10 @@
         <v>80</v>
       </c>
       <c r="E417" t="s">
-        <v>635</v>
+        <v>253</v>
       </c>
       <c r="F417" t="s">
-        <v>636</v>
+        <v>254</v>
       </c>
       <c r="G417" s="1">
         <v>46300</v>
@@ -14710,10 +14731,10 @@
         <v>80</v>
       </c>
       <c r="E418" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="F418" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="G418" s="1">
         <v>46300</v>
@@ -14736,10 +14757,10 @@
         <v>80</v>
       </c>
       <c r="E419" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="F419" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="G419" s="1">
         <v>46300</v>
@@ -14762,10 +14783,10 @@
         <v>80</v>
       </c>
       <c r="E420" t="s">
-        <v>152</v>
+        <v>641</v>
       </c>
       <c r="F420" t="s">
-        <v>153</v>
+        <v>642</v>
       </c>
       <c r="G420" s="1">
         <v>46300</v>
@@ -14788,10 +14809,10 @@
         <v>80</v>
       </c>
       <c r="E421" t="s">
-        <v>452</v>
+        <v>152</v>
       </c>
       <c r="F421" t="s">
-        <v>453</v>
+        <v>153</v>
       </c>
       <c r="G421" s="1">
         <v>46300</v>
@@ -14811,13 +14832,13 @@
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E422" t="s">
-        <v>830</v>
+        <v>451</v>
       </c>
       <c r="F422" t="s">
-        <v>831</v>
+        <v>452</v>
       </c>
       <c r="G422" s="1">
         <v>46300</v>
@@ -14831,19 +14852,19 @@
         <v>0</v>
       </c>
       <c r="B423" t="s">
+        <v>830</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>80</v>
+      </c>
+      <c r="E423" t="s">
+        <v>831</v>
+      </c>
+      <c r="F423" t="s">
         <v>832</v>
-      </c>
-      <c r="C423">
-        <v>1</v>
-      </c>
-      <c r="D423" t="s">
-        <v>80</v>
-      </c>
-      <c r="E423" t="s">
-        <v>833</v>
-      </c>
-      <c r="F423" t="s">
-        <v>834</v>
       </c>
       <c r="G423" s="1">
         <v>46300</v>
@@ -14857,19 +14878,19 @@
         <v>0</v>
       </c>
       <c r="B424" t="s">
+        <v>833</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424" t="s">
+        <v>80</v>
+      </c>
+      <c r="E424" t="s">
+        <v>834</v>
+      </c>
+      <c r="F424" t="s">
         <v>835</v>
-      </c>
-      <c r="C424">
-        <v>1</v>
-      </c>
-      <c r="D424" t="s">
-        <v>80</v>
-      </c>
-      <c r="E424" t="s">
-        <v>836</v>
-      </c>
-      <c r="F424" t="s">
-        <v>837</v>
       </c>
       <c r="G424" s="1">
         <v>46300</v>
@@ -14883,19 +14904,19 @@
         <v>0</v>
       </c>
       <c r="B425" t="s">
+        <v>836</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425" t="s">
+        <v>80</v>
+      </c>
+      <c r="E425" t="s">
+        <v>837</v>
+      </c>
+      <c r="F425" t="s">
         <v>838</v>
-      </c>
-      <c r="C425">
-        <v>1</v>
-      </c>
-      <c r="D425" t="s">
-        <v>80</v>
-      </c>
-      <c r="E425" t="s">
-        <v>839</v>
-      </c>
-      <c r="F425" t="s">
-        <v>840</v>
       </c>
       <c r="G425" s="1">
         <v>46300</v>
@@ -14909,19 +14930,19 @@
         <v>0</v>
       </c>
       <c r="B426" t="s">
+        <v>839</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+      <c r="D426" t="s">
+        <v>80</v>
+      </c>
+      <c r="E426" t="s">
+        <v>840</v>
+      </c>
+      <c r="F426" t="s">
         <v>841</v>
-      </c>
-      <c r="C426">
-        <v>1</v>
-      </c>
-      <c r="D426" t="s">
-        <v>80</v>
-      </c>
-      <c r="E426" t="s">
-        <v>842</v>
-      </c>
-      <c r="F426" t="s">
-        <v>843</v>
       </c>
       <c r="G426" s="1">
         <v>46300</v>
@@ -14935,19 +14956,19 @@
         <v>0</v>
       </c>
       <c r="B427" t="s">
+        <v>842</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+      <c r="D427" t="s">
+        <v>80</v>
+      </c>
+      <c r="E427" t="s">
+        <v>843</v>
+      </c>
+      <c r="F427" t="s">
         <v>844</v>
-      </c>
-      <c r="C427">
-        <v>1</v>
-      </c>
-      <c r="D427" t="s">
-        <v>80</v>
-      </c>
-      <c r="E427" t="s">
-        <v>845</v>
-      </c>
-      <c r="F427" t="s">
-        <v>846</v>
       </c>
       <c r="G427" s="1">
         <v>46300</v>
@@ -14961,19 +14982,19 @@
         <v>0</v>
       </c>
       <c r="B428" t="s">
+        <v>845</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428" t="s">
+        <v>80</v>
+      </c>
+      <c r="E428" t="s">
+        <v>846</v>
+      </c>
+      <c r="F428" t="s">
         <v>847</v>
-      </c>
-      <c r="C428">
-        <v>1</v>
-      </c>
-      <c r="D428" t="s">
-        <v>80</v>
-      </c>
-      <c r="E428" t="s">
-        <v>98</v>
-      </c>
-      <c r="F428" t="s">
-        <v>99</v>
       </c>
       <c r="G428" s="1">
         <v>46300</v>
@@ -14993,13 +15014,13 @@
         <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E429" t="s">
-        <v>849</v>
+        <v>98</v>
       </c>
       <c r="F429" t="s">
-        <v>850</v>
+        <v>99</v>
       </c>
       <c r="G429" s="1">
         <v>46300</v>
@@ -15013,19 +15034,19 @@
         <v>0</v>
       </c>
       <c r="B430" t="s">
+        <v>849</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>80</v>
+      </c>
+      <c r="E430" t="s">
+        <v>850</v>
+      </c>
+      <c r="F430" t="s">
         <v>851</v>
-      </c>
-      <c r="C430">
-        <v>1</v>
-      </c>
-      <c r="D430" t="s">
-        <v>80</v>
-      </c>
-      <c r="E430" t="s">
-        <v>852</v>
-      </c>
-      <c r="F430" t="s">
-        <v>853</v>
       </c>
       <c r="G430" s="1">
         <v>46300</v>
@@ -15039,19 +15060,19 @@
         <v>0</v>
       </c>
       <c r="B431" t="s">
+        <v>852</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431" t="s">
+        <v>80</v>
+      </c>
+      <c r="E431" t="s">
+        <v>853</v>
+      </c>
+      <c r="F431" t="s">
         <v>854</v>
-      </c>
-      <c r="C431">
-        <v>1</v>
-      </c>
-      <c r="D431" t="s">
-        <v>80</v>
-      </c>
-      <c r="E431" t="s">
-        <v>852</v>
-      </c>
-      <c r="F431" t="s">
-        <v>853</v>
       </c>
       <c r="G431" s="1">
         <v>46300</v>
@@ -15074,10 +15095,10 @@
         <v>80</v>
       </c>
       <c r="E432" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="F432" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="G432" s="1">
         <v>46300</v>
@@ -15091,19 +15112,19 @@
         <v>0</v>
       </c>
       <c r="B433" t="s">
+        <v>856</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433" t="s">
+        <v>80</v>
+      </c>
+      <c r="E433" t="s">
+        <v>857</v>
+      </c>
+      <c r="F433" t="s">
         <v>858</v>
-      </c>
-      <c r="C433">
-        <v>1</v>
-      </c>
-      <c r="D433" t="s">
-        <v>80</v>
-      </c>
-      <c r="E433" t="s">
-        <v>856</v>
-      </c>
-      <c r="F433" t="s">
-        <v>857</v>
       </c>
       <c r="G433" s="1">
         <v>46300</v>
@@ -15126,10 +15147,10 @@
         <v>80</v>
       </c>
       <c r="E434" t="s">
-        <v>587</v>
+        <v>857</v>
       </c>
       <c r="F434" t="s">
-        <v>588</v>
+        <v>858</v>
       </c>
       <c r="G434" s="1">
         <v>46300</v>
@@ -15152,10 +15173,10 @@
         <v>80</v>
       </c>
       <c r="E435" t="s">
-        <v>861</v>
+        <v>587</v>
       </c>
       <c r="F435" t="s">
-        <v>862</v>
+        <v>588</v>
       </c>
       <c r="G435" s="1">
         <v>46300</v>
@@ -15169,19 +15190,19 @@
         <v>0</v>
       </c>
       <c r="B436" t="s">
+        <v>861</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436" t="s">
+        <v>80</v>
+      </c>
+      <c r="E436" t="s">
+        <v>862</v>
+      </c>
+      <c r="F436" t="s">
         <v>863</v>
-      </c>
-      <c r="C436">
-        <v>1</v>
-      </c>
-      <c r="D436" t="s">
-        <v>80</v>
-      </c>
-      <c r="E436" t="s">
-        <v>864</v>
-      </c>
-      <c r="F436" t="s">
-        <v>865</v>
       </c>
       <c r="G436" s="1">
         <v>46300</v>
@@ -15195,19 +15216,19 @@
         <v>0</v>
       </c>
       <c r="B437" t="s">
+        <v>864</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437" t="s">
+        <v>2</v>
+      </c>
+      <c r="E437" t="s">
+        <v>865</v>
+      </c>
+      <c r="F437" t="s">
         <v>866</v>
-      </c>
-      <c r="C437">
-        <v>1</v>
-      </c>
-      <c r="D437" t="s">
-        <v>80</v>
-      </c>
-      <c r="E437" t="s">
-        <v>726</v>
-      </c>
-      <c r="F437" t="s">
-        <v>727</v>
       </c>
       <c r="G437" s="1">
         <v>46300</v>
@@ -15227,13 +15248,13 @@
         <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E438" t="s">
-        <v>868</v>
+        <v>727</v>
       </c>
       <c r="F438" t="s">
-        <v>869</v>
+        <v>728</v>
       </c>
       <c r="G438" s="1">
         <v>46300</v>
@@ -15247,19 +15268,19 @@
         <v>0</v>
       </c>
       <c r="B439" t="s">
+        <v>868</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+      <c r="D439" t="s">
+        <v>80</v>
+      </c>
+      <c r="E439" t="s">
+        <v>869</v>
+      </c>
+      <c r="F439" t="s">
         <v>870</v>
-      </c>
-      <c r="C439">
-        <v>1</v>
-      </c>
-      <c r="D439" t="s">
-        <v>80</v>
-      </c>
-      <c r="E439" t="s">
-        <v>16</v>
-      </c>
-      <c r="F439" t="s">
-        <v>17</v>
       </c>
       <c r="G439" s="1">
         <v>46300</v>
@@ -15282,10 +15303,10 @@
         <v>80</v>
       </c>
       <c r="E440" t="s">
-        <v>872</v>
+        <v>16</v>
       </c>
       <c r="F440" t="s">
-        <v>873</v>
+        <v>17</v>
       </c>
       <c r="G440" s="1">
         <v>46300</v>
@@ -15299,19 +15320,19 @@
         <v>0</v>
       </c>
       <c r="B441" t="s">
+        <v>872</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+      <c r="D441" t="s">
+        <v>80</v>
+      </c>
+      <c r="E441" t="s">
+        <v>873</v>
+      </c>
+      <c r="F441" t="s">
         <v>874</v>
-      </c>
-      <c r="C441">
-        <v>1</v>
-      </c>
-      <c r="D441" t="s">
-        <v>2</v>
-      </c>
-      <c r="E441" t="s">
-        <v>875</v>
-      </c>
-      <c r="F441" t="s">
-        <v>876</v>
       </c>
       <c r="G441" s="1">
         <v>46300</v>
@@ -15325,19 +15346,19 @@
         <v>0</v>
       </c>
       <c r="B442" t="s">
+        <v>875</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+      <c r="D442" t="s">
+        <v>2</v>
+      </c>
+      <c r="E442" t="s">
+        <v>876</v>
+      </c>
+      <c r="F442" t="s">
         <v>877</v>
-      </c>
-      <c r="C442">
-        <v>1</v>
-      </c>
-      <c r="D442" t="s">
-        <v>80</v>
-      </c>
-      <c r="E442" t="s">
-        <v>864</v>
-      </c>
-      <c r="F442" t="s">
-        <v>865</v>
       </c>
       <c r="G442" s="1">
         <v>46300</v>
@@ -15357,13 +15378,13 @@
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E443" t="s">
-        <v>16</v>
+        <v>865</v>
       </c>
       <c r="F443" t="s">
-        <v>17</v>
+        <v>866</v>
       </c>
       <c r="G443" s="1">
         <v>46300</v>
@@ -15386,10 +15407,10 @@
         <v>80</v>
       </c>
       <c r="E444" t="s">
-        <v>880</v>
+        <v>16</v>
       </c>
       <c r="F444" t="s">
-        <v>881</v>
+        <v>17</v>
       </c>
       <c r="G444" s="1">
         <v>46300</v>
@@ -15403,19 +15424,19 @@
         <v>0</v>
       </c>
       <c r="B445" t="s">
+        <v>880</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+      <c r="D445" t="s">
+        <v>2</v>
+      </c>
+      <c r="E445" t="s">
+        <v>881</v>
+      </c>
+      <c r="F445" t="s">
         <v>882</v>
-      </c>
-      <c r="C445">
-        <v>1</v>
-      </c>
-      <c r="D445" t="s">
-        <v>80</v>
-      </c>
-      <c r="E445" t="s">
-        <v>883</v>
-      </c>
-      <c r="F445" t="s">
-        <v>884</v>
       </c>
       <c r="G445" s="1">
         <v>46300</v>
@@ -15429,25 +15450,25 @@
         <v>0</v>
       </c>
       <c r="B446" t="s">
+        <v>883</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446" t="s">
+        <v>80</v>
+      </c>
+      <c r="E446" t="s">
+        <v>884</v>
+      </c>
+      <c r="F446" t="s">
         <v>885</v>
       </c>
-      <c r="C446">
-        <v>1</v>
-      </c>
-      <c r="D446" t="s">
-        <v>80</v>
-      </c>
-      <c r="E446" t="s">
-        <v>886</v>
-      </c>
-      <c r="F446" t="s">
-        <v>887</v>
-      </c>
       <c r="G446" s="1">
         <v>46300</v>
       </c>
       <c r="H446" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
@@ -15455,19 +15476,19 @@
         <v>0</v>
       </c>
       <c r="B447" t="s">
+        <v>886</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447" t="s">
+        <v>80</v>
+      </c>
+      <c r="E447" t="s">
+        <v>887</v>
+      </c>
+      <c r="F447" t="s">
         <v>888</v>
-      </c>
-      <c r="C447">
-        <v>1</v>
-      </c>
-      <c r="D447" t="s">
-        <v>80</v>
-      </c>
-      <c r="E447" t="s">
-        <v>886</v>
-      </c>
-      <c r="F447" t="s">
-        <v>887</v>
       </c>
       <c r="G447" s="1">
         <v>46300</v>
@@ -15490,10 +15511,10 @@
         <v>80</v>
       </c>
       <c r="E448" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F448" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G448" s="1">
         <v>46300</v>
@@ -15516,10 +15537,10 @@
         <v>80</v>
       </c>
       <c r="E449" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F449" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G449" s="1">
         <v>46300</v>
@@ -15533,19 +15554,19 @@
         <v>0</v>
       </c>
       <c r="B450" t="s">
+        <v>891</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+      <c r="D450" t="s">
+        <v>80</v>
+      </c>
+      <c r="E450" t="s">
+        <v>892</v>
+      </c>
+      <c r="F450" t="s">
         <v>893</v>
-      </c>
-      <c r="C450">
-        <v>1</v>
-      </c>
-      <c r="D450" t="s">
-        <v>80</v>
-      </c>
-      <c r="E450" t="s">
-        <v>894</v>
-      </c>
-      <c r="F450" t="s">
-        <v>895</v>
       </c>
       <c r="G450" s="1">
         <v>46300</v>
@@ -15559,22 +15580,22 @@
         <v>0</v>
       </c>
       <c r="B451" t="s">
+        <v>894</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451" t="s">
+        <v>80</v>
+      </c>
+      <c r="E451" t="s">
+        <v>895</v>
+      </c>
+      <c r="F451" t="s">
         <v>896</v>
       </c>
-      <c r="C451">
-        <v>1</v>
-      </c>
-      <c r="D451" t="s">
-        <v>80</v>
-      </c>
-      <c r="E451" t="s">
-        <v>880</v>
-      </c>
-      <c r="F451" t="s">
-        <v>881</v>
-      </c>
       <c r="G451" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H451" s="1">
         <v>46301</v>
@@ -15591,13 +15612,13 @@
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E452" t="s">
-        <v>22</v>
+        <v>881</v>
       </c>
       <c r="F452" t="s">
-        <v>23</v>
+        <v>882</v>
       </c>
       <c r="G452" s="1">
         <v>46301</v>
@@ -15620,10 +15641,10 @@
         <v>80</v>
       </c>
       <c r="E453" t="s">
-        <v>899</v>
+        <v>22</v>
       </c>
       <c r="F453" t="s">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="G453" s="1">
         <v>46301</v>
@@ -15637,19 +15658,19 @@
         <v>0</v>
       </c>
       <c r="B454" t="s">
+        <v>899</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>80</v>
+      </c>
+      <c r="E454" t="s">
+        <v>900</v>
+      </c>
+      <c r="F454" t="s">
         <v>901</v>
-      </c>
-      <c r="C454">
-        <v>1</v>
-      </c>
-      <c r="D454" t="s">
-        <v>2</v>
-      </c>
-      <c r="E454" t="s">
-        <v>77</v>
-      </c>
-      <c r="F454" t="s">
-        <v>78</v>
       </c>
       <c r="G454" s="1">
         <v>46301</v>
@@ -15669,13 +15690,13 @@
         <v>1</v>
       </c>
       <c r="D455" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E455" t="s">
-        <v>903</v>
+        <v>77</v>
       </c>
       <c r="F455" t="s">
-        <v>904</v>
+        <v>78</v>
       </c>
       <c r="G455" s="1">
         <v>46301</v>
@@ -15689,19 +15710,19 @@
         <v>0</v>
       </c>
       <c r="B456" t="s">
+        <v>903</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+      <c r="D456" t="s">
+        <v>80</v>
+      </c>
+      <c r="E456" t="s">
+        <v>904</v>
+      </c>
+      <c r="F456" t="s">
         <v>905</v>
-      </c>
-      <c r="C456">
-        <v>1</v>
-      </c>
-      <c r="D456" t="s">
-        <v>80</v>
-      </c>
-      <c r="E456" t="s">
-        <v>81</v>
-      </c>
-      <c r="F456" t="s">
-        <v>82</v>
       </c>
       <c r="G456" s="1">
         <v>46301</v>
@@ -15724,10 +15745,10 @@
         <v>80</v>
       </c>
       <c r="E457" t="s">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="F457" t="s">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="G457" s="1">
         <v>46301</v>
@@ -15750,10 +15771,10 @@
         <v>80</v>
       </c>
       <c r="E458" t="s">
-        <v>908</v>
+        <v>496</v>
       </c>
       <c r="F458" t="s">
-        <v>909</v>
+        <v>497</v>
       </c>
       <c r="G458" s="1">
         <v>46301</v>
@@ -15767,19 +15788,19 @@
         <v>0</v>
       </c>
       <c r="B459" t="s">
+        <v>908</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+      <c r="D459" t="s">
+        <v>80</v>
+      </c>
+      <c r="E459" t="s">
+        <v>909</v>
+      </c>
+      <c r="F459" t="s">
         <v>910</v>
-      </c>
-      <c r="C459">
-        <v>1</v>
-      </c>
-      <c r="D459" t="s">
-        <v>80</v>
-      </c>
-      <c r="E459" t="s">
-        <v>87</v>
-      </c>
-      <c r="F459" t="s">
-        <v>88</v>
       </c>
       <c r="G459" s="1">
         <v>46301</v>
@@ -15802,10 +15823,10 @@
         <v>80</v>
       </c>
       <c r="E460" t="s">
-        <v>452</v>
+        <v>87</v>
       </c>
       <c r="F460" t="s">
-        <v>453</v>
+        <v>88</v>
       </c>
       <c r="G460" s="1">
         <v>46301</v>
@@ -15825,13 +15846,13 @@
         <v>1</v>
       </c>
       <c r="D461" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E461" t="s">
-        <v>87</v>
+        <v>451</v>
       </c>
       <c r="F461" t="s">
-        <v>88</v>
+        <v>452</v>
       </c>
       <c r="G461" s="1">
         <v>46301</v>
@@ -15854,10 +15875,10 @@
         <v>80</v>
       </c>
       <c r="E462" t="s">
-        <v>452</v>
+        <v>87</v>
       </c>
       <c r="F462" t="s">
-        <v>453</v>
+        <v>88</v>
       </c>
       <c r="G462" s="1">
         <v>46301</v>
@@ -15877,13 +15898,13 @@
         <v>1</v>
       </c>
       <c r="D463" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E463" t="s">
-        <v>87</v>
+        <v>451</v>
       </c>
       <c r="F463" t="s">
-        <v>88</v>
+        <v>452</v>
       </c>
       <c r="G463" s="1">
         <v>46301</v>
@@ -16010,10 +16031,10 @@
         <v>80</v>
       </c>
       <c r="E468" t="s">
-        <v>920</v>
+        <v>87</v>
       </c>
       <c r="F468" t="s">
-        <v>921</v>
+        <v>88</v>
       </c>
       <c r="G468" s="1">
         <v>46301</v>
@@ -16027,19 +16048,19 @@
         <v>0</v>
       </c>
       <c r="B469" t="s">
+        <v>920</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469" t="s">
+        <v>80</v>
+      </c>
+      <c r="E469" t="s">
+        <v>921</v>
+      </c>
+      <c r="F469" t="s">
         <v>922</v>
-      </c>
-      <c r="C469">
-        <v>1</v>
-      </c>
-      <c r="D469" t="s">
-        <v>80</v>
-      </c>
-      <c r="E469" t="s">
-        <v>37</v>
-      </c>
-      <c r="F469" t="s">
-        <v>38</v>
       </c>
       <c r="G469" s="1">
         <v>46301</v>
@@ -16192,10 +16213,10 @@
         <v>80</v>
       </c>
       <c r="E475" t="s">
-        <v>929</v>
+        <v>37</v>
       </c>
       <c r="F475" t="s">
-        <v>930</v>
+        <v>38</v>
       </c>
       <c r="G475" s="1">
         <v>46301</v>
@@ -16209,19 +16230,19 @@
         <v>0</v>
       </c>
       <c r="B476" t="s">
+        <v>929</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+      <c r="D476" t="s">
+        <v>80</v>
+      </c>
+      <c r="E476" t="s">
+        <v>930</v>
+      </c>
+      <c r="F476" t="s">
         <v>931</v>
-      </c>
-      <c r="C476">
-        <v>1</v>
-      </c>
-      <c r="D476" t="s">
-        <v>80</v>
-      </c>
-      <c r="E476" t="s">
-        <v>932</v>
-      </c>
-      <c r="F476" t="s">
-        <v>933</v>
       </c>
       <c r="G476" s="1">
         <v>46301</v>
@@ -16235,19 +16256,19 @@
         <v>0</v>
       </c>
       <c r="B477" t="s">
+        <v>932</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+      <c r="D477" t="s">
+        <v>80</v>
+      </c>
+      <c r="E477" t="s">
+        <v>933</v>
+      </c>
+      <c r="F477" t="s">
         <v>934</v>
-      </c>
-      <c r="C477">
-        <v>1</v>
-      </c>
-      <c r="D477" t="s">
-        <v>80</v>
-      </c>
-      <c r="E477" t="s">
-        <v>16</v>
-      </c>
-      <c r="F477" t="s">
-        <v>17</v>
       </c>
       <c r="G477" s="1">
         <v>46301</v>
@@ -16296,10 +16317,10 @@
         <v>80</v>
       </c>
       <c r="E479" t="s">
-        <v>744</v>
+        <v>16</v>
       </c>
       <c r="F479" t="s">
-        <v>745</v>
+        <v>17</v>
       </c>
       <c r="G479" s="1">
         <v>46301</v>
@@ -16322,10 +16343,10 @@
         <v>80</v>
       </c>
       <c r="E480" t="s">
-        <v>389</v>
+        <v>745</v>
       </c>
       <c r="F480" t="s">
-        <v>390</v>
+        <v>746</v>
       </c>
       <c r="G480" s="1">
         <v>46301</v>
@@ -16348,10 +16369,10 @@
         <v>80</v>
       </c>
       <c r="E481" t="s">
-        <v>886</v>
+        <v>388</v>
       </c>
       <c r="F481" t="s">
-        <v>887</v>
+        <v>389</v>
       </c>
       <c r="G481" s="1">
         <v>46301</v>
@@ -16374,10 +16395,10 @@
         <v>80</v>
       </c>
       <c r="E482" t="s">
-        <v>19</v>
+        <v>887</v>
       </c>
       <c r="F482" t="s">
-        <v>20</v>
+        <v>888</v>
       </c>
       <c r="G482" s="1">
         <v>46301</v>
@@ -16400,10 +16421,10 @@
         <v>80</v>
       </c>
       <c r="E483" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F483" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G483" s="1">
         <v>46301</v>
@@ -16426,10 +16447,10 @@
         <v>80</v>
       </c>
       <c r="E484" t="s">
-        <v>942</v>
+        <v>16</v>
       </c>
       <c r="F484" t="s">
-        <v>943</v>
+        <v>17</v>
       </c>
       <c r="G484" s="1">
         <v>46301</v>
@@ -16443,19 +16464,19 @@
         <v>0</v>
       </c>
       <c r="B485" t="s">
+        <v>942</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485" t="s">
+        <v>80</v>
+      </c>
+      <c r="E485" t="s">
+        <v>943</v>
+      </c>
+      <c r="F485" t="s">
         <v>944</v>
-      </c>
-      <c r="C485">
-        <v>1</v>
-      </c>
-      <c r="D485" t="s">
-        <v>80</v>
-      </c>
-      <c r="E485" t="s">
-        <v>482</v>
-      </c>
-      <c r="F485" t="s">
-        <v>483</v>
       </c>
       <c r="G485" s="1">
         <v>46301</v>
@@ -16478,10 +16499,10 @@
         <v>80</v>
       </c>
       <c r="E486" t="s">
-        <v>661</v>
+        <v>481</v>
       </c>
       <c r="F486" t="s">
-        <v>662</v>
+        <v>482</v>
       </c>
       <c r="G486" s="1">
         <v>46301</v>
@@ -16504,10 +16525,10 @@
         <v>80</v>
       </c>
       <c r="E487" t="s">
-        <v>628</v>
+        <v>661</v>
       </c>
       <c r="F487" t="s">
-        <v>629</v>
+        <v>662</v>
       </c>
       <c r="G487" s="1">
         <v>46301</v>
@@ -16530,10 +16551,10 @@
         <v>80</v>
       </c>
       <c r="E488" t="s">
-        <v>948</v>
+        <v>628</v>
       </c>
       <c r="F488" t="s">
-        <v>949</v>
+        <v>629</v>
       </c>
       <c r="G488" s="1">
         <v>46301</v>
@@ -16547,19 +16568,19 @@
         <v>0</v>
       </c>
       <c r="B489" t="s">
+        <v>948</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+      <c r="D489" t="s">
+        <v>80</v>
+      </c>
+      <c r="E489" t="s">
+        <v>949</v>
+      </c>
+      <c r="F489" t="s">
         <v>950</v>
-      </c>
-      <c r="C489">
-        <v>1</v>
-      </c>
-      <c r="D489" t="s">
-        <v>80</v>
-      </c>
-      <c r="E489" t="s">
-        <v>951</v>
-      </c>
-      <c r="F489" t="s">
-        <v>952</v>
       </c>
       <c r="G489" s="1">
         <v>46301</v>
@@ -16573,19 +16594,19 @@
         <v>0</v>
       </c>
       <c r="B490" t="s">
+        <v>951</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+      <c r="D490" t="s">
+        <v>80</v>
+      </c>
+      <c r="E490" t="s">
+        <v>952</v>
+      </c>
+      <c r="F490" t="s">
         <v>953</v>
-      </c>
-      <c r="C490">
-        <v>1</v>
-      </c>
-      <c r="D490" t="s">
-        <v>80</v>
-      </c>
-      <c r="E490" t="s">
-        <v>497</v>
-      </c>
-      <c r="F490" t="s">
-        <v>498</v>
       </c>
       <c r="G490" s="1">
         <v>46301</v>
@@ -16608,10 +16629,10 @@
         <v>80</v>
       </c>
       <c r="E491" t="s">
-        <v>955</v>
+        <v>496</v>
       </c>
       <c r="F491" t="s">
-        <v>956</v>
+        <v>497</v>
       </c>
       <c r="G491" s="1">
         <v>46301</v>
@@ -16625,19 +16646,19 @@
         <v>0</v>
       </c>
       <c r="B492" t="s">
+        <v>955</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+      <c r="D492" t="s">
+        <v>80</v>
+      </c>
+      <c r="E492" t="s">
+        <v>956</v>
+      </c>
+      <c r="F492" t="s">
         <v>957</v>
-      </c>
-      <c r="C492">
-        <v>1</v>
-      </c>
-      <c r="D492" t="s">
-        <v>80</v>
-      </c>
-      <c r="E492" t="s">
-        <v>958</v>
-      </c>
-      <c r="F492" t="s">
-        <v>959</v>
       </c>
       <c r="G492" s="1">
         <v>46301</v>
@@ -16651,19 +16672,19 @@
         <v>0</v>
       </c>
       <c r="B493" t="s">
+        <v>958</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+      <c r="D493" t="s">
+        <v>80</v>
+      </c>
+      <c r="E493" t="s">
+        <v>959</v>
+      </c>
+      <c r="F493" t="s">
         <v>960</v>
-      </c>
-      <c r="C493">
-        <v>1</v>
-      </c>
-      <c r="D493" t="s">
-        <v>80</v>
-      </c>
-      <c r="E493" t="s">
-        <v>767</v>
-      </c>
-      <c r="F493" t="s">
-        <v>768</v>
       </c>
       <c r="G493" s="1">
         <v>46301</v>
@@ -16686,10 +16707,10 @@
         <v>80</v>
       </c>
       <c r="E494" t="s">
-        <v>962</v>
+        <v>768</v>
       </c>
       <c r="F494" t="s">
-        <v>963</v>
+        <v>769</v>
       </c>
       <c r="G494" s="1">
         <v>46301</v>
@@ -16703,19 +16724,19 @@
         <v>0</v>
       </c>
       <c r="B495" t="s">
+        <v>962</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495" t="s">
+        <v>80</v>
+      </c>
+      <c r="E495" t="s">
+        <v>963</v>
+      </c>
+      <c r="F495" t="s">
         <v>964</v>
-      </c>
-      <c r="C495">
-        <v>1</v>
-      </c>
-      <c r="D495" t="s">
-        <v>80</v>
-      </c>
-      <c r="E495" t="s">
-        <v>965</v>
-      </c>
-      <c r="F495" t="s">
-        <v>966</v>
       </c>
       <c r="G495" s="1">
         <v>46301</v>
@@ -16729,19 +16750,19 @@
         <v>0</v>
       </c>
       <c r="B496" t="s">
+        <v>965</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+      <c r="D496" t="s">
+        <v>80</v>
+      </c>
+      <c r="E496" t="s">
+        <v>966</v>
+      </c>
+      <c r="F496" t="s">
         <v>967</v>
-      </c>
-      <c r="C496">
-        <v>1</v>
-      </c>
-      <c r="D496" t="s">
-        <v>80</v>
-      </c>
-      <c r="E496" t="s">
-        <v>299</v>
-      </c>
-      <c r="F496" t="s">
-        <v>300</v>
       </c>
       <c r="G496" s="1">
         <v>46301</v>
@@ -16764,10 +16785,10 @@
         <v>80</v>
       </c>
       <c r="E497" t="s">
-        <v>482</v>
+        <v>299</v>
       </c>
       <c r="F497" t="s">
-        <v>483</v>
+        <v>300</v>
       </c>
       <c r="G497" s="1">
         <v>46301</v>
@@ -16790,10 +16811,10 @@
         <v>80</v>
       </c>
       <c r="E498" t="s">
-        <v>970</v>
+        <v>481</v>
       </c>
       <c r="F498" t="s">
-        <v>971</v>
+        <v>482</v>
       </c>
       <c r="G498" s="1">
         <v>46301</v>
@@ -16807,19 +16828,19 @@
         <v>0</v>
       </c>
       <c r="B499" t="s">
+        <v>970</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+      <c r="D499" t="s">
+        <v>80</v>
+      </c>
+      <c r="E499" t="s">
+        <v>971</v>
+      </c>
+      <c r="F499" t="s">
         <v>972</v>
-      </c>
-      <c r="C499">
-        <v>1</v>
-      </c>
-      <c r="D499" t="s">
-        <v>80</v>
-      </c>
-      <c r="E499" t="s">
-        <v>973</v>
-      </c>
-      <c r="F499" t="s">
-        <v>974</v>
       </c>
       <c r="G499" s="1">
         <v>46301</v>
@@ -16833,19 +16854,19 @@
         <v>0</v>
       </c>
       <c r="B500" t="s">
+        <v>973</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500" t="s">
+        <v>80</v>
+      </c>
+      <c r="E500" t="s">
+        <v>974</v>
+      </c>
+      <c r="F500" t="s">
         <v>975</v>
-      </c>
-      <c r="C500">
-        <v>1</v>
-      </c>
-      <c r="D500" t="s">
-        <v>80</v>
-      </c>
-      <c r="E500" t="s">
-        <v>976</v>
-      </c>
-      <c r="F500" t="s">
-        <v>977</v>
       </c>
       <c r="G500" s="1">
         <v>46301</v>
@@ -16859,19 +16880,19 @@
         <v>0</v>
       </c>
       <c r="B501" t="s">
+        <v>976</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+      <c r="D501" t="s">
+        <v>80</v>
+      </c>
+      <c r="E501" t="s">
+        <v>977</v>
+      </c>
+      <c r="F501" t="s">
         <v>978</v>
-      </c>
-      <c r="C501">
-        <v>1</v>
-      </c>
-      <c r="D501" t="s">
-        <v>80</v>
-      </c>
-      <c r="E501" t="s">
-        <v>211</v>
-      </c>
-      <c r="F501" t="s">
-        <v>212</v>
       </c>
       <c r="G501" s="1">
         <v>46301</v>
@@ -16894,10 +16915,10 @@
         <v>80</v>
       </c>
       <c r="E502" t="s">
-        <v>980</v>
+        <v>211</v>
       </c>
       <c r="F502" t="s">
-        <v>981</v>
+        <v>212</v>
       </c>
       <c r="G502" s="1">
         <v>46301</v>
@@ -16911,19 +16932,19 @@
         <v>0</v>
       </c>
       <c r="B503" t="s">
+        <v>980</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+      <c r="D503" t="s">
+        <v>80</v>
+      </c>
+      <c r="E503" t="s">
+        <v>981</v>
+      </c>
+      <c r="F503" t="s">
         <v>982</v>
-      </c>
-      <c r="C503">
-        <v>1</v>
-      </c>
-      <c r="D503" t="s">
-        <v>80</v>
-      </c>
-      <c r="E503" t="s">
-        <v>185</v>
-      </c>
-      <c r="F503" t="s">
-        <v>186</v>
       </c>
       <c r="G503" s="1">
         <v>46301</v>
@@ -16946,10 +16967,10 @@
         <v>80</v>
       </c>
       <c r="E504" t="s">
-        <v>984</v>
+        <v>185</v>
       </c>
       <c r="F504" t="s">
-        <v>985</v>
+        <v>186</v>
       </c>
       <c r="G504" s="1">
         <v>46301</v>
@@ -16963,19 +16984,19 @@
         <v>0</v>
       </c>
       <c r="B505" t="s">
+        <v>984</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+      <c r="D505" t="s">
+        <v>80</v>
+      </c>
+      <c r="E505" t="s">
+        <v>985</v>
+      </c>
+      <c r="F505" t="s">
         <v>986</v>
-      </c>
-      <c r="C505">
-        <v>1</v>
-      </c>
-      <c r="D505" t="s">
-        <v>80</v>
-      </c>
-      <c r="E505" t="s">
-        <v>785</v>
-      </c>
-      <c r="F505" t="s">
-        <v>786</v>
       </c>
       <c r="G505" s="1">
         <v>46301</v>
@@ -16998,10 +17019,10 @@
         <v>80</v>
       </c>
       <c r="E506" t="s">
-        <v>880</v>
+        <v>786</v>
       </c>
       <c r="F506" t="s">
-        <v>881</v>
+        <v>787</v>
       </c>
       <c r="G506" s="1">
         <v>46301</v>
@@ -17024,10 +17045,10 @@
         <v>80</v>
       </c>
       <c r="E507" t="s">
-        <v>16</v>
+        <v>881</v>
       </c>
       <c r="F507" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="G507" s="1">
         <v>46301</v>
@@ -17050,10 +17071,10 @@
         <v>80</v>
       </c>
       <c r="E508" t="s">
-        <v>452</v>
+        <v>16</v>
       </c>
       <c r="F508" t="s">
-        <v>453</v>
+        <v>17</v>
       </c>
       <c r="G508" s="1">
         <v>46301</v>
@@ -17076,10 +17097,10 @@
         <v>80</v>
       </c>
       <c r="E509" t="s">
-        <v>991</v>
+        <v>451</v>
       </c>
       <c r="F509" t="s">
-        <v>992</v>
+        <v>452</v>
       </c>
       <c r="G509" s="1">
         <v>46301</v>
@@ -17093,19 +17114,19 @@
         <v>0</v>
       </c>
       <c r="B510" t="s">
+        <v>991</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510" t="s">
+        <v>80</v>
+      </c>
+      <c r="E510" t="s">
+        <v>992</v>
+      </c>
+      <c r="F510" t="s">
         <v>993</v>
-      </c>
-      <c r="C510">
-        <v>1</v>
-      </c>
-      <c r="D510" t="s">
-        <v>80</v>
-      </c>
-      <c r="E510" t="s">
-        <v>994</v>
-      </c>
-      <c r="F510" t="s">
-        <v>995</v>
       </c>
       <c r="G510" s="1">
         <v>46301</v>
@@ -17119,19 +17140,19 @@
         <v>0</v>
       </c>
       <c r="B511" t="s">
+        <v>994</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+      <c r="D511" t="s">
+        <v>80</v>
+      </c>
+      <c r="E511" t="s">
+        <v>995</v>
+      </c>
+      <c r="F511" t="s">
         <v>996</v>
-      </c>
-      <c r="C511">
-        <v>1</v>
-      </c>
-      <c r="D511" t="s">
-        <v>80</v>
-      </c>
-      <c r="E511" t="s">
-        <v>997</v>
-      </c>
-      <c r="F511" t="s">
-        <v>998</v>
       </c>
       <c r="G511" s="1">
         <v>46301</v>
@@ -17145,19 +17166,19 @@
         <v>0</v>
       </c>
       <c r="B512" t="s">
+        <v>997</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512" t="s">
+        <v>80</v>
+      </c>
+      <c r="E512" t="s">
+        <v>998</v>
+      </c>
+      <c r="F512" t="s">
         <v>999</v>
-      </c>
-      <c r="C512">
-        <v>1</v>
-      </c>
-      <c r="D512" t="s">
-        <v>80</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F512" t="s">
-        <v>1001</v>
       </c>
       <c r="G512" s="1">
         <v>46301</v>
@@ -17171,19 +17192,19 @@
         <v>0</v>
       </c>
       <c r="B513" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+      <c r="D513" t="s">
+        <v>80</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F513" t="s">
         <v>1002</v>
-      </c>
-      <c r="C513">
-        <v>1</v>
-      </c>
-      <c r="D513" t="s">
-        <v>80</v>
-      </c>
-      <c r="E513" t="s">
-        <v>7</v>
-      </c>
-      <c r="F513" t="s">
-        <v>8</v>
       </c>
       <c r="G513" s="1">
         <v>46301</v>
@@ -17206,10 +17227,10 @@
         <v>80</v>
       </c>
       <c r="E514" t="s">
-        <v>1004</v>
+        <v>7</v>
       </c>
       <c r="F514" t="s">
-        <v>1005</v>
+        <v>8</v>
       </c>
       <c r="G514" s="1">
         <v>46301</v>
@@ -17223,19 +17244,19 @@
         <v>0</v>
       </c>
       <c r="B515" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515" t="s">
+        <v>80</v>
+      </c>
+      <c r="E515" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F515" t="s">
         <v>1006</v>
-      </c>
-      <c r="C515">
-        <v>1</v>
-      </c>
-      <c r="D515" t="s">
-        <v>80</v>
-      </c>
-      <c r="E515" t="s">
-        <v>16</v>
-      </c>
-      <c r="F515" t="s">
-        <v>17</v>
       </c>
       <c r="G515" s="1">
         <v>46301</v>
@@ -17258,10 +17279,10 @@
         <v>80</v>
       </c>
       <c r="E516" t="s">
-        <v>886</v>
+        <v>16</v>
       </c>
       <c r="F516" t="s">
-        <v>887</v>
+        <v>17</v>
       </c>
       <c r="G516" s="1">
         <v>46301</v>
@@ -17284,10 +17305,10 @@
         <v>80</v>
       </c>
       <c r="E517" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="F517" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="G517" s="1">
         <v>46301</v>
@@ -17310,10 +17331,10 @@
         <v>80</v>
       </c>
       <c r="E518" t="s">
-        <v>1010</v>
+        <v>869</v>
       </c>
       <c r="F518" t="s">
-        <v>1011</v>
+        <v>870</v>
       </c>
       <c r="G518" s="1">
         <v>46301</v>
@@ -17327,19 +17348,19 @@
         <v>0</v>
       </c>
       <c r="B519" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+      <c r="D519" t="s">
+        <v>80</v>
+      </c>
+      <c r="E519" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F519" t="s">
         <v>1012</v>
-      </c>
-      <c r="C519">
-        <v>1</v>
-      </c>
-      <c r="D519" t="s">
-        <v>80</v>
-      </c>
-      <c r="E519" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F519" t="s">
-        <v>1014</v>
       </c>
       <c r="G519" s="1">
         <v>46301</v>
@@ -17353,19 +17374,19 @@
         <v>0</v>
       </c>
       <c r="B520" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+      <c r="D520" t="s">
+        <v>80</v>
+      </c>
+      <c r="E520" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F520" t="s">
         <v>1015</v>
-      </c>
-      <c r="C520">
-        <v>1</v>
-      </c>
-      <c r="D520" t="s">
-        <v>80</v>
-      </c>
-      <c r="E520" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F520" t="s">
-        <v>1017</v>
       </c>
       <c r="G520" s="1">
         <v>46301</v>
@@ -17379,19 +17400,19 @@
         <v>0</v>
       </c>
       <c r="B521" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521" t="s">
+        <v>80</v>
+      </c>
+      <c r="E521" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F521" t="s">
         <v>1018</v>
-      </c>
-      <c r="C521">
-        <v>1</v>
-      </c>
-      <c r="D521" t="s">
-        <v>80</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F521" t="s">
-        <v>1017</v>
       </c>
       <c r="G521" s="1">
         <v>46301</v>
@@ -17402,62 +17423,62 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
+        <v>0</v>
+      </c>
+      <c r="B522" t="s">
         <v>1019</v>
       </c>
-      <c r="B522" t="s">
-        <v>1020</v>
-      </c>
       <c r="C522">
         <v>1</v>
       </c>
       <c r="D522" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E522" t="s">
-        <v>200</v>
+        <v>1017</v>
       </c>
       <c r="F522" t="s">
-        <v>201</v>
+        <v>1018</v>
       </c>
       <c r="G522" s="1">
-        <v>46148</v>
+        <v>46301</v>
       </c>
       <c r="H522" s="1">
-        <v>46149</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C523">
         <v>1</v>
       </c>
       <c r="D523" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E523" t="s">
-        <v>112</v>
+        <v>789</v>
       </c>
       <c r="F523" t="s">
-        <v>113</v>
+        <v>790</v>
       </c>
       <c r="G523" s="1">
-        <v>46268</v>
+        <v>46301</v>
       </c>
       <c r="H523" s="1">
-        <v>46268</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C524">
         <v>1</v>
@@ -17466,24 +17487,24 @@
         <v>80</v>
       </c>
       <c r="E524" t="s">
-        <v>741</v>
+        <v>776</v>
       </c>
       <c r="F524" t="s">
-        <v>742</v>
+        <v>777</v>
       </c>
       <c r="G524" s="1">
         <v>46301</v>
       </c>
       <c r="H524" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C525">
         <v>1</v>
@@ -17492,24 +17513,24 @@
         <v>80</v>
       </c>
       <c r="E525" t="s">
-        <v>1024</v>
+        <v>81</v>
       </c>
       <c r="F525" t="s">
-        <v>1025</v>
+        <v>82</v>
       </c>
       <c r="G525" s="1">
         <v>46301</v>
       </c>
       <c r="H525" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="B526" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C526">
         <v>1</v>
@@ -17518,47 +17539,47 @@
         <v>80</v>
       </c>
       <c r="E526" t="s">
-        <v>741</v>
+        <v>1024</v>
       </c>
       <c r="F526" t="s">
-        <v>742</v>
+        <v>1025</v>
       </c>
       <c r="G526" s="1">
         <v>46301</v>
       </c>
       <c r="H526" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>0</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+      <c r="D527" t="s">
+        <v>80</v>
+      </c>
+      <c r="E527" t="s">
         <v>1027</v>
       </c>
-      <c r="B527" t="s">
+      <c r="F527" t="s">
         <v>1028</v>
       </c>
-      <c r="C527">
-        <v>1</v>
-      </c>
-      <c r="D527" t="s">
-        <v>6</v>
-      </c>
-      <c r="E527" t="s">
-        <v>41</v>
-      </c>
-      <c r="F527" t="s">
-        <v>42</v>
-      </c>
       <c r="G527" s="1">
-        <v>46133</v>
+        <v>46301</v>
       </c>
       <c r="H527" s="1">
-        <v>46134</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1027</v>
+        <v>0</v>
       </c>
       <c r="B528" t="s">
         <v>1029</v>
@@ -17567,215 +17588,215 @@
         <v>1</v>
       </c>
       <c r="D528" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E528" t="s">
-        <v>41</v>
+        <v>1030</v>
       </c>
       <c r="F528" t="s">
-        <v>42</v>
+        <v>1031</v>
       </c>
       <c r="G528" s="1">
-        <v>46134</v>
+        <v>46301</v>
       </c>
       <c r="H528" s="1">
-        <v>46134</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1027</v>
+        <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C529">
         <v>1</v>
       </c>
       <c r="D529" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E529" t="s">
-        <v>19</v>
+        <v>1033</v>
       </c>
       <c r="F529" t="s">
-        <v>20</v>
+        <v>1034</v>
       </c>
       <c r="G529" s="1">
-        <v>46156</v>
+        <v>46301</v>
       </c>
       <c r="H529" s="1">
-        <v>46156</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1027</v>
+        <v>0</v>
       </c>
       <c r="B530" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C530">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D530" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E530" t="s">
-        <v>1032</v>
+        <v>544</v>
       </c>
       <c r="F530" t="s">
-        <v>1033</v>
+        <v>545</v>
       </c>
       <c r="G530" s="1">
-        <v>46209</v>
+        <v>46301</v>
       </c>
       <c r="H530" s="1">
-        <v>46218</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="B531" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C531">
         <v>1</v>
       </c>
       <c r="D531" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E531" t="s">
-        <v>1035</v>
+        <v>200</v>
       </c>
       <c r="F531" t="s">
-        <v>1036</v>
+        <v>201</v>
       </c>
       <c r="G531" s="1">
-        <v>46213</v>
+        <v>46148</v>
       </c>
       <c r="H531" s="1">
-        <v>46213</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="B532" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C532">
         <v>1</v>
       </c>
       <c r="D532" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="E532" t="s">
-        <v>1038</v>
+        <v>112</v>
       </c>
       <c r="F532" t="s">
-        <v>1039</v>
+        <v>113</v>
       </c>
       <c r="G532" s="1">
-        <v>46213</v>
+        <v>46268</v>
       </c>
       <c r="H532" s="1">
-        <v>46216</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="B533" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C533">
         <v>1</v>
       </c>
       <c r="D533" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E533" t="s">
-        <v>1038</v>
+        <v>742</v>
       </c>
       <c r="F533" t="s">
-        <v>1039</v>
+        <v>743</v>
       </c>
       <c r="G533" s="1">
-        <v>46224</v>
+        <v>46301</v>
       </c>
       <c r="H533" s="1">
-        <v>46224</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="B534" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+      <c r="D534" t="s">
+        <v>80</v>
+      </c>
+      <c r="E534" t="s">
         <v>1041</v>
       </c>
-      <c r="C534">
-        <v>1</v>
-      </c>
-      <c r="D534" t="s">
-        <v>6</v>
-      </c>
-      <c r="E534" t="s">
+      <c r="F534" t="s">
         <v>1042</v>
       </c>
-      <c r="F534" t="s">
-        <v>1043</v>
-      </c>
       <c r="G534" s="1">
-        <v>46253</v>
+        <v>46301</v>
       </c>
       <c r="H534" s="1">
-        <v>46253</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="B535" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C535">
         <v>1</v>
       </c>
       <c r="D535" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E535" t="s">
-        <v>211</v>
+        <v>742</v>
       </c>
       <c r="F535" t="s">
-        <v>212</v>
+        <v>743</v>
       </c>
       <c r="G535" s="1">
-        <v>46273</v>
+        <v>46301</v>
       </c>
       <c r="H535" s="1">
-        <v>46274</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B536" t="s">
         <v>1045</v>
       </c>
       <c r="C536">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D536" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E536" t="s">
         <v>41</v>
@@ -17784,15 +17805,15 @@
         <v>42</v>
       </c>
       <c r="G536" s="1">
-        <v>46289</v>
+        <v>46133</v>
       </c>
       <c r="H536" s="1">
-        <v>46296</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B537" t="s">
         <v>1046</v>
@@ -17801,24 +17822,24 @@
         <v>1</v>
       </c>
       <c r="D537" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E537" t="s">
-        <v>1032</v>
+        <v>41</v>
       </c>
       <c r="F537" t="s">
-        <v>1033</v>
+        <v>42</v>
       </c>
       <c r="G537" s="1">
-        <v>46295</v>
+        <v>46134</v>
       </c>
       <c r="H537" s="1">
-        <v>46295</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B538" t="s">
         <v>1047</v>
@@ -17827,50 +17848,50 @@
         <v>1</v>
       </c>
       <c r="D538" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E538" t="s">
-        <v>1048</v>
+        <v>19</v>
       </c>
       <c r="F538" t="s">
-        <v>1049</v>
+        <v>20</v>
       </c>
       <c r="G538" s="1">
-        <v>46295</v>
+        <v>46156</v>
       </c>
       <c r="H538" s="1">
-        <v>46301</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B539" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C539">
+        <v>2</v>
+      </c>
+      <c r="D539" t="s">
+        <v>96</v>
+      </c>
+      <c r="E539" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F539" t="s">
         <v>1050</v>
       </c>
-      <c r="C539">
-        <v>1</v>
-      </c>
-      <c r="D539" t="s">
-        <v>80</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1033</v>
-      </c>
       <c r="G539" s="1">
-        <v>46297</v>
+        <v>46209</v>
       </c>
       <c r="H539" s="1">
-        <v>46297</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B540" t="s">
         <v>1051</v>
@@ -17879,183 +17900,183 @@
         <v>1</v>
       </c>
       <c r="D540" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E540" t="s">
-        <v>710</v>
+        <v>1052</v>
       </c>
       <c r="F540" t="s">
-        <v>711</v>
+        <v>1053</v>
       </c>
       <c r="G540" s="1">
-        <v>46297</v>
+        <v>46213</v>
       </c>
       <c r="H540" s="1">
-        <v>46297</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B541" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="C541">
         <v>1</v>
       </c>
       <c r="D541" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E541" t="s">
-        <v>461</v>
+        <v>1055</v>
       </c>
       <c r="F541" t="s">
-        <v>462</v>
+        <v>1056</v>
       </c>
       <c r="G541" s="1">
-        <v>46297</v>
+        <v>46213</v>
       </c>
       <c r="H541" s="1">
-        <v>46300</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B542" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C542">
         <v>1</v>
       </c>
       <c r="D542" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E542" t="s">
-        <v>744</v>
+        <v>1055</v>
       </c>
       <c r="F542" t="s">
-        <v>745</v>
+        <v>1056</v>
       </c>
       <c r="G542" s="1">
-        <v>46300</v>
+        <v>46224</v>
       </c>
       <c r="H542" s="1">
-        <v>46300</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B543" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C543">
         <v>1</v>
       </c>
       <c r="D543" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E543" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="F543" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G543" s="1">
-        <v>46300</v>
+        <v>46253</v>
       </c>
       <c r="H543" s="1">
-        <v>46300</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B544" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C544">
         <v>1</v>
       </c>
       <c r="D544" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E544" t="s">
-        <v>1055</v>
+        <v>211</v>
       </c>
       <c r="F544" t="s">
-        <v>1056</v>
+        <v>212</v>
       </c>
       <c r="G544" s="1">
-        <v>46300</v>
+        <v>46273</v>
       </c>
       <c r="H544" s="1">
-        <v>46300</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B545" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C545">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D545" t="s">
         <v>80</v>
       </c>
       <c r="E545" t="s">
-        <v>1032</v>
+        <v>41</v>
       </c>
       <c r="F545" t="s">
-        <v>1033</v>
+        <v>42</v>
       </c>
       <c r="G545" s="1">
-        <v>46300</v>
+        <v>46289</v>
       </c>
       <c r="H545" s="1">
-        <v>46300</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B546" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C546">
         <v>1</v>
       </c>
       <c r="D546" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E546" t="s">
-        <v>221</v>
+        <v>1049</v>
       </c>
       <c r="F546" t="s">
-        <v>222</v>
+        <v>1050</v>
       </c>
       <c r="G546" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="H546" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B547" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C547">
         <v>1</v>
@@ -18064,24 +18085,24 @@
         <v>80</v>
       </c>
       <c r="E547" t="s">
-        <v>221</v>
+        <v>1065</v>
       </c>
       <c r="F547" t="s">
-        <v>222</v>
+        <v>1066</v>
       </c>
       <c r="G547" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="H547" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B548" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="C548">
         <v>1</v>
@@ -18090,24 +18111,24 @@
         <v>80</v>
       </c>
       <c r="E548" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="F548" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="G548" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H548" s="1">
-        <v>46301</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B549" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="C549">
         <v>1</v>
@@ -18116,24 +18137,24 @@
         <v>80</v>
       </c>
       <c r="E549" t="s">
-        <v>1038</v>
+        <v>711</v>
       </c>
       <c r="F549" t="s">
-        <v>1039</v>
+        <v>712</v>
       </c>
       <c r="G549" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H549" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B550" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C550">
         <v>1</v>
@@ -18142,10 +18163,10 @@
         <v>80</v>
       </c>
       <c r="E550" t="s">
-        <v>1038</v>
+        <v>745</v>
       </c>
       <c r="F550" t="s">
-        <v>1039</v>
+        <v>746</v>
       </c>
       <c r="G550" s="1">
         <v>46300</v>
@@ -18156,10 +18177,10 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B551" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C551">
         <v>1</v>
@@ -18168,24 +18189,24 @@
         <v>80</v>
       </c>
       <c r="E551" t="s">
-        <v>744</v>
+        <v>1071</v>
       </c>
       <c r="F551" t="s">
-        <v>745</v>
+        <v>1072</v>
       </c>
       <c r="G551" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H551" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="B552" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="C552">
         <v>1</v>
@@ -18194,238 +18215,238 @@
         <v>80</v>
       </c>
       <c r="E552" t="s">
-        <v>1055</v>
+        <v>1071</v>
       </c>
       <c r="F552" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="G552" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H552" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B553" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="C553">
         <v>1</v>
       </c>
       <c r="D553" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="E553" t="s">
-        <v>1068</v>
+        <v>221</v>
       </c>
       <c r="F553" t="s">
-        <v>1069</v>
+        <v>222</v>
       </c>
       <c r="G553" s="1">
-        <v>46063</v>
+        <v>46300</v>
       </c>
       <c r="H553" s="1">
-        <v>46064</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B554" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="C554">
         <v>1</v>
       </c>
       <c r="D554" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E554" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="F554" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="G554" s="1">
-        <v>46113</v>
+        <v>46300</v>
       </c>
       <c r="H554" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B555" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="C555">
         <v>1</v>
       </c>
       <c r="D555" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E555" t="s">
-        <v>57</v>
+        <v>1055</v>
       </c>
       <c r="F555" t="s">
-        <v>58</v>
+        <v>1056</v>
       </c>
       <c r="G555" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
       <c r="H555" s="1">
-        <v>46125</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B556" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="C556">
         <v>1</v>
       </c>
       <c r="D556" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E556" t="s">
-        <v>57</v>
+        <v>1055</v>
       </c>
       <c r="F556" t="s">
-        <v>58</v>
+        <v>1056</v>
       </c>
       <c r="G556" s="1">
-        <v>46126</v>
+        <v>46300</v>
       </c>
       <c r="H556" s="1">
-        <v>46126</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B557" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="C557">
         <v>1</v>
       </c>
       <c r="D557" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E557" t="s">
-        <v>57</v>
+        <v>1055</v>
       </c>
       <c r="F557" t="s">
-        <v>58</v>
+        <v>1056</v>
       </c>
       <c r="G557" s="1">
-        <v>46126</v>
+        <v>46300</v>
       </c>
       <c r="H557" s="1">
-        <v>46126</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B558" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="C558">
         <v>1</v>
       </c>
       <c r="D558" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E558" t="s">
-        <v>57</v>
+        <v>745</v>
       </c>
       <c r="F558" t="s">
-        <v>58</v>
+        <v>746</v>
       </c>
       <c r="G558" s="1">
-        <v>46128</v>
+        <v>46301</v>
       </c>
       <c r="H558" s="1">
-        <v>46128</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="B559" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="C559">
         <v>1</v>
       </c>
       <c r="D559" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E559" t="s">
-        <v>57</v>
+        <v>1071</v>
       </c>
       <c r="F559" t="s">
-        <v>58</v>
+        <v>1072</v>
       </c>
       <c r="G559" s="1">
-        <v>46132</v>
+        <v>46301</v>
       </c>
       <c r="H559" s="1">
-        <v>46132</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B560" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="C560">
         <v>1</v>
       </c>
       <c r="D560" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E560" t="s">
-        <v>57</v>
+        <v>1083</v>
       </c>
       <c r="F560" t="s">
-        <v>58</v>
+        <v>1084</v>
       </c>
       <c r="G560" s="1">
-        <v>46161</v>
+        <v>46063</v>
       </c>
       <c r="H560" s="1">
-        <v>46161</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B561" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C561">
         <v>1</v>
       </c>
       <c r="D561" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E561" t="s">
         <v>57</v>
@@ -18434,18 +18455,18 @@
         <v>58</v>
       </c>
       <c r="G561" s="1">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="H561" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B562" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="C562">
         <v>1</v>
@@ -18460,24 +18481,24 @@
         <v>58</v>
       </c>
       <c r="G562" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="H562" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B563" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C563">
         <v>1</v>
       </c>
       <c r="D563" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E563" t="s">
         <v>57</v>
@@ -18486,24 +18507,24 @@
         <v>58</v>
       </c>
       <c r="G563" s="1">
-        <v>46195</v>
+        <v>46126</v>
       </c>
       <c r="H563" s="1">
-        <v>46252</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B564" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="C564">
         <v>1</v>
       </c>
       <c r="D564" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E564" t="s">
         <v>57</v>
@@ -18512,18 +18533,18 @@
         <v>58</v>
       </c>
       <c r="G564" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
       <c r="H564" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B565" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C565">
         <v>1</v>
@@ -18538,18 +18559,18 @@
         <v>58</v>
       </c>
       <c r="G565" s="1">
-        <v>46213</v>
+        <v>46128</v>
       </c>
       <c r="H565" s="1">
-        <v>46213</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B566" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="C566">
         <v>1</v>
@@ -18564,50 +18585,50 @@
         <v>58</v>
       </c>
       <c r="G566" s="1">
-        <v>46218</v>
+        <v>46132</v>
       </c>
       <c r="H566" s="1">
-        <v>46252</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B567" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C567">
         <v>1</v>
       </c>
       <c r="D567" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E567" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F567" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G567" s="1">
-        <v>46226</v>
+        <v>46161</v>
       </c>
       <c r="H567" s="1">
-        <v>46226</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B568" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="C568">
         <v>1</v>
       </c>
       <c r="D568" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E568" t="s">
         <v>57</v>
@@ -18616,24 +18637,24 @@
         <v>58</v>
       </c>
       <c r="G568" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="H568" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B569" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C569">
         <v>1</v>
       </c>
       <c r="D569" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E569" t="s">
         <v>57</v>
@@ -18642,18 +18663,18 @@
         <v>58</v>
       </c>
       <c r="G569" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="H569" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B570" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="C570">
         <v>1</v>
@@ -18668,18 +18689,18 @@
         <v>58</v>
       </c>
       <c r="G570" s="1">
-        <v>46227</v>
+        <v>46195</v>
       </c>
       <c r="H570" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B571" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C571">
         <v>1</v>
@@ -18688,30 +18709,30 @@
         <v>6</v>
       </c>
       <c r="E571" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F571" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G571" s="1">
-        <v>46230</v>
+        <v>46210</v>
       </c>
       <c r="H571" s="1">
-        <v>46252</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B572" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="C572">
         <v>1</v>
       </c>
       <c r="D572" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E572" t="s">
         <v>57</v>
@@ -18720,18 +18741,18 @@
         <v>58</v>
       </c>
       <c r="G572" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
       <c r="H572" s="1">
-        <v>46231</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B573" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C573">
         <v>1</v>
@@ -18746,50 +18767,50 @@
         <v>58</v>
       </c>
       <c r="G573" s="1">
-        <v>46254</v>
+        <v>46218</v>
       </c>
       <c r="H573" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B574" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="C574">
         <v>1</v>
       </c>
       <c r="D574" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E574" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F574" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G574" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="H574" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B575" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C575">
         <v>1</v>
       </c>
       <c r="D575" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E575" t="s">
         <v>57</v>
@@ -18798,18 +18819,18 @@
         <v>58</v>
       </c>
       <c r="G575" s="1">
-        <v>46260</v>
+        <v>46227</v>
       </c>
       <c r="H575" s="1">
-        <v>46260</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B576" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="C576">
         <v>1</v>
@@ -18824,18 +18845,18 @@
         <v>58</v>
       </c>
       <c r="G576" s="1">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="H576" s="1">
-        <v>46289</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B577" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C577">
         <v>1</v>
@@ -18850,50 +18871,50 @@
         <v>58</v>
       </c>
       <c r="G577" s="1">
-        <v>46294</v>
+        <v>46227</v>
       </c>
       <c r="H577" s="1">
-        <v>46294</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B578" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="C578">
         <v>1</v>
       </c>
       <c r="D578" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E578" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F578" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G578" s="1">
-        <v>46301</v>
+        <v>46230</v>
       </c>
       <c r="H578" s="1">
-        <v>46301</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B579" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C579">
         <v>1</v>
       </c>
       <c r="D579" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E579" t="s">
         <v>57</v>
@@ -18902,24 +18923,24 @@
         <v>58</v>
       </c>
       <c r="G579" s="1">
-        <v>46301</v>
+        <v>46231</v>
       </c>
       <c r="H579" s="1">
-        <v>46301</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B580" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="C580">
         <v>1</v>
       </c>
       <c r="D580" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E580" t="s">
         <v>57</v>
@@ -18928,24 +18949,24 @@
         <v>58</v>
       </c>
       <c r="G580" s="1">
-        <v>46301</v>
+        <v>46254</v>
       </c>
       <c r="H580" s="1">
-        <v>46301</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B581" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C581">
         <v>1</v>
       </c>
       <c r="D581" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E581" t="s">
         <v>57</v>
@@ -18954,24 +18975,24 @@
         <v>58</v>
       </c>
       <c r="G581" s="1">
-        <v>46301</v>
+        <v>46255</v>
       </c>
       <c r="H581" s="1">
-        <v>46301</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B582" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="C582">
         <v>1</v>
       </c>
       <c r="D582" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E582" t="s">
         <v>57</v>
@@ -18980,24 +19001,24 @@
         <v>58</v>
       </c>
       <c r="G582" s="1">
-        <v>46301</v>
+        <v>46260</v>
       </c>
       <c r="H582" s="1">
-        <v>46301</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B583" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C583">
         <v>1</v>
       </c>
       <c r="D583" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E583" t="s">
         <v>57</v>
@@ -19006,24 +19027,24 @@
         <v>58</v>
       </c>
       <c r="G583" s="1">
-        <v>46301</v>
+        <v>46289</v>
       </c>
       <c r="H583" s="1">
-        <v>46301</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B584" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="C584">
         <v>1</v>
       </c>
       <c r="D584" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E584" t="s">
         <v>57</v>
@@ -19032,44 +19053,44 @@
         <v>58</v>
       </c>
       <c r="G584" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="H584" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1066</v>
+        <v>1109</v>
       </c>
       <c r="B585" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="C585">
         <v>1</v>
       </c>
       <c r="D585" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E585" t="s">
-        <v>57</v>
+        <v>1111</v>
       </c>
       <c r="F585" t="s">
-        <v>58</v>
+        <v>1112</v>
       </c>
       <c r="G585" s="1">
-        <v>46301</v>
+        <v>46157</v>
       </c>
       <c r="H585" s="1">
-        <v>46301</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B586" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
       <c r="C586">
         <v>1</v>
@@ -19078,24 +19099,24 @@
         <v>2</v>
       </c>
       <c r="E586" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="F586" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="G586" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="H586" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B587" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="C587">
         <v>1</v>
@@ -19104,24 +19125,24 @@
         <v>2</v>
       </c>
       <c r="E587" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="F587" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="G587" s="1">
-        <v>46168</v>
+        <v>46218</v>
       </c>
       <c r="H587" s="1">
-        <v>46170</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B588" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C588">
         <v>1</v>
@@ -19130,24 +19151,24 @@
         <v>2</v>
       </c>
       <c r="E588" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F588" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="G588" s="1">
-        <v>46218</v>
+        <v>46244</v>
       </c>
       <c r="H588" s="1">
-        <v>46218</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B589" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C589">
         <v>1</v>
@@ -19156,24 +19177,24 @@
         <v>2</v>
       </c>
       <c r="E589" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F589" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="G589" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="H589" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B590" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C590">
         <v>1</v>
@@ -19182,10 +19203,10 @@
         <v>2</v>
       </c>
       <c r="E590" t="s">
-        <v>1104</v>
+        <v>1120</v>
       </c>
       <c r="F590" t="s">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="G590" s="1">
         <v>46247</v>
@@ -19196,10 +19217,10 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B591" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="C591">
         <v>1</v>
@@ -19208,24 +19229,24 @@
         <v>2</v>
       </c>
       <c r="E591" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F591" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G591" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="H591" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B592" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="C592">
         <v>1</v>
@@ -19234,24 +19255,24 @@
         <v>2</v>
       </c>
       <c r="E592" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F592" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="G592" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H592" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B593" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C593">
         <v>1</v>
@@ -19260,67 +19281,41 @@
         <v>2</v>
       </c>
       <c r="E593" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F593" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="G593" s="1">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="H593" s="1">
-        <v>46258</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="B594" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="C594">
         <v>1</v>
       </c>
       <c r="D594" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E594" t="s">
-        <v>1104</v>
+        <v>13</v>
       </c>
       <c r="F594" t="s">
-        <v>1105</v>
+        <v>14</v>
       </c>
       <c r="G594" s="1">
-        <v>46262</v>
+        <v>46281</v>
       </c>
       <c r="H594" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A595" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B595" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C595">
-        <v>1</v>
-      </c>
-      <c r="D595" t="s">
-        <v>6</v>
-      </c>
-      <c r="E595" t="s">
-        <v>13</v>
-      </c>
-      <c r="F595" t="s">
-        <v>14</v>
-      </c>
-      <c r="G595" s="1">
-        <v>46281</v>
-      </c>
-      <c r="H595" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EAC9404-7A63-42B9-80ED-EA612F3D6A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AE01ED8-A4B1-4CC1-934F-86A74D524A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{C727072A-0D58-4435-95C8-6D57BFAA23E7}"/>
+    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{CF312FA0-55D7-4249-8BA7-8CABA3C451E8}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="968">
   <si>
     <t>0001</t>
   </si>
@@ -2458,6 +2458,15 @@
     <t xml:space="preserve">  217150</t>
   </si>
   <si>
+    <t xml:space="preserve">  217151</t>
+  </si>
+  <si>
+    <t>SY05</t>
+  </si>
+  <si>
+    <t>SANITARIOS YRIGOYEN CABRERA S. R. L.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217152</t>
   </si>
   <si>
@@ -2503,6 +2512,9 @@
     <t xml:space="preserve">  217161</t>
   </si>
   <si>
+    <t xml:space="preserve">  217162</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217163</t>
   </si>
   <si>
@@ -2530,6 +2542,15 @@
     <t xml:space="preserve">  217167</t>
   </si>
   <si>
+    <t xml:space="preserve">  217168</t>
+  </si>
+  <si>
+    <t>CM57</t>
+  </si>
+  <si>
+    <t>CELESIA MARIANO T-SANITARIOS LARRALDE 1724</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217169</t>
   </si>
   <si>
@@ -2540,6 +2561,60 @@
   </si>
   <si>
     <t xml:space="preserve">  217172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217175</t>
+  </si>
+  <si>
+    <t>RP08</t>
+  </si>
+  <si>
+    <t>RUSSO PABLO D. -CASA SAN JUAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217183</t>
+  </si>
+  <si>
+    <t>VL05</t>
+  </si>
+  <si>
+    <t>VENTURA LEANDRO ARIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217186</t>
   </si>
   <si>
     <t>0004</t>
@@ -3298,34 +3373,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F67BFF4B-4A03-4C70-B5CD-F4D4F6CABD57}">
-  <dimension ref="A1:H481"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DB821C-4677-411C-A378-21B5CB267C5F}">
+  <dimension ref="A1:H498"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>935</v>
+        <v>960</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>936</v>
+        <v>961</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>937</v>
+        <v>962</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>938</v>
+        <v>963</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>940</v>
+        <v>965</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -13612,10 +13687,10 @@
         <v>154</v>
       </c>
       <c r="E397" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="F397" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="G397" s="1">
         <v>46302</v>
@@ -13629,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -13638,10 +13713,10 @@
         <v>154</v>
       </c>
       <c r="E398" t="s">
-        <v>808</v>
+        <v>761</v>
       </c>
       <c r="F398" t="s">
-        <v>809</v>
+        <v>762</v>
       </c>
       <c r="G398" s="1">
         <v>46302</v>
@@ -13655,7 +13730,7 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C399">
         <v>1</v>
@@ -13664,10 +13739,10 @@
         <v>154</v>
       </c>
       <c r="E399" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="F399" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="G399" s="1">
         <v>46302</v>
@@ -13690,10 +13765,10 @@
         <v>154</v>
       </c>
       <c r="E400" t="s">
-        <v>139</v>
+        <v>824</v>
       </c>
       <c r="F400" t="s">
-        <v>140</v>
+        <v>825</v>
       </c>
       <c r="G400" s="1">
         <v>46302</v>
@@ -13707,7 +13782,7 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C401">
         <v>1</v>
@@ -13733,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C402">
         <v>1</v>
@@ -13742,10 +13817,10 @@
         <v>154</v>
       </c>
       <c r="E402" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="F402" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="G402" s="1">
         <v>46302</v>
@@ -13759,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="B403" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C403">
         <v>1</v>
@@ -13768,10 +13843,10 @@
         <v>154</v>
       </c>
       <c r="E403" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="F403" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="G403" s="1">
         <v>46302</v>
@@ -13785,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="B404" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C404">
         <v>1</v>
@@ -13811,7 +13886,7 @@
         <v>0</v>
       </c>
       <c r="B405" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C405">
         <v>1</v>
@@ -13820,10 +13895,10 @@
         <v>154</v>
       </c>
       <c r="E405" t="s">
-        <v>829</v>
+        <v>748</v>
       </c>
       <c r="F405" t="s">
-        <v>830</v>
+        <v>749</v>
       </c>
       <c r="G405" s="1">
         <v>46302</v>
@@ -13846,10 +13921,10 @@
         <v>154</v>
       </c>
       <c r="E406" t="s">
-        <v>832</v>
+        <v>139</v>
       </c>
       <c r="F406" t="s">
-        <v>833</v>
+        <v>140</v>
       </c>
       <c r="G406" s="1">
         <v>46302</v>
@@ -13863,19 +13938,19 @@
         <v>0</v>
       </c>
       <c r="B407" t="s">
+        <v>832</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>154</v>
+      </c>
+      <c r="E407" t="s">
+        <v>833</v>
+      </c>
+      <c r="F407" t="s">
         <v>834</v>
-      </c>
-      <c r="C407">
-        <v>1</v>
-      </c>
-      <c r="D407" t="s">
-        <v>154</v>
-      </c>
-      <c r="E407" t="s">
-        <v>37</v>
-      </c>
-      <c r="F407" t="s">
-        <v>38</v>
       </c>
       <c r="G407" s="1">
         <v>46302</v>
@@ -13898,10 +13973,10 @@
         <v>154</v>
       </c>
       <c r="E408" t="s">
-        <v>37</v>
+        <v>836</v>
       </c>
       <c r="F408" t="s">
-        <v>38</v>
+        <v>837</v>
       </c>
       <c r="G408" s="1">
         <v>46302</v>
@@ -13915,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -13941,7 +14016,7 @@
         <v>0</v>
       </c>
       <c r="B410" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -13950,10 +14025,10 @@
         <v>154</v>
       </c>
       <c r="E410" t="s">
-        <v>264</v>
+        <v>37</v>
       </c>
       <c r="F410" t="s">
-        <v>265</v>
+        <v>38</v>
       </c>
       <c r="G410" s="1">
         <v>46302</v>
@@ -13967,7 +14042,7 @@
         <v>0</v>
       </c>
       <c r="B411" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -13976,10 +14051,10 @@
         <v>154</v>
       </c>
       <c r="E411" t="s">
-        <v>692</v>
+        <v>841</v>
       </c>
       <c r="F411" t="s">
-        <v>693</v>
+        <v>842</v>
       </c>
       <c r="G411" s="1">
         <v>46302</v>
@@ -13993,7 +14068,7 @@
         <v>0</v>
       </c>
       <c r="B412" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C412">
         <v>1</v>
@@ -14016,62 +14091,62 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="B413" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C413">
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E413" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="F413" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="G413" s="1">
-        <v>46148</v>
+        <v>46302</v>
       </c>
       <c r="H413" s="1">
-        <v>46149</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="B414" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C414">
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E414" t="s">
-        <v>111</v>
+        <v>692</v>
       </c>
       <c r="F414" t="s">
-        <v>112</v>
+        <v>693</v>
       </c>
       <c r="G414" s="1">
-        <v>46268</v>
+        <v>46302</v>
       </c>
       <c r="H414" s="1">
-        <v>46268</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="B415" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C415">
         <v>1</v>
@@ -14080,24 +14155,24 @@
         <v>154</v>
       </c>
       <c r="E415" t="s">
-        <v>844</v>
+        <v>37</v>
       </c>
       <c r="F415" t="s">
-        <v>845</v>
+        <v>38</v>
       </c>
       <c r="G415" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H415" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="B416" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C416">
         <v>1</v>
@@ -14106,10 +14181,10 @@
         <v>154</v>
       </c>
       <c r="E416" t="s">
-        <v>692</v>
+        <v>758</v>
       </c>
       <c r="F416" t="s">
-        <v>693</v>
+        <v>759</v>
       </c>
       <c r="G416" s="1">
         <v>46302</v>
@@ -14120,10 +14195,10 @@
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="B417" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C417">
         <v>1</v>
@@ -14132,10 +14207,10 @@
         <v>154</v>
       </c>
       <c r="E417" t="s">
-        <v>848</v>
+        <v>37</v>
       </c>
       <c r="F417" t="s">
-        <v>849</v>
+        <v>38</v>
       </c>
       <c r="G417" s="1">
         <v>46302</v>
@@ -14146,33 +14221,33 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
+        <v>0</v>
+      </c>
+      <c r="B418" t="s">
+        <v>849</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418" t="s">
+        <v>154</v>
+      </c>
+      <c r="E418" t="s">
         <v>850</v>
       </c>
-      <c r="B418" t="s">
+      <c r="F418" t="s">
         <v>851</v>
       </c>
-      <c r="C418">
-        <v>1</v>
-      </c>
-      <c r="D418" t="s">
-        <v>6</v>
-      </c>
-      <c r="E418" t="s">
-        <v>41</v>
-      </c>
-      <c r="F418" t="s">
-        <v>42</v>
-      </c>
       <c r="G418" s="1">
-        <v>46133</v>
+        <v>46302</v>
       </c>
       <c r="H418" s="1">
-        <v>46134</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B419" t="s">
         <v>852</v>
@@ -14181,24 +14256,24 @@
         <v>1</v>
       </c>
       <c r="D419" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E419" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F419" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G419" s="1">
-        <v>46134</v>
+        <v>46302</v>
       </c>
       <c r="H419" s="1">
-        <v>46134</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B420" t="s">
         <v>853</v>
@@ -14207,183 +14282,183 @@
         <v>1</v>
       </c>
       <c r="D420" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E420" t="s">
-        <v>19</v>
+        <v>850</v>
       </c>
       <c r="F420" t="s">
-        <v>20</v>
+        <v>851</v>
       </c>
       <c r="G420" s="1">
-        <v>46156</v>
+        <v>46302</v>
       </c>
       <c r="H420" s="1">
-        <v>46156</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B421" t="s">
         <v>854</v>
       </c>
       <c r="C421">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D421" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E421" t="s">
-        <v>855</v>
+        <v>614</v>
       </c>
       <c r="F421" t="s">
-        <v>856</v>
+        <v>615</v>
       </c>
       <c r="G421" s="1">
-        <v>46209</v>
+        <v>46302</v>
       </c>
       <c r="H421" s="1">
-        <v>46218</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B422" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C422">
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E422" t="s">
-        <v>858</v>
+        <v>37</v>
       </c>
       <c r="F422" t="s">
-        <v>859</v>
+        <v>38</v>
       </c>
       <c r="G422" s="1">
-        <v>46213</v>
+        <v>46302</v>
       </c>
       <c r="H422" s="1">
-        <v>46213</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B423" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C423">
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E423" t="s">
-        <v>861</v>
+        <v>37</v>
       </c>
       <c r="F423" t="s">
-        <v>862</v>
+        <v>38</v>
       </c>
       <c r="G423" s="1">
-        <v>46213</v>
+        <v>46302</v>
       </c>
       <c r="H423" s="1">
-        <v>46216</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B424" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C424">
         <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E424" t="s">
-        <v>861</v>
+        <v>37</v>
       </c>
       <c r="F424" t="s">
-        <v>862</v>
+        <v>38</v>
       </c>
       <c r="G424" s="1">
-        <v>46224</v>
+        <v>46302</v>
       </c>
       <c r="H424" s="1">
-        <v>46224</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B425" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C425">
         <v>1</v>
       </c>
       <c r="D425" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E425" t="s">
-        <v>865</v>
+        <v>37</v>
       </c>
       <c r="F425" t="s">
-        <v>866</v>
+        <v>38</v>
       </c>
       <c r="G425" s="1">
-        <v>46253</v>
+        <v>46302</v>
       </c>
       <c r="H425" s="1">
-        <v>46253</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B426" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="C426">
         <v>1</v>
       </c>
       <c r="D426" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E426" t="s">
-        <v>211</v>
+        <v>860</v>
       </c>
       <c r="F426" t="s">
-        <v>212</v>
+        <v>861</v>
       </c>
       <c r="G426" s="1">
-        <v>46273</v>
+        <v>46302</v>
       </c>
       <c r="H426" s="1">
-        <v>46274</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B427" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C427">
         <v>1</v>
@@ -14392,24 +14467,24 @@
         <v>154</v>
       </c>
       <c r="E427" t="s">
-        <v>510</v>
+        <v>860</v>
       </c>
       <c r="F427" t="s">
-        <v>511</v>
+        <v>861</v>
       </c>
       <c r="G427" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="H427" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B428" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C428">
         <v>1</v>
@@ -14418,24 +14493,24 @@
         <v>154</v>
       </c>
       <c r="E428" t="s">
-        <v>870</v>
+        <v>628</v>
       </c>
       <c r="F428" t="s">
-        <v>871</v>
+        <v>629</v>
       </c>
       <c r="G428" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="H428" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="B429" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="C429">
         <v>1</v>
@@ -14444,24 +14519,24 @@
         <v>154</v>
       </c>
       <c r="E429" t="s">
-        <v>870</v>
+        <v>841</v>
       </c>
       <c r="F429" t="s">
-        <v>871</v>
+        <v>842</v>
       </c>
       <c r="G429" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="H429" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B430" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C430">
         <v>1</v>
@@ -14470,50 +14545,50 @@
         <v>2</v>
       </c>
       <c r="E430" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="F430" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="G430" s="1">
-        <v>46300</v>
+        <v>46148</v>
       </c>
       <c r="H430" s="1">
-        <v>46300</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B431" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="C431">
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E431" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="F431" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="G431" s="1">
-        <v>46300</v>
+        <v>46268</v>
       </c>
       <c r="H431" s="1">
-        <v>46300</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B432" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="C432">
         <v>1</v>
@@ -14522,13 +14597,13 @@
         <v>154</v>
       </c>
       <c r="E432" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="F432" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="G432" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H432" s="1">
         <v>46301</v>
@@ -14536,10 +14611,10 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B433" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C433">
         <v>1</v>
@@ -14548,24 +14623,24 @@
         <v>154</v>
       </c>
       <c r="E433" t="s">
-        <v>861</v>
+        <v>692</v>
       </c>
       <c r="F433" t="s">
-        <v>862</v>
+        <v>693</v>
       </c>
       <c r="G433" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="H433" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="B434" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C434">
         <v>1</v>
@@ -14574,125 +14649,125 @@
         <v>154</v>
       </c>
       <c r="E434" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="F434" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="G434" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="H434" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B435" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C435">
         <v>1</v>
       </c>
       <c r="D435" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E435" t="s">
-        <v>870</v>
+        <v>41</v>
       </c>
       <c r="F435" t="s">
-        <v>871</v>
+        <v>42</v>
       </c>
       <c r="G435" s="1">
-        <v>46301</v>
+        <v>46133</v>
       </c>
       <c r="H435" s="1">
-        <v>46301</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B436" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C436">
         <v>1</v>
       </c>
       <c r="D436" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E436" t="s">
-        <v>474</v>
+        <v>41</v>
       </c>
       <c r="F436" t="s">
-        <v>475</v>
+        <v>42</v>
       </c>
       <c r="G436" s="1">
-        <v>46302</v>
+        <v>46134</v>
       </c>
       <c r="H436" s="1">
-        <v>46302</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B437" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C437">
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E437" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="F437" t="s">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="G437" s="1">
-        <v>46302</v>
+        <v>46156</v>
       </c>
       <c r="H437" s="1">
-        <v>46302</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B438" t="s">
+        <v>879</v>
+      </c>
+      <c r="C438">
+        <v>2</v>
+      </c>
+      <c r="D438" t="s">
+        <v>95</v>
+      </c>
+      <c r="E438" t="s">
+        <v>880</v>
+      </c>
+      <c r="F438" t="s">
         <v>881</v>
       </c>
-      <c r="C438">
-        <v>1</v>
-      </c>
-      <c r="D438" t="s">
-        <v>154</v>
-      </c>
-      <c r="E438" t="s">
-        <v>855</v>
-      </c>
-      <c r="F438" t="s">
-        <v>856</v>
-      </c>
       <c r="G438" s="1">
-        <v>46302</v>
+        <v>46209</v>
       </c>
       <c r="H438" s="1">
-        <v>46302</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="B439" t="s">
         <v>882</v>
@@ -14701,27 +14776,27 @@
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E439" t="s">
-        <v>264</v>
+        <v>883</v>
       </c>
       <c r="F439" t="s">
-        <v>265</v>
+        <v>884</v>
       </c>
       <c r="G439" s="1">
-        <v>46302</v>
+        <v>46213</v>
       </c>
       <c r="H439" s="1">
-        <v>46302</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B440" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C440">
         <v>1</v>
@@ -14730,76 +14805,76 @@
         <v>95</v>
       </c>
       <c r="E440" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F440" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G440" s="1">
-        <v>46063</v>
+        <v>46213</v>
       </c>
       <c r="H440" s="1">
-        <v>46064</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B441" t="s">
+        <v>888</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+      <c r="D441" t="s">
+        <v>95</v>
+      </c>
+      <c r="E441" t="s">
+        <v>886</v>
+      </c>
+      <c r="F441" t="s">
         <v>887</v>
       </c>
-      <c r="C441">
-        <v>1</v>
-      </c>
-      <c r="D441" t="s">
-        <v>6</v>
-      </c>
-      <c r="E441" t="s">
-        <v>57</v>
-      </c>
-      <c r="F441" t="s">
-        <v>58</v>
-      </c>
       <c r="G441" s="1">
-        <v>46113</v>
+        <v>46224</v>
       </c>
       <c r="H441" s="1">
-        <v>46125</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B442" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C442">
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E442" t="s">
-        <v>57</v>
+        <v>890</v>
       </c>
       <c r="F442" t="s">
-        <v>58</v>
+        <v>891</v>
       </c>
       <c r="G442" s="1">
-        <v>46125</v>
+        <v>46253</v>
       </c>
       <c r="H442" s="1">
-        <v>46125</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B443" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C443">
         <v>1</v>
@@ -14808,102 +14883,102 @@
         <v>2</v>
       </c>
       <c r="E443" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="F443" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="G443" s="1">
-        <v>46126</v>
+        <v>46273</v>
       </c>
       <c r="H443" s="1">
-        <v>46126</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B444" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C444">
         <v>1</v>
       </c>
       <c r="D444" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E444" t="s">
-        <v>57</v>
+        <v>510</v>
       </c>
       <c r="F444" t="s">
-        <v>58</v>
+        <v>511</v>
       </c>
       <c r="G444" s="1">
-        <v>46126</v>
+        <v>46297</v>
       </c>
       <c r="H444" s="1">
-        <v>46126</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B445" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C445">
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E445" t="s">
-        <v>57</v>
+        <v>895</v>
       </c>
       <c r="F445" t="s">
-        <v>58</v>
+        <v>896</v>
       </c>
       <c r="G445" s="1">
-        <v>46128</v>
+        <v>46300</v>
       </c>
       <c r="H445" s="1">
-        <v>46128</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B446" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E446" t="s">
-        <v>57</v>
+        <v>895</v>
       </c>
       <c r="F446" t="s">
-        <v>58</v>
+        <v>896</v>
       </c>
       <c r="G446" s="1">
-        <v>46132</v>
+        <v>46300</v>
       </c>
       <c r="H446" s="1">
-        <v>46132</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B447" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C447">
         <v>1</v>
@@ -14912,206 +14987,206 @@
         <v>2</v>
       </c>
       <c r="E447" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="F447" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="G447" s="1">
-        <v>46161</v>
+        <v>46300</v>
       </c>
       <c r="H447" s="1">
-        <v>46161</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B448" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C448">
         <v>1</v>
       </c>
       <c r="D448" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E448" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="F448" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="G448" s="1">
-        <v>46174</v>
+        <v>46300</v>
       </c>
       <c r="H448" s="1">
-        <v>46174</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B449" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C449">
         <v>1</v>
       </c>
       <c r="D449" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E449" t="s">
-        <v>57</v>
+        <v>886</v>
       </c>
       <c r="F449" t="s">
-        <v>58</v>
+        <v>887</v>
       </c>
       <c r="G449" s="1">
-        <v>46174</v>
+        <v>46300</v>
       </c>
       <c r="H449" s="1">
-        <v>46174</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B450" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="C450">
         <v>1</v>
       </c>
       <c r="D450" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E450" t="s">
-        <v>57</v>
+        <v>886</v>
       </c>
       <c r="F450" t="s">
-        <v>58</v>
+        <v>887</v>
       </c>
       <c r="G450" s="1">
-        <v>46195</v>
+        <v>46300</v>
       </c>
       <c r="H450" s="1">
-        <v>46252</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C451">
         <v>1</v>
       </c>
       <c r="D451" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E451" t="s">
-        <v>57</v>
+        <v>886</v>
       </c>
       <c r="F451" t="s">
-        <v>58</v>
+        <v>887</v>
       </c>
       <c r="G451" s="1">
-        <v>46210</v>
+        <v>46300</v>
       </c>
       <c r="H451" s="1">
-        <v>46210</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B452" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C452">
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E452" t="s">
-        <v>57</v>
+        <v>895</v>
       </c>
       <c r="F452" t="s">
-        <v>58</v>
+        <v>896</v>
       </c>
       <c r="G452" s="1">
-        <v>46213</v>
+        <v>46301</v>
       </c>
       <c r="H452" s="1">
-        <v>46213</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B453" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E453" t="s">
-        <v>57</v>
+        <v>474</v>
       </c>
       <c r="F453" t="s">
-        <v>58</v>
+        <v>475</v>
       </c>
       <c r="G453" s="1">
-        <v>46218</v>
+        <v>46302</v>
       </c>
       <c r="H453" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B454" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C454">
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E454" t="s">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="F454" t="s">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="G454" s="1">
-        <v>46226</v>
+        <v>46302</v>
       </c>
       <c r="H454" s="1">
-        <v>46226</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B455" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="C455">
         <v>1</v>
@@ -15120,76 +15195,76 @@
         <v>154</v>
       </c>
       <c r="E455" t="s">
-        <v>57</v>
+        <v>880</v>
       </c>
       <c r="F455" t="s">
-        <v>58</v>
+        <v>881</v>
       </c>
       <c r="G455" s="1">
-        <v>46227</v>
+        <v>46302</v>
       </c>
       <c r="H455" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="B456" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="C456">
         <v>1</v>
       </c>
       <c r="D456" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E456" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="F456" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="G456" s="1">
-        <v>46227</v>
+        <v>46302</v>
       </c>
       <c r="H456" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B457" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="C457">
         <v>1</v>
       </c>
       <c r="D457" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E457" t="s">
-        <v>57</v>
+        <v>910</v>
       </c>
       <c r="F457" t="s">
-        <v>58</v>
+        <v>911</v>
       </c>
       <c r="G457" s="1">
-        <v>46227</v>
+        <v>46063</v>
       </c>
       <c r="H457" s="1">
-        <v>46228</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B458" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -15198,30 +15273,30 @@
         <v>6</v>
       </c>
       <c r="E458" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F458" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G458" s="1">
-        <v>46230</v>
+        <v>46113</v>
       </c>
       <c r="H458" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B459" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="C459">
         <v>1</v>
       </c>
       <c r="D459" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E459" t="s">
         <v>57</v>
@@ -15230,24 +15305,24 @@
         <v>58</v>
       </c>
       <c r="G459" s="1">
-        <v>46231</v>
+        <v>46125</v>
       </c>
       <c r="H459" s="1">
-        <v>46231</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B460" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C460">
         <v>1</v>
       </c>
       <c r="D460" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E460" t="s">
         <v>57</v>
@@ -15256,18 +15331,18 @@
         <v>58</v>
       </c>
       <c r="G460" s="1">
-        <v>46254</v>
+        <v>46126</v>
       </c>
       <c r="H460" s="1">
-        <v>46254</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B461" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="C461">
         <v>1</v>
@@ -15282,24 +15357,24 @@
         <v>58</v>
       </c>
       <c r="G461" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
       <c r="H461" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B462" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="C462">
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E462" t="s">
         <v>57</v>
@@ -15308,18 +15383,18 @@
         <v>58</v>
       </c>
       <c r="G462" s="1">
-        <v>46260</v>
+        <v>46128</v>
       </c>
       <c r="H462" s="1">
-        <v>46260</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B463" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="C463">
         <v>1</v>
@@ -15334,24 +15409,24 @@
         <v>58</v>
       </c>
       <c r="G463" s="1">
-        <v>46289</v>
+        <v>46132</v>
       </c>
       <c r="H463" s="1">
-        <v>46289</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B464" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="C464">
         <v>1</v>
       </c>
       <c r="D464" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E464" t="s">
         <v>57</v>
@@ -15360,24 +15435,24 @@
         <v>58</v>
       </c>
       <c r="G464" s="1">
-        <v>46294</v>
+        <v>46161</v>
       </c>
       <c r="H464" s="1">
-        <v>46294</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B465" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="C465">
         <v>1</v>
       </c>
       <c r="D465" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E465" t="s">
         <v>57</v>
@@ -15386,50 +15461,50 @@
         <v>58</v>
       </c>
       <c r="G465" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
       <c r="H465" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B466" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C466">
         <v>1</v>
       </c>
       <c r="D466" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E466" t="s">
-        <v>605</v>
+        <v>57</v>
       </c>
       <c r="F466" t="s">
-        <v>606</v>
+        <v>58</v>
       </c>
       <c r="G466" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
       <c r="H466" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B467" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="C467">
         <v>1</v>
       </c>
       <c r="D467" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E467" t="s">
         <v>57</v>
@@ -15438,24 +15513,24 @@
         <v>58</v>
       </c>
       <c r="G467" s="1">
-        <v>46302</v>
+        <v>46195</v>
       </c>
       <c r="H467" s="1">
-        <v>46302</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B468" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="C468">
         <v>1</v>
       </c>
       <c r="D468" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E468" t="s">
         <v>57</v>
@@ -15464,24 +15539,24 @@
         <v>58</v>
       </c>
       <c r="G468" s="1">
-        <v>46302</v>
+        <v>46210</v>
       </c>
       <c r="H468" s="1">
-        <v>46302</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B469" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="C469">
         <v>1</v>
       </c>
       <c r="D469" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E469" t="s">
         <v>57</v>
@@ -15490,24 +15565,24 @@
         <v>58</v>
       </c>
       <c r="G469" s="1">
-        <v>46302</v>
+        <v>46213</v>
       </c>
       <c r="H469" s="1">
-        <v>46302</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>883</v>
+        <v>908</v>
       </c>
       <c r="B470" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="C470">
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E470" t="s">
         <v>57</v>
@@ -15516,200 +15591,200 @@
         <v>58</v>
       </c>
       <c r="G470" s="1">
-        <v>46302</v>
+        <v>46218</v>
       </c>
       <c r="H470" s="1">
-        <v>46302</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B471" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="C471">
         <v>1</v>
       </c>
       <c r="D471" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E471" t="s">
-        <v>919</v>
+        <v>77</v>
       </c>
       <c r="F471" t="s">
-        <v>920</v>
+        <v>78</v>
       </c>
       <c r="G471" s="1">
-        <v>46157</v>
+        <v>46226</v>
       </c>
       <c r="H471" s="1">
-        <v>46157</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B472" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C472">
         <v>1</v>
       </c>
       <c r="D472" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E472" t="s">
-        <v>922</v>
+        <v>57</v>
       </c>
       <c r="F472" t="s">
-        <v>923</v>
+        <v>58</v>
       </c>
       <c r="G472" s="1">
-        <v>46168</v>
+        <v>46227</v>
       </c>
       <c r="H472" s="1">
-        <v>46170</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B473" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C473">
         <v>1</v>
       </c>
       <c r="D473" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E473" t="s">
-        <v>919</v>
+        <v>57</v>
       </c>
       <c r="F473" t="s">
-        <v>920</v>
+        <v>58</v>
       </c>
       <c r="G473" s="1">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="H473" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B474" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C474">
         <v>1</v>
       </c>
       <c r="D474" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E474" t="s">
-        <v>919</v>
+        <v>57</v>
       </c>
       <c r="F474" t="s">
-        <v>920</v>
+        <v>58</v>
       </c>
       <c r="G474" s="1">
-        <v>46244</v>
+        <v>46227</v>
       </c>
       <c r="H474" s="1">
-        <v>46244</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B475" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C475">
         <v>1</v>
       </c>
       <c r="D475" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E475" t="s">
-        <v>919</v>
+        <v>77</v>
       </c>
       <c r="F475" t="s">
-        <v>920</v>
+        <v>78</v>
       </c>
       <c r="G475" s="1">
-        <v>46247</v>
+        <v>46230</v>
       </c>
       <c r="H475" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B476" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C476">
         <v>1</v>
       </c>
       <c r="D476" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E476" t="s">
-        <v>928</v>
+        <v>57</v>
       </c>
       <c r="F476" t="s">
-        <v>929</v>
+        <v>58</v>
       </c>
       <c r="G476" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="H476" s="1">
-        <v>46247</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B477" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C477">
         <v>1</v>
       </c>
       <c r="D477" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E477" t="s">
-        <v>919</v>
+        <v>57</v>
       </c>
       <c r="F477" t="s">
-        <v>920</v>
+        <v>58</v>
       </c>
       <c r="G477" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="H477" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B478" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C478">
         <v>1</v>
@@ -15718,50 +15793,50 @@
         <v>2</v>
       </c>
       <c r="E478" t="s">
-        <v>919</v>
+        <v>57</v>
       </c>
       <c r="F478" t="s">
-        <v>920</v>
+        <v>58</v>
       </c>
       <c r="G478" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="H478" s="1">
-        <v>46258</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B479" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C479">
         <v>1</v>
       </c>
       <c r="D479" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E479" t="s">
-        <v>919</v>
+        <v>57</v>
       </c>
       <c r="F479" t="s">
-        <v>920</v>
+        <v>58</v>
       </c>
       <c r="G479" s="1">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="H479" s="1">
-        <v>46265</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B480" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C480">
         <v>1</v>
@@ -15770,41 +15845,483 @@
         <v>6</v>
       </c>
       <c r="E480" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F480" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G480" s="1">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="H480" s="1">
-        <v>46283</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B481" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C481">
         <v>1</v>
       </c>
       <c r="D481" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E481" t="s">
-        <v>861</v>
+        <v>57</v>
       </c>
       <c r="F481" t="s">
-        <v>862</v>
+        <v>58</v>
       </c>
       <c r="G481" s="1">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="H481" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>908</v>
+      </c>
+      <c r="B482" t="s">
+        <v>936</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>154</v>
+      </c>
+      <c r="E482" t="s">
+        <v>57</v>
+      </c>
+      <c r="F482" t="s">
+        <v>58</v>
+      </c>
+      <c r="G482" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H482" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>908</v>
+      </c>
+      <c r="B483" t="s">
+        <v>937</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+      <c r="D483" t="s">
+        <v>154</v>
+      </c>
+      <c r="E483" t="s">
+        <v>605</v>
+      </c>
+      <c r="F483" t="s">
+        <v>606</v>
+      </c>
+      <c r="G483" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H483" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>908</v>
+      </c>
+      <c r="B484" t="s">
+        <v>938</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+      <c r="D484" t="s">
+        <v>154</v>
+      </c>
+      <c r="E484" t="s">
+        <v>57</v>
+      </c>
+      <c r="F484" t="s">
+        <v>58</v>
+      </c>
+      <c r="G484" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H484" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>908</v>
+      </c>
+      <c r="B485" t="s">
+        <v>939</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485" t="s">
+        <v>154</v>
+      </c>
+      <c r="E485" t="s">
+        <v>57</v>
+      </c>
+      <c r="F485" t="s">
+        <v>58</v>
+      </c>
+      <c r="G485" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H485" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>908</v>
+      </c>
+      <c r="B486" t="s">
+        <v>940</v>
+      </c>
+      <c r="C486">
+        <v>1</v>
+      </c>
+      <c r="D486" t="s">
+        <v>154</v>
+      </c>
+      <c r="E486" t="s">
+        <v>57</v>
+      </c>
+      <c r="F486" t="s">
+        <v>58</v>
+      </c>
+      <c r="G486" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H486" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>908</v>
+      </c>
+      <c r="B487" t="s">
+        <v>941</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+      <c r="D487" t="s">
+        <v>154</v>
+      </c>
+      <c r="E487" t="s">
+        <v>57</v>
+      </c>
+      <c r="F487" t="s">
+        <v>58</v>
+      </c>
+      <c r="G487" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H487" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>942</v>
+      </c>
+      <c r="B488" t="s">
+        <v>943</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+      <c r="D488" t="s">
+        <v>2</v>
+      </c>
+      <c r="E488" t="s">
+        <v>944</v>
+      </c>
+      <c r="F488" t="s">
+        <v>945</v>
+      </c>
+      <c r="G488" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H488" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>942</v>
+      </c>
+      <c r="B489" t="s">
+        <v>946</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+      <c r="D489" t="s">
+        <v>2</v>
+      </c>
+      <c r="E489" t="s">
+        <v>947</v>
+      </c>
+      <c r="F489" t="s">
+        <v>948</v>
+      </c>
+      <c r="G489" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H489" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>942</v>
+      </c>
+      <c r="B490" t="s">
+        <v>949</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+      <c r="D490" t="s">
+        <v>2</v>
+      </c>
+      <c r="E490" t="s">
+        <v>944</v>
+      </c>
+      <c r="F490" t="s">
+        <v>945</v>
+      </c>
+      <c r="G490" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H490" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>942</v>
+      </c>
+      <c r="B491" t="s">
+        <v>950</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+      <c r="D491" t="s">
+        <v>2</v>
+      </c>
+      <c r="E491" t="s">
+        <v>944</v>
+      </c>
+      <c r="F491" t="s">
+        <v>945</v>
+      </c>
+      <c r="G491" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H491" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>942</v>
+      </c>
+      <c r="B492" t="s">
+        <v>951</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+      <c r="D492" t="s">
+        <v>2</v>
+      </c>
+      <c r="E492" t="s">
+        <v>944</v>
+      </c>
+      <c r="F492" t="s">
+        <v>945</v>
+      </c>
+      <c r="G492" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H492" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>942</v>
+      </c>
+      <c r="B493" t="s">
+        <v>952</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+      <c r="D493" t="s">
+        <v>2</v>
+      </c>
+      <c r="E493" t="s">
+        <v>953</v>
+      </c>
+      <c r="F493" t="s">
+        <v>954</v>
+      </c>
+      <c r="G493" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H493" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>942</v>
+      </c>
+      <c r="B494" t="s">
+        <v>955</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494" t="s">
+        <v>2</v>
+      </c>
+      <c r="E494" t="s">
+        <v>944</v>
+      </c>
+      <c r="F494" t="s">
+        <v>945</v>
+      </c>
+      <c r="G494" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H494" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A495" t="s">
+        <v>942</v>
+      </c>
+      <c r="B495" t="s">
+        <v>956</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2</v>
+      </c>
+      <c r="E495" t="s">
+        <v>944</v>
+      </c>
+      <c r="F495" t="s">
+        <v>945</v>
+      </c>
+      <c r="G495" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H495" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A496" t="s">
+        <v>942</v>
+      </c>
+      <c r="B496" t="s">
+        <v>957</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+      <c r="D496" t="s">
+        <v>2</v>
+      </c>
+      <c r="E496" t="s">
+        <v>944</v>
+      </c>
+      <c r="F496" t="s">
+        <v>945</v>
+      </c>
+      <c r="G496" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H496" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A497" t="s">
+        <v>942</v>
+      </c>
+      <c r="B497" t="s">
+        <v>958</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+      <c r="D497" t="s">
+        <v>6</v>
+      </c>
+      <c r="E497" t="s">
+        <v>13</v>
+      </c>
+      <c r="F497" t="s">
+        <v>14</v>
+      </c>
+      <c r="G497" s="1">
+        <v>46281</v>
+      </c>
+      <c r="H497" s="1">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A498" t="s">
+        <v>942</v>
+      </c>
+      <c r="B498" t="s">
+        <v>959</v>
+      </c>
+      <c r="C498">
+        <v>1</v>
+      </c>
+      <c r="D498" t="s">
+        <v>154</v>
+      </c>
+      <c r="E498" t="s">
+        <v>886</v>
+      </c>
+      <c r="F498" t="s">
+        <v>887</v>
+      </c>
+      <c r="G498" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H498" s="1">
         <v>46302</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AE01ED8-A4B1-4CC1-934F-86A74D524A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{610201F1-A254-4686-970A-966208E3BAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{CF312FA0-55D7-4249-8BA7-8CABA3C451E8}"/>
+    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{F95E397D-4038-4488-B2AD-99D02EA2A302}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="977">
   <si>
     <t>0001</t>
   </si>
@@ -2617,6 +2617,54 @@
     <t xml:space="preserve">  217186</t>
   </si>
   <si>
+    <t xml:space="preserve">  217187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217189</t>
+  </si>
+  <si>
+    <t>SC38</t>
+  </si>
+  <si>
+    <t>SANITARIOS CORTESE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217192</t>
+  </si>
+  <si>
+    <t>DA28</t>
+  </si>
+  <si>
+    <t>DAPESOL S.A. -MATERIALES ACON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217193</t>
+  </si>
+  <si>
+    <t>RR12</t>
+  </si>
+  <si>
+    <t>RIOS MARIA JOSE Y RIOS MARIA FERNANDA S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217197</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2725,12 +2773,6 @@
     <t xml:space="preserve">    3006</t>
   </si>
   <si>
-    <t xml:space="preserve">    3007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3008</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3010</t>
   </si>
   <si>
@@ -2830,22 +2872,7 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2740</t>
-  </si>
-  <si>
     <t xml:space="preserve">    2741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2748</t>
   </si>
   <si>
     <t>9999</t>
@@ -3373,34 +3400,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DB821C-4677-411C-A378-21B5CB267C5F}">
-  <dimension ref="A1:H498"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAE6636-3677-47F9-89D2-E2156C95ADD9}">
+  <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6430,7 +6457,7 @@
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E118" t="s">
         <v>290</v>
@@ -7990,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E178" t="s">
         <v>48</v>
@@ -8016,7 +8043,7 @@
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E179" t="s">
         <v>16</v>
@@ -8042,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E180" t="s">
         <v>182</v>
@@ -8250,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E188" t="s">
         <v>420</v>
@@ -8302,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E190" t="s">
         <v>417</v>
@@ -8484,7 +8511,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E197" t="s">
         <v>48</v>
@@ -8562,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
@@ -8588,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
         <v>290</v>
@@ -8614,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
         <v>182</v>
@@ -8692,7 +8719,7 @@
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
         <v>172</v>
@@ -10928,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E291" t="s">
         <v>620</v>
@@ -10980,7 +11007,7 @@
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E293" t="s">
         <v>624</v>
@@ -11084,7 +11111,7 @@
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E297" t="s">
         <v>635</v>
@@ -11110,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E298" t="s">
         <v>638</v>
@@ -11188,7 +11215,7 @@
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E301" t="s">
         <v>642</v>
@@ -11214,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E302" t="s">
         <v>642</v>
@@ -11786,7 +11813,7 @@
         <v>1</v>
       </c>
       <c r="D324" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E324" t="s">
         <v>16</v>
@@ -11812,7 +11839,7 @@
         <v>1</v>
       </c>
       <c r="D325" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E325" t="s">
         <v>16</v>
@@ -12514,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E352" t="s">
         <v>642</v>
@@ -12540,7 +12567,7 @@
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E353" t="s">
         <v>635</v>
@@ -12800,7 +12827,7 @@
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E363" t="s">
         <v>761</v>
@@ -12826,7 +12853,7 @@
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E364" t="s">
         <v>764</v>
@@ -13060,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E373" t="s">
         <v>172</v>
@@ -13632,7 +13659,7 @@
         <v>1</v>
       </c>
       <c r="D395" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E395" t="s">
         <v>813</v>
@@ -14533,88 +14560,88 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
+        <v>0</v>
+      </c>
+      <c r="B430" t="s">
         <v>865</v>
       </c>
-      <c r="B430" t="s">
-        <v>866</v>
-      </c>
       <c r="C430">
         <v>1</v>
       </c>
       <c r="D430" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E430" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F430" t="s">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="G430" s="1">
-        <v>46148</v>
+        <v>46302</v>
       </c>
       <c r="H430" s="1">
-        <v>46149</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="B431" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C431">
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E431" t="s">
-        <v>111</v>
+        <v>813</v>
       </c>
       <c r="F431" t="s">
-        <v>112</v>
+        <v>814</v>
       </c>
       <c r="G431" s="1">
-        <v>46268</v>
+        <v>46302</v>
       </c>
       <c r="H431" s="1">
-        <v>46268</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="B432" t="s">
+        <v>867</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+      <c r="D432" t="s">
+        <v>154</v>
+      </c>
+      <c r="E432" t="s">
         <v>868</v>
       </c>
-      <c r="C432">
-        <v>1</v>
-      </c>
-      <c r="D432" t="s">
-        <v>154</v>
-      </c>
-      <c r="E432" t="s">
+      <c r="F432" t="s">
         <v>869</v>
       </c>
-      <c r="F432" t="s">
-        <v>870</v>
-      </c>
       <c r="G432" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H432" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="B433" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C433">
         <v>1</v>
@@ -14623,73 +14650,73 @@
         <v>154</v>
       </c>
       <c r="E433" t="s">
-        <v>692</v>
+        <v>868</v>
       </c>
       <c r="F433" t="s">
-        <v>693</v>
+        <v>869</v>
       </c>
       <c r="G433" s="1">
         <v>46302</v>
       </c>
       <c r="H433" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="B434" t="s">
+        <v>871</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434" t="s">
+        <v>154</v>
+      </c>
+      <c r="E434" t="s">
         <v>872</v>
       </c>
-      <c r="C434">
-        <v>1</v>
-      </c>
-      <c r="D434" t="s">
-        <v>154</v>
-      </c>
-      <c r="E434" t="s">
+      <c r="F434" t="s">
         <v>873</v>
-      </c>
-      <c r="F434" t="s">
-        <v>874</v>
       </c>
       <c r="G434" s="1">
         <v>46302</v>
       </c>
       <c r="H434" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
+        <v>0</v>
+      </c>
+      <c r="B435" t="s">
+        <v>874</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435" t="s">
+        <v>154</v>
+      </c>
+      <c r="E435" t="s">
         <v>875</v>
       </c>
-      <c r="B435" t="s">
+      <c r="F435" t="s">
         <v>876</v>
       </c>
-      <c r="C435">
-        <v>1</v>
-      </c>
-      <c r="D435" t="s">
-        <v>6</v>
-      </c>
-      <c r="E435" t="s">
-        <v>41</v>
-      </c>
-      <c r="F435" t="s">
-        <v>42</v>
-      </c>
       <c r="G435" s="1">
-        <v>46133</v>
+        <v>46302</v>
       </c>
       <c r="H435" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="B436" t="s">
         <v>877</v>
@@ -14698,24 +14725,24 @@
         <v>1</v>
       </c>
       <c r="D436" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E436" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F436" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G436" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
       <c r="H436" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="B437" t="s">
         <v>878</v>
@@ -14724,183 +14751,183 @@
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E437" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F437" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G437" s="1">
-        <v>46156</v>
+        <v>46303</v>
       </c>
       <c r="H437" s="1">
-        <v>46156</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="B438" t="s">
         <v>879</v>
       </c>
       <c r="C438">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E438" t="s">
-        <v>880</v>
+        <v>37</v>
       </c>
       <c r="F438" t="s">
-        <v>881</v>
+        <v>38</v>
       </c>
       <c r="G438" s="1">
-        <v>46209</v>
+        <v>46303</v>
       </c>
       <c r="H438" s="1">
-        <v>46218</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="B439" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C439">
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E439" t="s">
-        <v>883</v>
+        <v>37</v>
       </c>
       <c r="F439" t="s">
-        <v>884</v>
+        <v>38</v>
       </c>
       <c r="G439" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
       <c r="H439" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B440" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C440">
         <v>1</v>
       </c>
       <c r="D440" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E440" t="s">
-        <v>886</v>
+        <v>200</v>
       </c>
       <c r="F440" t="s">
-        <v>887</v>
+        <v>201</v>
       </c>
       <c r="G440" s="1">
-        <v>46213</v>
+        <v>46148</v>
       </c>
       <c r="H440" s="1">
-        <v>46216</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B441" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C441">
         <v>1</v>
       </c>
       <c r="D441" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E441" t="s">
-        <v>886</v>
+        <v>111</v>
       </c>
       <c r="F441" t="s">
-        <v>887</v>
+        <v>112</v>
       </c>
       <c r="G441" s="1">
-        <v>46224</v>
+        <v>46268</v>
       </c>
       <c r="H441" s="1">
-        <v>46224</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B442" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C442">
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E442" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="F442" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="G442" s="1">
-        <v>46253</v>
+        <v>46301</v>
       </c>
       <c r="H442" s="1">
-        <v>46253</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B443" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C443">
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E443" t="s">
-        <v>211</v>
+        <v>692</v>
       </c>
       <c r="F443" t="s">
-        <v>212</v>
+        <v>693</v>
       </c>
       <c r="G443" s="1">
-        <v>46273</v>
+        <v>46302</v>
       </c>
       <c r="H443" s="1">
-        <v>46274</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B444" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C444">
         <v>1</v>
@@ -14909,151 +14936,151 @@
         <v>154</v>
       </c>
       <c r="E444" t="s">
-        <v>510</v>
+        <v>889</v>
       </c>
       <c r="F444" t="s">
-        <v>511</v>
+        <v>890</v>
       </c>
       <c r="G444" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="H444" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B445" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C445">
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E445" t="s">
-        <v>895</v>
+        <v>41</v>
       </c>
       <c r="F445" t="s">
-        <v>896</v>
+        <v>42</v>
       </c>
       <c r="G445" s="1">
-        <v>46300</v>
+        <v>46133</v>
       </c>
       <c r="H445" s="1">
-        <v>46300</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B446" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E446" t="s">
-        <v>895</v>
+        <v>41</v>
       </c>
       <c r="F446" t="s">
-        <v>896</v>
+        <v>42</v>
       </c>
       <c r="G446" s="1">
-        <v>46300</v>
+        <v>46134</v>
       </c>
       <c r="H446" s="1">
-        <v>46300</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B447" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C447">
         <v>1</v>
       </c>
       <c r="D447" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E447" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="F447" t="s">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="G447" s="1">
-        <v>46300</v>
+        <v>46156</v>
       </c>
       <c r="H447" s="1">
-        <v>46300</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B448" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C448">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D448" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E448" t="s">
-        <v>221</v>
+        <v>896</v>
       </c>
       <c r="F448" t="s">
-        <v>222</v>
+        <v>897</v>
       </c>
       <c r="G448" s="1">
-        <v>46300</v>
+        <v>46209</v>
       </c>
       <c r="H448" s="1">
-        <v>46300</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B449" t="s">
+        <v>898</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449" t="s">
+        <v>6</v>
+      </c>
+      <c r="E449" t="s">
+        <v>899</v>
+      </c>
+      <c r="F449" t="s">
         <v>900</v>
       </c>
-      <c r="C449">
-        <v>1</v>
-      </c>
-      <c r="D449" t="s">
-        <v>154</v>
-      </c>
-      <c r="E449" t="s">
-        <v>886</v>
-      </c>
-      <c r="F449" t="s">
-        <v>887</v>
-      </c>
       <c r="G449" s="1">
-        <v>46300</v>
+        <v>46213</v>
       </c>
       <c r="H449" s="1">
-        <v>46301</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B450" t="s">
         <v>901</v>
@@ -15062,105 +15089,105 @@
         <v>1</v>
       </c>
       <c r="D450" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E450" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="F450" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="G450" s="1">
-        <v>46300</v>
+        <v>46213</v>
       </c>
       <c r="H450" s="1">
-        <v>46300</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B451" t="s">
+        <v>904</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451" t="s">
+        <v>95</v>
+      </c>
+      <c r="E451" t="s">
         <v>902</v>
       </c>
-      <c r="C451">
-        <v>1</v>
-      </c>
-      <c r="D451" t="s">
-        <v>154</v>
-      </c>
-      <c r="E451" t="s">
-        <v>886</v>
-      </c>
       <c r="F451" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="G451" s="1">
-        <v>46300</v>
+        <v>46224</v>
       </c>
       <c r="H451" s="1">
-        <v>46300</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B452" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C452">
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E452" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="F452" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="G452" s="1">
-        <v>46301</v>
+        <v>46253</v>
       </c>
       <c r="H452" s="1">
-        <v>46301</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B453" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E453" t="s">
-        <v>474</v>
+        <v>211</v>
       </c>
       <c r="F453" t="s">
-        <v>475</v>
+        <v>212</v>
       </c>
       <c r="G453" s="1">
-        <v>46302</v>
+        <v>46273</v>
       </c>
       <c r="H453" s="1">
-        <v>46302</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B454" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C454">
         <v>1</v>
@@ -15169,24 +15196,24 @@
         <v>154</v>
       </c>
       <c r="E454" t="s">
-        <v>264</v>
+        <v>510</v>
       </c>
       <c r="F454" t="s">
-        <v>265</v>
+        <v>511</v>
       </c>
       <c r="G454" s="1">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="H454" s="1">
-        <v>46302</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B455" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C455">
         <v>1</v>
@@ -15195,24 +15222,24 @@
         <v>154</v>
       </c>
       <c r="E455" t="s">
-        <v>880</v>
+        <v>911</v>
       </c>
       <c r="F455" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="G455" s="1">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="H455" s="1">
-        <v>46302</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="B456" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C456">
         <v>1</v>
@@ -15221,76 +15248,76 @@
         <v>154</v>
       </c>
       <c r="E456" t="s">
-        <v>264</v>
+        <v>911</v>
       </c>
       <c r="F456" t="s">
-        <v>265</v>
+        <v>912</v>
       </c>
       <c r="G456" s="1">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="H456" s="1">
-        <v>46302</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B457" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="C457">
         <v>1</v>
       </c>
       <c r="D457" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E457" t="s">
-        <v>910</v>
+        <v>221</v>
       </c>
       <c r="F457" t="s">
-        <v>911</v>
+        <v>222</v>
       </c>
       <c r="G457" s="1">
-        <v>46063</v>
+        <v>46300</v>
       </c>
       <c r="H457" s="1">
-        <v>46064</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B458" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C458">
         <v>1</v>
       </c>
       <c r="D458" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E458" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="F458" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="G458" s="1">
-        <v>46113</v>
+        <v>46300</v>
       </c>
       <c r="H458" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B459" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C459">
         <v>1</v>
@@ -15299,186 +15326,186 @@
         <v>2</v>
       </c>
       <c r="E459" t="s">
-        <v>57</v>
+        <v>902</v>
       </c>
       <c r="F459" t="s">
-        <v>58</v>
+        <v>903</v>
       </c>
       <c r="G459" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
       <c r="H459" s="1">
-        <v>46125</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B460" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C460">
         <v>1</v>
       </c>
       <c r="D460" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E460" t="s">
-        <v>57</v>
+        <v>911</v>
       </c>
       <c r="F460" t="s">
-        <v>58</v>
+        <v>912</v>
       </c>
       <c r="G460" s="1">
-        <v>46126</v>
+        <v>46301</v>
       </c>
       <c r="H460" s="1">
-        <v>46126</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B461" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C461">
         <v>1</v>
       </c>
       <c r="D461" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E461" t="s">
-        <v>57</v>
+        <v>474</v>
       </c>
       <c r="F461" t="s">
-        <v>58</v>
+        <v>475</v>
       </c>
       <c r="G461" s="1">
-        <v>46126</v>
+        <v>46302</v>
       </c>
       <c r="H461" s="1">
-        <v>46126</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B462" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C462">
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E462" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="F462" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="G462" s="1">
-        <v>46128</v>
+        <v>46302</v>
       </c>
       <c r="H462" s="1">
-        <v>46128</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B463" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C463">
         <v>1</v>
       </c>
       <c r="D463" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E463" t="s">
-        <v>57</v>
+        <v>896</v>
       </c>
       <c r="F463" t="s">
-        <v>58</v>
+        <v>897</v>
       </c>
       <c r="G463" s="1">
-        <v>46132</v>
+        <v>46302</v>
       </c>
       <c r="H463" s="1">
-        <v>46132</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="B464" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C464">
         <v>1</v>
       </c>
       <c r="D464" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E464" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="F464" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="G464" s="1">
-        <v>46161</v>
+        <v>46302</v>
       </c>
       <c r="H464" s="1">
-        <v>46161</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B465" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C465">
         <v>1</v>
       </c>
       <c r="D465" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E465" t="s">
-        <v>57</v>
+        <v>924</v>
       </c>
       <c r="F465" t="s">
-        <v>58</v>
+        <v>925</v>
       </c>
       <c r="G465" s="1">
-        <v>46174</v>
+        <v>46063</v>
       </c>
       <c r="H465" s="1">
-        <v>46174</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B466" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="C466">
         <v>1</v>
       </c>
       <c r="D466" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E466" t="s">
         <v>57</v>
@@ -15487,24 +15514,24 @@
         <v>58</v>
       </c>
       <c r="G466" s="1">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="H466" s="1">
-        <v>46174</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B467" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="C467">
         <v>1</v>
       </c>
       <c r="D467" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E467" t="s">
         <v>57</v>
@@ -15513,24 +15540,24 @@
         <v>58</v>
       </c>
       <c r="G467" s="1">
-        <v>46195</v>
+        <v>46125</v>
       </c>
       <c r="H467" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B468" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="C468">
         <v>1</v>
       </c>
       <c r="D468" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E468" t="s">
         <v>57</v>
@@ -15539,18 +15566,18 @@
         <v>58</v>
       </c>
       <c r="G468" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
       <c r="H468" s="1">
-        <v>46210</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B469" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="C469">
         <v>1</v>
@@ -15565,24 +15592,24 @@
         <v>58</v>
       </c>
       <c r="G469" s="1">
-        <v>46213</v>
+        <v>46126</v>
       </c>
       <c r="H469" s="1">
-        <v>46213</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B470" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="C470">
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E470" t="s">
         <v>57</v>
@@ -15591,18 +15618,18 @@
         <v>58</v>
       </c>
       <c r="G470" s="1">
-        <v>46218</v>
+        <v>46128</v>
       </c>
       <c r="H470" s="1">
-        <v>46252</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B471" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="C471">
         <v>1</v>
@@ -15611,30 +15638,30 @@
         <v>6</v>
       </c>
       <c r="E471" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F471" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G471" s="1">
-        <v>46226</v>
+        <v>46132</v>
       </c>
       <c r="H471" s="1">
-        <v>46226</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B472" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C472">
         <v>1</v>
       </c>
       <c r="D472" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E472" t="s">
         <v>57</v>
@@ -15643,24 +15670,24 @@
         <v>58</v>
       </c>
       <c r="G472" s="1">
-        <v>46227</v>
+        <v>46161</v>
       </c>
       <c r="H472" s="1">
-        <v>46252</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B473" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C473">
         <v>1</v>
       </c>
       <c r="D473" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E473" t="s">
         <v>57</v>
@@ -15669,24 +15696,24 @@
         <v>58</v>
       </c>
       <c r="G473" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="H473" s="1">
-        <v>46252</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B474" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C474">
         <v>1</v>
       </c>
       <c r="D474" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E474" t="s">
         <v>57</v>
@@ -15695,18 +15722,18 @@
         <v>58</v>
       </c>
       <c r="G474" s="1">
-        <v>46227</v>
+        <v>46174</v>
       </c>
       <c r="H474" s="1">
-        <v>46228</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B475" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="C475">
         <v>1</v>
@@ -15715,13 +15742,13 @@
         <v>6</v>
       </c>
       <c r="E475" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F475" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G475" s="1">
-        <v>46230</v>
+        <v>46195</v>
       </c>
       <c r="H475" s="1">
         <v>46252</v>
@@ -15729,10 +15756,10 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B476" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="C476">
         <v>1</v>
@@ -15747,24 +15774,24 @@
         <v>58</v>
       </c>
       <c r="G476" s="1">
-        <v>46231</v>
+        <v>46210</v>
       </c>
       <c r="H476" s="1">
-        <v>46231</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B477" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="C477">
         <v>1</v>
       </c>
       <c r="D477" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E477" t="s">
         <v>57</v>
@@ -15773,24 +15800,24 @@
         <v>58</v>
       </c>
       <c r="G477" s="1">
-        <v>46254</v>
+        <v>46213</v>
       </c>
       <c r="H477" s="1">
-        <v>46254</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B478" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C478">
         <v>1</v>
       </c>
       <c r="D478" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E478" t="s">
         <v>57</v>
@@ -15799,18 +15826,18 @@
         <v>58</v>
       </c>
       <c r="G478" s="1">
-        <v>46255</v>
+        <v>46218</v>
       </c>
       <c r="H478" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B479" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C479">
         <v>1</v>
@@ -15819,30 +15846,30 @@
         <v>6</v>
       </c>
       <c r="E479" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F479" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G479" s="1">
-        <v>46260</v>
+        <v>46226</v>
       </c>
       <c r="H479" s="1">
-        <v>46260</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B480" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="C480">
         <v>1</v>
       </c>
       <c r="D480" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="E480" t="s">
         <v>57</v>
@@ -15851,18 +15878,18 @@
         <v>58</v>
       </c>
       <c r="G480" s="1">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="H480" s="1">
-        <v>46289</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B481" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="C481">
         <v>1</v>
@@ -15877,24 +15904,24 @@
         <v>58</v>
       </c>
       <c r="G481" s="1">
-        <v>46294</v>
+        <v>46227</v>
       </c>
       <c r="H481" s="1">
-        <v>46294</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B482" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="C482">
         <v>1</v>
       </c>
       <c r="D482" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E482" t="s">
         <v>57</v>
@@ -15903,50 +15930,50 @@
         <v>58</v>
       </c>
       <c r="G482" s="1">
-        <v>46302</v>
+        <v>46227</v>
       </c>
       <c r="H482" s="1">
-        <v>46302</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B483" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C483">
         <v>1</v>
       </c>
       <c r="D483" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E483" t="s">
-        <v>605</v>
+        <v>77</v>
       </c>
       <c r="F483" t="s">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="G483" s="1">
-        <v>46302</v>
+        <v>46230</v>
       </c>
       <c r="H483" s="1">
-        <v>46302</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B484" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="C484">
         <v>1</v>
       </c>
       <c r="D484" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E484" t="s">
         <v>57</v>
@@ -15955,24 +15982,24 @@
         <v>58</v>
       </c>
       <c r="G484" s="1">
-        <v>46302</v>
+        <v>46231</v>
       </c>
       <c r="H484" s="1">
-        <v>46302</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B485" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C485">
         <v>1</v>
       </c>
       <c r="D485" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E485" t="s">
         <v>57</v>
@@ -15981,24 +16008,24 @@
         <v>58</v>
       </c>
       <c r="G485" s="1">
-        <v>46302</v>
+        <v>46254</v>
       </c>
       <c r="H485" s="1">
-        <v>46302</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B486" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="C486">
         <v>1</v>
       </c>
       <c r="D486" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E486" t="s">
         <v>57</v>
@@ -16007,24 +16034,24 @@
         <v>58</v>
       </c>
       <c r="G486" s="1">
-        <v>46302</v>
+        <v>46255</v>
       </c>
       <c r="H486" s="1">
-        <v>46302</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B487" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C487">
         <v>1</v>
       </c>
       <c r="D487" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E487" t="s">
         <v>57</v>
@@ -16033,96 +16060,96 @@
         <v>58</v>
       </c>
       <c r="G487" s="1">
-        <v>46302</v>
+        <v>46260</v>
       </c>
       <c r="H487" s="1">
-        <v>46302</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="B488" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="C488">
         <v>1</v>
       </c>
       <c r="D488" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
-        <v>944</v>
+        <v>57</v>
       </c>
       <c r="F488" t="s">
-        <v>945</v>
+        <v>58</v>
       </c>
       <c r="G488" s="1">
-        <v>46157</v>
+        <v>46289</v>
       </c>
       <c r="H488" s="1">
-        <v>46157</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="B489" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C489">
         <v>1</v>
       </c>
       <c r="D489" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E489" t="s">
-        <v>947</v>
+        <v>57</v>
       </c>
       <c r="F489" t="s">
-        <v>948</v>
+        <v>58</v>
       </c>
       <c r="G489" s="1">
-        <v>46168</v>
+        <v>46294</v>
       </c>
       <c r="H489" s="1">
-        <v>46170</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="B490" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C490">
         <v>1</v>
       </c>
       <c r="D490" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E490" t="s">
-        <v>944</v>
+        <v>605</v>
       </c>
       <c r="F490" t="s">
-        <v>945</v>
+        <v>606</v>
       </c>
       <c r="G490" s="1">
-        <v>46218</v>
+        <v>46302</v>
       </c>
       <c r="H490" s="1">
-        <v>46218</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B491" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C491">
         <v>1</v>
@@ -16131,24 +16158,24 @@
         <v>2</v>
       </c>
       <c r="E491" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="F491" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="G491" s="1">
-        <v>46244</v>
+        <v>46157</v>
       </c>
       <c r="H491" s="1">
-        <v>46244</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B492" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C492">
         <v>1</v>
@@ -16157,24 +16184,24 @@
         <v>2</v>
       </c>
       <c r="E492" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="F492" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="G492" s="1">
-        <v>46247</v>
+        <v>46168</v>
       </c>
       <c r="H492" s="1">
-        <v>46247</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B493" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="C493">
         <v>1</v>
@@ -16189,18 +16216,18 @@
         <v>954</v>
       </c>
       <c r="G493" s="1">
-        <v>46247</v>
+        <v>46218</v>
       </c>
       <c r="H493" s="1">
-        <v>46247</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B494" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C494">
         <v>1</v>
@@ -16209,24 +16236,24 @@
         <v>2</v>
       </c>
       <c r="E494" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="F494" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="G494" s="1">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="H494" s="1">
-        <v>46255</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B495" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C495">
         <v>1</v>
@@ -16235,24 +16262,24 @@
         <v>2</v>
       </c>
       <c r="E495" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="F495" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="G495" s="1">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="H495" s="1">
-        <v>46258</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B496" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C496">
         <v>1</v>
@@ -16261,67 +16288,145 @@
         <v>2</v>
       </c>
       <c r="E496" t="s">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="F496" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="G496" s="1">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="H496" s="1">
-        <v>46265</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B497" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C497">
         <v>1</v>
       </c>
       <c r="D497" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E497" t="s">
-        <v>13</v>
+        <v>953</v>
       </c>
       <c r="F497" t="s">
-        <v>14</v>
+        <v>954</v>
       </c>
       <c r="G497" s="1">
-        <v>46281</v>
+        <v>46255</v>
       </c>
       <c r="H497" s="1">
-        <v>46283</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B498" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C498">
         <v>1</v>
       </c>
       <c r="D498" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E498" t="s">
-        <v>886</v>
+        <v>953</v>
       </c>
       <c r="F498" t="s">
-        <v>887</v>
+        <v>954</v>
       </c>
       <c r="G498" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H498" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A499" t="s">
+        <v>951</v>
+      </c>
+      <c r="B499" t="s">
+        <v>966</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+      <c r="D499" t="s">
+        <v>2</v>
+      </c>
+      <c r="E499" t="s">
+        <v>953</v>
+      </c>
+      <c r="F499" t="s">
+        <v>954</v>
+      </c>
+      <c r="G499" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H499" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A500" t="s">
+        <v>951</v>
+      </c>
+      <c r="B500" t="s">
+        <v>967</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500" t="s">
+        <v>6</v>
+      </c>
+      <c r="E500" t="s">
+        <v>13</v>
+      </c>
+      <c r="F500" t="s">
+        <v>14</v>
+      </c>
+      <c r="G500" s="1">
+        <v>46281</v>
+      </c>
+      <c r="H500" s="1">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A501" t="s">
+        <v>951</v>
+      </c>
+      <c r="B501" t="s">
+        <v>968</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+      <c r="D501" t="s">
+        <v>154</v>
+      </c>
+      <c r="E501" t="s">
+        <v>902</v>
+      </c>
+      <c r="F501" t="s">
+        <v>903</v>
+      </c>
+      <c r="G501" s="1">
         <v>46302</v>
       </c>
-      <c r="H498" s="1">
+      <c r="H501" s="1">
         <v>46302</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34584D4-9E3C-4FC2-B120-7E3DCEDFBC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DC9170-D960-4FD1-A5F4-916C1245B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{FA1481A3-4DDB-4BF8-BAAD-4745EBBB8662}"/>
+    <workbookView xWindow="30930" yWindow="10005" windowWidth="15000" windowHeight="6195" xr2:uid="{3D98A2EE-4257-4163-A192-6D22BD1A53C6}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="920">
   <si>
     <t>0001</t>
   </si>
@@ -790,9 +790,6 @@
     <t>EL MUNDO DEL PLOMERO S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  216073</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216095</t>
   </si>
   <si>
@@ -904,15 +901,6 @@
     <t>AURUX S. A. S.</t>
   </si>
   <si>
-    <t xml:space="preserve">  216537</t>
-  </si>
-  <si>
-    <t>HO05</t>
-  </si>
-  <si>
-    <t>HOLCIM (ARGENTINA) S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216555</t>
   </si>
   <si>
@@ -1516,6 +1504,15 @@
     <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
   </si>
   <si>
+    <t xml:space="preserve">  217016</t>
+  </si>
+  <si>
+    <t>RA22</t>
+  </si>
+  <si>
+    <t>RENUS ALFREDO R. -HERRAJES ARENALES</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217022</t>
   </si>
   <si>
@@ -1531,9 +1528,6 @@
     <t xml:space="preserve">  217032</t>
   </si>
   <si>
-    <t xml:space="preserve">  217037</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217039</t>
   </si>
   <si>
@@ -1783,15 +1777,6 @@
     <t>SONZINI LEONARDO S. -PROTER</t>
   </si>
   <si>
-    <t xml:space="preserve">  217108</t>
-  </si>
-  <si>
-    <t>TS11</t>
-  </si>
-  <si>
-    <t>TODO SANITARIOS Y GAS S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217110</t>
   </si>
   <si>
@@ -1816,9 +1801,6 @@
     <t xml:space="preserve">  217113</t>
   </si>
   <si>
-    <t xml:space="preserve">  217114</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217115</t>
   </si>
   <si>
@@ -1831,15 +1813,6 @@
     <t>CHEN CHING MEI- SANITARIOS DANIEL</t>
   </si>
   <si>
-    <t xml:space="preserve">  217119</t>
-  </si>
-  <si>
-    <t>BH09</t>
-  </si>
-  <si>
-    <t>BONOMI HERNAN ALBERTO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217120</t>
   </si>
   <si>
@@ -1993,15 +1966,6 @@
     <t>ANSBOR S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217155</t>
-  </si>
-  <si>
-    <t>CO42</t>
-  </si>
-  <si>
-    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217156</t>
   </si>
   <si>
@@ -2038,15 +2002,6 @@
     <t>VILANOVA DE MEIA S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217165</t>
-  </si>
-  <si>
-    <t>EC18</t>
-  </si>
-  <si>
-    <t>ECLECTICA BOIA -SOC. POR ACCIONES SIMPLIFICADA</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217166</t>
   </si>
   <si>
@@ -2119,9 +2074,6 @@
     <t xml:space="preserve">  217184</t>
   </si>
   <si>
-    <t xml:space="preserve">  217185</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217187</t>
   </si>
   <si>
@@ -2404,6 +2356,129 @@
     <t>SANITARIOS MATRECARI S.A.</t>
   </si>
   <si>
+    <t xml:space="preserve">  217244</t>
+  </si>
+  <si>
+    <t>AN17</t>
+  </si>
+  <si>
+    <t>ANGLER S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217245</t>
+  </si>
+  <si>
+    <t>NP01</t>
+  </si>
+  <si>
+    <t>NATALI PLASTICOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217247</t>
+  </si>
+  <si>
+    <t>BA26</t>
+  </si>
+  <si>
+    <t>BOCHATAY ANDREA VIVIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217254</t>
+  </si>
+  <si>
+    <t>BR02</t>
+  </si>
+  <si>
+    <t>BRITAM S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217262</t>
+  </si>
+  <si>
+    <t>PO01</t>
+  </si>
+  <si>
+    <t>PORAL S.A.C.I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217266</t>
+  </si>
+  <si>
+    <t>MM44</t>
+  </si>
+  <si>
+    <t>MOTTESI MATERIALES SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217267</t>
+  </si>
+  <si>
+    <t>SA66</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAÑUELAS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217269</t>
+  </si>
+  <si>
+    <t>FE15</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217272</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2540,6 +2615,9 @@
   </si>
   <si>
     <t xml:space="preserve">    3020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3022</t>
   </si>
   <si>
     <t>4444</t>
@@ -3151,34 +3229,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F674F9-E5B9-48FA-96FD-0958ED099C7F}">
-  <dimension ref="A1:H456"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86863E6-C860-4171-AB95-268CB016BB65}">
+  <dimension ref="A1:H474"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>886</v>
+        <v>912</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>887</v>
+        <v>913</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>893</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5867,22 +5945,22 @@
         <v>256</v>
       </c>
       <c r="C105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>221</v>
       </c>
       <c r="F105" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="G105" s="1">
         <v>46286</v>
       </c>
       <c r="H105" s="1">
-        <v>46302</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -5896,19 +5974,19 @@
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E106" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="F106" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="G106" s="1">
         <v>46286</v>
       </c>
       <c r="H106" s="1">
-        <v>46290</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -5916,25 +5994,25 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F107" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G107" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H107" s="1">
-        <v>46303</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -5942,25 +6020,25 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E108" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F108" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G108" s="1">
         <v>46287</v>
       </c>
       <c r="H108" s="1">
-        <v>46287</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -5968,25 +6046,25 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E109" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F109" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G109" s="1">
         <v>46287</v>
       </c>
       <c r="H109" s="1">
-        <v>46300</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -5994,25 +6072,25 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F110" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G110" s="1">
         <v>46287</v>
       </c>
       <c r="H110" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -6020,25 +6098,25 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E111" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F111" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G111" s="1">
         <v>46287</v>
       </c>
       <c r="H111" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -6046,25 +6124,25 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G112" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H112" s="1">
-        <v>46288</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -6072,25 +6150,25 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="s">
         <v>2</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G113" s="1">
         <v>46288</v>
       </c>
       <c r="H113" s="1">
-        <v>46295</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -6098,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -6107,10 +6185,10 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F114" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G114" s="1">
         <v>46288</v>
@@ -6124,25 +6202,25 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
-        <v>283</v>
+        <v>97</v>
       </c>
       <c r="F115" t="s">
-        <v>284</v>
+        <v>98</v>
       </c>
       <c r="G115" s="1">
         <v>46288</v>
       </c>
       <c r="H115" s="1">
-        <v>46288</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -6153,22 +6231,22 @@
         <v>285</v>
       </c>
       <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
         <v>2</v>
       </c>
-      <c r="D116" t="s">
-        <v>6</v>
-      </c>
       <c r="E116" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="F116" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="G116" s="1">
         <v>46288</v>
       </c>
       <c r="H116" s="1">
-        <v>46302</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -6179,22 +6257,22 @@
         <v>286</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" t="s">
         <v>2</v>
       </c>
       <c r="E117" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="F117" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="G117" s="1">
         <v>46288</v>
       </c>
       <c r="H117" s="1">
-        <v>46289</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -6205,22 +6283,22 @@
         <v>287</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D118" t="s">
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>92</v>
+        <v>288</v>
       </c>
       <c r="F118" t="s">
-        <v>93</v>
+        <v>289</v>
       </c>
       <c r="G118" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H118" s="1">
-        <v>46303</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -6228,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -6237,13 +6315,13 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F119" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G119" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H119" s="1">
         <v>46290</v>
@@ -6254,25 +6332,25 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E120" t="s">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="F120" t="s">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="G120" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H120" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -6295,10 +6373,10 @@
         <v>296</v>
       </c>
       <c r="G121" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H121" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -6312,19 +6390,19 @@
         <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E122" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F122" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G122" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H122" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -6341,16 +6419,16 @@
         <v>2</v>
       </c>
       <c r="E123" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c r="F123" t="s">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="G123" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H123" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -6358,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -6367,10 +6445,10 @@
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="F124" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="G124" s="1">
         <v>46294</v>
@@ -6393,10 +6471,10 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>142</v>
+        <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="G125" s="1">
         <v>46294</v>
@@ -6413,22 +6491,22 @@
         <v>303</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="F126" t="s">
-        <v>305</v>
+        <v>242</v>
       </c>
       <c r="G126" s="1">
         <v>46294</v>
       </c>
       <c r="H126" s="1">
-        <v>46294</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -6436,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -6445,10 +6523,10 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="F127" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="G127" s="1">
         <v>46294</v>
@@ -6462,25 +6540,25 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c r="F128" t="s">
-        <v>242</v>
+        <v>307</v>
       </c>
       <c r="G128" s="1">
         <v>46294</v>
       </c>
       <c r="H128" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -6497,16 +6575,16 @@
         <v>2</v>
       </c>
       <c r="E129" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="F129" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="G129" s="1">
         <v>46294</v>
       </c>
       <c r="H129" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -6514,25 +6592,25 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="s">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c r="F130" t="s">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="G130" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H130" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -6549,13 +6627,13 @@
         <v>2</v>
       </c>
       <c r="E131" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="F131" t="s">
-        <v>314</v>
+        <v>38</v>
       </c>
       <c r="G131" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H131" s="1">
         <v>46295</v>
@@ -6566,25 +6644,25 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E132" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F132" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G132" s="1">
         <v>46295</v>
       </c>
       <c r="H132" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -6592,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -6601,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="F133" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="G133" s="1">
         <v>46295</v>
@@ -6618,25 +6696,25 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
+        <v>315</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>316</v>
+      </c>
+      <c r="F134" t="s">
         <v>317</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>170</v>
-      </c>
-      <c r="E134" t="s">
-        <v>31</v>
-      </c>
-      <c r="F134" t="s">
-        <v>32</v>
       </c>
       <c r="G134" s="1">
         <v>46295</v>
       </c>
       <c r="H134" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -6650,13 +6728,13 @@
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E135" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="F135" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="G135" s="1">
         <v>46295</v>
@@ -6676,19 +6754,19 @@
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E136" t="s">
-        <v>320</v>
+        <v>37</v>
       </c>
       <c r="F136" t="s">
-        <v>321</v>
+        <v>38</v>
       </c>
       <c r="G136" s="1">
         <v>46295</v>
       </c>
       <c r="H136" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -6696,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -6722,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -6748,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -6774,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -6800,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -6826,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -6852,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -6878,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6904,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -6930,10 +7008,10 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="s">
         <v>170</v>
@@ -6948,7 +7026,7 @@
         <v>46295</v>
       </c>
       <c r="H146" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -6956,25 +7034,25 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
+        <v>330</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>6</v>
+      </c>
+      <c r="E147" t="s">
+        <v>331</v>
+      </c>
+      <c r="F147" t="s">
         <v>332</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>170</v>
-      </c>
-      <c r="E147" t="s">
-        <v>37</v>
-      </c>
-      <c r="F147" t="s">
-        <v>38</v>
       </c>
       <c r="G147" s="1">
         <v>46295</v>
       </c>
       <c r="H147" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -6985,22 +7063,22 @@
         <v>333</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
         <v>170</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>334</v>
       </c>
       <c r="F148" t="s">
-        <v>38</v>
+        <v>335</v>
       </c>
       <c r="G148" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H148" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -7008,22 +7086,22 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>335</v>
+        <v>37</v>
       </c>
       <c r="F149" t="s">
-        <v>336</v>
+        <v>38</v>
       </c>
       <c r="G149" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H149" s="1">
         <v>46296</v>
@@ -7063,22 +7141,22 @@
         <v>340</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E151" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
       <c r="F151" t="s">
-        <v>38</v>
+        <v>342</v>
       </c>
       <c r="G151" s="1">
         <v>46296</v>
       </c>
       <c r="H151" s="1">
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -7086,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7095,10 +7173,10 @@
         <v>170</v>
       </c>
       <c r="E152" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c r="F152" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="G152" s="1">
         <v>46296</v>
@@ -7115,22 +7193,22 @@
         <v>344</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="s">
         <v>170</v>
       </c>
       <c r="E153" t="s">
-        <v>345</v>
+        <v>37</v>
       </c>
       <c r="F153" t="s">
-        <v>346</v>
+        <v>38</v>
       </c>
       <c r="G153" s="1">
         <v>46296</v>
       </c>
       <c r="H153" s="1">
-        <v>46303</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -7138,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7156,7 +7234,7 @@
         <v>46296</v>
       </c>
       <c r="H154" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -7164,19 +7242,19 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
+        <v>346</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>170</v>
+      </c>
+      <c r="E155" t="s">
+        <v>347</v>
+      </c>
+      <c r="F155" t="s">
         <v>348</v>
-      </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155" t="s">
-        <v>170</v>
-      </c>
-      <c r="E155" t="s">
-        <v>37</v>
-      </c>
-      <c r="F155" t="s">
-        <v>38</v>
       </c>
       <c r="G155" s="1">
         <v>46296</v>
@@ -7196,19 +7274,19 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="F156" t="s">
-        <v>38</v>
+        <v>351</v>
       </c>
       <c r="G156" s="1">
         <v>46296</v>
       </c>
       <c r="H156" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -7216,19 +7294,19 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F157" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G157" s="1">
         <v>46296</v>
@@ -7242,19 +7320,19 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E158" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F158" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G158" s="1">
         <v>46296</v>
@@ -7268,19 +7346,19 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
+        <v>358</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159" t="s">
+        <v>170</v>
+      </c>
+      <c r="E159" t="s">
         <v>356</v>
       </c>
-      <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="D159" t="s">
-        <v>6</v>
-      </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>357</v>
-      </c>
-      <c r="F159" t="s">
-        <v>358</v>
       </c>
       <c r="G159" s="1">
         <v>46296</v>
@@ -7303,16 +7381,16 @@
         <v>170</v>
       </c>
       <c r="E160" t="s">
-        <v>360</v>
+        <v>145</v>
       </c>
       <c r="F160" t="s">
-        <v>361</v>
+        <v>146</v>
       </c>
       <c r="G160" s="1">
         <v>46296</v>
       </c>
       <c r="H160" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -7320,25 +7398,25 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>360</v>
+        <v>37</v>
       </c>
       <c r="F161" t="s">
-        <v>361</v>
+        <v>38</v>
       </c>
       <c r="G161" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H161" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -7346,22 +7424,22 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F162" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G162" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H162" s="1">
         <v>46297</v>
@@ -7372,19 +7450,19 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
+        <v>362</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>170</v>
+      </c>
+      <c r="E163" t="s">
+        <v>363</v>
+      </c>
+      <c r="F163" t="s">
         <v>364</v>
-      </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-      <c r="D163" t="s">
-        <v>170</v>
-      </c>
-      <c r="E163" t="s">
-        <v>37</v>
-      </c>
-      <c r="F163" t="s">
-        <v>38</v>
       </c>
       <c r="G163" s="1">
         <v>46297</v>
@@ -7404,13 +7482,13 @@
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E164" t="s">
-        <v>142</v>
+        <v>366</v>
       </c>
       <c r="F164" t="s">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="G164" s="1">
         <v>46297</v>
@@ -7424,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7433,10 +7511,10 @@
         <v>170</v>
       </c>
       <c r="E165" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F165" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G165" s="1">
         <v>46297</v>
@@ -7450,19 +7528,19 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>370</v>
+        <v>172</v>
       </c>
       <c r="F166" t="s">
-        <v>371</v>
+        <v>173</v>
       </c>
       <c r="G166" s="1">
         <v>46297</v>
@@ -7508,13 +7586,13 @@
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E168" t="s">
-        <v>172</v>
+        <v>376</v>
       </c>
       <c r="F168" t="s">
-        <v>173</v>
+        <v>377</v>
       </c>
       <c r="G168" s="1">
         <v>46297</v>
@@ -7528,19 +7606,19 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C169">
         <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E169" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F169" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G169" s="1">
         <v>46297</v>
@@ -7554,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7563,10 +7641,10 @@
         <v>170</v>
       </c>
       <c r="E170" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F170" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G170" s="1">
         <v>46297</v>
@@ -7586,13 +7664,13 @@
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>383</v>
+        <v>37</v>
       </c>
       <c r="F171" t="s">
-        <v>384</v>
+        <v>38</v>
       </c>
       <c r="G171" s="1">
         <v>46297</v>
@@ -7606,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7615,10 +7693,10 @@
         <v>170</v>
       </c>
       <c r="E172" t="s">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="F172" t="s">
-        <v>381</v>
+        <v>38</v>
       </c>
       <c r="G172" s="1">
         <v>46297</v>
@@ -7632,13 +7710,13 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E173" t="s">
         <v>37</v>
@@ -7658,7 +7736,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7684,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7710,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7736,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7762,19 +7840,19 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
+        <v>389</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>170</v>
+      </c>
+      <c r="E178" t="s">
+        <v>390</v>
+      </c>
+      <c r="F178" t="s">
         <v>391</v>
-      </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-      <c r="D178" t="s">
-        <v>170</v>
-      </c>
-      <c r="E178" t="s">
-        <v>37</v>
-      </c>
-      <c r="F178" t="s">
-        <v>38</v>
       </c>
       <c r="G178" s="1">
         <v>46297</v>
@@ -7797,16 +7875,16 @@
         <v>170</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="F179" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="G179" s="1">
         <v>46297</v>
       </c>
       <c r="H179" s="1">
-        <v>46297</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -7849,16 +7927,16 @@
         <v>170</v>
       </c>
       <c r="E181" t="s">
-        <v>230</v>
+        <v>397</v>
       </c>
       <c r="F181" t="s">
-        <v>231</v>
+        <v>398</v>
       </c>
       <c r="G181" s="1">
         <v>46297</v>
       </c>
       <c r="H181" s="1">
-        <v>46302</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -7866,25 +7944,25 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F182" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G182" s="1">
         <v>46297</v>
       </c>
       <c r="H182" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -7892,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7901,16 +7979,16 @@
         <v>170</v>
       </c>
       <c r="E183" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F183" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G183" s="1">
         <v>46297</v>
       </c>
       <c r="H183" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -7918,19 +7996,19 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E184" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F184" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G184" s="1">
         <v>46297</v>
@@ -7944,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -7953,13 +8031,13 @@
         <v>170</v>
       </c>
       <c r="E185" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F185" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G185" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H185" s="1">
         <v>46300</v>
@@ -7970,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -7979,13 +8057,13 @@
         <v>170</v>
       </c>
       <c r="E186" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="F186" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="G186" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H186" s="1">
         <v>46300</v>
@@ -8031,10 +8109,10 @@
         <v>170</v>
       </c>
       <c r="E188" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="F188" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="G188" s="1">
         <v>46300</v>
@@ -8048,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -8057,10 +8135,10 @@
         <v>170</v>
       </c>
       <c r="E189" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F189" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G189" s="1">
         <v>46300</v>
@@ -8074,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -8083,10 +8161,10 @@
         <v>170</v>
       </c>
       <c r="E190" t="s">
-        <v>420</v>
+        <v>234</v>
       </c>
       <c r="F190" t="s">
-        <v>421</v>
+        <v>235</v>
       </c>
       <c r="G190" s="1">
         <v>46300</v>
@@ -8135,10 +8213,10 @@
         <v>170</v>
       </c>
       <c r="E192" t="s">
-        <v>234</v>
+        <v>423</v>
       </c>
       <c r="F192" t="s">
-        <v>235</v>
+        <v>424</v>
       </c>
       <c r="G192" s="1">
         <v>46300</v>
@@ -8161,10 +8239,10 @@
         <v>170</v>
       </c>
       <c r="E193" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F193" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G193" s="1">
         <v>46300</v>
@@ -8178,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -8187,10 +8265,10 @@
         <v>170</v>
       </c>
       <c r="E194" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F194" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G194" s="1">
         <v>46300</v>
@@ -8204,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -8213,10 +8291,10 @@
         <v>170</v>
       </c>
       <c r="E195" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F195" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G195" s="1">
         <v>46300</v>
@@ -8230,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -8239,10 +8317,10 @@
         <v>170</v>
       </c>
       <c r="E196" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F196" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G196" s="1">
         <v>46300</v>
@@ -8256,19 +8334,19 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
+        <v>430</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
+        <v>170</v>
+      </c>
+      <c r="E197" t="s">
+        <v>431</v>
+      </c>
+      <c r="F197" t="s">
         <v>432</v>
-      </c>
-      <c r="C197">
-        <v>1</v>
-      </c>
-      <c r="D197" t="s">
-        <v>170</v>
-      </c>
-      <c r="E197" t="s">
-        <v>427</v>
-      </c>
-      <c r="F197" t="s">
-        <v>428</v>
       </c>
       <c r="G197" s="1">
         <v>46300</v>
@@ -8291,10 +8369,10 @@
         <v>170</v>
       </c>
       <c r="E198" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F198" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G198" s="1">
         <v>46300</v>
@@ -8343,10 +8421,10 @@
         <v>170</v>
       </c>
       <c r="E200" t="s">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="F200" t="s">
-        <v>428</v>
+        <v>205</v>
       </c>
       <c r="G200" s="1">
         <v>46300</v>
@@ -8392,13 +8470,13 @@
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="F202" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="G202" s="1">
         <v>46300</v>
@@ -8421,10 +8499,10 @@
         <v>170</v>
       </c>
       <c r="E203" t="s">
-        <v>443</v>
+        <v>288</v>
       </c>
       <c r="F203" t="s">
-        <v>444</v>
+        <v>289</v>
       </c>
       <c r="G203" s="1">
         <v>46300</v>
@@ -8438,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -8447,10 +8525,10 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="F204" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="G204" s="1">
         <v>46300</v>
@@ -8464,19 +8542,19 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
+        <v>444</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205" t="s">
+        <v>170</v>
+      </c>
+      <c r="E205" t="s">
+        <v>445</v>
+      </c>
+      <c r="F205" t="s">
         <v>446</v>
-      </c>
-      <c r="C205">
-        <v>1</v>
-      </c>
-      <c r="D205" t="s">
-        <v>170</v>
-      </c>
-      <c r="E205" t="s">
-        <v>289</v>
-      </c>
-      <c r="F205" t="s">
-        <v>290</v>
       </c>
       <c r="G205" s="1">
         <v>46300</v>
@@ -8496,13 +8574,13 @@
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E206" t="s">
-        <v>25</v>
+        <v>448</v>
       </c>
       <c r="F206" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
       <c r="G206" s="1">
         <v>46300</v>
@@ -8516,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -8525,10 +8603,10 @@
         <v>170</v>
       </c>
       <c r="E207" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F207" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G207" s="1">
         <v>46300</v>
@@ -8551,10 +8629,10 @@
         <v>170</v>
       </c>
       <c r="E208" t="s">
-        <v>452</v>
+        <v>234</v>
       </c>
       <c r="F208" t="s">
-        <v>453</v>
+        <v>235</v>
       </c>
       <c r="G208" s="1">
         <v>46300</v>
@@ -8568,19 +8646,19 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
+        <v>452</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>170</v>
+      </c>
+      <c r="E209" t="s">
+        <v>453</v>
+      </c>
+      <c r="F209" t="s">
         <v>454</v>
-      </c>
-      <c r="C209">
-        <v>1</v>
-      </c>
-      <c r="D209" t="s">
-        <v>170</v>
-      </c>
-      <c r="E209" t="s">
-        <v>449</v>
-      </c>
-      <c r="F209" t="s">
-        <v>450</v>
       </c>
       <c r="G209" s="1">
         <v>46300</v>
@@ -8603,10 +8681,10 @@
         <v>170</v>
       </c>
       <c r="E210" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="F210" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="G210" s="1">
         <v>46300</v>
@@ -8629,10 +8707,10 @@
         <v>170</v>
       </c>
       <c r="E211" t="s">
-        <v>457</v>
+        <v>331</v>
       </c>
       <c r="F211" t="s">
-        <v>458</v>
+        <v>332</v>
       </c>
       <c r="G211" s="1">
         <v>46300</v>
@@ -8646,19 +8724,19 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
+        <v>457</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="s">
+        <v>170</v>
+      </c>
+      <c r="E212" t="s">
+        <v>458</v>
+      </c>
+      <c r="F212" t="s">
         <v>459</v>
-      </c>
-      <c r="C212">
-        <v>1</v>
-      </c>
-      <c r="D212" t="s">
-        <v>170</v>
-      </c>
-      <c r="E212" t="s">
-        <v>335</v>
-      </c>
-      <c r="F212" t="s">
-        <v>336</v>
       </c>
       <c r="G212" s="1">
         <v>46300</v>
@@ -8681,10 +8759,10 @@
         <v>170</v>
       </c>
       <c r="E213" t="s">
-        <v>335</v>
+        <v>37</v>
       </c>
       <c r="F213" t="s">
-        <v>336</v>
+        <v>38</v>
       </c>
       <c r="G213" s="1">
         <v>46300</v>
@@ -8707,10 +8785,10 @@
         <v>170</v>
       </c>
       <c r="E214" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F214" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G214" s="1">
         <v>46300</v>
@@ -8724,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -8733,10 +8811,10 @@
         <v>170</v>
       </c>
       <c r="E215" t="s">
-        <v>37</v>
+        <v>431</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>432</v>
       </c>
       <c r="G215" s="1">
         <v>46300</v>
@@ -8750,19 +8828,19 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
+        <v>463</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="s">
+        <v>170</v>
+      </c>
+      <c r="E216" t="s">
+        <v>464</v>
+      </c>
+      <c r="F216" t="s">
         <v>465</v>
-      </c>
-      <c r="C216">
-        <v>1</v>
-      </c>
-      <c r="D216" t="s">
-        <v>170</v>
-      </c>
-      <c r="E216" t="s">
-        <v>462</v>
-      </c>
-      <c r="F216" t="s">
-        <v>463</v>
       </c>
       <c r="G216" s="1">
         <v>46300</v>
@@ -8785,10 +8863,10 @@
         <v>170</v>
       </c>
       <c r="E217" t="s">
-        <v>435</v>
+        <v>16</v>
       </c>
       <c r="F217" t="s">
-        <v>436</v>
+        <v>17</v>
       </c>
       <c r="G217" s="1">
         <v>46300</v>
@@ -8811,10 +8889,10 @@
         <v>170</v>
       </c>
       <c r="E218" t="s">
-        <v>468</v>
+        <v>350</v>
       </c>
       <c r="F218" t="s">
-        <v>469</v>
+        <v>351</v>
       </c>
       <c r="G218" s="1">
         <v>46300</v>
@@ -8828,19 +8906,19 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
+        <v>468</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219" t="s">
+        <v>170</v>
+      </c>
+      <c r="E219" t="s">
+        <v>469</v>
+      </c>
+      <c r="F219" t="s">
         <v>470</v>
-      </c>
-      <c r="C219">
-        <v>1</v>
-      </c>
-      <c r="D219" t="s">
-        <v>170</v>
-      </c>
-      <c r="E219" t="s">
-        <v>16</v>
-      </c>
-      <c r="F219" t="s">
-        <v>17</v>
       </c>
       <c r="G219" s="1">
         <v>46300</v>
@@ -8863,10 +8941,10 @@
         <v>170</v>
       </c>
       <c r="E220" t="s">
-        <v>354</v>
+        <v>472</v>
       </c>
       <c r="F220" t="s">
-        <v>355</v>
+        <v>473</v>
       </c>
       <c r="G220" s="1">
         <v>46300</v>
@@ -8880,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8889,10 +8967,10 @@
         <v>170</v>
       </c>
       <c r="E221" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F221" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G221" s="1">
         <v>46300</v>
@@ -8906,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -8915,10 +8993,10 @@
         <v>170</v>
       </c>
       <c r="E222" t="s">
-        <v>476</v>
+        <v>373</v>
       </c>
       <c r="F222" t="s">
-        <v>477</v>
+        <v>374</v>
       </c>
       <c r="G222" s="1">
         <v>46300</v>
@@ -8941,10 +9019,10 @@
         <v>170</v>
       </c>
       <c r="E223" t="s">
-        <v>479</v>
+        <v>151</v>
       </c>
       <c r="F223" t="s">
-        <v>480</v>
+        <v>152</v>
       </c>
       <c r="G223" s="1">
         <v>46300</v>
@@ -8958,19 +9036,19 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
+        <v>479</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
+        <v>170</v>
+      </c>
+      <c r="E224" t="s">
+        <v>480</v>
+      </c>
+      <c r="F224" t="s">
         <v>481</v>
-      </c>
-      <c r="C224">
-        <v>1</v>
-      </c>
-      <c r="D224" t="s">
-        <v>170</v>
-      </c>
-      <c r="E224" t="s">
-        <v>377</v>
-      </c>
-      <c r="F224" t="s">
-        <v>378</v>
       </c>
       <c r="G224" s="1">
         <v>46300</v>
@@ -8990,13 +9068,13 @@
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>151</v>
+        <v>483</v>
       </c>
       <c r="F225" t="s">
-        <v>152</v>
+        <v>484</v>
       </c>
       <c r="G225" s="1">
         <v>46300</v>
@@ -9010,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -9019,10 +9097,10 @@
         <v>170</v>
       </c>
       <c r="E226" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F226" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G226" s="1">
         <v>46300</v>
@@ -9036,25 +9114,25 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E227" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F227" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G227" s="1">
         <v>46300</v>
       </c>
       <c r="H227" s="1">
-        <v>46300</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -9062,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -9071,10 +9149,10 @@
         <v>170</v>
       </c>
       <c r="E228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G228" s="1">
         <v>46300</v>
@@ -9088,19 +9166,19 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D229" t="s">
         <v>170</v>
       </c>
       <c r="E229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F229" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G229" s="1">
         <v>46300</v>
@@ -9114,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -9123,10 +9201,10 @@
         <v>170</v>
       </c>
       <c r="E230" t="s">
-        <v>496</v>
+        <v>16</v>
       </c>
       <c r="F230" t="s">
-        <v>497</v>
+        <v>17</v>
       </c>
       <c r="G230" s="1">
         <v>46300</v>
@@ -9149,16 +9227,16 @@
         <v>170</v>
       </c>
       <c r="E231" t="s">
-        <v>16</v>
+        <v>499</v>
       </c>
       <c r="F231" t="s">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="G231" s="1">
         <v>46300</v>
       </c>
       <c r="H231" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
@@ -9166,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -9175,13 +9253,13 @@
         <v>170</v>
       </c>
       <c r="E232" t="s">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="F232" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G232" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H232" s="1">
         <v>46301</v>
@@ -9198,13 +9276,13 @@
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>22</v>
+        <v>503</v>
       </c>
       <c r="F233" t="s">
-        <v>23</v>
+        <v>504</v>
       </c>
       <c r="G233" s="1">
         <v>46301</v>
@@ -9218,19 +9296,19 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E234" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F234" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G234" s="1">
         <v>46301</v>
@@ -9244,7 +9322,7 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9253,10 +9331,10 @@
         <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>505</v>
+        <v>86</v>
       </c>
       <c r="F235" t="s">
-        <v>506</v>
+        <v>87</v>
       </c>
       <c r="G235" s="1">
         <v>46301</v>
@@ -9276,7 +9354,7 @@
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E236" t="s">
         <v>86</v>
@@ -9302,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E237" t="s">
         <v>86</v>
@@ -9328,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E238" t="s">
         <v>86</v>
@@ -9380,7 +9458,7 @@
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E240" t="s">
         <v>86</v>
@@ -9409,10 +9487,10 @@
         <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>86</v>
+        <v>513</v>
       </c>
       <c r="F241" t="s">
-        <v>87</v>
+        <v>514</v>
       </c>
       <c r="G241" s="1">
         <v>46301</v>
@@ -9426,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9435,10 +9513,10 @@
         <v>170</v>
       </c>
       <c r="E242" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="F242" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G242" s="1">
         <v>46301</v>
@@ -9452,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9461,10 +9539,10 @@
         <v>170</v>
       </c>
       <c r="E243" t="s">
-        <v>515</v>
+        <v>37</v>
       </c>
       <c r="F243" t="s">
-        <v>516</v>
+        <v>38</v>
       </c>
       <c r="G243" s="1">
         <v>46301</v>
@@ -9510,7 +9588,7 @@
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E245" t="s">
         <v>37</v>
@@ -9562,7 +9640,7 @@
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E247" t="s">
         <v>37</v>
@@ -9591,10 +9669,10 @@
         <v>170</v>
       </c>
       <c r="E248" t="s">
-        <v>37</v>
+        <v>522</v>
       </c>
       <c r="F248" t="s">
-        <v>38</v>
+        <v>523</v>
       </c>
       <c r="G248" s="1">
         <v>46301</v>
@@ -9608,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9617,10 +9695,10 @@
         <v>170</v>
       </c>
       <c r="E249" t="s">
-        <v>37</v>
+        <v>525</v>
       </c>
       <c r="F249" t="s">
-        <v>38</v>
+        <v>526</v>
       </c>
       <c r="G249" s="1">
         <v>46301</v>
@@ -9634,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9643,10 +9721,10 @@
         <v>170</v>
       </c>
       <c r="E250" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F250" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G250" s="1">
         <v>46301</v>
@@ -9660,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9669,10 +9747,10 @@
         <v>170</v>
       </c>
       <c r="E251" t="s">
-        <v>527</v>
+        <v>16</v>
       </c>
       <c r="F251" t="s">
-        <v>528</v>
+        <v>17</v>
       </c>
       <c r="G251" s="1">
         <v>46301</v>
@@ -9686,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9695,10 +9773,10 @@
         <v>170</v>
       </c>
       <c r="E252" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F252" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G252" s="1">
         <v>46301</v>
@@ -9712,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9721,10 +9799,10 @@
         <v>170</v>
       </c>
       <c r="E253" t="s">
-        <v>16</v>
+        <v>379</v>
       </c>
       <c r="F253" t="s">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="G253" s="1">
         <v>46301</v>
@@ -9738,7 +9816,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9747,10 +9825,10 @@
         <v>170</v>
       </c>
       <c r="E254" t="s">
-        <v>534</v>
+        <v>366</v>
       </c>
       <c r="F254" t="s">
-        <v>535</v>
+        <v>367</v>
       </c>
       <c r="G254" s="1">
         <v>46301</v>
@@ -9773,10 +9851,10 @@
         <v>170</v>
       </c>
       <c r="E255" t="s">
-        <v>383</v>
+        <v>537</v>
       </c>
       <c r="F255" t="s">
-        <v>384</v>
+        <v>538</v>
       </c>
       <c r="G255" s="1">
         <v>46301</v>
@@ -9790,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9799,10 +9877,10 @@
         <v>170</v>
       </c>
       <c r="E256" t="s">
-        <v>370</v>
+        <v>540</v>
       </c>
       <c r="F256" t="s">
-        <v>371</v>
+        <v>541</v>
       </c>
       <c r="G256" s="1">
         <v>46301</v>
@@ -9816,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9825,10 +9903,10 @@
         <v>170</v>
       </c>
       <c r="E257" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F257" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G257" s="1">
         <v>46301</v>
@@ -9842,7 +9920,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9851,10 +9929,10 @@
         <v>170</v>
       </c>
       <c r="E258" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F258" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G258" s="1">
         <v>46301</v>
@@ -9868,7 +9946,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9877,10 +9955,10 @@
         <v>170</v>
       </c>
       <c r="E259" t="s">
-        <v>545</v>
+        <v>431</v>
       </c>
       <c r="F259" t="s">
-        <v>546</v>
+        <v>432</v>
       </c>
       <c r="G259" s="1">
         <v>46301</v>
@@ -9894,7 +9972,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9903,10 +9981,10 @@
         <v>170</v>
       </c>
       <c r="E260" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F260" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G260" s="1">
         <v>46301</v>
@@ -9920,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9929,10 +10007,10 @@
         <v>170</v>
       </c>
       <c r="E261" t="s">
-        <v>435</v>
+        <v>553</v>
       </c>
       <c r="F261" t="s">
-        <v>436</v>
+        <v>554</v>
       </c>
       <c r="G261" s="1">
         <v>46301</v>
@@ -9946,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9955,10 +10033,10 @@
         <v>170</v>
       </c>
       <c r="E262" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F262" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G262" s="1">
         <v>46301</v>
@@ -9972,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9981,10 +10059,10 @@
         <v>170</v>
       </c>
       <c r="E263" t="s">
-        <v>555</v>
+        <v>211</v>
       </c>
       <c r="F263" t="s">
-        <v>556</v>
+        <v>212</v>
       </c>
       <c r="G263" s="1">
         <v>46301</v>
@@ -9998,7 +10076,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -10007,10 +10085,10 @@
         <v>170</v>
       </c>
       <c r="E264" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F264" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G264" s="1">
         <v>46301</v>
@@ -10024,7 +10102,7 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -10033,10 +10111,10 @@
         <v>170</v>
       </c>
       <c r="E265" t="s">
-        <v>211</v>
+        <v>445</v>
       </c>
       <c r="F265" t="s">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="G265" s="1">
         <v>46301</v>
@@ -10050,7 +10128,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -10059,10 +10137,10 @@
         <v>170</v>
       </c>
       <c r="E266" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F266" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G266" s="1">
         <v>46301</v>
@@ -10076,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -10085,10 +10163,10 @@
         <v>170</v>
       </c>
       <c r="E267" t="s">
-        <v>449</v>
+        <v>16</v>
       </c>
       <c r="F267" t="s">
-        <v>450</v>
+        <v>17</v>
       </c>
       <c r="G267" s="1">
         <v>46301</v>
@@ -10102,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -10111,10 +10189,10 @@
         <v>170</v>
       </c>
       <c r="E268" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F268" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G268" s="1">
         <v>46301</v>
@@ -10128,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -10137,10 +10215,10 @@
         <v>170</v>
       </c>
       <c r="E269" t="s">
-        <v>16</v>
+        <v>571</v>
       </c>
       <c r="F269" t="s">
-        <v>17</v>
+        <v>572</v>
       </c>
       <c r="G269" s="1">
         <v>46301</v>
@@ -10154,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -10163,10 +10241,10 @@
         <v>170</v>
       </c>
       <c r="E270" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F270" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G270" s="1">
         <v>46301</v>
@@ -10180,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -10189,10 +10267,10 @@
         <v>170</v>
       </c>
       <c r="E271" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F271" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G271" s="1">
         <v>46301</v>
@@ -10206,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -10215,10 +10293,10 @@
         <v>170</v>
       </c>
       <c r="E272" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F272" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G272" s="1">
         <v>46301</v>
@@ -10232,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -10241,10 +10319,10 @@
         <v>170</v>
       </c>
       <c r="E273" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="F273" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="G273" s="1">
         <v>46301</v>
@@ -10258,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -10267,10 +10345,10 @@
         <v>170</v>
       </c>
       <c r="E274" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="F274" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="G274" s="1">
         <v>46301</v>
@@ -10284,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -10293,10 +10371,10 @@
         <v>170</v>
       </c>
       <c r="E275" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F275" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G275" s="1">
         <v>46301</v>
@@ -10310,25 +10388,25 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E276" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F276" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G276" s="1">
         <v>46301</v>
       </c>
       <c r="H276" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
@@ -10336,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -10345,16 +10423,16 @@
         <v>170</v>
       </c>
       <c r="E277" t="s">
-        <v>591</v>
+        <v>448</v>
       </c>
       <c r="F277" t="s">
-        <v>592</v>
+        <v>449</v>
       </c>
       <c r="G277" s="1">
         <v>46301</v>
       </c>
       <c r="H277" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
@@ -10371,16 +10449,16 @@
         <v>170</v>
       </c>
       <c r="E278" t="s">
-        <v>594</v>
+        <v>80</v>
       </c>
       <c r="F278" t="s">
-        <v>595</v>
+        <v>81</v>
       </c>
       <c r="G278" s="1">
         <v>46301</v>
       </c>
       <c r="H278" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -10388,25 +10466,25 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
+        <v>594</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279" t="s">
+        <v>170</v>
+      </c>
+      <c r="E279" t="s">
+        <v>595</v>
+      </c>
+      <c r="F279" t="s">
         <v>596</v>
-      </c>
-      <c r="C279">
-        <v>1</v>
-      </c>
-      <c r="D279" t="s">
-        <v>170</v>
-      </c>
-      <c r="E279" t="s">
-        <v>594</v>
-      </c>
-      <c r="F279" t="s">
-        <v>595</v>
       </c>
       <c r="G279" s="1">
         <v>46301</v>
       </c>
       <c r="H279" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
@@ -10423,10 +10501,10 @@
         <v>170</v>
       </c>
       <c r="E280" t="s">
-        <v>452</v>
+        <v>334</v>
       </c>
       <c r="F280" t="s">
-        <v>453</v>
+        <v>335</v>
       </c>
       <c r="G280" s="1">
         <v>46301</v>
@@ -10446,16 +10524,16 @@
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E281" t="s">
-        <v>443</v>
+        <v>37</v>
       </c>
       <c r="F281" t="s">
-        <v>444</v>
+        <v>38</v>
       </c>
       <c r="G281" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H281" s="1">
         <v>46302</v>
@@ -10472,16 +10550,16 @@
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E282" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="F282" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="G282" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H282" s="1">
         <v>46302</v>
@@ -10501,13 +10579,13 @@
         <v>170</v>
       </c>
       <c r="E283" t="s">
-        <v>601</v>
+        <v>261</v>
       </c>
       <c r="F283" t="s">
-        <v>602</v>
+        <v>262</v>
       </c>
       <c r="G283" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H283" s="1">
         <v>46302</v>
@@ -10518,7 +10596,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -10527,13 +10605,13 @@
         <v>170</v>
       </c>
       <c r="E284" t="s">
-        <v>604</v>
+        <v>379</v>
       </c>
       <c r="F284" t="s">
-        <v>605</v>
+        <v>380</v>
       </c>
       <c r="G284" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H284" s="1">
         <v>46302</v>
@@ -10544,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -10553,13 +10631,13 @@
         <v>170</v>
       </c>
       <c r="E285" t="s">
-        <v>338</v>
+        <v>603</v>
       </c>
       <c r="F285" t="s">
-        <v>339</v>
+        <v>604</v>
       </c>
       <c r="G285" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H285" s="1">
         <v>46302</v>
@@ -10570,19 +10648,19 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E286" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="F286" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
       <c r="G286" s="1">
         <v>46302</v>
@@ -10596,19 +10674,19 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
+        <v>606</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>170</v>
+      </c>
+      <c r="E287" t="s">
+        <v>607</v>
+      </c>
+      <c r="F287" t="s">
         <v>608</v>
-      </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="D287" t="s">
-        <v>2</v>
-      </c>
-      <c r="E287" t="s">
-        <v>254</v>
-      </c>
-      <c r="F287" t="s">
-        <v>255</v>
       </c>
       <c r="G287" s="1">
         <v>46302</v>
@@ -10631,10 +10709,10 @@
         <v>170</v>
       </c>
       <c r="E288" t="s">
-        <v>262</v>
+        <v>423</v>
       </c>
       <c r="F288" t="s">
-        <v>263</v>
+        <v>424</v>
       </c>
       <c r="G288" s="1">
         <v>46302</v>
@@ -10657,10 +10735,10 @@
         <v>170</v>
       </c>
       <c r="E289" t="s">
-        <v>383</v>
+        <v>611</v>
       </c>
       <c r="F289" t="s">
-        <v>384</v>
+        <v>612</v>
       </c>
       <c r="G289" s="1">
         <v>46302</v>
@@ -10674,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10683,10 +10761,10 @@
         <v>170</v>
       </c>
       <c r="E290" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F290" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G290" s="1">
         <v>46302</v>
@@ -10700,19 +10778,19 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E291" t="s">
-        <v>254</v>
+        <v>617</v>
       </c>
       <c r="F291" t="s">
-        <v>255</v>
+        <v>618</v>
       </c>
       <c r="G291" s="1">
         <v>46302</v>
@@ -10726,7 +10804,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -10735,10 +10813,10 @@
         <v>170</v>
       </c>
       <c r="E292" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F292" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G292" s="1">
         <v>46302</v>
@@ -10752,7 +10830,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -10761,10 +10839,10 @@
         <v>170</v>
       </c>
       <c r="E293" t="s">
-        <v>427</v>
+        <v>620</v>
       </c>
       <c r="F293" t="s">
-        <v>428</v>
+        <v>621</v>
       </c>
       <c r="G293" s="1">
         <v>46302</v>
@@ -10778,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10787,10 +10865,10 @@
         <v>170</v>
       </c>
       <c r="E294" t="s">
-        <v>620</v>
+        <v>31</v>
       </c>
       <c r="F294" t="s">
-        <v>621</v>
+        <v>32</v>
       </c>
       <c r="G294" s="1">
         <v>46302</v>
@@ -10804,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10813,10 +10891,10 @@
         <v>170</v>
       </c>
       <c r="E295" t="s">
-        <v>623</v>
+        <v>279</v>
       </c>
       <c r="F295" t="s">
-        <v>624</v>
+        <v>280</v>
       </c>
       <c r="G295" s="1">
         <v>46302</v>
@@ -10839,10 +10917,10 @@
         <v>170</v>
       </c>
       <c r="E296" t="s">
-        <v>626</v>
+        <v>279</v>
       </c>
       <c r="F296" t="s">
-        <v>627</v>
+        <v>280</v>
       </c>
       <c r="G296" s="1">
         <v>46302</v>
@@ -10856,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10865,10 +10943,10 @@
         <v>170</v>
       </c>
       <c r="E297" t="s">
-        <v>629</v>
+        <v>16</v>
       </c>
       <c r="F297" t="s">
-        <v>630</v>
+        <v>17</v>
       </c>
       <c r="G297" s="1">
         <v>46302</v>
@@ -10882,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -10891,10 +10969,10 @@
         <v>170</v>
       </c>
       <c r="E298" t="s">
+        <v>628</v>
+      </c>
+      <c r="F298" t="s">
         <v>629</v>
-      </c>
-      <c r="F298" t="s">
-        <v>630</v>
       </c>
       <c r="G298" s="1">
         <v>46302</v>
@@ -10908,19 +10986,19 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
+        <v>630</v>
+      </c>
+      <c r="C299">
+        <v>1</v>
+      </c>
+      <c r="D299" t="s">
+        <v>170</v>
+      </c>
+      <c r="E299" t="s">
+        <v>631</v>
+      </c>
+      <c r="F299" t="s">
         <v>632</v>
-      </c>
-      <c r="C299">
-        <v>1</v>
-      </c>
-      <c r="D299" t="s">
-        <v>170</v>
-      </c>
-      <c r="E299" t="s">
-        <v>31</v>
-      </c>
-      <c r="F299" t="s">
-        <v>32</v>
       </c>
       <c r="G299" s="1">
         <v>46302</v>
@@ -10943,10 +11021,10 @@
         <v>170</v>
       </c>
       <c r="E300" t="s">
-        <v>280</v>
+        <v>142</v>
       </c>
       <c r="F300" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="G300" s="1">
         <v>46302</v>
@@ -10969,10 +11047,10 @@
         <v>170</v>
       </c>
       <c r="E301" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="F301" t="s">
-        <v>281</v>
+        <v>377</v>
       </c>
       <c r="G301" s="1">
         <v>46302</v>
@@ -10992,13 +11070,13 @@
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E302" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="F302" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="G302" s="1">
         <v>46302</v>
@@ -11018,13 +11096,13 @@
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E303" t="s">
-        <v>637</v>
+        <v>13</v>
       </c>
       <c r="F303" t="s">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="G303" s="1">
         <v>46302</v>
@@ -11038,19 +11116,19 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
+        <v>637</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="D304" t="s">
+        <v>170</v>
+      </c>
+      <c r="E304" t="s">
+        <v>638</v>
+      </c>
+      <c r="F304" t="s">
         <v>639</v>
-      </c>
-      <c r="C304">
-        <v>1</v>
-      </c>
-      <c r="D304" t="s">
-        <v>170</v>
-      </c>
-      <c r="E304" t="s">
-        <v>640</v>
-      </c>
-      <c r="F304" t="s">
-        <v>641</v>
       </c>
       <c r="G304" s="1">
         <v>46302</v>
@@ -11064,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -11073,10 +11151,10 @@
         <v>170</v>
       </c>
       <c r="E305" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="F305" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="G305" s="1">
         <v>46302</v>
@@ -11090,19 +11168,19 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D306" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E306" t="s">
-        <v>380</v>
+        <v>48</v>
       </c>
       <c r="F306" t="s">
-        <v>381</v>
+        <v>49</v>
       </c>
       <c r="G306" s="1">
         <v>46302</v>
@@ -11116,19 +11194,19 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
+        <v>642</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+      <c r="D307" t="s">
+        <v>170</v>
+      </c>
+      <c r="E307" t="s">
+        <v>643</v>
+      </c>
+      <c r="F307" t="s">
         <v>644</v>
-      </c>
-      <c r="C307">
-        <v>1</v>
-      </c>
-      <c r="D307" t="s">
-        <v>2</v>
-      </c>
-      <c r="E307" t="s">
-        <v>185</v>
-      </c>
-      <c r="F307" t="s">
-        <v>186</v>
       </c>
       <c r="G307" s="1">
         <v>46302</v>
@@ -11151,10 +11229,10 @@
         <v>170</v>
       </c>
       <c r="E308" t="s">
-        <v>13</v>
+        <v>646</v>
       </c>
       <c r="F308" t="s">
-        <v>14</v>
+        <v>647</v>
       </c>
       <c r="G308" s="1">
         <v>46302</v>
@@ -11168,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -11177,10 +11255,10 @@
         <v>170</v>
       </c>
       <c r="E309" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="F309" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="G309" s="1">
         <v>46302</v>
@@ -11203,10 +11281,10 @@
         <v>170</v>
       </c>
       <c r="E310" t="s">
-        <v>234</v>
+        <v>650</v>
       </c>
       <c r="F310" t="s">
-        <v>235</v>
+        <v>651</v>
       </c>
       <c r="G310" s="1">
         <v>46302</v>
@@ -11220,19 +11298,19 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E311" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="F311" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="G311" s="1">
         <v>46302</v>
@@ -11246,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -11255,10 +11333,10 @@
         <v>170</v>
       </c>
       <c r="E312" t="s">
-        <v>652</v>
+        <v>139</v>
       </c>
       <c r="F312" t="s">
-        <v>653</v>
+        <v>140</v>
       </c>
       <c r="G312" s="1">
         <v>46302</v>
@@ -11281,10 +11359,10 @@
         <v>170</v>
       </c>
       <c r="E313" t="s">
-        <v>655</v>
+        <v>139</v>
       </c>
       <c r="F313" t="s">
-        <v>656</v>
+        <v>140</v>
       </c>
       <c r="G313" s="1">
         <v>46302</v>
@@ -11298,19 +11376,19 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E314" t="s">
-        <v>658</v>
+        <v>586</v>
       </c>
       <c r="F314" t="s">
-        <v>659</v>
+        <v>587</v>
       </c>
       <c r="G314" s="1">
         <v>46302</v>
@@ -11324,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -11333,10 +11411,10 @@
         <v>170</v>
       </c>
       <c r="E315" t="s">
-        <v>647</v>
+        <v>139</v>
       </c>
       <c r="F315" t="s">
-        <v>648</v>
+        <v>140</v>
       </c>
       <c r="G315" s="1">
         <v>46302</v>
@@ -11350,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -11359,10 +11437,10 @@
         <v>170</v>
       </c>
       <c r="E316" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F316" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="G316" s="1">
         <v>46302</v>
@@ -11376,7 +11454,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -11385,10 +11463,10 @@
         <v>170</v>
       </c>
       <c r="E317" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="F317" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="G317" s="1">
         <v>46302</v>
@@ -11402,7 +11480,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -11411,10 +11489,10 @@
         <v>170</v>
       </c>
       <c r="E318" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="F318" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="G318" s="1">
         <v>46302</v>
@@ -11428,19 +11506,19 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E319" t="s">
-        <v>139</v>
+        <v>663</v>
       </c>
       <c r="F319" t="s">
-        <v>140</v>
+        <v>664</v>
       </c>
       <c r="G319" s="1">
         <v>46302</v>
@@ -11454,7 +11532,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -11463,10 +11541,10 @@
         <v>170</v>
       </c>
       <c r="E320" t="s">
-        <v>591</v>
+        <v>37</v>
       </c>
       <c r="F320" t="s">
-        <v>592</v>
+        <v>38</v>
       </c>
       <c r="G320" s="1">
         <v>46302</v>
@@ -11480,19 +11558,19 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C321">
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E321" t="s">
-        <v>139</v>
+        <v>254</v>
       </c>
       <c r="F321" t="s">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="G321" s="1">
         <v>46302</v>
@@ -11506,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -11515,10 +11593,10 @@
         <v>170</v>
       </c>
       <c r="E322" t="s">
-        <v>670</v>
+        <v>37</v>
       </c>
       <c r="F322" t="s">
-        <v>671</v>
+        <v>38</v>
       </c>
       <c r="G322" s="1">
         <v>46302</v>
@@ -11532,19 +11610,19 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C323">
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E323" t="s">
-        <v>673</v>
+        <v>595</v>
       </c>
       <c r="F323" t="s">
-        <v>674</v>
+        <v>596</v>
       </c>
       <c r="G323" s="1">
         <v>46302</v>
@@ -11558,7 +11636,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -11584,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11593,10 +11671,10 @@
         <v>170</v>
       </c>
       <c r="E325" t="s">
-        <v>37</v>
+        <v>671</v>
       </c>
       <c r="F325" t="s">
-        <v>38</v>
+        <v>672</v>
       </c>
       <c r="G325" s="1">
         <v>46302</v>
@@ -11610,19 +11688,19 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E326" t="s">
-        <v>678</v>
+        <v>37</v>
       </c>
       <c r="F326" t="s">
-        <v>679</v>
+        <v>38</v>
       </c>
       <c r="G326" s="1">
         <v>46302</v>
@@ -11636,7 +11714,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -11645,10 +11723,10 @@
         <v>170</v>
       </c>
       <c r="E327" t="s">
-        <v>37</v>
+        <v>671</v>
       </c>
       <c r="F327" t="s">
-        <v>38</v>
+        <v>672</v>
       </c>
       <c r="G327" s="1">
         <v>46302</v>
@@ -11662,19 +11740,19 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E328" t="s">
-        <v>254</v>
+        <v>486</v>
       </c>
       <c r="F328" t="s">
-        <v>255</v>
+        <v>487</v>
       </c>
       <c r="G328" s="1">
         <v>46302</v>
@@ -11688,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11714,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -11723,10 +11801,10 @@
         <v>170</v>
       </c>
       <c r="E330" t="s">
-        <v>601</v>
+        <v>37</v>
       </c>
       <c r="F330" t="s">
-        <v>602</v>
+        <v>38</v>
       </c>
       <c r="G330" s="1">
         <v>46302</v>
@@ -11740,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -11766,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -11775,10 +11853,10 @@
         <v>170</v>
       </c>
       <c r="E332" t="s">
-        <v>686</v>
+        <v>37</v>
       </c>
       <c r="F332" t="s">
-        <v>687</v>
+        <v>38</v>
       </c>
       <c r="G332" s="1">
         <v>46302</v>
@@ -11792,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11801,10 +11879,10 @@
         <v>170</v>
       </c>
       <c r="E333" t="s">
-        <v>37</v>
+        <v>681</v>
       </c>
       <c r="F333" t="s">
-        <v>38</v>
+        <v>682</v>
       </c>
       <c r="G333" s="1">
         <v>46302</v>
@@ -11818,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -11827,10 +11905,10 @@
         <v>170</v>
       </c>
       <c r="E334" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F334" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G334" s="1">
         <v>46302</v>
@@ -11844,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -11853,16 +11931,16 @@
         <v>170</v>
       </c>
       <c r="E335" t="s">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="F335" t="s">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="G335" s="1">
         <v>46302</v>
       </c>
       <c r="H335" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
@@ -11870,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -11879,16 +11957,16 @@
         <v>170</v>
       </c>
       <c r="E336" t="s">
-        <v>37</v>
+        <v>686</v>
       </c>
       <c r="F336" t="s">
-        <v>38</v>
+        <v>687</v>
       </c>
       <c r="G336" s="1">
         <v>46302</v>
       </c>
       <c r="H336" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
@@ -11896,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -11905,16 +11983,16 @@
         <v>170</v>
       </c>
       <c r="E337" t="s">
-        <v>37</v>
+        <v>686</v>
       </c>
       <c r="F337" t="s">
-        <v>38</v>
+        <v>687</v>
       </c>
       <c r="G337" s="1">
         <v>46302</v>
       </c>
       <c r="H337" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
@@ -11922,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -11931,16 +12009,16 @@
         <v>170</v>
       </c>
       <c r="E338" t="s">
-        <v>37</v>
+        <v>690</v>
       </c>
       <c r="F338" t="s">
-        <v>38</v>
+        <v>691</v>
       </c>
       <c r="G338" s="1">
         <v>46302</v>
       </c>
       <c r="H338" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
@@ -11948,25 +12026,25 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
+        <v>692</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+      <c r="D339" t="s">
+        <v>170</v>
+      </c>
+      <c r="E339" t="s">
+        <v>693</v>
+      </c>
+      <c r="F339" t="s">
         <v>694</v>
-      </c>
-      <c r="C339">
-        <v>1</v>
-      </c>
-      <c r="D339" t="s">
-        <v>170</v>
-      </c>
-      <c r="E339" t="s">
-        <v>37</v>
-      </c>
-      <c r="F339" t="s">
-        <v>38</v>
       </c>
       <c r="G339" s="1">
         <v>46302</v>
       </c>
       <c r="H339" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
@@ -11983,16 +12061,16 @@
         <v>170</v>
       </c>
       <c r="E340" t="s">
-        <v>696</v>
+        <v>37</v>
       </c>
       <c r="F340" t="s">
-        <v>697</v>
+        <v>38</v>
       </c>
       <c r="G340" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H340" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
@@ -12000,7 +12078,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -12009,16 +12087,16 @@
         <v>170</v>
       </c>
       <c r="E341" t="s">
-        <v>696</v>
+        <v>37</v>
       </c>
       <c r="F341" t="s">
-        <v>697</v>
+        <v>38</v>
       </c>
       <c r="G341" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H341" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
@@ -12026,25 +12104,25 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E342" t="s">
-        <v>588</v>
+        <v>37</v>
       </c>
       <c r="F342" t="s">
-        <v>589</v>
+        <v>38</v>
       </c>
       <c r="G342" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H342" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
@@ -12052,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -12061,13 +12139,13 @@
         <v>170</v>
       </c>
       <c r="E343" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="F343" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G343" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H343" s="1">
         <v>46303</v>
@@ -12078,22 +12156,22 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
+        <v>699</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344" t="s">
+        <v>170</v>
+      </c>
+      <c r="E344" t="s">
+        <v>700</v>
+      </c>
+      <c r="F344" t="s">
         <v>701</v>
       </c>
-      <c r="C344">
-        <v>1</v>
-      </c>
-      <c r="D344" t="s">
-        <v>170</v>
-      </c>
-      <c r="E344" t="s">
-        <v>702</v>
-      </c>
-      <c r="F344" t="s">
-        <v>703</v>
-      </c>
       <c r="G344" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H344" s="1">
         <v>46303</v>
@@ -12104,22 +12182,22 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
+        <v>702</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+      <c r="D345" t="s">
+        <v>170</v>
+      </c>
+      <c r="E345" t="s">
+        <v>703</v>
+      </c>
+      <c r="F345" t="s">
         <v>704</v>
       </c>
-      <c r="C345">
-        <v>1</v>
-      </c>
-      <c r="D345" t="s">
-        <v>170</v>
-      </c>
-      <c r="E345" t="s">
-        <v>702</v>
-      </c>
-      <c r="F345" t="s">
-        <v>703</v>
-      </c>
       <c r="G345" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H345" s="1">
         <v>46303</v>
@@ -12139,13 +12217,13 @@
         <v>170</v>
       </c>
       <c r="E346" t="s">
-        <v>706</v>
+        <v>204</v>
       </c>
       <c r="F346" t="s">
-        <v>707</v>
+        <v>205</v>
       </c>
       <c r="G346" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H346" s="1">
         <v>46303</v>
@@ -12156,22 +12234,22 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
+        <v>706</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347" t="s">
+        <v>170</v>
+      </c>
+      <c r="E347" t="s">
+        <v>707</v>
+      </c>
+      <c r="F347" t="s">
         <v>708</v>
       </c>
-      <c r="C347">
-        <v>1</v>
-      </c>
-      <c r="D347" t="s">
-        <v>170</v>
-      </c>
-      <c r="E347" t="s">
-        <v>709</v>
-      </c>
-      <c r="F347" t="s">
-        <v>710</v>
-      </c>
       <c r="G347" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H347" s="1">
         <v>46303</v>
@@ -12182,19 +12260,19 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
+        <v>709</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+      <c r="D348" t="s">
+        <v>170</v>
+      </c>
+      <c r="E348" t="s">
+        <v>710</v>
+      </c>
+      <c r="F348" t="s">
         <v>711</v>
-      </c>
-      <c r="C348">
-        <v>1</v>
-      </c>
-      <c r="D348" t="s">
-        <v>170</v>
-      </c>
-      <c r="E348" t="s">
-        <v>37</v>
-      </c>
-      <c r="F348" t="s">
-        <v>38</v>
       </c>
       <c r="G348" s="1">
         <v>46303</v>
@@ -12217,10 +12295,10 @@
         <v>170</v>
       </c>
       <c r="E349" t="s">
-        <v>37</v>
+        <v>483</v>
       </c>
       <c r="F349" t="s">
-        <v>38</v>
+        <v>484</v>
       </c>
       <c r="G349" s="1">
         <v>46303</v>
@@ -12243,10 +12321,10 @@
         <v>170</v>
       </c>
       <c r="E350" t="s">
-        <v>37</v>
+        <v>714</v>
       </c>
       <c r="F350" t="s">
-        <v>38</v>
+        <v>715</v>
       </c>
       <c r="G350" s="1">
         <v>46303</v>
@@ -12260,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -12269,10 +12347,10 @@
         <v>170</v>
       </c>
       <c r="E351" t="s">
-        <v>37</v>
+        <v>270</v>
       </c>
       <c r="F351" t="s">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="G351" s="1">
         <v>46303</v>
@@ -12286,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -12295,10 +12373,10 @@
         <v>170</v>
       </c>
       <c r="E352" t="s">
-        <v>716</v>
+        <v>638</v>
       </c>
       <c r="F352" t="s">
-        <v>717</v>
+        <v>639</v>
       </c>
       <c r="G352" s="1">
         <v>46303</v>
@@ -12347,10 +12425,10 @@
         <v>170</v>
       </c>
       <c r="E354" t="s">
-        <v>204</v>
+        <v>722</v>
       </c>
       <c r="F354" t="s">
-        <v>205</v>
+        <v>723</v>
       </c>
       <c r="G354" s="1">
         <v>46303</v>
@@ -12364,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -12373,10 +12451,10 @@
         <v>170</v>
       </c>
       <c r="E355" t="s">
-        <v>723</v>
+        <v>453</v>
       </c>
       <c r="F355" t="s">
-        <v>724</v>
+        <v>454</v>
       </c>
       <c r="G355" s="1">
         <v>46303</v>
@@ -12399,10 +12477,10 @@
         <v>170</v>
       </c>
       <c r="E356" t="s">
-        <v>726</v>
+        <v>7</v>
       </c>
       <c r="F356" t="s">
-        <v>727</v>
+        <v>8</v>
       </c>
       <c r="G356" s="1">
         <v>46303</v>
@@ -12416,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -12425,10 +12503,10 @@
         <v>170</v>
       </c>
       <c r="E357" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="F357" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="G357" s="1">
         <v>46303</v>
@@ -12442,19 +12520,19 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
+        <v>727</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+      <c r="D358" t="s">
+        <v>170</v>
+      </c>
+      <c r="E358" t="s">
+        <v>728</v>
+      </c>
+      <c r="F358" t="s">
         <v>729</v>
-      </c>
-      <c r="C358">
-        <v>1</v>
-      </c>
-      <c r="D358" t="s">
-        <v>170</v>
-      </c>
-      <c r="E358" t="s">
-        <v>730</v>
-      </c>
-      <c r="F358" t="s">
-        <v>731</v>
       </c>
       <c r="G358" s="1">
         <v>46303</v>
@@ -12468,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -12477,10 +12555,10 @@
         <v>170</v>
       </c>
       <c r="E359" t="s">
-        <v>271</v>
+        <v>45</v>
       </c>
       <c r="F359" t="s">
-        <v>272</v>
+        <v>46</v>
       </c>
       <c r="G359" s="1">
         <v>46303</v>
@@ -12494,19 +12572,19 @@
         <v>0</v>
       </c>
       <c r="B360" t="s">
+        <v>731</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+      <c r="D360" t="s">
+        <v>170</v>
+      </c>
+      <c r="E360" t="s">
+        <v>732</v>
+      </c>
+      <c r="F360" t="s">
         <v>733</v>
-      </c>
-      <c r="C360">
-        <v>1</v>
-      </c>
-      <c r="D360" t="s">
-        <v>170</v>
-      </c>
-      <c r="E360" t="s">
-        <v>647</v>
-      </c>
-      <c r="F360" t="s">
-        <v>648</v>
       </c>
       <c r="G360" s="1">
         <v>46303</v>
@@ -12529,10 +12607,10 @@
         <v>170</v>
       </c>
       <c r="E361" t="s">
-        <v>735</v>
+        <v>97</v>
       </c>
       <c r="F361" t="s">
-        <v>736</v>
+        <v>98</v>
       </c>
       <c r="G361" s="1">
         <v>46303</v>
@@ -12546,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -12555,10 +12633,10 @@
         <v>170</v>
       </c>
       <c r="E362" t="s">
-        <v>738</v>
+        <v>97</v>
       </c>
       <c r="F362" t="s">
-        <v>739</v>
+        <v>98</v>
       </c>
       <c r="G362" s="1">
         <v>46303</v>
@@ -12572,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -12581,10 +12659,10 @@
         <v>170</v>
       </c>
       <c r="E363" t="s">
-        <v>457</v>
+        <v>97</v>
       </c>
       <c r="F363" t="s">
-        <v>458</v>
+        <v>98</v>
       </c>
       <c r="G363" s="1">
         <v>46303</v>
@@ -12598,7 +12676,7 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -12607,10 +12685,10 @@
         <v>170</v>
       </c>
       <c r="E364" t="s">
-        <v>7</v>
+        <v>738</v>
       </c>
       <c r="F364" t="s">
-        <v>8</v>
+        <v>739</v>
       </c>
       <c r="G364" s="1">
         <v>46303</v>
@@ -12624,7 +12702,7 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -12633,10 +12711,10 @@
         <v>170</v>
       </c>
       <c r="E365" t="s">
-        <v>462</v>
+        <v>738</v>
       </c>
       <c r="F365" t="s">
-        <v>463</v>
+        <v>739</v>
       </c>
       <c r="G365" s="1">
         <v>46303</v>
@@ -12650,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -12659,10 +12737,10 @@
         <v>170</v>
       </c>
       <c r="E366" t="s">
-        <v>744</v>
+        <v>16</v>
       </c>
       <c r="F366" t="s">
-        <v>745</v>
+        <v>17</v>
       </c>
       <c r="G366" s="1">
         <v>46303</v>
@@ -12676,7 +12754,7 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -12685,10 +12763,10 @@
         <v>170</v>
       </c>
       <c r="E367" t="s">
-        <v>45</v>
+        <v>279</v>
       </c>
       <c r="F367" t="s">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="G367" s="1">
         <v>46303</v>
@@ -12702,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -12711,10 +12789,10 @@
         <v>170</v>
       </c>
       <c r="E368" t="s">
-        <v>748</v>
+        <v>37</v>
       </c>
       <c r="F368" t="s">
-        <v>749</v>
+        <v>38</v>
       </c>
       <c r="G368" s="1">
         <v>46303</v>
@@ -12728,7 +12806,7 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -12737,10 +12815,10 @@
         <v>170</v>
       </c>
       <c r="E369" t="s">
-        <v>97</v>
+        <v>745</v>
       </c>
       <c r="F369" t="s">
-        <v>98</v>
+        <v>746</v>
       </c>
       <c r="G369" s="1">
         <v>46303</v>
@@ -12754,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12763,10 +12841,10 @@
         <v>170</v>
       </c>
       <c r="E370" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="F370" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="G370" s="1">
         <v>46303</v>
@@ -12780,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C371">
         <v>1</v>
@@ -12789,10 +12867,10 @@
         <v>170</v>
       </c>
       <c r="E371" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F371" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G371" s="1">
         <v>46303</v>
@@ -12806,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -12815,10 +12893,10 @@
         <v>170</v>
       </c>
       <c r="E372" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F372" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G372" s="1">
         <v>46303</v>
@@ -12832,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12841,10 +12919,10 @@
         <v>170</v>
       </c>
       <c r="E373" t="s">
-        <v>754</v>
+        <v>16</v>
       </c>
       <c r="F373" t="s">
-        <v>755</v>
+        <v>17</v>
       </c>
       <c r="G373" s="1">
         <v>46303</v>
@@ -12858,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -12867,10 +12945,10 @@
         <v>170</v>
       </c>
       <c r="E374" t="s">
-        <v>16</v>
+        <v>754</v>
       </c>
       <c r="F374" t="s">
-        <v>17</v>
+        <v>755</v>
       </c>
       <c r="G374" s="1">
         <v>46303</v>
@@ -12884,19 +12962,19 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
+        <v>756</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+      <c r="D375" t="s">
+        <v>170</v>
+      </c>
+      <c r="E375" t="s">
+        <v>757</v>
+      </c>
+      <c r="F375" t="s">
         <v>758</v>
-      </c>
-      <c r="C375">
-        <v>1</v>
-      </c>
-      <c r="D375" t="s">
-        <v>170</v>
-      </c>
-      <c r="E375" t="s">
-        <v>280</v>
-      </c>
-      <c r="F375" t="s">
-        <v>281</v>
       </c>
       <c r="G375" s="1">
         <v>46303</v>
@@ -12919,10 +12997,10 @@
         <v>170</v>
       </c>
       <c r="E376" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F376" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G376" s="1">
         <v>46303</v>
@@ -12945,10 +13023,10 @@
         <v>170</v>
       </c>
       <c r="E377" t="s">
-        <v>761</v>
+        <v>492</v>
       </c>
       <c r="F377" t="s">
-        <v>762</v>
+        <v>493</v>
       </c>
       <c r="G377" s="1">
         <v>46303</v>
@@ -12962,19 +13040,19 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
+        <v>761</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+      <c r="D378" t="s">
+        <v>170</v>
+      </c>
+      <c r="E378" t="s">
+        <v>762</v>
+      </c>
+      <c r="F378" t="s">
         <v>763</v>
-      </c>
-      <c r="C378">
-        <v>1</v>
-      </c>
-      <c r="D378" t="s">
-        <v>170</v>
-      </c>
-      <c r="E378" t="s">
-        <v>19</v>
-      </c>
-      <c r="F378" t="s">
-        <v>20</v>
       </c>
       <c r="G378" s="1">
         <v>46303</v>
@@ -12997,10 +13075,10 @@
         <v>170</v>
       </c>
       <c r="E379" t="s">
-        <v>83</v>
+        <v>765</v>
       </c>
       <c r="F379" t="s">
-        <v>84</v>
+        <v>766</v>
       </c>
       <c r="G379" s="1">
         <v>46303</v>
@@ -13014,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -13023,10 +13101,10 @@
         <v>170</v>
       </c>
       <c r="E380" t="s">
-        <v>766</v>
+        <v>276</v>
       </c>
       <c r="F380" t="s">
-        <v>767</v>
+        <v>277</v>
       </c>
       <c r="G380" s="1">
         <v>46303</v>
@@ -13049,10 +13127,10 @@
         <v>170</v>
       </c>
       <c r="E381" t="s">
-        <v>16</v>
+        <v>769</v>
       </c>
       <c r="F381" t="s">
-        <v>17</v>
+        <v>770</v>
       </c>
       <c r="G381" s="1">
         <v>46303</v>
@@ -13066,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -13075,10 +13153,10 @@
         <v>170</v>
       </c>
       <c r="E382" t="s">
-        <v>770</v>
+        <v>261</v>
       </c>
       <c r="F382" t="s">
-        <v>771</v>
+        <v>262</v>
       </c>
       <c r="G382" s="1">
         <v>46303</v>
@@ -13127,10 +13205,10 @@
         <v>170</v>
       </c>
       <c r="E384" t="s">
-        <v>80</v>
+        <v>776</v>
       </c>
       <c r="F384" t="s">
-        <v>81</v>
+        <v>777</v>
       </c>
       <c r="G384" s="1">
         <v>46303</v>
@@ -13144,7 +13222,7 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C385">
         <v>1</v>
@@ -13153,10 +13231,10 @@
         <v>170</v>
       </c>
       <c r="E385" t="s">
-        <v>496</v>
+        <v>779</v>
       </c>
       <c r="F385" t="s">
-        <v>497</v>
+        <v>780</v>
       </c>
       <c r="G385" s="1">
         <v>46303</v>
@@ -13170,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -13179,10 +13257,10 @@
         <v>170</v>
       </c>
       <c r="E386" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F386" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="G386" s="1">
         <v>46303</v>
@@ -13196,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -13205,10 +13283,10 @@
         <v>170</v>
       </c>
       <c r="E387" t="s">
-        <v>781</v>
+        <v>142</v>
       </c>
       <c r="F387" t="s">
-        <v>782</v>
+        <v>143</v>
       </c>
       <c r="G387" s="1">
         <v>46303</v>
@@ -13222,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -13231,10 +13309,10 @@
         <v>170</v>
       </c>
       <c r="E388" t="s">
-        <v>277</v>
+        <v>786</v>
       </c>
       <c r="F388" t="s">
-        <v>278</v>
+        <v>787</v>
       </c>
       <c r="G388" s="1">
         <v>46303</v>
@@ -13248,7 +13326,7 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C389">
         <v>1</v>
@@ -13257,10 +13335,10 @@
         <v>170</v>
       </c>
       <c r="E389" t="s">
-        <v>785</v>
+        <v>306</v>
       </c>
       <c r="F389" t="s">
-        <v>786</v>
+        <v>307</v>
       </c>
       <c r="G389" s="1">
         <v>46303</v>
@@ -13274,7 +13352,7 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C390">
         <v>1</v>
@@ -13283,10 +13361,10 @@
         <v>170</v>
       </c>
       <c r="E390" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="F390" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="G390" s="1">
         <v>46303</v>
@@ -13300,7 +13378,7 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C391">
         <v>1</v>
@@ -13309,10 +13387,10 @@
         <v>170</v>
       </c>
       <c r="E391" t="s">
-        <v>789</v>
+        <v>200</v>
       </c>
       <c r="F391" t="s">
-        <v>790</v>
+        <v>201</v>
       </c>
       <c r="G391" s="1">
         <v>46303</v>
@@ -13335,10 +13413,10 @@
         <v>170</v>
       </c>
       <c r="E392" t="s">
-        <v>792</v>
+        <v>45</v>
       </c>
       <c r="F392" t="s">
-        <v>793</v>
+        <v>46</v>
       </c>
       <c r="G392" s="1">
         <v>46303</v>
@@ -13349,62 +13427,62 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" t="s">
+        <v>792</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>170</v>
+      </c>
+      <c r="E393" t="s">
+        <v>793</v>
+      </c>
+      <c r="F393" t="s">
         <v>794</v>
       </c>
-      <c r="B393" t="s">
-        <v>795</v>
-      </c>
-      <c r="C393">
-        <v>1</v>
-      </c>
-      <c r="D393" t="s">
-        <v>2</v>
-      </c>
-      <c r="E393" t="s">
-        <v>200</v>
-      </c>
-      <c r="F393" t="s">
-        <v>201</v>
-      </c>
       <c r="G393" s="1">
-        <v>46148</v>
+        <v>46303</v>
       </c>
       <c r="H393" s="1">
-        <v>46149</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C394">
         <v>1</v>
       </c>
       <c r="D394" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E394" t="s">
-        <v>111</v>
+        <v>331</v>
       </c>
       <c r="F394" t="s">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="G394" s="1">
-        <v>46268</v>
+        <v>46303</v>
       </c>
       <c r="H394" s="1">
-        <v>46268</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C395">
         <v>1</v>
@@ -13413,24 +13491,24 @@
         <v>170</v>
       </c>
       <c r="E395" t="s">
-        <v>798</v>
+        <v>97</v>
       </c>
       <c r="F395" t="s">
-        <v>799</v>
+        <v>98</v>
       </c>
       <c r="G395" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="H395" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C396">
         <v>1</v>
@@ -13439,24 +13517,24 @@
         <v>170</v>
       </c>
       <c r="E396" t="s">
-        <v>801</v>
+        <v>97</v>
       </c>
       <c r="F396" t="s">
-        <v>802</v>
+        <v>98</v>
       </c>
       <c r="G396" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H396" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C397">
         <v>1</v>
@@ -13465,10 +13543,10 @@
         <v>170</v>
       </c>
       <c r="E397" t="s">
-        <v>500</v>
+        <v>546</v>
       </c>
       <c r="F397" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
       <c r="G397" s="1">
         <v>46303</v>
@@ -13479,10 +13557,10 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -13491,10 +13569,10 @@
         <v>170</v>
       </c>
       <c r="E398" t="s">
-        <v>383</v>
+        <v>97</v>
       </c>
       <c r="F398" t="s">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="G398" s="1">
         <v>46303</v>
@@ -13505,10 +13583,10 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>794</v>
+        <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C399">
         <v>1</v>
@@ -13517,10 +13595,10 @@
         <v>170</v>
       </c>
       <c r="E399" t="s">
-        <v>806</v>
+        <v>97</v>
       </c>
       <c r="F399" t="s">
-        <v>807</v>
+        <v>98</v>
       </c>
       <c r="G399" s="1">
         <v>46303</v>
@@ -13531,244 +13609,244 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="C400">
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E400" t="s">
-        <v>41</v>
+        <v>802</v>
       </c>
       <c r="F400" t="s">
-        <v>42</v>
+        <v>803</v>
       </c>
       <c r="G400" s="1">
-        <v>46133</v>
+        <v>46303</v>
       </c>
       <c r="H400" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C401">
         <v>1</v>
       </c>
       <c r="D401" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E401" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="F401" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="G401" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
       <c r="H401" s="1">
-        <v>46134</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E402" t="s">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="F402" t="s">
-        <v>20</v>
+        <v>473</v>
       </c>
       <c r="G402" s="1">
-        <v>46156</v>
+        <v>46303</v>
       </c>
       <c r="H402" s="1">
-        <v>46156</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
+        <v>0</v>
+      </c>
+      <c r="B403" t="s">
+        <v>806</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>170</v>
+      </c>
+      <c r="E403" t="s">
+        <v>807</v>
+      </c>
+      <c r="F403" t="s">
         <v>808</v>
       </c>
-      <c r="B403" t="s">
-        <v>812</v>
-      </c>
-      <c r="C403">
-        <v>2</v>
-      </c>
-      <c r="D403" t="s">
-        <v>95</v>
-      </c>
-      <c r="E403" t="s">
-        <v>813</v>
-      </c>
-      <c r="F403" t="s">
-        <v>814</v>
-      </c>
       <c r="G403" s="1">
-        <v>46209</v>
+        <v>46303</v>
       </c>
       <c r="H403" s="1">
-        <v>46218</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B404" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="C404">
         <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E404" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F404" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="G404" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
       <c r="H404" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B405" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="C405">
         <v>1</v>
       </c>
       <c r="D405" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E405" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="F405" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="G405" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
       <c r="H405" s="1">
-        <v>46216</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B406" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C406">
         <v>1</v>
       </c>
       <c r="D406" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E406" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="F406" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="G406" s="1">
-        <v>46224</v>
+        <v>46303</v>
       </c>
       <c r="H406" s="1">
-        <v>46224</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B407" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C407">
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E407" t="s">
-        <v>823</v>
+        <v>757</v>
       </c>
       <c r="F407" t="s">
-        <v>824</v>
+        <v>758</v>
       </c>
       <c r="G407" s="1">
-        <v>46253</v>
+        <v>46303</v>
       </c>
       <c r="H407" s="1">
-        <v>46253</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B408" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="C408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E408" t="s">
-        <v>211</v>
+        <v>472</v>
       </c>
       <c r="F408" t="s">
-        <v>212</v>
+        <v>473</v>
       </c>
       <c r="G408" s="1">
-        <v>46273</v>
+        <v>46303</v>
       </c>
       <c r="H408" s="1">
-        <v>46274</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -13777,50 +13855,50 @@
         <v>170</v>
       </c>
       <c r="E409" t="s">
-        <v>827</v>
+        <v>80</v>
       </c>
       <c r="F409" t="s">
-        <v>828</v>
+        <v>81</v>
       </c>
       <c r="G409" s="1">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="H409" s="1">
-        <v>46300</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B410" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="C410">
         <v>1</v>
       </c>
       <c r="D410" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E410" t="s">
-        <v>827</v>
+        <v>200</v>
       </c>
       <c r="F410" t="s">
-        <v>828</v>
+        <v>201</v>
       </c>
       <c r="G410" s="1">
-        <v>46300</v>
+        <v>46148</v>
       </c>
       <c r="H410" s="1">
-        <v>46300</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B411" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -13829,39 +13907,39 @@
         <v>2</v>
       </c>
       <c r="E411" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="F411" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="G411" s="1">
-        <v>46300</v>
+        <v>46268</v>
       </c>
       <c r="H411" s="1">
-        <v>46300</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B412" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="C412">
         <v>1</v>
       </c>
       <c r="D412" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E412" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F412" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="G412" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H412" s="1">
         <v>46301</v>
@@ -13869,10 +13947,10 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B413" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -13881,24 +13959,24 @@
         <v>170</v>
       </c>
       <c r="E413" t="s">
+        <v>826</v>
+      </c>
+      <c r="F413" t="s">
         <v>827</v>
       </c>
-      <c r="F413" t="s">
-        <v>828</v>
-      </c>
       <c r="G413" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H413" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B414" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="C414">
         <v>1</v>
@@ -13907,24 +13985,24 @@
         <v>170</v>
       </c>
       <c r="E414" t="s">
-        <v>383</v>
+        <v>499</v>
       </c>
       <c r="F414" t="s">
-        <v>384</v>
+        <v>500</v>
       </c>
       <c r="G414" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H414" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B415" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="C415">
         <v>1</v>
@@ -13933,24 +14011,24 @@
         <v>170</v>
       </c>
       <c r="E415" t="s">
-        <v>813</v>
+        <v>379</v>
       </c>
       <c r="F415" t="s">
-        <v>814</v>
+        <v>380</v>
       </c>
       <c r="G415" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H415" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="B416" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C416">
         <v>1</v>
@@ -13959,10 +14037,10 @@
         <v>170</v>
       </c>
       <c r="E416" t="s">
-        <v>716</v>
+        <v>831</v>
       </c>
       <c r="F416" t="s">
-        <v>717</v>
+        <v>832</v>
       </c>
       <c r="G416" s="1">
         <v>46303</v>
@@ -13973,10 +14051,10 @@
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="B417" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C417">
         <v>1</v>
@@ -13985,206 +14063,206 @@
         <v>6</v>
       </c>
       <c r="E417" t="s">
-        <v>754</v>
+        <v>41</v>
       </c>
       <c r="F417" t="s">
-        <v>755</v>
+        <v>42</v>
       </c>
       <c r="G417" s="1">
-        <v>46303</v>
+        <v>46133</v>
       </c>
       <c r="H417" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="B418" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C418">
         <v>1</v>
       </c>
       <c r="D418" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E418" t="s">
-        <v>754</v>
+        <v>41</v>
       </c>
       <c r="F418" t="s">
-        <v>755</v>
+        <v>42</v>
       </c>
       <c r="G418" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
       <c r="H418" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="B419" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C419">
         <v>1</v>
       </c>
       <c r="D419" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E419" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="F419" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="G419" s="1">
-        <v>46303</v>
+        <v>46156</v>
       </c>
       <c r="H419" s="1">
-        <v>46303</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="B420" t="s">
+        <v>837</v>
+      </c>
+      <c r="C420">
+        <v>2</v>
+      </c>
+      <c r="D420" t="s">
+        <v>95</v>
+      </c>
+      <c r="E420" t="s">
+        <v>838</v>
+      </c>
+      <c r="F420" t="s">
         <v>839</v>
       </c>
-      <c r="C420">
-        <v>1</v>
-      </c>
-      <c r="D420" t="s">
-        <v>170</v>
-      </c>
-      <c r="E420" t="s">
-        <v>754</v>
-      </c>
-      <c r="F420" t="s">
-        <v>755</v>
-      </c>
       <c r="G420" s="1">
-        <v>46303</v>
+        <v>46209</v>
       </c>
       <c r="H420" s="1">
-        <v>46303</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
+        <v>833</v>
+      </c>
+      <c r="B421" t="s">
         <v>840</v>
       </c>
-      <c r="B421" t="s">
+      <c r="C421">
+        <v>1</v>
+      </c>
+      <c r="D421" t="s">
+        <v>6</v>
+      </c>
+      <c r="E421" t="s">
         <v>841</v>
       </c>
-      <c r="C421">
-        <v>1</v>
-      </c>
-      <c r="D421" t="s">
-        <v>95</v>
-      </c>
-      <c r="E421" t="s">
+      <c r="F421" t="s">
         <v>842</v>
       </c>
-      <c r="F421" t="s">
-        <v>843</v>
-      </c>
       <c r="G421" s="1">
-        <v>46063</v>
+        <v>46213</v>
       </c>
       <c r="H421" s="1">
-        <v>46064</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B422" t="s">
+        <v>843</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422" t="s">
+        <v>95</v>
+      </c>
+      <c r="E422" t="s">
         <v>844</v>
       </c>
-      <c r="C422">
-        <v>1</v>
-      </c>
-      <c r="D422" t="s">
-        <v>6</v>
-      </c>
-      <c r="E422" t="s">
-        <v>57</v>
-      </c>
       <c r="F422" t="s">
-        <v>58</v>
+        <v>845</v>
       </c>
       <c r="G422" s="1">
-        <v>46113</v>
+        <v>46213</v>
       </c>
       <c r="H422" s="1">
-        <v>46125</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B423" t="s">
+        <v>846</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>95</v>
+      </c>
+      <c r="E423" t="s">
+        <v>844</v>
+      </c>
+      <c r="F423" t="s">
         <v>845</v>
       </c>
-      <c r="C423">
-        <v>1</v>
-      </c>
-      <c r="D423" t="s">
-        <v>2</v>
-      </c>
-      <c r="E423" t="s">
-        <v>57</v>
-      </c>
-      <c r="F423" t="s">
-        <v>58</v>
-      </c>
       <c r="G423" s="1">
-        <v>46125</v>
+        <v>46224</v>
       </c>
       <c r="H423" s="1">
-        <v>46125</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B424" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C424">
         <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E424" t="s">
-        <v>57</v>
+        <v>848</v>
       </c>
       <c r="F424" t="s">
-        <v>58</v>
+        <v>849</v>
       </c>
       <c r="G424" s="1">
-        <v>46126</v>
+        <v>46253</v>
       </c>
       <c r="H424" s="1">
-        <v>46126</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B425" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C425">
         <v>1</v>
@@ -14193,76 +14271,76 @@
         <v>2</v>
       </c>
       <c r="E425" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="F425" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="G425" s="1">
-        <v>46126</v>
+        <v>46273</v>
       </c>
       <c r="H425" s="1">
-        <v>46126</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B426" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C426">
         <v>1</v>
       </c>
       <c r="D426" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E426" t="s">
-        <v>57</v>
+        <v>852</v>
       </c>
       <c r="F426" t="s">
-        <v>58</v>
+        <v>853</v>
       </c>
       <c r="G426" s="1">
-        <v>46128</v>
+        <v>46300</v>
       </c>
       <c r="H426" s="1">
-        <v>46128</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B427" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C427">
         <v>1</v>
       </c>
       <c r="D427" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E427" t="s">
-        <v>57</v>
+        <v>852</v>
       </c>
       <c r="F427" t="s">
-        <v>58</v>
+        <v>853</v>
       </c>
       <c r="G427" s="1">
-        <v>46132</v>
+        <v>46300</v>
       </c>
       <c r="H427" s="1">
-        <v>46132</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B428" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C428">
         <v>1</v>
@@ -14271,24 +14349,24 @@
         <v>2</v>
       </c>
       <c r="E428" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="F428" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="G428" s="1">
-        <v>46161</v>
+        <v>46300</v>
       </c>
       <c r="H428" s="1">
-        <v>46161</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B429" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C429">
         <v>1</v>
@@ -14297,128 +14375,128 @@
         <v>2</v>
       </c>
       <c r="E429" t="s">
-        <v>57</v>
+        <v>844</v>
       </c>
       <c r="F429" t="s">
-        <v>58</v>
+        <v>845</v>
       </c>
       <c r="G429" s="1">
-        <v>46174</v>
+        <v>46300</v>
       </c>
       <c r="H429" s="1">
-        <v>46174</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B430" t="s">
+        <v>857</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>170</v>
+      </c>
+      <c r="E430" t="s">
         <v>852</v>
       </c>
-      <c r="C430">
-        <v>1</v>
-      </c>
-      <c r="D430" t="s">
-        <v>2</v>
-      </c>
-      <c r="E430" t="s">
-        <v>57</v>
-      </c>
       <c r="F430" t="s">
-        <v>58</v>
+        <v>853</v>
       </c>
       <c r="G430" s="1">
-        <v>46174</v>
+        <v>46301</v>
       </c>
       <c r="H430" s="1">
-        <v>46174</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B431" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C431">
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E431" t="s">
-        <v>57</v>
+        <v>379</v>
       </c>
       <c r="F431" t="s">
-        <v>58</v>
+        <v>380</v>
       </c>
       <c r="G431" s="1">
-        <v>46195</v>
+        <v>46302</v>
       </c>
       <c r="H431" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B432" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C432">
         <v>1</v>
       </c>
       <c r="D432" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E432" t="s">
-        <v>57</v>
+        <v>838</v>
       </c>
       <c r="F432" t="s">
-        <v>58</v>
+        <v>839</v>
       </c>
       <c r="G432" s="1">
-        <v>46210</v>
+        <v>46302</v>
       </c>
       <c r="H432" s="1">
-        <v>46210</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B433" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C433">
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E433" t="s">
-        <v>57</v>
+        <v>700</v>
       </c>
       <c r="F433" t="s">
-        <v>58</v>
+        <v>701</v>
       </c>
       <c r="G433" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
       <c r="H433" s="1">
-        <v>46213</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B434" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C434">
         <v>1</v>
@@ -14427,50 +14505,50 @@
         <v>6</v>
       </c>
       <c r="E434" t="s">
-        <v>57</v>
+        <v>738</v>
       </c>
       <c r="F434" t="s">
-        <v>58</v>
+        <v>739</v>
       </c>
       <c r="G434" s="1">
-        <v>46218</v>
+        <v>46303</v>
       </c>
       <c r="H434" s="1">
-        <v>46252</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B435" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C435">
         <v>1</v>
       </c>
       <c r="D435" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E435" t="s">
-        <v>77</v>
+        <v>738</v>
       </c>
       <c r="F435" t="s">
-        <v>78</v>
+        <v>739</v>
       </c>
       <c r="G435" s="1">
-        <v>46226</v>
+        <v>46303</v>
       </c>
       <c r="H435" s="1">
-        <v>46226</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B436" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="C436">
         <v>1</v>
@@ -14479,102 +14557,102 @@
         <v>170</v>
       </c>
       <c r="E436" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F436" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G436" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H436" s="1">
-        <v>46252</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B437" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C437">
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E437" t="s">
-        <v>57</v>
+        <v>738</v>
       </c>
       <c r="F437" t="s">
-        <v>58</v>
+        <v>739</v>
       </c>
       <c r="G437" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H437" s="1">
-        <v>46252</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B438" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C438">
         <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E438" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="F438" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="G438" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H438" s="1">
-        <v>46228</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B439" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="C439">
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E439" t="s">
-        <v>77</v>
+        <v>868</v>
       </c>
       <c r="F439" t="s">
-        <v>78</v>
+        <v>869</v>
       </c>
       <c r="G439" s="1">
-        <v>46230</v>
+        <v>46063</v>
       </c>
       <c r="H439" s="1">
-        <v>46252</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B440" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C440">
         <v>1</v>
@@ -14589,24 +14667,24 @@
         <v>58</v>
       </c>
       <c r="G440" s="1">
-        <v>46231</v>
+        <v>46113</v>
       </c>
       <c r="H440" s="1">
-        <v>46231</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B441" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C441">
         <v>1</v>
       </c>
       <c r="D441" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E441" t="s">
         <v>57</v>
@@ -14615,18 +14693,18 @@
         <v>58</v>
       </c>
       <c r="G441" s="1">
-        <v>46254</v>
+        <v>46125</v>
       </c>
       <c r="H441" s="1">
-        <v>46254</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B442" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C442">
         <v>1</v>
@@ -14641,24 +14719,24 @@
         <v>58</v>
       </c>
       <c r="G442" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
       <c r="H442" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B443" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C443">
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E443" t="s">
         <v>57</v>
@@ -14667,24 +14745,24 @@
         <v>58</v>
       </c>
       <c r="G443" s="1">
-        <v>46260</v>
+        <v>46126</v>
       </c>
       <c r="H443" s="1">
-        <v>46260</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B444" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C444">
         <v>1</v>
       </c>
       <c r="D444" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E444" t="s">
         <v>57</v>
@@ -14693,18 +14771,18 @@
         <v>58</v>
       </c>
       <c r="G444" s="1">
-        <v>46289</v>
+        <v>46128</v>
       </c>
       <c r="H444" s="1">
-        <v>46289</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B445" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C445">
         <v>1</v>
@@ -14719,24 +14797,24 @@
         <v>58</v>
       </c>
       <c r="G445" s="1">
-        <v>46294</v>
+        <v>46132</v>
       </c>
       <c r="H445" s="1">
-        <v>46294</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="B446" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E446" t="s">
         <v>57</v>
@@ -14745,18 +14823,18 @@
         <v>58</v>
       </c>
       <c r="G446" s="1">
-        <v>46303</v>
+        <v>46161</v>
       </c>
       <c r="H446" s="1">
-        <v>46303</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B447" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="C447">
         <v>1</v>
@@ -14765,24 +14843,24 @@
         <v>2</v>
       </c>
       <c r="E447" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F447" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G447" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="H447" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B448" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="C448">
         <v>1</v>
@@ -14791,76 +14869,76 @@
         <v>2</v>
       </c>
       <c r="E448" t="s">
-        <v>874</v>
+        <v>57</v>
       </c>
       <c r="F448" t="s">
-        <v>875</v>
+        <v>58</v>
       </c>
       <c r="G448" s="1">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="H448" s="1">
-        <v>46170</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B449" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C449">
         <v>1</v>
       </c>
       <c r="D449" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F449" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G449" s="1">
-        <v>46218</v>
+        <v>46195</v>
       </c>
       <c r="H449" s="1">
-        <v>46218</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B450" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C450">
         <v>1</v>
       </c>
       <c r="D450" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E450" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F450" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G450" s="1">
-        <v>46244</v>
+        <v>46210</v>
       </c>
       <c r="H450" s="1">
-        <v>46244</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B451" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C451">
         <v>1</v>
@@ -14869,128 +14947,128 @@
         <v>2</v>
       </c>
       <c r="E451" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F451" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G451" s="1">
-        <v>46247</v>
+        <v>46213</v>
       </c>
       <c r="H451" s="1">
-        <v>46247</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B452" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C452">
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E452" t="s">
-        <v>880</v>
+        <v>57</v>
       </c>
       <c r="F452" t="s">
-        <v>881</v>
+        <v>58</v>
       </c>
       <c r="G452" s="1">
-        <v>46247</v>
+        <v>46218</v>
       </c>
       <c r="H452" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B453" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E453" t="s">
-        <v>871</v>
+        <v>77</v>
       </c>
       <c r="F453" t="s">
-        <v>872</v>
+        <v>78</v>
       </c>
       <c r="G453" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="H453" s="1">
-        <v>46255</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B454" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C454">
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E454" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F454" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G454" s="1">
-        <v>46258</v>
+        <v>46227</v>
       </c>
       <c r="H454" s="1">
-        <v>46258</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B455" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C455">
         <v>1</v>
       </c>
       <c r="D455" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E455" t="s">
-        <v>871</v>
+        <v>57</v>
       </c>
       <c r="F455" t="s">
-        <v>872</v>
+        <v>58</v>
       </c>
       <c r="G455" s="1">
-        <v>46262</v>
+        <v>46227</v>
       </c>
       <c r="H455" s="1">
-        <v>46265</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B456" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C456">
         <v>1</v>
@@ -14999,15 +15077,483 @@
         <v>6</v>
       </c>
       <c r="E456" t="s">
+        <v>57</v>
+      </c>
+      <c r="F456" t="s">
+        <v>58</v>
+      </c>
+      <c r="G456" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H456" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>866</v>
+      </c>
+      <c r="B457" t="s">
+        <v>887</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>6</v>
+      </c>
+      <c r="E457" t="s">
+        <v>77</v>
+      </c>
+      <c r="F457" t="s">
+        <v>78</v>
+      </c>
+      <c r="G457" s="1">
+        <v>46230</v>
+      </c>
+      <c r="H457" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>866</v>
+      </c>
+      <c r="B458" t="s">
+        <v>888</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+      <c r="D458" t="s">
+        <v>6</v>
+      </c>
+      <c r="E458" t="s">
+        <v>57</v>
+      </c>
+      <c r="F458" t="s">
+        <v>58</v>
+      </c>
+      <c r="G458" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H458" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>866</v>
+      </c>
+      <c r="B459" t="s">
+        <v>889</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+      <c r="D459" t="s">
+        <v>6</v>
+      </c>
+      <c r="E459" t="s">
+        <v>57</v>
+      </c>
+      <c r="F459" t="s">
+        <v>58</v>
+      </c>
+      <c r="G459" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H459" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>866</v>
+      </c>
+      <c r="B460" t="s">
+        <v>890</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460" t="s">
+        <v>2</v>
+      </c>
+      <c r="E460" t="s">
+        <v>57</v>
+      </c>
+      <c r="F460" t="s">
+        <v>58</v>
+      </c>
+      <c r="G460" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H460" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>866</v>
+      </c>
+      <c r="B461" t="s">
+        <v>891</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="s">
+        <v>6</v>
+      </c>
+      <c r="E461" t="s">
+        <v>57</v>
+      </c>
+      <c r="F461" t="s">
+        <v>58</v>
+      </c>
+      <c r="G461" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H461" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>866</v>
+      </c>
+      <c r="B462" t="s">
+        <v>892</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462" t="s">
+        <v>6</v>
+      </c>
+      <c r="E462" t="s">
+        <v>57</v>
+      </c>
+      <c r="F462" t="s">
+        <v>58</v>
+      </c>
+      <c r="G462" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H462" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>866</v>
+      </c>
+      <c r="B463" t="s">
+        <v>893</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463" t="s">
+        <v>6</v>
+      </c>
+      <c r="E463" t="s">
+        <v>57</v>
+      </c>
+      <c r="F463" t="s">
+        <v>58</v>
+      </c>
+      <c r="G463" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H463" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>866</v>
+      </c>
+      <c r="B464" t="s">
+        <v>894</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+      <c r="D464" t="s">
+        <v>170</v>
+      </c>
+      <c r="E464" t="s">
+        <v>57</v>
+      </c>
+      <c r="F464" t="s">
+        <v>58</v>
+      </c>
+      <c r="G464" s="1">
+        <v>46303</v>
+      </c>
+      <c r="H464" s="1">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>895</v>
+      </c>
+      <c r="B465" t="s">
+        <v>896</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+      <c r="D465" t="s">
+        <v>2</v>
+      </c>
+      <c r="E465" t="s">
+        <v>897</v>
+      </c>
+      <c r="F465" t="s">
+        <v>898</v>
+      </c>
+      <c r="G465" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H465" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>895</v>
+      </c>
+      <c r="B466" t="s">
+        <v>899</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+      <c r="D466" t="s">
+        <v>2</v>
+      </c>
+      <c r="E466" t="s">
+        <v>900</v>
+      </c>
+      <c r="F466" t="s">
+        <v>901</v>
+      </c>
+      <c r="G466" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H466" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>895</v>
+      </c>
+      <c r="B467" t="s">
+        <v>902</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467" t="s">
+        <v>2</v>
+      </c>
+      <c r="E467" t="s">
+        <v>897</v>
+      </c>
+      <c r="F467" t="s">
+        <v>898</v>
+      </c>
+      <c r="G467" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H467" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>895</v>
+      </c>
+      <c r="B468" t="s">
+        <v>903</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="D468" t="s">
+        <v>2</v>
+      </c>
+      <c r="E468" t="s">
+        <v>897</v>
+      </c>
+      <c r="F468" t="s">
+        <v>898</v>
+      </c>
+      <c r="G468" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H468" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>895</v>
+      </c>
+      <c r="B469" t="s">
+        <v>904</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469" t="s">
+        <v>2</v>
+      </c>
+      <c r="E469" t="s">
+        <v>897</v>
+      </c>
+      <c r="F469" t="s">
+        <v>898</v>
+      </c>
+      <c r="G469" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H469" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>895</v>
+      </c>
+      <c r="B470" t="s">
+        <v>905</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470" t="s">
+        <v>2</v>
+      </c>
+      <c r="E470" t="s">
+        <v>906</v>
+      </c>
+      <c r="F470" t="s">
+        <v>907</v>
+      </c>
+      <c r="G470" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H470" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>895</v>
+      </c>
+      <c r="B471" t="s">
+        <v>908</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+      <c r="D471" t="s">
+        <v>2</v>
+      </c>
+      <c r="E471" t="s">
+        <v>897</v>
+      </c>
+      <c r="F471" t="s">
+        <v>898</v>
+      </c>
+      <c r="G471" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H471" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>895</v>
+      </c>
+      <c r="B472" t="s">
+        <v>909</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+      <c r="D472" t="s">
+        <v>2</v>
+      </c>
+      <c r="E472" t="s">
+        <v>897</v>
+      </c>
+      <c r="F472" t="s">
+        <v>898</v>
+      </c>
+      <c r="G472" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H472" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>895</v>
+      </c>
+      <c r="B473" t="s">
+        <v>910</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473" t="s">
+        <v>2</v>
+      </c>
+      <c r="E473" t="s">
+        <v>897</v>
+      </c>
+      <c r="F473" t="s">
+        <v>898</v>
+      </c>
+      <c r="G473" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H473" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>895</v>
+      </c>
+      <c r="B474" t="s">
+        <v>911</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+      <c r="D474" t="s">
+        <v>6</v>
+      </c>
+      <c r="E474" t="s">
         <v>13</v>
       </c>
-      <c r="F456" t="s">
+      <c r="F474" t="s">
         <v>14</v>
       </c>
-      <c r="G456" s="1">
+      <c r="G474" s="1">
         <v>46281</v>
       </c>
-      <c r="H456" s="1">
+      <c r="H474" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BC9DD9E-D56E-40A1-AA26-2BDC9B7CB940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B9876D3-807C-4034-A5EC-B42D9524EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{2469D4A9-4E8A-4DD7-BBF2-FEA8318F9B4F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{D2CB09EE-8AA8-4E23-BE9E-BB5DBEBD4743}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="810">
   <si>
     <t>0001</t>
   </si>
@@ -934,12 +934,6 @@
     <t>HWANG ERIC -SANITARIOS DANIEL</t>
   </si>
   <si>
-    <t xml:space="preserve">  216679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  216680</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216707</t>
   </si>
   <si>
@@ -997,9 +991,6 @@
     <t>BRUNETTI ADRIANA NOEMI</t>
   </si>
   <si>
-    <t xml:space="preserve">  216776</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216781</t>
   </si>
   <si>
@@ -1045,9 +1036,6 @@
     <t>COSTA CALCAGNO SRL</t>
   </si>
   <si>
-    <t xml:space="preserve">  216841</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216845</t>
   </si>
   <si>
@@ -1081,9 +1069,6 @@
     <t>MERMOZ S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  216886</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216893</t>
   </si>
   <si>
@@ -1138,15 +1123,6 @@
     <t>BETOMAT S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  216948</t>
-  </si>
-  <si>
-    <t>FA30</t>
-  </si>
-  <si>
-    <t>FAMACON ALEM S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216950</t>
   </si>
   <si>
@@ -1159,9 +1135,6 @@
     <t xml:space="preserve">  216951</t>
   </si>
   <si>
-    <t xml:space="preserve">  216953</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216954</t>
   </si>
   <si>
@@ -1216,33 +1189,6 @@
     <t>AREVALO LUIS AGUSTIN</t>
   </si>
   <si>
-    <t xml:space="preserve">  216985</t>
-  </si>
-  <si>
-    <t>GA31</t>
-  </si>
-  <si>
-    <t>GALBAHIA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  216988</t>
-  </si>
-  <si>
-    <t>EC11</t>
-  </si>
-  <si>
-    <t>ES-COR DESIGN S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217003</t>
-  </si>
-  <si>
-    <t>RC10</t>
-  </si>
-  <si>
-    <t>RAN CO MATERIALES S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217008</t>
   </si>
   <si>
@@ -1273,21 +1219,9 @@
     <t>BURIAN MARIA ALEJANDRA</t>
   </si>
   <si>
-    <t xml:space="preserve">  217042</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217047</t>
   </si>
   <si>
-    <t xml:space="preserve">  217049</t>
-  </si>
-  <si>
-    <t>CM54</t>
-  </si>
-  <si>
-    <t>CERRITO MATERIALES S.A.S.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217050</t>
   </si>
   <si>
@@ -1297,9 +1231,6 @@
     <t xml:space="preserve">  217052</t>
   </si>
   <si>
-    <t xml:space="preserve">  217054</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217055</t>
   </si>
   <si>
@@ -1315,15 +1246,6 @@
     <t>EDEN SANITARIOS S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217058</t>
-  </si>
-  <si>
-    <t>LE19</t>
-  </si>
-  <si>
-    <t>LA ELENA SOCIEDAD ANONIMA</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217062</t>
   </si>
   <si>
@@ -1354,15 +1276,6 @@
     <t xml:space="preserve">  217076</t>
   </si>
   <si>
-    <t xml:space="preserve">  217077</t>
-  </si>
-  <si>
-    <t>EV02</t>
-  </si>
-  <si>
-    <t>ESTRUCTURAS VEGA SRL</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217081</t>
   </si>
   <si>
@@ -1408,33 +1321,6 @@
     <t>CEFALU S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217093</t>
-  </si>
-  <si>
-    <t>VN02</t>
-  </si>
-  <si>
-    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217095</t>
-  </si>
-  <si>
-    <t>CA54</t>
-  </si>
-  <si>
-    <t>MIMAT MATERIALES SA - CASA ALEKSY WASIUK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217101</t>
-  </si>
-  <si>
-    <t>SL11</t>
-  </si>
-  <si>
-    <t>SONZINI LEONARDO S. -PROTER</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217110</t>
   </si>
   <si>
@@ -1519,30 +1405,6 @@
     <t>VICTOR ALEJANDRO VEGA S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217134</t>
-  </si>
-  <si>
-    <t>RU07</t>
-  </si>
-  <si>
-    <t>RUTENIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217135</t>
-  </si>
-  <si>
-    <t>FU05</t>
-  </si>
-  <si>
-    <t>FUTURO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217137</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217138</t>
   </si>
   <si>
@@ -1639,9 +1501,6 @@
     <t xml:space="preserve">  217176</t>
   </si>
   <si>
-    <t xml:space="preserve">  217178</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217179</t>
   </si>
   <si>
@@ -1729,24 +1588,6 @@
     <t>QUBO S.A.S. - QUBO AMBIENTES</t>
   </si>
   <si>
-    <t xml:space="preserve">  217202</t>
-  </si>
-  <si>
-    <t>DR13</t>
-  </si>
-  <si>
-    <t>DOS RIZZO S. A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217203</t>
-  </si>
-  <si>
-    <t>CF02</t>
-  </si>
-  <si>
-    <t>CASA FUEGIA S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217204</t>
   </si>
   <si>
@@ -1777,7 +1618,292 @@
     <t xml:space="preserve">  217212</t>
   </si>
   <si>
-    <t xml:space="preserve">  217213</t>
+    <t xml:space="preserve">  217214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217215</t>
+  </si>
+  <si>
+    <t>AS18</t>
+  </si>
+  <si>
+    <t>ALVEAR SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217219</t>
+  </si>
+  <si>
+    <t>SO05</t>
+  </si>
+  <si>
+    <t>SANTOS OSCAR FERNANDO - ARGUAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217225</t>
+  </si>
+  <si>
+    <t>SS48</t>
+  </si>
+  <si>
+    <t>SEIP SERGIO MARCELO Y RODRIGUEZ PABLO MARTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217231</t>
+  </si>
+  <si>
+    <t>SH19</t>
+  </si>
+  <si>
+    <t>SUMA HOGAR 2021 S.R.L. -FULL HOGAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217237</t>
+  </si>
+  <si>
+    <t>DS15</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217238</t>
+  </si>
+  <si>
+    <t>SA72</t>
+  </si>
+  <si>
+    <t>SANI 3 S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217240</t>
+  </si>
+  <si>
+    <t>AL24</t>
+  </si>
+  <si>
+    <t>ALVARENGA VILLAR LUIS F.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217243</t>
+  </si>
+  <si>
+    <t>SM34</t>
+  </si>
+  <si>
+    <t>SANITARIOS MATRECARI S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217244</t>
+  </si>
+  <si>
+    <t>AN17</t>
+  </si>
+  <si>
+    <t>ANGLER S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217245</t>
+  </si>
+  <si>
+    <t>NP01</t>
+  </si>
+  <si>
+    <t>NATALI PLASTICOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217247</t>
+  </si>
+  <si>
+    <t>BA26</t>
+  </si>
+  <si>
+    <t>BOCHATAY ANDREA VIVIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217262</t>
+  </si>
+  <si>
+    <t>PO01</t>
+  </si>
+  <si>
+    <t>PORAL S.A.C.I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217265</t>
+  </si>
+  <si>
+    <t>WM03</t>
+  </si>
+  <si>
+    <t>WEN MARIANO A. -BAÑO MANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217266</t>
+  </si>
+  <si>
+    <t>MM44</t>
+  </si>
+  <si>
+    <t>MOTTESI MATERIALES SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217268</t>
+  </si>
+  <si>
+    <t>SA66</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAÑUELAS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217269</t>
+  </si>
+  <si>
+    <t>FE15</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217281</t>
+  </si>
+  <si>
+    <t>BJ19</t>
+  </si>
+  <si>
+    <t>BOLONDI JORGE A.-CORRALON MAILIN MADERAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217282</t>
+  </si>
+  <si>
+    <t>SA36</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217290</t>
+  </si>
+  <si>
+    <t>NS03</t>
+  </si>
+  <si>
+    <t>NESGAMET S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217292</t>
+  </si>
+  <si>
+    <t>GF11</t>
+  </si>
+  <si>
+    <t>GARCIA FLAVIA Y -CORRALON BRITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217293</t>
+  </si>
+  <si>
+    <t>CO28</t>
+  </si>
+  <si>
+    <t>CONSTRUDISENO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217294</t>
   </si>
   <si>
     <t>BA41</t>
@@ -1786,306 +1912,6 @@
     <t>BALCARCE 54 S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217215</t>
-  </si>
-  <si>
-    <t>AS18</t>
-  </si>
-  <si>
-    <t>ALVEAR SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217219</t>
-  </si>
-  <si>
-    <t>SO05</t>
-  </si>
-  <si>
-    <t>SANTOS OSCAR FERNANDO - ARGUAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217225</t>
-  </si>
-  <si>
-    <t>SS48</t>
-  </si>
-  <si>
-    <t>SEIP SERGIO MARCELO Y RODRIGUEZ PABLO MARTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217231</t>
-  </si>
-  <si>
-    <t>SH19</t>
-  </si>
-  <si>
-    <t>SUMA HOGAR 2021 S.R.L. -FULL HOGAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217237</t>
-  </si>
-  <si>
-    <t>DS15</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217238</t>
-  </si>
-  <si>
-    <t>SA72</t>
-  </si>
-  <si>
-    <t>SANI 3 S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217240</t>
-  </si>
-  <si>
-    <t>AL24</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217242</t>
-  </si>
-  <si>
-    <t>ED04</t>
-  </si>
-  <si>
-    <t>EDIFICOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217243</t>
-  </si>
-  <si>
-    <t>SM34</t>
-  </si>
-  <si>
-    <t>SANITARIOS MATRECARI S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217244</t>
-  </si>
-  <si>
-    <t>AN17</t>
-  </si>
-  <si>
-    <t>ANGLER S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217245</t>
-  </si>
-  <si>
-    <t>NP01</t>
-  </si>
-  <si>
-    <t>NATALI PLASTICOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217247</t>
-  </si>
-  <si>
-    <t>BA26</t>
-  </si>
-  <si>
-    <t>BOCHATAY ANDREA VIVIANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217262</t>
-  </si>
-  <si>
-    <t>PO01</t>
-  </si>
-  <si>
-    <t>PORAL S.A.C.I.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217265</t>
-  </si>
-  <si>
-    <t>WM03</t>
-  </si>
-  <si>
-    <t>WEN MARIANO A. -BAÑO MANIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217266</t>
-  </si>
-  <si>
-    <t>MM44</t>
-  </si>
-  <si>
-    <t>MOTTESI MATERIALES SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217268</t>
-  </si>
-  <si>
-    <t>SA66</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAÑUELAS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217269</t>
-  </si>
-  <si>
-    <t>FE15</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217281</t>
-  </si>
-  <si>
-    <t>BJ19</t>
-  </si>
-  <si>
-    <t>BOLONDI JORGE A.-CORRALON MAILIN MADERAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217282</t>
-  </si>
-  <si>
-    <t>SA36</t>
-  </si>
-  <si>
-    <t>SAMOT S.A.S.  -SANIPLAST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217290</t>
-  </si>
-  <si>
-    <t>NS03</t>
-  </si>
-  <si>
-    <t>NESGAMET S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217292</t>
-  </si>
-  <si>
-    <t>GF11</t>
-  </si>
-  <si>
-    <t>GARCIA FLAVIA Y -CORRALON BRITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217293</t>
-  </si>
-  <si>
-    <t>CO28</t>
-  </si>
-  <si>
-    <t>CONSTRUDISENO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217294</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217295</t>
   </si>
   <si>
@@ -2410,7 +2236,7 @@
     <t xml:space="preserve">    2912</t>
   </si>
   <si>
-    <t xml:space="preserve">    3001</t>
+    <t xml:space="preserve">    3002</t>
   </si>
   <si>
     <t>DA11</t>
@@ -2419,9 +2245,6 @@
     <t>DAFYS S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">    3002</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3004</t>
   </si>
   <si>
@@ -2543,6 +2366,9 @@
   </si>
   <si>
     <t xml:space="preserve">    2760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2781</t>
   </si>
   <si>
     <t>9999</t>
@@ -3073,34 +2899,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5E39B8-B063-4579-BD6D-96673ECA6557}">
-  <dimension ref="A1:H444"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9675168B-BF31-4FEE-B71B-A5364C0BB2C9}">
+  <dimension ref="A1:H416"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>861</v>
+        <v>803</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>862</v>
+        <v>804</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>863</v>
+        <v>805</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>864</v>
+        <v>806</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>865</v>
+        <v>807</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>866</v>
+        <v>808</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>867</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6367,10 +6193,10 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="F127" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="G127" s="1">
         <v>46295</v>
@@ -6393,16 +6219,16 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="F128" t="s">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="G128" s="1">
         <v>46295</v>
       </c>
       <c r="H128" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -6410,19 +6236,19 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E129" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="F129" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="G129" s="1">
         <v>46295</v>
@@ -6436,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -6445,16 +6271,16 @@
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
       <c r="F130" t="s">
-        <v>309</v>
+        <v>38</v>
       </c>
       <c r="G130" s="1">
         <v>46295</v>
       </c>
       <c r="H130" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -6699,7 +6525,7 @@
         <v>319</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="s">
         <v>170</v>
@@ -6714,7 +6540,7 @@
         <v>46295</v>
       </c>
       <c r="H140" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -6728,19 +6554,19 @@
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E141" t="s">
-        <v>37</v>
+        <v>321</v>
       </c>
       <c r="F141" t="s">
-        <v>38</v>
+        <v>322</v>
       </c>
       <c r="G141" s="1">
         <v>46295</v>
       </c>
       <c r="H141" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -6748,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -6757,16 +6583,16 @@
         <v>170</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>324</v>
       </c>
       <c r="F142" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="G142" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H142" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -6774,22 +6600,22 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>323</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="G143" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H143" s="1">
         <v>46296</v>
@@ -6800,13 +6626,13 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E144" t="s">
         <v>37</v>
@@ -6826,25 +6652,25 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="s">
         <v>170</v>
       </c>
       <c r="E145" t="s">
-        <v>327</v>
+        <v>37</v>
       </c>
       <c r="F145" t="s">
-        <v>328</v>
+        <v>38</v>
       </c>
       <c r="G145" s="1">
         <v>46296</v>
       </c>
       <c r="H145" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -6858,13 +6684,13 @@
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="F146" t="s">
-        <v>38</v>
+        <v>331</v>
       </c>
       <c r="G146" s="1">
         <v>46296</v>
@@ -6878,19 +6704,19 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>37</v>
+        <v>333</v>
       </c>
       <c r="F147" t="s">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="G147" s="1">
         <v>46296</v>
@@ -6904,25 +6730,25 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>336</v>
       </c>
       <c r="F148" t="s">
-        <v>38</v>
+        <v>337</v>
       </c>
       <c r="G148" s="1">
         <v>46296</v>
       </c>
       <c r="H148" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6930,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -6939,16 +6765,16 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>333</v>
+        <v>142</v>
       </c>
       <c r="F149" t="s">
-        <v>334</v>
+        <v>143</v>
       </c>
       <c r="G149" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H149" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6956,25 +6782,25 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F150" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G150" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H150" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6982,25 +6808,25 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F151" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G151" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H151" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -7008,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7017,10 +6843,10 @@
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>37</v>
+        <v>172</v>
       </c>
       <c r="F152" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="G152" s="1">
         <v>46297</v>
@@ -7034,19 +6860,19 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>142</v>
+        <v>347</v>
       </c>
       <c r="F153" t="s">
-        <v>143</v>
+        <v>348</v>
       </c>
       <c r="G153" s="1">
         <v>46297</v>
@@ -7060,19 +6886,19 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E154" t="s">
-        <v>344</v>
+        <v>37</v>
       </c>
       <c r="F154" t="s">
-        <v>345</v>
+        <v>38</v>
       </c>
       <c r="G154" s="1">
         <v>46297</v>
@@ -7086,19 +6912,19 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E155" t="s">
-        <v>347</v>
+        <v>37</v>
       </c>
       <c r="F155" t="s">
-        <v>348</v>
+        <v>38</v>
       </c>
       <c r="G155" s="1">
         <v>46297</v>
@@ -7112,19 +6938,19 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E156" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="F156" t="s">
-        <v>173</v>
+        <v>38</v>
       </c>
       <c r="G156" s="1">
         <v>46297</v>
@@ -7138,19 +6964,19 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E157" t="s">
-        <v>351</v>
+        <v>37</v>
       </c>
       <c r="F157" t="s">
-        <v>352</v>
+        <v>38</v>
       </c>
       <c r="G157" s="1">
         <v>46297</v>
@@ -7170,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E158" t="s">
         <v>37</v>
@@ -7222,19 +7048,19 @@
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>37</v>
+        <v>356</v>
       </c>
       <c r="F160" t="s">
-        <v>38</v>
+        <v>357</v>
       </c>
       <c r="G160" s="1">
         <v>46297</v>
       </c>
       <c r="H160" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -7242,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7251,16 +7077,16 @@
         <v>170</v>
       </c>
       <c r="E161" t="s">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="F161" t="s">
-        <v>38</v>
+        <v>360</v>
       </c>
       <c r="G161" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H161" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -7268,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7277,16 +7103,16 @@
         <v>170</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>362</v>
       </c>
       <c r="F162" t="s">
-        <v>38</v>
+        <v>363</v>
       </c>
       <c r="G162" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H162" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -7294,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7303,16 +7129,16 @@
         <v>170</v>
       </c>
       <c r="E163" t="s">
-        <v>37</v>
+        <v>365</v>
       </c>
       <c r="F163" t="s">
-        <v>38</v>
+        <v>366</v>
       </c>
       <c r="G163" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H163" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -7320,25 +7146,25 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>37</v>
+        <v>368</v>
       </c>
       <c r="F164" t="s">
-        <v>38</v>
+        <v>369</v>
       </c>
       <c r="G164" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H164" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -7346,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7355,13 +7181,13 @@
         <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>361</v>
+        <v>142</v>
       </c>
       <c r="F165" t="s">
-        <v>362</v>
+        <v>143</v>
       </c>
       <c r="G165" s="1">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H165" s="1">
         <v>46300</v>
@@ -7372,19 +7198,19 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>364</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="G166" s="1">
         <v>46300</v>
@@ -7398,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7407,10 +7233,10 @@
         <v>170</v>
       </c>
       <c r="E167" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F167" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G167" s="1">
         <v>46300</v>
@@ -7424,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7433,10 +7259,10 @@
         <v>170</v>
       </c>
       <c r="E168" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F168" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="G168" s="1">
         <v>46300</v>
@@ -7450,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7459,10 +7285,10 @@
         <v>170</v>
       </c>
       <c r="E169" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="F169" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="G169" s="1">
         <v>46300</v>
@@ -7476,19 +7302,19 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E170" t="s">
-        <v>376</v>
+        <v>321</v>
       </c>
       <c r="F170" t="s">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="G170" s="1">
         <v>46300</v>
@@ -7502,19 +7328,19 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E171" t="s">
-        <v>142</v>
+        <v>381</v>
       </c>
       <c r="F171" t="s">
-        <v>143</v>
+        <v>382</v>
       </c>
       <c r="G171" s="1">
         <v>46300</v>
@@ -7528,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7537,10 +7363,10 @@
         <v>170</v>
       </c>
       <c r="E172" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="F172" t="s">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="G172" s="1">
         <v>46300</v>
@@ -7554,19 +7380,19 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E173" t="s">
-        <v>25</v>
+        <v>381</v>
       </c>
       <c r="F173" t="s">
-        <v>26</v>
+        <v>382</v>
       </c>
       <c r="G173" s="1">
         <v>46300</v>
@@ -7580,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7589,10 +7415,10 @@
         <v>170</v>
       </c>
       <c r="E174" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="F174" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G174" s="1">
         <v>46300</v>
@@ -7606,19 +7432,19 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F175" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G175" s="1">
         <v>46300</v>
@@ -7632,25 +7458,25 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" t="s">
         <v>170</v>
       </c>
       <c r="E176" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="F176" t="s">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="G176" s="1">
         <v>46300</v>
       </c>
       <c r="H176" s="1">
-        <v>46300</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -7658,25 +7484,25 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D177" t="s">
         <v>170</v>
       </c>
       <c r="E177" t="s">
-        <v>323</v>
+        <v>393</v>
       </c>
       <c r="F177" t="s">
-        <v>324</v>
+        <v>394</v>
       </c>
       <c r="G177" s="1">
         <v>46300</v>
       </c>
       <c r="H177" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -7684,25 +7510,25 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="s">
         <v>170</v>
       </c>
       <c r="E178" t="s">
-        <v>390</v>
+        <v>22</v>
       </c>
       <c r="F178" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="G178" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H178" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -7710,25 +7536,25 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
       <c r="F179" t="s">
-        <v>38</v>
+        <v>398</v>
       </c>
       <c r="G179" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H179" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -7736,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7745,16 +7571,16 @@
         <v>170</v>
       </c>
       <c r="E180" t="s">
-        <v>390</v>
+        <v>86</v>
       </c>
       <c r="F180" t="s">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="G180" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H180" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -7762,25 +7588,25 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="F181" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="G181" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H181" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -7788,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7797,16 +7623,16 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="F182" t="s">
-        <v>397</v>
+        <v>38</v>
       </c>
       <c r="G182" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H182" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -7814,25 +7640,25 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>399</v>
+        <v>37</v>
       </c>
       <c r="F183" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="G183" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H183" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -7840,25 +7666,25 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>402</v>
+        <v>37</v>
       </c>
       <c r="F184" t="s">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="G184" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H184" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7872,19 +7698,19 @@
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>405</v>
+        <v>37</v>
       </c>
       <c r="F185" t="s">
-        <v>406</v>
+        <v>38</v>
       </c>
       <c r="G185" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H185" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -7892,25 +7718,25 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
+        <v>405</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>170</v>
+      </c>
+      <c r="E186" t="s">
+        <v>406</v>
+      </c>
+      <c r="F186" t="s">
         <v>407</v>
       </c>
-      <c r="C186">
-        <v>2</v>
-      </c>
-      <c r="D186" t="s">
-        <v>170</v>
-      </c>
-      <c r="E186" t="s">
-        <v>408</v>
-      </c>
-      <c r="F186" t="s">
-        <v>409</v>
-      </c>
       <c r="G186" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H186" s="1">
-        <v>46303</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -7918,25 +7744,25 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
+        <v>408</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>2</v>
+      </c>
+      <c r="E187" t="s">
+        <v>409</v>
+      </c>
+      <c r="F187" t="s">
         <v>410</v>
       </c>
-      <c r="C187">
-        <v>2</v>
-      </c>
-      <c r="D187" t="s">
-        <v>170</v>
-      </c>
-      <c r="E187" t="s">
-        <v>411</v>
-      </c>
-      <c r="F187" t="s">
-        <v>412</v>
-      </c>
       <c r="G187" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H187" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
@@ -7944,25 +7770,25 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
+        <v>411</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>170</v>
+      </c>
+      <c r="E188" t="s">
+        <v>412</v>
+      </c>
+      <c r="F188" t="s">
         <v>413</v>
-      </c>
-      <c r="C188">
-        <v>2</v>
-      </c>
-      <c r="D188" t="s">
-        <v>170</v>
-      </c>
-      <c r="E188" t="s">
-        <v>22</v>
-      </c>
-      <c r="F188" t="s">
-        <v>23</v>
       </c>
       <c r="G188" s="1">
         <v>46301</v>
       </c>
       <c r="H188" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
@@ -7976,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E189" t="s">
         <v>415</v>
@@ -8002,13 +7828,13 @@
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E190" t="s">
-        <v>86</v>
+        <v>365</v>
       </c>
       <c r="F190" t="s">
-        <v>87</v>
+        <v>366</v>
       </c>
       <c r="G190" s="1">
         <v>46301</v>
@@ -8031,10 +7857,10 @@
         <v>170</v>
       </c>
       <c r="E191" t="s">
-        <v>86</v>
+        <v>419</v>
       </c>
       <c r="F191" t="s">
-        <v>87</v>
+        <v>420</v>
       </c>
       <c r="G191" s="1">
         <v>46301</v>
@@ -8048,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -8057,10 +7883,10 @@
         <v>170</v>
       </c>
       <c r="E192" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F192" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G192" s="1">
         <v>46301</v>
@@ -8074,19 +7900,19 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E193" t="s">
-        <v>37</v>
+        <v>425</v>
       </c>
       <c r="F193" t="s">
-        <v>38</v>
+        <v>426</v>
       </c>
       <c r="G193" s="1">
         <v>46301</v>
@@ -8100,19 +7926,19 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E194" t="s">
-        <v>37</v>
+        <v>428</v>
       </c>
       <c r="F194" t="s">
-        <v>38</v>
+        <v>429</v>
       </c>
       <c r="G194" s="1">
         <v>46301</v>
@@ -8126,19 +7952,19 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E195" t="s">
-        <v>37</v>
+        <v>431</v>
       </c>
       <c r="F195" t="s">
-        <v>38</v>
+        <v>432</v>
       </c>
       <c r="G195" s="1">
         <v>46301</v>
@@ -8152,19 +7978,19 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E196" t="s">
-        <v>37</v>
+        <v>434</v>
       </c>
       <c r="F196" t="s">
-        <v>38</v>
+        <v>435</v>
       </c>
       <c r="G196" s="1">
         <v>46301</v>
@@ -8178,19 +8004,19 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E197" t="s">
-        <v>37</v>
+        <v>437</v>
       </c>
       <c r="F197" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="G197" s="1">
         <v>46301</v>
@@ -8204,19 +8030,19 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E198" t="s">
-        <v>37</v>
+        <v>437</v>
       </c>
       <c r="F198" t="s">
-        <v>38</v>
+        <v>438</v>
       </c>
       <c r="G198" s="1">
         <v>46301</v>
@@ -8230,7 +8056,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -8239,16 +8065,16 @@
         <v>170</v>
       </c>
       <c r="E199" t="s">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="F199" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="G199" s="1">
         <v>46301</v>
       </c>
       <c r="H199" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -8256,25 +8082,25 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>432</v>
+        <v>37</v>
       </c>
       <c r="F200" t="s">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="G200" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H200" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -8282,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -8291,16 +8117,16 @@
         <v>170</v>
       </c>
       <c r="E201" t="s">
-        <v>435</v>
+        <v>255</v>
       </c>
       <c r="F201" t="s">
-        <v>436</v>
+        <v>256</v>
       </c>
       <c r="G201" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H201" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -8308,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -8317,16 +8143,16 @@
         <v>170</v>
       </c>
       <c r="E202" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F202" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G202" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H202" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -8334,25 +8160,25 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F203" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G203" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H203" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -8360,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -8369,16 +8195,16 @@
         <v>170</v>
       </c>
       <c r="E204" t="s">
-        <v>370</v>
+        <v>450</v>
       </c>
       <c r="F204" t="s">
-        <v>371</v>
+        <v>451</v>
       </c>
       <c r="G204" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H204" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -8386,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -8395,16 +8221,16 @@
         <v>170</v>
       </c>
       <c r="E205" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="F205" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="G205" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H205" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -8412,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -8421,16 +8247,16 @@
         <v>170</v>
       </c>
       <c r="E206" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F206" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="G206" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H206" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -8438,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -8447,16 +8273,16 @@
         <v>170</v>
       </c>
       <c r="E207" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F207" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G207" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H207" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -8464,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -8473,16 +8299,16 @@
         <v>170</v>
       </c>
       <c r="E208" t="s">
-        <v>454</v>
+        <v>273</v>
       </c>
       <c r="F208" t="s">
-        <v>455</v>
+        <v>274</v>
       </c>
       <c r="G208" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H208" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -8490,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -8499,16 +8325,16 @@
         <v>170</v>
       </c>
       <c r="E209" t="s">
-        <v>457</v>
+        <v>273</v>
       </c>
       <c r="F209" t="s">
-        <v>458</v>
+        <v>274</v>
       </c>
       <c r="G209" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H209" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -8516,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -8525,16 +8351,16 @@
         <v>170</v>
       </c>
       <c r="E210" t="s">
-        <v>460</v>
+        <v>16</v>
       </c>
       <c r="F210" t="s">
-        <v>461</v>
+        <v>17</v>
       </c>
       <c r="G210" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H210" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -8542,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -8551,16 +8377,16 @@
         <v>170</v>
       </c>
       <c r="E211" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F211" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G211" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H211" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -8568,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -8577,16 +8403,16 @@
         <v>170</v>
       </c>
       <c r="E212" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F212" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G212" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H212" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
@@ -8594,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -8603,16 +8429,16 @@
         <v>170</v>
       </c>
       <c r="E213" t="s">
-        <v>469</v>
+        <v>142</v>
       </c>
       <c r="F213" t="s">
-        <v>470</v>
+        <v>143</v>
       </c>
       <c r="G213" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H213" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -8626,19 +8452,19 @@
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>472</v>
+        <v>185</v>
       </c>
       <c r="F214" t="s">
-        <v>473</v>
+        <v>186</v>
       </c>
       <c r="G214" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H214" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -8646,25 +8472,25 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D215" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>475</v>
+        <v>48</v>
       </c>
       <c r="F215" t="s">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="G215" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H215" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -8672,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8681,16 +8507,16 @@
         <v>170</v>
       </c>
       <c r="E216" t="s">
+        <v>474</v>
+      </c>
+      <c r="F216" t="s">
         <v>475</v>
       </c>
-      <c r="F216" t="s">
-        <v>476</v>
-      </c>
       <c r="G216" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H216" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -8698,22 +8524,22 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
+        <v>476</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217" t="s">
+        <v>170</v>
+      </c>
+      <c r="E217" t="s">
+        <v>477</v>
+      </c>
+      <c r="F217" t="s">
         <v>478</v>
       </c>
-      <c r="C217">
-        <v>1</v>
-      </c>
-      <c r="D217" t="s">
-        <v>170</v>
-      </c>
-      <c r="E217" t="s">
-        <v>382</v>
-      </c>
-      <c r="F217" t="s">
-        <v>383</v>
-      </c>
       <c r="G217" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H217" s="1">
         <v>46302</v>
@@ -8733,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="F218" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="G218" s="1">
         <v>46302</v>
@@ -8759,10 +8585,10 @@
         <v>170</v>
       </c>
       <c r="E219" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="F219" t="s">
-        <v>256</v>
+        <v>435</v>
       </c>
       <c r="G219" s="1">
         <v>46302</v>
@@ -8808,13 +8634,13 @@
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E221" t="s">
-        <v>485</v>
+        <v>37</v>
       </c>
       <c r="F221" t="s">
-        <v>486</v>
+        <v>38</v>
       </c>
       <c r="G221" s="1">
         <v>46302</v>
@@ -8828,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -8837,10 +8663,10 @@
         <v>170</v>
       </c>
       <c r="E222" t="s">
-        <v>488</v>
+        <v>37</v>
       </c>
       <c r="F222" t="s">
-        <v>489</v>
+        <v>38</v>
       </c>
       <c r="G222" s="1">
         <v>46302</v>
@@ -8854,19 +8680,19 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F223" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G223" s="1">
         <v>46302</v>
@@ -8880,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8889,10 +8715,10 @@
         <v>170</v>
       </c>
       <c r="E224" t="s">
-        <v>494</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
-        <v>495</v>
+        <v>38</v>
       </c>
       <c r="G224" s="1">
         <v>46302</v>
@@ -8906,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -8915,10 +8741,10 @@
         <v>170</v>
       </c>
       <c r="E225" t="s">
-        <v>497</v>
+        <v>37</v>
       </c>
       <c r="F225" t="s">
-        <v>498</v>
+        <v>38</v>
       </c>
       <c r="G225" s="1">
         <v>46302</v>
@@ -8932,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -8941,10 +8767,10 @@
         <v>170</v>
       </c>
       <c r="E226" t="s">
-        <v>500</v>
+        <v>37</v>
       </c>
       <c r="F226" t="s">
-        <v>501</v>
+        <v>38</v>
       </c>
       <c r="G226" s="1">
         <v>46302</v>
@@ -8958,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8967,10 +8793,10 @@
         <v>170</v>
       </c>
       <c r="E227" t="s">
-        <v>503</v>
+        <v>37</v>
       </c>
       <c r="F227" t="s">
-        <v>504</v>
+        <v>38</v>
       </c>
       <c r="G227" s="1">
         <v>46302</v>
@@ -8984,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -8993,10 +8819,10 @@
         <v>170</v>
       </c>
       <c r="E228" t="s">
-        <v>503</v>
+        <v>37</v>
       </c>
       <c r="F228" t="s">
-        <v>504</v>
+        <v>38</v>
       </c>
       <c r="G228" s="1">
         <v>46302</v>
@@ -9010,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -9019,10 +8845,10 @@
         <v>170</v>
       </c>
       <c r="E229" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F229" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G229" s="1">
         <v>46302</v>
@@ -9036,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -9045,10 +8871,10 @@
         <v>170</v>
       </c>
       <c r="E230" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="F230" t="s">
-        <v>274</v>
+        <v>38</v>
       </c>
       <c r="G230" s="1">
         <v>46302</v>
@@ -9062,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -9071,10 +8897,10 @@
         <v>170</v>
       </c>
       <c r="E231" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="F231" t="s">
-        <v>274</v>
+        <v>38</v>
       </c>
       <c r="G231" s="1">
         <v>46302</v>
@@ -9088,7 +8914,7 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -9097,10 +8923,10 @@
         <v>170</v>
       </c>
       <c r="E232" t="s">
-        <v>16</v>
+        <v>498</v>
       </c>
       <c r="F232" t="s">
-        <v>17</v>
+        <v>499</v>
       </c>
       <c r="G232" s="1">
         <v>46302</v>
@@ -9114,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -9123,10 +8949,10 @@
         <v>170</v>
       </c>
       <c r="E233" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="F233" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="G233" s="1">
         <v>46302</v>
@@ -9140,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9149,16 +8975,16 @@
         <v>170</v>
       </c>
       <c r="E234" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="F234" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="G234" s="1">
         <v>46302</v>
       </c>
       <c r="H234" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -9166,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9175,16 +9001,16 @@
         <v>170</v>
       </c>
       <c r="E235" t="s">
-        <v>142</v>
+        <v>502</v>
       </c>
       <c r="F235" t="s">
-        <v>143</v>
+        <v>503</v>
       </c>
       <c r="G235" s="1">
         <v>46302</v>
       </c>
       <c r="H235" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -9192,25 +9018,25 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E236" t="s">
-        <v>185</v>
+        <v>506</v>
       </c>
       <c r="F236" t="s">
-        <v>186</v>
+        <v>507</v>
       </c>
       <c r="G236" s="1">
         <v>46302</v>
       </c>
       <c r="H236" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -9218,25 +9044,25 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E237" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F237" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G237" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H237" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -9244,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9253,16 +9079,16 @@
         <v>170</v>
       </c>
       <c r="E238" t="s">
-        <v>520</v>
+        <v>37</v>
       </c>
       <c r="F238" t="s">
-        <v>521</v>
+        <v>38</v>
       </c>
       <c r="G238" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H238" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -9270,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9279,16 +9105,16 @@
         <v>170</v>
       </c>
       <c r="E239" t="s">
-        <v>523</v>
+        <v>37</v>
       </c>
       <c r="F239" t="s">
-        <v>524</v>
+        <v>38</v>
       </c>
       <c r="G239" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H239" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -9296,25 +9122,25 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E240" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="F240" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="G240" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H240" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -9322,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9331,16 +9157,16 @@
         <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="F241" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="G241" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H241" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -9348,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9357,16 +9183,16 @@
         <v>170</v>
       </c>
       <c r="E242" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="F242" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="G242" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H242" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -9374,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9383,16 +9209,16 @@
         <v>170</v>
       </c>
       <c r="E243" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="F243" t="s">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="G243" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H243" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -9400,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9409,16 +9235,16 @@
         <v>170</v>
       </c>
       <c r="E244" t="s">
-        <v>37</v>
+        <v>520</v>
       </c>
       <c r="F244" t="s">
-        <v>38</v>
+        <v>521</v>
       </c>
       <c r="G244" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H244" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -9426,25 +9252,25 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E245" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="F245" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="G245" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H245" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -9452,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9461,16 +9287,16 @@
         <v>170</v>
       </c>
       <c r="E246" t="s">
-        <v>37</v>
+        <v>264</v>
       </c>
       <c r="F246" t="s">
-        <v>38</v>
+        <v>265</v>
       </c>
       <c r="G246" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H246" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -9478,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9487,16 +9313,16 @@
         <v>170</v>
       </c>
       <c r="E247" t="s">
-        <v>37</v>
+        <v>527</v>
       </c>
       <c r="F247" t="s">
-        <v>38</v>
+        <v>528</v>
       </c>
       <c r="G247" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H247" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -9504,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9513,16 +9339,16 @@
         <v>170</v>
       </c>
       <c r="E248" t="s">
-        <v>37</v>
+        <v>376</v>
       </c>
       <c r="F248" t="s">
-        <v>38</v>
+        <v>377</v>
       </c>
       <c r="G248" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H248" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -9530,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9539,16 +9365,16 @@
         <v>170</v>
       </c>
       <c r="E249" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F249" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G249" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H249" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -9556,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9565,16 +9391,16 @@
         <v>170</v>
       </c>
       <c r="E250" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="F250" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="G250" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H250" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -9582,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9591,16 +9417,16 @@
         <v>170</v>
       </c>
       <c r="E251" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F251" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G251" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H251" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -9608,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9617,16 +9443,16 @@
         <v>170</v>
       </c>
       <c r="E252" t="s">
-        <v>37</v>
+        <v>534</v>
       </c>
       <c r="F252" t="s">
-        <v>38</v>
+        <v>535</v>
       </c>
       <c r="G252" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H252" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -9634,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9643,16 +9469,16 @@
         <v>170</v>
       </c>
       <c r="E253" t="s">
-        <v>37</v>
+        <v>537</v>
       </c>
       <c r="F253" t="s">
-        <v>38</v>
+        <v>538</v>
       </c>
       <c r="G253" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H253" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
@@ -9660,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9669,16 +9495,16 @@
         <v>170</v>
       </c>
       <c r="E254" t="s">
-        <v>37</v>
+        <v>537</v>
       </c>
       <c r="F254" t="s">
-        <v>38</v>
+        <v>538</v>
       </c>
       <c r="G254" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H254" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -9686,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9695,16 +9521,16 @@
         <v>170</v>
       </c>
       <c r="E255" t="s">
-        <v>545</v>
+        <v>16</v>
       </c>
       <c r="F255" t="s">
-        <v>546</v>
+        <v>17</v>
       </c>
       <c r="G255" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H255" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -9712,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9721,16 +9547,16 @@
         <v>170</v>
       </c>
       <c r="E256" t="s">
-        <v>545</v>
+        <v>273</v>
       </c>
       <c r="F256" t="s">
-        <v>546</v>
+        <v>274</v>
       </c>
       <c r="G256" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H256" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -9738,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9747,13 +9573,13 @@
         <v>170</v>
       </c>
       <c r="E257" t="s">
-        <v>549</v>
+        <v>37</v>
       </c>
       <c r="F257" t="s">
-        <v>550</v>
+        <v>38</v>
       </c>
       <c r="G257" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H257" s="1">
         <v>46303</v>
@@ -9764,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9773,13 +9599,13 @@
         <v>170</v>
       </c>
       <c r="E258" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F258" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G258" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H258" s="1">
         <v>46303</v>
@@ -9790,22 +9616,22 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="F259" t="s">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="G259" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H259" s="1">
         <v>46303</v>
@@ -9816,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9825,10 +9651,10 @@
         <v>170</v>
       </c>
       <c r="E260" t="s">
-        <v>37</v>
+        <v>548</v>
       </c>
       <c r="F260" t="s">
-        <v>38</v>
+        <v>549</v>
       </c>
       <c r="G260" s="1">
         <v>46303</v>
@@ -9842,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9851,10 +9677,10 @@
         <v>170</v>
       </c>
       <c r="E261" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F261" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G261" s="1">
         <v>46303</v>
@@ -9868,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9877,10 +9703,10 @@
         <v>170</v>
       </c>
       <c r="E262" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F262" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G262" s="1">
         <v>46303</v>
@@ -9894,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9903,10 +9729,10 @@
         <v>170</v>
       </c>
       <c r="E263" t="s">
-        <v>37</v>
+        <v>553</v>
       </c>
       <c r="F263" t="s">
-        <v>38</v>
+        <v>554</v>
       </c>
       <c r="G263" s="1">
         <v>46303</v>
@@ -9920,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9929,10 +9755,10 @@
         <v>170</v>
       </c>
       <c r="E264" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F264" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G264" s="1">
         <v>46303</v>
@@ -9946,19 +9772,19 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>563</v>
+        <v>270</v>
       </c>
       <c r="F265" t="s">
-        <v>564</v>
+        <v>271</v>
       </c>
       <c r="G265" s="1">
         <v>46303</v>
@@ -9972,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9981,10 +9807,10 @@
         <v>170</v>
       </c>
       <c r="E266" t="s">
-        <v>204</v>
+        <v>560</v>
       </c>
       <c r="F266" t="s">
-        <v>205</v>
+        <v>561</v>
       </c>
       <c r="G266" s="1">
         <v>46303</v>
@@ -9998,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -10007,10 +9833,10 @@
         <v>170</v>
       </c>
       <c r="E267" t="s">
-        <v>567</v>
+        <v>255</v>
       </c>
       <c r="F267" t="s">
-        <v>568</v>
+        <v>256</v>
       </c>
       <c r="G267" s="1">
         <v>46303</v>
@@ -10024,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -10033,10 +9859,10 @@
         <v>170</v>
       </c>
       <c r="E268" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="F268" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="G268" s="1">
         <v>46303</v>
@@ -10050,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -10059,10 +9885,10 @@
         <v>170</v>
       </c>
       <c r="E269" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F269" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="G269" s="1">
         <v>46303</v>
@@ -10076,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -10085,10 +9911,10 @@
         <v>170</v>
       </c>
       <c r="E270" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="F270" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="G270" s="1">
         <v>46303</v>
@@ -10102,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -10111,10 +9937,10 @@
         <v>170</v>
       </c>
       <c r="E271" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
       <c r="F271" t="s">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="G271" s="1">
         <v>46303</v>
@@ -10128,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -10137,10 +9963,10 @@
         <v>170</v>
       </c>
       <c r="E272" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="F272" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="G272" s="1">
         <v>46303</v>
@@ -10154,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -10163,10 +9989,10 @@
         <v>170</v>
       </c>
       <c r="E273" t="s">
-        <v>385</v>
+        <v>299</v>
       </c>
       <c r="F273" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="G273" s="1">
         <v>46303</v>
@@ -10180,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -10189,10 +10015,10 @@
         <v>170</v>
       </c>
       <c r="E274" t="s">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="F274" t="s">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="G274" s="1">
         <v>46303</v>
@@ -10206,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -10215,10 +10041,10 @@
         <v>170</v>
       </c>
       <c r="E275" t="s">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="F275" t="s">
-        <v>391</v>
+        <v>201</v>
       </c>
       <c r="G275" s="1">
         <v>46303</v>
@@ -10232,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -10241,16 +10067,16 @@
         <v>170</v>
       </c>
       <c r="E276" t="s">
-        <v>586</v>
+        <v>132</v>
       </c>
       <c r="F276" t="s">
-        <v>587</v>
+        <v>133</v>
       </c>
       <c r="G276" s="1">
         <v>46303</v>
       </c>
       <c r="H276" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
@@ -10258,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -10284,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -10293,10 +10119,10 @@
         <v>170</v>
       </c>
       <c r="E278" t="s">
-        <v>590</v>
+        <v>321</v>
       </c>
       <c r="F278" t="s">
-        <v>591</v>
+        <v>322</v>
       </c>
       <c r="G278" s="1">
         <v>46303</v>
@@ -10310,7 +10136,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -10319,10 +10145,10 @@
         <v>170</v>
       </c>
       <c r="E279" t="s">
-        <v>593</v>
+        <v>415</v>
       </c>
       <c r="F279" t="s">
-        <v>594</v>
+        <v>416</v>
       </c>
       <c r="G279" s="1">
         <v>46303</v>
@@ -10336,25 +10162,25 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D280" t="s">
         <v>170</v>
       </c>
       <c r="E280" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F280" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G280" s="1">
         <v>46303</v>
       </c>
       <c r="H280" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -10362,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10371,10 +10197,10 @@
         <v>170</v>
       </c>
       <c r="E281" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F281" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="G281" s="1">
         <v>46303</v>
@@ -10388,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -10397,10 +10223,10 @@
         <v>170</v>
       </c>
       <c r="E282" t="s">
-        <v>273</v>
+        <v>590</v>
       </c>
       <c r="F282" t="s">
-        <v>274</v>
+        <v>591</v>
       </c>
       <c r="G282" s="1">
         <v>46303</v>
@@ -10414,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -10423,10 +10249,10 @@
         <v>170</v>
       </c>
       <c r="E283" t="s">
-        <v>37</v>
+        <v>593</v>
       </c>
       <c r="F283" t="s">
-        <v>38</v>
+        <v>594</v>
       </c>
       <c r="G283" s="1">
         <v>46303</v>
@@ -10440,7 +10266,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -10449,10 +10275,10 @@
         <v>170</v>
       </c>
       <c r="E284" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F284" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="G284" s="1">
         <v>46303</v>
@@ -10466,19 +10292,19 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E285" t="s">
-        <v>19</v>
+        <v>587</v>
       </c>
       <c r="F285" t="s">
-        <v>20</v>
+        <v>588</v>
       </c>
       <c r="G285" s="1">
         <v>46303</v>
@@ -10492,19 +10318,19 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E286" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F286" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G286" s="1">
         <v>46303</v>
@@ -10518,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -10527,16 +10353,16 @@
         <v>170</v>
       </c>
       <c r="E287" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="F287" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="G287" s="1">
         <v>46303</v>
       </c>
       <c r="H287" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
@@ -10544,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10553,16 +10379,16 @@
         <v>170</v>
       </c>
       <c r="E288" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F288" t="s">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="G288" s="1">
         <v>46303</v>
       </c>
       <c r="H288" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
@@ -10570,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10579,16 +10405,16 @@
         <v>170</v>
       </c>
       <c r="E289" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F289" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G289" s="1">
         <v>46303</v>
       </c>
       <c r="H289" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
@@ -10596,25 +10422,25 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E290" t="s">
-        <v>610</v>
+        <v>333</v>
       </c>
       <c r="F290" t="s">
-        <v>611</v>
+        <v>334</v>
       </c>
       <c r="G290" s="1">
         <v>46303</v>
       </c>
       <c r="H290" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -10622,25 +10448,25 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E291" t="s">
-        <v>613</v>
+        <v>333</v>
       </c>
       <c r="F291" t="s">
-        <v>614</v>
+        <v>334</v>
       </c>
       <c r="G291" s="1">
         <v>46303</v>
       </c>
       <c r="H291" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
@@ -10648,25 +10474,25 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E292" t="s">
-        <v>270</v>
+        <v>606</v>
       </c>
       <c r="F292" t="s">
-        <v>271</v>
+        <v>607</v>
       </c>
       <c r="G292" s="1">
         <v>46303</v>
       </c>
       <c r="H292" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
@@ -10674,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -10683,16 +10509,16 @@
         <v>170</v>
       </c>
       <c r="E293" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F293" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G293" s="1">
         <v>46303</v>
       </c>
       <c r="H293" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -10700,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10709,16 +10535,16 @@
         <v>170</v>
       </c>
       <c r="E294" t="s">
-        <v>255</v>
+        <v>570</v>
       </c>
       <c r="F294" t="s">
-        <v>256</v>
+        <v>571</v>
       </c>
       <c r="G294" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H294" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
@@ -10726,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10735,16 +10561,16 @@
         <v>170</v>
       </c>
       <c r="E295" t="s">
-        <v>621</v>
+        <v>37</v>
       </c>
       <c r="F295" t="s">
-        <v>622</v>
+        <v>38</v>
       </c>
       <c r="G295" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H295" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -10752,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10761,16 +10587,16 @@
         <v>170</v>
       </c>
       <c r="E296" t="s">
-        <v>624</v>
+        <v>431</v>
       </c>
       <c r="F296" t="s">
-        <v>625</v>
+        <v>432</v>
       </c>
       <c r="G296" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H296" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
@@ -10778,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10787,16 +10613,16 @@
         <v>170</v>
       </c>
       <c r="E297" t="s">
-        <v>627</v>
+        <v>37</v>
       </c>
       <c r="F297" t="s">
-        <v>628</v>
+        <v>38</v>
       </c>
       <c r="G297" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H297" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
@@ -10804,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -10813,16 +10639,16 @@
         <v>170</v>
       </c>
       <c r="E298" t="s">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="F298" t="s">
-        <v>631</v>
+        <v>571</v>
       </c>
       <c r="G298" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H298" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
@@ -10830,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10839,16 +10665,16 @@
         <v>170</v>
       </c>
       <c r="E299" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="F299" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="G299" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H299" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
@@ -10856,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10865,16 +10691,16 @@
         <v>170</v>
       </c>
       <c r="E300" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="F300" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="G300" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H300" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
@@ -10882,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10891,16 +10717,16 @@
         <v>170</v>
       </c>
       <c r="E301" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="F301" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="G301" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H301" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
@@ -10908,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -10917,16 +10743,16 @@
         <v>170</v>
       </c>
       <c r="E302" t="s">
-        <v>204</v>
+        <v>622</v>
       </c>
       <c r="F302" t="s">
-        <v>205</v>
+        <v>623</v>
       </c>
       <c r="G302" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H302" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
@@ -10934,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10943,16 +10769,16 @@
         <v>170</v>
       </c>
       <c r="E303" t="s">
-        <v>200</v>
+        <v>625</v>
       </c>
       <c r="F303" t="s">
-        <v>201</v>
+        <v>626</v>
       </c>
       <c r="G303" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H303" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
@@ -10960,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10969,13 +10795,13 @@
         <v>170</v>
       </c>
       <c r="E304" t="s">
-        <v>132</v>
+        <v>628</v>
       </c>
       <c r="F304" t="s">
-        <v>133</v>
+        <v>629</v>
       </c>
       <c r="G304" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H304" s="1">
         <v>46304</v>
@@ -10986,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10995,16 +10821,16 @@
         <v>170</v>
       </c>
       <c r="E305" t="s">
-        <v>45</v>
+        <v>373</v>
       </c>
       <c r="F305" t="s">
-        <v>46</v>
+        <v>374</v>
       </c>
       <c r="G305" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H305" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
@@ -11012,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -11021,16 +10847,16 @@
         <v>170</v>
       </c>
       <c r="E306" t="s">
-        <v>323</v>
+        <v>632</v>
       </c>
       <c r="F306" t="s">
-        <v>324</v>
+        <v>633</v>
       </c>
       <c r="G306" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H306" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
@@ -11038,7 +10864,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -11047,16 +10873,16 @@
         <v>170</v>
       </c>
       <c r="E307" t="s">
-        <v>441</v>
+        <v>635</v>
       </c>
       <c r="F307" t="s">
-        <v>442</v>
+        <v>636</v>
       </c>
       <c r="G307" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H307" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
@@ -11064,22 +10890,22 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D308" t="s">
         <v>170</v>
       </c>
       <c r="E308" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="F308" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="G308" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H308" s="1">
         <v>46304</v>
@@ -11090,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -11099,16 +10925,16 @@
         <v>170</v>
       </c>
       <c r="E309" t="s">
-        <v>647</v>
+        <v>299</v>
       </c>
       <c r="F309" t="s">
-        <v>648</v>
+        <v>300</v>
       </c>
       <c r="G309" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H309" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
@@ -11116,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -11125,16 +10951,16 @@
         <v>170</v>
       </c>
       <c r="E310" t="s">
-        <v>650</v>
+        <v>16</v>
       </c>
       <c r="F310" t="s">
-        <v>651</v>
+        <v>17</v>
       </c>
       <c r="G310" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H310" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
@@ -11142,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -11151,16 +10977,16 @@
         <v>170</v>
       </c>
       <c r="E311" t="s">
-        <v>653</v>
+        <v>151</v>
       </c>
       <c r="F311" t="s">
-        <v>654</v>
+        <v>152</v>
       </c>
       <c r="G311" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H311" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
@@ -11168,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -11177,16 +11003,16 @@
         <v>170</v>
       </c>
       <c r="E312" t="s">
-        <v>656</v>
+        <v>182</v>
       </c>
       <c r="F312" t="s">
-        <v>657</v>
+        <v>183</v>
       </c>
       <c r="G312" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H312" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
@@ -11194,7 +11020,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -11203,16 +11029,16 @@
         <v>170</v>
       </c>
       <c r="E313" t="s">
-        <v>647</v>
+        <v>182</v>
       </c>
       <c r="F313" t="s">
-        <v>648</v>
+        <v>183</v>
       </c>
       <c r="G313" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H313" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
@@ -11220,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -11229,16 +11055,16 @@
         <v>170</v>
       </c>
       <c r="E314" t="s">
-        <v>80</v>
+        <v>646</v>
       </c>
       <c r="F314" t="s">
-        <v>81</v>
+        <v>647</v>
       </c>
       <c r="G314" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H314" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
@@ -11246,7 +11072,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -11255,13 +11081,13 @@
         <v>170</v>
       </c>
       <c r="E315" t="s">
-        <v>647</v>
+        <v>142</v>
       </c>
       <c r="F315" t="s">
-        <v>648</v>
+        <v>143</v>
       </c>
       <c r="G315" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H315" s="1">
         <v>46304</v>
@@ -11272,7 +11098,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -11281,13 +11107,13 @@
         <v>170</v>
       </c>
       <c r="E316" t="s">
-        <v>647</v>
+        <v>142</v>
       </c>
       <c r="F316" t="s">
-        <v>648</v>
+        <v>143</v>
       </c>
       <c r="G316" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H316" s="1">
         <v>46304</v>
@@ -11298,7 +11124,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -11307,13 +11133,13 @@
         <v>170</v>
       </c>
       <c r="E317" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F317" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G317" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H317" s="1">
         <v>46304</v>
@@ -11324,22 +11150,22 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="C318">
         <v>1</v>
       </c>
       <c r="D318" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E318" t="s">
-        <v>336</v>
+        <v>48</v>
       </c>
       <c r="F318" t="s">
-        <v>337</v>
+        <v>49</v>
       </c>
       <c r="G318" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H318" s="1">
         <v>46304</v>
@@ -11350,22 +11176,22 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="C319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E319" t="s">
-        <v>336</v>
+        <v>635</v>
       </c>
       <c r="F319" t="s">
-        <v>337</v>
+        <v>636</v>
       </c>
       <c r="G319" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H319" s="1">
         <v>46304</v>
@@ -11376,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -11385,13 +11211,13 @@
         <v>170</v>
       </c>
       <c r="E320" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="F320" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="G320" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H320" s="1">
         <v>46304</v>
@@ -11402,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -11411,13 +11237,13 @@
         <v>170</v>
       </c>
       <c r="E321" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="F321" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="G321" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H321" s="1">
         <v>46304</v>
@@ -11428,7 +11254,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -11437,10 +11263,10 @@
         <v>170</v>
       </c>
       <c r="E322" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="F322" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="G322" s="1">
         <v>46304</v>
@@ -11454,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -11463,10 +11289,10 @@
         <v>170</v>
       </c>
       <c r="E323" t="s">
-        <v>37</v>
+        <v>654</v>
       </c>
       <c r="F323" t="s">
-        <v>38</v>
+        <v>655</v>
       </c>
       <c r="G323" s="1">
         <v>46304</v>
@@ -11480,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -11489,10 +11315,10 @@
         <v>170</v>
       </c>
       <c r="E324" t="s">
-        <v>460</v>
+        <v>618</v>
       </c>
       <c r="F324" t="s">
-        <v>461</v>
+        <v>619</v>
       </c>
       <c r="G324" s="1">
         <v>46304</v>
@@ -11506,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11515,10 +11341,10 @@
         <v>170</v>
       </c>
       <c r="E325" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F325" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G325" s="1">
         <v>46304</v>
@@ -11532,7 +11358,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -11541,10 +11367,10 @@
         <v>170</v>
       </c>
       <c r="E326" t="s">
-        <v>630</v>
+        <v>664</v>
       </c>
       <c r="F326" t="s">
-        <v>631</v>
+        <v>665</v>
       </c>
       <c r="G326" s="1">
         <v>46304</v>
@@ -11558,7 +11384,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -11567,10 +11393,10 @@
         <v>170</v>
       </c>
       <c r="E327" t="s">
-        <v>37</v>
+        <v>667</v>
       </c>
       <c r="F327" t="s">
-        <v>38</v>
+        <v>668</v>
       </c>
       <c r="G327" s="1">
         <v>46304</v>
@@ -11584,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -11593,10 +11419,10 @@
         <v>170</v>
       </c>
       <c r="E328" t="s">
-        <v>678</v>
+        <v>584</v>
       </c>
       <c r="F328" t="s">
-        <v>679</v>
+        <v>585</v>
       </c>
       <c r="G328" s="1">
         <v>46304</v>
@@ -11610,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11619,10 +11445,10 @@
         <v>170</v>
       </c>
       <c r="E329" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="F329" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="G329" s="1">
         <v>46304</v>
@@ -11636,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -11645,10 +11471,10 @@
         <v>170</v>
       </c>
       <c r="E330" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F330" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="G330" s="1">
         <v>46304</v>
@@ -11662,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -11671,10 +11497,10 @@
         <v>170</v>
       </c>
       <c r="E331" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F331" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="G331" s="1">
         <v>46304</v>
@@ -11688,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -11697,10 +11523,10 @@
         <v>170</v>
       </c>
       <c r="E332" t="s">
-        <v>586</v>
+        <v>678</v>
       </c>
       <c r="F332" t="s">
-        <v>587</v>
+        <v>679</v>
       </c>
       <c r="G332" s="1">
         <v>46304</v>
@@ -11714,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11723,10 +11549,10 @@
         <v>170</v>
       </c>
       <c r="E333" t="s">
-        <v>382</v>
+        <v>487</v>
       </c>
       <c r="F333" t="s">
-        <v>383</v>
+        <v>488</v>
       </c>
       <c r="G333" s="1">
         <v>46304</v>
@@ -11740,7 +11566,7 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -11749,10 +11575,10 @@
         <v>170</v>
       </c>
       <c r="E334" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="F334" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="G334" s="1">
         <v>46304</v>
@@ -11766,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -11775,10 +11601,10 @@
         <v>170</v>
       </c>
       <c r="E335" t="s">
-        <v>693</v>
+        <v>264</v>
       </c>
       <c r="F335" t="s">
-        <v>694</v>
+        <v>265</v>
       </c>
       <c r="G335" s="1">
         <v>46304</v>
@@ -11792,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -11801,10 +11627,10 @@
         <v>170</v>
       </c>
       <c r="E336" t="s">
-        <v>696</v>
+        <v>459</v>
       </c>
       <c r="F336" t="s">
-        <v>697</v>
+        <v>460</v>
       </c>
       <c r="G336" s="1">
         <v>46304</v>
@@ -11818,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -11844,7 +11670,7 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -11853,10 +11679,10 @@
         <v>170</v>
       </c>
       <c r="E338" t="s">
-        <v>16</v>
+        <v>362</v>
       </c>
       <c r="F338" t="s">
-        <v>17</v>
+        <v>363</v>
       </c>
       <c r="G338" s="1">
         <v>46304</v>
@@ -11870,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -11879,10 +11705,10 @@
         <v>170</v>
       </c>
       <c r="E339" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="F339" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="G339" s="1">
         <v>46304</v>
@@ -11896,7 +11722,7 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -11905,10 +11731,10 @@
         <v>170</v>
       </c>
       <c r="E340" t="s">
-        <v>182</v>
+        <v>690</v>
       </c>
       <c r="F340" t="s">
-        <v>183</v>
+        <v>691</v>
       </c>
       <c r="G340" s="1">
         <v>46304</v>
@@ -11922,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -11931,10 +11757,10 @@
         <v>170</v>
       </c>
       <c r="E341" t="s">
-        <v>182</v>
+        <v>693</v>
       </c>
       <c r="F341" t="s">
-        <v>183</v>
+        <v>694</v>
       </c>
       <c r="G341" s="1">
         <v>46304</v>
@@ -11948,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -11957,10 +11783,10 @@
         <v>170</v>
       </c>
       <c r="E342" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="F342" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="G342" s="1">
         <v>46304</v>
@@ -11974,7 +11800,7 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -11983,10 +11809,10 @@
         <v>170</v>
       </c>
       <c r="E343" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F343" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="G343" s="1">
         <v>46304</v>
@@ -12000,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -12009,10 +11835,10 @@
         <v>170</v>
       </c>
       <c r="E344" t="s">
-        <v>142</v>
+        <v>698</v>
       </c>
       <c r="F344" t="s">
-        <v>143</v>
+        <v>699</v>
       </c>
       <c r="G344" s="1">
         <v>46304</v>
@@ -12026,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -12035,10 +11861,10 @@
         <v>170</v>
       </c>
       <c r="E345" t="s">
-        <v>16</v>
+        <v>701</v>
       </c>
       <c r="F345" t="s">
-        <v>17</v>
+        <v>702</v>
       </c>
       <c r="G345" s="1">
         <v>46304</v>
@@ -12052,7 +11878,7 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -12061,10 +11887,10 @@
         <v>170</v>
       </c>
       <c r="E346" t="s">
-        <v>48</v>
+        <v>704</v>
       </c>
       <c r="F346" t="s">
-        <v>49</v>
+        <v>705</v>
       </c>
       <c r="G346" s="1">
         <v>46304</v>
@@ -12078,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -12087,10 +11913,10 @@
         <v>170</v>
       </c>
       <c r="E347" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="F347" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="G347" s="1">
         <v>46304</v>
@@ -12104,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -12113,10 +11939,10 @@
         <v>170</v>
       </c>
       <c r="E348" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="F348" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="G348" s="1">
         <v>46304</v>
@@ -12130,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -12139,10 +11965,10 @@
         <v>170</v>
       </c>
       <c r="E349" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="F349" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="G349" s="1">
         <v>46304</v>
@@ -12156,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -12165,10 +11991,10 @@
         <v>170</v>
       </c>
       <c r="E350" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F350" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G350" s="1">
         <v>46304</v>
@@ -12182,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -12191,10 +12017,10 @@
         <v>170</v>
       </c>
       <c r="E351" t="s">
-        <v>712</v>
+        <v>197</v>
       </c>
       <c r="F351" t="s">
-        <v>713</v>
+        <v>198</v>
       </c>
       <c r="G351" s="1">
         <v>46304</v>
@@ -12205,62 +12031,62 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B352" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C352">
         <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E352" t="s">
-        <v>678</v>
+        <v>200</v>
       </c>
       <c r="F352" t="s">
-        <v>679</v>
+        <v>201</v>
       </c>
       <c r="G352" s="1">
-        <v>46304</v>
+        <v>46148</v>
       </c>
       <c r="H352" s="1">
-        <v>46304</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B353" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E353" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="F353" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="G353" s="1">
-        <v>46304</v>
+        <v>46268</v>
       </c>
       <c r="H353" s="1">
-        <v>46304</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B354" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -12269,24 +12095,24 @@
         <v>170</v>
       </c>
       <c r="E354" t="s">
-        <v>722</v>
+        <v>393</v>
       </c>
       <c r="F354" t="s">
-        <v>723</v>
+        <v>394</v>
       </c>
       <c r="G354" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H354" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="B355" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -12295,273 +12121,273 @@
         <v>170</v>
       </c>
       <c r="E355" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F355" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G355" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H355" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B356" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C356">
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
-        <v>644</v>
+        <v>41</v>
       </c>
       <c r="F356" t="s">
-        <v>645</v>
+        <v>42</v>
       </c>
       <c r="G356" s="1">
-        <v>46304</v>
+        <v>46133</v>
       </c>
       <c r="H356" s="1">
-        <v>46304</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E357" t="s">
-        <v>234</v>
+        <v>41</v>
       </c>
       <c r="F357" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="G357" s="1">
-        <v>46304</v>
+        <v>46134</v>
       </c>
       <c r="H357" s="1">
-        <v>46304</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B358" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E358" t="s">
-        <v>730</v>
+        <v>19</v>
       </c>
       <c r="F358" t="s">
-        <v>731</v>
+        <v>20</v>
       </c>
       <c r="G358" s="1">
-        <v>46304</v>
+        <v>46156</v>
       </c>
       <c r="H358" s="1">
-        <v>46304</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B359" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D359" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E359" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F359" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="G359" s="1">
-        <v>46304</v>
+        <v>46209</v>
       </c>
       <c r="H359" s="1">
-        <v>46304</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B360" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E360" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="F360" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="G360" s="1">
-        <v>46304</v>
+        <v>46213</v>
       </c>
       <c r="H360" s="1">
-        <v>46304</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B361" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E361" t="s">
-        <v>533</v>
+        <v>625</v>
       </c>
       <c r="F361" t="s">
-        <v>534</v>
+        <v>626</v>
       </c>
       <c r="G361" s="1">
-        <v>46304</v>
+        <v>46213</v>
       </c>
       <c r="H361" s="1">
-        <v>46304</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B362" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E362" t="s">
-        <v>740</v>
+        <v>625</v>
       </c>
       <c r="F362" t="s">
-        <v>741</v>
+        <v>626</v>
       </c>
       <c r="G362" s="1">
-        <v>46304</v>
+        <v>46224</v>
       </c>
       <c r="H362" s="1">
-        <v>46304</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B363" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
-        <v>264</v>
+        <v>735</v>
       </c>
       <c r="F363" t="s">
-        <v>265</v>
+        <v>736</v>
       </c>
       <c r="G363" s="1">
-        <v>46304</v>
+        <v>46253</v>
       </c>
       <c r="H363" s="1">
-        <v>46304</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B364" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E364" t="s">
-        <v>497</v>
+        <v>211</v>
       </c>
       <c r="F364" t="s">
-        <v>498</v>
+        <v>212</v>
       </c>
       <c r="G364" s="1">
-        <v>46304</v>
+        <v>46273</v>
       </c>
       <c r="H364" s="1">
-        <v>46304</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B365" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C365">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D365" t="s">
         <v>170</v>
       </c>
       <c r="E365" t="s">
-        <v>299</v>
+        <v>739</v>
       </c>
       <c r="F365" t="s">
-        <v>300</v>
+        <v>740</v>
       </c>
       <c r="G365" s="1">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="H365" s="1">
         <v>46304</v>
@@ -12569,88 +12395,88 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B366" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>367</v>
+        <v>221</v>
       </c>
       <c r="F366" t="s">
-        <v>368</v>
+        <v>222</v>
       </c>
       <c r="G366" s="1">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="H366" s="1">
-        <v>46304</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B367" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E367" t="s">
-        <v>37</v>
+        <v>625</v>
       </c>
       <c r="F367" t="s">
-        <v>38</v>
+        <v>626</v>
       </c>
       <c r="G367" s="1">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="H367" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B368" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>748</v>
+        <v>347</v>
       </c>
       <c r="F368" t="s">
-        <v>749</v>
+        <v>348</v>
       </c>
       <c r="G368" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="H368" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B369" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -12659,24 +12485,24 @@
         <v>170</v>
       </c>
       <c r="E369" t="s">
-        <v>751</v>
+        <v>727</v>
       </c>
       <c r="F369" t="s">
-        <v>752</v>
+        <v>728</v>
       </c>
       <c r="G369" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="H369" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B370" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12685,50 +12511,50 @@
         <v>170</v>
       </c>
       <c r="E370" t="s">
-        <v>748</v>
+        <v>513</v>
       </c>
       <c r="F370" t="s">
-        <v>749</v>
+        <v>514</v>
       </c>
       <c r="G370" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H370" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B371" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="F371" t="s">
-        <v>84</v>
+        <v>538</v>
       </c>
       <c r="G371" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H371" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B372" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -12737,24 +12563,24 @@
         <v>170</v>
       </c>
       <c r="E372" t="s">
-        <v>756</v>
+        <v>537</v>
       </c>
       <c r="F372" t="s">
-        <v>757</v>
+        <v>538</v>
       </c>
       <c r="G372" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H372" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B373" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12763,24 +12589,24 @@
         <v>170</v>
       </c>
       <c r="E373" t="s">
-        <v>759</v>
+        <v>537</v>
       </c>
       <c r="F373" t="s">
-        <v>760</v>
+        <v>538</v>
       </c>
       <c r="G373" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H373" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B374" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -12789,13 +12615,13 @@
         <v>170</v>
       </c>
       <c r="E374" t="s">
-        <v>762</v>
+        <v>132</v>
       </c>
       <c r="F374" t="s">
-        <v>763</v>
+        <v>133</v>
       </c>
       <c r="G374" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H374" s="1">
         <v>46304</v>
@@ -12803,10 +12629,10 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B375" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -12815,10 +12641,10 @@
         <v>170</v>
       </c>
       <c r="E375" t="s">
-        <v>765</v>
+        <v>625</v>
       </c>
       <c r="F375" t="s">
-        <v>766</v>
+        <v>626</v>
       </c>
       <c r="G375" s="1">
         <v>46304</v>
@@ -12829,10 +12655,10 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B376" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -12841,10 +12667,10 @@
         <v>170</v>
       </c>
       <c r="E376" t="s">
-        <v>765</v>
+        <v>727</v>
       </c>
       <c r="F376" t="s">
-        <v>766</v>
+        <v>728</v>
       </c>
       <c r="G376" s="1">
         <v>46304</v>
@@ -12855,10 +12681,10 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="B377" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -12867,10 +12693,10 @@
         <v>170</v>
       </c>
       <c r="E377" t="s">
-        <v>765</v>
+        <v>657</v>
       </c>
       <c r="F377" t="s">
-        <v>766</v>
+        <v>658</v>
       </c>
       <c r="G377" s="1">
         <v>46304</v>
@@ -12881,62 +12707,62 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="B378" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E378" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="F378" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G378" s="1">
-        <v>46304</v>
+        <v>46063</v>
       </c>
       <c r="H378" s="1">
-        <v>46304</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="B379" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E379" t="s">
-        <v>197</v>
+        <v>57</v>
       </c>
       <c r="F379" t="s">
-        <v>198</v>
+        <v>58</v>
       </c>
       <c r="G379" s="1">
-        <v>46304</v>
+        <v>46113</v>
       </c>
       <c r="H379" s="1">
-        <v>46304</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="B380" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -12945,24 +12771,24 @@
         <v>2</v>
       </c>
       <c r="E380" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="F380" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="G380" s="1">
-        <v>46148</v>
+        <v>46125</v>
       </c>
       <c r="H380" s="1">
-        <v>46149</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="B381" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -12971,76 +12797,76 @@
         <v>2</v>
       </c>
       <c r="E381" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="F381" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="G381" s="1">
-        <v>46268</v>
+        <v>46126</v>
       </c>
       <c r="H381" s="1">
-        <v>46268</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="B382" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="C382">
         <v>1</v>
       </c>
       <c r="D382" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E382" t="s">
-        <v>411</v>
+        <v>57</v>
       </c>
       <c r="F382" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="G382" s="1">
-        <v>46303</v>
+        <v>46126</v>
       </c>
       <c r="H382" s="1">
-        <v>46303</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="B383" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="C383">
         <v>1</v>
       </c>
       <c r="D383" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>778</v>
+        <v>57</v>
       </c>
       <c r="F383" t="s">
-        <v>779</v>
+        <v>58</v>
       </c>
       <c r="G383" s="1">
-        <v>46303</v>
+        <v>46128</v>
       </c>
       <c r="H383" s="1">
-        <v>46303</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B384" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -13049,102 +12875,102 @@
         <v>6</v>
       </c>
       <c r="E384" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F384" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G384" s="1">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="H384" s="1">
-        <v>46134</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B385" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="C385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E385" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F385" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G385" s="1">
-        <v>46134</v>
+        <v>46161</v>
       </c>
       <c r="H385" s="1">
-        <v>46134</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B386" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="C386">
         <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E386" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F386" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="G386" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="H386" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B387" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
         <v>2</v>
       </c>
-      <c r="D387" t="s">
-        <v>95</v>
-      </c>
       <c r="E387" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="F387" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="G387" s="1">
-        <v>46209</v>
+        <v>46174</v>
       </c>
       <c r="H387" s="1">
-        <v>46218</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B388" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -13153,76 +12979,76 @@
         <v>6</v>
       </c>
       <c r="E388" t="s">
-        <v>788</v>
+        <v>57</v>
       </c>
       <c r="F388" t="s">
-        <v>789</v>
+        <v>58</v>
       </c>
       <c r="G388" s="1">
-        <v>46213</v>
+        <v>46195</v>
       </c>
       <c r="H388" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B389" t="s">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="C389">
         <v>1</v>
       </c>
       <c r="D389" t="s">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="E389" t="s">
-        <v>685</v>
+        <v>57</v>
       </c>
       <c r="F389" t="s">
-        <v>686</v>
+        <v>58</v>
       </c>
       <c r="G389" s="1">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="H389" s="1">
-        <v>46216</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B390" t="s">
-        <v>791</v>
+        <v>768</v>
       </c>
       <c r="C390">
         <v>1</v>
       </c>
       <c r="D390" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E390" t="s">
-        <v>685</v>
+        <v>57</v>
       </c>
       <c r="F390" t="s">
-        <v>686</v>
+        <v>58</v>
       </c>
       <c r="G390" s="1">
-        <v>46224</v>
+        <v>46213</v>
       </c>
       <c r="H390" s="1">
-        <v>46224</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B391" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="C391">
         <v>1</v>
@@ -13231,50 +13057,50 @@
         <v>6</v>
       </c>
       <c r="E391" t="s">
-        <v>793</v>
+        <v>57</v>
       </c>
       <c r="F391" t="s">
-        <v>794</v>
+        <v>58</v>
       </c>
       <c r="G391" s="1">
-        <v>46253</v>
+        <v>46218</v>
       </c>
       <c r="H391" s="1">
-        <v>46253</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B392" t="s">
-        <v>795</v>
+        <v>770</v>
       </c>
       <c r="C392">
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E392" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="F392" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="G392" s="1">
-        <v>46273</v>
+        <v>46226</v>
       </c>
       <c r="H392" s="1">
-        <v>46274</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B393" t="s">
-        <v>796</v>
+        <v>771</v>
       </c>
       <c r="C393">
         <v>1</v>
@@ -13283,180 +13109,180 @@
         <v>170</v>
       </c>
       <c r="E393" t="s">
-        <v>797</v>
+        <v>57</v>
       </c>
       <c r="F393" t="s">
-        <v>798</v>
+        <v>58</v>
       </c>
       <c r="G393" s="1">
-        <v>46300</v>
+        <v>46227</v>
       </c>
       <c r="H393" s="1">
-        <v>46300</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B394" t="s">
-        <v>799</v>
+        <v>772</v>
       </c>
       <c r="C394">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D394" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E394" t="s">
-        <v>797</v>
+        <v>57</v>
       </c>
       <c r="F394" t="s">
-        <v>798</v>
+        <v>58</v>
       </c>
       <c r="G394" s="1">
-        <v>46300</v>
+        <v>46227</v>
       </c>
       <c r="H394" s="1">
-        <v>46304</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B395" t="s">
-        <v>800</v>
+        <v>773</v>
       </c>
       <c r="C395">
         <v>1</v>
       </c>
       <c r="D395" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E395" t="s">
-        <v>221</v>
+        <v>57</v>
       </c>
       <c r="F395" t="s">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="G395" s="1">
-        <v>46300</v>
+        <v>46227</v>
       </c>
       <c r="H395" s="1">
-        <v>46300</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B396" t="s">
-        <v>801</v>
+        <v>774</v>
       </c>
       <c r="C396">
         <v>1</v>
       </c>
       <c r="D396" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E396" t="s">
-        <v>685</v>
+        <v>77</v>
       </c>
       <c r="F396" t="s">
-        <v>686</v>
+        <v>78</v>
       </c>
       <c r="G396" s="1">
-        <v>46300</v>
+        <v>46230</v>
       </c>
       <c r="H396" s="1">
-        <v>46301</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B397" t="s">
-        <v>802</v>
+        <v>775</v>
       </c>
       <c r="C397">
         <v>1</v>
       </c>
       <c r="D397" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E397" t="s">
-        <v>351</v>
+        <v>57</v>
       </c>
       <c r="F397" t="s">
-        <v>352</v>
+        <v>58</v>
       </c>
       <c r="G397" s="1">
-        <v>46302</v>
+        <v>46231</v>
       </c>
       <c r="H397" s="1">
-        <v>46302</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B398" t="s">
-        <v>803</v>
+        <v>776</v>
       </c>
       <c r="C398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E398" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="F398" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="G398" s="1">
-        <v>46302</v>
+        <v>46254</v>
       </c>
       <c r="H398" s="1">
-        <v>46302</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B399" t="s">
-        <v>804</v>
+        <v>777</v>
       </c>
       <c r="C399">
         <v>1</v>
       </c>
       <c r="D399" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E399" t="s">
-        <v>560</v>
+        <v>57</v>
       </c>
       <c r="F399" t="s">
-        <v>561</v>
+        <v>58</v>
       </c>
       <c r="G399" s="1">
-        <v>46303</v>
+        <v>46255</v>
       </c>
       <c r="H399" s="1">
-        <v>46303</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B400" t="s">
-        <v>805</v>
+        <v>778</v>
       </c>
       <c r="C400">
         <v>1</v>
@@ -13465,88 +13291,88 @@
         <v>6</v>
       </c>
       <c r="E400" t="s">
-        <v>593</v>
+        <v>57</v>
       </c>
       <c r="F400" t="s">
-        <v>594</v>
+        <v>58</v>
       </c>
       <c r="G400" s="1">
-        <v>46303</v>
+        <v>46260</v>
       </c>
       <c r="H400" s="1">
-        <v>46303</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B401" t="s">
-        <v>806</v>
+        <v>779</v>
       </c>
       <c r="C401">
         <v>1</v>
       </c>
       <c r="D401" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E401" t="s">
-        <v>593</v>
+        <v>57</v>
       </c>
       <c r="F401" t="s">
-        <v>594</v>
+        <v>58</v>
       </c>
       <c r="G401" s="1">
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="H401" s="1">
-        <v>46303</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
+        <v>753</v>
+      </c>
+      <c r="B402" t="s">
         <v>780</v>
       </c>
-      <c r="B402" t="s">
-        <v>807</v>
-      </c>
       <c r="C402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E402" t="s">
-        <v>593</v>
+        <v>57</v>
       </c>
       <c r="F402" t="s">
-        <v>594</v>
+        <v>58</v>
       </c>
       <c r="G402" s="1">
-        <v>46303</v>
+        <v>46294</v>
       </c>
       <c r="H402" s="1">
-        <v>46303</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B403" t="s">
-        <v>808</v>
+        <v>781</v>
       </c>
       <c r="C403">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E403" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="F403" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="G403" s="1">
         <v>46303</v>
@@ -13557,10 +13383,10 @@
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="B404" t="s">
-        <v>809</v>
+        <v>782</v>
       </c>
       <c r="C404">
         <v>1</v>
@@ -13569,30 +13395,30 @@
         <v>170</v>
       </c>
       <c r="E404" t="s">
-        <v>685</v>
+        <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>686</v>
+        <v>58</v>
       </c>
       <c r="G404" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H404" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B405" t="s">
-        <v>810</v>
+        <v>784</v>
       </c>
       <c r="C405">
         <v>1</v>
       </c>
       <c r="D405" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E405" t="s">
         <v>785</v>
@@ -13601,96 +13427,96 @@
         <v>786</v>
       </c>
       <c r="G405" s="1">
-        <v>46304</v>
+        <v>46157</v>
       </c>
       <c r="H405" s="1">
-        <v>46304</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B406" t="s">
-        <v>811</v>
+        <v>787</v>
       </c>
       <c r="C406">
         <v>1</v>
       </c>
       <c r="D406" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E406" t="s">
-        <v>715</v>
+        <v>788</v>
       </c>
       <c r="F406" t="s">
-        <v>716</v>
+        <v>789</v>
       </c>
       <c r="G406" s="1">
-        <v>46304</v>
+        <v>46168</v>
       </c>
       <c r="H406" s="1">
-        <v>46304</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B407" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="C407">
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E407" t="s">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="F407" t="s">
-        <v>815</v>
+        <v>786</v>
       </c>
       <c r="G407" s="1">
-        <v>46063</v>
+        <v>46218</v>
       </c>
       <c r="H407" s="1">
-        <v>46064</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B408" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="C408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E408" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="F408" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="G408" s="1">
-        <v>46113</v>
+        <v>46244</v>
       </c>
       <c r="H408" s="1">
-        <v>46125</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B409" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -13699,24 +13525,24 @@
         <v>2</v>
       </c>
       <c r="E409" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="F409" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="G409" s="1">
-        <v>46125</v>
+        <v>46247</v>
       </c>
       <c r="H409" s="1">
-        <v>46125</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B410" t="s">
-        <v>818</v>
+        <v>793</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -13725,24 +13551,24 @@
         <v>2</v>
       </c>
       <c r="E410" t="s">
-        <v>57</v>
+        <v>794</v>
       </c>
       <c r="F410" t="s">
-        <v>58</v>
+        <v>795</v>
       </c>
       <c r="G410" s="1">
-        <v>46126</v>
+        <v>46247</v>
       </c>
       <c r="H410" s="1">
-        <v>46126</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B411" t="s">
-        <v>819</v>
+        <v>796</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -13751,24 +13577,24 @@
         <v>2</v>
       </c>
       <c r="E411" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="F411" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="G411" s="1">
-        <v>46126</v>
+        <v>46255</v>
       </c>
       <c r="H411" s="1">
-        <v>46126</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B412" t="s">
-        <v>820</v>
+        <v>797</v>
       </c>
       <c r="C412">
         <v>1</v>
@@ -13777,82 +13603,82 @@
         <v>2</v>
       </c>
       <c r="E412" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="F412" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="G412" s="1">
-        <v>46128</v>
+        <v>46258</v>
       </c>
       <c r="H412" s="1">
-        <v>46128</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B413" t="s">
-        <v>821</v>
+        <v>798</v>
       </c>
       <c r="C413">
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E413" t="s">
-        <v>57</v>
+        <v>785</v>
       </c>
       <c r="F413" t="s">
-        <v>58</v>
+        <v>786</v>
       </c>
       <c r="G413" s="1">
-        <v>46132</v>
+        <v>46262</v>
       </c>
       <c r="H413" s="1">
-        <v>46132</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B414" t="s">
-        <v>822</v>
+        <v>799</v>
       </c>
       <c r="C414">
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E414" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F414" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G414" s="1">
-        <v>46161</v>
+        <v>46281</v>
       </c>
       <c r="H414" s="1">
-        <v>46161</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B415" t="s">
-        <v>823</v>
+        <v>800</v>
       </c>
       <c r="C415">
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
@@ -13861,24 +13687,24 @@
         <v>58</v>
       </c>
       <c r="G415" s="1">
-        <v>46174</v>
+        <v>46304</v>
       </c>
       <c r="H415" s="1">
-        <v>46174</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="B416" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="C416">
         <v>1</v>
       </c>
       <c r="D416" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E416" t="s">
         <v>57</v>
@@ -13887,737 +13713,9 @@
         <v>58</v>
       </c>
       <c r="G416" s="1">
-        <v>46174</v>
+        <v>46304</v>
       </c>
       <c r="H416" s="1">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
-        <v>812</v>
-      </c>
-      <c r="B417" t="s">
-        <v>825</v>
-      </c>
-      <c r="C417">
-        <v>1</v>
-      </c>
-      <c r="D417" t="s">
-        <v>6</v>
-      </c>
-      <c r="E417" t="s">
-        <v>57</v>
-      </c>
-      <c r="F417" t="s">
-        <v>58</v>
-      </c>
-      <c r="G417" s="1">
-        <v>46195</v>
-      </c>
-      <c r="H417" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
-        <v>812</v>
-      </c>
-      <c r="B418" t="s">
-        <v>826</v>
-      </c>
-      <c r="C418">
-        <v>1</v>
-      </c>
-      <c r="D418" t="s">
-        <v>6</v>
-      </c>
-      <c r="E418" t="s">
-        <v>57</v>
-      </c>
-      <c r="F418" t="s">
-        <v>58</v>
-      </c>
-      <c r="G418" s="1">
-        <v>46210</v>
-      </c>
-      <c r="H418" s="1">
-        <v>46210</v>
-      </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
-        <v>812</v>
-      </c>
-      <c r="B419" t="s">
-        <v>827</v>
-      </c>
-      <c r="C419">
-        <v>1</v>
-      </c>
-      <c r="D419" t="s">
-        <v>2</v>
-      </c>
-      <c r="E419" t="s">
-        <v>57</v>
-      </c>
-      <c r="F419" t="s">
-        <v>58</v>
-      </c>
-      <c r="G419" s="1">
-        <v>46213</v>
-      </c>
-      <c r="H419" s="1">
-        <v>46213</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
-        <v>812</v>
-      </c>
-      <c r="B420" t="s">
-        <v>828</v>
-      </c>
-      <c r="C420">
-        <v>1</v>
-      </c>
-      <c r="D420" t="s">
-        <v>6</v>
-      </c>
-      <c r="E420" t="s">
-        <v>57</v>
-      </c>
-      <c r="F420" t="s">
-        <v>58</v>
-      </c>
-      <c r="G420" s="1">
-        <v>46218</v>
-      </c>
-      <c r="H420" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A421" t="s">
-        <v>812</v>
-      </c>
-      <c r="B421" t="s">
-        <v>829</v>
-      </c>
-      <c r="C421">
-        <v>1</v>
-      </c>
-      <c r="D421" t="s">
-        <v>6</v>
-      </c>
-      <c r="E421" t="s">
-        <v>77</v>
-      </c>
-      <c r="F421" t="s">
-        <v>78</v>
-      </c>
-      <c r="G421" s="1">
-        <v>46226</v>
-      </c>
-      <c r="H421" s="1">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A422" t="s">
-        <v>812</v>
-      </c>
-      <c r="B422" t="s">
-        <v>830</v>
-      </c>
-      <c r="C422">
-        <v>1</v>
-      </c>
-      <c r="D422" t="s">
-        <v>170</v>
-      </c>
-      <c r="E422" t="s">
-        <v>57</v>
-      </c>
-      <c r="F422" t="s">
-        <v>58</v>
-      </c>
-      <c r="G422" s="1">
-        <v>46227</v>
-      </c>
-      <c r="H422" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
-        <v>812</v>
-      </c>
-      <c r="B423" t="s">
-        <v>831</v>
-      </c>
-      <c r="C423">
-        <v>1</v>
-      </c>
-      <c r="D423" t="s">
-        <v>6</v>
-      </c>
-      <c r="E423" t="s">
-        <v>57</v>
-      </c>
-      <c r="F423" t="s">
-        <v>58</v>
-      </c>
-      <c r="G423" s="1">
-        <v>46227</v>
-      </c>
-      <c r="H423" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
-        <v>812</v>
-      </c>
-      <c r="B424" t="s">
-        <v>832</v>
-      </c>
-      <c r="C424">
-        <v>1</v>
-      </c>
-      <c r="D424" t="s">
-        <v>6</v>
-      </c>
-      <c r="E424" t="s">
-        <v>57</v>
-      </c>
-      <c r="F424" t="s">
-        <v>58</v>
-      </c>
-      <c r="G424" s="1">
-        <v>46227</v>
-      </c>
-      <c r="H424" s="1">
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
-        <v>812</v>
-      </c>
-      <c r="B425" t="s">
-        <v>833</v>
-      </c>
-      <c r="C425">
-        <v>1</v>
-      </c>
-      <c r="D425" t="s">
-        <v>6</v>
-      </c>
-      <c r="E425" t="s">
-        <v>77</v>
-      </c>
-      <c r="F425" t="s">
-        <v>78</v>
-      </c>
-      <c r="G425" s="1">
-        <v>46230</v>
-      </c>
-      <c r="H425" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
-        <v>812</v>
-      </c>
-      <c r="B426" t="s">
-        <v>834</v>
-      </c>
-      <c r="C426">
-        <v>1</v>
-      </c>
-      <c r="D426" t="s">
-        <v>6</v>
-      </c>
-      <c r="E426" t="s">
-        <v>57</v>
-      </c>
-      <c r="F426" t="s">
-        <v>58</v>
-      </c>
-      <c r="G426" s="1">
-        <v>46231</v>
-      </c>
-      <c r="H426" s="1">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
-        <v>812</v>
-      </c>
-      <c r="B427" t="s">
-        <v>835</v>
-      </c>
-      <c r="C427">
-        <v>1</v>
-      </c>
-      <c r="D427" t="s">
-        <v>6</v>
-      </c>
-      <c r="E427" t="s">
-        <v>57</v>
-      </c>
-      <c r="F427" t="s">
-        <v>58</v>
-      </c>
-      <c r="G427" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H427" s="1">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
-        <v>812</v>
-      </c>
-      <c r="B428" t="s">
-        <v>836</v>
-      </c>
-      <c r="C428">
-        <v>1</v>
-      </c>
-      <c r="D428" t="s">
-        <v>2</v>
-      </c>
-      <c r="E428" t="s">
-        <v>57</v>
-      </c>
-      <c r="F428" t="s">
-        <v>58</v>
-      </c>
-      <c r="G428" s="1">
-        <v>46255</v>
-      </c>
-      <c r="H428" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A429" t="s">
-        <v>812</v>
-      </c>
-      <c r="B429" t="s">
-        <v>837</v>
-      </c>
-      <c r="C429">
-        <v>1</v>
-      </c>
-      <c r="D429" t="s">
-        <v>6</v>
-      </c>
-      <c r="E429" t="s">
-        <v>57</v>
-      </c>
-      <c r="F429" t="s">
-        <v>58</v>
-      </c>
-      <c r="G429" s="1">
-        <v>46260</v>
-      </c>
-      <c r="H429" s="1">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
-        <v>812</v>
-      </c>
-      <c r="B430" t="s">
-        <v>838</v>
-      </c>
-      <c r="C430">
-        <v>1</v>
-      </c>
-      <c r="D430" t="s">
-        <v>6</v>
-      </c>
-      <c r="E430" t="s">
-        <v>57</v>
-      </c>
-      <c r="F430" t="s">
-        <v>58</v>
-      </c>
-      <c r="G430" s="1">
-        <v>46289</v>
-      </c>
-      <c r="H430" s="1">
-        <v>46289</v>
-      </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>812</v>
-      </c>
-      <c r="B431" t="s">
-        <v>839</v>
-      </c>
-      <c r="C431">
-        <v>1</v>
-      </c>
-      <c r="D431" t="s">
-        <v>6</v>
-      </c>
-      <c r="E431" t="s">
-        <v>57</v>
-      </c>
-      <c r="F431" t="s">
-        <v>58</v>
-      </c>
-      <c r="G431" s="1">
-        <v>46294</v>
-      </c>
-      <c r="H431" s="1">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>812</v>
-      </c>
-      <c r="B432" t="s">
-        <v>840</v>
-      </c>
-      <c r="C432">
-        <v>2</v>
-      </c>
-      <c r="D432" t="s">
-        <v>170</v>
-      </c>
-      <c r="E432" t="s">
-        <v>57</v>
-      </c>
-      <c r="F432" t="s">
-        <v>58</v>
-      </c>
-      <c r="G432" s="1">
-        <v>46303</v>
-      </c>
-      <c r="H432" s="1">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>841</v>
-      </c>
-      <c r="B433" t="s">
-        <v>842</v>
-      </c>
-      <c r="C433">
-        <v>1</v>
-      </c>
-      <c r="D433" t="s">
-        <v>2</v>
-      </c>
-      <c r="E433" t="s">
-        <v>843</v>
-      </c>
-      <c r="F433" t="s">
-        <v>844</v>
-      </c>
-      <c r="G433" s="1">
-        <v>46157</v>
-      </c>
-      <c r="H433" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>841</v>
-      </c>
-      <c r="B434" t="s">
-        <v>845</v>
-      </c>
-      <c r="C434">
-        <v>1</v>
-      </c>
-      <c r="D434" t="s">
-        <v>2</v>
-      </c>
-      <c r="E434" t="s">
-        <v>846</v>
-      </c>
-      <c r="F434" t="s">
-        <v>847</v>
-      </c>
-      <c r="G434" s="1">
-        <v>46168</v>
-      </c>
-      <c r="H434" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>841</v>
-      </c>
-      <c r="B435" t="s">
-        <v>848</v>
-      </c>
-      <c r="C435">
-        <v>1</v>
-      </c>
-      <c r="D435" t="s">
-        <v>2</v>
-      </c>
-      <c r="E435" t="s">
-        <v>843</v>
-      </c>
-      <c r="F435" t="s">
-        <v>844</v>
-      </c>
-      <c r="G435" s="1">
-        <v>46218</v>
-      </c>
-      <c r="H435" s="1">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>841</v>
-      </c>
-      <c r="B436" t="s">
-        <v>849</v>
-      </c>
-      <c r="C436">
-        <v>1</v>
-      </c>
-      <c r="D436" t="s">
-        <v>2</v>
-      </c>
-      <c r="E436" t="s">
-        <v>843</v>
-      </c>
-      <c r="F436" t="s">
-        <v>844</v>
-      </c>
-      <c r="G436" s="1">
-        <v>46244</v>
-      </c>
-      <c r="H436" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>841</v>
-      </c>
-      <c r="B437" t="s">
-        <v>850</v>
-      </c>
-      <c r="C437">
-        <v>1</v>
-      </c>
-      <c r="D437" t="s">
-        <v>2</v>
-      </c>
-      <c r="E437" t="s">
-        <v>843</v>
-      </c>
-      <c r="F437" t="s">
-        <v>844</v>
-      </c>
-      <c r="G437" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H437" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
-        <v>841</v>
-      </c>
-      <c r="B438" t="s">
-        <v>851</v>
-      </c>
-      <c r="C438">
-        <v>1</v>
-      </c>
-      <c r="D438" t="s">
-        <v>2</v>
-      </c>
-      <c r="E438" t="s">
-        <v>852</v>
-      </c>
-      <c r="F438" t="s">
-        <v>853</v>
-      </c>
-      <c r="G438" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H438" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
-        <v>841</v>
-      </c>
-      <c r="B439" t="s">
-        <v>854</v>
-      </c>
-      <c r="C439">
-        <v>1</v>
-      </c>
-      <c r="D439" t="s">
-        <v>2</v>
-      </c>
-      <c r="E439" t="s">
-        <v>843</v>
-      </c>
-      <c r="F439" t="s">
-        <v>844</v>
-      </c>
-      <c r="G439" s="1">
-        <v>46255</v>
-      </c>
-      <c r="H439" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>841</v>
-      </c>
-      <c r="B440" t="s">
-        <v>855</v>
-      </c>
-      <c r="C440">
-        <v>1</v>
-      </c>
-      <c r="D440" t="s">
-        <v>2</v>
-      </c>
-      <c r="E440" t="s">
-        <v>843</v>
-      </c>
-      <c r="F440" t="s">
-        <v>844</v>
-      </c>
-      <c r="G440" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H440" s="1">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>841</v>
-      </c>
-      <c r="B441" t="s">
-        <v>856</v>
-      </c>
-      <c r="C441">
-        <v>1</v>
-      </c>
-      <c r="D441" t="s">
-        <v>2</v>
-      </c>
-      <c r="E441" t="s">
-        <v>843</v>
-      </c>
-      <c r="F441" t="s">
-        <v>844</v>
-      </c>
-      <c r="G441" s="1">
-        <v>46262</v>
-      </c>
-      <c r="H441" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
-        <v>841</v>
-      </c>
-      <c r="B442" t="s">
-        <v>857</v>
-      </c>
-      <c r="C442">
-        <v>1</v>
-      </c>
-      <c r="D442" t="s">
-        <v>6</v>
-      </c>
-      <c r="E442" t="s">
-        <v>13</v>
-      </c>
-      <c r="F442" t="s">
-        <v>14</v>
-      </c>
-      <c r="G442" s="1">
-        <v>46281</v>
-      </c>
-      <c r="H442" s="1">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>841</v>
-      </c>
-      <c r="B443" t="s">
-        <v>858</v>
-      </c>
-      <c r="C443">
-        <v>1</v>
-      </c>
-      <c r="D443" t="s">
-        <v>170</v>
-      </c>
-      <c r="E443" t="s">
-        <v>57</v>
-      </c>
-      <c r="F443" t="s">
-        <v>58</v>
-      </c>
-      <c r="G443" s="1">
-        <v>46304</v>
-      </c>
-      <c r="H443" s="1">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
-        <v>841</v>
-      </c>
-      <c r="B444" t="s">
-        <v>859</v>
-      </c>
-      <c r="C444">
-        <v>1</v>
-      </c>
-      <c r="D444" t="s">
-        <v>170</v>
-      </c>
-      <c r="E444" t="s">
-        <v>57</v>
-      </c>
-      <c r="F444" t="s">
-        <v>58</v>
-      </c>
-      <c r="G444" s="1">
-        <v>46304</v>
-      </c>
-      <c r="H444" s="1">
         <v>46304</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B9876D3-807C-4034-A5EC-B42D9524EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA011AFE-DE55-43AF-AB39-5E0BC944D65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{D2CB09EE-8AA8-4E23-BE9E-BB5DBEBD4743}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{683CEE99-5F64-4EA1-9111-00B5A2B7BAD5}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="860">
   <si>
     <t>0001</t>
   </si>
@@ -2167,6 +2167,162 @@
     <t xml:space="preserve">  217344</t>
   </si>
   <si>
+    <t xml:space="preserve">  217345</t>
+  </si>
+  <si>
+    <t>SC39</t>
+  </si>
+  <si>
+    <t>SURVALMEDA CONSTRUCCIONES S. A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217346</t>
+  </si>
+  <si>
+    <t>DB14</t>
+  </si>
+  <si>
+    <t>DIMA BAÑOS &amp; COCINAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217352</t>
+  </si>
+  <si>
+    <t>JA01</t>
+  </si>
+  <si>
+    <t>JOSE ANACLETO E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217353</t>
+  </si>
+  <si>
+    <t>SA40</t>
+  </si>
+  <si>
+    <t>SANICENTRO S.A. SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217355</t>
+  </si>
+  <si>
+    <t>MJ21</t>
+  </si>
+  <si>
+    <t>MELCON JUAN CARLOS - SANITARIOS CAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217356</t>
+  </si>
+  <si>
+    <t>HI10</t>
+  </si>
+  <si>
+    <t>HIPERCAÑO S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217357</t>
+  </si>
+  <si>
+    <t>DC18</t>
+  </si>
+  <si>
+    <t>DI CARLO SEBASTIAN F -DI CARLO SANIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217361</t>
+  </si>
+  <si>
+    <t>TR21</t>
+  </si>
+  <si>
+    <t>TROFA SA - MUNDO CAÑO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217374</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TRIPOLI CARLOS L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217375</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>TRIPOLI ARNALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217376</t>
+  </si>
+  <si>
+    <t>AA05</t>
+  </si>
+  <si>
+    <t>SANITARIOS ALVAREZ SOC. LEY 19550 CAP. I SECCION I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217379</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2281,6 +2437,9 @@
     <t xml:space="preserve">    3025</t>
   </si>
   <si>
+    <t xml:space="preserve">    3026</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2365,10 +2524,7 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2781</t>
+    <t xml:space="preserve">    2783</t>
   </si>
   <si>
     <t>9999</t>
@@ -2420,12 +2576,6 @@
   </si>
   <si>
     <t xml:space="preserve">      98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     120</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2899,34 +3049,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9675168B-BF31-4FEE-B71B-A5364C0BB2C9}">
-  <dimension ref="A1:H416"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{774CBD00-FDE7-40F4-898D-A22423531B4A}">
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>802</v>
+        <v>852</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>803</v>
+        <v>853</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>804</v>
+        <v>854</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>805</v>
+        <v>855</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>806</v>
+        <v>856</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>807</v>
+        <v>857</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>808</v>
+        <v>858</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>809</v>
+        <v>859</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6242,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E129" t="s">
         <v>37</v>
@@ -7724,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E186" t="s">
         <v>406</v>
@@ -7880,7 +8030,7 @@
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E192" t="s">
         <v>422</v>
@@ -9596,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
         <v>544</v>
@@ -9648,7 +9798,7 @@
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E260" t="s">
         <v>548</v>
@@ -10064,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E276" t="s">
         <v>132</v>
@@ -10220,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E282" t="s">
         <v>590</v>
@@ -10246,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E283" t="s">
         <v>593</v>
@@ -10974,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E311" t="s">
         <v>151</v>
@@ -11208,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E320" t="s">
         <v>654</v>
@@ -11286,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E323" t="s">
         <v>654</v>
@@ -12031,62 +12181,62 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" t="s">
         <v>715</v>
       </c>
-      <c r="B352" t="s">
+      <c r="C352">
+        <v>1</v>
+      </c>
+      <c r="D352" t="s">
+        <v>170</v>
+      </c>
+      <c r="E352" t="s">
         <v>716</v>
       </c>
-      <c r="C352">
-        <v>1</v>
-      </c>
-      <c r="D352" t="s">
-        <v>2</v>
-      </c>
-      <c r="E352" t="s">
-        <v>200</v>
-      </c>
       <c r="F352" t="s">
-        <v>201</v>
+        <v>717</v>
       </c>
       <c r="G352" s="1">
-        <v>46148</v>
+        <v>46304</v>
       </c>
       <c r="H352" s="1">
-        <v>46149</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C353">
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E353" t="s">
-        <v>111</v>
+        <v>719</v>
       </c>
       <c r="F353" t="s">
-        <v>112</v>
+        <v>720</v>
       </c>
       <c r="G353" s="1">
-        <v>46268</v>
+        <v>46304</v>
       </c>
       <c r="H353" s="1">
-        <v>46268</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -12095,24 +12245,24 @@
         <v>170</v>
       </c>
       <c r="E354" t="s">
-        <v>393</v>
+        <v>719</v>
       </c>
       <c r="F354" t="s">
-        <v>394</v>
+        <v>720</v>
       </c>
       <c r="G354" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H354" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -12121,21 +12271,21 @@
         <v>170</v>
       </c>
       <c r="E355" t="s">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="F355" t="s">
-        <v>721</v>
+        <v>591</v>
       </c>
       <c r="G355" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H355" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B356" t="s">
         <v>723</v>
@@ -12144,24 +12294,24 @@
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E356" t="s">
-        <v>41</v>
+        <v>214</v>
       </c>
       <c r="F356" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="G356" s="1">
-        <v>46133</v>
+        <v>46304</v>
       </c>
       <c r="H356" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B357" t="s">
         <v>724</v>
@@ -12170,24 +12320,24 @@
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>214</v>
       </c>
       <c r="F357" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="G357" s="1">
-        <v>46134</v>
+        <v>46304</v>
       </c>
       <c r="H357" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B358" t="s">
         <v>725</v>
@@ -12196,287 +12346,287 @@
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E358" t="s">
-        <v>19</v>
+        <v>726</v>
       </c>
       <c r="F358" t="s">
-        <v>20</v>
+        <v>727</v>
       </c>
       <c r="G358" s="1">
-        <v>46156</v>
+        <v>46305</v>
       </c>
       <c r="H358" s="1">
-        <v>46156</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C359">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E359" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F359" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G359" s="1">
-        <v>46209</v>
+        <v>46305</v>
       </c>
       <c r="H359" s="1">
-        <v>46218</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E360" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F360" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G360" s="1">
-        <v>46213</v>
+        <v>46305</v>
       </c>
       <c r="H360" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E361" t="s">
-        <v>625</v>
+        <v>735</v>
       </c>
       <c r="F361" t="s">
-        <v>626</v>
+        <v>736</v>
       </c>
       <c r="G361" s="1">
-        <v>46213</v>
+        <v>46305</v>
       </c>
       <c r="H361" s="1">
-        <v>46216</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E362" t="s">
-        <v>625</v>
+        <v>738</v>
       </c>
       <c r="F362" t="s">
-        <v>626</v>
+        <v>739</v>
       </c>
       <c r="G362" s="1">
-        <v>46224</v>
+        <v>46305</v>
       </c>
       <c r="H362" s="1">
-        <v>46224</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E363" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="F363" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="G363" s="1">
-        <v>46253</v>
+        <v>46305</v>
       </c>
       <c r="H363" s="1">
-        <v>46253</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E364" t="s">
-        <v>211</v>
+        <v>719</v>
       </c>
       <c r="F364" t="s">
-        <v>212</v>
+        <v>720</v>
       </c>
       <c r="G364" s="1">
-        <v>46273</v>
+        <v>46307</v>
       </c>
       <c r="H364" s="1">
-        <v>46274</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" t="s">
         <v>170</v>
       </c>
       <c r="E365" t="s">
-        <v>739</v>
+        <v>376</v>
       </c>
       <c r="F365" t="s">
-        <v>740</v>
+        <v>377</v>
       </c>
       <c r="G365" s="1">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="H365" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E366" t="s">
-        <v>221</v>
+        <v>744</v>
       </c>
       <c r="F366" t="s">
-        <v>222</v>
+        <v>745</v>
       </c>
       <c r="G366" s="1">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="H366" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E367" t="s">
-        <v>625</v>
+        <v>744</v>
       </c>
       <c r="F367" t="s">
-        <v>626</v>
+        <v>745</v>
       </c>
       <c r="G367" s="1">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="H367" s="1">
-        <v>46301</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E368" t="s">
-        <v>347</v>
+        <v>596</v>
       </c>
       <c r="F368" t="s">
-        <v>348</v>
+        <v>597</v>
       </c>
       <c r="G368" s="1">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="H368" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -12485,24 +12635,24 @@
         <v>170</v>
       </c>
       <c r="E369" t="s">
+        <v>726</v>
+      </c>
+      <c r="F369" t="s">
         <v>727</v>
       </c>
-      <c r="F369" t="s">
-        <v>728</v>
-      </c>
       <c r="G369" s="1">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="H369" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12511,50 +12661,50 @@
         <v>170</v>
       </c>
       <c r="E370" t="s">
-        <v>513</v>
+        <v>373</v>
       </c>
       <c r="F370" t="s">
-        <v>514</v>
+        <v>374</v>
       </c>
       <c r="G370" s="1">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="H370" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E371" t="s">
-        <v>537</v>
+        <v>234</v>
       </c>
       <c r="F371" t="s">
-        <v>538</v>
+        <v>235</v>
       </c>
       <c r="G371" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H371" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -12563,24 +12713,24 @@
         <v>170</v>
       </c>
       <c r="E372" t="s">
-        <v>537</v>
+        <v>204</v>
       </c>
       <c r="F372" t="s">
-        <v>538</v>
+        <v>205</v>
       </c>
       <c r="G372" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H372" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12589,24 +12739,24 @@
         <v>170</v>
       </c>
       <c r="E373" t="s">
-        <v>537</v>
+        <v>92</v>
       </c>
       <c r="F373" t="s">
-        <v>538</v>
+        <v>93</v>
       </c>
       <c r="G373" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H373" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -12615,24 +12765,24 @@
         <v>170</v>
       </c>
       <c r="E374" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="F374" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="G374" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H374" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -12641,24 +12791,24 @@
         <v>170</v>
       </c>
       <c r="E375" t="s">
-        <v>625</v>
+        <v>16</v>
       </c>
       <c r="F375" t="s">
-        <v>626</v>
+        <v>17</v>
       </c>
       <c r="G375" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H375" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -12667,24 +12817,24 @@
         <v>170</v>
       </c>
       <c r="E376" t="s">
-        <v>727</v>
+        <v>487</v>
       </c>
       <c r="F376" t="s">
-        <v>728</v>
+        <v>488</v>
       </c>
       <c r="G376" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H376" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -12693,128 +12843,128 @@
         <v>170</v>
       </c>
       <c r="E377" t="s">
-        <v>657</v>
+        <v>757</v>
       </c>
       <c r="F377" t="s">
-        <v>658</v>
+        <v>758</v>
       </c>
       <c r="G377" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H377" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E378" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="F378" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="G378" s="1">
-        <v>46063</v>
+        <v>46308</v>
       </c>
       <c r="H378" s="1">
-        <v>46064</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E379" t="s">
-        <v>57</v>
+        <v>763</v>
       </c>
       <c r="F379" t="s">
-        <v>58</v>
+        <v>764</v>
       </c>
       <c r="G379" s="1">
-        <v>46113</v>
+        <v>46308</v>
       </c>
       <c r="H379" s="1">
-        <v>46125</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E380" t="s">
-        <v>57</v>
+        <v>224</v>
       </c>
       <c r="F380" t="s">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="G380" s="1">
-        <v>46125</v>
+        <v>46308</v>
       </c>
       <c r="H380" s="1">
-        <v>46125</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E381" t="s">
-        <v>57</v>
+        <v>431</v>
       </c>
       <c r="F381" t="s">
-        <v>58</v>
+        <v>432</v>
       </c>
       <c r="G381" s="1">
-        <v>46126</v>
+        <v>46308</v>
       </c>
       <c r="H381" s="1">
-        <v>46126</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="B382" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -12823,24 +12973,24 @@
         <v>2</v>
       </c>
       <c r="E382" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="F382" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="G382" s="1">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="H382" s="1">
-        <v>46126</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="B383" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -12849,128 +12999,128 @@
         <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="F383" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="G383" s="1">
-        <v>46128</v>
+        <v>46268</v>
       </c>
       <c r="H383" s="1">
-        <v>46128</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="B384" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="C384">
         <v>1</v>
       </c>
       <c r="D384" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E384" t="s">
-        <v>57</v>
+        <v>393</v>
       </c>
       <c r="F384" t="s">
-        <v>58</v>
+        <v>394</v>
       </c>
       <c r="G384" s="1">
-        <v>46132</v>
+        <v>46303</v>
       </c>
       <c r="H384" s="1">
-        <v>46132</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="B385" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E385" t="s">
-        <v>57</v>
+        <v>772</v>
       </c>
       <c r="F385" t="s">
-        <v>58</v>
+        <v>773</v>
       </c>
       <c r="G385" s="1">
-        <v>46161</v>
+        <v>46303</v>
       </c>
       <c r="H385" s="1">
-        <v>46161</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B386" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="C386">
         <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E386" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F386" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G386" s="1">
-        <v>46174</v>
+        <v>46133</v>
       </c>
       <c r="H386" s="1">
-        <v>46174</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B387" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="C387">
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E387" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F387" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G387" s="1">
-        <v>46174</v>
+        <v>46134</v>
       </c>
       <c r="H387" s="1">
-        <v>46174</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B388" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -12979,62 +13129,62 @@
         <v>6</v>
       </c>
       <c r="E388" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="F388" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G388" s="1">
-        <v>46195</v>
+        <v>46156</v>
       </c>
       <c r="H388" s="1">
-        <v>46252</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B389" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="C389">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D389" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E389" t="s">
-        <v>57</v>
+        <v>779</v>
       </c>
       <c r="F389" t="s">
-        <v>58</v>
+        <v>780</v>
       </c>
       <c r="G389" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="H389" s="1">
-        <v>46210</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B390" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="C390">
         <v>1</v>
       </c>
       <c r="D390" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E390" t="s">
-        <v>57</v>
+        <v>782</v>
       </c>
       <c r="F390" t="s">
-        <v>58</v>
+        <v>783</v>
       </c>
       <c r="G390" s="1">
         <v>46213</v>
@@ -13045,270 +13195,270 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B391" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="C391">
         <v>1</v>
       </c>
       <c r="D391" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E391" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="F391" t="s">
-        <v>58</v>
+        <v>626</v>
       </c>
       <c r="G391" s="1">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="H391" s="1">
-        <v>46252</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B392" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="C392">
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E392" t="s">
-        <v>77</v>
+        <v>625</v>
       </c>
       <c r="F392" t="s">
-        <v>78</v>
+        <v>626</v>
       </c>
       <c r="G392" s="1">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="H392" s="1">
-        <v>46226</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B393" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="C393">
         <v>1</v>
       </c>
       <c r="D393" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E393" t="s">
-        <v>57</v>
+        <v>787</v>
       </c>
       <c r="F393" t="s">
-        <v>58</v>
+        <v>788</v>
       </c>
       <c r="G393" s="1">
-        <v>46227</v>
+        <v>46253</v>
       </c>
       <c r="H393" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B394" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="C394">
         <v>1</v>
       </c>
       <c r="D394" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E394" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="F394" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="G394" s="1">
-        <v>46227</v>
+        <v>46273</v>
       </c>
       <c r="H394" s="1">
-        <v>46252</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B395" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="C395">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D395" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E395" t="s">
-        <v>57</v>
+        <v>791</v>
       </c>
       <c r="F395" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
       <c r="G395" s="1">
-        <v>46227</v>
+        <v>46300</v>
       </c>
       <c r="H395" s="1">
-        <v>46228</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B396" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="C396">
         <v>1</v>
       </c>
       <c r="D396" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E396" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="F396" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="G396" s="1">
-        <v>46230</v>
+        <v>46300</v>
       </c>
       <c r="H396" s="1">
-        <v>46252</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B397" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
       <c r="C397">
         <v>1</v>
       </c>
       <c r="D397" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E397" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="F397" t="s">
-        <v>58</v>
+        <v>626</v>
       </c>
       <c r="G397" s="1">
-        <v>46231</v>
+        <v>46300</v>
       </c>
       <c r="H397" s="1">
-        <v>46231</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B398" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="C398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E398" t="s">
-        <v>57</v>
+        <v>347</v>
       </c>
       <c r="F398" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G398" s="1">
-        <v>46254</v>
+        <v>46302</v>
       </c>
       <c r="H398" s="1">
-        <v>46254</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B399" t="s">
-        <v>777</v>
+        <v>796</v>
       </c>
       <c r="C399">
         <v>1</v>
       </c>
       <c r="D399" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E399" t="s">
-        <v>57</v>
+        <v>779</v>
       </c>
       <c r="F399" t="s">
-        <v>58</v>
+        <v>780</v>
       </c>
       <c r="G399" s="1">
-        <v>46255</v>
+        <v>46302</v>
       </c>
       <c r="H399" s="1">
-        <v>46255</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B400" t="s">
-        <v>778</v>
+        <v>797</v>
       </c>
       <c r="C400">
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E400" t="s">
-        <v>57</v>
+        <v>513</v>
       </c>
       <c r="F400" t="s">
-        <v>58</v>
+        <v>514</v>
       </c>
       <c r="G400" s="1">
-        <v>46260</v>
+        <v>46303</v>
       </c>
       <c r="H400" s="1">
-        <v>46260</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B401" t="s">
-        <v>779</v>
+        <v>798</v>
       </c>
       <c r="C401">
         <v>1</v>
@@ -13317,76 +13467,76 @@
         <v>6</v>
       </c>
       <c r="E401" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F401" t="s">
-        <v>58</v>
+        <v>538</v>
       </c>
       <c r="G401" s="1">
-        <v>46289</v>
+        <v>46303</v>
       </c>
       <c r="H401" s="1">
-        <v>46289</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B402" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
       <c r="C402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E402" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F402" t="s">
-        <v>58</v>
+        <v>538</v>
       </c>
       <c r="G402" s="1">
-        <v>46294</v>
+        <v>46303</v>
       </c>
       <c r="H402" s="1">
-        <v>46294</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B403" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
       <c r="C403">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E403" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F403" t="s">
-        <v>58</v>
+        <v>538</v>
       </c>
       <c r="G403" s="1">
         <v>46303</v>
       </c>
       <c r="H403" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="B404" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="C404">
         <v>1</v>
@@ -13395,180 +13545,180 @@
         <v>170</v>
       </c>
       <c r="E404" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="F404" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="G404" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
       <c r="H404" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B405" t="s">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="C405">
         <v>1</v>
       </c>
       <c r="D405" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E405" t="s">
-        <v>785</v>
+        <v>625</v>
       </c>
       <c r="F405" t="s">
-        <v>786</v>
+        <v>626</v>
       </c>
       <c r="G405" s="1">
-        <v>46157</v>
+        <v>46304</v>
       </c>
       <c r="H405" s="1">
-        <v>46157</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B406" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="C406">
         <v>1</v>
       </c>
       <c r="D406" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E406" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="F406" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="G406" s="1">
-        <v>46168</v>
+        <v>46304</v>
       </c>
       <c r="H406" s="1">
-        <v>46170</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B407" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="C407">
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E407" t="s">
-        <v>785</v>
+        <v>657</v>
       </c>
       <c r="F407" t="s">
-        <v>786</v>
+        <v>658</v>
       </c>
       <c r="G407" s="1">
-        <v>46218</v>
+        <v>46304</v>
       </c>
       <c r="H407" s="1">
-        <v>46218</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B408" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="C408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E408" t="s">
-        <v>785</v>
+        <v>83</v>
       </c>
       <c r="F408" t="s">
-        <v>786</v>
+        <v>84</v>
       </c>
       <c r="G408" s="1">
-        <v>46244</v>
+        <v>46308</v>
       </c>
       <c r="H408" s="1">
-        <v>46244</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B409" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="C409">
         <v>1</v>
       </c>
       <c r="D409" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E409" t="s">
-        <v>785</v>
+        <v>808</v>
       </c>
       <c r="F409" t="s">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="G409" s="1">
-        <v>46247</v>
+        <v>46063</v>
       </c>
       <c r="H409" s="1">
-        <v>46247</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B410" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="C410">
         <v>1</v>
       </c>
       <c r="D410" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E410" t="s">
-        <v>794</v>
+        <v>57</v>
       </c>
       <c r="F410" t="s">
-        <v>795</v>
+        <v>58</v>
       </c>
       <c r="G410" s="1">
-        <v>46247</v>
+        <v>46113</v>
       </c>
       <c r="H410" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B411" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -13577,24 +13727,24 @@
         <v>2</v>
       </c>
       <c r="E411" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="F411" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="G411" s="1">
-        <v>46255</v>
+        <v>46125</v>
       </c>
       <c r="H411" s="1">
-        <v>46255</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B412" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="C412">
         <v>1</v>
@@ -13603,24 +13753,24 @@
         <v>2</v>
       </c>
       <c r="E412" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="F412" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="G412" s="1">
-        <v>46258</v>
+        <v>46126</v>
       </c>
       <c r="H412" s="1">
-        <v>46258</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B413" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -13629,56 +13779,56 @@
         <v>2</v>
       </c>
       <c r="E413" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="F413" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="G413" s="1">
-        <v>46262</v>
+        <v>46126</v>
       </c>
       <c r="H413" s="1">
-        <v>46265</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B414" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="C414">
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E414" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F414" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G414" s="1">
-        <v>46281</v>
+        <v>46128</v>
       </c>
       <c r="H414" s="1">
-        <v>46283</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B415" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="C415">
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
@@ -13687,24 +13837,24 @@
         <v>58</v>
       </c>
       <c r="G415" s="1">
-        <v>46304</v>
+        <v>46132</v>
       </c>
       <c r="H415" s="1">
-        <v>46304</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="B416" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="C416">
         <v>1</v>
       </c>
       <c r="D416" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E416" t="s">
         <v>57</v>
@@ -13713,10 +13863,738 @@
         <v>58</v>
       </c>
       <c r="G416" s="1">
-        <v>46304</v>
+        <v>46161</v>
       </c>
       <c r="H416" s="1">
-        <v>46304</v>
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>806</v>
+      </c>
+      <c r="B417" t="s">
+        <v>817</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" t="s">
+        <v>2</v>
+      </c>
+      <c r="E417" t="s">
+        <v>57</v>
+      </c>
+      <c r="F417" t="s">
+        <v>58</v>
+      </c>
+      <c r="G417" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H417" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>806</v>
+      </c>
+      <c r="B418" t="s">
+        <v>818</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418" t="s">
+        <v>2</v>
+      </c>
+      <c r="E418" t="s">
+        <v>57</v>
+      </c>
+      <c r="F418" t="s">
+        <v>58</v>
+      </c>
+      <c r="G418" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H418" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>806</v>
+      </c>
+      <c r="B419" t="s">
+        <v>819</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419" t="s">
+        <v>6</v>
+      </c>
+      <c r="E419" t="s">
+        <v>57</v>
+      </c>
+      <c r="F419" t="s">
+        <v>58</v>
+      </c>
+      <c r="G419" s="1">
+        <v>46195</v>
+      </c>
+      <c r="H419" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>806</v>
+      </c>
+      <c r="B420" t="s">
+        <v>820</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+      <c r="D420" t="s">
+        <v>6</v>
+      </c>
+      <c r="E420" t="s">
+        <v>57</v>
+      </c>
+      <c r="F420" t="s">
+        <v>58</v>
+      </c>
+      <c r="G420" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H420" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>806</v>
+      </c>
+      <c r="B421" t="s">
+        <v>821</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+      <c r="D421" t="s">
+        <v>2</v>
+      </c>
+      <c r="E421" t="s">
+        <v>57</v>
+      </c>
+      <c r="F421" t="s">
+        <v>58</v>
+      </c>
+      <c r="G421" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H421" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>806</v>
+      </c>
+      <c r="B422" t="s">
+        <v>822</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422" t="s">
+        <v>6</v>
+      </c>
+      <c r="E422" t="s">
+        <v>57</v>
+      </c>
+      <c r="F422" t="s">
+        <v>58</v>
+      </c>
+      <c r="G422" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H422" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>806</v>
+      </c>
+      <c r="B423" t="s">
+        <v>823</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>6</v>
+      </c>
+      <c r="E423" t="s">
+        <v>77</v>
+      </c>
+      <c r="F423" t="s">
+        <v>78</v>
+      </c>
+      <c r="G423" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H423" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>806</v>
+      </c>
+      <c r="B424" t="s">
+        <v>824</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424" t="s">
+        <v>170</v>
+      </c>
+      <c r="E424" t="s">
+        <v>57</v>
+      </c>
+      <c r="F424" t="s">
+        <v>58</v>
+      </c>
+      <c r="G424" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H424" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>806</v>
+      </c>
+      <c r="B425" t="s">
+        <v>825</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425" t="s">
+        <v>6</v>
+      </c>
+      <c r="E425" t="s">
+        <v>57</v>
+      </c>
+      <c r="F425" t="s">
+        <v>58</v>
+      </c>
+      <c r="G425" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H425" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>806</v>
+      </c>
+      <c r="B426" t="s">
+        <v>826</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+      <c r="D426" t="s">
+        <v>6</v>
+      </c>
+      <c r="E426" t="s">
+        <v>57</v>
+      </c>
+      <c r="F426" t="s">
+        <v>58</v>
+      </c>
+      <c r="G426" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H426" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>806</v>
+      </c>
+      <c r="B427" t="s">
+        <v>827</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+      <c r="D427" t="s">
+        <v>6</v>
+      </c>
+      <c r="E427" t="s">
+        <v>77</v>
+      </c>
+      <c r="F427" t="s">
+        <v>78</v>
+      </c>
+      <c r="G427" s="1">
+        <v>46230</v>
+      </c>
+      <c r="H427" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>806</v>
+      </c>
+      <c r="B428" t="s">
+        <v>828</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428" t="s">
+        <v>6</v>
+      </c>
+      <c r="E428" t="s">
+        <v>57</v>
+      </c>
+      <c r="F428" t="s">
+        <v>58</v>
+      </c>
+      <c r="G428" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H428" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>806</v>
+      </c>
+      <c r="B429" t="s">
+        <v>829</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
+      <c r="D429" t="s">
+        <v>6</v>
+      </c>
+      <c r="E429" t="s">
+        <v>57</v>
+      </c>
+      <c r="F429" t="s">
+        <v>58</v>
+      </c>
+      <c r="G429" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H429" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>806</v>
+      </c>
+      <c r="B430" t="s">
+        <v>830</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>2</v>
+      </c>
+      <c r="E430" t="s">
+        <v>57</v>
+      </c>
+      <c r="F430" t="s">
+        <v>58</v>
+      </c>
+      <c r="G430" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H430" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>806</v>
+      </c>
+      <c r="B431" t="s">
+        <v>831</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431" t="s">
+        <v>6</v>
+      </c>
+      <c r="E431" t="s">
+        <v>57</v>
+      </c>
+      <c r="F431" t="s">
+        <v>58</v>
+      </c>
+      <c r="G431" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H431" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>806</v>
+      </c>
+      <c r="B432" t="s">
+        <v>832</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+      <c r="D432" t="s">
+        <v>6</v>
+      </c>
+      <c r="E432" t="s">
+        <v>57</v>
+      </c>
+      <c r="F432" t="s">
+        <v>58</v>
+      </c>
+      <c r="G432" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H432" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>806</v>
+      </c>
+      <c r="B433" t="s">
+        <v>833</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433" t="s">
+        <v>6</v>
+      </c>
+      <c r="E433" t="s">
+        <v>57</v>
+      </c>
+      <c r="F433" t="s">
+        <v>58</v>
+      </c>
+      <c r="G433" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H433" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>806</v>
+      </c>
+      <c r="B434" t="s">
+        <v>834</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434" t="s">
+        <v>170</v>
+      </c>
+      <c r="E434" t="s">
+        <v>132</v>
+      </c>
+      <c r="F434" t="s">
+        <v>133</v>
+      </c>
+      <c r="G434" s="1">
+        <v>46308</v>
+      </c>
+      <c r="H434" s="1">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>835</v>
+      </c>
+      <c r="B435" t="s">
+        <v>836</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435" t="s">
+        <v>2</v>
+      </c>
+      <c r="E435" t="s">
+        <v>837</v>
+      </c>
+      <c r="F435" t="s">
+        <v>838</v>
+      </c>
+      <c r="G435" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H435" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>835</v>
+      </c>
+      <c r="B436" t="s">
+        <v>839</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436" t="s">
+        <v>2</v>
+      </c>
+      <c r="E436" t="s">
+        <v>840</v>
+      </c>
+      <c r="F436" t="s">
+        <v>841</v>
+      </c>
+      <c r="G436" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H436" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>835</v>
+      </c>
+      <c r="B437" t="s">
+        <v>842</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437" t="s">
+        <v>2</v>
+      </c>
+      <c r="E437" t="s">
+        <v>837</v>
+      </c>
+      <c r="F437" t="s">
+        <v>838</v>
+      </c>
+      <c r="G437" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H437" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>835</v>
+      </c>
+      <c r="B438" t="s">
+        <v>843</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+      <c r="D438" t="s">
+        <v>2</v>
+      </c>
+      <c r="E438" t="s">
+        <v>837</v>
+      </c>
+      <c r="F438" t="s">
+        <v>838</v>
+      </c>
+      <c r="G438" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H438" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>835</v>
+      </c>
+      <c r="B439" t="s">
+        <v>844</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+      <c r="D439" t="s">
+        <v>2</v>
+      </c>
+      <c r="E439" t="s">
+        <v>837</v>
+      </c>
+      <c r="F439" t="s">
+        <v>838</v>
+      </c>
+      <c r="G439" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H439" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>835</v>
+      </c>
+      <c r="B440" t="s">
+        <v>845</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+      <c r="D440" t="s">
+        <v>2</v>
+      </c>
+      <c r="E440" t="s">
+        <v>846</v>
+      </c>
+      <c r="F440" t="s">
+        <v>847</v>
+      </c>
+      <c r="G440" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H440" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>835</v>
+      </c>
+      <c r="B441" t="s">
+        <v>848</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+      <c r="D441" t="s">
+        <v>2</v>
+      </c>
+      <c r="E441" t="s">
+        <v>837</v>
+      </c>
+      <c r="F441" t="s">
+        <v>838</v>
+      </c>
+      <c r="G441" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H441" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>835</v>
+      </c>
+      <c r="B442" t="s">
+        <v>849</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+      <c r="D442" t="s">
+        <v>2</v>
+      </c>
+      <c r="E442" t="s">
+        <v>837</v>
+      </c>
+      <c r="F442" t="s">
+        <v>838</v>
+      </c>
+      <c r="G442" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H442" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>835</v>
+      </c>
+      <c r="B443" t="s">
+        <v>850</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+      <c r="D443" t="s">
+        <v>2</v>
+      </c>
+      <c r="E443" t="s">
+        <v>837</v>
+      </c>
+      <c r="F443" t="s">
+        <v>838</v>
+      </c>
+      <c r="G443" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H443" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>835</v>
+      </c>
+      <c r="B444" t="s">
+        <v>851</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+      <c r="D444" t="s">
+        <v>6</v>
+      </c>
+      <c r="E444" t="s">
+        <v>13</v>
+      </c>
+      <c r="F444" t="s">
+        <v>14</v>
+      </c>
+      <c r="G444" s="1">
+        <v>46281</v>
+      </c>
+      <c r="H444" s="1">
+        <v>46283</v>
       </c>
     </row>
   </sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E25ADC7-40BE-4287-B9F0-51E2A098B669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52D8A3B5-4D2D-40CB-9D94-9107C70803C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9E1BFF19-7E50-46EE-BCF8-644DF56743E7}"/>
+    <workbookView xWindow="28320" yWindow="2505" windowWidth="15375" windowHeight="8325" xr2:uid="{BD70D57C-6A22-4E38-90CD-E502C61EE9E2}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="922">
   <si>
     <t>0001</t>
   </si>
@@ -757,6 +757,15 @@
     <t xml:space="preserve">  215803</t>
   </si>
   <si>
+    <t xml:space="preserve">  215897</t>
+  </si>
+  <si>
+    <t>CG25</t>
+  </si>
+  <si>
+    <t>CASAGRES S.A.S.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  215948</t>
   </si>
   <si>
@@ -877,6 +886,15 @@
     <t>HEINZE GABRIEL ESTEBAN</t>
   </si>
   <si>
+    <t xml:space="preserve">  216512</t>
+  </si>
+  <si>
+    <t>GM22</t>
+  </si>
+  <si>
+    <t>GRUPO MERCANTILES S. A. S</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216514</t>
   </si>
   <si>
@@ -1834,18 +1852,6 @@
     <t xml:space="preserve">  217308</t>
   </si>
   <si>
-    <t xml:space="preserve">  217312</t>
-  </si>
-  <si>
-    <t>SC33</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217313</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217315</t>
   </si>
   <si>
@@ -2365,6 +2371,138 @@
     <t>CORRALON PASQUINI SRL</t>
   </si>
   <si>
+    <t xml:space="preserve">  217420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217421</t>
+  </si>
+  <si>
+    <t>GF01</t>
+  </si>
+  <si>
+    <t>GUIDOLI FLORIO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217422</t>
+  </si>
+  <si>
+    <t>LJ15</t>
+  </si>
+  <si>
+    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217430</t>
+  </si>
+  <si>
+    <t>GA31</t>
+  </si>
+  <si>
+    <t>GALBAHIA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217434</t>
+  </si>
+  <si>
+    <t>MM45</t>
+  </si>
+  <si>
+    <t>MATERIALES MONTSERRAT S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217441</t>
+  </si>
+  <si>
+    <t>CO42</t>
+  </si>
+  <si>
+    <t>COLADONATO FEDERICO N.-SANITARIOS CARUPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217442</t>
+  </si>
+  <si>
+    <t>PM26</t>
+  </si>
+  <si>
+    <t>PEGORER MARTIN EDUARDO - SANITARIOS RINCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217443</t>
+  </si>
+  <si>
+    <t>AG26</t>
+  </si>
+  <si>
+    <t>AGROREDES SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217446</t>
+  </si>
+  <si>
+    <t>LE14</t>
+  </si>
+  <si>
+    <t>L.E.CER S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217448</t>
+  </si>
+  <si>
+    <t>EP11</t>
+  </si>
+  <si>
+    <t>ELIAS PABLO E -ISMAEL MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217449</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2377,13 +2515,16 @@
     <t xml:space="preserve">     136</t>
   </si>
   <si>
-    <t xml:space="preserve">     138</t>
-  </si>
-  <si>
-    <t>TB02</t>
-  </si>
-  <si>
-    <t>IT BROKERS S.A.</t>
+    <t>0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  177122</t>
+  </si>
+  <si>
+    <t>CS52</t>
+  </si>
+  <si>
+    <t>CONSTRUCTORA SUDAMERICANA ING Y CONST SA</t>
   </si>
   <si>
     <t>0008</t>
@@ -2482,6 +2623,9 @@
     <t xml:space="preserve">    3028</t>
   </si>
   <si>
+    <t xml:space="preserve">    3029</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2564,6 +2708,9 @@
   </si>
   <si>
     <t xml:space="preserve">    2644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2794</t>
   </si>
   <si>
     <t>9999</t>
@@ -3088,34 +3235,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC711EFA-49BB-4BDB-B006-7BE0CD882873}">
-  <dimension ref="A1:H453"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46579758-A2A5-4DDC-80DA-3BD8D8C6BF5E}">
+  <dimension ref="A1:H481"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>865</v>
+        <v>914</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>866</v>
+        <v>915</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>867</v>
+        <v>916</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>868</v>
+        <v>917</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>869</v>
+        <v>918</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>870</v>
+        <v>919</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>871</v>
+        <v>920</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>872</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5729,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E102" t="s">
         <v>246</v>
@@ -5738,10 +5885,10 @@
         <v>247</v>
       </c>
       <c r="G102" s="1">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="H102" s="1">
-        <v>46282</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -5755,7 +5902,7 @@
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E103" t="s">
         <v>249</v>
@@ -5764,10 +5911,10 @@
         <v>250</v>
       </c>
       <c r="G103" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="H103" s="1">
-        <v>46287</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -5781,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E104" t="s">
         <v>252</v>
@@ -5793,7 +5940,7 @@
         <v>46283</v>
       </c>
       <c r="H104" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -5804,22 +5951,22 @@
         <v>254</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E105" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="F105" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="G105" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="H105" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -5827,25 +5974,25 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E106" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="F106" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="G106" s="1">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="H106" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -5856,10 +6003,10 @@
         <v>258</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E107" t="s">
         <v>259</v>
@@ -5871,7 +6018,7 @@
         <v>46287</v>
       </c>
       <c r="H107" s="1">
-        <v>46300</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -5882,10 +6029,10 @@
         <v>261</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E108" t="s">
         <v>262</v>
@@ -5897,7 +6044,7 @@
         <v>46287</v>
       </c>
       <c r="H108" s="1">
-        <v>46294</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -5911,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E109" t="s">
         <v>265</v>
@@ -5923,7 +6070,7 @@
         <v>46287</v>
       </c>
       <c r="H109" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -5937,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E110" t="s">
         <v>268</v>
@@ -5949,7 +6096,7 @@
         <v>46287</v>
       </c>
       <c r="H110" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -5960,10 +6107,10 @@
         <v>270</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E111" t="s">
         <v>271</v>
@@ -5972,10 +6119,10 @@
         <v>272</v>
       </c>
       <c r="G111" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H111" s="1">
         <v>46288</v>
-      </c>
-      <c r="H111" s="1">
-        <v>46295</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -5986,7 +6133,7 @@
         <v>273</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112" t="s">
         <v>2</v>
@@ -6001,7 +6148,7 @@
         <v>46288</v>
       </c>
       <c r="H112" s="1">
-        <v>46288</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -6012,10 +6159,10 @@
         <v>276</v>
       </c>
       <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="s">
         <v>2</v>
-      </c>
-      <c r="D113" t="s">
-        <v>170</v>
       </c>
       <c r="E113" t="s">
         <v>277</v>
@@ -6027,7 +6174,7 @@
         <v>46288</v>
       </c>
       <c r="H113" s="1">
-        <v>46308</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -6041,19 +6188,19 @@
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E114" t="s">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="F114" t="s">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="G114" s="1">
         <v>46288</v>
       </c>
       <c r="H114" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -6061,25 +6208,25 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="F115" t="s">
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="G115" s="1">
         <v>46288</v>
       </c>
       <c r="H115" s="1">
-        <v>46289</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -6087,25 +6234,25 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>92</v>
+        <v>222</v>
       </c>
       <c r="F116" t="s">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="G116" s="1">
         <v>46288</v>
       </c>
       <c r="H116" s="1">
-        <v>46308</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -6113,25 +6260,25 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E117" t="s">
-        <v>283</v>
+        <v>92</v>
       </c>
       <c r="F117" t="s">
-        <v>284</v>
+        <v>93</v>
       </c>
       <c r="G117" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="H117" s="1">
-        <v>46290</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -6142,10 +6289,10 @@
         <v>285</v>
       </c>
       <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
         <v>2</v>
-      </c>
-      <c r="D118" t="s">
-        <v>170</v>
       </c>
       <c r="E118" t="s">
         <v>286</v>
@@ -6154,10 +6301,10 @@
         <v>287</v>
       </c>
       <c r="G118" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H118" s="1">
         <v>46290</v>
-      </c>
-      <c r="H118" s="1">
-        <v>46308</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -6171,19 +6318,19 @@
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E119" t="s">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="F119" t="s">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="G119" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="H119" s="1">
-        <v>46293</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -6191,25 +6338,25 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E120" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F120" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G120" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="H120" s="1">
-        <v>46293</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -6217,25 +6364,25 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="F121" t="s">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="G121" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="H121" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -6252,16 +6399,16 @@
         <v>2</v>
       </c>
       <c r="E122" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="F122" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="G122" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="H122" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -6269,25 +6416,25 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
         <v>2</v>
       </c>
-      <c r="D123" t="s">
-        <v>6</v>
-      </c>
       <c r="E123" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="F123" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="G123" s="1">
         <v>46294</v>
       </c>
       <c r="H123" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -6295,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -6304,10 +6451,10 @@
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="F124" t="s">
-        <v>155</v>
+        <v>243</v>
       </c>
       <c r="G124" s="1">
         <v>46294</v>
@@ -6321,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E125" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="F125" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="G125" s="1">
         <v>46294</v>
       </c>
       <c r="H125" s="1">
-        <v>46308</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -6347,25 +6494,25 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126" t="s">
         <v>2</v>
       </c>
-      <c r="D126" t="s">
-        <v>170</v>
-      </c>
       <c r="E126" t="s">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="F126" t="s">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="G126" s="1">
         <v>46294</v>
       </c>
       <c r="H126" s="1">
-        <v>46308</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -6376,10 +6523,10 @@
         <v>304</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E127" t="s">
         <v>305</v>
@@ -6388,10 +6535,10 @@
         <v>306</v>
       </c>
       <c r="G127" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="H127" s="1">
-        <v>46296</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -6402,22 +6549,22 @@
         <v>307</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E128" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="F128" t="s">
-        <v>38</v>
+        <v>309</v>
       </c>
       <c r="G128" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="H128" s="1">
-        <v>46295</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -6425,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -6434,16 +6581,16 @@
         <v>2</v>
       </c>
       <c r="E129" t="s">
-        <v>37</v>
+        <v>311</v>
       </c>
       <c r="F129" t="s">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="G129" s="1">
         <v>46295</v>
       </c>
       <c r="H129" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -6451,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -6477,13 +6624,13 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C131">
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E131" t="s">
         <v>37</v>
@@ -6503,13 +6650,13 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E132" t="s">
         <v>37</v>
@@ -6529,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -6555,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -6581,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -6607,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -6633,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -6659,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -6685,13 +6832,13 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E139" t="s">
         <v>37</v>
@@ -6703,7 +6850,7 @@
         <v>46295</v>
       </c>
       <c r="H139" s="1">
-        <v>46302</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -6711,25 +6858,25 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>320</v>
+        <v>37</v>
       </c>
       <c r="F140" t="s">
-        <v>321</v>
+        <v>38</v>
       </c>
       <c r="G140" s="1">
         <v>46295</v>
       </c>
       <c r="H140" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -6737,25 +6884,25 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C141">
         <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>323</v>
+        <v>37</v>
       </c>
       <c r="F141" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="G141" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="H141" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -6769,16 +6916,16 @@
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>326</v>
       </c>
       <c r="F142" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
       <c r="G142" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="H142" s="1">
         <v>46296</v>
@@ -6789,25 +6936,25 @@
         <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" t="s">
         <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>37</v>
+        <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
       <c r="G143" s="1">
         <v>46296</v>
       </c>
       <c r="H143" s="1">
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -6815,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6833,7 +6980,7 @@
         <v>46296</v>
       </c>
       <c r="H144" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -6841,7 +6988,7 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -6850,16 +6997,16 @@
         <v>170</v>
       </c>
       <c r="E145" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="F145" t="s">
-        <v>223</v>
+        <v>38</v>
       </c>
       <c r="G145" s="1">
         <v>46296</v>
       </c>
       <c r="H145" s="1">
-        <v>46308</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -6867,25 +7014,25 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E146" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="F146" t="s">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="G146" s="1">
         <v>46296</v>
       </c>
       <c r="H146" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -6893,25 +7040,25 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E147" t="s">
-        <v>333</v>
+        <v>222</v>
       </c>
       <c r="F147" t="s">
-        <v>334</v>
+        <v>223</v>
       </c>
       <c r="G147" s="1">
         <v>46296</v>
       </c>
       <c r="H147" s="1">
-        <v>46296</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -6925,7 +7072,7 @@
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E148" t="s">
         <v>336</v>
@@ -6951,7 +7098,7 @@
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E149" t="s">
         <v>339</v>
@@ -6960,10 +7107,10 @@
         <v>340</v>
       </c>
       <c r="G149" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="H149" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6977,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E150" t="s">
         <v>342</v>
@@ -6986,10 +7133,10 @@
         <v>343</v>
       </c>
       <c r="G150" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="H150" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -7006,10 +7153,10 @@
         <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>172</v>
+        <v>345</v>
       </c>
       <c r="F151" t="s">
-        <v>173</v>
+        <v>346</v>
       </c>
       <c r="G151" s="1">
         <v>46297</v>
@@ -7023,19 +7170,19 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F152" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G152" s="1">
         <v>46297</v>
@@ -7049,19 +7196,19 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>37</v>
+        <v>172</v>
       </c>
       <c r="F153" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="G153" s="1">
         <v>46297</v>
@@ -7075,19 +7222,19 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E154" t="s">
-        <v>37</v>
+        <v>352</v>
       </c>
       <c r="F154" t="s">
-        <v>38</v>
+        <v>353</v>
       </c>
       <c r="G154" s="1">
         <v>46297</v>
@@ -7101,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7127,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7153,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7179,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7205,25 +7352,25 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E159" t="s">
-        <v>355</v>
+        <v>37</v>
       </c>
       <c r="F159" t="s">
-        <v>356</v>
+        <v>38</v>
       </c>
       <c r="G159" s="1">
         <v>46297</v>
       </c>
       <c r="H159" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -7231,25 +7378,25 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E160" t="s">
-        <v>358</v>
+        <v>37</v>
       </c>
       <c r="F160" t="s">
-        <v>359</v>
+        <v>38</v>
       </c>
       <c r="G160" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H160" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -7263,7 +7410,7 @@
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E161" t="s">
         <v>361</v>
@@ -7272,7 +7419,7 @@
         <v>362</v>
       </c>
       <c r="G161" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H161" s="1">
         <v>46300</v>
@@ -7286,10 +7433,10 @@
         <v>363</v>
       </c>
       <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162" t="s">
         <v>2</v>
-      </c>
-      <c r="D162" t="s">
-        <v>170</v>
       </c>
       <c r="E162" t="s">
         <v>364</v>
@@ -7301,7 +7448,7 @@
         <v>46300</v>
       </c>
       <c r="H162" s="1">
-        <v>46308</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -7312,22 +7459,22 @@
         <v>366</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="s">
         <v>170</v>
       </c>
       <c r="E163" t="s">
-        <v>25</v>
+        <v>367</v>
       </c>
       <c r="F163" t="s">
-        <v>26</v>
+        <v>368</v>
       </c>
       <c r="G163" s="1">
         <v>46300</v>
       </c>
       <c r="H163" s="1">
-        <v>46308</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -7335,25 +7482,25 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E164" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="F164" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="G164" s="1">
         <v>46300</v>
       </c>
       <c r="H164" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -7361,25 +7508,25 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>170</v>
       </c>
       <c r="E165" t="s">
-        <v>369</v>
+        <v>25</v>
       </c>
       <c r="F165" t="s">
-        <v>370</v>
+        <v>26</v>
       </c>
       <c r="G165" s="1">
         <v>46300</v>
       </c>
       <c r="H165" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -7387,19 +7534,19 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>37</v>
+        <v>326</v>
       </c>
       <c r="F166" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
       <c r="G166" s="1">
         <v>46300</v>
@@ -7413,7 +7560,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7422,10 +7569,10 @@
         <v>170</v>
       </c>
       <c r="E167" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F167" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G167" s="1">
         <v>46300</v>
@@ -7439,19 +7586,19 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E168" t="s">
-        <v>374</v>
+        <v>37</v>
       </c>
       <c r="F168" t="s">
-        <v>375</v>
+        <v>38</v>
       </c>
       <c r="G168" s="1">
         <v>46300</v>
@@ -7465,25 +7612,25 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
+        <v>378</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
+        <v>170</v>
+      </c>
+      <c r="E169" t="s">
+        <v>375</v>
+      </c>
+      <c r="F169" t="s">
         <v>376</v>
-      </c>
-      <c r="C169">
-        <v>2</v>
-      </c>
-      <c r="D169" t="s">
-        <v>170</v>
-      </c>
-      <c r="E169" t="s">
-        <v>377</v>
-      </c>
-      <c r="F169" t="s">
-        <v>378</v>
       </c>
       <c r="G169" s="1">
         <v>46300</v>
       </c>
       <c r="H169" s="1">
-        <v>46303</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
@@ -7494,10 +7641,10 @@
         <v>379</v>
       </c>
       <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="s">
         <v>2</v>
-      </c>
-      <c r="D170" t="s">
-        <v>170</v>
       </c>
       <c r="E170" t="s">
         <v>380</v>
@@ -7509,7 +7656,7 @@
         <v>46300</v>
       </c>
       <c r="H170" s="1">
-        <v>46304</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -7526,16 +7673,16 @@
         <v>170</v>
       </c>
       <c r="E171" t="s">
-        <v>22</v>
+        <v>383</v>
       </c>
       <c r="F171" t="s">
-        <v>23</v>
+        <v>384</v>
       </c>
       <c r="G171" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H171" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -7543,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C172">
         <v>2</v>
@@ -7552,16 +7699,16 @@
         <v>170</v>
       </c>
       <c r="E172" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F172" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G172" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H172" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -7569,25 +7716,25 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="s">
         <v>170</v>
       </c>
       <c r="E173" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F173" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="G173" s="1">
         <v>46301</v>
       </c>
       <c r="H173" s="1">
-        <v>46301</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -7595,25 +7742,25 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E174" t="s">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="F174" t="s">
-        <v>38</v>
+        <v>391</v>
       </c>
       <c r="G174" s="1">
         <v>46301</v>
       </c>
       <c r="H174" s="1">
-        <v>46301</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -7621,19 +7768,19 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E175" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F175" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G175" s="1">
         <v>46301</v>
@@ -7647,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7673,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7699,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7725,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7734,10 +7881,10 @@
         <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>393</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
-        <v>394</v>
+        <v>38</v>
       </c>
       <c r="G179" s="1">
         <v>46301</v>
@@ -7751,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7760,10 +7907,10 @@
         <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="F180" t="s">
-        <v>397</v>
+        <v>38</v>
       </c>
       <c r="G180" s="1">
         <v>46301</v>
@@ -7835,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E183" t="s">
         <v>405</v>
@@ -7861,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
         <v>408</v>
@@ -7887,7 +8034,7 @@
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E185" t="s">
         <v>411</v>
@@ -7965,13 +8112,13 @@
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E188" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F188" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G188" s="1">
         <v>46301</v>
@@ -7985,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -7994,16 +8141,16 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>37</v>
+        <v>423</v>
       </c>
       <c r="F189" t="s">
-        <v>38</v>
+        <v>424</v>
       </c>
       <c r="G189" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="H189" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
@@ -8011,25 +8158,25 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="F190" t="s">
-        <v>257</v>
+        <v>424</v>
       </c>
       <c r="G190" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="H190" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
@@ -8037,19 +8184,19 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>423</v>
+        <v>37</v>
       </c>
       <c r="F191" t="s">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="G191" s="1">
         <v>46302</v>
@@ -8063,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E192" t="s">
-        <v>426</v>
+        <v>259</v>
       </c>
       <c r="F192" t="s">
-        <v>427</v>
+        <v>260</v>
       </c>
       <c r="G192" s="1">
         <v>46302</v>
@@ -8121,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E194" t="s">
         <v>432</v>
@@ -8173,7 +8320,7 @@
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
         <v>438</v>
@@ -8202,10 +8349,10 @@
         <v>170</v>
       </c>
       <c r="E197" t="s">
-        <v>274</v>
+        <v>441</v>
       </c>
       <c r="F197" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
       <c r="G197" s="1">
         <v>46302</v>
@@ -8219,19 +8366,19 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>274</v>
+        <v>444</v>
       </c>
       <c r="F198" t="s">
-        <v>275</v>
+        <v>445</v>
       </c>
       <c r="G198" s="1">
         <v>46302</v>
@@ -8245,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -8254,10 +8401,10 @@
         <v>170</v>
       </c>
       <c r="E199" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="F199" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="G199" s="1">
         <v>46302</v>
@@ -8271,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -8280,10 +8427,10 @@
         <v>170</v>
       </c>
       <c r="E200" t="s">
-        <v>444</v>
+        <v>277</v>
       </c>
       <c r="F200" t="s">
-        <v>445</v>
+        <v>278</v>
       </c>
       <c r="G200" s="1">
         <v>46302</v>
@@ -8297,19 +8444,19 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E201" t="s">
-        <v>447</v>
+        <v>16</v>
       </c>
       <c r="F201" t="s">
-        <v>448</v>
+        <v>17</v>
       </c>
       <c r="G201" s="1">
         <v>46302</v>
@@ -8332,10 +8479,10 @@
         <v>170</v>
       </c>
       <c r="E202" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="F202" t="s">
-        <v>143</v>
+        <v>451</v>
       </c>
       <c r="G202" s="1">
         <v>46302</v>
@@ -8349,19 +8496,19 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E203" t="s">
-        <v>185</v>
+        <v>453</v>
       </c>
       <c r="F203" t="s">
-        <v>186</v>
+        <v>454</v>
       </c>
       <c r="G203" s="1">
         <v>46302</v>
@@ -8375,19 +8522,19 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E204" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F204" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="G204" s="1">
         <v>46302</v>
@@ -8401,7 +8548,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -8410,10 +8557,10 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="F205" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
       <c r="G205" s="1">
         <v>46302</v>
@@ -8427,19 +8574,19 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" t="s">
         <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="F206" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="G206" s="1">
         <v>46302</v>
@@ -8453,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -8462,10 +8609,10 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F207" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G207" s="1">
         <v>46302</v>
@@ -8479,19 +8626,19 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E208" t="s">
-        <v>460</v>
+        <v>139</v>
       </c>
       <c r="F208" t="s">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="G208" s="1">
         <v>46302</v>
@@ -8511,13 +8658,13 @@
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>37</v>
+        <v>463</v>
       </c>
       <c r="F209" t="s">
-        <v>38</v>
+        <v>464</v>
       </c>
       <c r="G209" s="1">
         <v>46302</v>
@@ -8531,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -8540,10 +8687,10 @@
         <v>170</v>
       </c>
       <c r="E210" t="s">
-        <v>37</v>
+        <v>466</v>
       </c>
       <c r="F210" t="s">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="G210" s="1">
         <v>46302</v>
@@ -8557,19 +8704,19 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E211" t="s">
-        <v>465</v>
+        <v>37</v>
       </c>
       <c r="F211" t="s">
-        <v>466</v>
+        <v>38</v>
       </c>
       <c r="G211" s="1">
         <v>46302</v>
@@ -8583,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -8609,19 +8756,19 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E213" t="s">
-        <v>37</v>
+        <v>471</v>
       </c>
       <c r="F213" t="s">
-        <v>38</v>
+        <v>472</v>
       </c>
       <c r="G213" s="1">
         <v>46302</v>
@@ -8635,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -8661,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -8687,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8713,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8739,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8765,7 +8912,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8791,25 +8938,25 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220" t="s">
         <v>170</v>
       </c>
       <c r="E220" t="s">
-        <v>476</v>
+        <v>37</v>
       </c>
       <c r="F220" t="s">
-        <v>477</v>
+        <v>38</v>
       </c>
       <c r="G220" s="1">
         <v>46302</v>
       </c>
       <c r="H220" s="1">
-        <v>46308</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -8817,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8826,16 +8973,16 @@
         <v>170</v>
       </c>
       <c r="E221" t="s">
-        <v>479</v>
+        <v>37</v>
       </c>
       <c r="F221" t="s">
-        <v>480</v>
+        <v>38</v>
       </c>
       <c r="G221" s="1">
         <v>46302</v>
       </c>
       <c r="H221" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -8846,22 +8993,22 @@
         <v>481</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D222" t="s">
         <v>170</v>
       </c>
       <c r="E222" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F222" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G222" s="1">
         <v>46302</v>
       </c>
       <c r="H222" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -8869,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -8878,13 +9025,13 @@
         <v>170</v>
       </c>
       <c r="E223" t="s">
-        <v>37</v>
+        <v>485</v>
       </c>
       <c r="F223" t="s">
-        <v>38</v>
+        <v>486</v>
       </c>
       <c r="G223" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="H223" s="1">
         <v>46303</v>
@@ -8895,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8904,13 +9051,13 @@
         <v>170</v>
       </c>
       <c r="E224" t="s">
-        <v>37</v>
+        <v>485</v>
       </c>
       <c r="F224" t="s">
-        <v>38</v>
+        <v>486</v>
       </c>
       <c r="G224" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="H224" s="1">
         <v>46303</v>
@@ -8921,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -8947,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -8973,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8982,10 +9129,10 @@
         <v>170</v>
       </c>
       <c r="E227" t="s">
-        <v>487</v>
+        <v>37</v>
       </c>
       <c r="F227" t="s">
-        <v>488</v>
+        <v>38</v>
       </c>
       <c r="G227" s="1">
         <v>46303</v>
@@ -8999,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -9008,10 +9155,10 @@
         <v>170</v>
       </c>
       <c r="E228" t="s">
-        <v>490</v>
+        <v>37</v>
       </c>
       <c r="F228" t="s">
-        <v>491</v>
+        <v>38</v>
       </c>
       <c r="G228" s="1">
         <v>46303</v>
@@ -9034,10 +9181,10 @@
         <v>170</v>
       </c>
       <c r="E229" t="s">
-        <v>204</v>
+        <v>493</v>
       </c>
       <c r="F229" t="s">
-        <v>205</v>
+        <v>494</v>
       </c>
       <c r="G229" s="1">
         <v>46303</v>
@@ -9051,19 +9198,19 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F230" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G230" s="1">
         <v>46303</v>
@@ -9077,19 +9224,19 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>497</v>
+        <v>204</v>
       </c>
       <c r="F231" t="s">
-        <v>498</v>
+        <v>205</v>
       </c>
       <c r="G231" s="1">
         <v>46303</v>
@@ -9109,13 +9256,13 @@
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>265</v>
+        <v>500</v>
       </c>
       <c r="F232" t="s">
-        <v>266</v>
+        <v>501</v>
       </c>
       <c r="G232" s="1">
         <v>46303</v>
@@ -9129,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -9138,10 +9285,10 @@
         <v>170</v>
       </c>
       <c r="E233" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F233" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G233" s="1">
         <v>46303</v>
@@ -9155,19 +9302,19 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E234" t="s">
-        <v>504</v>
+        <v>268</v>
       </c>
       <c r="F234" t="s">
-        <v>505</v>
+        <v>269</v>
       </c>
       <c r="G234" s="1">
         <v>46303</v>
@@ -9187,13 +9334,13 @@
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>7</v>
+        <v>507</v>
       </c>
       <c r="F235" t="s">
-        <v>8</v>
+        <v>508</v>
       </c>
       <c r="G235" s="1">
         <v>46303</v>
@@ -9207,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9216,10 +9363,10 @@
         <v>170</v>
       </c>
       <c r="E236" t="s">
-        <v>369</v>
+        <v>510</v>
       </c>
       <c r="F236" t="s">
-        <v>370</v>
+        <v>511</v>
       </c>
       <c r="G236" s="1">
         <v>46303</v>
@@ -9233,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9242,10 +9389,10 @@
         <v>170</v>
       </c>
       <c r="E237" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="F237" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="G237" s="1">
         <v>46303</v>
@@ -9259,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9268,10 +9415,10 @@
         <v>170</v>
       </c>
       <c r="E238" t="s">
-        <v>510</v>
+        <v>375</v>
       </c>
       <c r="F238" t="s">
-        <v>511</v>
+        <v>376</v>
       </c>
       <c r="G238" s="1">
         <v>46303</v>
@@ -9285,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9294,10 +9441,10 @@
         <v>170</v>
       </c>
       <c r="E239" t="s">
-        <v>513</v>
+        <v>45</v>
       </c>
       <c r="F239" t="s">
-        <v>514</v>
+        <v>46</v>
       </c>
       <c r="G239" s="1">
         <v>46303</v>
@@ -9320,10 +9467,10 @@
         <v>170</v>
       </c>
       <c r="E240" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F240" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G240" s="1">
         <v>46303</v>
@@ -9337,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9346,10 +9493,10 @@
         <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>16</v>
+        <v>519</v>
       </c>
       <c r="F241" t="s">
-        <v>17</v>
+        <v>520</v>
       </c>
       <c r="G241" s="1">
         <v>46303</v>
@@ -9363,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9372,10 +9519,10 @@
         <v>170</v>
       </c>
       <c r="E242" t="s">
-        <v>274</v>
+        <v>519</v>
       </c>
       <c r="F242" t="s">
-        <v>275</v>
+        <v>520</v>
       </c>
       <c r="G242" s="1">
         <v>46303</v>
@@ -9389,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9398,10 +9545,10 @@
         <v>170</v>
       </c>
       <c r="E243" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F243" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G243" s="1">
         <v>46303</v>
@@ -9415,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9424,10 +9571,10 @@
         <v>170</v>
       </c>
       <c r="E244" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="F244" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="G244" s="1">
         <v>46303</v>
@@ -9441,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9450,10 +9597,10 @@
         <v>170</v>
       </c>
       <c r="E245" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="F245" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G245" s="1">
         <v>46303</v>
@@ -9467,19 +9614,19 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E246" t="s">
-        <v>522</v>
+        <v>16</v>
       </c>
       <c r="F246" t="s">
-        <v>523</v>
+        <v>17</v>
       </c>
       <c r="G246" s="1">
         <v>46303</v>
@@ -9493,25 +9640,25 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247" t="s">
         <v>170</v>
       </c>
       <c r="E247" t="s">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="F247" t="s">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="G247" s="1">
         <v>46303</v>
       </c>
       <c r="H247" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -9519,19 +9666,19 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F248" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G248" s="1">
         <v>46303</v>
@@ -9545,25 +9692,25 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="s">
         <v>170</v>
       </c>
       <c r="E249" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="F249" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="G249" s="1">
         <v>46303</v>
       </c>
       <c r="H249" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -9571,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9580,10 +9727,10 @@
         <v>170</v>
       </c>
       <c r="E250" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F250" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G250" s="1">
         <v>46303</v>
@@ -9597,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9606,10 +9753,10 @@
         <v>170</v>
       </c>
       <c r="E251" t="s">
-        <v>533</v>
+        <v>259</v>
       </c>
       <c r="F251" t="s">
-        <v>534</v>
+        <v>260</v>
       </c>
       <c r="G251" s="1">
         <v>46303</v>
@@ -9655,13 +9802,13 @@
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E253" t="s">
-        <v>142</v>
+        <v>539</v>
       </c>
       <c r="F253" t="s">
-        <v>143</v>
+        <v>540</v>
       </c>
       <c r="G253" s="1">
         <v>46303</v>
@@ -9675,19 +9822,19 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F254" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G254" s="1">
         <v>46303</v>
@@ -9701,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9710,10 +9857,10 @@
         <v>170</v>
       </c>
       <c r="E255" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="F255" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="G255" s="1">
         <v>46303</v>
@@ -9727,19 +9874,19 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E256" t="s">
-        <v>200</v>
+        <v>546</v>
       </c>
       <c r="F256" t="s">
-        <v>201</v>
+        <v>547</v>
       </c>
       <c r="G256" s="1">
         <v>46303</v>
@@ -9753,25 +9900,25 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="D257" t="s">
         <v>2</v>
       </c>
-      <c r="D257" t="s">
-        <v>170</v>
-      </c>
       <c r="E257" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="F257" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="G257" s="1">
         <v>46303</v>
       </c>
       <c r="H257" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -9779,7 +9926,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9788,10 +9935,10 @@
         <v>170</v>
       </c>
       <c r="E258" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="F258" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="G258" s="1">
         <v>46303</v>
@@ -9805,25 +9952,25 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E259" t="s">
-        <v>399</v>
+        <v>132</v>
       </c>
       <c r="F259" t="s">
-        <v>400</v>
+        <v>133</v>
       </c>
       <c r="G259" s="1">
         <v>46303</v>
       </c>
       <c r="H259" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -9831,25 +9978,25 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E260" t="s">
-        <v>548</v>
+        <v>45</v>
       </c>
       <c r="F260" t="s">
-        <v>549</v>
+        <v>46</v>
       </c>
       <c r="G260" s="1">
         <v>46303</v>
       </c>
       <c r="H260" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -9857,19 +10004,19 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>551</v>
+        <v>405</v>
       </c>
       <c r="F261" t="s">
-        <v>552</v>
+        <v>406</v>
       </c>
       <c r="G261" s="1">
         <v>46303</v>
@@ -9886,10 +10033,10 @@
         <v>553</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D262" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E262" t="s">
         <v>554</v>
@@ -9901,7 +10048,7 @@
         <v>46303</v>
       </c>
       <c r="H262" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -9915,13 +10062,13 @@
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E263" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F263" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="G263" s="1">
         <v>46303</v>
@@ -9935,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9944,10 +10091,10 @@
         <v>170</v>
       </c>
       <c r="E264" t="s">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="F264" t="s">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="G264" s="1">
         <v>46303</v>
@@ -9961,25 +10108,25 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
+        <v>562</v>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+      <c r="D265" t="s">
+        <v>2</v>
+      </c>
+      <c r="E265" t="s">
+        <v>557</v>
+      </c>
+      <c r="F265" t="s">
         <v>558</v>
-      </c>
-      <c r="C265">
-        <v>1</v>
-      </c>
-      <c r="D265" t="s">
-        <v>170</v>
-      </c>
-      <c r="E265" t="s">
-        <v>551</v>
-      </c>
-      <c r="F265" t="s">
-        <v>552</v>
       </c>
       <c r="G265" s="1">
         <v>46303</v>
       </c>
       <c r="H265" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9987,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9996,16 +10143,16 @@
         <v>170</v>
       </c>
       <c r="E266" t="s">
-        <v>551</v>
+        <v>80</v>
       </c>
       <c r="F266" t="s">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="G266" s="1">
         <v>46303</v>
       </c>
       <c r="H266" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -10013,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -10022,10 +10169,10 @@
         <v>170</v>
       </c>
       <c r="E267" t="s">
-        <v>45</v>
+        <v>557</v>
       </c>
       <c r="F267" t="s">
-        <v>46</v>
+        <v>558</v>
       </c>
       <c r="G267" s="1">
         <v>46303</v>
@@ -10039,19 +10186,19 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E268" t="s">
-        <v>333</v>
+        <v>557</v>
       </c>
       <c r="F268" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="G268" s="1">
         <v>46303</v>
@@ -10065,19 +10212,19 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E269" t="s">
-        <v>333</v>
+        <v>45</v>
       </c>
       <c r="F269" t="s">
-        <v>334</v>
+        <v>46</v>
       </c>
       <c r="G269" s="1">
         <v>46303</v>
@@ -10091,19 +10238,19 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E270" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="F270" t="s">
-        <v>565</v>
+        <v>340</v>
       </c>
       <c r="G270" s="1">
         <v>46303</v>
@@ -10117,19 +10264,19 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E271" t="s">
-        <v>567</v>
+        <v>339</v>
       </c>
       <c r="F271" t="s">
-        <v>568</v>
+        <v>340</v>
       </c>
       <c r="G271" s="1">
         <v>46303</v>
@@ -10149,16 +10296,16 @@
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E272" t="s">
-        <v>536</v>
+        <v>570</v>
       </c>
       <c r="F272" t="s">
-        <v>537</v>
+        <v>571</v>
       </c>
       <c r="G272" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H272" s="1">
         <v>46304</v>
@@ -10169,7 +10316,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -10178,13 +10325,13 @@
         <v>170</v>
       </c>
       <c r="E273" t="s">
-        <v>37</v>
+        <v>573</v>
       </c>
       <c r="F273" t="s">
-        <v>38</v>
+        <v>574</v>
       </c>
       <c r="G273" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H273" s="1">
         <v>46304</v>
@@ -10195,19 +10342,19 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E274" t="s">
-        <v>414</v>
+        <v>542</v>
       </c>
       <c r="F274" t="s">
-        <v>415</v>
+        <v>543</v>
       </c>
       <c r="G274" s="1">
         <v>46304</v>
@@ -10221,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -10247,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -10256,10 +10403,10 @@
         <v>170</v>
       </c>
       <c r="E276" t="s">
-        <v>536</v>
+        <v>420</v>
       </c>
       <c r="F276" t="s">
-        <v>537</v>
+        <v>421</v>
       </c>
       <c r="G276" s="1">
         <v>46304</v>
@@ -10273,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -10299,19 +10446,19 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E278" t="s">
-        <v>576</v>
+        <v>542</v>
       </c>
       <c r="F278" t="s">
-        <v>577</v>
+        <v>543</v>
       </c>
       <c r="G278" s="1">
         <v>46304</v>
@@ -10325,7 +10472,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -10334,10 +10481,10 @@
         <v>170</v>
       </c>
       <c r="E279" t="s">
-        <v>274</v>
+        <v>37</v>
       </c>
       <c r="F279" t="s">
-        <v>275</v>
+        <v>38</v>
       </c>
       <c r="G279" s="1">
         <v>46304</v>
@@ -10351,19 +10498,19 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E280" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F280" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G280" s="1">
         <v>46304</v>
@@ -10377,7 +10524,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10386,10 +10533,10 @@
         <v>170</v>
       </c>
       <c r="E281" t="s">
-        <v>583</v>
+        <v>277</v>
       </c>
       <c r="F281" t="s">
-        <v>584</v>
+        <v>278</v>
       </c>
       <c r="G281" s="1">
         <v>46304</v>
@@ -10435,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E283" t="s">
         <v>589</v>
@@ -10487,13 +10634,13 @@
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E285" t="s">
-        <v>16</v>
+        <v>595</v>
       </c>
       <c r="F285" t="s">
-        <v>17</v>
+        <v>596</v>
       </c>
       <c r="G285" s="1">
         <v>46304</v>
@@ -10507,7 +10654,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -10516,10 +10663,10 @@
         <v>170</v>
       </c>
       <c r="E286" t="s">
-        <v>182</v>
+        <v>598</v>
       </c>
       <c r="F286" t="s">
-        <v>183</v>
+        <v>599</v>
       </c>
       <c r="G286" s="1">
         <v>46304</v>
@@ -10533,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -10542,10 +10689,10 @@
         <v>170</v>
       </c>
       <c r="E287" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F287" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="G287" s="1">
         <v>46304</v>
@@ -10559,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10568,10 +10715,10 @@
         <v>170</v>
       </c>
       <c r="E288" t="s">
-        <v>598</v>
+        <v>182</v>
       </c>
       <c r="F288" t="s">
-        <v>599</v>
+        <v>183</v>
       </c>
       <c r="G288" s="1">
         <v>46304</v>
@@ -10585,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10594,10 +10741,10 @@
         <v>170</v>
       </c>
       <c r="E289" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="F289" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="G289" s="1">
         <v>46304</v>
@@ -10611,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10620,10 +10767,10 @@
         <v>170</v>
       </c>
       <c r="E290" t="s">
-        <v>142</v>
+        <v>604</v>
       </c>
       <c r="F290" t="s">
-        <v>143</v>
+        <v>605</v>
       </c>
       <c r="G290" s="1">
         <v>46304</v>
@@ -10637,7 +10784,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -10646,10 +10793,10 @@
         <v>170</v>
       </c>
       <c r="E291" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="F291" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G291" s="1">
         <v>46304</v>
@@ -10663,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -10672,10 +10819,10 @@
         <v>170</v>
       </c>
       <c r="E292" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F292" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="G292" s="1">
         <v>46304</v>
@@ -10689,19 +10836,19 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E293" t="s">
-        <v>605</v>
+        <v>16</v>
       </c>
       <c r="F293" t="s">
-        <v>606</v>
+        <v>17</v>
       </c>
       <c r="G293" s="1">
         <v>46304</v>
@@ -10715,19 +10862,19 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E294" t="s">
-        <v>605</v>
+        <v>48</v>
       </c>
       <c r="F294" t="s">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="G294" s="1">
         <v>46304</v>
@@ -10741,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10750,10 +10897,10 @@
         <v>2</v>
       </c>
       <c r="E295" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F295" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G295" s="1">
         <v>46304</v>
@@ -10767,7 +10914,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10776,10 +10923,10 @@
         <v>170</v>
       </c>
       <c r="E296" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F296" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G296" s="1">
         <v>46304</v>
@@ -10793,7 +10940,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10802,10 +10949,10 @@
         <v>170</v>
       </c>
       <c r="E297" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F297" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G297" s="1">
         <v>46304</v>
@@ -10819,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -10828,10 +10975,10 @@
         <v>2</v>
       </c>
       <c r="E298" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="F298" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="G298" s="1">
         <v>46304</v>
@@ -10845,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10871,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10880,10 +11027,10 @@
         <v>170</v>
       </c>
       <c r="E300" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F300" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G300" s="1">
         <v>46304</v>
@@ -10897,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10906,10 +11053,10 @@
         <v>170</v>
       </c>
       <c r="E301" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F301" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G301" s="1">
         <v>46304</v>
@@ -10923,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -10932,10 +11079,10 @@
         <v>170</v>
       </c>
       <c r="E302" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F302" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G302" s="1">
         <v>46304</v>
@@ -10949,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10958,10 +11105,10 @@
         <v>170</v>
       </c>
       <c r="E303" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F303" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G303" s="1">
         <v>46304</v>
@@ -10975,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10984,10 +11131,10 @@
         <v>170</v>
       </c>
       <c r="E304" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F304" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G304" s="1">
         <v>46304</v>
@@ -11001,7 +11148,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -11010,10 +11157,10 @@
         <v>170</v>
       </c>
       <c r="E305" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F305" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G305" s="1">
         <v>46304</v>
@@ -11027,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -11036,10 +11183,10 @@
         <v>170</v>
       </c>
       <c r="E306" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F306" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="G306" s="1">
         <v>46304</v>
@@ -11053,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -11079,7 +11226,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -11088,10 +11235,10 @@
         <v>170</v>
       </c>
       <c r="E308" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F308" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G308" s="1">
         <v>46304</v>
@@ -11105,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -11114,10 +11261,10 @@
         <v>170</v>
       </c>
       <c r="E309" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F309" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G309" s="1">
         <v>46304</v>
@@ -11131,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -11140,10 +11287,10 @@
         <v>170</v>
       </c>
       <c r="E310" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F310" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G310" s="1">
         <v>46304</v>
@@ -11157,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -11166,10 +11313,10 @@
         <v>170</v>
       </c>
       <c r="E311" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F311" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G311" s="1">
         <v>46304</v>
@@ -11183,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -11192,10 +11339,10 @@
         <v>170</v>
       </c>
       <c r="E312" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F312" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G312" s="1">
         <v>46304</v>
@@ -11209,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -11218,10 +11365,10 @@
         <v>170</v>
       </c>
       <c r="E313" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F313" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G313" s="1">
         <v>46304</v>
@@ -11235,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -11244,10 +11391,10 @@
         <v>170</v>
       </c>
       <c r="E314" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F314" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G314" s="1">
         <v>46304</v>
@@ -11261,19 +11408,19 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>654</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>170</v>
+      </c>
+      <c r="E315" t="s">
         <v>652</v>
       </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>170</v>
-      </c>
-      <c r="E315" t="s">
-        <v>650</v>
-      </c>
       <c r="F315" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G315" s="1">
         <v>46304</v>
@@ -11287,19 +11434,19 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
+        <v>655</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316" t="s">
+        <v>170</v>
+      </c>
+      <c r="E316" t="s">
+        <v>652</v>
+      </c>
+      <c r="F316" t="s">
         <v>653</v>
-      </c>
-      <c r="C316">
-        <v>1</v>
-      </c>
-      <c r="D316" t="s">
-        <v>170</v>
-      </c>
-      <c r="E316" t="s">
-        <v>650</v>
-      </c>
-      <c r="F316" t="s">
-        <v>651</v>
       </c>
       <c r="G316" s="1">
         <v>46304</v>
@@ -11313,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -11322,10 +11469,10 @@
         <v>170</v>
       </c>
       <c r="E317" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F317" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G317" s="1">
         <v>46304</v>
@@ -11339,7 +11486,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -11348,10 +11495,10 @@
         <v>2</v>
       </c>
       <c r="E318" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F318" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G318" s="1">
         <v>46304</v>
@@ -11365,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -11374,10 +11521,10 @@
         <v>170</v>
       </c>
       <c r="E319" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F319" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G319" s="1">
         <v>46304</v>
@@ -11391,19 +11538,19 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>665</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>170</v>
+      </c>
+      <c r="E320" t="s">
         <v>663</v>
       </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320" t="s">
-        <v>170</v>
-      </c>
-      <c r="E320" t="s">
-        <v>661</v>
-      </c>
       <c r="F320" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G320" s="1">
         <v>46304</v>
@@ -11417,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -11426,10 +11573,10 @@
         <v>2</v>
       </c>
       <c r="E321" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F321" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G321" s="1">
         <v>46304</v>
@@ -11443,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -11469,7 +11616,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -11495,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -11504,10 +11651,10 @@
         <v>170</v>
       </c>
       <c r="E324" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F324" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G324" s="1">
         <v>46305</v>
@@ -11521,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11530,10 +11677,10 @@
         <v>170</v>
       </c>
       <c r="E325" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F325" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G325" s="1">
         <v>46305</v>
@@ -11547,7 +11694,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -11556,10 +11703,10 @@
         <v>170</v>
       </c>
       <c r="E326" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F326" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G326" s="1">
         <v>46305</v>
@@ -11573,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -11582,10 +11729,10 @@
         <v>170</v>
       </c>
       <c r="E327" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F327" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G327" s="1">
         <v>46305</v>
@@ -11599,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -11608,10 +11755,10 @@
         <v>170</v>
       </c>
       <c r="E328" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F328" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G328" s="1">
         <v>46305</v>
@@ -11625,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11634,10 +11781,10 @@
         <v>170</v>
       </c>
       <c r="E329" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F329" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G329" s="1">
         <v>46305</v>
@@ -11651,19 +11798,19 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
+        <v>689</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+      <c r="D330" t="s">
+        <v>170</v>
+      </c>
+      <c r="E330" t="s">
         <v>687</v>
       </c>
-      <c r="C330">
-        <v>1</v>
-      </c>
-      <c r="D330" t="s">
-        <v>170</v>
-      </c>
-      <c r="E330" t="s">
-        <v>685</v>
-      </c>
       <c r="F330" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G330" s="1">
         <v>46305</v>
@@ -11677,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -11686,10 +11833,10 @@
         <v>170</v>
       </c>
       <c r="E331" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F331" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G331" s="1">
         <v>46307</v>
@@ -11703,7 +11850,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -11712,10 +11859,10 @@
         <v>170</v>
       </c>
       <c r="E332" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F332" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G332" s="1">
         <v>46307</v>
@@ -11729,7 +11876,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11738,10 +11885,10 @@
         <v>170</v>
       </c>
       <c r="E333" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F333" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G333" s="1">
         <v>46307</v>
@@ -11755,19 +11902,19 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
+        <v>695</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334" t="s">
+        <v>170</v>
+      </c>
+      <c r="E334" t="s">
         <v>693</v>
       </c>
-      <c r="C334">
-        <v>1</v>
-      </c>
-      <c r="D334" t="s">
-        <v>170</v>
-      </c>
-      <c r="E334" t="s">
-        <v>691</v>
-      </c>
       <c r="F334" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G334" s="1">
         <v>46307</v>
@@ -11781,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -11790,10 +11937,10 @@
         <v>170</v>
       </c>
       <c r="E335" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F335" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="G335" s="1">
         <v>46307</v>
@@ -11807,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -11816,10 +11963,10 @@
         <v>170</v>
       </c>
       <c r="E336" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F336" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G336" s="1">
         <v>46307</v>
@@ -11833,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -11842,10 +11989,10 @@
         <v>170</v>
       </c>
       <c r="E337" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F337" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G337" s="1">
         <v>46307</v>
@@ -11859,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -11868,10 +12015,10 @@
         <v>2</v>
       </c>
       <c r="E338" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F338" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="G338" s="1">
         <v>46307</v>
@@ -11885,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -11911,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -11937,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -11963,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -11989,7 +12136,7 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -12015,7 +12162,7 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -12041,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -12050,10 +12197,10 @@
         <v>2</v>
       </c>
       <c r="E345" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F345" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G345" s="1">
         <v>46308</v>
@@ -12067,7 +12214,7 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -12076,10 +12223,10 @@
         <v>170</v>
       </c>
       <c r="E346" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F346" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G346" s="1">
         <v>46308</v>
@@ -12093,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -12102,10 +12249,10 @@
         <v>170</v>
       </c>
       <c r="E347" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F347" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G347" s="1">
         <v>46308</v>
@@ -12119,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -12128,10 +12275,10 @@
         <v>170</v>
       </c>
       <c r="E348" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F348" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G348" s="1">
         <v>46308</v>
@@ -12145,7 +12292,7 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -12171,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -12180,10 +12327,10 @@
         <v>170</v>
       </c>
       <c r="E350" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F350" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G350" s="1">
         <v>46308</v>
@@ -12197,7 +12344,7 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -12206,10 +12353,10 @@
         <v>170</v>
       </c>
       <c r="E351" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="F351" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G351" s="1">
         <v>46308</v>
@@ -12223,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -12232,10 +12379,10 @@
         <v>170</v>
       </c>
       <c r="E352" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F352" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G352" s="1">
         <v>46308</v>
@@ -12249,19 +12396,19 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
+        <v>724</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353" t="s">
+        <v>170</v>
+      </c>
+      <c r="E353" t="s">
         <v>722</v>
       </c>
-      <c r="C353">
-        <v>1</v>
-      </c>
-      <c r="D353" t="s">
-        <v>170</v>
-      </c>
-      <c r="E353" t="s">
-        <v>720</v>
-      </c>
       <c r="F353" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G353" s="1">
         <v>46308</v>
@@ -12275,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -12301,7 +12448,7 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -12310,10 +12457,10 @@
         <v>170</v>
       </c>
       <c r="E355" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F355" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G355" s="1">
         <v>46308</v>
@@ -12327,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -12353,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -12362,10 +12509,10 @@
         <v>170</v>
       </c>
       <c r="E357" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F357" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G357" s="1">
         <v>46308</v>
@@ -12379,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -12388,10 +12535,10 @@
         <v>170</v>
       </c>
       <c r="E358" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F358" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G358" s="1">
         <v>46308</v>
@@ -12405,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -12414,10 +12561,10 @@
         <v>170</v>
       </c>
       <c r="E359" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F359" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G359" s="1">
         <v>46308</v>
@@ -12431,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="B360" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -12440,10 +12587,10 @@
         <v>170</v>
       </c>
       <c r="E360" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F360" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G360" s="1">
         <v>46308</v>
@@ -12457,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -12483,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -12492,10 +12639,10 @@
         <v>170</v>
       </c>
       <c r="E362" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="F362" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G362" s="1">
         <v>46308</v>
@@ -12509,7 +12656,7 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -12518,10 +12665,10 @@
         <v>170</v>
       </c>
       <c r="E363" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F363" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G363" s="1">
         <v>46308</v>
@@ -12535,7 +12682,7 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -12544,10 +12691,10 @@
         <v>170</v>
       </c>
       <c r="E364" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F364" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="G364" s="1">
         <v>46308</v>
@@ -12561,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -12570,10 +12717,10 @@
         <v>170</v>
       </c>
       <c r="E365" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F365" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G365" s="1">
         <v>46308</v>
@@ -12587,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -12596,10 +12743,10 @@
         <v>170</v>
       </c>
       <c r="E366" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F366" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G366" s="1">
         <v>46308</v>
@@ -12613,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -12639,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -12648,10 +12795,10 @@
         <v>170</v>
       </c>
       <c r="E368" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F368" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G368" s="1">
         <v>46308</v>
@@ -12665,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -12691,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12700,10 +12847,10 @@
         <v>170</v>
       </c>
       <c r="E370" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F370" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G370" s="1">
         <v>46308</v>
@@ -12717,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C371">
         <v>1</v>
@@ -12726,10 +12873,10 @@
         <v>170</v>
       </c>
       <c r="E371" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F371" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G371" s="1">
         <v>46308</v>
@@ -12743,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -12769,7 +12916,7 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12795,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -12821,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -12830,10 +12977,10 @@
         <v>170</v>
       </c>
       <c r="E375" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F375" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G375" s="1">
         <v>46308</v>
@@ -12847,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -12873,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -12899,7 +13046,7 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -12925,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C379">
         <v>1</v>
@@ -12934,10 +13081,10 @@
         <v>170</v>
       </c>
       <c r="E379" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F379" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G379" s="1">
         <v>46308</v>
@@ -12951,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -12977,7 +13124,7 @@
         <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -13003,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -13029,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -13055,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -13081,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C385">
         <v>1</v>
@@ -13090,10 +13237,10 @@
         <v>170</v>
       </c>
       <c r="E385" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F385" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G385" s="1">
         <v>46308</v>
@@ -13107,7 +13254,7 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -13133,7 +13280,7 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -13142,10 +13289,10 @@
         <v>170</v>
       </c>
       <c r="E387" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F387" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G387" s="1">
         <v>46308</v>
@@ -13159,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -13168,10 +13315,10 @@
         <v>170</v>
       </c>
       <c r="E388" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F388" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G388" s="1">
         <v>46308</v>
@@ -13185,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C389">
         <v>1</v>
@@ -13211,7 +13358,7 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C390">
         <v>1</v>
@@ -13220,10 +13367,10 @@
         <v>170</v>
       </c>
       <c r="E390" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F390" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G390" s="1">
         <v>46308</v>
@@ -13237,7 +13384,7 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C391">
         <v>1</v>
@@ -13246,10 +13393,10 @@
         <v>170</v>
       </c>
       <c r="E391" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F391" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G391" s="1">
         <v>46308</v>
@@ -13260,62 +13407,62 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C392">
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E392" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="F392" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="G392" s="1">
-        <v>46148</v>
+        <v>46308</v>
       </c>
       <c r="H392" s="1">
-        <v>46149</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C393">
         <v>1</v>
       </c>
       <c r="D393" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E393" t="s">
-        <v>111</v>
+        <v>785</v>
       </c>
       <c r="F393" t="s">
-        <v>112</v>
+        <v>786</v>
       </c>
       <c r="G393" s="1">
-        <v>46268</v>
+        <v>46308</v>
       </c>
       <c r="H393" s="1">
-        <v>46268</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C394">
         <v>1</v>
@@ -13324,24 +13471,24 @@
         <v>170</v>
       </c>
       <c r="E394" t="s">
-        <v>380</v>
+        <v>788</v>
       </c>
       <c r="F394" t="s">
-        <v>381</v>
+        <v>789</v>
       </c>
       <c r="G394" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H394" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C395">
         <v>1</v>
@@ -13350,125 +13497,125 @@
         <v>170</v>
       </c>
       <c r="E395" t="s">
-        <v>786</v>
+        <v>185</v>
       </c>
       <c r="F395" t="s">
-        <v>787</v>
+        <v>186</v>
       </c>
       <c r="G395" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H395" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C396">
         <v>1</v>
       </c>
       <c r="D396" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E396" t="s">
-        <v>41</v>
+        <v>649</v>
       </c>
       <c r="F396" t="s">
-        <v>42</v>
+        <v>650</v>
       </c>
       <c r="G396" s="1">
-        <v>46133</v>
+        <v>46308</v>
       </c>
       <c r="H396" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C397">
         <v>1</v>
       </c>
       <c r="D397" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E397" t="s">
-        <v>41</v>
+        <v>516</v>
       </c>
       <c r="F397" t="s">
-        <v>42</v>
+        <v>517</v>
       </c>
       <c r="G397" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
       <c r="H397" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E398" t="s">
-        <v>19</v>
+        <v>663</v>
       </c>
       <c r="F398" t="s">
-        <v>20</v>
+        <v>664</v>
       </c>
       <c r="G398" s="1">
-        <v>46156</v>
+        <v>46308</v>
       </c>
       <c r="H398" s="1">
-        <v>46156</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C399">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D399" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E399" t="s">
-        <v>793</v>
+        <v>97</v>
       </c>
       <c r="F399" t="s">
-        <v>794</v>
+        <v>98</v>
       </c>
       <c r="G399" s="1">
-        <v>46209</v>
+        <v>46308</v>
       </c>
       <c r="H399" s="1">
-        <v>46218</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B400" t="s">
         <v>795</v>
@@ -13477,76 +13624,76 @@
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E400" t="s">
-        <v>796</v>
+        <v>97</v>
       </c>
       <c r="F400" t="s">
-        <v>797</v>
+        <v>98</v>
       </c>
       <c r="G400" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
       <c r="H400" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C401">
         <v>1</v>
       </c>
       <c r="D401" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E401" t="s">
-        <v>583</v>
+        <v>212</v>
       </c>
       <c r="F401" t="s">
-        <v>584</v>
+        <v>213</v>
       </c>
       <c r="G401" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
       <c r="H401" s="1">
-        <v>46216</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B402" t="s">
+        <v>797</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>170</v>
+      </c>
+      <c r="E402" t="s">
+        <v>798</v>
+      </c>
+      <c r="F402" t="s">
         <v>799</v>
       </c>
-      <c r="C402">
-        <v>1</v>
-      </c>
-      <c r="D402" t="s">
-        <v>95</v>
-      </c>
-      <c r="E402" t="s">
-        <v>583</v>
-      </c>
-      <c r="F402" t="s">
-        <v>584</v>
-      </c>
       <c r="G402" s="1">
-        <v>46224</v>
+        <v>46308</v>
       </c>
       <c r="H402" s="1">
-        <v>46224</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B403" t="s">
         <v>800</v>
@@ -13555,157 +13702,157 @@
         <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E403" t="s">
-        <v>801</v>
+        <v>604</v>
       </c>
       <c r="F403" t="s">
-        <v>802</v>
+        <v>605</v>
       </c>
       <c r="G403" s="1">
-        <v>46253</v>
+        <v>46308</v>
       </c>
       <c r="H403" s="1">
-        <v>46253</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B404" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C404">
         <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E404" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="F404" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G404" s="1">
-        <v>46273</v>
+        <v>46308</v>
       </c>
       <c r="H404" s="1">
-        <v>46274</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B405" t="s">
+        <v>802</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>170</v>
+      </c>
+      <c r="E405" t="s">
+        <v>803</v>
+      </c>
+      <c r="F405" t="s">
         <v>804</v>
       </c>
-      <c r="C405">
-        <v>2</v>
-      </c>
-      <c r="D405" t="s">
-        <v>170</v>
-      </c>
-      <c r="E405" t="s">
-        <v>805</v>
-      </c>
-      <c r="F405" t="s">
-        <v>806</v>
-      </c>
       <c r="G405" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="H405" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B406" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C406">
         <v>1</v>
       </c>
       <c r="D406" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E406" t="s">
-        <v>222</v>
+        <v>16</v>
       </c>
       <c r="F406" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="G406" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="H406" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B407" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C407">
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E407" t="s">
-        <v>583</v>
+        <v>235</v>
       </c>
       <c r="F407" t="s">
-        <v>584</v>
+        <v>236</v>
       </c>
       <c r="G407" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="H407" s="1">
-        <v>46301</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B408" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E408" t="s">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="F408" t="s">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="G408" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="H408" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -13714,47 +13861,47 @@
         <v>170</v>
       </c>
       <c r="E409" t="s">
-        <v>793</v>
+        <v>92</v>
       </c>
       <c r="F409" t="s">
-        <v>794</v>
+        <v>93</v>
       </c>
       <c r="G409" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="H409" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B410" t="s">
+        <v>809</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="s">
+        <v>170</v>
+      </c>
+      <c r="E410" t="s">
+        <v>810</v>
+      </c>
+      <c r="F410" t="s">
         <v>811</v>
       </c>
-      <c r="C410">
-        <v>1</v>
-      </c>
-      <c r="D410" t="s">
-        <v>170</v>
-      </c>
-      <c r="E410" t="s">
-        <v>487</v>
-      </c>
-      <c r="F410" t="s">
-        <v>488</v>
-      </c>
       <c r="G410" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H410" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B411" t="s">
         <v>812</v>
@@ -13763,27 +13910,27 @@
         <v>1</v>
       </c>
       <c r="D411" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E411" t="s">
-        <v>513</v>
+        <v>813</v>
       </c>
       <c r="F411" t="s">
-        <v>514</v>
+        <v>814</v>
       </c>
       <c r="G411" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H411" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B412" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C412">
         <v>1</v>
@@ -13792,24 +13939,24 @@
         <v>170</v>
       </c>
       <c r="E412" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="F412" t="s">
-        <v>514</v>
+        <v>817</v>
       </c>
       <c r="G412" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H412" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B413" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -13818,39 +13965,39 @@
         <v>170</v>
       </c>
       <c r="E413" t="s">
-        <v>513</v>
+        <v>185</v>
       </c>
       <c r="F413" t="s">
-        <v>514</v>
+        <v>186</v>
       </c>
       <c r="G413" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H413" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B414" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C414">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D414" t="s">
         <v>170</v>
       </c>
       <c r="E414" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="F414" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="G414" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H414" s="1">
         <v>46308</v>
@@ -13858,10 +14005,10 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B415" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C415">
         <v>1</v>
@@ -13870,24 +14017,24 @@
         <v>170</v>
       </c>
       <c r="E415" t="s">
-        <v>583</v>
+        <v>821</v>
       </c>
       <c r="F415" t="s">
-        <v>584</v>
+        <v>822</v>
       </c>
       <c r="G415" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H415" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B416" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C416">
         <v>1</v>
@@ -13896,24 +14043,24 @@
         <v>170</v>
       </c>
       <c r="E416" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="F416" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="G416" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H416" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="B417" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C417">
         <v>1</v>
@@ -13922,10 +14069,10 @@
         <v>170</v>
       </c>
       <c r="E417" t="s">
-        <v>706</v>
+        <v>429</v>
       </c>
       <c r="F417" t="s">
-        <v>707</v>
+        <v>430</v>
       </c>
       <c r="G417" s="1">
         <v>46308</v>
@@ -13936,296 +14083,296 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>788</v>
+        <v>827</v>
       </c>
       <c r="B418" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="C418">
         <v>1</v>
       </c>
       <c r="D418" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E418" t="s">
-        <v>706</v>
+        <v>200</v>
       </c>
       <c r="F418" t="s">
-        <v>707</v>
+        <v>201</v>
       </c>
       <c r="G418" s="1">
-        <v>46308</v>
+        <v>46148</v>
       </c>
       <c r="H418" s="1">
-        <v>46308</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B419" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C419">
         <v>1</v>
       </c>
       <c r="D419" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E419" t="s">
-        <v>822</v>
+        <v>111</v>
       </c>
       <c r="F419" t="s">
-        <v>823</v>
+        <v>112</v>
       </c>
       <c r="G419" s="1">
-        <v>46063</v>
+        <v>46268</v>
       </c>
       <c r="H419" s="1">
-        <v>46064</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B420" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C420">
         <v>1</v>
       </c>
       <c r="D420" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E420" t="s">
-        <v>57</v>
+        <v>386</v>
       </c>
       <c r="F420" t="s">
-        <v>58</v>
+        <v>387</v>
       </c>
       <c r="G420" s="1">
-        <v>46113</v>
+        <v>46303</v>
       </c>
       <c r="H420" s="1">
-        <v>46125</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
       <c r="B421" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="C421">
         <v>1</v>
       </c>
       <c r="D421" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E421" t="s">
-        <v>57</v>
+        <v>833</v>
       </c>
       <c r="F421" t="s">
-        <v>58</v>
+        <v>834</v>
       </c>
       <c r="G421" s="1">
-        <v>46125</v>
+        <v>46308</v>
       </c>
       <c r="H421" s="1">
-        <v>46125</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B422" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="C422">
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E422" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F422" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G422" s="1">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="H422" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B423" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="C423">
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E423" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F423" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G423" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="H423" s="1">
-        <v>46126</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B424" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="C424">
         <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E424" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="F424" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G424" s="1">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="H424" s="1">
-        <v>46128</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B425" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="C425">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D425" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="E425" t="s">
-        <v>57</v>
+        <v>840</v>
       </c>
       <c r="F425" t="s">
-        <v>58</v>
+        <v>841</v>
       </c>
       <c r="G425" s="1">
-        <v>46132</v>
+        <v>46209</v>
       </c>
       <c r="H425" s="1">
-        <v>46132</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B426" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C426">
         <v>1</v>
       </c>
       <c r="D426" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E426" t="s">
-        <v>57</v>
+        <v>843</v>
       </c>
       <c r="F426" t="s">
-        <v>58</v>
+        <v>844</v>
       </c>
       <c r="G426" s="1">
-        <v>46161</v>
+        <v>46213</v>
       </c>
       <c r="H426" s="1">
-        <v>46161</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B427" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="C427">
         <v>1</v>
       </c>
       <c r="D427" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E427" t="s">
-        <v>57</v>
+        <v>589</v>
       </c>
       <c r="F427" t="s">
-        <v>58</v>
+        <v>590</v>
       </c>
       <c r="G427" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
       <c r="H427" s="1">
-        <v>46174</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B428" t="s">
-        <v>832</v>
+        <v>846</v>
       </c>
       <c r="C428">
         <v>1</v>
       </c>
       <c r="D428" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E428" t="s">
-        <v>57</v>
+        <v>589</v>
       </c>
       <c r="F428" t="s">
-        <v>58</v>
+        <v>590</v>
       </c>
       <c r="G428" s="1">
-        <v>46174</v>
+        <v>46224</v>
       </c>
       <c r="H428" s="1">
-        <v>46174</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B429" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="C429">
         <v>1</v>
@@ -14234,206 +14381,206 @@
         <v>6</v>
       </c>
       <c r="E429" t="s">
-        <v>57</v>
+        <v>848</v>
       </c>
       <c r="F429" t="s">
-        <v>58</v>
+        <v>849</v>
       </c>
       <c r="G429" s="1">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="H429" s="1">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B430" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="C430">
         <v>1</v>
       </c>
       <c r="D430" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E430" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="F430" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="G430" s="1">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="H430" s="1">
-        <v>46210</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B431" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="C431">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D431" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E431" t="s">
-        <v>57</v>
+        <v>852</v>
       </c>
       <c r="F431" t="s">
-        <v>58</v>
+        <v>853</v>
       </c>
       <c r="G431" s="1">
-        <v>46213</v>
+        <v>46300</v>
       </c>
       <c r="H431" s="1">
-        <v>46213</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B432" t="s">
-        <v>836</v>
+        <v>854</v>
       </c>
       <c r="C432">
         <v>1</v>
       </c>
       <c r="D432" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E432" t="s">
-        <v>57</v>
+        <v>222</v>
       </c>
       <c r="F432" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="G432" s="1">
-        <v>46218</v>
+        <v>46300</v>
       </c>
       <c r="H432" s="1">
-        <v>46252</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B433" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="C433">
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E433" t="s">
-        <v>77</v>
+        <v>589</v>
       </c>
       <c r="F433" t="s">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="G433" s="1">
-        <v>46226</v>
+        <v>46300</v>
       </c>
       <c r="H433" s="1">
-        <v>46226</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B434" t="s">
-        <v>838</v>
+        <v>856</v>
       </c>
       <c r="C434">
         <v>1</v>
       </c>
       <c r="D434" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E434" t="s">
-        <v>57</v>
+        <v>352</v>
       </c>
       <c r="F434" t="s">
-        <v>58</v>
+        <v>353</v>
       </c>
       <c r="G434" s="1">
-        <v>46227</v>
+        <v>46302</v>
       </c>
       <c r="H434" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B435" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="C435">
         <v>1</v>
       </c>
       <c r="D435" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E435" t="s">
-        <v>57</v>
+        <v>840</v>
       </c>
       <c r="F435" t="s">
-        <v>58</v>
+        <v>841</v>
       </c>
       <c r="G435" s="1">
-        <v>46227</v>
+        <v>46302</v>
       </c>
       <c r="H435" s="1">
-        <v>46252</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B436" t="s">
-        <v>840</v>
+        <v>858</v>
       </c>
       <c r="C436">
         <v>1</v>
       </c>
       <c r="D436" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E436" t="s">
-        <v>57</v>
+        <v>493</v>
       </c>
       <c r="F436" t="s">
-        <v>58</v>
+        <v>494</v>
       </c>
       <c r="G436" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H436" s="1">
-        <v>46228</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B437" t="s">
-        <v>841</v>
+        <v>859</v>
       </c>
       <c r="C437">
         <v>1</v>
@@ -14442,284 +14589,284 @@
         <v>6</v>
       </c>
       <c r="E437" t="s">
-        <v>77</v>
+        <v>519</v>
       </c>
       <c r="F437" t="s">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="G437" s="1">
-        <v>46230</v>
+        <v>46303</v>
       </c>
       <c r="H437" s="1">
-        <v>46252</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B438" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="C438">
         <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E438" t="s">
-        <v>57</v>
+        <v>519</v>
       </c>
       <c r="F438" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G438" s="1">
-        <v>46231</v>
+        <v>46303</v>
       </c>
       <c r="H438" s="1">
-        <v>46231</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B439" t="s">
-        <v>843</v>
+        <v>861</v>
       </c>
       <c r="C439">
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E439" t="s">
-        <v>57</v>
+        <v>519</v>
       </c>
       <c r="F439" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G439" s="1">
-        <v>46254</v>
+        <v>46303</v>
       </c>
       <c r="H439" s="1">
-        <v>46254</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B440" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="C440">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D440" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E440" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="F440" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="G440" s="1">
-        <v>46255</v>
+        <v>46303</v>
       </c>
       <c r="H440" s="1">
-        <v>46255</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B441" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
       <c r="C441">
         <v>1</v>
       </c>
       <c r="D441" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E441" t="s">
-        <v>57</v>
+        <v>589</v>
       </c>
       <c r="F441" t="s">
-        <v>58</v>
+        <v>590</v>
       </c>
       <c r="G441" s="1">
-        <v>46260</v>
+        <v>46304</v>
       </c>
       <c r="H441" s="1">
-        <v>46260</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B442" t="s">
-        <v>846</v>
+        <v>864</v>
       </c>
       <c r="C442">
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E442" t="s">
-        <v>57</v>
+        <v>840</v>
       </c>
       <c r="F442" t="s">
-        <v>58</v>
+        <v>841</v>
       </c>
       <c r="G442" s="1">
-        <v>46289</v>
+        <v>46304</v>
       </c>
       <c r="H442" s="1">
-        <v>46289</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B443" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="C443">
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E443" t="s">
-        <v>57</v>
+        <v>708</v>
       </c>
       <c r="F443" t="s">
-        <v>58</v>
+        <v>709</v>
       </c>
       <c r="G443" s="1">
-        <v>46294</v>
+        <v>46308</v>
       </c>
       <c r="H443" s="1">
-        <v>46294</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="B444" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="C444">
         <v>1</v>
       </c>
       <c r="D444" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E444" t="s">
-        <v>850</v>
+        <v>708</v>
       </c>
       <c r="F444" t="s">
-        <v>851</v>
+        <v>709</v>
       </c>
       <c r="G444" s="1">
-        <v>46157</v>
+        <v>46308</v>
       </c>
       <c r="H444" s="1">
-        <v>46157</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="B445" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="C445">
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E445" t="s">
-        <v>853</v>
+        <v>429</v>
       </c>
       <c r="F445" t="s">
-        <v>854</v>
+        <v>430</v>
       </c>
       <c r="G445" s="1">
-        <v>46168</v>
+        <v>46308</v>
       </c>
       <c r="H445" s="1">
-        <v>46170</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B446" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E446" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="F446" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="G446" s="1">
-        <v>46218</v>
+        <v>46063</v>
       </c>
       <c r="H446" s="1">
-        <v>46218</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B447" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="C447">
         <v>1</v>
       </c>
       <c r="D447" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E447" t="s">
-        <v>850</v>
+        <v>57</v>
       </c>
       <c r="F447" t="s">
-        <v>851</v>
+        <v>58</v>
       </c>
       <c r="G447" s="1">
-        <v>46244</v>
+        <v>46113</v>
       </c>
       <c r="H447" s="1">
-        <v>46244</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B448" t="s">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="C448">
         <v>1</v>
@@ -14728,24 +14875,24 @@
         <v>2</v>
       </c>
       <c r="E448" t="s">
-        <v>850</v>
+        <v>57</v>
       </c>
       <c r="F448" t="s">
-        <v>851</v>
+        <v>58</v>
       </c>
       <c r="G448" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
       <c r="H448" s="1">
-        <v>46247</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B449" t="s">
-        <v>858</v>
+        <v>874</v>
       </c>
       <c r="C449">
         <v>1</v>
@@ -14754,24 +14901,24 @@
         <v>2</v>
       </c>
       <c r="E449" t="s">
-        <v>859</v>
+        <v>57</v>
       </c>
       <c r="F449" t="s">
-        <v>860</v>
+        <v>58</v>
       </c>
       <c r="G449" s="1">
-        <v>46247</v>
+        <v>46126</v>
       </c>
       <c r="H449" s="1">
-        <v>46247</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B450" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="C450">
         <v>1</v>
@@ -14780,24 +14927,24 @@
         <v>2</v>
       </c>
       <c r="E450" t="s">
-        <v>850</v>
+        <v>57</v>
       </c>
       <c r="F450" t="s">
-        <v>851</v>
+        <v>58</v>
       </c>
       <c r="G450" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
       <c r="H450" s="1">
-        <v>46255</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B451" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="C451">
         <v>1</v>
@@ -14806,67 +14953,795 @@
         <v>2</v>
       </c>
       <c r="E451" t="s">
-        <v>850</v>
+        <v>57</v>
       </c>
       <c r="F451" t="s">
-        <v>851</v>
+        <v>58</v>
       </c>
       <c r="G451" s="1">
-        <v>46258</v>
+        <v>46128</v>
       </c>
       <c r="H451" s="1">
-        <v>46258</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B452" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="C452">
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E452" t="s">
-        <v>850</v>
+        <v>57</v>
       </c>
       <c r="F452" t="s">
-        <v>851</v>
+        <v>58</v>
       </c>
       <c r="G452" s="1">
-        <v>46262</v>
+        <v>46132</v>
       </c>
       <c r="H452" s="1">
-        <v>46265</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B453" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
+        <v>2</v>
+      </c>
+      <c r="E453" t="s">
+        <v>57</v>
+      </c>
+      <c r="F453" t="s">
+        <v>58</v>
+      </c>
+      <c r="G453" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H453" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>868</v>
+      </c>
+      <c r="B454" t="s">
+        <v>879</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>2</v>
+      </c>
+      <c r="E454" t="s">
+        <v>57</v>
+      </c>
+      <c r="F454" t="s">
+        <v>58</v>
+      </c>
+      <c r="G454" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H454" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>868</v>
+      </c>
+      <c r="B455" t="s">
+        <v>880</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+      <c r="D455" t="s">
+        <v>2</v>
+      </c>
+      <c r="E455" t="s">
+        <v>57</v>
+      </c>
+      <c r="F455" t="s">
+        <v>58</v>
+      </c>
+      <c r="G455" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H455" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>868</v>
+      </c>
+      <c r="B456" t="s">
+        <v>881</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+      <c r="D456" t="s">
         <v>6</v>
       </c>
-      <c r="E453" t="s">
+      <c r="E456" t="s">
+        <v>57</v>
+      </c>
+      <c r="F456" t="s">
+        <v>58</v>
+      </c>
+      <c r="G456" s="1">
+        <v>46195</v>
+      </c>
+      <c r="H456" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>868</v>
+      </c>
+      <c r="B457" t="s">
+        <v>882</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>6</v>
+      </c>
+      <c r="E457" t="s">
+        <v>57</v>
+      </c>
+      <c r="F457" t="s">
+        <v>58</v>
+      </c>
+      <c r="G457" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H457" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>868</v>
+      </c>
+      <c r="B458" t="s">
+        <v>883</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+      <c r="D458" t="s">
+        <v>2</v>
+      </c>
+      <c r="E458" t="s">
+        <v>57</v>
+      </c>
+      <c r="F458" t="s">
+        <v>58</v>
+      </c>
+      <c r="G458" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H458" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>868</v>
+      </c>
+      <c r="B459" t="s">
+        <v>884</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+      <c r="D459" t="s">
+        <v>6</v>
+      </c>
+      <c r="E459" t="s">
+        <v>57</v>
+      </c>
+      <c r="F459" t="s">
+        <v>58</v>
+      </c>
+      <c r="G459" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H459" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>868</v>
+      </c>
+      <c r="B460" t="s">
+        <v>885</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460" t="s">
+        <v>6</v>
+      </c>
+      <c r="E460" t="s">
+        <v>77</v>
+      </c>
+      <c r="F460" t="s">
+        <v>78</v>
+      </c>
+      <c r="G460" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H460" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>868</v>
+      </c>
+      <c r="B461" t="s">
+        <v>886</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="s">
+        <v>170</v>
+      </c>
+      <c r="E461" t="s">
+        <v>57</v>
+      </c>
+      <c r="F461" t="s">
+        <v>58</v>
+      </c>
+      <c r="G461" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H461" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>868</v>
+      </c>
+      <c r="B462" t="s">
+        <v>887</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462" t="s">
+        <v>6</v>
+      </c>
+      <c r="E462" t="s">
+        <v>57</v>
+      </c>
+      <c r="F462" t="s">
+        <v>58</v>
+      </c>
+      <c r="G462" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H462" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>868</v>
+      </c>
+      <c r="B463" t="s">
+        <v>888</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463" t="s">
+        <v>6</v>
+      </c>
+      <c r="E463" t="s">
+        <v>57</v>
+      </c>
+      <c r="F463" t="s">
+        <v>58</v>
+      </c>
+      <c r="G463" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H463" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>868</v>
+      </c>
+      <c r="B464" t="s">
+        <v>889</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+      <c r="D464" t="s">
+        <v>6</v>
+      </c>
+      <c r="E464" t="s">
+        <v>77</v>
+      </c>
+      <c r="F464" t="s">
+        <v>78</v>
+      </c>
+      <c r="G464" s="1">
+        <v>46230</v>
+      </c>
+      <c r="H464" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>868</v>
+      </c>
+      <c r="B465" t="s">
+        <v>890</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+      <c r="D465" t="s">
+        <v>6</v>
+      </c>
+      <c r="E465" t="s">
+        <v>57</v>
+      </c>
+      <c r="F465" t="s">
+        <v>58</v>
+      </c>
+      <c r="G465" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H465" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>868</v>
+      </c>
+      <c r="B466" t="s">
+        <v>891</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+      <c r="D466" t="s">
+        <v>6</v>
+      </c>
+      <c r="E466" t="s">
+        <v>57</v>
+      </c>
+      <c r="F466" t="s">
+        <v>58</v>
+      </c>
+      <c r="G466" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H466" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>868</v>
+      </c>
+      <c r="B467" t="s">
+        <v>892</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467" t="s">
+        <v>2</v>
+      </c>
+      <c r="E467" t="s">
+        <v>57</v>
+      </c>
+      <c r="F467" t="s">
+        <v>58</v>
+      </c>
+      <c r="G467" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H467" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>868</v>
+      </c>
+      <c r="B468" t="s">
+        <v>893</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="D468" t="s">
+        <v>6</v>
+      </c>
+      <c r="E468" t="s">
+        <v>57</v>
+      </c>
+      <c r="F468" t="s">
+        <v>58</v>
+      </c>
+      <c r="G468" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H468" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>868</v>
+      </c>
+      <c r="B469" t="s">
+        <v>894</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469" t="s">
+        <v>6</v>
+      </c>
+      <c r="E469" t="s">
+        <v>57</v>
+      </c>
+      <c r="F469" t="s">
+        <v>58</v>
+      </c>
+      <c r="G469" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H469" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>868</v>
+      </c>
+      <c r="B470" t="s">
+        <v>895</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470" t="s">
+        <v>6</v>
+      </c>
+      <c r="E470" t="s">
+        <v>57</v>
+      </c>
+      <c r="F470" t="s">
+        <v>58</v>
+      </c>
+      <c r="G470" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H470" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>868</v>
+      </c>
+      <c r="B471" t="s">
+        <v>896</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+      <c r="D471" t="s">
+        <v>170</v>
+      </c>
+      <c r="E471" t="s">
+        <v>57</v>
+      </c>
+      <c r="F471" t="s">
+        <v>58</v>
+      </c>
+      <c r="G471" s="1">
+        <v>46308</v>
+      </c>
+      <c r="H471" s="1">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>897</v>
+      </c>
+      <c r="B472" t="s">
+        <v>898</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+      <c r="D472" t="s">
+        <v>2</v>
+      </c>
+      <c r="E472" t="s">
+        <v>899</v>
+      </c>
+      <c r="F472" t="s">
+        <v>900</v>
+      </c>
+      <c r="G472" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H472" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>897</v>
+      </c>
+      <c r="B473" t="s">
+        <v>901</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473" t="s">
+        <v>2</v>
+      </c>
+      <c r="E473" t="s">
+        <v>902</v>
+      </c>
+      <c r="F473" t="s">
+        <v>903</v>
+      </c>
+      <c r="G473" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H473" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>897</v>
+      </c>
+      <c r="B474" t="s">
+        <v>904</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+      <c r="D474" t="s">
+        <v>2</v>
+      </c>
+      <c r="E474" t="s">
+        <v>899</v>
+      </c>
+      <c r="F474" t="s">
+        <v>900</v>
+      </c>
+      <c r="G474" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H474" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>897</v>
+      </c>
+      <c r="B475" t="s">
+        <v>905</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+      <c r="D475" t="s">
+        <v>2</v>
+      </c>
+      <c r="E475" t="s">
+        <v>899</v>
+      </c>
+      <c r="F475" t="s">
+        <v>900</v>
+      </c>
+      <c r="G475" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H475" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>897</v>
+      </c>
+      <c r="B476" t="s">
+        <v>906</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+      <c r="D476" t="s">
+        <v>2</v>
+      </c>
+      <c r="E476" t="s">
+        <v>899</v>
+      </c>
+      <c r="F476" t="s">
+        <v>900</v>
+      </c>
+      <c r="G476" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H476" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>897</v>
+      </c>
+      <c r="B477" t="s">
+        <v>907</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+      <c r="D477" t="s">
+        <v>2</v>
+      </c>
+      <c r="E477" t="s">
+        <v>908</v>
+      </c>
+      <c r="F477" t="s">
+        <v>909</v>
+      </c>
+      <c r="G477" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H477" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>897</v>
+      </c>
+      <c r="B478" t="s">
+        <v>910</v>
+      </c>
+      <c r="C478">
+        <v>1</v>
+      </c>
+      <c r="D478" t="s">
+        <v>2</v>
+      </c>
+      <c r="E478" t="s">
+        <v>899</v>
+      </c>
+      <c r="F478" t="s">
+        <v>900</v>
+      </c>
+      <c r="G478" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H478" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>897</v>
+      </c>
+      <c r="B479" t="s">
+        <v>911</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+      <c r="D479" t="s">
+        <v>2</v>
+      </c>
+      <c r="E479" t="s">
+        <v>899</v>
+      </c>
+      <c r="F479" t="s">
+        <v>900</v>
+      </c>
+      <c r="G479" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H479" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>897</v>
+      </c>
+      <c r="B480" t="s">
+        <v>912</v>
+      </c>
+      <c r="C480">
+        <v>1</v>
+      </c>
+      <c r="D480" t="s">
+        <v>2</v>
+      </c>
+      <c r="E480" t="s">
+        <v>899</v>
+      </c>
+      <c r="F480" t="s">
+        <v>900</v>
+      </c>
+      <c r="G480" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H480" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>897</v>
+      </c>
+      <c r="B481" t="s">
+        <v>913</v>
+      </c>
+      <c r="C481">
+        <v>1</v>
+      </c>
+      <c r="D481" t="s">
+        <v>6</v>
+      </c>
+      <c r="E481" t="s">
         <v>13</v>
       </c>
-      <c r="F453" t="s">
+      <c r="F481" t="s">
         <v>14</v>
       </c>
-      <c r="G453" s="1">
+      <c r="G481" s="1">
         <v>46281</v>
       </c>
-      <c r="H453" s="1">
+      <c r="H481" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52D8A3B5-4D2D-40CB-9D94-9107C70803C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EBFD6E-77ED-42C4-A202-C7546DB6F1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28320" yWindow="2505" windowWidth="15375" windowHeight="8325" xr2:uid="{BD70D57C-6A22-4E38-90CD-E502C61EE9E2}"/>
+    <workbookView xWindow="28320" yWindow="2505" windowWidth="15375" windowHeight="8325" xr2:uid="{F25A0148-7FEF-49B4-A290-E6F1AFC7BB97}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="954">
   <si>
     <t>0001</t>
   </si>
@@ -1027,6 +1027,15 @@
     <t xml:space="preserve">  216791</t>
   </si>
   <si>
+    <t xml:space="preserve">  216793</t>
+  </si>
+  <si>
+    <t>FE15</t>
+  </si>
+  <si>
+    <t>FEDAN S.A.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  216798</t>
   </si>
   <si>
@@ -1288,6 +1297,15 @@
     <t>CEFALU S.A.</t>
   </si>
   <si>
+    <t xml:space="preserve">  217104</t>
+  </si>
+  <si>
+    <t>CF20</t>
+  </si>
+  <si>
+    <t>CASA FERRALIC SRL - MARMOLERIA PATAGONICA</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217111</t>
   </si>
   <si>
@@ -1702,12 +1720,6 @@
     <t xml:space="preserve">  217269</t>
   </si>
   <si>
-    <t>FE15</t>
-  </si>
-  <si>
-    <t>FEDAN S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217271</t>
   </si>
   <si>
@@ -2503,6 +2515,90 @@
     <t xml:space="preserve">  217449</t>
   </si>
   <si>
+    <t xml:space="preserve">  217451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217454</t>
+  </si>
+  <si>
+    <t>GE12</t>
+  </si>
+  <si>
+    <t>GERMANO S.R.L. -GERMANO MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217455</t>
+  </si>
+  <si>
+    <t>OR06</t>
+  </si>
+  <si>
+    <t>ORSI OSCAR A. Y ORSI LUCIANO O.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217457</t>
+  </si>
+  <si>
+    <t>EF07</t>
+  </si>
+  <si>
+    <t>EL FUTURO DEL OESTE S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217458</t>
+  </si>
+  <si>
+    <t>MA42</t>
+  </si>
+  <si>
+    <t>MAYOR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217459</t>
+  </si>
+  <si>
+    <t>AF07</t>
+  </si>
+  <si>
+    <t>ANDRES LUIS DE FRANCESCO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217460</t>
+  </si>
+  <si>
+    <t>CB15</t>
+  </si>
+  <si>
+    <t>CASA BOUCIGUEZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217461</t>
+  </si>
+  <si>
+    <t>DP09</t>
+  </si>
+  <si>
+    <t>DEL PRADO SERGIO A. -SANIT GAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217464</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2710,7 +2806,7 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2794</t>
+    <t xml:space="preserve">    2797</t>
   </si>
   <si>
     <t>9999</t>
@@ -3235,34 +3331,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46579758-A2A5-4DDC-80DA-3BD8D8C6BF5E}">
-  <dimension ref="A1:H481"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE39F19E-A1EE-458C-8F46-D1C42D824C01}">
+  <dimension ref="A1:H497"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6526,7 +6622,7 @@
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E127" t="s">
         <v>305</v>
@@ -6708,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E134" t="s">
         <v>37</v>
@@ -6838,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E139" t="s">
         <v>37</v>
@@ -7072,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E148" t="s">
         <v>336</v>
@@ -7084,7 +7180,7 @@
         <v>46296</v>
       </c>
       <c r="H148" s="1">
-        <v>46296</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -7098,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E149" t="s">
         <v>339</v>
@@ -7150,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>345</v>
@@ -7159,10 +7255,10 @@
         <v>346</v>
       </c>
       <c r="G151" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="H151" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -7205,10 +7301,10 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>172</v>
+        <v>351</v>
       </c>
       <c r="F153" t="s">
-        <v>173</v>
+        <v>352</v>
       </c>
       <c r="G153" s="1">
         <v>46297</v>
@@ -7222,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>352</v>
+        <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>353</v>
+        <v>173</v>
       </c>
       <c r="G154" s="1">
         <v>46297</v>
@@ -7254,13 +7350,13 @@
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E155" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="F155" t="s">
-        <v>38</v>
+        <v>356</v>
       </c>
       <c r="G155" s="1">
         <v>46297</v>
@@ -7274,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7300,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7326,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7352,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7378,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7404,25 +7500,25 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E161" t="s">
-        <v>361</v>
+        <v>37</v>
       </c>
       <c r="F161" t="s">
-        <v>362</v>
+        <v>38</v>
       </c>
       <c r="G161" s="1">
         <v>46297</v>
       </c>
       <c r="H161" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -7445,7 +7541,7 @@
         <v>365</v>
       </c>
       <c r="G162" s="1">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="H162" s="1">
         <v>46300</v>
@@ -7462,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E163" t="s">
         <v>367</v>
@@ -7485,7 +7581,7 @@
         <v>369</v>
       </c>
       <c r="C164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="s">
         <v>170</v>
@@ -7500,7 +7596,7 @@
         <v>46300</v>
       </c>
       <c r="H164" s="1">
-        <v>46308</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -7517,10 +7613,10 @@
         <v>170</v>
       </c>
       <c r="E165" t="s">
-        <v>25</v>
+        <v>373</v>
       </c>
       <c r="F165" t="s">
-        <v>26</v>
+        <v>374</v>
       </c>
       <c r="G165" s="1">
         <v>46300</v>
@@ -7534,25 +7630,25 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E166" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>327</v>
+        <v>26</v>
       </c>
       <c r="G166" s="1">
         <v>46300</v>
       </c>
       <c r="H166" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -7560,19 +7656,19 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>375</v>
+        <v>326</v>
       </c>
       <c r="F167" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="G167" s="1">
         <v>46300</v>
@@ -7595,10 +7691,10 @@
         <v>170</v>
       </c>
       <c r="E168" t="s">
-        <v>37</v>
+        <v>378</v>
       </c>
       <c r="F168" t="s">
-        <v>38</v>
+        <v>379</v>
       </c>
       <c r="G168" s="1">
         <v>46300</v>
@@ -7612,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7621,10 +7717,10 @@
         <v>170</v>
       </c>
       <c r="E169" t="s">
-        <v>375</v>
+        <v>37</v>
       </c>
       <c r="F169" t="s">
-        <v>376</v>
+        <v>38</v>
       </c>
       <c r="G169" s="1">
         <v>46300</v>
@@ -7638,19 +7734,19 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
+        <v>381</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="s">
+        <v>170</v>
+      </c>
+      <c r="E170" t="s">
+        <v>378</v>
+      </c>
+      <c r="F170" t="s">
         <v>379</v>
-      </c>
-      <c r="C170">
-        <v>1</v>
-      </c>
-      <c r="D170" t="s">
-        <v>2</v>
-      </c>
-      <c r="E170" t="s">
-        <v>380</v>
-      </c>
-      <c r="F170" t="s">
-        <v>381</v>
       </c>
       <c r="G170" s="1">
         <v>46300</v>
@@ -7667,10 +7763,10 @@
         <v>382</v>
       </c>
       <c r="C171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E171" t="s">
         <v>383</v>
@@ -7682,7 +7778,7 @@
         <v>46300</v>
       </c>
       <c r="H171" s="1">
-        <v>46303</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -7708,7 +7804,7 @@
         <v>46300</v>
       </c>
       <c r="H172" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -7725,13 +7821,13 @@
         <v>170</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>389</v>
       </c>
       <c r="F173" t="s">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="G173" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="H173" s="1">
         <v>46304</v>
@@ -7742,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C174">
         <v>2</v>
@@ -7751,16 +7847,16 @@
         <v>170</v>
       </c>
       <c r="E174" t="s">
-        <v>390</v>
+        <v>22</v>
       </c>
       <c r="F174" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="G174" s="1">
         <v>46301</v>
       </c>
       <c r="H174" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -7771,22 +7867,22 @@
         <v>392</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
         <v>170</v>
       </c>
       <c r="E175" t="s">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="F175" t="s">
-        <v>87</v>
+        <v>394</v>
       </c>
       <c r="G175" s="1">
         <v>46301</v>
       </c>
       <c r="H175" s="1">
-        <v>46301</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
@@ -7794,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7803,10 +7899,10 @@
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F176" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G176" s="1">
         <v>46301</v>
@@ -7820,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7846,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7872,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7898,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7924,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -7933,10 +8029,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>399</v>
+        <v>37</v>
       </c>
       <c r="F181" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="G181" s="1">
         <v>46301</v>
@@ -8060,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E186" t="s">
         <v>414</v>
@@ -8086,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E187" t="s">
         <v>417</v>
@@ -8164,19 +8260,19 @@
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E190" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F190" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G190" s="1">
         <v>46301</v>
       </c>
       <c r="H190" s="1">
-        <v>46301</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
@@ -8184,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -8193,16 +8289,16 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>37</v>
+        <v>429</v>
       </c>
       <c r="F191" t="s">
-        <v>38</v>
+        <v>430</v>
       </c>
       <c r="G191" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="H191" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -8210,25 +8306,25 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>259</v>
+        <v>429</v>
       </c>
       <c r="F192" t="s">
-        <v>260</v>
+        <v>430</v>
       </c>
       <c r="G192" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="H192" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -8236,19 +8332,19 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E193" t="s">
-        <v>429</v>
+        <v>37</v>
       </c>
       <c r="F193" t="s">
-        <v>430</v>
+        <v>38</v>
       </c>
       <c r="G193" s="1">
         <v>46302</v>
@@ -8262,19 +8358,19 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E194" t="s">
-        <v>432</v>
+        <v>259</v>
       </c>
       <c r="F194" t="s">
-        <v>433</v>
+        <v>260</v>
       </c>
       <c r="G194" s="1">
         <v>46302</v>
@@ -8346,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E197" t="s">
         <v>441</v>
@@ -8398,13 +8494,13 @@
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>277</v>
+        <v>447</v>
       </c>
       <c r="F199" t="s">
-        <v>278</v>
+        <v>448</v>
       </c>
       <c r="G199" s="1">
         <v>46302</v>
@@ -8418,19 +8514,19 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>277</v>
+        <v>450</v>
       </c>
       <c r="F200" t="s">
-        <v>278</v>
+        <v>451</v>
       </c>
       <c r="G200" s="1">
         <v>46302</v>
@@ -8444,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -8453,10 +8549,10 @@
         <v>170</v>
       </c>
       <c r="E201" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="F201" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="G201" s="1">
         <v>46302</v>
@@ -8470,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -8479,10 +8575,10 @@
         <v>170</v>
       </c>
       <c r="E202" t="s">
-        <v>450</v>
+        <v>277</v>
       </c>
       <c r="F202" t="s">
-        <v>451</v>
+        <v>278</v>
       </c>
       <c r="G202" s="1">
         <v>46302</v>
@@ -8496,19 +8592,19 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>453</v>
+        <v>16</v>
       </c>
       <c r="F203" t="s">
-        <v>454</v>
+        <v>17</v>
       </c>
       <c r="G203" s="1">
         <v>46302</v>
@@ -8528,13 +8624,13 @@
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>142</v>
+        <v>456</v>
       </c>
       <c r="F204" t="s">
-        <v>143</v>
+        <v>457</v>
       </c>
       <c r="G204" s="1">
         <v>46302</v>
@@ -8548,19 +8644,19 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
-        <v>185</v>
+        <v>459</v>
       </c>
       <c r="F205" t="s">
-        <v>186</v>
+        <v>460</v>
       </c>
       <c r="G205" s="1">
         <v>46302</v>
@@ -8574,19 +8670,19 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E206" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F206" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="G206" s="1">
         <v>46302</v>
@@ -8600,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -8609,10 +8705,10 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>459</v>
+        <v>185</v>
       </c>
       <c r="F207" t="s">
-        <v>460</v>
+        <v>186</v>
       </c>
       <c r="G207" s="1">
         <v>46302</v>
@@ -8626,19 +8722,19 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D208" t="s">
         <v>2</v>
       </c>
       <c r="E208" t="s">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="F208" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="G208" s="1">
         <v>46302</v>
@@ -8652,7 +8748,7 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -8661,10 +8757,10 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F209" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G209" s="1">
         <v>46302</v>
@@ -8678,19 +8774,19 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>466</v>
+        <v>139</v>
       </c>
       <c r="F210" t="s">
-        <v>467</v>
+        <v>140</v>
       </c>
       <c r="G210" s="1">
         <v>46302</v>
@@ -8710,13 +8806,13 @@
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>37</v>
+        <v>469</v>
       </c>
       <c r="F211" t="s">
-        <v>38</v>
+        <v>470</v>
       </c>
       <c r="G211" s="1">
         <v>46302</v>
@@ -8730,19 +8826,19 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>37</v>
+        <v>472</v>
       </c>
       <c r="F212" t="s">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="G212" s="1">
         <v>46302</v>
@@ -8756,19 +8852,19 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E213" t="s">
-        <v>471</v>
+        <v>37</v>
       </c>
       <c r="F213" t="s">
-        <v>472</v>
+        <v>38</v>
       </c>
       <c r="G213" s="1">
         <v>46302</v>
@@ -8782,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -8808,19 +8904,19 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>478</v>
       </c>
       <c r="G215" s="1">
         <v>46302</v>
@@ -8834,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8860,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8886,7 +8982,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8912,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8938,7 +9034,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -8964,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8990,25 +9086,25 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222" t="s">
         <v>170</v>
       </c>
       <c r="E222" t="s">
-        <v>482</v>
+        <v>37</v>
       </c>
       <c r="F222" t="s">
-        <v>483</v>
+        <v>38</v>
       </c>
       <c r="G222" s="1">
         <v>46302</v>
       </c>
       <c r="H222" s="1">
-        <v>46308</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -9016,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -9025,16 +9121,16 @@
         <v>170</v>
       </c>
       <c r="E223" t="s">
-        <v>485</v>
+        <v>37</v>
       </c>
       <c r="F223" t="s">
-        <v>486</v>
+        <v>38</v>
       </c>
       <c r="G223" s="1">
         <v>46302</v>
       </c>
       <c r="H223" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -9045,22 +9141,22 @@
         <v>487</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D224" t="s">
         <v>170</v>
       </c>
       <c r="E224" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G224" s="1">
         <v>46302</v>
       </c>
       <c r="H224" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -9068,22 +9164,22 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E225" t="s">
-        <v>37</v>
+        <v>491</v>
       </c>
       <c r="F225" t="s">
-        <v>38</v>
+        <v>492</v>
       </c>
       <c r="G225" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="H225" s="1">
         <v>46303</v>
@@ -9094,22 +9190,22 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E226" t="s">
-        <v>37</v>
+        <v>491</v>
       </c>
       <c r="F226" t="s">
-        <v>38</v>
+        <v>492</v>
       </c>
       <c r="G226" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="H226" s="1">
         <v>46303</v>
@@ -9120,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -9146,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -9172,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -9181,10 +9277,10 @@
         <v>170</v>
       </c>
       <c r="E229" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="F229" t="s">
-        <v>494</v>
+        <v>38</v>
       </c>
       <c r="G229" s="1">
         <v>46303</v>
@@ -9198,19 +9294,19 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E230" t="s">
-        <v>496</v>
+        <v>37</v>
       </c>
       <c r="F230" t="s">
-        <v>497</v>
+        <v>38</v>
       </c>
       <c r="G230" s="1">
         <v>46303</v>
@@ -9230,13 +9326,13 @@
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E231" t="s">
-        <v>204</v>
+        <v>499</v>
       </c>
       <c r="F231" t="s">
-        <v>205</v>
+        <v>500</v>
       </c>
       <c r="G231" s="1">
         <v>46303</v>
@@ -9250,7 +9346,7 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -9259,10 +9355,10 @@
         <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F232" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G232" s="1">
         <v>46303</v>
@@ -9276,19 +9372,19 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>503</v>
+        <v>204</v>
       </c>
       <c r="F233" t="s">
-        <v>504</v>
+        <v>205</v>
       </c>
       <c r="G233" s="1">
         <v>46303</v>
@@ -9311,10 +9407,10 @@
         <v>2</v>
       </c>
       <c r="E234" t="s">
-        <v>268</v>
+        <v>506</v>
       </c>
       <c r="F234" t="s">
-        <v>269</v>
+        <v>507</v>
       </c>
       <c r="G234" s="1">
         <v>46303</v>
@@ -9328,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9337,10 +9433,10 @@
         <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F235" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G235" s="1">
         <v>46303</v>
@@ -9354,19 +9450,19 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E236" t="s">
-        <v>510</v>
+        <v>268</v>
       </c>
       <c r="F236" t="s">
-        <v>511</v>
+        <v>269</v>
       </c>
       <c r="G236" s="1">
         <v>46303</v>
@@ -9386,13 +9482,13 @@
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>7</v>
+        <v>513</v>
       </c>
       <c r="F237" t="s">
-        <v>8</v>
+        <v>514</v>
       </c>
       <c r="G237" s="1">
         <v>46303</v>
@@ -9406,7 +9502,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9415,10 +9511,10 @@
         <v>170</v>
       </c>
       <c r="E238" t="s">
-        <v>375</v>
+        <v>516</v>
       </c>
       <c r="F238" t="s">
-        <v>376</v>
+        <v>517</v>
       </c>
       <c r="G238" s="1">
         <v>46303</v>
@@ -9432,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9441,10 +9537,10 @@
         <v>170</v>
       </c>
       <c r="E239" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="F239" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="G239" s="1">
         <v>46303</v>
@@ -9458,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9467,10 +9563,10 @@
         <v>170</v>
       </c>
       <c r="E240" t="s">
-        <v>516</v>
+        <v>378</v>
       </c>
       <c r="F240" t="s">
-        <v>517</v>
+        <v>379</v>
       </c>
       <c r="G240" s="1">
         <v>46303</v>
@@ -9484,7 +9580,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9493,10 +9589,10 @@
         <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>519</v>
+        <v>45</v>
       </c>
       <c r="F241" t="s">
-        <v>520</v>
+        <v>46</v>
       </c>
       <c r="G241" s="1">
         <v>46303</v>
@@ -9519,10 +9615,10 @@
         <v>170</v>
       </c>
       <c r="E242" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F242" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G242" s="1">
         <v>46303</v>
@@ -9536,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9545,10 +9641,10 @@
         <v>170</v>
       </c>
       <c r="E243" t="s">
-        <v>16</v>
+        <v>525</v>
       </c>
       <c r="F243" t="s">
-        <v>17</v>
+        <v>526</v>
       </c>
       <c r="G243" s="1">
         <v>46303</v>
@@ -9562,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9571,10 +9667,10 @@
         <v>170</v>
       </c>
       <c r="E244" t="s">
-        <v>277</v>
+        <v>525</v>
       </c>
       <c r="F244" t="s">
-        <v>278</v>
+        <v>526</v>
       </c>
       <c r="G244" s="1">
         <v>46303</v>
@@ -9588,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9597,10 +9693,10 @@
         <v>170</v>
       </c>
       <c r="E245" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F245" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G245" s="1">
         <v>46303</v>
@@ -9614,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9623,10 +9719,10 @@
         <v>170</v>
       </c>
       <c r="E246" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="F246" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="G246" s="1">
         <v>46303</v>
@@ -9640,7 +9736,7 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9649,10 +9745,10 @@
         <v>170</v>
       </c>
       <c r="E247" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="F247" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G247" s="1">
         <v>46303</v>
@@ -9666,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9675,10 +9771,10 @@
         <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>528</v>
+        <v>16</v>
       </c>
       <c r="F248" t="s">
-        <v>529</v>
+        <v>17</v>
       </c>
       <c r="G248" s="1">
         <v>46303</v>
@@ -9692,25 +9788,25 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249" t="s">
         <v>170</v>
       </c>
       <c r="E249" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="F249" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="G249" s="1">
         <v>46303</v>
       </c>
       <c r="H249" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -9718,19 +9814,19 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E250" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F250" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G250" s="1">
         <v>46303</v>
@@ -9744,25 +9840,25 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D251" t="s">
         <v>170</v>
       </c>
       <c r="E251" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="F251" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G251" s="1">
         <v>46303</v>
       </c>
       <c r="H251" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -9770,7 +9866,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9779,10 +9875,10 @@
         <v>170</v>
       </c>
       <c r="E252" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F252" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G252" s="1">
         <v>46303</v>
@@ -9796,19 +9892,19 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E253" t="s">
-        <v>539</v>
+        <v>259</v>
       </c>
       <c r="F253" t="s">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="G253" s="1">
         <v>46303</v>
@@ -9828,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E254" t="s">
         <v>542</v>
@@ -9854,13 +9950,13 @@
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E255" t="s">
-        <v>142</v>
+        <v>545</v>
       </c>
       <c r="F255" t="s">
-        <v>143</v>
+        <v>546</v>
       </c>
       <c r="G255" s="1">
         <v>46303</v>
@@ -9874,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9883,10 +9979,10 @@
         <v>2</v>
       </c>
       <c r="E256" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F256" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G256" s="1">
         <v>46303</v>
@@ -9900,19 +9996,19 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E257" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="F257" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="G257" s="1">
         <v>46303</v>
@@ -9926,19 +10022,19 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>200</v>
+        <v>552</v>
       </c>
       <c r="F258" t="s">
-        <v>201</v>
+        <v>553</v>
       </c>
       <c r="G258" s="1">
         <v>46303</v>
@@ -9952,25 +10048,25 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="F259" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="G259" s="1">
         <v>46303</v>
       </c>
       <c r="H259" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -9978,7 +10074,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9987,10 +10083,10 @@
         <v>170</v>
       </c>
       <c r="E260" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="F260" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="G260" s="1">
         <v>46303</v>
@@ -10004,25 +10100,25 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D261" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E261" t="s">
-        <v>405</v>
+        <v>132</v>
       </c>
       <c r="F261" t="s">
-        <v>406</v>
+        <v>133</v>
       </c>
       <c r="G261" s="1">
         <v>46303</v>
       </c>
       <c r="H261" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
@@ -10030,25 +10126,25 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E262" t="s">
-        <v>554</v>
+        <v>45</v>
       </c>
       <c r="F262" t="s">
-        <v>555</v>
+        <v>46</v>
       </c>
       <c r="G262" s="1">
         <v>46303</v>
       </c>
       <c r="H262" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -10056,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -10065,10 +10161,10 @@
         <v>2</v>
       </c>
       <c r="E263" t="s">
-        <v>557</v>
+        <v>408</v>
       </c>
       <c r="F263" t="s">
-        <v>558</v>
+        <v>409</v>
       </c>
       <c r="G263" s="1">
         <v>46303</v>
@@ -10085,10 +10181,10 @@
         <v>559</v>
       </c>
       <c r="C264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D264" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E264" t="s">
         <v>560</v>
@@ -10100,7 +10196,7 @@
         <v>46303</v>
       </c>
       <c r="H264" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -10117,10 +10213,10 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F265" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="G265" s="1">
         <v>46303</v>
@@ -10134,19 +10230,19 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="F266" t="s">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="G266" s="1">
         <v>46303</v>
@@ -10160,25 +10256,25 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
+        <v>566</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+      <c r="D267" t="s">
+        <v>2</v>
+      </c>
+      <c r="E267" t="s">
+        <v>563</v>
+      </c>
+      <c r="F267" t="s">
         <v>564</v>
-      </c>
-      <c r="C267">
-        <v>1</v>
-      </c>
-      <c r="D267" t="s">
-        <v>170</v>
-      </c>
-      <c r="E267" t="s">
-        <v>557</v>
-      </c>
-      <c r="F267" t="s">
-        <v>558</v>
       </c>
       <c r="G267" s="1">
         <v>46303</v>
       </c>
       <c r="H267" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -10186,7 +10282,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -10195,16 +10291,16 @@
         <v>170</v>
       </c>
       <c r="E268" t="s">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="F268" t="s">
-        <v>558</v>
+        <v>81</v>
       </c>
       <c r="G268" s="1">
         <v>46303</v>
       </c>
       <c r="H268" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -10212,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -10221,10 +10317,10 @@
         <v>170</v>
       </c>
       <c r="E269" t="s">
-        <v>45</v>
+        <v>563</v>
       </c>
       <c r="F269" t="s">
-        <v>46</v>
+        <v>564</v>
       </c>
       <c r="G269" s="1">
         <v>46303</v>
@@ -10238,19 +10334,19 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E270" t="s">
-        <v>339</v>
+        <v>563</v>
       </c>
       <c r="F270" t="s">
-        <v>340</v>
+        <v>564</v>
       </c>
       <c r="G270" s="1">
         <v>46303</v>
@@ -10264,19 +10360,19 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E271" t="s">
-        <v>339</v>
+        <v>45</v>
       </c>
       <c r="F271" t="s">
-        <v>340</v>
+        <v>46</v>
       </c>
       <c r="G271" s="1">
         <v>46303</v>
@@ -10290,19 +10386,19 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E272" t="s">
-        <v>570</v>
+        <v>342</v>
       </c>
       <c r="F272" t="s">
-        <v>571</v>
+        <v>343</v>
       </c>
       <c r="G272" s="1">
         <v>46303</v>
@@ -10322,13 +10418,13 @@
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E273" t="s">
-        <v>573</v>
+        <v>342</v>
       </c>
       <c r="F273" t="s">
-        <v>574</v>
+        <v>343</v>
       </c>
       <c r="G273" s="1">
         <v>46303</v>
@@ -10342,22 +10438,22 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
+        <v>573</v>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+      <c r="D274" t="s">
+        <v>170</v>
+      </c>
+      <c r="E274" t="s">
+        <v>574</v>
+      </c>
+      <c r="F274" t="s">
         <v>575</v>
       </c>
-      <c r="C274">
-        <v>1</v>
-      </c>
-      <c r="D274" t="s">
-        <v>6</v>
-      </c>
-      <c r="E274" t="s">
-        <v>542</v>
-      </c>
-      <c r="F274" t="s">
-        <v>543</v>
-      </c>
       <c r="G274" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H274" s="1">
         <v>46304</v>
@@ -10377,13 +10473,13 @@
         <v>170</v>
       </c>
       <c r="E275" t="s">
-        <v>37</v>
+        <v>577</v>
       </c>
       <c r="F275" t="s">
-        <v>38</v>
+        <v>578</v>
       </c>
       <c r="G275" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H275" s="1">
         <v>46304</v>
@@ -10394,19 +10490,19 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E276" t="s">
-        <v>420</v>
+        <v>548</v>
       </c>
       <c r="F276" t="s">
-        <v>421</v>
+        <v>549</v>
       </c>
       <c r="G276" s="1">
         <v>46304</v>
@@ -10420,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -10446,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -10455,10 +10551,10 @@
         <v>170</v>
       </c>
       <c r="E278" t="s">
-        <v>542</v>
+        <v>423</v>
       </c>
       <c r="F278" t="s">
-        <v>543</v>
+        <v>424</v>
       </c>
       <c r="G278" s="1">
         <v>46304</v>
@@ -10472,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -10498,19 +10594,19 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E280" t="s">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="F280" t="s">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="G280" s="1">
         <v>46304</v>
@@ -10533,10 +10629,10 @@
         <v>170</v>
       </c>
       <c r="E281" t="s">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="F281" t="s">
-        <v>278</v>
+        <v>38</v>
       </c>
       <c r="G281" s="1">
         <v>46304</v>
@@ -10556,7 +10652,7 @@
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E282" t="s">
         <v>586</v>
@@ -10585,10 +10681,10 @@
         <v>170</v>
       </c>
       <c r="E283" t="s">
-        <v>589</v>
+        <v>277</v>
       </c>
       <c r="F283" t="s">
-        <v>590</v>
+        <v>278</v>
       </c>
       <c r="G283" s="1">
         <v>46304</v>
@@ -10602,19 +10698,19 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
+        <v>589</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>170</v>
+      </c>
+      <c r="E284" t="s">
+        <v>590</v>
+      </c>
+      <c r="F284" t="s">
         <v>591</v>
-      </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284" t="s">
-        <v>170</v>
-      </c>
-      <c r="E284" t="s">
-        <v>592</v>
-      </c>
-      <c r="F284" t="s">
-        <v>593</v>
       </c>
       <c r="G284" s="1">
         <v>46304</v>
@@ -10628,19 +10724,19 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
+        <v>592</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285" t="s">
+        <v>170</v>
+      </c>
+      <c r="E285" t="s">
+        <v>593</v>
+      </c>
+      <c r="F285" t="s">
         <v>594</v>
-      </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="D285" t="s">
-        <v>2</v>
-      </c>
-      <c r="E285" t="s">
-        <v>595</v>
-      </c>
-      <c r="F285" t="s">
-        <v>596</v>
       </c>
       <c r="G285" s="1">
         <v>46304</v>
@@ -10654,19 +10750,19 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
+        <v>595</v>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+      <c r="D286" t="s">
+        <v>170</v>
+      </c>
+      <c r="E286" t="s">
+        <v>596</v>
+      </c>
+      <c r="F286" t="s">
         <v>597</v>
-      </c>
-      <c r="C286">
-        <v>1</v>
-      </c>
-      <c r="D286" t="s">
-        <v>170</v>
-      </c>
-      <c r="E286" t="s">
-        <v>598</v>
-      </c>
-      <c r="F286" t="s">
-        <v>599</v>
       </c>
       <c r="G286" s="1">
         <v>46304</v>
@@ -10680,19 +10776,19 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
+        <v>598</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>2</v>
+      </c>
+      <c r="E287" t="s">
+        <v>599</v>
+      </c>
+      <c r="F287" t="s">
         <v>600</v>
-      </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="D287" t="s">
-        <v>170</v>
-      </c>
-      <c r="E287" t="s">
-        <v>16</v>
-      </c>
-      <c r="F287" t="s">
-        <v>17</v>
       </c>
       <c r="G287" s="1">
         <v>46304</v>
@@ -10712,13 +10808,13 @@
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E288" t="s">
-        <v>182</v>
+        <v>602</v>
       </c>
       <c r="F288" t="s">
-        <v>183</v>
+        <v>603</v>
       </c>
       <c r="G288" s="1">
         <v>46304</v>
@@ -10732,19 +10828,19 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E289" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F289" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="G289" s="1">
         <v>46304</v>
@@ -10758,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10767,10 +10863,10 @@
         <v>170</v>
       </c>
       <c r="E290" t="s">
-        <v>604</v>
+        <v>182</v>
       </c>
       <c r="F290" t="s">
-        <v>605</v>
+        <v>183</v>
       </c>
       <c r="G290" s="1">
         <v>46304</v>
@@ -10793,10 +10889,10 @@
         <v>170</v>
       </c>
       <c r="E291" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="F291" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="G291" s="1">
         <v>46304</v>
@@ -10819,10 +10915,10 @@
         <v>170</v>
       </c>
       <c r="E292" t="s">
-        <v>142</v>
+        <v>608</v>
       </c>
       <c r="F292" t="s">
-        <v>143</v>
+        <v>609</v>
       </c>
       <c r="G292" s="1">
         <v>46304</v>
@@ -10836,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -10845,10 +10941,10 @@
         <v>170</v>
       </c>
       <c r="E293" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="F293" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="G293" s="1">
         <v>46304</v>
@@ -10862,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10871,10 +10967,10 @@
         <v>170</v>
       </c>
       <c r="E294" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F294" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="G294" s="1">
         <v>46304</v>
@@ -10888,19 +10984,19 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E295" t="s">
-        <v>582</v>
+        <v>16</v>
       </c>
       <c r="F295" t="s">
-        <v>583</v>
+        <v>17</v>
       </c>
       <c r="G295" s="1">
         <v>46304</v>
@@ -10914,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10923,10 +11019,10 @@
         <v>170</v>
       </c>
       <c r="E296" t="s">
-        <v>612</v>
+        <v>48</v>
       </c>
       <c r="F296" t="s">
-        <v>613</v>
+        <v>49</v>
       </c>
       <c r="G296" s="1">
         <v>46304</v>
@@ -10946,13 +11042,13 @@
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E297" t="s">
-        <v>615</v>
+        <v>586</v>
       </c>
       <c r="F297" t="s">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="G297" s="1">
         <v>46304</v>
@@ -10966,19 +11062,19 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
+        <v>615</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298" t="s">
+        <v>170</v>
+      </c>
+      <c r="E298" t="s">
+        <v>616</v>
+      </c>
+      <c r="F298" t="s">
         <v>617</v>
-      </c>
-      <c r="C298">
-        <v>1</v>
-      </c>
-      <c r="D298" t="s">
-        <v>2</v>
-      </c>
-      <c r="E298" t="s">
-        <v>554</v>
-      </c>
-      <c r="F298" t="s">
-        <v>555</v>
       </c>
       <c r="G298" s="1">
         <v>46304</v>
@@ -11001,10 +11097,10 @@
         <v>170</v>
       </c>
       <c r="E299" t="s">
-        <v>235</v>
+        <v>619</v>
       </c>
       <c r="F299" t="s">
-        <v>236</v>
+        <v>620</v>
       </c>
       <c r="G299" s="1">
         <v>46304</v>
@@ -11018,19 +11114,19 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E300" t="s">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="F300" t="s">
-        <v>621</v>
+        <v>561</v>
       </c>
       <c r="G300" s="1">
         <v>46304</v>
@@ -11053,10 +11149,10 @@
         <v>170</v>
       </c>
       <c r="E301" t="s">
-        <v>623</v>
+        <v>235</v>
       </c>
       <c r="F301" t="s">
-        <v>624</v>
+        <v>236</v>
       </c>
       <c r="G301" s="1">
         <v>46304</v>
@@ -11070,19 +11166,19 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
+        <v>623</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="D302" t="s">
+        <v>2</v>
+      </c>
+      <c r="E302" t="s">
+        <v>624</v>
+      </c>
+      <c r="F302" t="s">
         <v>625</v>
-      </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-      <c r="D302" t="s">
-        <v>170</v>
-      </c>
-      <c r="E302" t="s">
-        <v>626</v>
-      </c>
-      <c r="F302" t="s">
-        <v>627</v>
       </c>
       <c r="G302" s="1">
         <v>46304</v>
@@ -11096,19 +11192,19 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
+        <v>626</v>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+      <c r="D303" t="s">
+        <v>170</v>
+      </c>
+      <c r="E303" t="s">
+        <v>627</v>
+      </c>
+      <c r="F303" t="s">
         <v>628</v>
-      </c>
-      <c r="C303">
-        <v>1</v>
-      </c>
-      <c r="D303" t="s">
-        <v>170</v>
-      </c>
-      <c r="E303" t="s">
-        <v>629</v>
-      </c>
-      <c r="F303" t="s">
-        <v>630</v>
       </c>
       <c r="G303" s="1">
         <v>46304</v>
@@ -11122,19 +11218,19 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
+        <v>629</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="D304" t="s">
+        <v>170</v>
+      </c>
+      <c r="E304" t="s">
+        <v>630</v>
+      </c>
+      <c r="F304" t="s">
         <v>631</v>
-      </c>
-      <c r="C304">
-        <v>1</v>
-      </c>
-      <c r="D304" t="s">
-        <v>170</v>
-      </c>
-      <c r="E304" t="s">
-        <v>268</v>
-      </c>
-      <c r="F304" t="s">
-        <v>269</v>
       </c>
       <c r="G304" s="1">
         <v>46304</v>
@@ -11157,10 +11253,10 @@
         <v>170</v>
       </c>
       <c r="E305" t="s">
-        <v>444</v>
+        <v>633</v>
       </c>
       <c r="F305" t="s">
-        <v>445</v>
+        <v>634</v>
       </c>
       <c r="G305" s="1">
         <v>46304</v>
@@ -11174,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -11183,10 +11279,10 @@
         <v>170</v>
       </c>
       <c r="E306" t="s">
-        <v>367</v>
+        <v>268</v>
       </c>
       <c r="F306" t="s">
-        <v>368</v>
+        <v>269</v>
       </c>
       <c r="G306" s="1">
         <v>46304</v>
@@ -11200,7 +11296,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -11209,10 +11305,10 @@
         <v>170</v>
       </c>
       <c r="E307" t="s">
-        <v>37</v>
+        <v>450</v>
       </c>
       <c r="F307" t="s">
-        <v>38</v>
+        <v>451</v>
       </c>
       <c r="G307" s="1">
         <v>46304</v>
@@ -11226,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -11235,10 +11331,10 @@
         <v>170</v>
       </c>
       <c r="E308" t="s">
-        <v>636</v>
+        <v>370</v>
       </c>
       <c r="F308" t="s">
-        <v>637</v>
+        <v>371</v>
       </c>
       <c r="G308" s="1">
         <v>46304</v>
@@ -11261,10 +11357,10 @@
         <v>170</v>
       </c>
       <c r="E309" t="s">
-        <v>639</v>
+        <v>37</v>
       </c>
       <c r="F309" t="s">
-        <v>640</v>
+        <v>38</v>
       </c>
       <c r="G309" s="1">
         <v>46304</v>
@@ -11278,19 +11374,19 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
+        <v>639</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+      <c r="D310" t="s">
+        <v>170</v>
+      </c>
+      <c r="E310" t="s">
+        <v>640</v>
+      </c>
+      <c r="F310" t="s">
         <v>641</v>
-      </c>
-      <c r="C310">
-        <v>1</v>
-      </c>
-      <c r="D310" t="s">
-        <v>170</v>
-      </c>
-      <c r="E310" t="s">
-        <v>636</v>
-      </c>
-      <c r="F310" t="s">
-        <v>637</v>
       </c>
       <c r="G310" s="1">
         <v>46304</v>
@@ -11339,10 +11435,10 @@
         <v>170</v>
       </c>
       <c r="E312" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F312" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G312" s="1">
         <v>46304</v>
@@ -11356,19 +11452,19 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
+        <v>646</v>
+      </c>
+      <c r="C313">
+        <v>1</v>
+      </c>
+      <c r="D313" t="s">
+        <v>170</v>
+      </c>
+      <c r="E313" t="s">
+        <v>647</v>
+      </c>
+      <c r="F313" t="s">
         <v>648</v>
-      </c>
-      <c r="C313">
-        <v>1</v>
-      </c>
-      <c r="D313" t="s">
-        <v>170</v>
-      </c>
-      <c r="E313" t="s">
-        <v>649</v>
-      </c>
-      <c r="F313" t="s">
-        <v>650</v>
       </c>
       <c r="G313" s="1">
         <v>46304</v>
@@ -11382,19 +11478,19 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
+        <v>649</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+      <c r="D314" t="s">
+        <v>170</v>
+      </c>
+      <c r="E314" t="s">
+        <v>650</v>
+      </c>
+      <c r="F314" t="s">
         <v>651</v>
-      </c>
-      <c r="C314">
-        <v>1</v>
-      </c>
-      <c r="D314" t="s">
-        <v>170</v>
-      </c>
-      <c r="E314" t="s">
-        <v>652</v>
-      </c>
-      <c r="F314" t="s">
-        <v>653</v>
       </c>
       <c r="G314" s="1">
         <v>46304</v>
@@ -11408,19 +11504,19 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
+        <v>652</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>2</v>
+      </c>
+      <c r="E315" t="s">
+        <v>653</v>
+      </c>
+      <c r="F315" t="s">
         <v>654</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>170</v>
-      </c>
-      <c r="E315" t="s">
-        <v>652</v>
-      </c>
-      <c r="F315" t="s">
-        <v>653</v>
       </c>
       <c r="G315" s="1">
         <v>46304</v>
@@ -11443,10 +11539,10 @@
         <v>170</v>
       </c>
       <c r="E316" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F316" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G316" s="1">
         <v>46304</v>
@@ -11460,19 +11556,19 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
+        <v>658</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>170</v>
+      </c>
+      <c r="E317" t="s">
         <v>656</v>
       </c>
-      <c r="C317">
-        <v>1</v>
-      </c>
-      <c r="D317" t="s">
-        <v>170</v>
-      </c>
-      <c r="E317" t="s">
+      <c r="F317" t="s">
         <v>657</v>
-      </c>
-      <c r="F317" t="s">
-        <v>658</v>
       </c>
       <c r="G317" s="1">
         <v>46304</v>
@@ -11492,19 +11588,19 @@
         <v>1</v>
       </c>
       <c r="D318" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E318" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F318" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="G318" s="1">
         <v>46304</v>
       </c>
       <c r="H318" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
@@ -11512,25 +11608,25 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
+        <v>660</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>170</v>
+      </c>
+      <c r="E319" t="s">
+        <v>661</v>
+      </c>
+      <c r="F319" t="s">
         <v>662</v>
-      </c>
-      <c r="C319">
-        <v>1</v>
-      </c>
-      <c r="D319" t="s">
-        <v>170</v>
-      </c>
-      <c r="E319" t="s">
-        <v>663</v>
-      </c>
-      <c r="F319" t="s">
-        <v>664</v>
       </c>
       <c r="G319" s="1">
         <v>46304</v>
       </c>
       <c r="H319" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
@@ -11538,19 +11634,19 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
+        <v>663</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>2</v>
+      </c>
+      <c r="E320" t="s">
+        <v>664</v>
+      </c>
+      <c r="F320" t="s">
         <v>665</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320" t="s">
-        <v>170</v>
-      </c>
-      <c r="E320" t="s">
-        <v>663</v>
-      </c>
-      <c r="F320" t="s">
-        <v>664</v>
       </c>
       <c r="G320" s="1">
         <v>46304</v>
@@ -11570,7 +11666,7 @@
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E321" t="s">
         <v>667</v>
@@ -11596,13 +11692,13 @@
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E322" t="s">
-        <v>215</v>
+        <v>667</v>
       </c>
       <c r="F322" t="s">
-        <v>216</v>
+        <v>668</v>
       </c>
       <c r="G322" s="1">
         <v>46304</v>
@@ -11625,10 +11721,10 @@
         <v>2</v>
       </c>
       <c r="E323" t="s">
-        <v>215</v>
+        <v>671</v>
       </c>
       <c r="F323" t="s">
-        <v>216</v>
+        <v>672</v>
       </c>
       <c r="G323" s="1">
         <v>46304</v>
@@ -11642,22 +11738,22 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C324">
         <v>1</v>
       </c>
       <c r="D324" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E324" t="s">
-        <v>672</v>
+        <v>215</v>
       </c>
       <c r="F324" t="s">
-        <v>673</v>
+        <v>216</v>
       </c>
       <c r="G324" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="H324" s="1">
         <v>46308</v>
@@ -11674,16 +11770,16 @@
         <v>1</v>
       </c>
       <c r="D325" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E325" t="s">
-        <v>675</v>
+        <v>215</v>
       </c>
       <c r="F325" t="s">
-        <v>676</v>
+        <v>216</v>
       </c>
       <c r="G325" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="H325" s="1">
         <v>46308</v>
@@ -11694,19 +11790,19 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
+        <v>675</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+      <c r="D326" t="s">
+        <v>95</v>
+      </c>
+      <c r="E326" t="s">
+        <v>676</v>
+      </c>
+      <c r="F326" t="s">
         <v>677</v>
-      </c>
-      <c r="C326">
-        <v>1</v>
-      </c>
-      <c r="D326" t="s">
-        <v>170</v>
-      </c>
-      <c r="E326" t="s">
-        <v>678</v>
-      </c>
-      <c r="F326" t="s">
-        <v>679</v>
       </c>
       <c r="G326" s="1">
         <v>46305</v>
@@ -11720,19 +11816,19 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
+        <v>678</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327" t="s">
+        <v>2</v>
+      </c>
+      <c r="E327" t="s">
+        <v>679</v>
+      </c>
+      <c r="F327" t="s">
         <v>680</v>
-      </c>
-      <c r="C327">
-        <v>1</v>
-      </c>
-      <c r="D327" t="s">
-        <v>170</v>
-      </c>
-      <c r="E327" t="s">
-        <v>681</v>
-      </c>
-      <c r="F327" t="s">
-        <v>682</v>
       </c>
       <c r="G327" s="1">
         <v>46305</v>
@@ -11746,19 +11842,19 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
+        <v>681</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+      <c r="D328" t="s">
+        <v>170</v>
+      </c>
+      <c r="E328" t="s">
+        <v>682</v>
+      </c>
+      <c r="F328" t="s">
         <v>683</v>
-      </c>
-      <c r="C328">
-        <v>1</v>
-      </c>
-      <c r="D328" t="s">
-        <v>170</v>
-      </c>
-      <c r="E328" t="s">
-        <v>684</v>
-      </c>
-      <c r="F328" t="s">
-        <v>685</v>
       </c>
       <c r="G328" s="1">
         <v>46305</v>
@@ -11772,19 +11868,19 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
+        <v>684</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329" t="s">
+        <v>170</v>
+      </c>
+      <c r="E329" t="s">
+        <v>685</v>
+      </c>
+      <c r="F329" t="s">
         <v>686</v>
-      </c>
-      <c r="C329">
-        <v>1</v>
-      </c>
-      <c r="D329" t="s">
-        <v>170</v>
-      </c>
-      <c r="E329" t="s">
-        <v>687</v>
-      </c>
-      <c r="F329" t="s">
-        <v>688</v>
       </c>
       <c r="G329" s="1">
         <v>46305</v>
@@ -11798,19 +11894,19 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
+        <v>687</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+      <c r="D330" t="s">
+        <v>170</v>
+      </c>
+      <c r="E330" t="s">
+        <v>688</v>
+      </c>
+      <c r="F330" t="s">
         <v>689</v>
-      </c>
-      <c r="C330">
-        <v>1</v>
-      </c>
-      <c r="D330" t="s">
-        <v>170</v>
-      </c>
-      <c r="E330" t="s">
-        <v>687</v>
-      </c>
-      <c r="F330" t="s">
-        <v>688</v>
       </c>
       <c r="G330" s="1">
         <v>46305</v>
@@ -11833,13 +11929,13 @@
         <v>170</v>
       </c>
       <c r="E331" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="F331" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="G331" s="1">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="H331" s="1">
         <v>46308</v>
@@ -11850,22 +11946,22 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
+        <v>693</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332" t="s">
+        <v>170</v>
+      </c>
+      <c r="E332" t="s">
         <v>691</v>
       </c>
-      <c r="C332">
-        <v>1</v>
-      </c>
-      <c r="D332" t="s">
-        <v>170</v>
-      </c>
-      <c r="E332" t="s">
-        <v>510</v>
-      </c>
       <c r="F332" t="s">
-        <v>511</v>
+        <v>692</v>
       </c>
       <c r="G332" s="1">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="H332" s="1">
         <v>46308</v>
@@ -11876,7 +11972,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11885,10 +11981,10 @@
         <v>170</v>
       </c>
       <c r="E333" t="s">
-        <v>693</v>
+        <v>667</v>
       </c>
       <c r="F333" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="G333" s="1">
         <v>46307</v>
@@ -11911,10 +12007,10 @@
         <v>170</v>
       </c>
       <c r="E334" t="s">
-        <v>693</v>
+        <v>516</v>
       </c>
       <c r="F334" t="s">
-        <v>694</v>
+        <v>517</v>
       </c>
       <c r="G334" s="1">
         <v>46307</v>
@@ -11937,10 +12033,10 @@
         <v>170</v>
       </c>
       <c r="E335" t="s">
-        <v>560</v>
+        <v>697</v>
       </c>
       <c r="F335" t="s">
-        <v>561</v>
+        <v>698</v>
       </c>
       <c r="G335" s="1">
         <v>46307</v>
@@ -11954,19 +12050,19 @@
         <v>0</v>
       </c>
       <c r="B336" t="s">
+        <v>699</v>
+      </c>
+      <c r="C336">
+        <v>1</v>
+      </c>
+      <c r="D336" t="s">
+        <v>170</v>
+      </c>
+      <c r="E336" t="s">
         <v>697</v>
       </c>
-      <c r="C336">
-        <v>1</v>
-      </c>
-      <c r="D336" t="s">
-        <v>170</v>
-      </c>
-      <c r="E336" t="s">
-        <v>672</v>
-      </c>
       <c r="F336" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="G336" s="1">
         <v>46307</v>
@@ -11980,19 +12076,19 @@
         <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E337" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="F337" t="s">
-        <v>409</v>
+        <v>337</v>
       </c>
       <c r="G337" s="1">
         <v>46307</v>
@@ -12006,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -12015,10 +12111,10 @@
         <v>2</v>
       </c>
       <c r="E338" t="s">
-        <v>595</v>
+        <v>676</v>
       </c>
       <c r="F338" t="s">
-        <v>596</v>
+        <v>677</v>
       </c>
       <c r="G338" s="1">
         <v>46307</v>
@@ -12032,7 +12128,7 @@
         <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -12041,13 +12137,13 @@
         <v>170</v>
       </c>
       <c r="E339" t="s">
-        <v>235</v>
+        <v>411</v>
       </c>
       <c r="F339" t="s">
-        <v>236</v>
+        <v>412</v>
       </c>
       <c r="G339" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="H339" s="1">
         <v>46308</v>
@@ -12058,22 +12154,22 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E340" t="s">
-        <v>204</v>
+        <v>599</v>
       </c>
       <c r="F340" t="s">
-        <v>205</v>
+        <v>600</v>
       </c>
       <c r="G340" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="H340" s="1">
         <v>46308</v>
@@ -12084,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -12093,10 +12189,10 @@
         <v>170</v>
       </c>
       <c r="E341" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="F341" t="s">
-        <v>93</v>
+        <v>236</v>
       </c>
       <c r="G341" s="1">
         <v>46308</v>
@@ -12110,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -12119,10 +12215,10 @@
         <v>170</v>
       </c>
       <c r="E342" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="F342" t="s">
-        <v>93</v>
+        <v>205</v>
       </c>
       <c r="G342" s="1">
         <v>46308</v>
@@ -12136,19 +12232,19 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C343">
         <v>1</v>
       </c>
       <c r="D343" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E343" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="F343" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="G343" s="1">
         <v>46308</v>
@@ -12162,19 +12258,19 @@
         <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E344" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F344" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G344" s="1">
         <v>46308</v>
@@ -12188,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -12197,10 +12293,10 @@
         <v>2</v>
       </c>
       <c r="E345" t="s">
-        <v>471</v>
+        <v>16</v>
       </c>
       <c r="F345" t="s">
-        <v>472</v>
+        <v>17</v>
       </c>
       <c r="G345" s="1">
         <v>46308</v>
@@ -12214,7 +12310,7 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -12223,10 +12319,10 @@
         <v>170</v>
       </c>
       <c r="E346" t="s">
-        <v>708</v>
+        <v>80</v>
       </c>
       <c r="F346" t="s">
-        <v>709</v>
+        <v>81</v>
       </c>
       <c r="G346" s="1">
         <v>46308</v>
@@ -12246,13 +12342,13 @@
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E347" t="s">
-        <v>711</v>
+        <v>477</v>
       </c>
       <c r="F347" t="s">
-        <v>712</v>
+        <v>478</v>
       </c>
       <c r="G347" s="1">
         <v>46308</v>
@@ -12266,19 +12362,19 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
+        <v>711</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+      <c r="D348" t="s">
+        <v>170</v>
+      </c>
+      <c r="E348" t="s">
+        <v>712</v>
+      </c>
+      <c r="F348" t="s">
         <v>713</v>
-      </c>
-      <c r="C348">
-        <v>1</v>
-      </c>
-      <c r="D348" t="s">
-        <v>170</v>
-      </c>
-      <c r="E348" t="s">
-        <v>714</v>
-      </c>
-      <c r="F348" t="s">
-        <v>715</v>
       </c>
       <c r="G348" s="1">
         <v>46308</v>
@@ -12292,19 +12388,19 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
+        <v>714</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+      <c r="D349" t="s">
+        <v>170</v>
+      </c>
+      <c r="E349" t="s">
+        <v>715</v>
+      </c>
+      <c r="F349" t="s">
         <v>716</v>
-      </c>
-      <c r="C349">
-        <v>1</v>
-      </c>
-      <c r="D349" t="s">
-        <v>170</v>
-      </c>
-      <c r="E349" t="s">
-        <v>225</v>
-      </c>
-      <c r="F349" t="s">
-        <v>226</v>
       </c>
       <c r="G349" s="1">
         <v>46308</v>
@@ -12353,10 +12449,10 @@
         <v>170</v>
       </c>
       <c r="E351" t="s">
-        <v>420</v>
+        <v>225</v>
       </c>
       <c r="F351" t="s">
-        <v>421</v>
+        <v>226</v>
       </c>
       <c r="G351" s="1">
         <v>46308</v>
@@ -12402,13 +12498,13 @@
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E353" t="s">
-        <v>722</v>
+        <v>423</v>
       </c>
       <c r="F353" t="s">
-        <v>723</v>
+        <v>424</v>
       </c>
       <c r="G353" s="1">
         <v>46308</v>
@@ -12431,10 +12527,10 @@
         <v>170</v>
       </c>
       <c r="E354" t="s">
-        <v>97</v>
+        <v>726</v>
       </c>
       <c r="F354" t="s">
-        <v>98</v>
+        <v>727</v>
       </c>
       <c r="G354" s="1">
         <v>46308</v>
@@ -12448,19 +12544,19 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
+        <v>728</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355" t="s">
+        <v>170</v>
+      </c>
+      <c r="E355" t="s">
         <v>726</v>
       </c>
-      <c r="C355">
-        <v>1</v>
-      </c>
-      <c r="D355" t="s">
-        <v>170</v>
-      </c>
-      <c r="E355" t="s">
+      <c r="F355" t="s">
         <v>727</v>
-      </c>
-      <c r="F355" t="s">
-        <v>728</v>
       </c>
       <c r="G355" s="1">
         <v>46308</v>
@@ -12483,10 +12579,10 @@
         <v>170</v>
       </c>
       <c r="E356" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="F356" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="G356" s="1">
         <v>46308</v>
@@ -12509,10 +12605,10 @@
         <v>170</v>
       </c>
       <c r="E357" t="s">
-        <v>326</v>
+        <v>731</v>
       </c>
       <c r="F357" t="s">
-        <v>327</v>
+        <v>732</v>
       </c>
       <c r="G357" s="1">
         <v>46308</v>
@@ -12526,7 +12622,7 @@
         <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -12535,10 +12631,10 @@
         <v>170</v>
       </c>
       <c r="E358" t="s">
-        <v>732</v>
+        <v>172</v>
       </c>
       <c r="F358" t="s">
-        <v>733</v>
+        <v>173</v>
       </c>
       <c r="G358" s="1">
         <v>46308</v>
@@ -12561,10 +12657,10 @@
         <v>170</v>
       </c>
       <c r="E359" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="F359" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="G359" s="1">
         <v>46308</v>
@@ -12587,10 +12683,10 @@
         <v>170</v>
       </c>
       <c r="E360" t="s">
-        <v>255</v>
+        <v>736</v>
       </c>
       <c r="F360" t="s">
-        <v>256</v>
+        <v>737</v>
       </c>
       <c r="G360" s="1">
         <v>46308</v>
@@ -12604,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -12613,10 +12709,10 @@
         <v>170</v>
       </c>
       <c r="E361" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="F361" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="G361" s="1">
         <v>46308</v>
@@ -12630,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -12639,10 +12735,10 @@
         <v>170</v>
       </c>
       <c r="E362" t="s">
-        <v>738</v>
+        <v>255</v>
       </c>
       <c r="F362" t="s">
-        <v>739</v>
+        <v>256</v>
       </c>
       <c r="G362" s="1">
         <v>46308</v>
@@ -12665,10 +12761,10 @@
         <v>170</v>
       </c>
       <c r="E363" t="s">
-        <v>741</v>
+        <v>48</v>
       </c>
       <c r="F363" t="s">
-        <v>742</v>
+        <v>49</v>
       </c>
       <c r="G363" s="1">
         <v>46308</v>
@@ -12682,19 +12778,19 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
+        <v>741</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+      <c r="D364" t="s">
+        <v>2</v>
+      </c>
+      <c r="E364" t="s">
+        <v>742</v>
+      </c>
+      <c r="F364" t="s">
         <v>743</v>
-      </c>
-      <c r="C364">
-        <v>1</v>
-      </c>
-      <c r="D364" t="s">
-        <v>170</v>
-      </c>
-      <c r="E364" t="s">
-        <v>532</v>
-      </c>
-      <c r="F364" t="s">
-        <v>533</v>
       </c>
       <c r="G364" s="1">
         <v>46308</v>
@@ -12743,10 +12839,10 @@
         <v>170</v>
       </c>
       <c r="E366" t="s">
-        <v>305</v>
+        <v>538</v>
       </c>
       <c r="F366" t="s">
-        <v>306</v>
+        <v>539</v>
       </c>
       <c r="G366" s="1">
         <v>46308</v>
@@ -12769,10 +12865,10 @@
         <v>170</v>
       </c>
       <c r="E367" t="s">
-        <v>111</v>
+        <v>749</v>
       </c>
       <c r="F367" t="s">
-        <v>112</v>
+        <v>750</v>
       </c>
       <c r="G367" s="1">
         <v>46308</v>
@@ -12786,19 +12882,19 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="F368" t="s">
-        <v>253</v>
+        <v>306</v>
       </c>
       <c r="G368" s="1">
         <v>46308</v>
@@ -12812,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -12838,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12847,10 +12943,10 @@
         <v>170</v>
       </c>
       <c r="E370" t="s">
-        <v>408</v>
+        <v>252</v>
       </c>
       <c r="F370" t="s">
-        <v>409</v>
+        <v>253</v>
       </c>
       <c r="G370" s="1">
         <v>46308</v>
@@ -12864,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C371">
         <v>1</v>
@@ -12873,10 +12969,10 @@
         <v>170</v>
       </c>
       <c r="E371" t="s">
-        <v>678</v>
+        <v>111</v>
       </c>
       <c r="F371" t="s">
-        <v>679</v>
+        <v>112</v>
       </c>
       <c r="G371" s="1">
         <v>46308</v>
@@ -12890,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -12899,10 +12995,10 @@
         <v>170</v>
       </c>
       <c r="E372" t="s">
-        <v>111</v>
+        <v>411</v>
       </c>
       <c r="F372" t="s">
-        <v>112</v>
+        <v>412</v>
       </c>
       <c r="G372" s="1">
         <v>46308</v>
@@ -12916,7 +13012,7 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12925,10 +13021,10 @@
         <v>170</v>
       </c>
       <c r="E373" t="s">
-        <v>111</v>
+        <v>682</v>
       </c>
       <c r="F373" t="s">
-        <v>112</v>
+        <v>683</v>
       </c>
       <c r="G373" s="1">
         <v>46308</v>
@@ -12942,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -12968,7 +13064,7 @@
         <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -12977,10 +13073,10 @@
         <v>170</v>
       </c>
       <c r="E375" t="s">
-        <v>471</v>
+        <v>111</v>
       </c>
       <c r="F375" t="s">
-        <v>472</v>
+        <v>112</v>
       </c>
       <c r="G375" s="1">
         <v>46308</v>
@@ -12994,7 +13090,7 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -13020,19 +13116,19 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E377" t="s">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="F377" t="s">
-        <v>112</v>
+        <v>478</v>
       </c>
       <c r="G377" s="1">
         <v>46308</v>
@@ -13046,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -13072,7 +13168,7 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C379">
         <v>1</v>
@@ -13081,10 +13177,10 @@
         <v>170</v>
       </c>
       <c r="E379" t="s">
-        <v>761</v>
+        <v>111</v>
       </c>
       <c r="F379" t="s">
-        <v>762</v>
+        <v>112</v>
       </c>
       <c r="G379" s="1">
         <v>46308</v>
@@ -13130,13 +13226,13 @@
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E381" t="s">
-        <v>111</v>
+        <v>765</v>
       </c>
       <c r="F381" t="s">
-        <v>112</v>
+        <v>766</v>
       </c>
       <c r="G381" s="1">
         <v>46308</v>
@@ -13150,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -13176,7 +13272,7 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -13202,7 +13298,7 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -13228,7 +13324,7 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C385">
         <v>1</v>
@@ -13237,10 +13333,10 @@
         <v>170</v>
       </c>
       <c r="E385" t="s">
-        <v>769</v>
+        <v>111</v>
       </c>
       <c r="F385" t="s">
-        <v>770</v>
+        <v>112</v>
       </c>
       <c r="G385" s="1">
         <v>46308</v>
@@ -13263,10 +13359,10 @@
         <v>170</v>
       </c>
       <c r="E386" t="s">
-        <v>225</v>
+        <v>111</v>
       </c>
       <c r="F386" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="G386" s="1">
         <v>46308</v>
@@ -13315,10 +13411,10 @@
         <v>170</v>
       </c>
       <c r="E388" t="s">
-        <v>776</v>
+        <v>225</v>
       </c>
       <c r="F388" t="s">
-        <v>777</v>
+        <v>226</v>
       </c>
       <c r="G388" s="1">
         <v>46308</v>
@@ -13332,19 +13428,19 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
+        <v>776</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>170</v>
+      </c>
+      <c r="E389" t="s">
+        <v>777</v>
+      </c>
+      <c r="F389" t="s">
         <v>778</v>
-      </c>
-      <c r="C389">
-        <v>1</v>
-      </c>
-      <c r="D389" t="s">
-        <v>170</v>
-      </c>
-      <c r="E389" t="s">
-        <v>16</v>
-      </c>
-      <c r="F389" t="s">
-        <v>17</v>
       </c>
       <c r="G389" s="1">
         <v>46308</v>
@@ -13367,10 +13463,10 @@
         <v>170</v>
       </c>
       <c r="E390" t="s">
-        <v>612</v>
+        <v>780</v>
       </c>
       <c r="F390" t="s">
-        <v>613</v>
+        <v>781</v>
       </c>
       <c r="G390" s="1">
         <v>46308</v>
@@ -13384,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C391">
         <v>1</v>
@@ -13393,10 +13489,10 @@
         <v>170</v>
       </c>
       <c r="E391" t="s">
-        <v>781</v>
+        <v>16</v>
       </c>
       <c r="F391" t="s">
-        <v>782</v>
+        <v>17</v>
       </c>
       <c r="G391" s="1">
         <v>46308</v>
@@ -13419,10 +13515,10 @@
         <v>170</v>
       </c>
       <c r="E392" t="s">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="F392" t="s">
-        <v>17</v>
+        <v>617</v>
       </c>
       <c r="G392" s="1">
         <v>46308</v>
@@ -13471,10 +13567,10 @@
         <v>170</v>
       </c>
       <c r="E394" t="s">
-        <v>788</v>
+        <v>16</v>
       </c>
       <c r="F394" t="s">
-        <v>789</v>
+        <v>17</v>
       </c>
       <c r="G394" s="1">
         <v>46308</v>
@@ -13488,19 +13584,19 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
+        <v>788</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>170</v>
+      </c>
+      <c r="E395" t="s">
+        <v>789</v>
+      </c>
+      <c r="F395" t="s">
         <v>790</v>
-      </c>
-      <c r="C395">
-        <v>1</v>
-      </c>
-      <c r="D395" t="s">
-        <v>170</v>
-      </c>
-      <c r="E395" t="s">
-        <v>185</v>
-      </c>
-      <c r="F395" t="s">
-        <v>186</v>
       </c>
       <c r="G395" s="1">
         <v>46308</v>
@@ -13523,10 +13619,10 @@
         <v>170</v>
       </c>
       <c r="E396" t="s">
-        <v>649</v>
+        <v>792</v>
       </c>
       <c r="F396" t="s">
-        <v>650</v>
+        <v>793</v>
       </c>
       <c r="G396" s="1">
         <v>46308</v>
@@ -13540,7 +13636,7 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C397">
         <v>1</v>
@@ -13549,10 +13645,10 @@
         <v>170</v>
       </c>
       <c r="E397" t="s">
-        <v>516</v>
+        <v>185</v>
       </c>
       <c r="F397" t="s">
-        <v>517</v>
+        <v>186</v>
       </c>
       <c r="G397" s="1">
         <v>46308</v>
@@ -13566,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -13575,10 +13671,10 @@
         <v>170</v>
       </c>
       <c r="E398" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="F398" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="G398" s="1">
         <v>46308</v>
@@ -13592,7 +13688,7 @@
         <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C399">
         <v>1</v>
@@ -13601,10 +13697,10 @@
         <v>170</v>
       </c>
       <c r="E399" t="s">
-        <v>97</v>
+        <v>522</v>
       </c>
       <c r="F399" t="s">
-        <v>98</v>
+        <v>523</v>
       </c>
       <c r="G399" s="1">
         <v>46308</v>
@@ -13618,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C400">
         <v>1</v>
@@ -13627,10 +13723,10 @@
         <v>170</v>
       </c>
       <c r="E400" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="F400" t="s">
-        <v>98</v>
+        <v>668</v>
       </c>
       <c r="G400" s="1">
         <v>46308</v>
@@ -13644,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C401">
         <v>1</v>
@@ -13653,10 +13749,10 @@
         <v>170</v>
       </c>
       <c r="E401" t="s">
-        <v>212</v>
+        <v>97</v>
       </c>
       <c r="F401" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="G401" s="1">
         <v>46308</v>
@@ -13670,19 +13766,19 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E402" t="s">
-        <v>798</v>
+        <v>97</v>
       </c>
       <c r="F402" t="s">
-        <v>799</v>
+        <v>98</v>
       </c>
       <c r="G402" s="1">
         <v>46308</v>
@@ -13705,10 +13801,10 @@
         <v>170</v>
       </c>
       <c r="E403" t="s">
-        <v>604</v>
+        <v>212</v>
       </c>
       <c r="F403" t="s">
-        <v>605</v>
+        <v>213</v>
       </c>
       <c r="G403" s="1">
         <v>46308</v>
@@ -13731,10 +13827,10 @@
         <v>170</v>
       </c>
       <c r="E404" t="s">
-        <v>182</v>
+        <v>802</v>
       </c>
       <c r="F404" t="s">
-        <v>183</v>
+        <v>803</v>
       </c>
       <c r="G404" s="1">
         <v>46308</v>
@@ -13748,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="B405" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C405">
         <v>1</v>
@@ -13757,10 +13853,10 @@
         <v>170</v>
       </c>
       <c r="E405" t="s">
-        <v>803</v>
+        <v>608</v>
       </c>
       <c r="F405" t="s">
-        <v>804</v>
+        <v>609</v>
       </c>
       <c r="G405" s="1">
         <v>46308</v>
@@ -13783,10 +13879,10 @@
         <v>170</v>
       </c>
       <c r="E406" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="F406" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="G406" s="1">
         <v>46308</v>
@@ -13806,13 +13902,13 @@
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E407" t="s">
-        <v>235</v>
+        <v>807</v>
       </c>
       <c r="F407" t="s">
-        <v>236</v>
+        <v>808</v>
       </c>
       <c r="G407" s="1">
         <v>46308</v>
@@ -13826,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="B408" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C408">
         <v>1</v>
@@ -13835,10 +13931,10 @@
         <v>170</v>
       </c>
       <c r="E408" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="F408" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G408" s="1">
         <v>46308</v>
@@ -13852,7 +13948,7 @@
         <v>0</v>
       </c>
       <c r="B409" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -13861,10 +13957,10 @@
         <v>170</v>
       </c>
       <c r="E409" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="F409" t="s">
-        <v>93</v>
+        <v>236</v>
       </c>
       <c r="G409" s="1">
         <v>46308</v>
@@ -13878,7 +13974,7 @@
         <v>0</v>
       </c>
       <c r="B410" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -13887,10 +13983,10 @@
         <v>170</v>
       </c>
       <c r="E410" t="s">
-        <v>810</v>
+        <v>80</v>
       </c>
       <c r="F410" t="s">
-        <v>811</v>
+        <v>81</v>
       </c>
       <c r="G410" s="1">
         <v>46308</v>
@@ -13913,10 +14009,10 @@
         <v>170</v>
       </c>
       <c r="E411" t="s">
-        <v>813</v>
+        <v>92</v>
       </c>
       <c r="F411" t="s">
-        <v>814</v>
+        <v>93</v>
       </c>
       <c r="G411" s="1">
         <v>46308</v>
@@ -13930,19 +14026,19 @@
         <v>0</v>
       </c>
       <c r="B412" t="s">
+        <v>813</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" t="s">
+        <v>170</v>
+      </c>
+      <c r="E412" t="s">
+        <v>814</v>
+      </c>
+      <c r="F412" t="s">
         <v>815</v>
-      </c>
-      <c r="C412">
-        <v>1</v>
-      </c>
-      <c r="D412" t="s">
-        <v>170</v>
-      </c>
-      <c r="E412" t="s">
-        <v>816</v>
-      </c>
-      <c r="F412" t="s">
-        <v>817</v>
       </c>
       <c r="G412" s="1">
         <v>46308</v>
@@ -13956,19 +14052,19 @@
         <v>0</v>
       </c>
       <c r="B413" t="s">
+        <v>816</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="s">
+        <v>170</v>
+      </c>
+      <c r="E413" t="s">
+        <v>817</v>
+      </c>
+      <c r="F413" t="s">
         <v>818</v>
-      </c>
-      <c r="C413">
-        <v>1</v>
-      </c>
-      <c r="D413" t="s">
-        <v>170</v>
-      </c>
-      <c r="E413" t="s">
-        <v>185</v>
-      </c>
-      <c r="F413" t="s">
-        <v>186</v>
       </c>
       <c r="G413" s="1">
         <v>46308</v>
@@ -13991,10 +14087,10 @@
         <v>170</v>
       </c>
       <c r="E414" t="s">
-        <v>57</v>
+        <v>820</v>
       </c>
       <c r="F414" t="s">
-        <v>58</v>
+        <v>821</v>
       </c>
       <c r="G414" s="1">
         <v>46308</v>
@@ -14008,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="B415" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C415">
         <v>1</v>
@@ -14017,10 +14113,10 @@
         <v>170</v>
       </c>
       <c r="E415" t="s">
-        <v>821</v>
+        <v>185</v>
       </c>
       <c r="F415" t="s">
-        <v>822</v>
+        <v>186</v>
       </c>
       <c r="G415" s="1">
         <v>46308</v>
@@ -14040,13 +14136,13 @@
         <v>1</v>
       </c>
       <c r="D416" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E416" t="s">
-        <v>824</v>
+        <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>825</v>
+        <v>58</v>
       </c>
       <c r="G416" s="1">
         <v>46308</v>
@@ -14060,19 +14156,19 @@
         <v>0</v>
       </c>
       <c r="B417" t="s">
+        <v>824</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" t="s">
+        <v>170</v>
+      </c>
+      <c r="E417" t="s">
+        <v>825</v>
+      </c>
+      <c r="F417" t="s">
         <v>826</v>
-      </c>
-      <c r="C417">
-        <v>1</v>
-      </c>
-      <c r="D417" t="s">
-        <v>170</v>
-      </c>
-      <c r="E417" t="s">
-        <v>429</v>
-      </c>
-      <c r="F417" t="s">
-        <v>430</v>
       </c>
       <c r="G417" s="1">
         <v>46308</v>
@@ -14083,62 +14179,62 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
+        <v>0</v>
+      </c>
+      <c r="B418" t="s">
         <v>827</v>
       </c>
-      <c r="B418" t="s">
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418" t="s">
+        <v>170</v>
+      </c>
+      <c r="E418" t="s">
         <v>828</v>
       </c>
-      <c r="C418">
-        <v>1</v>
-      </c>
-      <c r="D418" t="s">
-        <v>2</v>
-      </c>
-      <c r="E418" t="s">
-        <v>200</v>
-      </c>
       <c r="F418" t="s">
-        <v>201</v>
+        <v>829</v>
       </c>
       <c r="G418" s="1">
-        <v>46148</v>
+        <v>46308</v>
       </c>
       <c r="H418" s="1">
-        <v>46149</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="B419" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C419">
         <v>1</v>
       </c>
       <c r="D419" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E419" t="s">
-        <v>111</v>
+        <v>435</v>
       </c>
       <c r="F419" t="s">
-        <v>112</v>
+        <v>436</v>
       </c>
       <c r="G419" s="1">
-        <v>46268</v>
+        <v>46308</v>
       </c>
       <c r="H419" s="1">
-        <v>46268</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="B420" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C420">
         <v>1</v>
@@ -14147,21 +14243,21 @@
         <v>170</v>
       </c>
       <c r="E420" t="s">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="F420" t="s">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="G420" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H420" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="B421" t="s">
         <v>832</v>
@@ -14173,336 +14269,336 @@
         <v>170</v>
       </c>
       <c r="E421" t="s">
-        <v>833</v>
+        <v>599</v>
       </c>
       <c r="F421" t="s">
-        <v>834</v>
+        <v>600</v>
       </c>
       <c r="G421" s="1">
         <v>46308</v>
       </c>
       <c r="H421" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B422" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C422">
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E422" t="s">
-        <v>41</v>
+        <v>599</v>
       </c>
       <c r="F422" t="s">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="G422" s="1">
-        <v>46133</v>
+        <v>46308</v>
       </c>
       <c r="H422" s="1">
-        <v>46134</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
+        <v>0</v>
+      </c>
+      <c r="B423" t="s">
+        <v>834</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>170</v>
+      </c>
+      <c r="E423" t="s">
         <v>835</v>
       </c>
-      <c r="B423" t="s">
-        <v>837</v>
-      </c>
-      <c r="C423">
-        <v>1</v>
-      </c>
-      <c r="D423" t="s">
-        <v>6</v>
-      </c>
-      <c r="E423" t="s">
-        <v>41</v>
-      </c>
       <c r="F423" t="s">
-        <v>42</v>
+        <v>836</v>
       </c>
       <c r="G423" s="1">
-        <v>46134</v>
+        <v>46308</v>
       </c>
       <c r="H423" s="1">
-        <v>46134</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B424" t="s">
+        <v>837</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424" t="s">
+        <v>170</v>
+      </c>
+      <c r="E424" t="s">
         <v>838</v>
       </c>
-      <c r="C424">
-        <v>1</v>
-      </c>
-      <c r="D424" t="s">
-        <v>6</v>
-      </c>
-      <c r="E424" t="s">
-        <v>19</v>
-      </c>
       <c r="F424" t="s">
-        <v>20</v>
+        <v>839</v>
       </c>
       <c r="G424" s="1">
-        <v>46156</v>
+        <v>46308</v>
       </c>
       <c r="H424" s="1">
-        <v>46156</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B425" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C425">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D425" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E425" t="s">
-        <v>840</v>
+        <v>105</v>
       </c>
       <c r="F425" t="s">
-        <v>841</v>
+        <v>106</v>
       </c>
       <c r="G425" s="1">
-        <v>46209</v>
+        <v>46308</v>
       </c>
       <c r="H425" s="1">
-        <v>46218</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B426" t="s">
+        <v>841</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+      <c r="D426" t="s">
+        <v>170</v>
+      </c>
+      <c r="E426" t="s">
         <v>842</v>
       </c>
-      <c r="C426">
-        <v>1</v>
-      </c>
-      <c r="D426" t="s">
-        <v>6</v>
-      </c>
-      <c r="E426" t="s">
+      <c r="F426" t="s">
         <v>843</v>
       </c>
-      <c r="F426" t="s">
-        <v>844</v>
-      </c>
       <c r="G426" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
       <c r="H426" s="1">
-        <v>46213</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B427" t="s">
+        <v>844</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+      <c r="D427" t="s">
+        <v>170</v>
+      </c>
+      <c r="E427" t="s">
         <v>845</v>
       </c>
-      <c r="C427">
-        <v>1</v>
-      </c>
-      <c r="D427" t="s">
-        <v>95</v>
-      </c>
-      <c r="E427" t="s">
-        <v>589</v>
-      </c>
       <c r="F427" t="s">
-        <v>590</v>
+        <v>846</v>
       </c>
       <c r="G427" s="1">
-        <v>46213</v>
+        <v>46308</v>
       </c>
       <c r="H427" s="1">
-        <v>46216</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B428" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C428">
         <v>1</v>
       </c>
       <c r="D428" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E428" t="s">
-        <v>589</v>
+        <v>848</v>
       </c>
       <c r="F428" t="s">
-        <v>590</v>
+        <v>849</v>
       </c>
       <c r="G428" s="1">
-        <v>46224</v>
+        <v>46308</v>
       </c>
       <c r="H428" s="1">
-        <v>46224</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B429" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C429">
         <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E429" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="F429" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="G429" s="1">
-        <v>46253</v>
+        <v>46308</v>
       </c>
       <c r="H429" s="1">
-        <v>46253</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B430" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C430">
         <v>1</v>
       </c>
       <c r="D430" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E430" t="s">
-        <v>212</v>
+        <v>854</v>
       </c>
       <c r="F430" t="s">
-        <v>213</v>
+        <v>855</v>
       </c>
       <c r="G430" s="1">
-        <v>46273</v>
+        <v>46308</v>
       </c>
       <c r="H430" s="1">
-        <v>46274</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B431" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C431">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D431" t="s">
         <v>170</v>
       </c>
       <c r="E431" t="s">
-        <v>852</v>
+        <v>101</v>
       </c>
       <c r="F431" t="s">
-        <v>853</v>
+        <v>102</v>
       </c>
       <c r="G431" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="H431" s="1">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B432" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C432">
         <v>1</v>
       </c>
       <c r="D432" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E432" t="s">
-        <v>222</v>
+        <v>435</v>
       </c>
       <c r="F432" t="s">
-        <v>223</v>
+        <v>436</v>
       </c>
       <c r="G432" s="1">
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="H432" s="1">
-        <v>46300</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="B433" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C433">
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E433" t="s">
-        <v>589</v>
+        <v>185</v>
       </c>
       <c r="F433" t="s">
-        <v>590</v>
+        <v>186</v>
       </c>
       <c r="G433" s="1">
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="H433" s="1">
-        <v>46301</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="B434" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C434">
         <v>1</v>
@@ -14511,50 +14607,50 @@
         <v>2</v>
       </c>
       <c r="E434" t="s">
-        <v>352</v>
+        <v>200</v>
       </c>
       <c r="F434" t="s">
-        <v>353</v>
+        <v>201</v>
       </c>
       <c r="G434" s="1">
-        <v>46302</v>
+        <v>46148</v>
       </c>
       <c r="H434" s="1">
-        <v>46302</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="B435" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C435">
         <v>1</v>
       </c>
       <c r="D435" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E435" t="s">
-        <v>840</v>
+        <v>111</v>
       </c>
       <c r="F435" t="s">
-        <v>841</v>
+        <v>112</v>
       </c>
       <c r="G435" s="1">
-        <v>46302</v>
+        <v>46268</v>
       </c>
       <c r="H435" s="1">
-        <v>46302</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="B436" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C436">
         <v>1</v>
@@ -14563,10 +14659,10 @@
         <v>170</v>
       </c>
       <c r="E436" t="s">
-        <v>493</v>
+        <v>389</v>
       </c>
       <c r="F436" t="s">
-        <v>494</v>
+        <v>390</v>
       </c>
       <c r="G436" s="1">
         <v>46303</v>
@@ -14577,296 +14673,296 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>835</v>
+        <v>863</v>
       </c>
       <c r="B437" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C437">
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E437" t="s">
-        <v>519</v>
+        <v>865</v>
       </c>
       <c r="F437" t="s">
-        <v>520</v>
+        <v>866</v>
       </c>
       <c r="G437" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
       <c r="H437" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B438" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C438">
         <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E438" t="s">
-        <v>519</v>
+        <v>41</v>
       </c>
       <c r="F438" t="s">
-        <v>520</v>
+        <v>42</v>
       </c>
       <c r="G438" s="1">
-        <v>46303</v>
+        <v>46133</v>
       </c>
       <c r="H438" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B439" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="C439">
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E439" t="s">
-        <v>519</v>
+        <v>41</v>
       </c>
       <c r="F439" t="s">
-        <v>520</v>
+        <v>42</v>
       </c>
       <c r="G439" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
       <c r="H439" s="1">
-        <v>46303</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B440" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C440">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D440" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E440" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="F440" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="G440" s="1">
-        <v>46303</v>
+        <v>46156</v>
       </c>
       <c r="H440" s="1">
-        <v>46308</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B441" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C441">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D441" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E441" t="s">
-        <v>589</v>
+        <v>872</v>
       </c>
       <c r="F441" t="s">
-        <v>590</v>
+        <v>873</v>
       </c>
       <c r="G441" s="1">
-        <v>46304</v>
+        <v>46209</v>
       </c>
       <c r="H441" s="1">
-        <v>46304</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B442" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="C442">
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E442" t="s">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="F442" t="s">
-        <v>841</v>
+        <v>876</v>
       </c>
       <c r="G442" s="1">
-        <v>46304</v>
+        <v>46213</v>
       </c>
       <c r="H442" s="1">
-        <v>46304</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B443" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="C443">
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E443" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F443" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
       <c r="G443" s="1">
-        <v>46308</v>
+        <v>46213</v>
       </c>
       <c r="H443" s="1">
-        <v>46308</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B444" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C444">
         <v>1</v>
       </c>
       <c r="D444" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="E444" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F444" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
       <c r="G444" s="1">
-        <v>46308</v>
+        <v>46224</v>
       </c>
       <c r="H444" s="1">
-        <v>46308</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="B445" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="C445">
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E445" t="s">
-        <v>429</v>
+        <v>880</v>
       </c>
       <c r="F445" t="s">
-        <v>430</v>
+        <v>881</v>
       </c>
       <c r="G445" s="1">
-        <v>46308</v>
+        <v>46253</v>
       </c>
       <c r="H445" s="1">
-        <v>46308</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B446" t="s">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="C446">
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="E446" t="s">
-        <v>870</v>
+        <v>212</v>
       </c>
       <c r="F446" t="s">
-        <v>871</v>
+        <v>213</v>
       </c>
       <c r="G446" s="1">
-        <v>46063</v>
+        <v>46273</v>
       </c>
       <c r="H446" s="1">
-        <v>46064</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B447" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="C447">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D447" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E447" t="s">
-        <v>57</v>
+        <v>884</v>
       </c>
       <c r="F447" t="s">
-        <v>58</v>
+        <v>885</v>
       </c>
       <c r="G447" s="1">
-        <v>46113</v>
+        <v>46300</v>
       </c>
       <c r="H447" s="1">
-        <v>46125</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B448" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="C448">
         <v>1</v>
@@ -14875,24 +14971,24 @@
         <v>2</v>
       </c>
       <c r="E448" t="s">
-        <v>57</v>
+        <v>222</v>
       </c>
       <c r="F448" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="G448" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
       <c r="H448" s="1">
-        <v>46125</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B449" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="C449">
         <v>1</v>
@@ -14901,24 +14997,24 @@
         <v>2</v>
       </c>
       <c r="E449" t="s">
-        <v>57</v>
+        <v>593</v>
       </c>
       <c r="F449" t="s">
-        <v>58</v>
+        <v>594</v>
       </c>
       <c r="G449" s="1">
-        <v>46126</v>
+        <v>46300</v>
       </c>
       <c r="H449" s="1">
-        <v>46126</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B450" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="C450">
         <v>1</v>
@@ -14927,284 +15023,284 @@
         <v>2</v>
       </c>
       <c r="E450" t="s">
-        <v>57</v>
+        <v>355</v>
       </c>
       <c r="F450" t="s">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="G450" s="1">
-        <v>46126</v>
+        <v>46302</v>
       </c>
       <c r="H450" s="1">
-        <v>46126</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B451" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="C451">
         <v>1</v>
       </c>
       <c r="D451" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E451" t="s">
-        <v>57</v>
+        <v>872</v>
       </c>
       <c r="F451" t="s">
-        <v>58</v>
+        <v>873</v>
       </c>
       <c r="G451" s="1">
-        <v>46128</v>
+        <v>46302</v>
       </c>
       <c r="H451" s="1">
-        <v>46128</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B452" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
       <c r="C452">
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E452" t="s">
-        <v>57</v>
+        <v>499</v>
       </c>
       <c r="F452" t="s">
-        <v>58</v>
+        <v>500</v>
       </c>
       <c r="G452" s="1">
-        <v>46132</v>
+        <v>46303</v>
       </c>
       <c r="H452" s="1">
-        <v>46132</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B453" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E453" t="s">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="F453" t="s">
-        <v>58</v>
+        <v>526</v>
       </c>
       <c r="G453" s="1">
-        <v>46161</v>
+        <v>46303</v>
       </c>
       <c r="H453" s="1">
-        <v>46161</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B454" t="s">
-        <v>879</v>
+        <v>892</v>
       </c>
       <c r="C454">
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E454" t="s">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="F454" t="s">
-        <v>58</v>
+        <v>526</v>
       </c>
       <c r="G454" s="1">
-        <v>46174</v>
+        <v>46303</v>
       </c>
       <c r="H454" s="1">
-        <v>46174</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B455" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="C455">
         <v>1</v>
       </c>
       <c r="D455" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E455" t="s">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="F455" t="s">
-        <v>58</v>
+        <v>526</v>
       </c>
       <c r="G455" s="1">
-        <v>46174</v>
+        <v>46303</v>
       </c>
       <c r="H455" s="1">
-        <v>46174</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B456" t="s">
-        <v>881</v>
+        <v>894</v>
       </c>
       <c r="C456">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D456" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E456" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="F456" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="G456" s="1">
-        <v>46195</v>
+        <v>46303</v>
       </c>
       <c r="H456" s="1">
-        <v>46252</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B457" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="C457">
         <v>1</v>
       </c>
       <c r="D457" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E457" t="s">
-        <v>57</v>
+        <v>593</v>
       </c>
       <c r="F457" t="s">
-        <v>58</v>
+        <v>594</v>
       </c>
       <c r="G457" s="1">
-        <v>46210</v>
+        <v>46304</v>
       </c>
       <c r="H457" s="1">
-        <v>46210</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B458" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="C458">
         <v>1</v>
       </c>
       <c r="D458" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E458" t="s">
-        <v>57</v>
+        <v>872</v>
       </c>
       <c r="F458" t="s">
-        <v>58</v>
+        <v>873</v>
       </c>
       <c r="G458" s="1">
-        <v>46213</v>
+        <v>46304</v>
       </c>
       <c r="H458" s="1">
-        <v>46213</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B459" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="C459">
         <v>1</v>
       </c>
       <c r="D459" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E459" t="s">
-        <v>57</v>
+        <v>712</v>
       </c>
       <c r="F459" t="s">
-        <v>58</v>
+        <v>713</v>
       </c>
       <c r="G459" s="1">
-        <v>46218</v>
+        <v>46308</v>
       </c>
       <c r="H459" s="1">
-        <v>46252</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B460" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="C460">
         <v>1</v>
       </c>
       <c r="D460" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="E460" t="s">
-        <v>77</v>
+        <v>712</v>
       </c>
       <c r="F460" t="s">
-        <v>78</v>
+        <v>713</v>
       </c>
       <c r="G460" s="1">
-        <v>46226</v>
+        <v>46308</v>
       </c>
       <c r="H460" s="1">
-        <v>46226</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B461" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="C461">
         <v>1</v>
@@ -15213,50 +15309,50 @@
         <v>170</v>
       </c>
       <c r="E461" t="s">
-        <v>57</v>
+        <v>435</v>
       </c>
       <c r="F461" t="s">
-        <v>58</v>
+        <v>436</v>
       </c>
       <c r="G461" s="1">
-        <v>46227</v>
+        <v>46308</v>
       </c>
       <c r="H461" s="1">
-        <v>46252</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B462" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="C462">
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E462" t="s">
-        <v>57</v>
+        <v>902</v>
       </c>
       <c r="F462" t="s">
-        <v>58</v>
+        <v>903</v>
       </c>
       <c r="G462" s="1">
-        <v>46227</v>
+        <v>46063</v>
       </c>
       <c r="H462" s="1">
-        <v>46252</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B463" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="C463">
         <v>1</v>
@@ -15271,50 +15367,50 @@
         <v>58</v>
       </c>
       <c r="G463" s="1">
-        <v>46227</v>
+        <v>46113</v>
       </c>
       <c r="H463" s="1">
-        <v>46228</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B464" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="C464">
         <v>1</v>
       </c>
       <c r="D464" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E464" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F464" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G464" s="1">
-        <v>46230</v>
+        <v>46125</v>
       </c>
       <c r="H464" s="1">
-        <v>46252</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B465" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="C465">
         <v>1</v>
       </c>
       <c r="D465" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E465" t="s">
         <v>57</v>
@@ -15323,24 +15419,24 @@
         <v>58</v>
       </c>
       <c r="G465" s="1">
-        <v>46231</v>
+        <v>46126</v>
       </c>
       <c r="H465" s="1">
-        <v>46231</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B466" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="C466">
         <v>1</v>
       </c>
       <c r="D466" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E466" t="s">
         <v>57</v>
@@ -15349,18 +15445,18 @@
         <v>58</v>
       </c>
       <c r="G466" s="1">
-        <v>46254</v>
+        <v>46126</v>
       </c>
       <c r="H466" s="1">
-        <v>46254</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B467" t="s">
-        <v>892</v>
+        <v>908</v>
       </c>
       <c r="C467">
         <v>1</v>
@@ -15375,18 +15471,18 @@
         <v>58</v>
       </c>
       <c r="G467" s="1">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="H467" s="1">
-        <v>46255</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B468" t="s">
-        <v>893</v>
+        <v>909</v>
       </c>
       <c r="C468">
         <v>1</v>
@@ -15401,24 +15497,24 @@
         <v>58</v>
       </c>
       <c r="G468" s="1">
-        <v>46260</v>
+        <v>46132</v>
       </c>
       <c r="H468" s="1">
-        <v>46260</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B469" t="s">
-        <v>894</v>
+        <v>910</v>
       </c>
       <c r="C469">
         <v>1</v>
       </c>
       <c r="D469" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E469" t="s">
         <v>57</v>
@@ -15427,24 +15523,24 @@
         <v>58</v>
       </c>
       <c r="G469" s="1">
-        <v>46289</v>
+        <v>46161</v>
       </c>
       <c r="H469" s="1">
-        <v>46289</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B470" t="s">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="C470">
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E470" t="s">
         <v>57</v>
@@ -15453,24 +15549,24 @@
         <v>58</v>
       </c>
       <c r="G470" s="1">
-        <v>46294</v>
+        <v>46174</v>
       </c>
       <c r="H470" s="1">
-        <v>46294</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B471" t="s">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="C471">
         <v>1</v>
       </c>
       <c r="D471" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="E471" t="s">
         <v>57</v>
@@ -15479,70 +15575,70 @@
         <v>58</v>
       </c>
       <c r="G471" s="1">
-        <v>46308</v>
+        <v>46174</v>
       </c>
       <c r="H471" s="1">
-        <v>46308</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B472" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="C472">
         <v>1</v>
       </c>
       <c r="D472" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E472" t="s">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="F472" t="s">
-        <v>900</v>
+        <v>58</v>
       </c>
       <c r="G472" s="1">
-        <v>46157</v>
+        <v>46195</v>
       </c>
       <c r="H472" s="1">
-        <v>46157</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B473" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="C473">
         <v>1</v>
       </c>
       <c r="D473" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E473" t="s">
-        <v>902</v>
+        <v>57</v>
       </c>
       <c r="F473" t="s">
-        <v>903</v>
+        <v>58</v>
       </c>
       <c r="G473" s="1">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="H473" s="1">
-        <v>46170</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B474" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="C474">
         <v>1</v>
@@ -15551,180 +15647,180 @@
         <v>2</v>
       </c>
       <c r="E474" t="s">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="F474" t="s">
-        <v>900</v>
+        <v>58</v>
       </c>
       <c r="G474" s="1">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="H474" s="1">
-        <v>46218</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B475" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="C475">
         <v>1</v>
       </c>
       <c r="D475" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E475" t="s">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="F475" t="s">
-        <v>900</v>
+        <v>58</v>
       </c>
       <c r="G475" s="1">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="H475" s="1">
-        <v>46244</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B476" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="C476">
         <v>1</v>
       </c>
       <c r="D476" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E476" t="s">
-        <v>899</v>
+        <v>77</v>
       </c>
       <c r="F476" t="s">
-        <v>900</v>
+        <v>78</v>
       </c>
       <c r="G476" s="1">
-        <v>46247</v>
+        <v>46226</v>
       </c>
       <c r="H476" s="1">
-        <v>46247</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B477" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="C477">
         <v>1</v>
       </c>
       <c r="D477" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="E477" t="s">
-        <v>908</v>
+        <v>57</v>
       </c>
       <c r="F477" t="s">
-        <v>909</v>
+        <v>58</v>
       </c>
       <c r="G477" s="1">
-        <v>46247</v>
+        <v>46227</v>
       </c>
       <c r="H477" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B478" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="C478">
         <v>1</v>
       </c>
       <c r="D478" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E478" t="s">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="F478" t="s">
-        <v>900</v>
+        <v>58</v>
       </c>
       <c r="G478" s="1">
-        <v>46255</v>
+        <v>46227</v>
       </c>
       <c r="H478" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B479" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="C479">
         <v>1</v>
       </c>
       <c r="D479" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E479" t="s">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="F479" t="s">
-        <v>900</v>
+        <v>58</v>
       </c>
       <c r="G479" s="1">
-        <v>46258</v>
+        <v>46227</v>
       </c>
       <c r="H479" s="1">
-        <v>46258</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B480" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="C480">
         <v>1</v>
       </c>
       <c r="D480" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E480" t="s">
-        <v>899</v>
+        <v>77</v>
       </c>
       <c r="F480" t="s">
-        <v>900</v>
+        <v>78</v>
       </c>
       <c r="G480" s="1">
-        <v>46262</v>
+        <v>46230</v>
       </c>
       <c r="H480" s="1">
-        <v>46265</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B481" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="C481">
         <v>1</v>
@@ -15733,15 +15829,431 @@
         <v>6</v>
       </c>
       <c r="E481" t="s">
+        <v>57</v>
+      </c>
+      <c r="F481" t="s">
+        <v>58</v>
+      </c>
+      <c r="G481" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H481" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>900</v>
+      </c>
+      <c r="B482" t="s">
+        <v>923</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>6</v>
+      </c>
+      <c r="E482" t="s">
+        <v>57</v>
+      </c>
+      <c r="F482" t="s">
+        <v>58</v>
+      </c>
+      <c r="G482" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H482" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>900</v>
+      </c>
+      <c r="B483" t="s">
+        <v>924</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+      <c r="D483" t="s">
+        <v>2</v>
+      </c>
+      <c r="E483" t="s">
+        <v>57</v>
+      </c>
+      <c r="F483" t="s">
+        <v>58</v>
+      </c>
+      <c r="G483" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H483" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>900</v>
+      </c>
+      <c r="B484" t="s">
+        <v>925</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+      <c r="D484" t="s">
+        <v>6</v>
+      </c>
+      <c r="E484" t="s">
+        <v>57</v>
+      </c>
+      <c r="F484" t="s">
+        <v>58</v>
+      </c>
+      <c r="G484" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H484" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>900</v>
+      </c>
+      <c r="B485" t="s">
+        <v>926</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485" t="s">
+        <v>6</v>
+      </c>
+      <c r="E485" t="s">
+        <v>57</v>
+      </c>
+      <c r="F485" t="s">
+        <v>58</v>
+      </c>
+      <c r="G485" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H485" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>900</v>
+      </c>
+      <c r="B486" t="s">
+        <v>927</v>
+      </c>
+      <c r="C486">
+        <v>1</v>
+      </c>
+      <c r="D486" t="s">
+        <v>6</v>
+      </c>
+      <c r="E486" t="s">
+        <v>57</v>
+      </c>
+      <c r="F486" t="s">
+        <v>58</v>
+      </c>
+      <c r="G486" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H486" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>900</v>
+      </c>
+      <c r="B487" t="s">
+        <v>928</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+      <c r="D487" t="s">
+        <v>170</v>
+      </c>
+      <c r="E487" t="s">
+        <v>57</v>
+      </c>
+      <c r="F487" t="s">
+        <v>58</v>
+      </c>
+      <c r="G487" s="1">
+        <v>46309</v>
+      </c>
+      <c r="H487" s="1">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>929</v>
+      </c>
+      <c r="B488" t="s">
+        <v>930</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+      <c r="D488" t="s">
+        <v>2</v>
+      </c>
+      <c r="E488" t="s">
+        <v>931</v>
+      </c>
+      <c r="F488" t="s">
+        <v>932</v>
+      </c>
+      <c r="G488" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H488" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>929</v>
+      </c>
+      <c r="B489" t="s">
+        <v>933</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+      <c r="D489" t="s">
+        <v>2</v>
+      </c>
+      <c r="E489" t="s">
+        <v>934</v>
+      </c>
+      <c r="F489" t="s">
+        <v>935</v>
+      </c>
+      <c r="G489" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H489" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>929</v>
+      </c>
+      <c r="B490" t="s">
+        <v>936</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+      <c r="D490" t="s">
+        <v>2</v>
+      </c>
+      <c r="E490" t="s">
+        <v>931</v>
+      </c>
+      <c r="F490" t="s">
+        <v>932</v>
+      </c>
+      <c r="G490" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H490" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>929</v>
+      </c>
+      <c r="B491" t="s">
+        <v>937</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+      <c r="D491" t="s">
+        <v>2</v>
+      </c>
+      <c r="E491" t="s">
+        <v>931</v>
+      </c>
+      <c r="F491" t="s">
+        <v>932</v>
+      </c>
+      <c r="G491" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H491" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>929</v>
+      </c>
+      <c r="B492" t="s">
+        <v>938</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+      <c r="D492" t="s">
+        <v>2</v>
+      </c>
+      <c r="E492" t="s">
+        <v>931</v>
+      </c>
+      <c r="F492" t="s">
+        <v>932</v>
+      </c>
+      <c r="G492" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H492" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>929</v>
+      </c>
+      <c r="B493" t="s">
+        <v>939</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+      <c r="D493" t="s">
+        <v>2</v>
+      </c>
+      <c r="E493" t="s">
+        <v>940</v>
+      </c>
+      <c r="F493" t="s">
+        <v>941</v>
+      </c>
+      <c r="G493" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H493" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>929</v>
+      </c>
+      <c r="B494" t="s">
+        <v>942</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494" t="s">
+        <v>2</v>
+      </c>
+      <c r="E494" t="s">
+        <v>931</v>
+      </c>
+      <c r="F494" t="s">
+        <v>932</v>
+      </c>
+      <c r="G494" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H494" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A495" t="s">
+        <v>929</v>
+      </c>
+      <c r="B495" t="s">
+        <v>943</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2</v>
+      </c>
+      <c r="E495" t="s">
+        <v>931</v>
+      </c>
+      <c r="F495" t="s">
+        <v>932</v>
+      </c>
+      <c r="G495" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H495" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A496" t="s">
+        <v>929</v>
+      </c>
+      <c r="B496" t="s">
+        <v>944</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+      <c r="D496" t="s">
+        <v>2</v>
+      </c>
+      <c r="E496" t="s">
+        <v>931</v>
+      </c>
+      <c r="F496" t="s">
+        <v>932</v>
+      </c>
+      <c r="G496" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H496" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A497" t="s">
+        <v>929</v>
+      </c>
+      <c r="B497" t="s">
+        <v>945</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+      <c r="D497" t="s">
+        <v>6</v>
+      </c>
+      <c r="E497" t="s">
         <v>13</v>
       </c>
-      <c r="F481" t="s">
+      <c r="F497" t="s">
         <v>14</v>
       </c>
-      <c r="G481" s="1">
+      <c r="G497" s="1">
         <v>46281</v>
       </c>
-      <c r="H481" s="1">
+      <c r="H497" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD903A38-D6B7-4602-8FB3-5314C3DD4FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6A3A16C-D12B-41FC-BE84-DF85B159CE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{248C6DD4-9882-42C3-AB75-DACACA196D23}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B5D148D-8907-4D34-8130-1B44EED7A688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FA5A3AC-CC1E-4F40-B5D2-47AB9C430851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21615" yWindow="1125" windowWidth="21600" windowHeight="11835" xr2:uid="{231BCA37-E3CC-4427-91B0-C58E51263DD7}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A8DE5F5-13C4-4D4E-B914-D22A014EDC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{393257E2-19BB-4D5B-8BC0-972C7C62CAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21615" yWindow="1125" windowWidth="21600" windowHeight="11835" xr2:uid="{5A4E75B8-F044-41AE-96E2-21D3F12B7FAC}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{934C53FF-2504-43AC-A559-62B4F0965047}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="758">
   <si>
     <t>0001</t>
   </si>
@@ -1342,15 +1342,6 @@
     <t>IMEPHO S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217419</t>
-  </si>
-  <si>
-    <t>VP01</t>
-  </si>
-  <si>
-    <t>CORRALON PASQUINI SRL</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217421</t>
   </si>
   <si>
@@ -1375,9 +1366,6 @@
     <t xml:space="preserve">  217429</t>
   </si>
   <si>
-    <t xml:space="preserve">  217445</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217452</t>
   </si>
   <si>
@@ -1402,15 +1390,6 @@
     <t>NESTOR A BIONDINI</t>
   </si>
   <si>
-    <t xml:space="preserve">  217457</t>
-  </si>
-  <si>
-    <t>EF07</t>
-  </si>
-  <si>
-    <t>EL FUTURO DEL OESTE S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217459</t>
   </si>
   <si>
@@ -1450,15 +1429,6 @@
     <t xml:space="preserve">  217468</t>
   </si>
   <si>
-    <t xml:space="preserve">  217473</t>
-  </si>
-  <si>
-    <t>BH14</t>
-  </si>
-  <si>
-    <t>BENETTI HUGO D -CONSTRUCCIONES DEL OESTE</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217474</t>
   </si>
   <si>
@@ -1552,16 +1522,538 @@
     <t>HIEMACAR S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217513</t>
+    <t xml:space="preserve">  217515</t>
+  </si>
+  <si>
+    <t>CP31</t>
+  </si>
+  <si>
+    <t>CASAPAULINO SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217518</t>
+  </si>
+  <si>
+    <t>FE26</t>
+  </si>
+  <si>
+    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217524</t>
+  </si>
+  <si>
+    <t>MA31</t>
+  </si>
+  <si>
+    <t>MATRIGAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217527</t>
+  </si>
+  <si>
+    <t>BN08</t>
+  </si>
+  <si>
+    <t>BONINO NORBERTO DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217541</t>
+  </si>
+  <si>
+    <t>SM26</t>
+  </si>
+  <si>
+    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217543</t>
+  </si>
+  <si>
+    <t>ED04</t>
+  </si>
+  <si>
+    <t>EDIFICOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217544</t>
+  </si>
+  <si>
+    <t>VA09</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO VEGA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217545</t>
+  </si>
+  <si>
+    <t>DA28</t>
+  </si>
+  <si>
+    <t>DAPESOL S.A. -MATERIALES ACON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217549</t>
+  </si>
+  <si>
+    <t>PR22</t>
+  </si>
+  <si>
+    <t>PEREZ RUBEN -LA CLARITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217550</t>
+  </si>
+  <si>
+    <t>BA41</t>
+  </si>
+  <si>
+    <t>BALCARCE 54 S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217551</t>
+  </si>
+  <si>
+    <t>SM19</t>
+  </si>
+  <si>
+    <t>STRINGHETTI MATERIALES SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217553</t>
+  </si>
+  <si>
+    <t>DR14</t>
+  </si>
+  <si>
+    <t>DREC SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217558</t>
+  </si>
+  <si>
+    <t>CI15</t>
+  </si>
+  <si>
+    <t>CISILOTTO HNOS SACIFEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217561</t>
+  </si>
+  <si>
+    <t>SC33</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAMPANA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217562</t>
+  </si>
+  <si>
+    <t>LP11</t>
+  </si>
+  <si>
+    <t>SANITARIOS LA PRIMERA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217564</t>
+  </si>
+  <si>
+    <t>CO14</t>
+  </si>
+  <si>
+    <t>CASANO OSVALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217567</t>
+  </si>
+  <si>
+    <t>MA37</t>
+  </si>
+  <si>
+    <t>MARCHISONE S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217569</t>
+  </si>
+  <si>
+    <t>RC10</t>
+  </si>
+  <si>
+    <t>RAN CO MATERIALES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217571</t>
+  </si>
+  <si>
+    <t>SC38</t>
+  </si>
+  <si>
+    <t>SANITARIOS CORTESE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217572</t>
+  </si>
+  <si>
+    <t>AA24</t>
+  </si>
+  <si>
+    <t>ANDREONE ANDREA F.-ELECTROMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217583</t>
+  </si>
+  <si>
+    <t>CV16</t>
+  </si>
+  <si>
+    <t>CLERICO VICTORY NANNI SILVIA S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217584</t>
+  </si>
+  <si>
+    <t>SA40</t>
+  </si>
+  <si>
+    <t>SANICENTRO S.A. SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217589</t>
+  </si>
+  <si>
+    <t>CC59</t>
+  </si>
+  <si>
+    <t>CLACE CDC S. A.-CLACE REVESTIMIENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217592</t>
+  </si>
+  <si>
+    <t>ES13</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217593</t>
+  </si>
+  <si>
+    <t>TS10</t>
+  </si>
+  <si>
+    <t>TOTAL 25 SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217596</t>
+  </si>
+  <si>
+    <t>SU09</t>
+  </si>
+  <si>
+    <t>SUPERMAT CENTRAL S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217597</t>
+  </si>
+  <si>
+    <t>CS40</t>
+  </si>
+  <si>
+    <t>CORDA SANITARIOS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217604</t>
+  </si>
+  <si>
+    <t>AL24</t>
+  </si>
+  <si>
+    <t>ALVARENGA VILLAR LUIS F.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217606</t>
+  </si>
+  <si>
+    <t>DU04</t>
+  </si>
+  <si>
+    <t>DURANTE HNOS S R L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217607</t>
+  </si>
+  <si>
+    <t>SA66</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAÑUELAS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217608</t>
+  </si>
+  <si>
+    <t>VN02</t>
+  </si>
+  <si>
+    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217609</t>
+  </si>
+  <si>
+    <t>UG01</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217610</t>
+  </si>
+  <si>
+    <t>SA60</t>
+  </si>
+  <si>
+    <t>SANTAGAL S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217618</t>
+  </si>
+  <si>
+    <t>CR23</t>
+  </si>
+  <si>
+    <t>CRETA PORCELLANATOS S.A. -CRETA DISEGNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217621</t>
+  </si>
+  <si>
+    <t>SA72</t>
+  </si>
+  <si>
+    <t>SANI 3 S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217627</t>
+  </si>
+  <si>
+    <t>NS01</t>
+  </si>
+  <si>
+    <t>NUEVO SUR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217630</t>
+  </si>
+  <si>
+    <t>AM04</t>
+  </si>
+  <si>
+    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217632</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     112</t>
+  </si>
+  <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  177122</t>
+  </si>
+  <si>
+    <t>CS52</t>
+  </si>
+  <si>
+    <t>CONSTRUCTORA SUDAMERICANA ING Y CONST SA</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2667</t>
   </si>
   <si>
     <t>GS10</t>
@@ -1570,49 +2062,31 @@
     <t>GOMEZ SILVIA P Y BARBIERI DANIEL SH -SANIT. ZABALA</t>
   </si>
   <si>
-    <t xml:space="preserve">  217514</t>
-  </si>
-  <si>
-    <t>LN02</t>
-  </si>
-  <si>
-    <t>LA NORIA REVESIMIENTOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217515</t>
-  </si>
-  <si>
-    <t>CP31</t>
-  </si>
-  <si>
-    <t>CASAPAULINO SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217516</t>
-  </si>
-  <si>
-    <t>FM21</t>
-  </si>
-  <si>
-    <t>FIUMANI MATIAS EZEQUIEL - SANITARIOS MARQUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217518</t>
-  </si>
-  <si>
-    <t>FE26</t>
-  </si>
-  <si>
-    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217520</t>
+    <t xml:space="preserve">    2817</t>
+  </si>
+  <si>
+    <t>PE15</t>
+  </si>
+  <si>
+    <t>PITA EPPER NICOLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3002</t>
+  </si>
+  <si>
+    <t>DA11</t>
+  </si>
+  <si>
+    <t>DAFYS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3006</t>
   </si>
   <si>
     <t>CO28</t>
@@ -1621,588 +2095,6 @@
     <t>CONSTRUDISENO S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217521</t>
-  </si>
-  <si>
-    <t>GE12</t>
-  </si>
-  <si>
-    <t>GERMANO S.R.L. -GERMANO MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217522</t>
-  </si>
-  <si>
-    <t>FG17</t>
-  </si>
-  <si>
-    <t>FERNANDEZ GONZALO M.-SANITARIOS FERNANDEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217524</t>
-  </si>
-  <si>
-    <t>MA31</t>
-  </si>
-  <si>
-    <t>MATRIGAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217527</t>
-  </si>
-  <si>
-    <t>BN08</t>
-  </si>
-  <si>
-    <t>BONINO NORBERTO DANIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217538</t>
-  </si>
-  <si>
-    <t>DC16</t>
-  </si>
-  <si>
-    <t>DISEÑO Y CONSTRUCCION LEO SRL -CASA LEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217540</t>
-  </si>
-  <si>
-    <t>TF05</t>
-  </si>
-  <si>
-    <t>TORRES FLAVIO GONZALEZ - BATH AND COMPANY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217541</t>
-  </si>
-  <si>
-    <t>SM26</t>
-  </si>
-  <si>
-    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217543</t>
-  </si>
-  <si>
-    <t>ED04</t>
-  </si>
-  <si>
-    <t>EDIFICOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217544</t>
-  </si>
-  <si>
-    <t>VA09</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO VEGA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217545</t>
-  </si>
-  <si>
-    <t>DA28</t>
-  </si>
-  <si>
-    <t>DAPESOL S.A. -MATERIALES ACON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217546</t>
-  </si>
-  <si>
-    <t>MM39</t>
-  </si>
-  <si>
-    <t>MIGUEL MUKDISE HNOS SRL  -CORRALON MUKDISE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217549</t>
-  </si>
-  <si>
-    <t>PR22</t>
-  </si>
-  <si>
-    <t>PEREZ RUBEN -LA CLARITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217550</t>
-  </si>
-  <si>
-    <t>BA41</t>
-  </si>
-  <si>
-    <t>BALCARCE 54 S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217551</t>
-  </si>
-  <si>
-    <t>SM19</t>
-  </si>
-  <si>
-    <t>STRINGHETTI MATERIALES SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217553</t>
-  </si>
-  <si>
-    <t>DR14</t>
-  </si>
-  <si>
-    <t>DREC SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217558</t>
-  </si>
-  <si>
-    <t>CI15</t>
-  </si>
-  <si>
-    <t>CISILOTTO HNOS SACIFEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217561</t>
-  </si>
-  <si>
-    <t>SC33</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217562</t>
-  </si>
-  <si>
-    <t>LP11</t>
-  </si>
-  <si>
-    <t>SANITARIOS LA PRIMERA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217564</t>
-  </si>
-  <si>
-    <t>CO14</t>
-  </si>
-  <si>
-    <t>CASANO OSVALDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217567</t>
-  </si>
-  <si>
-    <t>MA37</t>
-  </si>
-  <si>
-    <t>MARCHISONE S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217569</t>
-  </si>
-  <si>
-    <t>RC10</t>
-  </si>
-  <si>
-    <t>RAN CO MATERIALES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217571</t>
-  </si>
-  <si>
-    <t>SC38</t>
-  </si>
-  <si>
-    <t>SANITARIOS CORTESE SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217572</t>
-  </si>
-  <si>
-    <t>AA24</t>
-  </si>
-  <si>
-    <t>ANDREONE ANDREA F.-ELECTROMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217583</t>
-  </si>
-  <si>
-    <t>CV16</t>
-  </si>
-  <si>
-    <t>CLERICO VICTORY NANNI SILVIA S.H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217584</t>
-  </si>
-  <si>
-    <t>SA40</t>
-  </si>
-  <si>
-    <t>SANICENTRO S.A. SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217589</t>
-  </si>
-  <si>
-    <t>CC59</t>
-  </si>
-  <si>
-    <t>CLACE CDC S. A.-CLACE REVESTIMIENTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217590</t>
-  </si>
-  <si>
-    <t>VA12</t>
-  </si>
-  <si>
-    <t>VALEANT S.R.L.-SANITARIOS TITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217592</t>
-  </si>
-  <si>
-    <t>ES13</t>
-  </si>
-  <si>
-    <t>EDEN SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217593</t>
-  </si>
-  <si>
-    <t>TS10</t>
-  </si>
-  <si>
-    <t>TOTAL 25 SANITARIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217596</t>
-  </si>
-  <si>
-    <t>SU09</t>
-  </si>
-  <si>
-    <t>SUPERMAT CENTRAL S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217597</t>
-  </si>
-  <si>
-    <t>CS40</t>
-  </si>
-  <si>
-    <t>CORDA SANITARIOS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217604</t>
-  </si>
-  <si>
-    <t>AL24</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217606</t>
-  </si>
-  <si>
-    <t>DU04</t>
-  </si>
-  <si>
-    <t>DURANTE HNOS S R L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217607</t>
-  </si>
-  <si>
-    <t>SA66</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAÑUELAS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217608</t>
-  </si>
-  <si>
-    <t>VN02</t>
-  </si>
-  <si>
-    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217609</t>
-  </si>
-  <si>
-    <t>UG01</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217610</t>
-  </si>
-  <si>
-    <t>SA60</t>
-  </si>
-  <si>
-    <t>SANTAGAL S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217618</t>
-  </si>
-  <si>
-    <t>CR23</t>
-  </si>
-  <si>
-    <t>CRETA PORCELLANATOS S.A. -CRETA DISEGNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217621</t>
-  </si>
-  <si>
-    <t>SA72</t>
-  </si>
-  <si>
-    <t>SANI 3 S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217622</t>
-  </si>
-  <si>
-    <t>0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     112</t>
-  </si>
-  <si>
-    <t>0007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  177122</t>
-  </si>
-  <si>
-    <t>CS52</t>
-  </si>
-  <si>
-    <t>CONSTRUCTORA SUDAMERICANA ING Y CONST SA</t>
-  </si>
-  <si>
-    <t>0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2817</t>
-  </si>
-  <si>
-    <t>PE15</t>
-  </si>
-  <si>
-    <t>PITA EPPER NICOLAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3002</t>
-  </si>
-  <si>
-    <t>DA11</t>
-  </si>
-  <si>
-    <t>DAFYS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3006</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3011</t>
   </si>
   <si>
@@ -2242,6 +2134,9 @@
     <t xml:space="preserve">    3034</t>
   </si>
   <si>
+    <t xml:space="preserve">    3035</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2375,9 +2270,6 @@
   </si>
   <si>
     <t xml:space="preserve">      98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     121</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2851,34 +2743,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9032D8E5-B07D-4663-A3BB-4CC486603122}">
-  <dimension ref="A1:H410"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D0BF34-BF14-45BA-9591-BD058A89B890}">
+  <dimension ref="A1:H392"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>787</v>
+        <v>751</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>788</v>
+        <v>752</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>789</v>
+        <v>753</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>790</v>
+        <v>754</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>792</v>
+        <v>756</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>793</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6740,7 +6632,7 @@
         <v>3</v>
       </c>
       <c r="D150" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E150" t="s">
         <v>331</v>
@@ -7624,7 +7516,7 @@
         <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
         <v>385</v>
@@ -8407,10 +8299,10 @@
         <v>128</v>
       </c>
       <c r="E214" t="s">
-        <v>447</v>
+        <v>95</v>
       </c>
       <c r="F214" t="s">
-        <v>448</v>
+        <v>96</v>
       </c>
       <c r="G214" s="1">
         <v>46308</v>
@@ -8424,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -8433,10 +8325,10 @@
         <v>128</v>
       </c>
       <c r="E215" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="F215" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="G215" s="1">
         <v>46308</v>
@@ -8450,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8459,16 +8351,16 @@
         <v>128</v>
       </c>
       <c r="E216" t="s">
-        <v>172</v>
+        <v>395</v>
       </c>
       <c r="F216" t="s">
-        <v>173</v>
+        <v>396</v>
       </c>
       <c r="G216" s="1">
         <v>46308</v>
       </c>
       <c r="H216" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -8476,25 +8368,25 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E217" t="s">
-        <v>57</v>
+        <v>395</v>
       </c>
       <c r="F217" t="s">
-        <v>58</v>
+        <v>396</v>
       </c>
       <c r="G217" s="1">
         <v>46308</v>
       </c>
       <c r="H217" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -8502,19 +8394,19 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
+        <v>450</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="s">
+        <v>128</v>
+      </c>
+      <c r="E218" t="s">
+        <v>451</v>
+      </c>
+      <c r="F218" t="s">
         <v>452</v>
-      </c>
-      <c r="C218">
-        <v>1</v>
-      </c>
-      <c r="D218" t="s">
-        <v>128</v>
-      </c>
-      <c r="E218" t="s">
-        <v>395</v>
-      </c>
-      <c r="F218" t="s">
-        <v>396</v>
       </c>
       <c r="G218" s="1">
         <v>46308</v>
@@ -8537,10 +8429,10 @@
         <v>128</v>
       </c>
       <c r="E219" t="s">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="F219" t="s">
-        <v>396</v>
+        <v>455</v>
       </c>
       <c r="G219" s="1">
         <v>46308</v>
@@ -8554,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -8563,10 +8455,10 @@
         <v>128</v>
       </c>
       <c r="E220" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F220" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G220" s="1">
         <v>46308</v>
@@ -8580,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8589,10 +8481,10 @@
         <v>128</v>
       </c>
       <c r="E221" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F221" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G221" s="1">
         <v>46308</v>
@@ -8606,22 +8498,22 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E222" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F222" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G222" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H222" s="1">
         <v>46309</v>
@@ -8632,22 +8524,22 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F223" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G223" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H223" s="1">
         <v>46309</v>
@@ -8658,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8667,13 +8559,13 @@
         <v>128</v>
       </c>
       <c r="E224" t="s">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="F224" t="s">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="G224" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H224" s="1">
         <v>46309</v>
@@ -8693,10 +8585,10 @@
         <v>128</v>
       </c>
       <c r="E225" t="s">
-        <v>470</v>
+        <v>406</v>
       </c>
       <c r="F225" t="s">
-        <v>471</v>
+        <v>407</v>
       </c>
       <c r="G225" s="1">
         <v>46309</v>
@@ -8710,19 +8602,19 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
+        <v>470</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>2</v>
+      </c>
+      <c r="E226" t="s">
+        <v>471</v>
+      </c>
+      <c r="F226" t="s">
         <v>472</v>
-      </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-      <c r="D226" t="s">
-        <v>2</v>
-      </c>
-      <c r="E226" t="s">
-        <v>473</v>
-      </c>
-      <c r="F226" t="s">
-        <v>474</v>
       </c>
       <c r="G226" s="1">
         <v>46309</v>
@@ -8736,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8745,10 +8637,10 @@
         <v>128</v>
       </c>
       <c r="E227" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F227" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G227" s="1">
         <v>46309</v>
@@ -8762,19 +8654,19 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E228" t="s">
-        <v>477</v>
+        <v>37</v>
       </c>
       <c r="F228" t="s">
-        <v>478</v>
+        <v>38</v>
       </c>
       <c r="G228" s="1">
         <v>46309</v>
@@ -8788,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -8797,10 +8689,10 @@
         <v>128</v>
       </c>
       <c r="E229" t="s">
-        <v>406</v>
+        <v>37</v>
       </c>
       <c r="F229" t="s">
-        <v>407</v>
+        <v>38</v>
       </c>
       <c r="G229" s="1">
         <v>46309</v>
@@ -8814,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8823,10 +8715,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>481</v>
+        <v>37</v>
       </c>
       <c r="F230" t="s">
-        <v>482</v>
+        <v>38</v>
       </c>
       <c r="G230" s="1">
         <v>46309</v>
@@ -8840,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8866,25 +8758,25 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="s">
         <v>128</v>
       </c>
       <c r="E232" t="s">
-        <v>37</v>
+        <v>479</v>
       </c>
       <c r="F232" t="s">
-        <v>38</v>
+        <v>480</v>
       </c>
       <c r="G232" s="1">
         <v>46309</v>
       </c>
       <c r="H232" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -8892,25 +8784,25 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233" t="s">
         <v>128</v>
       </c>
       <c r="E233" t="s">
-        <v>37</v>
+        <v>479</v>
       </c>
       <c r="F233" t="s">
-        <v>38</v>
+        <v>480</v>
       </c>
       <c r="G233" s="1">
         <v>46309</v>
       </c>
       <c r="H233" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8918,25 +8810,25 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>479</v>
       </c>
       <c r="F234" t="s">
-        <v>38</v>
+        <v>480</v>
       </c>
       <c r="G234" s="1">
         <v>46309</v>
       </c>
       <c r="H234" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -8944,19 +8836,19 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>484</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>485</v>
       </c>
       <c r="G235" s="1">
         <v>46309</v>
@@ -8970,25 +8862,25 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
+        <v>486</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="s">
+        <v>2</v>
+      </c>
+      <c r="E236" t="s">
+        <v>487</v>
+      </c>
+      <c r="F236" t="s">
         <v>488</v>
-      </c>
-      <c r="C236">
-        <v>2</v>
-      </c>
-      <c r="D236" t="s">
-        <v>128</v>
-      </c>
-      <c r="E236" t="s">
-        <v>489</v>
-      </c>
-      <c r="F236" t="s">
-        <v>490</v>
       </c>
       <c r="G236" s="1">
         <v>46309</v>
       </c>
       <c r="H236" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -8996,25 +8888,25 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
         <v>128</v>
       </c>
       <c r="E237" t="s">
-        <v>489</v>
+        <v>285</v>
       </c>
       <c r="F237" t="s">
-        <v>490</v>
+        <v>286</v>
       </c>
       <c r="G237" s="1">
         <v>46309</v>
       </c>
       <c r="H237" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -9022,25 +8914,25 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
+        <v>490</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238" t="s">
+        <v>128</v>
+      </c>
+      <c r="E238" t="s">
+        <v>491</v>
+      </c>
+      <c r="F238" t="s">
         <v>492</v>
-      </c>
-      <c r="C238">
-        <v>2</v>
-      </c>
-      <c r="D238" t="s">
-        <v>128</v>
-      </c>
-      <c r="E238" t="s">
-        <v>489</v>
-      </c>
-      <c r="F238" t="s">
-        <v>490</v>
       </c>
       <c r="G238" s="1">
         <v>46309</v>
       </c>
       <c r="H238" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -9054,13 +8946,13 @@
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E239" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F239" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G239" s="1">
         <v>46309</v>
@@ -9074,19 +8966,19 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E240" t="s">
-        <v>497</v>
+        <v>86</v>
       </c>
       <c r="F240" t="s">
-        <v>498</v>
+        <v>87</v>
       </c>
       <c r="G240" s="1">
         <v>46309</v>
@@ -9100,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9109,10 +9001,10 @@
         <v>128</v>
       </c>
       <c r="E241" t="s">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="F241" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="G241" s="1">
         <v>46309</v>
@@ -9126,7 +9018,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9135,10 +9027,10 @@
         <v>128</v>
       </c>
       <c r="E242" t="s">
-        <v>501</v>
+        <v>86</v>
       </c>
       <c r="F242" t="s">
-        <v>502</v>
+        <v>87</v>
       </c>
       <c r="G242" s="1">
         <v>46309</v>
@@ -9152,19 +9044,19 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E243" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F243" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G243" s="1">
         <v>46309</v>
@@ -9178,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9187,10 +9079,10 @@
         <v>128</v>
       </c>
       <c r="E244" t="s">
-        <v>86</v>
+        <v>501</v>
       </c>
       <c r="F244" t="s">
-        <v>87</v>
+        <v>502</v>
       </c>
       <c r="G244" s="1">
         <v>46309</v>
@@ -9204,19 +9096,19 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
+        <v>503</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245" t="s">
+        <v>128</v>
+      </c>
+      <c r="E245" t="s">
+        <v>504</v>
+      </c>
+      <c r="F245" t="s">
         <v>505</v>
-      </c>
-      <c r="C245">
-        <v>1</v>
-      </c>
-      <c r="D245" t="s">
-        <v>128</v>
-      </c>
-      <c r="E245" t="s">
-        <v>86</v>
-      </c>
-      <c r="F245" t="s">
-        <v>87</v>
       </c>
       <c r="G245" s="1">
         <v>46309</v>
@@ -9239,10 +9131,10 @@
         <v>128</v>
       </c>
       <c r="E246" t="s">
-        <v>86</v>
+        <v>507</v>
       </c>
       <c r="F246" t="s">
-        <v>87</v>
+        <v>508</v>
       </c>
       <c r="G246" s="1">
         <v>46309</v>
@@ -9256,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9265,10 +9157,10 @@
         <v>128</v>
       </c>
       <c r="E247" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="F247" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="G247" s="1">
         <v>46309</v>
@@ -9288,13 +9180,13 @@
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>358</v>
+        <v>511</v>
       </c>
       <c r="F248" t="s">
-        <v>359</v>
+        <v>512</v>
       </c>
       <c r="G248" s="1">
         <v>46309</v>
@@ -9308,19 +9200,19 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E249" t="s">
-        <v>358</v>
+        <v>219</v>
       </c>
       <c r="F249" t="s">
-        <v>359</v>
+        <v>220</v>
       </c>
       <c r="G249" s="1">
         <v>46309</v>
@@ -9334,19 +9226,19 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E250" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="F250" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="G250" s="1">
         <v>46309</v>
@@ -9360,19 +9252,19 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E251" t="s">
-        <v>514</v>
+        <v>202</v>
       </c>
       <c r="F251" t="s">
-        <v>515</v>
+        <v>203</v>
       </c>
       <c r="G251" s="1">
         <v>46309</v>
@@ -9392,13 +9284,13 @@
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E252" t="s">
-        <v>517</v>
+        <v>202</v>
       </c>
       <c r="F252" t="s">
-        <v>518</v>
+        <v>203</v>
       </c>
       <c r="G252" s="1">
         <v>46309</v>
@@ -9412,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9421,10 +9313,10 @@
         <v>128</v>
       </c>
       <c r="E253" t="s">
-        <v>520</v>
+        <v>202</v>
       </c>
       <c r="F253" t="s">
-        <v>521</v>
+        <v>203</v>
       </c>
       <c r="G253" s="1">
         <v>46309</v>
@@ -9438,19 +9330,19 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E254" t="s">
-        <v>523</v>
+        <v>68</v>
       </c>
       <c r="F254" t="s">
-        <v>524</v>
+        <v>69</v>
       </c>
       <c r="G254" s="1">
         <v>46309</v>
@@ -9464,25 +9356,25 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E255" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
       <c r="F255" t="s">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="G255" s="1">
         <v>46309</v>
       </c>
       <c r="H255" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -9490,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9499,10 +9391,10 @@
         <v>128</v>
       </c>
       <c r="E256" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F256" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="G256" s="1">
         <v>46309</v>
@@ -9516,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9525,16 +9417,16 @@
         <v>128</v>
       </c>
       <c r="E257" t="s">
-        <v>134</v>
+        <v>463</v>
       </c>
       <c r="F257" t="s">
-        <v>135</v>
+        <v>464</v>
       </c>
       <c r="G257" s="1">
         <v>46309</v>
       </c>
       <c r="H257" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -9542,19 +9434,19 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E258" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F258" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="G258" s="1">
         <v>46309</v>
@@ -9568,19 +9460,19 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E259" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F259" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G259" s="1">
         <v>46309</v>
@@ -9594,19 +9486,19 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E260" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="F260" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="G260" s="1">
         <v>46309</v>
@@ -9620,19 +9512,19 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>540</v>
+        <v>92</v>
       </c>
       <c r="F261" t="s">
-        <v>541</v>
+        <v>93</v>
       </c>
       <c r="G261" s="1">
         <v>46309</v>
@@ -9646,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9655,16 +9547,16 @@
         <v>128</v>
       </c>
       <c r="E262" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="F262" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G262" s="1">
         <v>46309</v>
       </c>
       <c r="H262" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -9672,25 +9564,25 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E263" t="s">
-        <v>146</v>
+        <v>538</v>
       </c>
       <c r="F263" t="s">
-        <v>147</v>
+        <v>539</v>
       </c>
       <c r="G263" s="1">
         <v>46309</v>
       </c>
       <c r="H263" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
@@ -9698,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9707,16 +9599,16 @@
         <v>128</v>
       </c>
       <c r="E264" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F264" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G264" s="1">
         <v>46309</v>
       </c>
       <c r="H264" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -9724,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9733,16 +9625,16 @@
         <v>128</v>
       </c>
       <c r="E265" t="s">
-        <v>219</v>
+        <v>409</v>
       </c>
       <c r="F265" t="s">
-        <v>220</v>
+        <v>410</v>
       </c>
       <c r="G265" s="1">
         <v>46309</v>
       </c>
       <c r="H265" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -9750,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9759,16 +9651,16 @@
         <v>128</v>
       </c>
       <c r="E266" t="s">
-        <v>344</v>
+        <v>545</v>
       </c>
       <c r="F266" t="s">
-        <v>345</v>
+        <v>546</v>
       </c>
       <c r="G266" s="1">
         <v>46309</v>
       </c>
       <c r="H266" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -9776,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9785,16 +9677,16 @@
         <v>128</v>
       </c>
       <c r="E267" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="F267" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="G267" s="1">
         <v>46309</v>
       </c>
       <c r="H267" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -9802,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9811,16 +9703,16 @@
         <v>128</v>
       </c>
       <c r="E268" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="F268" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="G268" s="1">
         <v>46309</v>
       </c>
       <c r="H268" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -9828,25 +9720,25 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
+        <v>549</v>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+      <c r="D269" t="s">
+        <v>128</v>
+      </c>
+      <c r="E269" t="s">
+        <v>550</v>
+      </c>
+      <c r="F269" t="s">
         <v>551</v>
-      </c>
-      <c r="C269">
-        <v>1</v>
-      </c>
-      <c r="D269" t="s">
-        <v>128</v>
-      </c>
-      <c r="E269" t="s">
-        <v>202</v>
-      </c>
-      <c r="F269" t="s">
-        <v>203</v>
       </c>
       <c r="G269" s="1">
         <v>46309</v>
       </c>
       <c r="H269" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
@@ -9860,19 +9752,19 @@
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E270" t="s">
-        <v>16</v>
+        <v>550</v>
       </c>
       <c r="F270" t="s">
-        <v>17</v>
+        <v>551</v>
       </c>
       <c r="G270" s="1">
         <v>46309</v>
       </c>
       <c r="H270" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -9889,16 +9781,16 @@
         <v>2</v>
       </c>
       <c r="E271" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="F271" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G271" s="1">
         <v>46309</v>
       </c>
       <c r="H271" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
@@ -9912,19 +9804,19 @@
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E272" t="s">
-        <v>358</v>
+        <v>555</v>
       </c>
       <c r="F272" t="s">
-        <v>359</v>
+        <v>556</v>
       </c>
       <c r="G272" s="1">
         <v>46309</v>
       </c>
       <c r="H272" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
@@ -9932,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9941,16 +9833,16 @@
         <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>68</v>
+        <v>558</v>
       </c>
       <c r="F273" t="s">
-        <v>69</v>
+        <v>559</v>
       </c>
       <c r="G273" s="1">
         <v>46309</v>
       </c>
       <c r="H273" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
@@ -9958,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -9967,10 +9859,10 @@
         <v>128</v>
       </c>
       <c r="E274" t="s">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="F274" t="s">
-        <v>173</v>
+        <v>345</v>
       </c>
       <c r="G274" s="1">
         <v>46309</v>
@@ -9984,25 +9876,25 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E275" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F275" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G275" s="1">
         <v>46309</v>
       </c>
       <c r="H275" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
@@ -10010,25 +9902,25 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E276" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F276" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G276" s="1">
         <v>46309</v>
       </c>
       <c r="H276" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
@@ -10036,25 +9928,25 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E277" t="s">
-        <v>562</v>
+        <v>152</v>
       </c>
       <c r="F277" t="s">
-        <v>563</v>
+        <v>153</v>
       </c>
       <c r="G277" s="1">
         <v>46309</v>
       </c>
       <c r="H277" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
@@ -10062,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -10071,16 +9963,16 @@
         <v>128</v>
       </c>
       <c r="E278" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F278" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G278" s="1">
         <v>46309</v>
       </c>
       <c r="H278" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -10088,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -10097,10 +9989,10 @@
         <v>128</v>
       </c>
       <c r="E279" t="s">
-        <v>470</v>
+        <v>570</v>
       </c>
       <c r="F279" t="s">
-        <v>471</v>
+        <v>571</v>
       </c>
       <c r="G279" s="1">
         <v>46309</v>
@@ -10114,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -10123,16 +10015,16 @@
         <v>128</v>
       </c>
       <c r="E280" t="s">
-        <v>569</v>
+        <v>463</v>
       </c>
       <c r="F280" t="s">
-        <v>570</v>
+        <v>464</v>
       </c>
       <c r="G280" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H280" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -10140,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10149,16 +10041,16 @@
         <v>128</v>
       </c>
       <c r="E281" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F281" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G281" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H281" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
@@ -10166,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -10175,16 +10067,16 @@
         <v>128</v>
       </c>
       <c r="E282" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F282" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G282" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H282" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
@@ -10192,25 +10084,25 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E283" t="s">
-        <v>578</v>
+        <v>37</v>
       </c>
       <c r="F283" t="s">
-        <v>579</v>
+        <v>38</v>
       </c>
       <c r="G283" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H283" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
@@ -10227,16 +10119,16 @@
         <v>128</v>
       </c>
       <c r="E284" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="F284" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G284" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H284" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
@@ -10250,19 +10142,19 @@
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E285" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F285" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G285" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H285" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
@@ -10279,13 +10171,13 @@
         <v>128</v>
       </c>
       <c r="E286" t="s">
-        <v>583</v>
+        <v>37</v>
       </c>
       <c r="F286" t="s">
-        <v>584</v>
+        <v>38</v>
       </c>
       <c r="G286" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H286" s="1">
         <v>46310</v>
@@ -10296,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -10305,13 +10197,13 @@
         <v>128</v>
       </c>
       <c r="E287" t="s">
-        <v>586</v>
+        <v>37</v>
       </c>
       <c r="F287" t="s">
-        <v>587</v>
+        <v>38</v>
       </c>
       <c r="G287" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H287" s="1">
         <v>46310</v>
@@ -10322,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10331,13 +10223,13 @@
         <v>128</v>
       </c>
       <c r="E288" t="s">
-        <v>589</v>
+        <v>37</v>
       </c>
       <c r="F288" t="s">
-        <v>590</v>
+        <v>38</v>
       </c>
       <c r="G288" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H288" s="1">
         <v>46310</v>
@@ -10348,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10357,13 +10249,13 @@
         <v>128</v>
       </c>
       <c r="E289" t="s">
-        <v>409</v>
+        <v>37</v>
       </c>
       <c r="F289" t="s">
-        <v>410</v>
+        <v>38</v>
       </c>
       <c r="G289" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H289" s="1">
         <v>46310</v>
@@ -10374,7 +10266,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10383,13 +10275,13 @@
         <v>128</v>
       </c>
       <c r="E290" t="s">
-        <v>593</v>
+        <v>37</v>
       </c>
       <c r="F290" t="s">
-        <v>594</v>
+        <v>38</v>
       </c>
       <c r="G290" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H290" s="1">
         <v>46310</v>
@@ -10400,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -10409,13 +10301,13 @@
         <v>128</v>
       </c>
       <c r="E291" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F291" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G291" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H291" s="1">
         <v>46310</v>
@@ -10426,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -10435,13 +10327,13 @@
         <v>128</v>
       </c>
       <c r="E292" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F292" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G292" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H292" s="1">
         <v>46310</v>
@@ -10452,22 +10344,22 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E293" t="s">
-        <v>143</v>
+        <v>590</v>
       </c>
       <c r="F293" t="s">
-        <v>144</v>
+        <v>591</v>
       </c>
       <c r="G293" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H293" s="1">
         <v>46310</v>
@@ -10478,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10487,13 +10379,13 @@
         <v>128</v>
       </c>
       <c r="E294" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F294" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="G294" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H294" s="1">
         <v>46310</v>
@@ -10504,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10513,13 +10405,13 @@
         <v>128</v>
       </c>
       <c r="E295" t="s">
-        <v>599</v>
+        <v>252</v>
       </c>
       <c r="F295" t="s">
-        <v>600</v>
+        <v>253</v>
       </c>
       <c r="G295" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H295" s="1">
         <v>46310</v>
@@ -10530,22 +10422,22 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E296" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F296" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G296" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H296" s="1">
         <v>46310</v>
@@ -10556,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10565,13 +10457,13 @@
         <v>128</v>
       </c>
       <c r="E297" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="F297" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="G297" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H297" s="1">
         <v>46310</v>
@@ -10582,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -10591,13 +10483,13 @@
         <v>128</v>
       </c>
       <c r="E298" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="F298" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="G298" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H298" s="1">
         <v>46310</v>
@@ -10608,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10617,13 +10509,13 @@
         <v>128</v>
       </c>
       <c r="E299" t="s">
-        <v>344</v>
+        <v>604</v>
       </c>
       <c r="F299" t="s">
-        <v>345</v>
+        <v>605</v>
       </c>
       <c r="G299" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H299" s="1">
         <v>46310</v>
@@ -10634,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10643,13 +10535,13 @@
         <v>128</v>
       </c>
       <c r="E300" t="s">
-        <v>611</v>
+        <v>237</v>
       </c>
       <c r="F300" t="s">
-        <v>612</v>
+        <v>238</v>
       </c>
       <c r="G300" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H300" s="1">
         <v>46310</v>
@@ -10660,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10669,13 +10561,13 @@
         <v>128</v>
       </c>
       <c r="E301" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="F301" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="G301" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H301" s="1">
         <v>46310</v>
@@ -10686,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -10695,13 +10587,13 @@
         <v>128</v>
       </c>
       <c r="E302" t="s">
-        <v>152</v>
+        <v>609</v>
       </c>
       <c r="F302" t="s">
-        <v>153</v>
+        <v>610</v>
       </c>
       <c r="G302" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H302" s="1">
         <v>46310</v>
@@ -10712,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10721,13 +10613,13 @@
         <v>128</v>
       </c>
       <c r="E303" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F303" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G303" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H303" s="1">
         <v>46310</v>
@@ -10738,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10747,13 +10639,13 @@
         <v>128</v>
       </c>
       <c r="E304" t="s">
-        <v>619</v>
+        <v>16</v>
       </c>
       <c r="F304" t="s">
-        <v>620</v>
+        <v>17</v>
       </c>
       <c r="G304" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H304" s="1">
         <v>46310</v>
@@ -10764,19 +10656,19 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305" t="s">
         <v>128</v>
       </c>
       <c r="E305" t="s">
-        <v>470</v>
+        <v>16</v>
       </c>
       <c r="F305" t="s">
-        <v>471</v>
+        <v>17</v>
       </c>
       <c r="G305" s="1">
         <v>46310</v>
@@ -10790,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10799,10 +10691,10 @@
         <v>128</v>
       </c>
       <c r="E306" t="s">
-        <v>623</v>
+        <v>16</v>
       </c>
       <c r="F306" t="s">
-        <v>624</v>
+        <v>17</v>
       </c>
       <c r="G306" s="1">
         <v>46310</v>
@@ -10816,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10825,10 +10717,10 @@
         <v>128</v>
       </c>
       <c r="E307" t="s">
-        <v>626</v>
+        <v>385</v>
       </c>
       <c r="F307" t="s">
-        <v>627</v>
+        <v>386</v>
       </c>
       <c r="G307" s="1">
         <v>46310</v>
@@ -10842,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -10851,10 +10743,10 @@
         <v>128</v>
       </c>
       <c r="E308" t="s">
-        <v>37</v>
+        <v>555</v>
       </c>
       <c r="F308" t="s">
-        <v>38</v>
+        <v>556</v>
       </c>
       <c r="G308" s="1">
         <v>46310</v>
@@ -10868,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10877,10 +10769,10 @@
         <v>128</v>
       </c>
       <c r="E309" t="s">
-        <v>37</v>
+        <v>620</v>
       </c>
       <c r="F309" t="s">
-        <v>38</v>
+        <v>621</v>
       </c>
       <c r="G309" s="1">
         <v>46310</v>
@@ -10894,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -10903,10 +10795,10 @@
         <v>128</v>
       </c>
       <c r="E310" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F310" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G310" s="1">
         <v>46310</v>
@@ -10920,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -10929,10 +10821,10 @@
         <v>128</v>
       </c>
       <c r="E311" t="s">
-        <v>37</v>
+        <v>624</v>
       </c>
       <c r="F311" t="s">
-        <v>38</v>
+        <v>625</v>
       </c>
       <c r="G311" s="1">
         <v>46310</v>
@@ -10946,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10955,10 +10847,10 @@
         <v>128</v>
       </c>
       <c r="E312" t="s">
-        <v>37</v>
+        <v>627</v>
       </c>
       <c r="F312" t="s">
-        <v>38</v>
+        <v>628</v>
       </c>
       <c r="G312" s="1">
         <v>46310</v>
@@ -10972,7 +10864,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10981,10 +10873,10 @@
         <v>128</v>
       </c>
       <c r="E313" t="s">
-        <v>37</v>
+        <v>630</v>
       </c>
       <c r="F313" t="s">
-        <v>38</v>
+        <v>631</v>
       </c>
       <c r="G313" s="1">
         <v>46310</v>
@@ -10998,19 +10890,19 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
+        <v>632</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+      <c r="D314" t="s">
+        <v>128</v>
+      </c>
+      <c r="E314" t="s">
+        <v>633</v>
+      </c>
+      <c r="F314" t="s">
         <v>634</v>
-      </c>
-      <c r="C314">
-        <v>1</v>
-      </c>
-      <c r="D314" t="s">
-        <v>128</v>
-      </c>
-      <c r="E314" t="s">
-        <v>37</v>
-      </c>
-      <c r="F314" t="s">
-        <v>38</v>
       </c>
       <c r="G314" s="1">
         <v>46310</v>
@@ -11033,10 +10925,10 @@
         <v>128</v>
       </c>
       <c r="E315" t="s">
-        <v>37</v>
+        <v>636</v>
       </c>
       <c r="F315" t="s">
-        <v>38</v>
+        <v>637</v>
       </c>
       <c r="G315" s="1">
         <v>46310</v>
@@ -11050,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -11059,10 +10951,10 @@
         <v>128</v>
       </c>
       <c r="E316" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F316" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G316" s="1">
         <v>46310</v>
@@ -11076,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -11085,10 +10977,10 @@
         <v>128</v>
       </c>
       <c r="E317" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F317" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G317" s="1">
         <v>46310</v>
@@ -11102,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -11111,10 +11003,10 @@
         <v>128</v>
       </c>
       <c r="E318" t="s">
-        <v>639</v>
+        <v>16</v>
       </c>
       <c r="F318" t="s">
-        <v>640</v>
+        <v>17</v>
       </c>
       <c r="G318" s="1">
         <v>46310</v>
@@ -11137,10 +11029,10 @@
         <v>128</v>
       </c>
       <c r="E319" t="s">
-        <v>642</v>
+        <v>16</v>
       </c>
       <c r="F319" t="s">
-        <v>643</v>
+        <v>17</v>
       </c>
       <c r="G319" s="1">
         <v>46310</v>
@@ -11154,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -11163,10 +11055,10 @@
         <v>128</v>
       </c>
       <c r="E320" t="s">
-        <v>252</v>
+        <v>528</v>
       </c>
       <c r="F320" t="s">
-        <v>253</v>
+        <v>529</v>
       </c>
       <c r="G320" s="1">
         <v>46310</v>
@@ -11180,7 +11072,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -11189,10 +11081,10 @@
         <v>128</v>
       </c>
       <c r="E321" t="s">
-        <v>57</v>
+        <v>463</v>
       </c>
       <c r="F321" t="s">
-        <v>58</v>
+        <v>464</v>
       </c>
       <c r="G321" s="1">
         <v>46310</v>
@@ -11206,19 +11098,19 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
+        <v>644</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322" t="s">
+        <v>128</v>
+      </c>
+      <c r="E322" t="s">
+        <v>645</v>
+      </c>
+      <c r="F322" t="s">
         <v>646</v>
-      </c>
-      <c r="C322">
-        <v>1</v>
-      </c>
-      <c r="D322" t="s">
-        <v>2</v>
-      </c>
-      <c r="E322" t="s">
-        <v>531</v>
-      </c>
-      <c r="F322" t="s">
-        <v>532</v>
       </c>
       <c r="G322" s="1">
         <v>46310</v>
@@ -11241,10 +11133,10 @@
         <v>128</v>
       </c>
       <c r="E323" t="s">
-        <v>648</v>
+        <v>92</v>
       </c>
       <c r="F323" t="s">
-        <v>649</v>
+        <v>93</v>
       </c>
       <c r="G323" s="1">
         <v>46310</v>
@@ -11258,19 +11150,19 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C324">
         <v>1</v>
       </c>
       <c r="D324" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E324" t="s">
-        <v>651</v>
+        <v>122</v>
       </c>
       <c r="F324" t="s">
-        <v>652</v>
+        <v>123</v>
       </c>
       <c r="G324" s="1">
         <v>46310</v>
@@ -11284,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11293,10 +11185,10 @@
         <v>128</v>
       </c>
       <c r="E325" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F325" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G325" s="1">
         <v>46310</v>
@@ -11310,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -11319,10 +11211,10 @@
         <v>128</v>
       </c>
       <c r="E326" t="s">
-        <v>657</v>
+        <v>558</v>
       </c>
       <c r="F326" t="s">
-        <v>658</v>
+        <v>559</v>
       </c>
       <c r="G326" s="1">
         <v>46310</v>
@@ -11336,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -11345,10 +11237,10 @@
         <v>128</v>
       </c>
       <c r="E327" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="F327" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="G327" s="1">
         <v>46310</v>
@@ -11362,7 +11254,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -11371,10 +11263,10 @@
         <v>128</v>
       </c>
       <c r="E328" t="s">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="F328" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="G328" s="1">
         <v>46310</v>
@@ -11388,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11397,10 +11289,10 @@
         <v>128</v>
       </c>
       <c r="E329" t="s">
-        <v>662</v>
+        <v>80</v>
       </c>
       <c r="F329" t="s">
-        <v>663</v>
+        <v>81</v>
       </c>
       <c r="G329" s="1">
         <v>46310</v>
@@ -11414,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -11423,10 +11315,10 @@
         <v>128</v>
       </c>
       <c r="E330" t="s">
-        <v>665</v>
+        <v>16</v>
       </c>
       <c r="F330" t="s">
-        <v>666</v>
+        <v>17</v>
       </c>
       <c r="G330" s="1">
         <v>46310</v>
@@ -11440,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -11449,10 +11341,10 @@
         <v>128</v>
       </c>
       <c r="E331" t="s">
-        <v>16</v>
+        <v>658</v>
       </c>
       <c r="F331" t="s">
-        <v>17</v>
+        <v>659</v>
       </c>
       <c r="G331" s="1">
         <v>46310</v>
@@ -11466,10 +11358,10 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D332" t="s">
         <v>128</v>
@@ -11492,7 +11384,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11501,10 +11393,10 @@
         <v>128</v>
       </c>
       <c r="E333" t="s">
-        <v>16</v>
+        <v>645</v>
       </c>
       <c r="F333" t="s">
-        <v>17</v>
+        <v>646</v>
       </c>
       <c r="G333" s="1">
         <v>46310</v>
@@ -11518,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -11527,10 +11419,10 @@
         <v>128</v>
       </c>
       <c r="E334" t="s">
-        <v>385</v>
+        <v>663</v>
       </c>
       <c r="F334" t="s">
-        <v>386</v>
+        <v>664</v>
       </c>
       <c r="G334" s="1">
         <v>46310</v>
@@ -11544,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -11553,10 +11445,10 @@
         <v>128</v>
       </c>
       <c r="E335" t="s">
-        <v>604</v>
+        <v>398</v>
       </c>
       <c r="F335" t="s">
-        <v>605</v>
+        <v>399</v>
       </c>
       <c r="G335" s="1">
         <v>46310</v>
@@ -11567,62 +11459,62 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="B336" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E336" t="s">
-        <v>673</v>
+        <v>160</v>
       </c>
       <c r="F336" t="s">
-        <v>674</v>
+        <v>161</v>
       </c>
       <c r="G336" s="1">
-        <v>46310</v>
+        <v>46148</v>
       </c>
       <c r="H336" s="1">
-        <v>46310</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="B337" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E337" t="s">
-        <v>48</v>
+        <v>427</v>
       </c>
       <c r="F337" t="s">
-        <v>49</v>
+        <v>428</v>
       </c>
       <c r="G337" s="1">
-        <v>46310</v>
+        <v>46268</v>
       </c>
       <c r="H337" s="1">
-        <v>46310</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="B338" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -11631,388 +11523,388 @@
         <v>128</v>
       </c>
       <c r="E338" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F338" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="G338" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="H338" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B339" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E339" t="s">
-        <v>680</v>
+        <v>41</v>
       </c>
       <c r="F339" t="s">
-        <v>681</v>
+        <v>42</v>
       </c>
       <c r="G339" s="1">
-        <v>46310</v>
+        <v>46133</v>
       </c>
       <c r="H339" s="1">
-        <v>46310</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B340" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E340" t="s">
-        <v>683</v>
+        <v>41</v>
       </c>
       <c r="F340" t="s">
-        <v>684</v>
+        <v>42</v>
       </c>
       <c r="G340" s="1">
-        <v>46310</v>
+        <v>46134</v>
       </c>
       <c r="H340" s="1">
-        <v>46310</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B341" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E341" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="F341" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="G341" s="1">
-        <v>46310</v>
+        <v>46156</v>
       </c>
       <c r="H341" s="1">
-        <v>46310</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B342" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E342" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="F342" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="G342" s="1">
-        <v>46310</v>
+        <v>46213</v>
       </c>
       <c r="H342" s="1">
-        <v>46310</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B343" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="C343">
         <v>1</v>
       </c>
       <c r="D343" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E343" t="s">
-        <v>16</v>
+        <v>681</v>
       </c>
       <c r="F343" t="s">
-        <v>17</v>
+        <v>682</v>
       </c>
       <c r="G343" s="1">
-        <v>46310</v>
+        <v>46253</v>
       </c>
       <c r="H343" s="1">
-        <v>46310</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B344" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E344" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="F344" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="G344" s="1">
-        <v>46310</v>
+        <v>46273</v>
       </c>
       <c r="H344" s="1">
-        <v>46310</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B345" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="C345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D345" t="s">
         <v>128</v>
       </c>
       <c r="E345" t="s">
-        <v>16</v>
+        <v>685</v>
       </c>
       <c r="F345" t="s">
-        <v>17</v>
+        <v>686</v>
       </c>
       <c r="G345" s="1">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="H345" s="1">
-        <v>46310</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B346" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="C346">
         <v>1</v>
       </c>
       <c r="D346" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E346" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="F346" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="G346" s="1">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="H346" s="1">
-        <v>46310</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B347" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E347" t="s">
-        <v>572</v>
+        <v>689</v>
       </c>
       <c r="F347" t="s">
-        <v>573</v>
+        <v>690</v>
       </c>
       <c r="G347" s="1">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="H347" s="1">
-        <v>46310</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B348" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E348" t="s">
-        <v>470</v>
+        <v>304</v>
       </c>
       <c r="F348" t="s">
-        <v>471</v>
+        <v>305</v>
       </c>
       <c r="G348" s="1">
-        <v>46310</v>
+        <v>46302</v>
       </c>
       <c r="H348" s="1">
-        <v>46310</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B349" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C349">
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E349" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F349" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="G349" s="1">
-        <v>46310</v>
+        <v>46303</v>
       </c>
       <c r="H349" s="1">
-        <v>46310</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B350" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D350" t="s">
         <v>128</v>
       </c>
       <c r="E350" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="F350" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="G350" s="1">
-        <v>46310</v>
+        <v>46303</v>
       </c>
       <c r="H350" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B351" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" t="s">
         <v>128</v>
       </c>
       <c r="E351" t="s">
-        <v>122</v>
+        <v>697</v>
       </c>
       <c r="F351" t="s">
-        <v>123</v>
+        <v>698</v>
       </c>
       <c r="G351" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="H351" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B352" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D352" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E352" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F352" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="G352" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="H352" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="B353" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -12021,76 +11913,76 @@
         <v>128</v>
       </c>
       <c r="E353" t="s">
-        <v>607</v>
+        <v>521</v>
       </c>
       <c r="F353" t="s">
-        <v>608</v>
+        <v>522</v>
       </c>
       <c r="G353" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="H353" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>706</v>
+        <v>673</v>
       </c>
       <c r="B354" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E354" t="s">
-        <v>160</v>
+        <v>636</v>
       </c>
       <c r="F354" t="s">
-        <v>161</v>
+        <v>637</v>
       </c>
       <c r="G354" s="1">
-        <v>46148</v>
+        <v>46310</v>
       </c>
       <c r="H354" s="1">
-        <v>46149</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>706</v>
+        <v>673</v>
       </c>
       <c r="B355" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E355" t="s">
-        <v>427</v>
+        <v>636</v>
       </c>
       <c r="F355" t="s">
-        <v>428</v>
+        <v>637</v>
       </c>
       <c r="G355" s="1">
-        <v>46268</v>
+        <v>46310</v>
       </c>
       <c r="H355" s="1">
-        <v>46268</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>709</v>
+        <v>673</v>
       </c>
       <c r="B356" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -12099,76 +11991,76 @@
         <v>128</v>
       </c>
       <c r="E356" t="s">
-        <v>711</v>
+        <v>636</v>
       </c>
       <c r="F356" t="s">
-        <v>712</v>
+        <v>637</v>
       </c>
       <c r="G356" s="1">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="H356" s="1">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>713</v>
+        <v>673</v>
       </c>
       <c r="B357" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="F357" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="G357" s="1">
-        <v>46133</v>
+        <v>46310</v>
       </c>
       <c r="H357" s="1">
-        <v>46134</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B358" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>707</v>
       </c>
       <c r="F358" t="s">
-        <v>42</v>
+        <v>708</v>
       </c>
       <c r="G358" s="1">
-        <v>46134</v>
+        <v>46063</v>
       </c>
       <c r="H358" s="1">
-        <v>46134</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B359" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -12177,76 +12069,76 @@
         <v>6</v>
       </c>
       <c r="E359" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F359" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="G359" s="1">
-        <v>46156</v>
+        <v>46113</v>
       </c>
       <c r="H359" s="1">
-        <v>46156</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B360" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E360" t="s">
-        <v>514</v>
+        <v>57</v>
       </c>
       <c r="F360" t="s">
-        <v>515</v>
+        <v>58</v>
       </c>
       <c r="G360" s="1">
-        <v>46213</v>
+        <v>46125</v>
       </c>
       <c r="H360" s="1">
-        <v>46213</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B361" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E361" t="s">
-        <v>719</v>
+        <v>57</v>
       </c>
       <c r="F361" t="s">
-        <v>720</v>
+        <v>58</v>
       </c>
       <c r="G361" s="1">
-        <v>46253</v>
+        <v>46126</v>
       </c>
       <c r="H361" s="1">
-        <v>46253</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B362" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -12255,76 +12147,76 @@
         <v>2</v>
       </c>
       <c r="E362" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F362" t="s">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="G362" s="1">
-        <v>46273</v>
+        <v>46126</v>
       </c>
       <c r="H362" s="1">
-        <v>46274</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
+        <v>705</v>
+      </c>
+      <c r="B363" t="s">
         <v>713</v>
       </c>
-      <c r="B363" t="s">
-        <v>722</v>
-      </c>
       <c r="C363">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E363" t="s">
-        <v>723</v>
+        <v>57</v>
       </c>
       <c r="F363" t="s">
-        <v>724</v>
+        <v>58</v>
       </c>
       <c r="G363" s="1">
-        <v>46300</v>
+        <v>46128</v>
       </c>
       <c r="H363" s="1">
-        <v>46304</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B364" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E364" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
       <c r="F364" t="s">
-        <v>183</v>
+        <v>58</v>
       </c>
       <c r="G364" s="1">
-        <v>46300</v>
+        <v>46132</v>
       </c>
       <c r="H364" s="1">
-        <v>46300</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B365" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -12333,24 +12225,24 @@
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>531</v>
+        <v>57</v>
       </c>
       <c r="F365" t="s">
-        <v>532</v>
+        <v>58</v>
       </c>
       <c r="G365" s="1">
-        <v>46300</v>
+        <v>46161</v>
       </c>
       <c r="H365" s="1">
-        <v>46301</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B366" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -12359,180 +12251,180 @@
         <v>2</v>
       </c>
       <c r="E366" t="s">
-        <v>304</v>
+        <v>57</v>
       </c>
       <c r="F366" t="s">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="G366" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
       <c r="H366" s="1">
-        <v>46302</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B367" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E367" t="s">
-        <v>729</v>
+        <v>57</v>
       </c>
       <c r="F367" t="s">
-        <v>730</v>
+        <v>58</v>
       </c>
       <c r="G367" s="1">
-        <v>46303</v>
+        <v>46174</v>
       </c>
       <c r="H367" s="1">
-        <v>46303</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B368" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C368">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E368" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="F368" t="s">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="G368" s="1">
-        <v>46303</v>
+        <v>46195</v>
       </c>
       <c r="H368" s="1">
-        <v>46308</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B369" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E369" t="s">
-        <v>733</v>
+        <v>57</v>
       </c>
       <c r="F369" t="s">
-        <v>734</v>
+        <v>58</v>
       </c>
       <c r="G369" s="1">
-        <v>46308</v>
+        <v>46210</v>
       </c>
       <c r="H369" s="1">
-        <v>46309</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B370" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="C370">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E370" t="s">
-        <v>733</v>
+        <v>57</v>
       </c>
       <c r="F370" t="s">
-        <v>734</v>
+        <v>58</v>
       </c>
       <c r="G370" s="1">
-        <v>46308</v>
+        <v>46213</v>
       </c>
       <c r="H370" s="1">
-        <v>46309</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B371" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
-        <v>565</v>
+        <v>57</v>
       </c>
       <c r="F371" t="s">
-        <v>566</v>
+        <v>58</v>
       </c>
       <c r="G371" s="1">
-        <v>46309</v>
+        <v>46218</v>
       </c>
       <c r="H371" s="1">
-        <v>46309</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B372" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="C372">
         <v>1</v>
       </c>
       <c r="D372" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E372" t="s">
-        <v>689</v>
+        <v>77</v>
       </c>
       <c r="F372" t="s">
-        <v>690</v>
+        <v>78</v>
       </c>
       <c r="G372" s="1">
-        <v>46310</v>
+        <v>46226</v>
       </c>
       <c r="H372" s="1">
-        <v>46310</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B373" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -12541,76 +12433,76 @@
         <v>128</v>
       </c>
       <c r="E373" t="s">
-        <v>689</v>
+        <v>57</v>
       </c>
       <c r="F373" t="s">
-        <v>690</v>
+        <v>58</v>
       </c>
       <c r="G373" s="1">
-        <v>46310</v>
+        <v>46227</v>
       </c>
       <c r="H373" s="1">
-        <v>46310</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B374" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
-        <v>689</v>
+        <v>57</v>
       </c>
       <c r="F374" t="s">
-        <v>690</v>
+        <v>58</v>
       </c>
       <c r="G374" s="1">
-        <v>46310</v>
+        <v>46227</v>
       </c>
       <c r="H374" s="1">
-        <v>46310</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B375" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="C375">
         <v>1</v>
       </c>
       <c r="D375" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E375" t="s">
-        <v>742</v>
+        <v>57</v>
       </c>
       <c r="F375" t="s">
-        <v>743</v>
+        <v>58</v>
       </c>
       <c r="G375" s="1">
-        <v>46063</v>
+        <v>46227</v>
       </c>
       <c r="H375" s="1">
-        <v>46064</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B376" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -12619,30 +12511,30 @@
         <v>6</v>
       </c>
       <c r="E376" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F376" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G376" s="1">
-        <v>46113</v>
+        <v>46230</v>
       </c>
       <c r="H376" s="1">
-        <v>46125</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B377" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E377" t="s">
         <v>57</v>
@@ -12651,24 +12543,24 @@
         <v>58</v>
       </c>
       <c r="G377" s="1">
-        <v>46125</v>
+        <v>46231</v>
       </c>
       <c r="H377" s="1">
-        <v>46125</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B378" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E378" t="s">
         <v>57</v>
@@ -12677,18 +12569,18 @@
         <v>58</v>
       </c>
       <c r="G378" s="1">
-        <v>46126</v>
+        <v>46254</v>
       </c>
       <c r="H378" s="1">
-        <v>46126</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B379" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="C379">
         <v>1</v>
@@ -12703,24 +12595,24 @@
         <v>58</v>
       </c>
       <c r="G379" s="1">
-        <v>46126</v>
+        <v>46255</v>
       </c>
       <c r="H379" s="1">
-        <v>46126</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B380" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E380" t="s">
         <v>57</v>
@@ -12729,18 +12621,18 @@
         <v>58</v>
       </c>
       <c r="G380" s="1">
-        <v>46128</v>
+        <v>46260</v>
       </c>
       <c r="H380" s="1">
-        <v>46128</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B381" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -12755,24 +12647,24 @@
         <v>58</v>
       </c>
       <c r="G381" s="1">
-        <v>46132</v>
+        <v>46289</v>
       </c>
       <c r="H381" s="1">
-        <v>46132</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="B382" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="C382">
         <v>1</v>
       </c>
       <c r="D382" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E382" t="s">
         <v>57</v>
@@ -12781,18 +12673,18 @@
         <v>58</v>
       </c>
       <c r="G382" s="1">
-        <v>46161</v>
+        <v>46294</v>
       </c>
       <c r="H382" s="1">
-        <v>46161</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B383" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -12801,24 +12693,24 @@
         <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F383" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G383" s="1">
-        <v>46174</v>
+        <v>46157</v>
       </c>
       <c r="H383" s="1">
-        <v>46174</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B384" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -12827,76 +12719,76 @@
         <v>2</v>
       </c>
       <c r="E384" t="s">
-        <v>57</v>
+        <v>738</v>
       </c>
       <c r="F384" t="s">
-        <v>58</v>
+        <v>739</v>
       </c>
       <c r="G384" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="H384" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
+        <v>733</v>
+      </c>
+      <c r="B385" t="s">
         <v>740</v>
       </c>
-      <c r="B385" t="s">
-        <v>753</v>
-      </c>
       <c r="C385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E385" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F385" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G385" s="1">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="H385" s="1">
-        <v>46252</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B386" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C386">
         <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E386" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F386" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G386" s="1">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="H386" s="1">
-        <v>46210</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B387" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -12905,128 +12797,128 @@
         <v>2</v>
       </c>
       <c r="E387" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F387" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G387" s="1">
-        <v>46213</v>
+        <v>46247</v>
       </c>
       <c r="H387" s="1">
-        <v>46213</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B388" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="C388">
         <v>1</v>
       </c>
       <c r="D388" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E388" t="s">
-        <v>57</v>
+        <v>744</v>
       </c>
       <c r="F388" t="s">
-        <v>58</v>
+        <v>745</v>
       </c>
       <c r="G388" s="1">
-        <v>46218</v>
+        <v>46247</v>
       </c>
       <c r="H388" s="1">
-        <v>46252</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B389" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="C389">
         <v>1</v>
       </c>
       <c r="D389" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E389" t="s">
-        <v>77</v>
+        <v>735</v>
       </c>
       <c r="F389" t="s">
-        <v>78</v>
+        <v>736</v>
       </c>
       <c r="G389" s="1">
-        <v>46226</v>
+        <v>46255</v>
       </c>
       <c r="H389" s="1">
-        <v>46226</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B390" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="C390">
         <v>1</v>
       </c>
       <c r="D390" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E390" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F390" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G390" s="1">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="H390" s="1">
-        <v>46252</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B391" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="C391">
         <v>1</v>
       </c>
       <c r="D391" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E391" t="s">
-        <v>57</v>
+        <v>735</v>
       </c>
       <c r="F391" t="s">
-        <v>58</v>
+        <v>736</v>
       </c>
       <c r="G391" s="1">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="H391" s="1">
-        <v>46252</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B392" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="C392">
         <v>1</v>
@@ -13035,484 +12927,16 @@
         <v>6</v>
       </c>
       <c r="E392" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F392" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G392" s="1">
-        <v>46227</v>
+        <v>46281</v>
       </c>
       <c r="H392" s="1">
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>740</v>
-      </c>
-      <c r="B393" t="s">
-        <v>761</v>
-      </c>
-      <c r="C393">
-        <v>1</v>
-      </c>
-      <c r="D393" t="s">
-        <v>6</v>
-      </c>
-      <c r="E393" t="s">
-        <v>77</v>
-      </c>
-      <c r="F393" t="s">
-        <v>78</v>
-      </c>
-      <c r="G393" s="1">
-        <v>46230</v>
-      </c>
-      <c r="H393" s="1">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>740</v>
-      </c>
-      <c r="B394" t="s">
-        <v>762</v>
-      </c>
-      <c r="C394">
-        <v>1</v>
-      </c>
-      <c r="D394" t="s">
-        <v>6</v>
-      </c>
-      <c r="E394" t="s">
-        <v>57</v>
-      </c>
-      <c r="F394" t="s">
-        <v>58</v>
-      </c>
-      <c r="G394" s="1">
-        <v>46231</v>
-      </c>
-      <c r="H394" s="1">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
-        <v>740</v>
-      </c>
-      <c r="B395" t="s">
-        <v>763</v>
-      </c>
-      <c r="C395">
-        <v>1</v>
-      </c>
-      <c r="D395" t="s">
-        <v>6</v>
-      </c>
-      <c r="E395" t="s">
-        <v>57</v>
-      </c>
-      <c r="F395" t="s">
-        <v>58</v>
-      </c>
-      <c r="G395" s="1">
-        <v>46254</v>
-      </c>
-      <c r="H395" s="1">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A396" t="s">
-        <v>740</v>
-      </c>
-      <c r="B396" t="s">
-        <v>764</v>
-      </c>
-      <c r="C396">
-        <v>1</v>
-      </c>
-      <c r="D396" t="s">
-        <v>2</v>
-      </c>
-      <c r="E396" t="s">
-        <v>57</v>
-      </c>
-      <c r="F396" t="s">
-        <v>58</v>
-      </c>
-      <c r="G396" s="1">
-        <v>46255</v>
-      </c>
-      <c r="H396" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>740</v>
-      </c>
-      <c r="B397" t="s">
-        <v>765</v>
-      </c>
-      <c r="C397">
-        <v>1</v>
-      </c>
-      <c r="D397" t="s">
-        <v>6</v>
-      </c>
-      <c r="E397" t="s">
-        <v>57</v>
-      </c>
-      <c r="F397" t="s">
-        <v>58</v>
-      </c>
-      <c r="G397" s="1">
-        <v>46260</v>
-      </c>
-      <c r="H397" s="1">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
-        <v>740</v>
-      </c>
-      <c r="B398" t="s">
-        <v>766</v>
-      </c>
-      <c r="C398">
-        <v>1</v>
-      </c>
-      <c r="D398" t="s">
-        <v>6</v>
-      </c>
-      <c r="E398" t="s">
-        <v>57</v>
-      </c>
-      <c r="F398" t="s">
-        <v>58</v>
-      </c>
-      <c r="G398" s="1">
-        <v>46289</v>
-      </c>
-      <c r="H398" s="1">
-        <v>46289</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>740</v>
-      </c>
-      <c r="B399" t="s">
-        <v>767</v>
-      </c>
-      <c r="C399">
-        <v>1</v>
-      </c>
-      <c r="D399" t="s">
-        <v>6</v>
-      </c>
-      <c r="E399" t="s">
-        <v>57</v>
-      </c>
-      <c r="F399" t="s">
-        <v>58</v>
-      </c>
-      <c r="G399" s="1">
-        <v>46294</v>
-      </c>
-      <c r="H399" s="1">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>768</v>
-      </c>
-      <c r="B400" t="s">
-        <v>769</v>
-      </c>
-      <c r="C400">
-        <v>1</v>
-      </c>
-      <c r="D400" t="s">
-        <v>2</v>
-      </c>
-      <c r="E400" t="s">
-        <v>770</v>
-      </c>
-      <c r="F400" t="s">
-        <v>771</v>
-      </c>
-      <c r="G400" s="1">
-        <v>46157</v>
-      </c>
-      <c r="H400" s="1">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>768</v>
-      </c>
-      <c r="B401" t="s">
-        <v>772</v>
-      </c>
-      <c r="C401">
-        <v>1</v>
-      </c>
-      <c r="D401" t="s">
-        <v>2</v>
-      </c>
-      <c r="E401" t="s">
-        <v>773</v>
-      </c>
-      <c r="F401" t="s">
-        <v>774</v>
-      </c>
-      <c r="G401" s="1">
-        <v>46168</v>
-      </c>
-      <c r="H401" s="1">
-        <v>46170</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A402" t="s">
-        <v>768</v>
-      </c>
-      <c r="B402" t="s">
-        <v>775</v>
-      </c>
-      <c r="C402">
-        <v>1</v>
-      </c>
-      <c r="D402" t="s">
-        <v>2</v>
-      </c>
-      <c r="E402" t="s">
-        <v>770</v>
-      </c>
-      <c r="F402" t="s">
-        <v>771</v>
-      </c>
-      <c r="G402" s="1">
-        <v>46218</v>
-      </c>
-      <c r="H402" s="1">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A403" t="s">
-        <v>768</v>
-      </c>
-      <c r="B403" t="s">
-        <v>776</v>
-      </c>
-      <c r="C403">
-        <v>1</v>
-      </c>
-      <c r="D403" t="s">
-        <v>2</v>
-      </c>
-      <c r="E403" t="s">
-        <v>770</v>
-      </c>
-      <c r="F403" t="s">
-        <v>771</v>
-      </c>
-      <c r="G403" s="1">
-        <v>46244</v>
-      </c>
-      <c r="H403" s="1">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>768</v>
-      </c>
-      <c r="B404" t="s">
-        <v>777</v>
-      </c>
-      <c r="C404">
-        <v>1</v>
-      </c>
-      <c r="D404" t="s">
-        <v>2</v>
-      </c>
-      <c r="E404" t="s">
-        <v>770</v>
-      </c>
-      <c r="F404" t="s">
-        <v>771</v>
-      </c>
-      <c r="G404" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H404" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>768</v>
-      </c>
-      <c r="B405" t="s">
-        <v>778</v>
-      </c>
-      <c r="C405">
-        <v>1</v>
-      </c>
-      <c r="D405" t="s">
-        <v>2</v>
-      </c>
-      <c r="E405" t="s">
-        <v>779</v>
-      </c>
-      <c r="F405" t="s">
-        <v>780</v>
-      </c>
-      <c r="G405" s="1">
-        <v>46247</v>
-      </c>
-      <c r="H405" s="1">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>768</v>
-      </c>
-      <c r="B406" t="s">
-        <v>781</v>
-      </c>
-      <c r="C406">
-        <v>1</v>
-      </c>
-      <c r="D406" t="s">
-        <v>2</v>
-      </c>
-      <c r="E406" t="s">
-        <v>770</v>
-      </c>
-      <c r="F406" t="s">
-        <v>771</v>
-      </c>
-      <c r="G406" s="1">
-        <v>46255</v>
-      </c>
-      <c r="H406" s="1">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>768</v>
-      </c>
-      <c r="B407" t="s">
-        <v>782</v>
-      </c>
-      <c r="C407">
-        <v>1</v>
-      </c>
-      <c r="D407" t="s">
-        <v>2</v>
-      </c>
-      <c r="E407" t="s">
-        <v>770</v>
-      </c>
-      <c r="F407" t="s">
-        <v>771</v>
-      </c>
-      <c r="G407" s="1">
-        <v>46258</v>
-      </c>
-      <c r="H407" s="1">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
-        <v>768</v>
-      </c>
-      <c r="B408" t="s">
-        <v>783</v>
-      </c>
-      <c r="C408">
-        <v>1</v>
-      </c>
-      <c r="D408" t="s">
-        <v>2</v>
-      </c>
-      <c r="E408" t="s">
-        <v>770</v>
-      </c>
-      <c r="F408" t="s">
-        <v>771</v>
-      </c>
-      <c r="G408" s="1">
-        <v>46262</v>
-      </c>
-      <c r="H408" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
-        <v>768</v>
-      </c>
-      <c r="B409" t="s">
-        <v>784</v>
-      </c>
-      <c r="C409">
-        <v>1</v>
-      </c>
-      <c r="D409" t="s">
-        <v>6</v>
-      </c>
-      <c r="E409" t="s">
-        <v>13</v>
-      </c>
-      <c r="F409" t="s">
-        <v>14</v>
-      </c>
-      <c r="G409" s="1">
-        <v>46281</v>
-      </c>
-      <c r="H409" s="1">
         <v>46283</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
-        <v>768</v>
-      </c>
-      <c r="B410" t="s">
-        <v>785</v>
-      </c>
-      <c r="C410">
-        <v>1</v>
-      </c>
-      <c r="D410" t="s">
-        <v>128</v>
-      </c>
-      <c r="E410" t="s">
-        <v>92</v>
-      </c>
-      <c r="F410" t="s">
-        <v>93</v>
-      </c>
-      <c r="G410" s="1">
-        <v>46309</v>
-      </c>
-      <c r="H410" s="1">
-        <v>46309</v>
       </c>
     </row>
   </sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{393257E2-19BB-4D5B-8BC0-972C7C62CAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4755AC24-2F04-4909-BF02-E53A2D39915A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{934C53FF-2504-43AC-A559-62B4F0965047}"/>
   </bookViews>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4755AC24-2F04-4909-BF02-E53A2D39915A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82B7846-E46D-4380-AAAD-6B72BE52B358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{934C53FF-2504-43AC-A559-62B4F0965047}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35B8C581-9CD6-415A-ABA7-491E748F213D}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="800">
   <si>
     <t>0001</t>
   </si>
@@ -1012,24 +1012,6 @@
     <t>AREVALO LUIS AGUSTIN</t>
   </si>
   <si>
-    <t xml:space="preserve">  217008</t>
-  </si>
-  <si>
-    <t>AA25</t>
-  </si>
-  <si>
-    <t>AGUERO ANTONIO G- SERVICIOS AGUERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217030</t>
-  </si>
-  <si>
-    <t>CJ32</t>
-  </si>
-  <si>
-    <t>CONLON JUAN I. -POMPEI SANITARIOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217032</t>
   </si>
   <si>
@@ -1060,6 +1042,12 @@
     <t>BETOMAT S.R.L.</t>
   </si>
   <si>
+    <t xml:space="preserve">  217088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217096</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217104</t>
   </si>
   <si>
@@ -1078,7 +1066,1048 @@
     <t>EL MUNDO DEL PLOMERO S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217142</t>
+    <t xml:space="preserve">  217146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217159</t>
+  </si>
+  <si>
+    <t>SS43</t>
+  </si>
+  <si>
+    <t>SANITARIOS SIONE S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217162</t>
+  </si>
+  <si>
+    <t>AB08</t>
+  </si>
+  <si>
+    <t>ABELSON S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217168</t>
+  </si>
+  <si>
+    <t>CM57</t>
+  </si>
+  <si>
+    <t>CELESIA MARIANO T-SANITARIOS LARRALDE 1724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217184</t>
+  </si>
+  <si>
+    <t>VL05</t>
+  </si>
+  <si>
+    <t>VENTURA LEANDRO ARIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217245</t>
+  </si>
+  <si>
+    <t>NP01</t>
+  </si>
+  <si>
+    <t>NATALI PLASTICOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217295</t>
+  </si>
+  <si>
+    <t>DR01</t>
+  </si>
+  <si>
+    <t>DOMINGO RESTA Y CIA. SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217335</t>
+  </si>
+  <si>
+    <t>AS17</t>
+  </si>
+  <si>
+    <t>AQUA SANITARIOS TANDIL S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217339</t>
+  </si>
+  <si>
+    <t>WA02</t>
+  </si>
+  <si>
+    <t>WALTER CARLOS A. -EL FUERTE MATERIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217354</t>
+  </si>
+  <si>
+    <t>CQ01</t>
+  </si>
+  <si>
+    <t>CAMARGO QUISPE VICENTE - MATERIALES CAMARGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217357</t>
+  </si>
+  <si>
+    <t>DC18</t>
+  </si>
+  <si>
+    <t>DI CARLO SEBASTIAN F -DI CARLO SANIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217378</t>
+  </si>
+  <si>
+    <t>GL01</t>
+  </si>
+  <si>
+    <t>GOBBI LUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217393</t>
+  </si>
+  <si>
+    <t>DS15</t>
+  </si>
+  <si>
+    <t>DI STABILE E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217395</t>
+  </si>
+  <si>
+    <t>ET02</t>
+  </si>
+  <si>
+    <t>EL TEHUELCHE S.A.C.I.C.I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217416</t>
+  </si>
+  <si>
+    <t>IM05</t>
+  </si>
+  <si>
+    <t>IMEPHO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217421</t>
+  </si>
+  <si>
+    <t>GF01</t>
+  </si>
+  <si>
+    <t>GUIDOLI FLORIO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217422</t>
+  </si>
+  <si>
+    <t>LJ15</t>
+  </si>
+  <si>
+    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217455</t>
+  </si>
+  <si>
+    <t>OR06</t>
+  </si>
+  <si>
+    <t>ORSI OSCAR A. Y ORSI LUCIANO O.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217456</t>
+  </si>
+  <si>
+    <t>NB03</t>
+  </si>
+  <si>
+    <t>NESTOR A BIONDINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217459</t>
+  </si>
+  <si>
+    <t>AF07</t>
+  </si>
+  <si>
+    <t>ANDRES LUIS DE FRANCESCO S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217460</t>
+  </si>
+  <si>
+    <t>CB15</t>
+  </si>
+  <si>
+    <t>CASA BOUCIGUEZ S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217465</t>
+  </si>
+  <si>
+    <t>CE23</t>
+  </si>
+  <si>
+    <t>CEFALU S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217466</t>
+  </si>
+  <si>
+    <t>SY05</t>
+  </si>
+  <si>
+    <t>SANITARIOS YRIGOYEN CABRERA S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217477</t>
+  </si>
+  <si>
+    <t>GJ17</t>
+  </si>
+  <si>
+    <t>GUALTIERI JUAN A. CONSTRU-MEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217485</t>
+  </si>
+  <si>
+    <t>CI03</t>
+  </si>
+  <si>
+    <t>CARLOS ISLA Y CIA. S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217486</t>
+  </si>
+  <si>
+    <t>FP04</t>
+  </si>
+  <si>
+    <t>FLUIDOS PATAGONIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217487</t>
+  </si>
+  <si>
+    <t>765</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ, Tiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217494</t>
+  </si>
+  <si>
+    <t>ZZ02</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217515</t>
+  </si>
+  <si>
+    <t>CP31</t>
+  </si>
+  <si>
+    <t>CASAPAULINO SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217518</t>
+  </si>
+  <si>
+    <t>FE26</t>
+  </si>
+  <si>
+    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217523</t>
+  </si>
+  <si>
+    <t>BG15</t>
+  </si>
+  <si>
+    <t>BULFON GUILLERMO JESUS - SANIT. MATISA -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217524</t>
+  </si>
+  <si>
+    <t>MA31</t>
+  </si>
+  <si>
+    <t>MATRIGAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217527</t>
+  </si>
+  <si>
+    <t>BN08</t>
+  </si>
+  <si>
+    <t>BONINO NORBERTO DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217541</t>
+  </si>
+  <si>
+    <t>SM26</t>
+  </si>
+  <si>
+    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217543</t>
+  </si>
+  <si>
+    <t>ED04</t>
+  </si>
+  <si>
+    <t>EDIFICOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217544</t>
+  </si>
+  <si>
+    <t>VA09</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO VEGA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217545</t>
+  </si>
+  <si>
+    <t>DA28</t>
+  </si>
+  <si>
+    <t>DAPESOL S.A. -MATERIALES ACON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217549</t>
+  </si>
+  <si>
+    <t>PR22</t>
+  </si>
+  <si>
+    <t>PEREZ RUBEN -LA CLARITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217550</t>
+  </si>
+  <si>
+    <t>BA41</t>
+  </si>
+  <si>
+    <t>BALCARCE 54 S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217551</t>
+  </si>
+  <si>
+    <t>SM19</t>
+  </si>
+  <si>
+    <t>STRINGHETTI MATERIALES SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217553</t>
+  </si>
+  <si>
+    <t>DR14</t>
+  </si>
+  <si>
+    <t>DREC SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217558</t>
+  </si>
+  <si>
+    <t>CI15</t>
+  </si>
+  <si>
+    <t>CISILOTTO HNOS SACIFEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217561</t>
+  </si>
+  <si>
+    <t>SC33</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAMPANA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217562</t>
+  </si>
+  <si>
+    <t>LP11</t>
+  </si>
+  <si>
+    <t>SANITARIOS LA PRIMERA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217564</t>
+  </si>
+  <si>
+    <t>CO14</t>
+  </si>
+  <si>
+    <t>CASANO OSVALDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217567</t>
+  </si>
+  <si>
+    <t>MA37</t>
+  </si>
+  <si>
+    <t>MARCHISONE S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217569</t>
+  </si>
+  <si>
+    <t>RC10</t>
+  </si>
+  <si>
+    <t>RAN CO MATERIALES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217571</t>
+  </si>
+  <si>
+    <t>SC38</t>
+  </si>
+  <si>
+    <t>SANITARIOS CORTESE SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217572</t>
+  </si>
+  <si>
+    <t>AA24</t>
+  </si>
+  <si>
+    <t>ANDREONE ANDREA F.-ELECTROMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217583</t>
+  </si>
+  <si>
+    <t>CV16</t>
+  </si>
+  <si>
+    <t>CLERICO VICTORY NANNI SILVIA S.H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217584</t>
+  </si>
+  <si>
+    <t>SA40</t>
+  </si>
+  <si>
+    <t>SANICENTRO S.A. SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217589</t>
+  </si>
+  <si>
+    <t>CC59</t>
+  </si>
+  <si>
+    <t>CLACE CDC S. A.-CLACE REVESTIMIENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217592</t>
+  </si>
+  <si>
+    <t>ES13</t>
+  </si>
+  <si>
+    <t>EDEN SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217593</t>
+  </si>
+  <si>
+    <t>TS10</t>
+  </si>
+  <si>
+    <t>TOTAL 25 SANITARIOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217596</t>
+  </si>
+  <si>
+    <t>SU09</t>
+  </si>
+  <si>
+    <t>SUPERMAT CENTRAL S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217597</t>
+  </si>
+  <si>
+    <t>CS40</t>
+  </si>
+  <si>
+    <t>CORDA SANITARIOS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217604</t>
+  </si>
+  <si>
+    <t>AL24</t>
+  </si>
+  <si>
+    <t>ALVARENGA VILLAR LUIS F.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217606</t>
+  </si>
+  <si>
+    <t>DU04</t>
+  </si>
+  <si>
+    <t>DURANTE HNOS S R L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217607</t>
+  </si>
+  <si>
+    <t>SA66</t>
+  </si>
+  <si>
+    <t>SANITARIOS CAÑUELAS SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217608</t>
+  </si>
+  <si>
+    <t>VN02</t>
+  </si>
+  <si>
+    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217609</t>
+  </si>
+  <si>
+    <t>UG01</t>
+  </si>
+  <si>
+    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217610</t>
+  </si>
+  <si>
+    <t>SA60</t>
+  </si>
+  <si>
+    <t>SANTAGAL S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217621</t>
+  </si>
+  <si>
+    <t>SA72</t>
+  </si>
+  <si>
+    <t>SANI 3 S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217627</t>
+  </si>
+  <si>
+    <t>NS01</t>
+  </si>
+  <si>
+    <t>NUEVO SUR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217629</t>
+  </si>
+  <si>
+    <t>CR23</t>
+  </si>
+  <si>
+    <t>CRETA PORCELLANATOS S.A. -CRETA DISEGNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217630</t>
+  </si>
+  <si>
+    <t>AM04</t>
+  </si>
+  <si>
+    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217632</t>
+  </si>
+  <si>
+    <t>PO01</t>
+  </si>
+  <si>
+    <t>PORAL S.A.C.I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217636</t>
+  </si>
+  <si>
+    <t>LS08</t>
+  </si>
+  <si>
+    <t>LUQUE SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217639</t>
+  </si>
+  <si>
+    <t>CC63</t>
+  </si>
+  <si>
+    <t>LA CASA DE LA CONSTRUCCION S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217640</t>
+  </si>
+  <si>
+    <t>SA36</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217648</t>
+  </si>
+  <si>
+    <t>PR29</t>
+  </si>
+  <si>
+    <t>PREMOLCHACO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217649</t>
+  </si>
+  <si>
+    <t>KO01</t>
+  </si>
+  <si>
+    <t>KOCUDEL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217653</t>
+  </si>
+  <si>
+    <t>RP07</t>
+  </si>
+  <si>
+    <t>RIO PLOMO S.A.S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217657</t>
+  </si>
+  <si>
+    <t>PM26</t>
+  </si>
+  <si>
+    <t>PEGORER MARTIN EDUARDO - SANITARIOS RINCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217658</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>SOLER, Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217661</t>
+  </si>
+  <si>
+    <t>AX01</t>
+  </si>
+  <si>
+    <t>SANITARIOS AXANTRA S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217662</t>
+  </si>
+  <si>
+    <t>SP23</t>
+  </si>
+  <si>
+    <t>SEGA PROVISIONES - SANIT CABALLITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217665</t>
   </si>
   <si>
     <t>TU03</t>
@@ -1087,937 +2116,22 @@
     <t>TUBONOR S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217159</t>
-  </si>
-  <si>
-    <t>SS43</t>
-  </si>
-  <si>
-    <t>SANITARIOS SIONE S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217162</t>
-  </si>
-  <si>
-    <t>AB08</t>
-  </si>
-  <si>
-    <t>ABELSON S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217168</t>
-  </si>
-  <si>
-    <t>CM57</t>
-  </si>
-  <si>
-    <t>CELESIA MARIANO T-SANITARIOS LARRALDE 1724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217184</t>
-  </si>
-  <si>
-    <t>VL05</t>
-  </si>
-  <si>
-    <t>VENTURA LEANDRO ARIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217245</t>
-  </si>
-  <si>
-    <t>NP01</t>
-  </si>
-  <si>
-    <t>NATALI PLASTICOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217295</t>
-  </si>
-  <si>
-    <t>DR01</t>
-  </si>
-  <si>
-    <t>DOMINGO RESTA Y CIA. SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217319</t>
-  </si>
-  <si>
-    <t>PO01</t>
-  </si>
-  <si>
-    <t>PORAL S.A.C.I.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217333</t>
-  </si>
-  <si>
-    <t>AP09</t>
-  </si>
-  <si>
-    <t>ABATEDAGA PABLO D.J.-CONECTANDO INST. SANIT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217335</t>
-  </si>
-  <si>
-    <t>AS17</t>
-  </si>
-  <si>
-    <t>AQUA SANITARIOS TANDIL S. R. L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217339</t>
-  </si>
-  <si>
-    <t>WA02</t>
-  </si>
-  <si>
-    <t>WALTER CARLOS A. -EL FUERTE MATERIALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217354</t>
-  </si>
-  <si>
-    <t>CQ01</t>
-  </si>
-  <si>
-    <t>CAMARGO QUISPE VICENTE - MATERIALES CAMARGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217357</t>
-  </si>
-  <si>
-    <t>DC18</t>
-  </si>
-  <si>
-    <t>DI CARLO SEBASTIAN F -DI CARLO SANIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217378</t>
-  </si>
-  <si>
-    <t>GL01</t>
-  </si>
-  <si>
-    <t>GOBBI LUIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217393</t>
-  </si>
-  <si>
-    <t>DS15</t>
-  </si>
-  <si>
-    <t>DI STABILE E HIJOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217395</t>
-  </si>
-  <si>
-    <t>ET02</t>
-  </si>
-  <si>
-    <t>EL TEHUELCHE S.A.C.I.C.I.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217416</t>
-  </si>
-  <si>
-    <t>IM05</t>
-  </si>
-  <si>
-    <t>IMEPHO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217421</t>
-  </si>
-  <si>
-    <t>GF01</t>
-  </si>
-  <si>
-    <t>GUIDOLI FLORIO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217422</t>
-  </si>
-  <si>
-    <t>LJ15</t>
-  </si>
-  <si>
-    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217455</t>
-  </si>
-  <si>
-    <t>OR06</t>
-  </si>
-  <si>
-    <t>ORSI OSCAR A. Y ORSI LUCIANO O.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217456</t>
-  </si>
-  <si>
-    <t>NB03</t>
-  </si>
-  <si>
-    <t>NESTOR A BIONDINI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217459</t>
-  </si>
-  <si>
-    <t>AF07</t>
-  </si>
-  <si>
-    <t>ANDRES LUIS DE FRANCESCO S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217460</t>
-  </si>
-  <si>
-    <t>CB15</t>
-  </si>
-  <si>
-    <t>CASA BOUCIGUEZ S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217465</t>
-  </si>
-  <si>
-    <t>CE23</t>
-  </si>
-  <si>
-    <t>CEFALU S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217466</t>
-  </si>
-  <si>
-    <t>SY05</t>
-  </si>
-  <si>
-    <t>SANITARIOS YRIGOYEN CABRERA S. R. L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217477</t>
-  </si>
-  <si>
-    <t>GJ17</t>
-  </si>
-  <si>
-    <t>GUALTIERI JUAN A. CONSTRU-MEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217483</t>
-  </si>
-  <si>
-    <t>CI03</t>
-  </si>
-  <si>
-    <t>CARLOS ISLA Y CIA. S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217486</t>
-  </si>
-  <si>
-    <t>FP04</t>
-  </si>
-  <si>
-    <t>FLUIDOS PATAGONIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217487</t>
-  </si>
-  <si>
-    <t>765</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ, Tiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217494</t>
-  </si>
-  <si>
-    <t>ZZ02</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217507</t>
-  </si>
-  <si>
-    <t>HI07</t>
-  </si>
-  <si>
-    <t>HIEMACAR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217515</t>
-  </si>
-  <si>
-    <t>CP31</t>
-  </si>
-  <si>
-    <t>CASAPAULINO SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217518</t>
-  </si>
-  <si>
-    <t>FE26</t>
-  </si>
-  <si>
-    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217524</t>
-  </si>
-  <si>
-    <t>MA31</t>
-  </si>
-  <si>
-    <t>MATRIGAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217527</t>
-  </si>
-  <si>
-    <t>BN08</t>
-  </si>
-  <si>
-    <t>BONINO NORBERTO DANIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217541</t>
-  </si>
-  <si>
-    <t>SM26</t>
-  </si>
-  <si>
-    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217543</t>
-  </si>
-  <si>
-    <t>ED04</t>
-  </si>
-  <si>
-    <t>EDIFICOR S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217544</t>
-  </si>
-  <si>
-    <t>VA09</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO VEGA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217545</t>
-  </si>
-  <si>
-    <t>DA28</t>
-  </si>
-  <si>
-    <t>DAPESOL S.A. -MATERIALES ACON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217549</t>
-  </si>
-  <si>
-    <t>PR22</t>
-  </si>
-  <si>
-    <t>PEREZ RUBEN -LA CLARITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217550</t>
-  </si>
-  <si>
-    <t>BA41</t>
-  </si>
-  <si>
-    <t>BALCARCE 54 S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217551</t>
-  </si>
-  <si>
-    <t>SM19</t>
-  </si>
-  <si>
-    <t>STRINGHETTI MATERIALES SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217553</t>
-  </si>
-  <si>
-    <t>DR14</t>
-  </si>
-  <si>
-    <t>DREC SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217558</t>
-  </si>
-  <si>
-    <t>CI15</t>
-  </si>
-  <si>
-    <t>CISILOTTO HNOS SACIFEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217561</t>
-  </si>
-  <si>
-    <t>SC33</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAMPANA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217562</t>
-  </si>
-  <si>
-    <t>LP11</t>
-  </si>
-  <si>
-    <t>SANITARIOS LA PRIMERA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217564</t>
-  </si>
-  <si>
-    <t>CO14</t>
-  </si>
-  <si>
-    <t>CASANO OSVALDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217567</t>
-  </si>
-  <si>
-    <t>MA37</t>
-  </si>
-  <si>
-    <t>MARCHISONE S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217569</t>
-  </si>
-  <si>
-    <t>RC10</t>
-  </si>
-  <si>
-    <t>RAN CO MATERIALES S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217571</t>
-  </si>
-  <si>
-    <t>SC38</t>
-  </si>
-  <si>
-    <t>SANITARIOS CORTESE SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217572</t>
-  </si>
-  <si>
-    <t>AA24</t>
-  </si>
-  <si>
-    <t>ANDREONE ANDREA F.-ELECTROMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217583</t>
-  </si>
-  <si>
-    <t>CV16</t>
-  </si>
-  <si>
-    <t>CLERICO VICTORY NANNI SILVIA S.H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217584</t>
-  </si>
-  <si>
-    <t>SA40</t>
-  </si>
-  <si>
-    <t>SANICENTRO S.A. SANITARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217589</t>
-  </si>
-  <si>
-    <t>CC59</t>
-  </si>
-  <si>
-    <t>CLACE CDC S. A.-CLACE REVESTIMIENTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217592</t>
-  </si>
-  <si>
-    <t>ES13</t>
-  </si>
-  <si>
-    <t>EDEN SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217593</t>
-  </si>
-  <si>
-    <t>TS10</t>
-  </si>
-  <si>
-    <t>TOTAL 25 SANITARIOS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217596</t>
-  </si>
-  <si>
-    <t>SU09</t>
-  </si>
-  <si>
-    <t>SUPERMAT CENTRAL S.A.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217597</t>
-  </si>
-  <si>
-    <t>CS40</t>
-  </si>
-  <si>
-    <t>CORDA SANITARIOS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217604</t>
-  </si>
-  <si>
-    <t>AL24</t>
-  </si>
-  <si>
-    <t>ALVARENGA VILLAR LUIS F.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217606</t>
-  </si>
-  <si>
-    <t>DU04</t>
-  </si>
-  <si>
-    <t>DURANTE HNOS S R L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217607</t>
-  </si>
-  <si>
-    <t>SA66</t>
-  </si>
-  <si>
-    <t>SANITARIOS CAÑUELAS SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217608</t>
-  </si>
-  <si>
-    <t>VN02</t>
-  </si>
-  <si>
-    <t>VICTOR NADIA ANTONELA -SANTIANO CONSTRUCCIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217609</t>
-  </si>
-  <si>
-    <t>UG01</t>
-  </si>
-  <si>
-    <t>UCCELI GABRIEL A.-SANITARIOS GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217610</t>
-  </si>
-  <si>
-    <t>SA60</t>
-  </si>
-  <si>
-    <t>SANTAGAL S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217618</t>
-  </si>
-  <si>
-    <t>CR23</t>
-  </si>
-  <si>
-    <t>CRETA PORCELLANATOS S.A. -CRETA DISEGNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217621</t>
-  </si>
-  <si>
-    <t>SA72</t>
-  </si>
-  <si>
-    <t>SANI 3 S.R.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217627</t>
-  </si>
-  <si>
-    <t>NS01</t>
-  </si>
-  <si>
-    <t>NUEVO SUR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217630</t>
-  </si>
-  <si>
-    <t>AM04</t>
-  </si>
-  <si>
-    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217632</t>
+    <t xml:space="preserve">  217666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217669</t>
+  </si>
+  <si>
+    <t>VS04</t>
+  </si>
+  <si>
+    <t>V.S.MATERIALES DE J.C.MOREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217670</t>
   </si>
   <si>
     <t>0004</t>
@@ -2029,6 +2143,18 @@
     <t xml:space="preserve">     112</t>
   </si>
   <si>
+    <t xml:space="preserve">     140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     141</t>
+  </si>
+  <si>
+    <t>CO28</t>
+  </si>
+  <si>
+    <t>CONSTRUDISENO S.A.</t>
+  </si>
+  <si>
     <t>0007</t>
   </si>
   <si>
@@ -2089,12 +2215,6 @@
     <t xml:space="preserve">    3006</t>
   </si>
   <si>
-    <t>CO28</t>
-  </si>
-  <si>
-    <t>CONSTRUDISENO S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3011</t>
   </si>
   <si>
@@ -2125,18 +2245,15 @@
     <t xml:space="preserve">    3031</t>
   </si>
   <si>
-    <t xml:space="preserve">    3032</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3033</t>
   </si>
   <si>
-    <t xml:space="preserve">    3034</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3035</t>
   </si>
   <si>
+    <t xml:space="preserve">    3036</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2221,6 +2338,12 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
+    <t xml:space="preserve">    2823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2824</t>
+  </si>
+  <si>
     <t>9999</t>
   </si>
   <si>
@@ -2270,6 +2393,9 @@
   </si>
   <si>
     <t xml:space="preserve">      98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     122</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2743,34 +2869,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D0BF34-BF14-45BA-9591-BD058A89B890}">
-  <dimension ref="A1:H392"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3931C34D-4BDE-4B7C-903C-AB1780024926}">
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>750</v>
+        <v>792</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>751</v>
+        <v>793</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>752</v>
+        <v>794</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>753</v>
+        <v>795</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>754</v>
+        <v>796</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>757</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5251,10 +5377,10 @@
         <v>233</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
         <v>234</v>
@@ -5266,7 +5392,7 @@
         <v>46288</v>
       </c>
       <c r="H97" s="1">
-        <v>46295</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -6629,22 +6755,22 @@
         <v>330</v>
       </c>
       <c r="C150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D150" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E150" t="s">
-        <v>331</v>
+        <v>22</v>
       </c>
       <c r="F150" t="s">
-        <v>332</v>
+        <v>23</v>
       </c>
       <c r="G150" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H150" s="1">
-        <v>46310</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -6652,25 +6778,25 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
+        <v>331</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+      <c r="D151" t="s">
+        <v>2</v>
+      </c>
+      <c r="E151" t="s">
+        <v>332</v>
+      </c>
+      <c r="F151" t="s">
         <v>333</v>
       </c>
-      <c r="C151">
-        <v>3</v>
-      </c>
-      <c r="D151" t="s">
-        <v>128</v>
-      </c>
-      <c r="E151" t="s">
-        <v>334</v>
-      </c>
-      <c r="F151" t="s">
-        <v>335</v>
-      </c>
       <c r="G151" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H151" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -6678,25 +6804,25 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
+        <v>334</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>335</v>
+      </c>
+      <c r="F152" t="s">
         <v>336</v>
-      </c>
-      <c r="C152">
-        <v>2</v>
-      </c>
-      <c r="D152" t="s">
-        <v>128</v>
-      </c>
-      <c r="E152" t="s">
-        <v>22</v>
-      </c>
-      <c r="F152" t="s">
-        <v>23</v>
       </c>
       <c r="G152" s="1">
         <v>46301</v>
       </c>
       <c r="H152" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -6707,7 +6833,7 @@
         <v>337</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="s">
         <v>2</v>
@@ -6722,7 +6848,7 @@
         <v>46301</v>
       </c>
       <c r="H153" s="1">
-        <v>46308</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -6736,19 +6862,19 @@
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E154" t="s">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="F154" t="s">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="G154" s="1">
         <v>46301</v>
       </c>
       <c r="H154" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -6756,25 +6882,25 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E155" t="s">
-        <v>344</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
-        <v>345</v>
+        <v>23</v>
       </c>
       <c r="G155" s="1">
         <v>46301</v>
       </c>
       <c r="H155" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -6782,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -6791,10 +6917,10 @@
         <v>128</v>
       </c>
       <c r="E156" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F156" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G156" s="1">
         <v>46301</v>
@@ -6808,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -6817,10 +6943,10 @@
         <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F157" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G157" s="1">
         <v>46302</v>
@@ -6834,25 +6960,25 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>353</v>
+        <v>143</v>
       </c>
       <c r="F158" t="s">
-        <v>354</v>
+        <v>144</v>
       </c>
       <c r="G158" s="1">
         <v>46302</v>
       </c>
       <c r="H158" s="1">
-        <v>46309</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -6860,19 +6986,19 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="s">
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="F159" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="G159" s="1">
         <v>46302</v>
@@ -6886,19 +7012,19 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>48</v>
+        <v>351</v>
       </c>
       <c r="F160" t="s">
-        <v>49</v>
+        <v>352</v>
       </c>
       <c r="G160" s="1">
         <v>46302</v>
@@ -6912,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6921,10 +7047,10 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F161" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G161" s="1">
         <v>46302</v>
@@ -6938,19 +7064,19 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E162" t="s">
-        <v>361</v>
+        <v>37</v>
       </c>
       <c r="F162" t="s">
-        <v>362</v>
+        <v>38</v>
       </c>
       <c r="G162" s="1">
         <v>46302</v>
@@ -6964,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6990,19 +7116,19 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="F164" t="s">
-        <v>38</v>
+        <v>360</v>
       </c>
       <c r="G164" s="1">
         <v>46302</v>
@@ -7016,19 +7142,19 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E165" t="s">
-        <v>366</v>
+        <v>37</v>
       </c>
       <c r="F165" t="s">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="G165" s="1">
         <v>46302</v>
@@ -7042,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7068,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7094,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7120,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7146,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7172,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -7198,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7224,25 +7350,25 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="s">
         <v>128</v>
       </c>
       <c r="E173" t="s">
-        <v>37</v>
+        <v>370</v>
       </c>
       <c r="F173" t="s">
-        <v>38</v>
+        <v>371</v>
       </c>
       <c r="G173" s="1">
         <v>46302</v>
       </c>
       <c r="H173" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -7250,25 +7376,25 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="s">
         <v>128</v>
       </c>
       <c r="E174" t="s">
-        <v>377</v>
+        <v>37</v>
       </c>
       <c r="F174" t="s">
-        <v>378</v>
+        <v>38</v>
       </c>
       <c r="G174" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H174" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -7276,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7302,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7328,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7354,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7380,25 +7506,25 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>378</v>
       </c>
       <c r="F179" t="s">
-        <v>38</v>
+        <v>379</v>
       </c>
       <c r="G179" s="1">
         <v>46303</v>
       </c>
       <c r="H179" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -7406,25 +7532,25 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C180">
         <v>2</v>
       </c>
       <c r="D180" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>149</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>150</v>
       </c>
       <c r="G180" s="1">
         <v>46303</v>
       </c>
       <c r="H180" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -7432,25 +7558,25 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="F181" t="s">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="G181" s="1">
         <v>46303</v>
       </c>
       <c r="H181" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -7458,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7484,25 +7610,25 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>291</v>
+        <v>378</v>
       </c>
       <c r="F183" t="s">
-        <v>292</v>
+        <v>379</v>
       </c>
       <c r="G183" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H183" s="1">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -7510,25 +7636,25 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="s">
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="F184" t="s">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="G184" s="1">
         <v>46304</v>
       </c>
       <c r="H184" s="1">
-        <v>46309</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7536,13 +7662,13 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E185" t="s">
         <v>37</v>
@@ -7562,7 +7688,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -7588,19 +7714,19 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="F187" t="s">
-        <v>38</v>
+        <v>389</v>
       </c>
       <c r="G187" s="1">
         <v>46304</v>
@@ -7614,19 +7740,19 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E188" t="s">
-        <v>395</v>
+        <v>319</v>
       </c>
       <c r="F188" t="s">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="G188" s="1">
         <v>46304</v>
@@ -7640,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -7649,10 +7775,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>398</v>
+        <v>37</v>
       </c>
       <c r="F189" t="s">
-        <v>399</v>
+        <v>38</v>
       </c>
       <c r="G189" s="1">
         <v>46304</v>
@@ -7666,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -7675,10 +7801,10 @@
         <v>128</v>
       </c>
       <c r="E190" t="s">
-        <v>319</v>
+        <v>393</v>
       </c>
       <c r="F190" t="s">
-        <v>320</v>
+        <v>394</v>
       </c>
       <c r="G190" s="1">
         <v>46304</v>
@@ -7692,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -7701,10 +7827,10 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>37</v>
+        <v>396</v>
       </c>
       <c r="F191" t="s">
-        <v>38</v>
+        <v>397</v>
       </c>
       <c r="G191" s="1">
         <v>46304</v>
@@ -7718,25 +7844,25 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E192" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F192" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G192" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="H192" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -7744,25 +7870,25 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E193" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F193" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G193" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="H193" s="1">
-        <v>46304</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -7770,25 +7896,25 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E194" t="s">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="F194" t="s">
-        <v>410</v>
+        <v>339</v>
       </c>
       <c r="G194" s="1">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H194" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -7796,25 +7922,25 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="s">
         <v>128</v>
       </c>
       <c r="E195" t="s">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="F195" t="s">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="G195" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="H195" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -7822,25 +7948,25 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="F196" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G196" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="H196" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7848,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -7857,13 +7983,13 @@
         <v>128</v>
       </c>
       <c r="E197" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="F197" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="G197" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H197" s="1">
         <v>46308</v>
@@ -7874,19 +8000,19 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E198" t="s">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="F198" t="s">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="G198" s="1">
         <v>46308</v>
@@ -7900,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -7909,10 +8035,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F199" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G199" s="1">
         <v>46308</v>
@@ -7926,19 +8052,19 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="F200" t="s">
-        <v>277</v>
+        <v>213</v>
       </c>
       <c r="G200" s="1">
         <v>46308</v>
@@ -7952,19 +8078,19 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="F201" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="G201" s="1">
         <v>46308</v>
@@ -7978,19 +8104,19 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E202" t="s">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="F202" t="s">
-        <v>428</v>
+        <v>339</v>
       </c>
       <c r="G202" s="1">
         <v>46308</v>
@@ -8004,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -8013,10 +8139,10 @@
         <v>128</v>
       </c>
       <c r="E203" t="s">
-        <v>212</v>
+        <v>399</v>
       </c>
       <c r="F203" t="s">
-        <v>213</v>
+        <v>400</v>
       </c>
       <c r="G203" s="1">
         <v>46308</v>
@@ -8030,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -8039,10 +8165,10 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F204" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="G204" s="1">
         <v>46308</v>
@@ -8056,19 +8182,19 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="F205" t="s">
-        <v>345</v>
+        <v>415</v>
       </c>
       <c r="G205" s="1">
         <v>46308</v>
@@ -8082,19 +8208,19 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F206" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G206" s="1">
         <v>46308</v>
@@ -8108,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -8117,10 +8243,10 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F207" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="G207" s="1">
         <v>46308</v>
@@ -8134,19 +8260,19 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E208" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F208" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G208" s="1">
         <v>46308</v>
@@ -8160,19 +8286,19 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E209" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F209" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G209" s="1">
         <v>46308</v>
@@ -8186,19 +8312,19 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E210" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F210" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G210" s="1">
         <v>46308</v>
@@ -8212,7 +8338,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -8221,10 +8347,10 @@
         <v>128</v>
       </c>
       <c r="E211" t="s">
-        <v>438</v>
+        <v>95</v>
       </c>
       <c r="F211" t="s">
-        <v>439</v>
+        <v>96</v>
       </c>
       <c r="G211" s="1">
         <v>46308</v>
@@ -8238,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -8247,10 +8373,10 @@
         <v>128</v>
       </c>
       <c r="E212" t="s">
-        <v>441</v>
+        <v>172</v>
       </c>
       <c r="F212" t="s">
-        <v>442</v>
+        <v>173</v>
       </c>
       <c r="G212" s="1">
         <v>46308</v>
@@ -8264,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -8273,16 +8399,16 @@
         <v>128</v>
       </c>
       <c r="E213" t="s">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="F213" t="s">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="G213" s="1">
         <v>46308</v>
       </c>
       <c r="H213" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -8290,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="B214" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -8299,16 +8425,16 @@
         <v>128</v>
       </c>
       <c r="E214" t="s">
-        <v>95</v>
+        <v>388</v>
       </c>
       <c r="F214" t="s">
-        <v>96</v>
+        <v>389</v>
       </c>
       <c r="G214" s="1">
         <v>46308</v>
       </c>
       <c r="H214" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -8316,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -8325,16 +8451,16 @@
         <v>128</v>
       </c>
       <c r="E215" t="s">
-        <v>172</v>
+        <v>438</v>
       </c>
       <c r="F215" t="s">
-        <v>173</v>
+        <v>439</v>
       </c>
       <c r="G215" s="1">
         <v>46308</v>
       </c>
       <c r="H215" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -8342,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8351,10 +8477,10 @@
         <v>128</v>
       </c>
       <c r="E216" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="F216" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="G216" s="1">
         <v>46308</v>
@@ -8368,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8377,10 +8503,10 @@
         <v>128</v>
       </c>
       <c r="E217" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="F217" t="s">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="G217" s="1">
         <v>46308</v>
@@ -8394,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8403,10 +8529,10 @@
         <v>128</v>
       </c>
       <c r="E218" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F218" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G218" s="1">
         <v>46308</v>
@@ -8420,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8429,13 +8555,13 @@
         <v>128</v>
       </c>
       <c r="E219" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F219" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G219" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H219" s="1">
         <v>46309</v>
@@ -8446,22 +8572,22 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F220" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G220" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H220" s="1">
         <v>46309</v>
@@ -8472,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8481,13 +8607,13 @@
         <v>128</v>
       </c>
       <c r="E221" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="F221" t="s">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="G221" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H221" s="1">
         <v>46309</v>
@@ -8498,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -8507,10 +8633,10 @@
         <v>128</v>
       </c>
       <c r="E222" t="s">
-        <v>463</v>
+        <v>393</v>
       </c>
       <c r="F222" t="s">
-        <v>464</v>
+        <v>394</v>
       </c>
       <c r="G222" s="1">
         <v>46309</v>
@@ -8524,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -8533,10 +8659,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F223" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G223" s="1">
         <v>46309</v>
@@ -8550,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8559,10 +8685,10 @@
         <v>128</v>
       </c>
       <c r="E224" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G224" s="1">
         <v>46309</v>
@@ -8576,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -8585,10 +8711,10 @@
         <v>128</v>
       </c>
       <c r="E225" t="s">
-        <v>406</v>
+        <v>37</v>
       </c>
       <c r="F225" t="s">
-        <v>407</v>
+        <v>38</v>
       </c>
       <c r="G225" s="1">
         <v>46309</v>
@@ -8602,19 +8728,19 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E226" t="s">
-        <v>471</v>
+        <v>37</v>
       </c>
       <c r="F226" t="s">
-        <v>472</v>
+        <v>38</v>
       </c>
       <c r="G226" s="1">
         <v>46309</v>
@@ -8628,13 +8754,13 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E227" t="s">
         <v>37</v>
@@ -8654,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -8680,25 +8806,25 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>37</v>
+        <v>466</v>
       </c>
       <c r="F229" t="s">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="G229" s="1">
         <v>46309</v>
       </c>
       <c r="H229" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
@@ -8706,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8715,10 +8841,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>37</v>
+        <v>469</v>
       </c>
       <c r="F230" t="s">
-        <v>38</v>
+        <v>470</v>
       </c>
       <c r="G230" s="1">
         <v>46309</v>
@@ -8732,19 +8858,19 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>37</v>
+        <v>472</v>
       </c>
       <c r="F231" t="s">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="G231" s="1">
         <v>46309</v>
@@ -8758,25 +8884,25 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232" t="s">
         <v>128</v>
       </c>
       <c r="E232" t="s">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="F232" t="s">
-        <v>480</v>
+        <v>286</v>
       </c>
       <c r="G232" s="1">
         <v>46309</v>
       </c>
       <c r="H232" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -8784,25 +8910,25 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233" t="s">
         <v>128</v>
       </c>
       <c r="E233" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F233" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G233" s="1">
         <v>46309</v>
       </c>
       <c r="H233" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -8810,25 +8936,25 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234" t="s">
         <v>128</v>
       </c>
       <c r="E234" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F234" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G234" s="1">
         <v>46309</v>
       </c>
       <c r="H234" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -8836,19 +8962,19 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E235" t="s">
-        <v>484</v>
+        <v>86</v>
       </c>
       <c r="F235" t="s">
-        <v>485</v>
+        <v>87</v>
       </c>
       <c r="G235" s="1">
         <v>46309</v>
@@ -8862,19 +8988,19 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E236" t="s">
-        <v>487</v>
+        <v>86</v>
       </c>
       <c r="F236" t="s">
-        <v>488</v>
+        <v>87</v>
       </c>
       <c r="G236" s="1">
         <v>46309</v>
@@ -8888,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8897,10 +9023,10 @@
         <v>128</v>
       </c>
       <c r="E237" t="s">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="F237" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="G237" s="1">
         <v>46309</v>
@@ -8914,7 +9040,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8923,10 +9049,10 @@
         <v>128</v>
       </c>
       <c r="E238" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="F238" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="G238" s="1">
         <v>46309</v>
@@ -8940,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8949,10 +9075,10 @@
         <v>128</v>
       </c>
       <c r="E239" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F239" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G239" s="1">
         <v>46309</v>
@@ -8966,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8975,16 +9101,16 @@
         <v>128</v>
       </c>
       <c r="E240" t="s">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="F240" t="s">
-        <v>87</v>
+        <v>490</v>
       </c>
       <c r="G240" s="1">
         <v>46309</v>
       </c>
       <c r="H240" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -8992,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9001,10 +9127,10 @@
         <v>128</v>
       </c>
       <c r="E241" t="s">
-        <v>86</v>
+        <v>492</v>
       </c>
       <c r="F241" t="s">
-        <v>87</v>
+        <v>493</v>
       </c>
       <c r="G241" s="1">
         <v>46309</v>
@@ -9018,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9027,10 +9153,10 @@
         <v>128</v>
       </c>
       <c r="E242" t="s">
-        <v>86</v>
+        <v>469</v>
       </c>
       <c r="F242" t="s">
-        <v>87</v>
+        <v>470</v>
       </c>
       <c r="G242" s="1">
         <v>46309</v>
@@ -9044,19 +9170,19 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
+        <v>495</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+      <c r="D243" t="s">
+        <v>128</v>
+      </c>
+      <c r="E243" t="s">
+        <v>496</v>
+      </c>
+      <c r="F243" t="s">
         <v>497</v>
-      </c>
-      <c r="C243">
-        <v>1</v>
-      </c>
-      <c r="D243" t="s">
-        <v>2</v>
-      </c>
-      <c r="E243" t="s">
-        <v>498</v>
-      </c>
-      <c r="F243" t="s">
-        <v>499</v>
       </c>
       <c r="G243" s="1">
         <v>46309</v>
@@ -9070,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9079,10 +9205,10 @@
         <v>128</v>
       </c>
       <c r="E244" t="s">
-        <v>501</v>
+        <v>219</v>
       </c>
       <c r="F244" t="s">
-        <v>502</v>
+        <v>220</v>
       </c>
       <c r="G244" s="1">
         <v>46309</v>
@@ -9096,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9105,10 +9231,10 @@
         <v>128</v>
       </c>
       <c r="E245" t="s">
-        <v>504</v>
+        <v>338</v>
       </c>
       <c r="F245" t="s">
-        <v>505</v>
+        <v>339</v>
       </c>
       <c r="G245" s="1">
         <v>46309</v>
@@ -9122,7 +9248,7 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9131,10 +9257,10 @@
         <v>128</v>
       </c>
       <c r="E246" t="s">
-        <v>507</v>
+        <v>202</v>
       </c>
       <c r="F246" t="s">
-        <v>508</v>
+        <v>203</v>
       </c>
       <c r="G246" s="1">
         <v>46309</v>
@@ -9148,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9157,10 +9283,10 @@
         <v>128</v>
       </c>
       <c r="E247" t="s">
-        <v>484</v>
+        <v>202</v>
       </c>
       <c r="F247" t="s">
-        <v>485</v>
+        <v>203</v>
       </c>
       <c r="G247" s="1">
         <v>46309</v>
@@ -9174,7 +9300,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9183,10 +9309,10 @@
         <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>511</v>
+        <v>202</v>
       </c>
       <c r="F248" t="s">
-        <v>512</v>
+        <v>203</v>
       </c>
       <c r="G248" s="1">
         <v>46309</v>
@@ -9200,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9209,10 +9335,10 @@
         <v>128</v>
       </c>
       <c r="E249" t="s">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="F249" t="s">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="G249" s="1">
         <v>46309</v>
@@ -9226,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9235,16 +9361,16 @@
         <v>128</v>
       </c>
       <c r="E250" t="s">
-        <v>344</v>
+        <v>172</v>
       </c>
       <c r="F250" t="s">
-        <v>345</v>
+        <v>173</v>
       </c>
       <c r="G250" s="1">
         <v>46309</v>
       </c>
       <c r="H250" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -9252,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9261,10 +9387,10 @@
         <v>128</v>
       </c>
       <c r="E251" t="s">
-        <v>202</v>
+        <v>506</v>
       </c>
       <c r="F251" t="s">
-        <v>203</v>
+        <v>507</v>
       </c>
       <c r="G251" s="1">
         <v>46309</v>
@@ -9278,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9287,16 +9413,16 @@
         <v>128</v>
       </c>
       <c r="E252" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="F252" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="G252" s="1">
         <v>46309</v>
       </c>
       <c r="H252" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -9304,7 +9430,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9313,10 +9439,10 @@
         <v>128</v>
       </c>
       <c r="E253" t="s">
-        <v>202</v>
+        <v>510</v>
       </c>
       <c r="F253" t="s">
-        <v>203</v>
+        <v>511</v>
       </c>
       <c r="G253" s="1">
         <v>46309</v>
@@ -9330,7 +9456,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9339,10 +9465,10 @@
         <v>128</v>
       </c>
       <c r="E254" t="s">
-        <v>68</v>
+        <v>513</v>
       </c>
       <c r="F254" t="s">
-        <v>69</v>
+        <v>514</v>
       </c>
       <c r="G254" s="1">
         <v>46309</v>
@@ -9356,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9365,16 +9491,16 @@
         <v>128</v>
       </c>
       <c r="E255" t="s">
-        <v>172</v>
+        <v>516</v>
       </c>
       <c r="F255" t="s">
-        <v>173</v>
+        <v>517</v>
       </c>
       <c r="G255" s="1">
         <v>46309</v>
       </c>
       <c r="H255" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -9382,25 +9508,25 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
+        <v>518</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256" t="s">
+        <v>128</v>
+      </c>
+      <c r="E256" t="s">
+        <v>519</v>
+      </c>
+      <c r="F256" t="s">
         <v>520</v>
-      </c>
-      <c r="C256">
-        <v>1</v>
-      </c>
-      <c r="D256" t="s">
-        <v>128</v>
-      </c>
-      <c r="E256" t="s">
-        <v>521</v>
-      </c>
-      <c r="F256" t="s">
-        <v>522</v>
       </c>
       <c r="G256" s="1">
         <v>46309</v>
       </c>
       <c r="H256" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -9408,19 +9534,19 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
+        <v>521</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="D257" t="s">
+        <v>128</v>
+      </c>
+      <c r="E257" t="s">
+        <v>522</v>
+      </c>
+      <c r="F257" t="s">
         <v>523</v>
-      </c>
-      <c r="C257">
-        <v>1</v>
-      </c>
-      <c r="D257" t="s">
-        <v>128</v>
-      </c>
-      <c r="E257" t="s">
-        <v>463</v>
-      </c>
-      <c r="F257" t="s">
-        <v>464</v>
       </c>
       <c r="G257" s="1">
         <v>46309</v>
@@ -9452,7 +9578,7 @@
         <v>46309</v>
       </c>
       <c r="H258" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -9469,16 +9595,16 @@
         <v>128</v>
       </c>
       <c r="E259" t="s">
-        <v>528</v>
+        <v>396</v>
       </c>
       <c r="F259" t="s">
-        <v>529</v>
+        <v>397</v>
       </c>
       <c r="G259" s="1">
         <v>46309</v>
       </c>
       <c r="H259" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -9486,25 +9612,25 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
+        <v>528</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260" t="s">
+        <v>128</v>
+      </c>
+      <c r="E260" t="s">
+        <v>529</v>
+      </c>
+      <c r="F260" t="s">
         <v>530</v>
-      </c>
-      <c r="C260">
-        <v>1</v>
-      </c>
-      <c r="D260" t="s">
-        <v>128</v>
-      </c>
-      <c r="E260" t="s">
-        <v>531</v>
-      </c>
-      <c r="F260" t="s">
-        <v>532</v>
       </c>
       <c r="G260" s="1">
         <v>46309</v>
       </c>
       <c r="H260" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -9512,25 +9638,25 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E261" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F261" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G261" s="1">
         <v>46309</v>
       </c>
       <c r="H261" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
@@ -9538,7 +9664,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9547,10 +9673,10 @@
         <v>128</v>
       </c>
       <c r="E262" t="s">
-        <v>535</v>
+        <v>77</v>
       </c>
       <c r="F262" t="s">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="G262" s="1">
         <v>46309</v>
@@ -9564,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9573,10 +9699,10 @@
         <v>128</v>
       </c>
       <c r="E263" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F263" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G263" s="1">
         <v>46309</v>
@@ -9590,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9599,10 +9725,10 @@
         <v>128</v>
       </c>
       <c r="E264" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F264" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="G264" s="1">
         <v>46309</v>
@@ -9616,19 +9742,19 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>409</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
-        <v>410</v>
+        <v>14</v>
       </c>
       <c r="G265" s="1">
         <v>46309</v>
@@ -9642,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9651,10 +9777,10 @@
         <v>128</v>
       </c>
       <c r="E266" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="F266" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G266" s="1">
         <v>46309</v>
@@ -9668,7 +9794,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9677,10 +9803,10 @@
         <v>128</v>
       </c>
       <c r="E267" t="s">
-        <v>77</v>
+        <v>542</v>
       </c>
       <c r="F267" t="s">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="G267" s="1">
         <v>46309</v>
@@ -9694,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9703,10 +9829,10 @@
         <v>128</v>
       </c>
       <c r="E268" t="s">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="F268" t="s">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G268" s="1">
         <v>46309</v>
@@ -9720,7 +9846,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9729,10 +9855,10 @@
         <v>128</v>
       </c>
       <c r="E269" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F269" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G269" s="1">
         <v>46309</v>
@@ -9746,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9755,10 +9881,10 @@
         <v>128</v>
       </c>
       <c r="E270" t="s">
-        <v>550</v>
+        <v>152</v>
       </c>
       <c r="F270" t="s">
-        <v>551</v>
+        <v>153</v>
       </c>
       <c r="G270" s="1">
         <v>46309</v>
@@ -9772,19 +9898,19 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E271" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="F271" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="G271" s="1">
         <v>46309</v>
@@ -9798,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9807,10 +9933,10 @@
         <v>128</v>
       </c>
       <c r="E272" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F272" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G272" s="1">
         <v>46309</v>
@@ -9824,7 +9950,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9833,10 +9959,10 @@
         <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F273" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G273" s="1">
         <v>46309</v>
@@ -9850,7 +9976,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -9859,13 +9985,13 @@
         <v>128</v>
       </c>
       <c r="E274" t="s">
-        <v>344</v>
+        <v>450</v>
       </c>
       <c r="F274" t="s">
-        <v>345</v>
+        <v>451</v>
       </c>
       <c r="G274" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H274" s="1">
         <v>46310</v>
@@ -9876,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -9885,13 +10011,13 @@
         <v>128</v>
       </c>
       <c r="E275" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="F275" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G275" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H275" s="1">
         <v>46310</v>
@@ -9902,7 +10028,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -9911,13 +10037,13 @@
         <v>128</v>
       </c>
       <c r="E276" t="s">
-        <v>152</v>
+        <v>561</v>
       </c>
       <c r="F276" t="s">
-        <v>153</v>
+        <v>562</v>
       </c>
       <c r="G276" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H276" s="1">
         <v>46310</v>
@@ -9928,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -9937,13 +10063,13 @@
         <v>128</v>
       </c>
       <c r="E277" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F277" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="G277" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H277" s="1">
         <v>46310</v>
@@ -9954,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -9963,13 +10089,13 @@
         <v>128</v>
       </c>
       <c r="E278" t="s">
-        <v>567</v>
+        <v>37</v>
       </c>
       <c r="F278" t="s">
-        <v>568</v>
+        <v>38</v>
       </c>
       <c r="G278" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H278" s="1">
         <v>46310</v>
@@ -9980,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -9989,13 +10115,13 @@
         <v>128</v>
       </c>
       <c r="E279" t="s">
-        <v>570</v>
+        <v>37</v>
       </c>
       <c r="F279" t="s">
-        <v>571</v>
+        <v>38</v>
       </c>
       <c r="G279" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H279" s="1">
         <v>46310</v>
@@ -10006,7 +10132,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -10015,10 +10141,10 @@
         <v>128</v>
       </c>
       <c r="E280" t="s">
-        <v>463</v>
+        <v>37</v>
       </c>
       <c r="F280" t="s">
-        <v>464</v>
+        <v>38</v>
       </c>
       <c r="G280" s="1">
         <v>46310</v>
@@ -10032,7 +10158,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10041,10 +10167,10 @@
         <v>128</v>
       </c>
       <c r="E281" t="s">
-        <v>574</v>
+        <v>37</v>
       </c>
       <c r="F281" t="s">
-        <v>575</v>
+        <v>38</v>
       </c>
       <c r="G281" s="1">
         <v>46310</v>
@@ -10058,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -10067,10 +10193,10 @@
         <v>128</v>
       </c>
       <c r="E282" t="s">
-        <v>577</v>
+        <v>37</v>
       </c>
       <c r="F282" t="s">
-        <v>578</v>
+        <v>38</v>
       </c>
       <c r="G282" s="1">
         <v>46310</v>
@@ -10084,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -10110,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -10136,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -10162,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="B286" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -10188,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -10197,10 +10323,10 @@
         <v>128</v>
       </c>
       <c r="E287" t="s">
-        <v>37</v>
+        <v>574</v>
       </c>
       <c r="F287" t="s">
-        <v>38</v>
+        <v>575</v>
       </c>
       <c r="G287" s="1">
         <v>46310</v>
@@ -10214,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10223,10 +10349,10 @@
         <v>128</v>
       </c>
       <c r="E288" t="s">
-        <v>37</v>
+        <v>577</v>
       </c>
       <c r="F288" t="s">
-        <v>38</v>
+        <v>578</v>
       </c>
       <c r="G288" s="1">
         <v>46310</v>
@@ -10240,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10249,10 +10375,10 @@
         <v>128</v>
       </c>
       <c r="E289" t="s">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="F289" t="s">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="G289" s="1">
         <v>46310</v>
@@ -10266,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10275,16 +10401,16 @@
         <v>128</v>
       </c>
       <c r="E290" t="s">
-        <v>37</v>
+        <v>525</v>
       </c>
       <c r="F290" t="s">
-        <v>38</v>
+        <v>526</v>
       </c>
       <c r="G290" s="1">
         <v>46310</v>
       </c>
       <c r="H290" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -10292,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -10301,10 +10427,10 @@
         <v>128</v>
       </c>
       <c r="E291" t="s">
-        <v>37</v>
+        <v>582</v>
       </c>
       <c r="F291" t="s">
-        <v>38</v>
+        <v>583</v>
       </c>
       <c r="G291" s="1">
         <v>46310</v>
@@ -10318,7 +10444,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -10327,10 +10453,10 @@
         <v>128</v>
       </c>
       <c r="E292" t="s">
-        <v>37</v>
+        <v>585</v>
       </c>
       <c r="F292" t="s">
-        <v>38</v>
+        <v>586</v>
       </c>
       <c r="G292" s="1">
         <v>46310</v>
@@ -10344,19 +10470,19 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
+        <v>587</v>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+      <c r="D293" t="s">
+        <v>128</v>
+      </c>
+      <c r="E293" t="s">
+        <v>588</v>
+      </c>
+      <c r="F293" t="s">
         <v>589</v>
-      </c>
-      <c r="C293">
-        <v>1</v>
-      </c>
-      <c r="D293" t="s">
-        <v>128</v>
-      </c>
-      <c r="E293" t="s">
-        <v>590</v>
-      </c>
-      <c r="F293" t="s">
-        <v>591</v>
       </c>
       <c r="G293" s="1">
         <v>46310</v>
@@ -10370,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10379,10 +10505,10 @@
         <v>128</v>
       </c>
       <c r="E294" t="s">
-        <v>593</v>
+        <v>237</v>
       </c>
       <c r="F294" t="s">
-        <v>594</v>
+        <v>238</v>
       </c>
       <c r="G294" s="1">
         <v>46310</v>
@@ -10396,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10405,10 +10531,10 @@
         <v>128</v>
       </c>
       <c r="E295" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="F295" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="G295" s="1">
         <v>46310</v>
@@ -10422,7 +10548,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10431,10 +10557,10 @@
         <v>128</v>
       </c>
       <c r="E296" t="s">
-        <v>57</v>
+        <v>593</v>
       </c>
       <c r="F296" t="s">
-        <v>58</v>
+        <v>594</v>
       </c>
       <c r="G296" s="1">
         <v>46310</v>
@@ -10448,19 +10574,19 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
+        <v>595</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297" t="s">
+        <v>128</v>
+      </c>
+      <c r="E297" t="s">
+        <v>596</v>
+      </c>
+      <c r="F297" t="s">
         <v>597</v>
-      </c>
-      <c r="C297">
-        <v>1</v>
-      </c>
-      <c r="D297" t="s">
-        <v>128</v>
-      </c>
-      <c r="E297" t="s">
-        <v>598</v>
-      </c>
-      <c r="F297" t="s">
-        <v>599</v>
       </c>
       <c r="G297" s="1">
         <v>46310</v>
@@ -10474,19 +10600,19 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298" t="s">
         <v>128</v>
       </c>
       <c r="E298" t="s">
-        <v>601</v>
+        <v>16</v>
       </c>
       <c r="F298" t="s">
-        <v>602</v>
+        <v>17</v>
       </c>
       <c r="G298" s="1">
         <v>46310</v>
@@ -10500,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10509,10 +10635,10 @@
         <v>128</v>
       </c>
       <c r="E299" t="s">
-        <v>604</v>
+        <v>16</v>
       </c>
       <c r="F299" t="s">
-        <v>605</v>
+        <v>17</v>
       </c>
       <c r="G299" s="1">
         <v>46310</v>
@@ -10526,7 +10652,7 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -10535,10 +10661,10 @@
         <v>128</v>
       </c>
       <c r="E300" t="s">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="F300" t="s">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="G300" s="1">
         <v>46310</v>
@@ -10552,7 +10678,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -10561,10 +10687,10 @@
         <v>128</v>
       </c>
       <c r="E301" t="s">
-        <v>195</v>
+        <v>539</v>
       </c>
       <c r="F301" t="s">
-        <v>196</v>
+        <v>540</v>
       </c>
       <c r="G301" s="1">
         <v>46310</v>
@@ -10578,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="B302" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -10587,10 +10713,10 @@
         <v>128</v>
       </c>
       <c r="E302" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F302" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="G302" s="1">
         <v>46310</v>
@@ -10604,7 +10730,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10613,10 +10739,10 @@
         <v>128</v>
       </c>
       <c r="E303" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F303" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G303" s="1">
         <v>46310</v>
@@ -10630,7 +10756,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10639,10 +10765,10 @@
         <v>128</v>
       </c>
       <c r="E304" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
       <c r="F304" t="s">
-        <v>17</v>
+        <v>610</v>
       </c>
       <c r="G304" s="1">
         <v>46310</v>
@@ -10656,19 +10782,19 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D305" t="s">
         <v>128</v>
       </c>
       <c r="E305" t="s">
-        <v>16</v>
+        <v>612</v>
       </c>
       <c r="F305" t="s">
-        <v>17</v>
+        <v>613</v>
       </c>
       <c r="G305" s="1">
         <v>46310</v>
@@ -10682,19 +10808,19 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
+        <v>614</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="D306" t="s">
+        <v>128</v>
+      </c>
+      <c r="E306" t="s">
+        <v>615</v>
+      </c>
+      <c r="F306" t="s">
         <v>616</v>
-      </c>
-      <c r="C306">
-        <v>1</v>
-      </c>
-      <c r="D306" t="s">
-        <v>128</v>
-      </c>
-      <c r="E306" t="s">
-        <v>16</v>
-      </c>
-      <c r="F306" t="s">
-        <v>17</v>
       </c>
       <c r="G306" s="1">
         <v>46310</v>
@@ -10717,10 +10843,10 @@
         <v>128</v>
       </c>
       <c r="E307" t="s">
-        <v>385</v>
+        <v>618</v>
       </c>
       <c r="F307" t="s">
-        <v>386</v>
+        <v>619</v>
       </c>
       <c r="G307" s="1">
         <v>46310</v>
@@ -10734,7 +10860,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -10743,10 +10869,10 @@
         <v>128</v>
       </c>
       <c r="E308" t="s">
-        <v>555</v>
+        <v>16</v>
       </c>
       <c r="F308" t="s">
-        <v>556</v>
+        <v>17</v>
       </c>
       <c r="G308" s="1">
         <v>46310</v>
@@ -10760,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10769,10 +10895,10 @@
         <v>128</v>
       </c>
       <c r="E309" t="s">
-        <v>620</v>
+        <v>16</v>
       </c>
       <c r="F309" t="s">
-        <v>621</v>
+        <v>17</v>
       </c>
       <c r="G309" s="1">
         <v>46310</v>
@@ -10795,10 +10921,10 @@
         <v>128</v>
       </c>
       <c r="E310" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F310" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G310" s="1">
         <v>46310</v>
@@ -10821,10 +10947,10 @@
         <v>128</v>
       </c>
       <c r="E311" t="s">
-        <v>624</v>
+        <v>16</v>
       </c>
       <c r="F311" t="s">
-        <v>625</v>
+        <v>17</v>
       </c>
       <c r="G311" s="1">
         <v>46310</v>
@@ -10838,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -10847,10 +10973,10 @@
         <v>128</v>
       </c>
       <c r="E312" t="s">
-        <v>627</v>
+        <v>513</v>
       </c>
       <c r="F312" t="s">
-        <v>628</v>
+        <v>514</v>
       </c>
       <c r="G312" s="1">
         <v>46310</v>
@@ -10864,7 +10990,7 @@
         <v>0</v>
       </c>
       <c r="B313" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -10873,10 +10999,10 @@
         <v>128</v>
       </c>
       <c r="E313" t="s">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="F313" t="s">
-        <v>631</v>
+        <v>451</v>
       </c>
       <c r="G313" s="1">
         <v>46310</v>
@@ -10890,7 +11016,7 @@
         <v>0</v>
       </c>
       <c r="B314" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -10899,10 +11025,10 @@
         <v>128</v>
       </c>
       <c r="E314" t="s">
-        <v>633</v>
+        <v>92</v>
       </c>
       <c r="F314" t="s">
-        <v>634</v>
+        <v>93</v>
       </c>
       <c r="G314" s="1">
         <v>46310</v>
@@ -10916,7 +11042,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -10925,10 +11051,10 @@
         <v>128</v>
       </c>
       <c r="E315" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F315" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G315" s="1">
         <v>46310</v>
@@ -10942,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -10951,10 +11077,10 @@
         <v>128</v>
       </c>
       <c r="E316" t="s">
-        <v>16</v>
+        <v>542</v>
       </c>
       <c r="F316" t="s">
-        <v>17</v>
+        <v>543</v>
       </c>
       <c r="G316" s="1">
         <v>46310</v>
@@ -10968,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10977,10 +11103,10 @@
         <v>128</v>
       </c>
       <c r="E317" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="F317" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="G317" s="1">
         <v>46310</v>
@@ -10994,7 +11120,7 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -11020,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -11046,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -11055,10 +11181,10 @@
         <v>128</v>
       </c>
       <c r="E320" t="s">
-        <v>528</v>
+        <v>635</v>
       </c>
       <c r="F320" t="s">
-        <v>529</v>
+        <v>636</v>
       </c>
       <c r="G320" s="1">
         <v>46310</v>
@@ -11072,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -11081,10 +11207,10 @@
         <v>128</v>
       </c>
       <c r="E321" t="s">
-        <v>463</v>
+        <v>16</v>
       </c>
       <c r="F321" t="s">
-        <v>464</v>
+        <v>17</v>
       </c>
       <c r="G321" s="1">
         <v>46310</v>
@@ -11098,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -11107,10 +11233,10 @@
         <v>128</v>
       </c>
       <c r="E322" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="F322" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="G322" s="1">
         <v>46310</v>
@@ -11124,7 +11250,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -11133,10 +11259,10 @@
         <v>128</v>
       </c>
       <c r="E323" t="s">
-        <v>92</v>
+        <v>642</v>
       </c>
       <c r="F323" t="s">
-        <v>93</v>
+        <v>643</v>
       </c>
       <c r="G323" s="1">
         <v>46310</v>
@@ -11150,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -11159,10 +11285,10 @@
         <v>128</v>
       </c>
       <c r="E324" t="s">
-        <v>122</v>
+        <v>645</v>
       </c>
       <c r="F324" t="s">
-        <v>123</v>
+        <v>646</v>
       </c>
       <c r="G324" s="1">
         <v>46310</v>
@@ -11176,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11185,16 +11311,16 @@
         <v>128</v>
       </c>
       <c r="E325" t="s">
-        <v>650</v>
+        <v>28</v>
       </c>
       <c r="F325" t="s">
-        <v>651</v>
+        <v>29</v>
       </c>
       <c r="G325" s="1">
         <v>46310</v>
       </c>
       <c r="H325" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
@@ -11202,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -11211,16 +11337,16 @@
         <v>128</v>
       </c>
       <c r="E326" t="s">
-        <v>558</v>
+        <v>313</v>
       </c>
       <c r="F326" t="s">
-        <v>559</v>
+        <v>314</v>
       </c>
       <c r="G326" s="1">
         <v>46310</v>
       </c>
       <c r="H326" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
@@ -11228,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -11237,16 +11363,16 @@
         <v>128</v>
       </c>
       <c r="E327" t="s">
-        <v>149</v>
+        <v>393</v>
       </c>
       <c r="F327" t="s">
-        <v>150</v>
+        <v>394</v>
       </c>
       <c r="G327" s="1">
         <v>46310</v>
       </c>
       <c r="H327" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
@@ -11254,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -11263,16 +11389,16 @@
         <v>128</v>
       </c>
       <c r="E328" t="s">
-        <v>16</v>
+        <v>651</v>
       </c>
       <c r="F328" t="s">
-        <v>17</v>
+        <v>652</v>
       </c>
       <c r="G328" s="1">
         <v>46310</v>
       </c>
       <c r="H328" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
@@ -11280,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11289,16 +11415,16 @@
         <v>128</v>
       </c>
       <c r="E329" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="F329" t="s">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="G329" s="1">
         <v>46310</v>
       </c>
       <c r="H329" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
@@ -11306,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -11315,16 +11441,16 @@
         <v>128</v>
       </c>
       <c r="E330" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="F330" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="G330" s="1">
         <v>46310</v>
       </c>
       <c r="H330" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
@@ -11332,25 +11458,25 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
+        <v>655</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331" t="s">
+        <v>128</v>
+      </c>
+      <c r="E331" t="s">
+        <v>656</v>
+      </c>
+      <c r="F331" t="s">
         <v>657</v>
-      </c>
-      <c r="C331">
-        <v>1</v>
-      </c>
-      <c r="D331" t="s">
-        <v>128</v>
-      </c>
-      <c r="E331" t="s">
-        <v>658</v>
-      </c>
-      <c r="F331" t="s">
-        <v>659</v>
       </c>
       <c r="G331" s="1">
         <v>46310</v>
       </c>
       <c r="H331" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
@@ -11358,25 +11484,25 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
+        <v>658</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332" t="s">
+        <v>128</v>
+      </c>
+      <c r="E332" t="s">
+        <v>659</v>
+      </c>
+      <c r="F332" t="s">
         <v>660</v>
-      </c>
-      <c r="C332">
-        <v>1</v>
-      </c>
-      <c r="D332" t="s">
-        <v>128</v>
-      </c>
-      <c r="E332" t="s">
-        <v>16</v>
-      </c>
-      <c r="F332" t="s">
-        <v>17</v>
       </c>
       <c r="G332" s="1">
         <v>46310</v>
       </c>
       <c r="H332" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
@@ -11393,16 +11519,16 @@
         <v>128</v>
       </c>
       <c r="E333" t="s">
-        <v>645</v>
+        <v>388</v>
       </c>
       <c r="F333" t="s">
-        <v>646</v>
+        <v>389</v>
       </c>
       <c r="G333" s="1">
         <v>46310</v>
       </c>
       <c r="H333" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
@@ -11419,16 +11545,16 @@
         <v>128</v>
       </c>
       <c r="E334" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F334" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="G334" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H334" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
@@ -11436,7 +11562,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -11445,76 +11571,76 @@
         <v>128</v>
       </c>
       <c r="E335" t="s">
-        <v>398</v>
+        <v>191</v>
       </c>
       <c r="F335" t="s">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="G335" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H335" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="B336" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E336" t="s">
-        <v>160</v>
+        <v>628</v>
       </c>
       <c r="F336" t="s">
-        <v>161</v>
+        <v>629</v>
       </c>
       <c r="G336" s="1">
-        <v>46148</v>
+        <v>46311</v>
       </c>
       <c r="H336" s="1">
-        <v>46149</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="B337" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E337" t="s">
-        <v>427</v>
+        <v>41</v>
       </c>
       <c r="F337" t="s">
-        <v>428</v>
+        <v>42</v>
       </c>
       <c r="G337" s="1">
-        <v>46268</v>
+        <v>46311</v>
       </c>
       <c r="H337" s="1">
-        <v>46268</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="B338" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -11523,388 +11649,388 @@
         <v>128</v>
       </c>
       <c r="E338" t="s">
-        <v>671</v>
+        <v>202</v>
       </c>
       <c r="F338" t="s">
-        <v>672</v>
+        <v>203</v>
       </c>
       <c r="G338" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H338" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B339" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C339">
         <v>1</v>
       </c>
       <c r="D339" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E339" t="s">
-        <v>41</v>
+        <v>668</v>
       </c>
       <c r="F339" t="s">
-        <v>42</v>
+        <v>669</v>
       </c>
       <c r="G339" s="1">
-        <v>46133</v>
+        <v>46311</v>
       </c>
       <c r="H339" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E340" t="s">
-        <v>41</v>
+        <v>671</v>
       </c>
       <c r="F340" t="s">
-        <v>42</v>
+        <v>672</v>
       </c>
       <c r="G340" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
       <c r="H340" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>0</v>
+      </c>
+      <c r="B341" t="s">
         <v>673</v>
       </c>
-      <c r="B341" t="s">
-        <v>676</v>
-      </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E341" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F341" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G341" s="1">
-        <v>46156</v>
+        <v>46311</v>
       </c>
       <c r="H341" s="1">
-        <v>46156</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E342" t="s">
-        <v>678</v>
+        <v>16</v>
       </c>
       <c r="F342" t="s">
-        <v>679</v>
+        <v>17</v>
       </c>
       <c r="G342" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
       <c r="H342" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B343" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C343">
         <v>1</v>
       </c>
       <c r="D343" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E343" t="s">
-        <v>681</v>
+        <v>16</v>
       </c>
       <c r="F343" t="s">
-        <v>682</v>
+        <v>17</v>
       </c>
       <c r="G343" s="1">
-        <v>46253</v>
+        <v>46311</v>
       </c>
       <c r="H343" s="1">
-        <v>46253</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B344" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E344" t="s">
-        <v>172</v>
+        <v>677</v>
       </c>
       <c r="F344" t="s">
-        <v>173</v>
+        <v>678</v>
       </c>
       <c r="G344" s="1">
-        <v>46273</v>
+        <v>46311</v>
       </c>
       <c r="H344" s="1">
-        <v>46274</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="C345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D345" t="s">
         <v>128</v>
       </c>
       <c r="E345" t="s">
-        <v>685</v>
+        <v>16</v>
       </c>
       <c r="F345" t="s">
-        <v>686</v>
+        <v>17</v>
       </c>
       <c r="G345" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H345" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="C346">
         <v>1</v>
       </c>
       <c r="D346" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E346" t="s">
-        <v>182</v>
+        <v>681</v>
       </c>
       <c r="F346" t="s">
-        <v>183</v>
+        <v>682</v>
       </c>
       <c r="G346" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H346" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E347" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="F347" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="G347" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H347" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C348">
         <v>1</v>
       </c>
       <c r="D348" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E348" t="s">
-        <v>304</v>
+        <v>48</v>
       </c>
       <c r="F348" t="s">
-        <v>305</v>
+        <v>49</v>
       </c>
       <c r="G348" s="1">
-        <v>46302</v>
+        <v>46311</v>
       </c>
       <c r="H348" s="1">
-        <v>46302</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C349">
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E349" t="s">
-        <v>693</v>
+        <v>237</v>
       </c>
       <c r="F349" t="s">
-        <v>694</v>
+        <v>238</v>
       </c>
       <c r="G349" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="H349" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B350" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C350">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D350" t="s">
         <v>128</v>
       </c>
       <c r="E350" t="s">
-        <v>149</v>
+        <v>689</v>
       </c>
       <c r="F350" t="s">
-        <v>150</v>
+        <v>690</v>
       </c>
       <c r="G350" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="H350" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C351">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D351" t="s">
         <v>128</v>
       </c>
       <c r="E351" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="F351" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="G351" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H351" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C352">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D352" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E352" t="s">
-        <v>697</v>
+        <v>16</v>
       </c>
       <c r="F352" t="s">
-        <v>698</v>
+        <v>17</v>
       </c>
       <c r="G352" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H352" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -11913,24 +12039,24 @@
         <v>128</v>
       </c>
       <c r="E353" t="s">
-        <v>521</v>
+        <v>696</v>
       </c>
       <c r="F353" t="s">
-        <v>522</v>
+        <v>697</v>
       </c>
       <c r="G353" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="H353" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -11939,24 +12065,24 @@
         <v>128</v>
       </c>
       <c r="E354" t="s">
-        <v>636</v>
+        <v>225</v>
       </c>
       <c r="F354" t="s">
-        <v>637</v>
+        <v>226</v>
       </c>
       <c r="G354" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H354" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -11965,24 +12091,24 @@
         <v>128</v>
       </c>
       <c r="E355" t="s">
-        <v>636</v>
+        <v>74</v>
       </c>
       <c r="F355" t="s">
-        <v>637</v>
+        <v>75</v>
       </c>
       <c r="G355" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H355" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -11991,24 +12117,24 @@
         <v>128</v>
       </c>
       <c r="E356" t="s">
-        <v>636</v>
+        <v>701</v>
       </c>
       <c r="F356" t="s">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="G356" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H356" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -12017,25 +12143,25 @@
         <v>128</v>
       </c>
       <c r="E357" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="F357" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="G357" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H357" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
+        <v>704</v>
+      </c>
+      <c r="B358" t="s">
         <v>705</v>
       </c>
-      <c r="B358" t="s">
-        <v>706</v>
-      </c>
       <c r="C358">
         <v>1</v>
       </c>
@@ -12043,99 +12169,99 @@
         <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>707</v>
+        <v>160</v>
       </c>
       <c r="F358" t="s">
-        <v>708</v>
+        <v>161</v>
       </c>
       <c r="G358" s="1">
-        <v>46063</v>
+        <v>46148</v>
       </c>
       <c r="H358" s="1">
-        <v>46064</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B359" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E359" t="s">
-        <v>57</v>
+        <v>414</v>
       </c>
       <c r="F359" t="s">
-        <v>58</v>
+        <v>415</v>
       </c>
       <c r="G359" s="1">
-        <v>46113</v>
+        <v>46268</v>
       </c>
       <c r="H359" s="1">
-        <v>46125</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B360" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C360">
         <v>1</v>
       </c>
       <c r="D360" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E360" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F360" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G360" s="1">
-        <v>46125</v>
+        <v>46311</v>
       </c>
       <c r="H360" s="1">
-        <v>46125</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B361" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E361" t="s">
-        <v>57</v>
+        <v>709</v>
       </c>
       <c r="F361" t="s">
-        <v>58</v>
+        <v>710</v>
       </c>
       <c r="G361" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
       <c r="H361" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B362" t="s">
         <v>712</v>
@@ -12144,53 +12270,53 @@
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E362" t="s">
-        <v>57</v>
+        <v>713</v>
       </c>
       <c r="F362" t="s">
-        <v>58</v>
+        <v>714</v>
       </c>
       <c r="G362" s="1">
-        <v>46126</v>
+        <v>46308</v>
       </c>
       <c r="H362" s="1">
-        <v>46126</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B363" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F363" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G363" s="1">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="H363" s="1">
-        <v>46128</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B364" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -12199,154 +12325,154 @@
         <v>6</v>
       </c>
       <c r="E364" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F364" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G364" s="1">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="H364" s="1">
-        <v>46132</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B365" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C365">
         <v>1</v>
       </c>
       <c r="D365" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="F365" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G365" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="H365" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B366" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
-        <v>57</v>
+        <v>720</v>
       </c>
       <c r="F366" t="s">
-        <v>58</v>
+        <v>721</v>
       </c>
       <c r="G366" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
       <c r="H366" s="1">
-        <v>46174</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B367" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E367" t="s">
-        <v>57</v>
+        <v>723</v>
       </c>
       <c r="F367" t="s">
-        <v>58</v>
+        <v>724</v>
       </c>
       <c r="G367" s="1">
-        <v>46174</v>
+        <v>46253</v>
       </c>
       <c r="H367" s="1">
-        <v>46174</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B368" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F368" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="G368" s="1">
-        <v>46195</v>
+        <v>46273</v>
       </c>
       <c r="H368" s="1">
-        <v>46252</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B369" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="C369">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E369" t="s">
-        <v>57</v>
+        <v>727</v>
       </c>
       <c r="F369" t="s">
-        <v>58</v>
+        <v>728</v>
       </c>
       <c r="G369" s="1">
-        <v>46210</v>
+        <v>46300</v>
       </c>
       <c r="H369" s="1">
-        <v>46210</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B370" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -12355,310 +12481,310 @@
         <v>2</v>
       </c>
       <c r="E370" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="F370" t="s">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="G370" s="1">
-        <v>46213</v>
+        <v>46300</v>
       </c>
       <c r="H370" s="1">
-        <v>46213</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B371" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E371" t="s">
-        <v>57</v>
+        <v>709</v>
       </c>
       <c r="F371" t="s">
-        <v>58</v>
+        <v>710</v>
       </c>
       <c r="G371" s="1">
-        <v>46218</v>
+        <v>46300</v>
       </c>
       <c r="H371" s="1">
-        <v>46252</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B372" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="C372">
         <v>1</v>
       </c>
       <c r="D372" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E372" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="F372" t="s">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="G372" s="1">
-        <v>46226</v>
+        <v>46302</v>
       </c>
       <c r="H372" s="1">
-        <v>46226</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B373" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C373">
         <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E373" t="s">
-        <v>57</v>
+        <v>733</v>
       </c>
       <c r="F373" t="s">
-        <v>58</v>
+        <v>734</v>
       </c>
       <c r="G373" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H373" s="1">
-        <v>46252</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B374" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="C374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D374" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E374" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="F374" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="G374" s="1">
-        <v>46227</v>
+        <v>46303</v>
       </c>
       <c r="H374" s="1">
-        <v>46252</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B375" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="C375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D375" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E375" t="s">
-        <v>57</v>
+        <v>737</v>
       </c>
       <c r="F375" t="s">
-        <v>58</v>
+        <v>738</v>
       </c>
       <c r="G375" s="1">
-        <v>46227</v>
+        <v>46308</v>
       </c>
       <c r="H375" s="1">
-        <v>46228</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B376" t="s">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="C376">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D376" t="s">
         <v>6</v>
       </c>
       <c r="E376" t="s">
-        <v>77</v>
+        <v>737</v>
       </c>
       <c r="F376" t="s">
-        <v>78</v>
+        <v>738</v>
       </c>
       <c r="G376" s="1">
-        <v>46230</v>
+        <v>46308</v>
       </c>
       <c r="H376" s="1">
-        <v>46252</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B377" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E377" t="s">
-        <v>57</v>
+        <v>506</v>
       </c>
       <c r="F377" t="s">
-        <v>58</v>
+        <v>507</v>
       </c>
       <c r="G377" s="1">
-        <v>46231</v>
+        <v>46309</v>
       </c>
       <c r="H377" s="1">
-        <v>46231</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B378" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="C378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E378" t="s">
-        <v>57</v>
+        <v>618</v>
       </c>
       <c r="F378" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
       <c r="G378" s="1">
-        <v>46254</v>
+        <v>46310</v>
       </c>
       <c r="H378" s="1">
-        <v>46254</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B379" t="s">
-        <v>729</v>
+        <v>742</v>
       </c>
       <c r="C379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E379" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="F379" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="G379" s="1">
-        <v>46255</v>
+        <v>46310</v>
       </c>
       <c r="H379" s="1">
-        <v>46255</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B380" t="s">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E380" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F380" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G380" s="1">
-        <v>46260</v>
+        <v>46311</v>
       </c>
       <c r="H380" s="1">
-        <v>46260</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="B381" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E381" t="s">
-        <v>57</v>
+        <v>746</v>
       </c>
       <c r="F381" t="s">
-        <v>58</v>
+        <v>747</v>
       </c>
       <c r="G381" s="1">
-        <v>46289</v>
+        <v>46063</v>
       </c>
       <c r="H381" s="1">
-        <v>46289</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="B382" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -12673,18 +12799,18 @@
         <v>58</v>
       </c>
       <c r="G382" s="1">
-        <v>46294</v>
+        <v>46113</v>
       </c>
       <c r="H382" s="1">
-        <v>46294</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B383" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -12693,24 +12819,24 @@
         <v>2</v>
       </c>
       <c r="E383" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F383" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G383" s="1">
-        <v>46157</v>
+        <v>46125</v>
       </c>
       <c r="H383" s="1">
-        <v>46157</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B384" t="s">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -12719,24 +12845,24 @@
         <v>2</v>
       </c>
       <c r="E384" t="s">
-        <v>738</v>
+        <v>57</v>
       </c>
       <c r="F384" t="s">
-        <v>739</v>
+        <v>58</v>
       </c>
       <c r="G384" s="1">
-        <v>46168</v>
+        <v>46126</v>
       </c>
       <c r="H384" s="1">
-        <v>46170</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B385" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="C385">
         <v>1</v>
@@ -12745,24 +12871,24 @@
         <v>2</v>
       </c>
       <c r="E385" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F385" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G385" s="1">
-        <v>46218</v>
+        <v>46126</v>
       </c>
       <c r="H385" s="1">
-        <v>46218</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B386" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -12771,50 +12897,50 @@
         <v>2</v>
       </c>
       <c r="E386" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F386" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G386" s="1">
-        <v>46244</v>
+        <v>46128</v>
       </c>
       <c r="H386" s="1">
-        <v>46244</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B387" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="C387">
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E387" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F387" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G387" s="1">
-        <v>46247</v>
+        <v>46132</v>
       </c>
       <c r="H387" s="1">
-        <v>46247</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B388" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -12823,24 +12949,24 @@
         <v>2</v>
       </c>
       <c r="E388" t="s">
-        <v>744</v>
+        <v>57</v>
       </c>
       <c r="F388" t="s">
-        <v>745</v>
+        <v>58</v>
       </c>
       <c r="G388" s="1">
-        <v>46247</v>
+        <v>46161</v>
       </c>
       <c r="H388" s="1">
-        <v>46247</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B389" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="C389">
         <v>1</v>
@@ -12849,24 +12975,24 @@
         <v>2</v>
       </c>
       <c r="E389" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F389" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G389" s="1">
-        <v>46255</v>
+        <v>46174</v>
       </c>
       <c r="H389" s="1">
-        <v>46255</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B390" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="C390">
         <v>1</v>
@@ -12875,50 +13001,50 @@
         <v>2</v>
       </c>
       <c r="E390" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F390" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G390" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="H390" s="1">
-        <v>46258</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B391" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="C391">
         <v>1</v>
       </c>
       <c r="D391" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E391" t="s">
-        <v>735</v>
+        <v>57</v>
       </c>
       <c r="F391" t="s">
-        <v>736</v>
+        <v>58</v>
       </c>
       <c r="G391" s="1">
-        <v>46262</v>
+        <v>46195</v>
       </c>
       <c r="H391" s="1">
-        <v>46265</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B392" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="C392">
         <v>1</v>
@@ -12927,16 +13053,692 @@
         <v>6</v>
       </c>
       <c r="E392" t="s">
+        <v>57</v>
+      </c>
+      <c r="F392" t="s">
+        <v>58</v>
+      </c>
+      <c r="G392" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H392" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>744</v>
+      </c>
+      <c r="B393" t="s">
+        <v>759</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>2</v>
+      </c>
+      <c r="E393" t="s">
+        <v>57</v>
+      </c>
+      <c r="F393" t="s">
+        <v>58</v>
+      </c>
+      <c r="G393" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H393" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>744</v>
+      </c>
+      <c r="B394" t="s">
+        <v>760</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>6</v>
+      </c>
+      <c r="E394" t="s">
+        <v>57</v>
+      </c>
+      <c r="F394" t="s">
+        <v>58</v>
+      </c>
+      <c r="G394" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H394" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>744</v>
+      </c>
+      <c r="B395" t="s">
+        <v>761</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>6</v>
+      </c>
+      <c r="E395" t="s">
+        <v>77</v>
+      </c>
+      <c r="F395" t="s">
+        <v>78</v>
+      </c>
+      <c r="G395" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H395" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>744</v>
+      </c>
+      <c r="B396" t="s">
+        <v>762</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>128</v>
+      </c>
+      <c r="E396" t="s">
+        <v>57</v>
+      </c>
+      <c r="F396" t="s">
+        <v>58</v>
+      </c>
+      <c r="G396" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H396" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>744</v>
+      </c>
+      <c r="B397" t="s">
+        <v>763</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>6</v>
+      </c>
+      <c r="E397" t="s">
+        <v>57</v>
+      </c>
+      <c r="F397" t="s">
+        <v>58</v>
+      </c>
+      <c r="G397" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H397" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>744</v>
+      </c>
+      <c r="B398" t="s">
+        <v>764</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="s">
+        <v>6</v>
+      </c>
+      <c r="E398" t="s">
+        <v>57</v>
+      </c>
+      <c r="F398" t="s">
+        <v>58</v>
+      </c>
+      <c r="G398" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H398" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>744</v>
+      </c>
+      <c r="B399" t="s">
+        <v>765</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>6</v>
+      </c>
+      <c r="E399" t="s">
+        <v>77</v>
+      </c>
+      <c r="F399" t="s">
+        <v>78</v>
+      </c>
+      <c r="G399" s="1">
+        <v>46230</v>
+      </c>
+      <c r="H399" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>744</v>
+      </c>
+      <c r="B400" t="s">
+        <v>766</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>6</v>
+      </c>
+      <c r="E400" t="s">
+        <v>57</v>
+      </c>
+      <c r="F400" t="s">
+        <v>58</v>
+      </c>
+      <c r="G400" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H400" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>744</v>
+      </c>
+      <c r="B401" t="s">
+        <v>767</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E401" t="s">
+        <v>57</v>
+      </c>
+      <c r="F401" t="s">
+        <v>58</v>
+      </c>
+      <c r="G401" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H401" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>744</v>
+      </c>
+      <c r="B402" t="s">
+        <v>768</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>2</v>
+      </c>
+      <c r="E402" t="s">
+        <v>57</v>
+      </c>
+      <c r="F402" t="s">
+        <v>58</v>
+      </c>
+      <c r="G402" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H402" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>744</v>
+      </c>
+      <c r="B403" t="s">
+        <v>769</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>6</v>
+      </c>
+      <c r="E403" t="s">
+        <v>57</v>
+      </c>
+      <c r="F403" t="s">
+        <v>58</v>
+      </c>
+      <c r="G403" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H403" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>744</v>
+      </c>
+      <c r="B404" t="s">
+        <v>770</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>6</v>
+      </c>
+      <c r="E404" t="s">
+        <v>57</v>
+      </c>
+      <c r="F404" t="s">
+        <v>58</v>
+      </c>
+      <c r="G404" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H404" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>744</v>
+      </c>
+      <c r="B405" t="s">
+        <v>771</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>6</v>
+      </c>
+      <c r="E405" t="s">
+        <v>57</v>
+      </c>
+      <c r="F405" t="s">
+        <v>58</v>
+      </c>
+      <c r="G405" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H405" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>744</v>
+      </c>
+      <c r="B406" t="s">
+        <v>772</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" t="s">
+        <v>128</v>
+      </c>
+      <c r="E406" t="s">
+        <v>57</v>
+      </c>
+      <c r="F406" t="s">
+        <v>58</v>
+      </c>
+      <c r="G406" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H406" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>744</v>
+      </c>
+      <c r="B407" t="s">
+        <v>773</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>128</v>
+      </c>
+      <c r="E407" t="s">
+        <v>57</v>
+      </c>
+      <c r="F407" t="s">
+        <v>58</v>
+      </c>
+      <c r="G407" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H407" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>774</v>
+      </c>
+      <c r="B408" t="s">
+        <v>775</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>2</v>
+      </c>
+      <c r="E408" t="s">
+        <v>776</v>
+      </c>
+      <c r="F408" t="s">
+        <v>777</v>
+      </c>
+      <c r="G408" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H408" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>774</v>
+      </c>
+      <c r="B409" t="s">
+        <v>778</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" t="s">
+        <v>2</v>
+      </c>
+      <c r="E409" t="s">
+        <v>779</v>
+      </c>
+      <c r="F409" t="s">
+        <v>780</v>
+      </c>
+      <c r="G409" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H409" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>774</v>
+      </c>
+      <c r="B410" t="s">
+        <v>781</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="s">
+        <v>2</v>
+      </c>
+      <c r="E410" t="s">
+        <v>776</v>
+      </c>
+      <c r="F410" t="s">
+        <v>777</v>
+      </c>
+      <c r="G410" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H410" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>774</v>
+      </c>
+      <c r="B411" t="s">
+        <v>782</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" t="s">
+        <v>2</v>
+      </c>
+      <c r="E411" t="s">
+        <v>776</v>
+      </c>
+      <c r="F411" t="s">
+        <v>777</v>
+      </c>
+      <c r="G411" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H411" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>774</v>
+      </c>
+      <c r="B412" t="s">
+        <v>783</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412" t="s">
+        <v>2</v>
+      </c>
+      <c r="E412" t="s">
+        <v>776</v>
+      </c>
+      <c r="F412" t="s">
+        <v>777</v>
+      </c>
+      <c r="G412" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H412" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>774</v>
+      </c>
+      <c r="B413" t="s">
+        <v>784</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="s">
+        <v>2</v>
+      </c>
+      <c r="E413" t="s">
+        <v>785</v>
+      </c>
+      <c r="F413" t="s">
+        <v>786</v>
+      </c>
+      <c r="G413" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H413" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>774</v>
+      </c>
+      <c r="B414" t="s">
+        <v>787</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+      <c r="D414" t="s">
+        <v>2</v>
+      </c>
+      <c r="E414" t="s">
+        <v>776</v>
+      </c>
+      <c r="F414" t="s">
+        <v>777</v>
+      </c>
+      <c r="G414" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H414" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>774</v>
+      </c>
+      <c r="B415" t="s">
+        <v>788</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+      <c r="D415" t="s">
+        <v>2</v>
+      </c>
+      <c r="E415" t="s">
+        <v>776</v>
+      </c>
+      <c r="F415" t="s">
+        <v>777</v>
+      </c>
+      <c r="G415" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H415" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>774</v>
+      </c>
+      <c r="B416" t="s">
+        <v>789</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416" t="s">
+        <v>2</v>
+      </c>
+      <c r="E416" t="s">
+        <v>776</v>
+      </c>
+      <c r="F416" t="s">
+        <v>777</v>
+      </c>
+      <c r="G416" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H416" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>774</v>
+      </c>
+      <c r="B417" t="s">
+        <v>790</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417" t="s">
+        <v>6</v>
+      </c>
+      <c r="E417" t="s">
         <v>13</v>
       </c>
-      <c r="F392" t="s">
+      <c r="F417" t="s">
         <v>14</v>
       </c>
-      <c r="G392" s="1">
+      <c r="G417" s="1">
         <v>46281</v>
       </c>
-      <c r="H392" s="1">
+      <c r="H417" s="1">
         <v>46283</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>774</v>
+      </c>
+      <c r="B418" t="s">
+        <v>791</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418" t="s">
+        <v>128</v>
+      </c>
+      <c r="E418" t="s">
+        <v>57</v>
+      </c>
+      <c r="F418" t="s">
+        <v>58</v>
+      </c>
+      <c r="G418" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H418" s="1">
+        <v>46311</v>
       </c>
     </row>
   </sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82B7846-E46D-4380-AAAD-6B72BE52B358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53CC9516-8E4E-465F-AA1C-259475813A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35B8C581-9CD6-415A-ABA7-491E748F213D}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{22288D16-38B9-40A5-878C-524199312A9F}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="875">
   <si>
     <t>0001</t>
   </si>
@@ -1171,6 +1171,15 @@
     <t xml:space="preserve">  217277</t>
   </si>
   <si>
+    <t xml:space="preserve">  217278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217280</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217284</t>
   </si>
   <si>
@@ -2107,6 +2116,9 @@
     <t xml:space="preserve">  217663</t>
   </si>
   <si>
+    <t xml:space="preserve">  217664</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217665</t>
   </si>
   <si>
@@ -2134,6 +2146,228 @@
     <t xml:space="preserve">  217670</t>
   </si>
   <si>
+    <t xml:space="preserve">  217671</t>
+  </si>
+  <si>
+    <t>LG10</t>
+  </si>
+  <si>
+    <t>LOPEZ GAS ONLINE S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217676</t>
+  </si>
+  <si>
+    <t>TB02</t>
+  </si>
+  <si>
+    <t>IT BROKERS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217679</t>
+  </si>
+  <si>
+    <t>CL40</t>
+  </si>
+  <si>
+    <t>CLICK-ON S.A. -TIOSO HOGAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217687</t>
+  </si>
+  <si>
+    <t>OL01</t>
+  </si>
+  <si>
+    <t>ORQUEDA LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217690</t>
+  </si>
+  <si>
+    <t>MC19</t>
+  </si>
+  <si>
+    <t>MEDRANO CONSTRUCCIONES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217693</t>
+  </si>
+  <si>
+    <t>ML16</t>
+  </si>
+  <si>
+    <t>MORINICO LEONEL E-MARKET FULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217695</t>
+  </si>
+  <si>
+    <t>NS03</t>
+  </si>
+  <si>
+    <t>NESGAMET S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217699</t>
+  </si>
+  <si>
+    <t>SO05</t>
+  </si>
+  <si>
+    <t>SANTOS OSCAR FERNANDO - ARGUAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217701</t>
+  </si>
+  <si>
+    <t>NM04</t>
+  </si>
+  <si>
+    <t>NEO MATERIALES S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217702</t>
+  </si>
+  <si>
+    <t>MM42</t>
+  </si>
+  <si>
+    <t>MASIELLO MATIAS A. -MATEO SANITARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217707</t>
+  </si>
+  <si>
+    <t>HL02</t>
+  </si>
+  <si>
+    <t>HEREDIA LEONARDO A - FERRETERIA HEREDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217711</t>
+  </si>
+  <si>
+    <t>AN18</t>
+  </si>
+  <si>
+    <t>ANSBOR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217715</t>
+  </si>
+  <si>
+    <t>JA01</t>
+  </si>
+  <si>
+    <t>JOSE ANACLETO E HIJOS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217719</t>
+  </si>
+  <si>
+    <t>MO21</t>
+  </si>
+  <si>
+    <t>MATERIALES OS-CAR S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217720</t>
+  </si>
+  <si>
+    <t>TF05</t>
+  </si>
+  <si>
+    <t>TORRES FLAVIO GONZALEZ - BATH AND COMPANY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217723</t>
+  </si>
+  <si>
+    <t>IC16</t>
+  </si>
+  <si>
+    <t>EL IMPERIO DEL CERAMICO S.R.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217728</t>
+  </si>
+  <si>
     <t>0004</t>
   </si>
   <si>
@@ -2221,12 +2455,6 @@
     <t xml:space="preserve">    3017</t>
   </si>
   <si>
-    <t>SO05</t>
-  </si>
-  <si>
-    <t>SANTOS OSCAR FERNANDO - ARGUAY</t>
-  </si>
-  <si>
     <t xml:space="preserve">    3021</t>
   </si>
   <si>
@@ -2254,6 +2482,9 @@
     <t xml:space="preserve">    3036</t>
   </si>
   <si>
+    <t xml:space="preserve">    3037</t>
+  </si>
+  <si>
     <t>4444</t>
   </si>
   <si>
@@ -2338,10 +2569,7 @@
     <t xml:space="preserve">    2644</t>
   </si>
   <si>
-    <t xml:space="preserve">    2823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2824</t>
+    <t xml:space="preserve">    2827</t>
   </si>
   <si>
     <t>9999</t>
@@ -2393,9 +2621,6 @@
   </si>
   <si>
     <t xml:space="preserve">      98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     122</t>
   </si>
   <si>
     <t>Puesto</t>
@@ -2869,34 +3094,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3931C34D-4BDE-4B7C-903C-AB1780024926}">
-  <dimension ref="A1:H418"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AB220E-B375-4697-AECF-D3A2A53895DE}">
+  <dimension ref="A1:H463"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>792</v>
+        <v>867</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>793</v>
+        <v>868</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>795</v>
+        <v>870</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>796</v>
+        <v>871</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>797</v>
+        <v>872</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>798</v>
+        <v>873</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>799</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6235,10 +6460,10 @@
         <v>290</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E130" t="s">
         <v>291</v>
@@ -6250,7 +6475,7 @@
         <v>46296</v>
       </c>
       <c r="H130" s="1">
-        <v>46296</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -7561,10 +7786,10 @@
         <v>381</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E181" t="s">
         <v>291</v>
@@ -7576,7 +7801,7 @@
         <v>46303</v>
       </c>
       <c r="H181" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -7587,10 +7812,10 @@
         <v>382</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E182" t="s">
         <v>291</v>
@@ -7602,7 +7827,7 @@
         <v>46303</v>
       </c>
       <c r="H182" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -7613,22 +7838,22 @@
         <v>383</v>
       </c>
       <c r="C183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E183" t="s">
-        <v>378</v>
+        <v>291</v>
       </c>
       <c r="F183" t="s">
-        <v>379</v>
+        <v>292</v>
       </c>
       <c r="G183" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H183" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -7642,19 +7867,19 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E184" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="F184" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
       <c r="G184" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H184" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7671,16 +7896,16 @@
         <v>128</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="F185" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
       <c r="G185" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H185" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -7691,22 +7916,22 @@
         <v>386</v>
       </c>
       <c r="C186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D186" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>37</v>
+        <v>378</v>
       </c>
       <c r="F186" t="s">
-        <v>38</v>
+        <v>379</v>
       </c>
       <c r="G186" s="1">
         <v>46304</v>
       </c>
       <c r="H186" s="1">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -7723,10 +7948,10 @@
         <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="F187" t="s">
-        <v>389</v>
+        <v>38</v>
       </c>
       <c r="G187" s="1">
         <v>46304</v>
@@ -7740,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -7749,10 +7974,10 @@
         <v>128</v>
       </c>
       <c r="E188" t="s">
-        <v>319</v>
+        <v>37</v>
       </c>
       <c r="F188" t="s">
-        <v>320</v>
+        <v>38</v>
       </c>
       <c r="G188" s="1">
         <v>46304</v>
@@ -7766,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E189" t="s">
         <v>37</v>
@@ -7792,19 +8017,19 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
+        <v>390</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>2</v>
+      </c>
+      <c r="E190" t="s">
+        <v>391</v>
+      </c>
+      <c r="F190" t="s">
         <v>392</v>
-      </c>
-      <c r="C190">
-        <v>1</v>
-      </c>
-      <c r="D190" t="s">
-        <v>128</v>
-      </c>
-      <c r="E190" t="s">
-        <v>393</v>
-      </c>
-      <c r="F190" t="s">
-        <v>394</v>
       </c>
       <c r="G190" s="1">
         <v>46304</v>
@@ -7818,19 +8043,19 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E191" t="s">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="F191" t="s">
-        <v>397</v>
+        <v>320</v>
       </c>
       <c r="G191" s="1">
         <v>46304</v>
@@ -7844,25 +8069,25 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>399</v>
+        <v>37</v>
       </c>
       <c r="F192" t="s">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="G192" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="H192" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -7870,25 +8095,25 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E193" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="F193" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="G193" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="H193" s="1">
-        <v>46310</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -7896,25 +8121,25 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>338</v>
+        <v>399</v>
       </c>
       <c r="F194" t="s">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="G194" s="1">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="H194" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -7922,25 +8147,25 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D195" t="s">
         <v>128</v>
       </c>
       <c r="E195" t="s">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="F195" t="s">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="G195" s="1">
+        <v>46305</v>
+      </c>
+      <c r="H195" s="1">
         <v>46308</v>
-      </c>
-      <c r="H195" s="1">
-        <v>46311</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -7948,25 +8173,25 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
+        <v>404</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+      <c r="D196" t="s">
+        <v>6</v>
+      </c>
+      <c r="E196" t="s">
+        <v>405</v>
+      </c>
+      <c r="F196" t="s">
         <v>406</v>
       </c>
-      <c r="C196">
-        <v>1</v>
-      </c>
-      <c r="D196" t="s">
-        <v>2</v>
-      </c>
-      <c r="E196" t="s">
-        <v>407</v>
-      </c>
-      <c r="F196" t="s">
-        <v>408</v>
-      </c>
       <c r="G196" s="1">
-        <v>46308</v>
+        <v>46305</v>
       </c>
       <c r="H196" s="1">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -7974,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -7983,13 +8208,13 @@
         <v>128</v>
       </c>
       <c r="E197" t="s">
-        <v>276</v>
+        <v>338</v>
       </c>
       <c r="F197" t="s">
-        <v>277</v>
+        <v>339</v>
       </c>
       <c r="G197" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="H197" s="1">
         <v>46308</v>
@@ -8000,25 +8225,25 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" t="s">
         <v>128</v>
       </c>
       <c r="E198" t="s">
-        <v>411</v>
+        <v>80</v>
       </c>
       <c r="F198" t="s">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="G198" s="1">
         <v>46308</v>
       </c>
       <c r="H198" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -8026,7 +8251,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -8035,10 +8260,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F199" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G199" s="1">
         <v>46308</v>
@@ -8052,19 +8277,19 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E200" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="F200" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="G200" s="1">
         <v>46308</v>
@@ -8078,13 +8303,13 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E201" t="s">
         <v>414</v>
@@ -8104,19 +8329,19 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
+        <v>416</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" t="s">
+        <v>417</v>
+      </c>
+      <c r="F202" t="s">
         <v>418</v>
-      </c>
-      <c r="C202">
-        <v>1</v>
-      </c>
-      <c r="D202" t="s">
-        <v>128</v>
-      </c>
-      <c r="E202" t="s">
-        <v>338</v>
-      </c>
-      <c r="F202" t="s">
-        <v>339</v>
       </c>
       <c r="G202" s="1">
         <v>46308</v>
@@ -8136,13 +8361,13 @@
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>399</v>
+        <v>212</v>
       </c>
       <c r="F203" t="s">
-        <v>400</v>
+        <v>213</v>
       </c>
       <c r="G203" s="1">
         <v>46308</v>
@@ -8165,10 +8390,10 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F204" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G204" s="1">
         <v>46308</v>
@@ -8188,13 +8413,13 @@
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E205" t="s">
-        <v>414</v>
+        <v>338</v>
       </c>
       <c r="F205" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
       <c r="G205" s="1">
         <v>46308</v>
@@ -8214,13 +8439,13 @@
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E206" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="F206" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="G206" s="1">
         <v>46308</v>
@@ -8243,10 +8468,10 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F207" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G207" s="1">
         <v>46308</v>
@@ -8266,13 +8491,13 @@
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E208" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="F208" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="G208" s="1">
         <v>46308</v>
@@ -8286,19 +8511,19 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="F209" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="G209" s="1">
         <v>46308</v>
@@ -8312,19 +8537,19 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F210" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="G210" s="1">
         <v>46308</v>
@@ -8338,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -8347,10 +8572,10 @@
         <v>128</v>
       </c>
       <c r="E211" t="s">
-        <v>95</v>
+        <v>428</v>
       </c>
       <c r="F211" t="s">
-        <v>96</v>
+        <v>429</v>
       </c>
       <c r="G211" s="1">
         <v>46308</v>
@@ -8364,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -8373,10 +8598,10 @@
         <v>128</v>
       </c>
       <c r="E212" t="s">
-        <v>172</v>
+        <v>431</v>
       </c>
       <c r="F212" t="s">
-        <v>173</v>
+        <v>432</v>
       </c>
       <c r="G212" s="1">
         <v>46308</v>
@@ -8390,25 +8615,25 @@
         <v>0</v>
       </c>
       <c r="B213" t="s">
+        <v>433</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213" t="s">
+        <v>2</v>
+      </c>
+      <c r="E213" t="s">
+        <v>434</v>
+      </c>
+      <c r="F213" t="s">
         <v>435</v>
-      </c>
-      <c r="C213">
-        <v>1</v>
-      </c>
-      <c r="D213" t="s">
-        <v>128</v>
-      </c>
-      <c r="E213" t="s">
-        <v>388</v>
-      </c>
-      <c r="F213" t="s">
-        <v>389</v>
       </c>
       <c r="G213" s="1">
         <v>46308</v>
       </c>
       <c r="H213" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -8425,16 +8650,16 @@
         <v>128</v>
       </c>
       <c r="E214" t="s">
-        <v>388</v>
+        <v>95</v>
       </c>
       <c r="F214" t="s">
-        <v>389</v>
+        <v>96</v>
       </c>
       <c r="G214" s="1">
         <v>46308</v>
       </c>
       <c r="H214" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -8451,16 +8676,16 @@
         <v>128</v>
       </c>
       <c r="E215" t="s">
-        <v>438</v>
+        <v>172</v>
       </c>
       <c r="F215" t="s">
-        <v>439</v>
+        <v>173</v>
       </c>
       <c r="G215" s="1">
         <v>46308</v>
       </c>
       <c r="H215" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -8468,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -8477,10 +8702,10 @@
         <v>128</v>
       </c>
       <c r="E216" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="F216" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
       <c r="G216" s="1">
         <v>46308</v>
@@ -8494,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8503,10 +8728,10 @@
         <v>128</v>
       </c>
       <c r="E217" t="s">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="F217" t="s">
-        <v>445</v>
+        <v>392</v>
       </c>
       <c r="G217" s="1">
         <v>46308</v>
@@ -8520,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8529,10 +8754,10 @@
         <v>128</v>
       </c>
       <c r="E218" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F218" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G218" s="1">
         <v>46308</v>
@@ -8546,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8555,13 +8780,13 @@
         <v>128</v>
       </c>
       <c r="E219" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F219" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="G219" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="H219" s="1">
         <v>46309</v>
@@ -8572,22 +8797,22 @@
         <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E220" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F220" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G220" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="H220" s="1">
         <v>46309</v>
@@ -8598,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8607,13 +8832,13 @@
         <v>128</v>
       </c>
       <c r="E221" t="s">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="F221" t="s">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="G221" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="H221" s="1">
         <v>46309</v>
@@ -8624,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -8633,10 +8858,10 @@
         <v>128</v>
       </c>
       <c r="E222" t="s">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="F222" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="G222" s="1">
         <v>46309</v>
@@ -8650,19 +8875,19 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
+        <v>455</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>2</v>
+      </c>
+      <c r="E223" t="s">
+        <v>456</v>
+      </c>
+      <c r="F223" t="s">
         <v>457</v>
-      </c>
-      <c r="C223">
-        <v>1</v>
-      </c>
-      <c r="D223" t="s">
-        <v>2</v>
-      </c>
-      <c r="E223" t="s">
-        <v>458</v>
-      </c>
-      <c r="F223" t="s">
-        <v>459</v>
       </c>
       <c r="G223" s="1">
         <v>46309</v>
@@ -8676,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -8685,10 +8910,10 @@
         <v>128</v>
       </c>
       <c r="E224" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F224" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="G224" s="1">
         <v>46309</v>
@@ -8702,19 +8927,19 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>37</v>
+        <v>396</v>
       </c>
       <c r="F225" t="s">
-        <v>38</v>
+        <v>397</v>
       </c>
       <c r="G225" s="1">
         <v>46309</v>
@@ -8728,19 +8953,19 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
+        <v>460</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>2</v>
+      </c>
+      <c r="E226" t="s">
+        <v>461</v>
+      </c>
+      <c r="F226" t="s">
         <v>462</v>
-      </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-      <c r="D226" t="s">
-        <v>128</v>
-      </c>
-      <c r="E226" t="s">
-        <v>37</v>
-      </c>
-      <c r="F226" t="s">
-        <v>38</v>
       </c>
       <c r="G226" s="1">
         <v>46309</v>
@@ -8760,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E227" t="s">
         <v>37</v>
@@ -8809,22 +9034,22 @@
         <v>465</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E229" t="s">
-        <v>466</v>
+        <v>37</v>
       </c>
       <c r="F229" t="s">
-        <v>467</v>
+        <v>38</v>
       </c>
       <c r="G229" s="1">
         <v>46309</v>
       </c>
       <c r="H229" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
@@ -8832,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8841,10 +9066,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>469</v>
+        <v>37</v>
       </c>
       <c r="F230" t="s">
-        <v>470</v>
+        <v>38</v>
       </c>
       <c r="G230" s="1">
         <v>46309</v>
@@ -8858,19 +9083,19 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E231" t="s">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="F231" t="s">
-        <v>473</v>
+        <v>38</v>
       </c>
       <c r="G231" s="1">
         <v>46309</v>
@@ -8884,25 +9109,25 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>285</v>
+        <v>469</v>
       </c>
       <c r="F232" t="s">
-        <v>286</v>
+        <v>470</v>
       </c>
       <c r="G232" s="1">
         <v>46309</v>
       </c>
       <c r="H232" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -8910,19 +9135,19 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F233" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G233" s="1">
         <v>46309</v>
@@ -8936,19 +9161,19 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E234" t="s">
+        <v>475</v>
+      </c>
+      <c r="F234" t="s">
         <v>476</v>
-      </c>
-      <c r="F234" t="s">
-        <v>477</v>
       </c>
       <c r="G234" s="1">
         <v>46309</v>
@@ -8962,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8971,10 +9196,10 @@
         <v>128</v>
       </c>
       <c r="E235" t="s">
-        <v>86</v>
+        <v>285</v>
       </c>
       <c r="F235" t="s">
-        <v>87</v>
+        <v>286</v>
       </c>
       <c r="G235" s="1">
         <v>46309</v>
@@ -8988,19 +9213,19 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
+        <v>478</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="s">
+        <v>128</v>
+      </c>
+      <c r="E236" t="s">
+        <v>479</v>
+      </c>
+      <c r="F236" t="s">
         <v>480</v>
-      </c>
-      <c r="C236">
-        <v>1</v>
-      </c>
-      <c r="D236" t="s">
-        <v>128</v>
-      </c>
-      <c r="E236" t="s">
-        <v>86</v>
-      </c>
-      <c r="F236" t="s">
-        <v>87</v>
       </c>
       <c r="G236" s="1">
         <v>46309</v>
@@ -9023,10 +9248,10 @@
         <v>128</v>
       </c>
       <c r="E237" t="s">
-        <v>86</v>
+        <v>479</v>
       </c>
       <c r="F237" t="s">
-        <v>87</v>
+        <v>480</v>
       </c>
       <c r="G237" s="1">
         <v>46309</v>
@@ -9049,10 +9274,10 @@
         <v>128</v>
       </c>
       <c r="E238" t="s">
-        <v>483</v>
+        <v>86</v>
       </c>
       <c r="F238" t="s">
-        <v>484</v>
+        <v>87</v>
       </c>
       <c r="G238" s="1">
         <v>46309</v>
@@ -9066,7 +9291,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9075,10 +9300,10 @@
         <v>128</v>
       </c>
       <c r="E239" t="s">
-        <v>486</v>
+        <v>86</v>
       </c>
       <c r="F239" t="s">
-        <v>487</v>
+        <v>87</v>
       </c>
       <c r="G239" s="1">
         <v>46309</v>
@@ -9092,7 +9317,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9101,16 +9326,16 @@
         <v>128</v>
       </c>
       <c r="E240" t="s">
-        <v>489</v>
+        <v>86</v>
       </c>
       <c r="F240" t="s">
-        <v>490</v>
+        <v>87</v>
       </c>
       <c r="G240" s="1">
         <v>46309</v>
       </c>
       <c r="H240" s="1">
-        <v>46311</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -9118,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9127,10 +9352,10 @@
         <v>128</v>
       </c>
       <c r="E241" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F241" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G241" s="1">
         <v>46309</v>
@@ -9144,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9153,10 +9378,10 @@
         <v>128</v>
       </c>
       <c r="E242" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="F242" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="G242" s="1">
         <v>46309</v>
@@ -9170,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9179,16 +9404,16 @@
         <v>128</v>
       </c>
       <c r="E243" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F243" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G243" s="1">
         <v>46309</v>
       </c>
       <c r="H243" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -9196,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9205,10 +9430,10 @@
         <v>128</v>
       </c>
       <c r="E244" t="s">
-        <v>219</v>
+        <v>495</v>
       </c>
       <c r="F244" t="s">
-        <v>220</v>
+        <v>496</v>
       </c>
       <c r="G244" s="1">
         <v>46309</v>
@@ -9222,7 +9447,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9231,10 +9456,10 @@
         <v>128</v>
       </c>
       <c r="E245" t="s">
-        <v>338</v>
+        <v>472</v>
       </c>
       <c r="F245" t="s">
-        <v>339</v>
+        <v>473</v>
       </c>
       <c r="G245" s="1">
         <v>46309</v>
@@ -9248,19 +9473,19 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
+        <v>498</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="D246" t="s">
+        <v>128</v>
+      </c>
+      <c r="E246" t="s">
+        <v>499</v>
+      </c>
+      <c r="F246" t="s">
         <v>500</v>
-      </c>
-      <c r="C246">
-        <v>1</v>
-      </c>
-      <c r="D246" t="s">
-        <v>128</v>
-      </c>
-      <c r="E246" t="s">
-        <v>202</v>
-      </c>
-      <c r="F246" t="s">
-        <v>203</v>
       </c>
       <c r="G246" s="1">
         <v>46309</v>
@@ -9283,10 +9508,10 @@
         <v>128</v>
       </c>
       <c r="E247" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F247" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G247" s="1">
         <v>46309</v>
@@ -9309,10 +9534,10 @@
         <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>202</v>
+        <v>338</v>
       </c>
       <c r="F248" t="s">
-        <v>203</v>
+        <v>339</v>
       </c>
       <c r="G248" s="1">
         <v>46309</v>
@@ -9335,10 +9560,10 @@
         <v>128</v>
       </c>
       <c r="E249" t="s">
-        <v>68</v>
+        <v>202</v>
       </c>
       <c r="F249" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="G249" s="1">
         <v>46309</v>
@@ -9361,16 +9586,16 @@
         <v>128</v>
       </c>
       <c r="E250" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="F250" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="G250" s="1">
         <v>46309</v>
       </c>
       <c r="H250" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -9387,10 +9612,10 @@
         <v>128</v>
       </c>
       <c r="E251" t="s">
-        <v>506</v>
+        <v>202</v>
       </c>
       <c r="F251" t="s">
-        <v>507</v>
+        <v>203</v>
       </c>
       <c r="G251" s="1">
         <v>46309</v>
@@ -9404,25 +9629,25 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>450</v>
+        <v>68</v>
       </c>
       <c r="F252" t="s">
-        <v>451</v>
+        <v>69</v>
       </c>
       <c r="G252" s="1">
         <v>46309</v>
       </c>
       <c r="H252" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -9430,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9439,16 +9664,16 @@
         <v>128</v>
       </c>
       <c r="E253" t="s">
-        <v>510</v>
+        <v>172</v>
       </c>
       <c r="F253" t="s">
-        <v>511</v>
+        <v>173</v>
       </c>
       <c r="G253" s="1">
         <v>46309</v>
       </c>
       <c r="H253" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
@@ -9456,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9465,10 +9690,10 @@
         <v>128</v>
       </c>
       <c r="E254" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F254" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G254" s="1">
         <v>46309</v>
@@ -9482,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9491,16 +9716,16 @@
         <v>128</v>
       </c>
       <c r="E255" t="s">
-        <v>516</v>
+        <v>453</v>
       </c>
       <c r="F255" t="s">
-        <v>517</v>
+        <v>454</v>
       </c>
       <c r="G255" s="1">
         <v>46309</v>
       </c>
       <c r="H255" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -9508,7 +9733,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9517,16 +9742,16 @@
         <v>128</v>
       </c>
       <c r="E256" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F256" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G256" s="1">
         <v>46309</v>
       </c>
       <c r="H256" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -9534,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9543,16 +9768,16 @@
         <v>128</v>
       </c>
       <c r="E257" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F257" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="G257" s="1">
         <v>46309</v>
       </c>
       <c r="H257" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -9560,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9569,16 +9794,16 @@
         <v>128</v>
       </c>
       <c r="E258" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F258" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="G258" s="1">
         <v>46309</v>
       </c>
       <c r="H258" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -9586,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9595,10 +9820,10 @@
         <v>128</v>
       </c>
       <c r="E259" t="s">
-        <v>396</v>
+        <v>522</v>
       </c>
       <c r="F259" t="s">
-        <v>397</v>
+        <v>523</v>
       </c>
       <c r="G259" s="1">
         <v>46309</v>
@@ -9612,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9621,10 +9846,10 @@
         <v>128</v>
       </c>
       <c r="E260" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F260" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="G260" s="1">
         <v>46309</v>
@@ -9638,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9647,10 +9872,10 @@
         <v>128</v>
       </c>
       <c r="E261" t="s">
-        <v>77</v>
+        <v>528</v>
       </c>
       <c r="F261" t="s">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="G261" s="1">
         <v>46309</v>
@@ -9664,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9673,10 +9898,10 @@
         <v>128</v>
       </c>
       <c r="E262" t="s">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="F262" t="s">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="G262" s="1">
         <v>46309</v>
@@ -9690,19 +9915,19 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
+        <v>531</v>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+      <c r="D263" t="s">
+        <v>128</v>
+      </c>
+      <c r="E263" t="s">
+        <v>532</v>
+      </c>
+      <c r="F263" t="s">
         <v>533</v>
-      </c>
-      <c r="C263">
-        <v>1</v>
-      </c>
-      <c r="D263" t="s">
-        <v>128</v>
-      </c>
-      <c r="E263" t="s">
-        <v>534</v>
-      </c>
-      <c r="F263" t="s">
-        <v>535</v>
       </c>
       <c r="G263" s="1">
         <v>46309</v>
@@ -9716,7 +9941,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9725,10 +9950,10 @@
         <v>128</v>
       </c>
       <c r="E264" t="s">
-        <v>534</v>
+        <v>77</v>
       </c>
       <c r="F264" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="G264" s="1">
         <v>46309</v>
@@ -9742,19 +9967,19 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E265" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="F265" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="G265" s="1">
         <v>46309</v>
@@ -9768,19 +9993,19 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
+        <v>536</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+      <c r="D266" t="s">
+        <v>128</v>
+      </c>
+      <c r="E266" t="s">
+        <v>537</v>
+      </c>
+      <c r="F266" t="s">
         <v>538</v>
-      </c>
-      <c r="C266">
-        <v>1</v>
-      </c>
-      <c r="D266" t="s">
-        <v>128</v>
-      </c>
-      <c r="E266" t="s">
-        <v>539</v>
-      </c>
-      <c r="F266" t="s">
-        <v>540</v>
       </c>
       <c r="G266" s="1">
         <v>46309</v>
@@ -9794,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9803,10 +10028,10 @@
         <v>128</v>
       </c>
       <c r="E267" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F267" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="G267" s="1">
         <v>46309</v>
@@ -9820,19 +10045,19 @@
         <v>0</v>
       </c>
       <c r="B268" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
       <c r="F268" t="s">
-        <v>339</v>
+        <v>14</v>
       </c>
       <c r="G268" s="1">
         <v>46309</v>
@@ -9846,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9855,10 +10080,10 @@
         <v>128</v>
       </c>
       <c r="E269" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F269" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G269" s="1">
         <v>46309</v>
@@ -9872,19 +10097,19 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E270" t="s">
-        <v>152</v>
+        <v>545</v>
       </c>
       <c r="F270" t="s">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="G270" s="1">
         <v>46309</v>
@@ -9898,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9907,10 +10132,10 @@
         <v>128</v>
       </c>
       <c r="E271" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="F271" t="s">
-        <v>153</v>
+        <v>339</v>
       </c>
       <c r="G271" s="1">
         <v>46309</v>
@@ -9924,19 +10149,19 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
+        <v>548</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272" t="s">
+        <v>128</v>
+      </c>
+      <c r="E272" t="s">
+        <v>549</v>
+      </c>
+      <c r="F272" t="s">
         <v>550</v>
-      </c>
-      <c r="C272">
-        <v>1</v>
-      </c>
-      <c r="D272" t="s">
-        <v>128</v>
-      </c>
-      <c r="E272" t="s">
-        <v>551</v>
-      </c>
-      <c r="F272" t="s">
-        <v>552</v>
       </c>
       <c r="G272" s="1">
         <v>46309</v>
@@ -9950,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9959,10 +10184,10 @@
         <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>554</v>
+        <v>152</v>
       </c>
       <c r="F273" t="s">
-        <v>555</v>
+        <v>153</v>
       </c>
       <c r="G273" s="1">
         <v>46309</v>
@@ -9976,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -9985,13 +10210,13 @@
         <v>128</v>
       </c>
       <c r="E274" t="s">
-        <v>450</v>
+        <v>152</v>
       </c>
       <c r="F274" t="s">
-        <v>451</v>
+        <v>153</v>
       </c>
       <c r="G274" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="H274" s="1">
         <v>46310</v>
@@ -10002,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -10011,13 +10236,13 @@
         <v>128</v>
       </c>
       <c r="E275" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F275" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G275" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="H275" s="1">
         <v>46310</v>
@@ -10028,7 +10253,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -10037,13 +10262,13 @@
         <v>128</v>
       </c>
       <c r="E276" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F276" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="G276" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="H276" s="1">
         <v>46310</v>
@@ -10054,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -10063,10 +10288,10 @@
         <v>128</v>
       </c>
       <c r="E277" t="s">
-        <v>37</v>
+        <v>453</v>
       </c>
       <c r="F277" t="s">
-        <v>38</v>
+        <v>454</v>
       </c>
       <c r="G277" s="1">
         <v>46310</v>
@@ -10080,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -10089,10 +10314,10 @@
         <v>128</v>
       </c>
       <c r="E278" t="s">
-        <v>37</v>
+        <v>561</v>
       </c>
       <c r="F278" t="s">
-        <v>38</v>
+        <v>562</v>
       </c>
       <c r="G278" s="1">
         <v>46310</v>
@@ -10106,19 +10331,19 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
+        <v>563</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279" t="s">
+        <v>128</v>
+      </c>
+      <c r="E279" t="s">
+        <v>564</v>
+      </c>
+      <c r="F279" t="s">
         <v>565</v>
-      </c>
-      <c r="C279">
-        <v>1</v>
-      </c>
-      <c r="D279" t="s">
-        <v>128</v>
-      </c>
-      <c r="E279" t="s">
-        <v>37</v>
-      </c>
-      <c r="F279" t="s">
-        <v>38</v>
       </c>
       <c r="G279" s="1">
         <v>46310</v>
@@ -10323,10 +10548,10 @@
         <v>128</v>
       </c>
       <c r="E287" t="s">
-        <v>574</v>
+        <v>37</v>
       </c>
       <c r="F287" t="s">
-        <v>575</v>
+        <v>38</v>
       </c>
       <c r="G287" s="1">
         <v>46310</v>
@@ -10340,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10349,10 +10574,10 @@
         <v>128</v>
       </c>
       <c r="E288" t="s">
-        <v>577</v>
+        <v>37</v>
       </c>
       <c r="F288" t="s">
-        <v>578</v>
+        <v>38</v>
       </c>
       <c r="G288" s="1">
         <v>46310</v>
@@ -10366,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10375,10 +10600,10 @@
         <v>128</v>
       </c>
       <c r="E289" t="s">
-        <v>252</v>
+        <v>37</v>
       </c>
       <c r="F289" t="s">
-        <v>253</v>
+        <v>38</v>
       </c>
       <c r="G289" s="1">
         <v>46310</v>
@@ -10392,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10401,16 +10626,16 @@
         <v>128</v>
       </c>
       <c r="E290" t="s">
-        <v>525</v>
+        <v>577</v>
       </c>
       <c r="F290" t="s">
-        <v>526</v>
+        <v>578</v>
       </c>
       <c r="G290" s="1">
         <v>46310</v>
       </c>
       <c r="H290" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -10418,19 +10643,19 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
+        <v>579</v>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+      <c r="D291" t="s">
+        <v>128</v>
+      </c>
+      <c r="E291" t="s">
+        <v>580</v>
+      </c>
+      <c r="F291" t="s">
         <v>581</v>
-      </c>
-      <c r="C291">
-        <v>1</v>
-      </c>
-      <c r="D291" t="s">
-        <v>128</v>
-      </c>
-      <c r="E291" t="s">
-        <v>582</v>
-      </c>
-      <c r="F291" t="s">
-        <v>583</v>
       </c>
       <c r="G291" s="1">
         <v>46310</v>
@@ -10444,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -10453,10 +10678,10 @@
         <v>128</v>
       </c>
       <c r="E292" t="s">
-        <v>585</v>
+        <v>252</v>
       </c>
       <c r="F292" t="s">
-        <v>586</v>
+        <v>253</v>
       </c>
       <c r="G292" s="1">
         <v>46310</v>
@@ -10470,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -10479,16 +10704,16 @@
         <v>128</v>
       </c>
       <c r="E293" t="s">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="F293" t="s">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="G293" s="1">
         <v>46310</v>
       </c>
       <c r="H293" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -10496,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10505,10 +10730,10 @@
         <v>128</v>
       </c>
       <c r="E294" t="s">
-        <v>237</v>
+        <v>585</v>
       </c>
       <c r="F294" t="s">
-        <v>238</v>
+        <v>586</v>
       </c>
       <c r="G294" s="1">
         <v>46310</v>
@@ -10522,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -10531,10 +10756,10 @@
         <v>128</v>
       </c>
       <c r="E295" t="s">
-        <v>195</v>
+        <v>588</v>
       </c>
       <c r="F295" t="s">
-        <v>196</v>
+        <v>589</v>
       </c>
       <c r="G295" s="1">
         <v>46310</v>
@@ -10548,19 +10773,19 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
+        <v>590</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+      <c r="D296" t="s">
+        <v>128</v>
+      </c>
+      <c r="E296" t="s">
+        <v>591</v>
+      </c>
+      <c r="F296" t="s">
         <v>592</v>
-      </c>
-      <c r="C296">
-        <v>1</v>
-      </c>
-      <c r="D296" t="s">
-        <v>128</v>
-      </c>
-      <c r="E296" t="s">
-        <v>593</v>
-      </c>
-      <c r="F296" t="s">
-        <v>594</v>
       </c>
       <c r="G296" s="1">
         <v>46310</v>
@@ -10574,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10583,10 +10808,10 @@
         <v>128</v>
       </c>
       <c r="E297" t="s">
-        <v>596</v>
+        <v>237</v>
       </c>
       <c r="F297" t="s">
-        <v>597</v>
+        <v>238</v>
       </c>
       <c r="G297" s="1">
         <v>46310</v>
@@ -10600,19 +10825,19 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D298" t="s">
         <v>128</v>
       </c>
       <c r="E298" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="F298" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="G298" s="1">
         <v>46310</v>
@@ -10626,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10635,10 +10860,10 @@
         <v>128</v>
       </c>
       <c r="E299" t="s">
-        <v>16</v>
+        <v>596</v>
       </c>
       <c r="F299" t="s">
-        <v>17</v>
+        <v>597</v>
       </c>
       <c r="G299" s="1">
         <v>46310</v>
@@ -10652,19 +10877,19 @@
         <v>0</v>
       </c>
       <c r="B300" t="s">
+        <v>598</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+      <c r="D300" t="s">
+        <v>128</v>
+      </c>
+      <c r="E300" t="s">
+        <v>599</v>
+      </c>
+      <c r="F300" t="s">
         <v>600</v>
-      </c>
-      <c r="C300">
-        <v>1</v>
-      </c>
-      <c r="D300" t="s">
-        <v>128</v>
-      </c>
-      <c r="E300" t="s">
-        <v>378</v>
-      </c>
-      <c r="F300" t="s">
-        <v>379</v>
       </c>
       <c r="G300" s="1">
         <v>46310</v>
@@ -10681,16 +10906,16 @@
         <v>601</v>
       </c>
       <c r="C301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>
       </c>
       <c r="E301" t="s">
-        <v>539</v>
+        <v>16</v>
       </c>
       <c r="F301" t="s">
-        <v>540</v>
+        <v>17</v>
       </c>
       <c r="G301" s="1">
         <v>46310</v>
@@ -10713,10 +10938,10 @@
         <v>128</v>
       </c>
       <c r="E302" t="s">
-        <v>603</v>
+        <v>16</v>
       </c>
       <c r="F302" t="s">
-        <v>604</v>
+        <v>17</v>
       </c>
       <c r="G302" s="1">
         <v>46310</v>
@@ -10730,7 +10955,7 @@
         <v>0</v>
       </c>
       <c r="B303" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -10739,10 +10964,10 @@
         <v>128</v>
       </c>
       <c r="E303" t="s">
-        <v>606</v>
+        <v>378</v>
       </c>
       <c r="F303" t="s">
-        <v>607</v>
+        <v>379</v>
       </c>
       <c r="G303" s="1">
         <v>46310</v>
@@ -10756,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -10765,10 +10990,10 @@
         <v>128</v>
       </c>
       <c r="E304" t="s">
-        <v>609</v>
+        <v>542</v>
       </c>
       <c r="F304" t="s">
-        <v>610</v>
+        <v>543</v>
       </c>
       <c r="G304" s="1">
         <v>46310</v>
@@ -10782,7 +11007,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -10791,10 +11016,10 @@
         <v>128</v>
       </c>
       <c r="E305" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F305" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G305" s="1">
         <v>46310</v>
@@ -10808,7 +11033,7 @@
         <v>0</v>
       </c>
       <c r="B306" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -10817,10 +11042,10 @@
         <v>128</v>
       </c>
       <c r="E306" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="F306" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="G306" s="1">
         <v>46310</v>
@@ -10834,7 +11059,7 @@
         <v>0</v>
       </c>
       <c r="B307" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -10843,10 +11068,10 @@
         <v>128</v>
       </c>
       <c r="E307" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="F307" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="G307" s="1">
         <v>46310</v>
@@ -10860,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="B308" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -10869,10 +11094,10 @@
         <v>128</v>
       </c>
       <c r="E308" t="s">
-        <v>16</v>
+        <v>615</v>
       </c>
       <c r="F308" t="s">
-        <v>17</v>
+        <v>616</v>
       </c>
       <c r="G308" s="1">
         <v>46310</v>
@@ -10886,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -10895,10 +11120,10 @@
         <v>128</v>
       </c>
       <c r="E309" t="s">
-        <v>16</v>
+        <v>618</v>
       </c>
       <c r="F309" t="s">
-        <v>17</v>
+        <v>619</v>
       </c>
       <c r="G309" s="1">
         <v>46310</v>
@@ -10912,19 +11137,19 @@
         <v>0</v>
       </c>
       <c r="B310" t="s">
+        <v>620</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+      <c r="D310" t="s">
+        <v>2</v>
+      </c>
+      <c r="E310" t="s">
+        <v>621</v>
+      </c>
+      <c r="F310" t="s">
         <v>622</v>
-      </c>
-      <c r="C310">
-        <v>1</v>
-      </c>
-      <c r="D310" t="s">
-        <v>128</v>
-      </c>
-      <c r="E310" t="s">
-        <v>16</v>
-      </c>
-      <c r="F310" t="s">
-        <v>17</v>
       </c>
       <c r="G310" s="1">
         <v>46310</v>
@@ -10973,10 +11198,10 @@
         <v>128</v>
       </c>
       <c r="E312" t="s">
-        <v>513</v>
+        <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>514</v>
+        <v>17</v>
       </c>
       <c r="G312" s="1">
         <v>46310</v>
@@ -10999,10 +11224,10 @@
         <v>128</v>
       </c>
       <c r="E313" t="s">
-        <v>450</v>
+        <v>16</v>
       </c>
       <c r="F313" t="s">
-        <v>451</v>
+        <v>17</v>
       </c>
       <c r="G313" s="1">
         <v>46310</v>
@@ -11025,10 +11250,10 @@
         <v>128</v>
       </c>
       <c r="E314" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="F314" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="G314" s="1">
         <v>46310</v>
@@ -11051,10 +11276,10 @@
         <v>128</v>
       </c>
       <c r="E315" t="s">
-        <v>628</v>
+        <v>516</v>
       </c>
       <c r="F315" t="s">
-        <v>629</v>
+        <v>517</v>
       </c>
       <c r="G315" s="1">
         <v>46310</v>
@@ -11068,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="B316" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -11077,10 +11302,10 @@
         <v>128</v>
       </c>
       <c r="E316" t="s">
-        <v>542</v>
+        <v>453</v>
       </c>
       <c r="F316" t="s">
-        <v>543</v>
+        <v>454</v>
       </c>
       <c r="G316" s="1">
         <v>46310</v>
@@ -11094,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -11103,10 +11328,10 @@
         <v>128</v>
       </c>
       <c r="E317" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="F317" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="G317" s="1">
         <v>46310</v>
@@ -11120,19 +11345,19 @@
         <v>0</v>
       </c>
       <c r="B318" t="s">
+        <v>630</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318" t="s">
+        <v>128</v>
+      </c>
+      <c r="E318" t="s">
+        <v>631</v>
+      </c>
+      <c r="F318" t="s">
         <v>632</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318" t="s">
-        <v>128</v>
-      </c>
-      <c r="E318" t="s">
-        <v>16</v>
-      </c>
-      <c r="F318" t="s">
-        <v>17</v>
       </c>
       <c r="G318" s="1">
         <v>46310</v>
@@ -11152,13 +11377,13 @@
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E319" t="s">
-        <v>16</v>
+        <v>545</v>
       </c>
       <c r="F319" t="s">
-        <v>17</v>
+        <v>546</v>
       </c>
       <c r="G319" s="1">
         <v>46310</v>
@@ -11181,10 +11406,10 @@
         <v>128</v>
       </c>
       <c r="E320" t="s">
-        <v>635</v>
+        <v>149</v>
       </c>
       <c r="F320" t="s">
-        <v>636</v>
+        <v>150</v>
       </c>
       <c r="G320" s="1">
         <v>46310</v>
@@ -11198,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -11224,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="B322" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -11233,10 +11458,10 @@
         <v>128</v>
       </c>
       <c r="E322" t="s">
-        <v>639</v>
+        <v>16</v>
       </c>
       <c r="F322" t="s">
-        <v>640</v>
+        <v>17</v>
       </c>
       <c r="G322" s="1">
         <v>46310</v>
@@ -11250,7 +11475,7 @@
         <v>0</v>
       </c>
       <c r="B323" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -11259,10 +11484,10 @@
         <v>128</v>
       </c>
       <c r="E323" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F323" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="G323" s="1">
         <v>46310</v>
@@ -11276,7 +11501,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -11285,10 +11510,10 @@
         <v>128</v>
       </c>
       <c r="E324" t="s">
-        <v>645</v>
+        <v>16</v>
       </c>
       <c r="F324" t="s">
-        <v>646</v>
+        <v>17</v>
       </c>
       <c r="G324" s="1">
         <v>46310</v>
@@ -11302,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -11311,16 +11536,16 @@
         <v>128</v>
       </c>
       <c r="E325" t="s">
-        <v>28</v>
+        <v>642</v>
       </c>
       <c r="F325" t="s">
-        <v>29</v>
+        <v>643</v>
       </c>
       <c r="G325" s="1">
         <v>46310</v>
       </c>
       <c r="H325" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
@@ -11328,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -11337,16 +11562,16 @@
         <v>128</v>
       </c>
       <c r="E326" t="s">
-        <v>313</v>
+        <v>645</v>
       </c>
       <c r="F326" t="s">
-        <v>314</v>
+        <v>646</v>
       </c>
       <c r="G326" s="1">
         <v>46310</v>
       </c>
       <c r="H326" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
@@ -11354,25 +11579,25 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
+        <v>647</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327" t="s">
+        <v>128</v>
+      </c>
+      <c r="E327" t="s">
+        <v>648</v>
+      </c>
+      <c r="F327" t="s">
         <v>649</v>
-      </c>
-      <c r="C327">
-        <v>1</v>
-      </c>
-      <c r="D327" t="s">
-        <v>128</v>
-      </c>
-      <c r="E327" t="s">
-        <v>393</v>
-      </c>
-      <c r="F327" t="s">
-        <v>394</v>
       </c>
       <c r="G327" s="1">
         <v>46310</v>
       </c>
       <c r="H327" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
@@ -11389,10 +11614,10 @@
         <v>128</v>
       </c>
       <c r="E328" t="s">
-        <v>651</v>
+        <v>28</v>
       </c>
       <c r="F328" t="s">
-        <v>652</v>
+        <v>29</v>
       </c>
       <c r="G328" s="1">
         <v>46310</v>
@@ -11406,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -11415,10 +11640,10 @@
         <v>128</v>
       </c>
       <c r="E329" t="s">
-        <v>191</v>
+        <v>313</v>
       </c>
       <c r="F329" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
       <c r="G329" s="1">
         <v>46310</v>
@@ -11432,19 +11657,19 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E330" t="s">
-        <v>115</v>
+        <v>396</v>
       </c>
       <c r="F330" t="s">
-        <v>116</v>
+        <v>397</v>
       </c>
       <c r="G330" s="1">
         <v>46310</v>
@@ -11458,19 +11683,19 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
+        <v>653</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331" t="s">
+        <v>128</v>
+      </c>
+      <c r="E331" t="s">
+        <v>654</v>
+      </c>
+      <c r="F331" t="s">
         <v>655</v>
-      </c>
-      <c r="C331">
-        <v>1</v>
-      </c>
-      <c r="D331" t="s">
-        <v>128</v>
-      </c>
-      <c r="E331" t="s">
-        <v>656</v>
-      </c>
-      <c r="F331" t="s">
-        <v>657</v>
       </c>
       <c r="G331" s="1">
         <v>46310</v>
@@ -11484,7 +11709,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -11493,10 +11718,10 @@
         <v>128</v>
       </c>
       <c r="E332" t="s">
-        <v>659</v>
+        <v>191</v>
       </c>
       <c r="F332" t="s">
-        <v>660</v>
+        <v>192</v>
       </c>
       <c r="G332" s="1">
         <v>46310</v>
@@ -11510,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -11519,10 +11744,10 @@
         <v>128</v>
       </c>
       <c r="E333" t="s">
-        <v>388</v>
+        <v>115</v>
       </c>
       <c r="F333" t="s">
-        <v>389</v>
+        <v>116</v>
       </c>
       <c r="G333" s="1">
         <v>46310</v>
@@ -11536,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="B334" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -11551,7 +11776,7 @@
         <v>660</v>
       </c>
       <c r="G334" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="H334" s="1">
         <v>46311</v>
@@ -11562,22 +11787,22 @@
         <v>0</v>
       </c>
       <c r="B335" t="s">
+        <v>661</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+      <c r="D335" t="s">
+        <v>128</v>
+      </c>
+      <c r="E335" t="s">
+        <v>662</v>
+      </c>
+      <c r="F335" t="s">
         <v>663</v>
       </c>
-      <c r="C335">
-        <v>1</v>
-      </c>
-      <c r="D335" t="s">
-        <v>128</v>
-      </c>
-      <c r="E335" t="s">
-        <v>191</v>
-      </c>
-      <c r="F335" t="s">
-        <v>192</v>
-      </c>
       <c r="G335" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="H335" s="1">
         <v>46311</v>
@@ -11597,13 +11822,13 @@
         <v>128</v>
       </c>
       <c r="E336" t="s">
-        <v>628</v>
+        <v>391</v>
       </c>
       <c r="F336" t="s">
-        <v>629</v>
+        <v>392</v>
       </c>
       <c r="G336" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="H336" s="1">
         <v>46311</v>
@@ -11623,10 +11848,10 @@
         <v>128</v>
       </c>
       <c r="E337" t="s">
-        <v>41</v>
+        <v>662</v>
       </c>
       <c r="F337" t="s">
-        <v>42</v>
+        <v>663</v>
       </c>
       <c r="G337" s="1">
         <v>46311</v>
@@ -11649,10 +11874,10 @@
         <v>128</v>
       </c>
       <c r="E338" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F338" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G338" s="1">
         <v>46311</v>
@@ -11675,10 +11900,10 @@
         <v>128</v>
       </c>
       <c r="E339" t="s">
-        <v>668</v>
+        <v>631</v>
       </c>
       <c r="F339" t="s">
-        <v>669</v>
+        <v>632</v>
       </c>
       <c r="G339" s="1">
         <v>46311</v>
@@ -11692,7 +11917,7 @@
         <v>0</v>
       </c>
       <c r="B340" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -11701,10 +11926,10 @@
         <v>128</v>
       </c>
       <c r="E340" t="s">
-        <v>671</v>
+        <v>41</v>
       </c>
       <c r="F340" t="s">
-        <v>672</v>
+        <v>42</v>
       </c>
       <c r="G340" s="1">
         <v>46311</v>
@@ -11718,7 +11943,7 @@
         <v>0</v>
       </c>
       <c r="B341" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -11727,10 +11952,10 @@
         <v>128</v>
       </c>
       <c r="E341" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="F341" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="G341" s="1">
         <v>46311</v>
@@ -11744,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="B342" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -11753,10 +11978,10 @@
         <v>128</v>
       </c>
       <c r="E342" t="s">
-        <v>16</v>
+        <v>671</v>
       </c>
       <c r="F342" t="s">
-        <v>17</v>
+        <v>672</v>
       </c>
       <c r="G342" s="1">
         <v>46311</v>
@@ -11770,19 +11995,19 @@
         <v>0</v>
       </c>
       <c r="B343" t="s">
+        <v>673</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+      <c r="D343" t="s">
+        <v>128</v>
+      </c>
+      <c r="E343" t="s">
+        <v>674</v>
+      </c>
+      <c r="F343" t="s">
         <v>675</v>
-      </c>
-      <c r="C343">
-        <v>1</v>
-      </c>
-      <c r="D343" t="s">
-        <v>128</v>
-      </c>
-      <c r="E343" t="s">
-        <v>16</v>
-      </c>
-      <c r="F343" t="s">
-        <v>17</v>
       </c>
       <c r="G343" s="1">
         <v>46311</v>
@@ -11805,10 +12030,10 @@
         <v>128</v>
       </c>
       <c r="E344" t="s">
-        <v>677</v>
+        <v>16</v>
       </c>
       <c r="F344" t="s">
-        <v>678</v>
+        <v>17</v>
       </c>
       <c r="G344" s="1">
         <v>46311</v>
@@ -11822,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="B345" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -11848,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="B346" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -11857,10 +12082,10 @@
         <v>128</v>
       </c>
       <c r="E346" t="s">
-        <v>681</v>
+        <v>16</v>
       </c>
       <c r="F346" t="s">
-        <v>682</v>
+        <v>17</v>
       </c>
       <c r="G346" s="1">
         <v>46311</v>
@@ -11874,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="B347" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -11883,10 +12108,10 @@
         <v>128</v>
       </c>
       <c r="E347" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F347" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="G347" s="1">
         <v>46311</v>
@@ -11900,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="B348" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -11909,10 +12134,10 @@
         <v>128</v>
       </c>
       <c r="E348" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F348" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G348" s="1">
         <v>46311</v>
@@ -11926,7 +12151,7 @@
         <v>0</v>
       </c>
       <c r="B349" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -11935,10 +12160,10 @@
         <v>128</v>
       </c>
       <c r="E349" t="s">
-        <v>237</v>
+        <v>684</v>
       </c>
       <c r="F349" t="s">
-        <v>238</v>
+        <v>685</v>
       </c>
       <c r="G349" s="1">
         <v>46311</v>
@@ -11952,19 +12177,19 @@
         <v>0</v>
       </c>
       <c r="B350" t="s">
+        <v>686</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="s">
+        <v>2</v>
+      </c>
+      <c r="E350" t="s">
+        <v>687</v>
+      </c>
+      <c r="F350" t="s">
         <v>688</v>
-      </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-      <c r="D350" t="s">
-        <v>128</v>
-      </c>
-      <c r="E350" t="s">
-        <v>689</v>
-      </c>
-      <c r="F350" t="s">
-        <v>690</v>
       </c>
       <c r="G350" s="1">
         <v>46311</v>
@@ -11978,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="B351" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -11987,10 +12212,10 @@
         <v>128</v>
       </c>
       <c r="E351" t="s">
-        <v>692</v>
+        <v>48</v>
       </c>
       <c r="F351" t="s">
-        <v>693</v>
+        <v>49</v>
       </c>
       <c r="G351" s="1">
         <v>46311</v>
@@ -12004,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="B352" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -12013,10 +12238,10 @@
         <v>128</v>
       </c>
       <c r="E352" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="F352" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="G352" s="1">
         <v>46311</v>
@@ -12030,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="B353" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -12039,10 +12264,10 @@
         <v>128</v>
       </c>
       <c r="E353" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F353" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="G353" s="1">
         <v>46311</v>
@@ -12056,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="B354" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -12065,10 +12290,10 @@
         <v>128</v>
       </c>
       <c r="E354" t="s">
-        <v>225</v>
+        <v>695</v>
       </c>
       <c r="F354" t="s">
-        <v>226</v>
+        <v>696</v>
       </c>
       <c r="G354" s="1">
         <v>46311</v>
@@ -12082,7 +12307,7 @@
         <v>0</v>
       </c>
       <c r="B355" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -12091,10 +12316,10 @@
         <v>128</v>
       </c>
       <c r="E355" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F355" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G355" s="1">
         <v>46311</v>
@@ -12108,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="B356" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -12117,10 +12342,10 @@
         <v>128</v>
       </c>
       <c r="E356" t="s">
-        <v>701</v>
+        <v>16</v>
       </c>
       <c r="F356" t="s">
-        <v>702</v>
+        <v>17</v>
       </c>
       <c r="G356" s="1">
         <v>46311</v>
@@ -12134,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="B357" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -12143,10 +12368,10 @@
         <v>128</v>
       </c>
       <c r="E357" t="s">
-        <v>77</v>
+        <v>700</v>
       </c>
       <c r="F357" t="s">
-        <v>78</v>
+        <v>701</v>
       </c>
       <c r="G357" s="1">
         <v>46311</v>
@@ -12157,63 +12382,63 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="B358" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E358" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="F358" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="G358" s="1">
-        <v>46148</v>
+        <v>46311</v>
       </c>
       <c r="H358" s="1">
-        <v>46149</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="B359" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E359" t="s">
-        <v>414</v>
+        <v>74</v>
       </c>
       <c r="F359" t="s">
-        <v>415</v>
+        <v>75</v>
       </c>
       <c r="G359" s="1">
-        <v>46268</v>
+        <v>46311</v>
       </c>
       <c r="H359" s="1">
-        <v>46268</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" t="s">
         <v>704</v>
       </c>
-      <c r="B360" t="s">
-        <v>707</v>
-      </c>
       <c r="C360">
         <v>1</v>
       </c>
@@ -12221,10 +12446,10 @@
         <v>128</v>
       </c>
       <c r="E360" t="s">
-        <v>80</v>
+        <v>705</v>
       </c>
       <c r="F360" t="s">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="G360" s="1">
         <v>46311</v>
@@ -12235,10 +12460,10 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -12247,10 +12472,10 @@
         <v>128</v>
       </c>
       <c r="E361" t="s">
-        <v>709</v>
+        <v>77</v>
       </c>
       <c r="F361" t="s">
-        <v>710</v>
+        <v>78</v>
       </c>
       <c r="G361" s="1">
         <v>46311</v>
@@ -12261,10 +12486,10 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>711</v>
+        <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -12273,388 +12498,388 @@
         <v>128</v>
       </c>
       <c r="E362" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F362" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G362" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H362" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="C363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>709</v>
       </c>
       <c r="F363" t="s">
-        <v>42</v>
+        <v>710</v>
       </c>
       <c r="G363" s="1">
-        <v>46133</v>
+        <v>46311</v>
       </c>
       <c r="H363" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E364" t="s">
-        <v>41</v>
+        <v>453</v>
       </c>
       <c r="F364" t="s">
-        <v>42</v>
+        <v>454</v>
       </c>
       <c r="G364" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
       <c r="H364" s="1">
-        <v>46134</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C365">
         <v>1</v>
       </c>
       <c r="D365" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>19</v>
+        <v>648</v>
       </c>
       <c r="F365" t="s">
-        <v>20</v>
+        <v>649</v>
       </c>
       <c r="G365" s="1">
-        <v>46156</v>
+        <v>46311</v>
       </c>
       <c r="H365" s="1">
-        <v>46156</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C366">
         <v>1</v>
       </c>
       <c r="D366" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E366" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="F366" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="G366" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
       <c r="H366" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
+        <v>0</v>
+      </c>
+      <c r="B367" t="s">
         <v>715</v>
       </c>
-      <c r="B367" t="s">
-        <v>722</v>
-      </c>
       <c r="C367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E367" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="F367" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="G367" s="1">
-        <v>46253</v>
+        <v>46311</v>
       </c>
       <c r="H367" s="1">
-        <v>46253</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E368" t="s">
-        <v>172</v>
+        <v>716</v>
       </c>
       <c r="F368" t="s">
-        <v>173</v>
+        <v>717</v>
       </c>
       <c r="G368" s="1">
-        <v>46273</v>
+        <v>46311</v>
       </c>
       <c r="H368" s="1">
-        <v>46274</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="C369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="s">
         <v>128</v>
       </c>
       <c r="E369" t="s">
-        <v>727</v>
+        <v>219</v>
       </c>
       <c r="F369" t="s">
-        <v>728</v>
+        <v>220</v>
       </c>
       <c r="G369" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H369" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="C370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E370" t="s">
-        <v>182</v>
+        <v>721</v>
       </c>
       <c r="F370" t="s">
-        <v>183</v>
+        <v>722</v>
       </c>
       <c r="G370" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H370" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E371" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="F371" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="G371" s="1">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H371" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="C372">
         <v>1</v>
       </c>
       <c r="D372" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E372" t="s">
-        <v>304</v>
+        <v>721</v>
       </c>
       <c r="F372" t="s">
-        <v>305</v>
+        <v>722</v>
       </c>
       <c r="G372" s="1">
-        <v>46302</v>
+        <v>46311</v>
       </c>
       <c r="H372" s="1">
-        <v>46302</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="C373">
         <v>1</v>
       </c>
       <c r="D373" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E373" t="s">
-        <v>733</v>
+        <v>370</v>
       </c>
       <c r="F373" t="s">
-        <v>734</v>
+        <v>371</v>
       </c>
       <c r="G373" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="H373" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="C374">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D374" t="s">
         <v>128</v>
       </c>
       <c r="E374" t="s">
-        <v>149</v>
+        <v>304</v>
       </c>
       <c r="F374" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="G374" s="1">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="H374" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="C375">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D375" t="s">
         <v>128</v>
       </c>
       <c r="E375" t="s">
-        <v>737</v>
+        <v>414</v>
       </c>
       <c r="F375" t="s">
-        <v>738</v>
+        <v>415</v>
       </c>
       <c r="G375" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H375" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="C376">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E376" t="s">
-        <v>737</v>
+        <v>399</v>
       </c>
       <c r="F376" t="s">
-        <v>738</v>
+        <v>400</v>
       </c>
       <c r="G376" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="H376" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -12663,24 +12888,24 @@
         <v>128</v>
       </c>
       <c r="E377" t="s">
-        <v>506</v>
+        <v>730</v>
       </c>
       <c r="F377" t="s">
-        <v>507</v>
+        <v>731</v>
       </c>
       <c r="G377" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="H377" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -12689,24 +12914,24 @@
         <v>128</v>
       </c>
       <c r="E378" t="s">
-        <v>618</v>
+        <v>730</v>
       </c>
       <c r="F378" t="s">
-        <v>619</v>
+        <v>731</v>
       </c>
       <c r="G378" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H378" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="C379">
         <v>1</v>
@@ -12715,24 +12940,24 @@
         <v>128</v>
       </c>
       <c r="E379" t="s">
-        <v>149</v>
+        <v>734</v>
       </c>
       <c r="F379" t="s">
-        <v>150</v>
+        <v>735</v>
       </c>
       <c r="G379" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H379" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -12741,10 +12966,10 @@
         <v>128</v>
       </c>
       <c r="E380" t="s">
-        <v>41</v>
+        <v>737</v>
       </c>
       <c r="F380" t="s">
-        <v>42</v>
+        <v>738</v>
       </c>
       <c r="G380" s="1">
         <v>46311</v>
@@ -12755,163 +12980,163 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C381">
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E381" t="s">
-        <v>746</v>
+        <v>7</v>
       </c>
       <c r="F381" t="s">
-        <v>747</v>
+        <v>8</v>
       </c>
       <c r="G381" s="1">
-        <v>46063</v>
+        <v>46311</v>
       </c>
       <c r="H381" s="1">
-        <v>46064</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="C382">
         <v>1</v>
       </c>
       <c r="D382" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E382" t="s">
-        <v>57</v>
+        <v>741</v>
       </c>
       <c r="F382" t="s">
-        <v>58</v>
+        <v>742</v>
       </c>
       <c r="G382" s="1">
-        <v>46113</v>
+        <v>46311</v>
       </c>
       <c r="H382" s="1">
-        <v>46125</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C383">
         <v>1</v>
       </c>
       <c r="D383" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E383" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F383" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="G383" s="1">
-        <v>46125</v>
+        <v>46311</v>
       </c>
       <c r="H383" s="1">
-        <v>46125</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
+        <v>0</v>
+      </c>
+      <c r="B384" t="s">
         <v>744</v>
       </c>
-      <c r="B384" t="s">
-        <v>750</v>
-      </c>
       <c r="C384">
         <v>1</v>
       </c>
       <c r="D384" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E384" t="s">
-        <v>57</v>
+        <v>745</v>
       </c>
       <c r="F384" t="s">
-        <v>58</v>
+        <v>746</v>
       </c>
       <c r="G384" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
       <c r="H384" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E385" t="s">
-        <v>57</v>
+        <v>748</v>
       </c>
       <c r="F385" t="s">
-        <v>58</v>
+        <v>749</v>
       </c>
       <c r="G385" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
       <c r="H385" s="1">
-        <v>46126</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B386" t="s">
+        <v>750</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>128</v>
+      </c>
+      <c r="E386" t="s">
+        <v>751</v>
+      </c>
+      <c r="F386" t="s">
         <v>752</v>
       </c>
-      <c r="C386">
-        <v>1</v>
-      </c>
-      <c r="D386" t="s">
-        <v>2</v>
-      </c>
-      <c r="E386" t="s">
-        <v>57</v>
-      </c>
-      <c r="F386" t="s">
-        <v>58</v>
-      </c>
       <c r="G386" s="1">
-        <v>46128</v>
+        <v>46311</v>
       </c>
       <c r="H386" s="1">
-        <v>46128</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B387" t="s">
         <v>753</v>
@@ -12920,24 +13145,24 @@
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E387" t="s">
-        <v>57</v>
+        <v>751</v>
       </c>
       <c r="F387" t="s">
-        <v>58</v>
+        <v>752</v>
       </c>
       <c r="G387" s="1">
-        <v>46132</v>
+        <v>46311</v>
       </c>
       <c r="H387" s="1">
-        <v>46132</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B388" t="s">
         <v>754</v>
@@ -12946,209 +13171,209 @@
         <v>1</v>
       </c>
       <c r="D388" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E388" t="s">
-        <v>57</v>
+        <v>755</v>
       </c>
       <c r="F388" t="s">
-        <v>58</v>
+        <v>756</v>
       </c>
       <c r="G388" s="1">
-        <v>46161</v>
+        <v>46311</v>
       </c>
       <c r="H388" s="1">
-        <v>46161</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C389">
         <v>1</v>
       </c>
       <c r="D389" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E389" t="s">
-        <v>57</v>
+        <v>606</v>
       </c>
       <c r="F389" t="s">
-        <v>58</v>
+        <v>607</v>
       </c>
       <c r="G389" s="1">
-        <v>46174</v>
+        <v>46311</v>
       </c>
       <c r="H389" s="1">
-        <v>46174</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C390">
         <v>1</v>
       </c>
       <c r="D390" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E390" t="s">
-        <v>57</v>
+        <v>759</v>
       </c>
       <c r="F390" t="s">
-        <v>58</v>
+        <v>760</v>
       </c>
       <c r="G390" s="1">
-        <v>46174</v>
+        <v>46311</v>
       </c>
       <c r="H390" s="1">
-        <v>46174</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C391">
         <v>1</v>
       </c>
       <c r="D391" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E391" t="s">
-        <v>57</v>
+        <v>580</v>
       </c>
       <c r="F391" t="s">
-        <v>58</v>
+        <v>581</v>
       </c>
       <c r="G391" s="1">
-        <v>46195</v>
+        <v>46311</v>
       </c>
       <c r="H391" s="1">
-        <v>46252</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C392">
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E392" t="s">
-        <v>57</v>
+        <v>759</v>
       </c>
       <c r="F392" t="s">
-        <v>58</v>
+        <v>760</v>
       </c>
       <c r="G392" s="1">
-        <v>46210</v>
+        <v>46311</v>
       </c>
       <c r="H392" s="1">
-        <v>46210</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C393">
         <v>1</v>
       </c>
       <c r="D393" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E393" t="s">
-        <v>57</v>
+        <v>764</v>
       </c>
       <c r="F393" t="s">
-        <v>58</v>
+        <v>765</v>
       </c>
       <c r="G393" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
       <c r="H393" s="1">
-        <v>46213</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C394">
         <v>1</v>
       </c>
       <c r="D394" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E394" t="s">
-        <v>57</v>
+        <v>767</v>
       </c>
       <c r="F394" t="s">
-        <v>58</v>
+        <v>768</v>
       </c>
       <c r="G394" s="1">
-        <v>46218</v>
+        <v>46311</v>
       </c>
       <c r="H394" s="1">
-        <v>46252</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C395">
         <v>1</v>
       </c>
       <c r="D395" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E395" t="s">
-        <v>77</v>
+        <v>770</v>
       </c>
       <c r="F395" t="s">
-        <v>78</v>
+        <v>771</v>
       </c>
       <c r="G395" s="1">
-        <v>46226</v>
+        <v>46311</v>
       </c>
       <c r="H395" s="1">
-        <v>46226</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="C396">
         <v>1</v>
@@ -13157,258 +13382,258 @@
         <v>128</v>
       </c>
       <c r="E396" t="s">
-        <v>57</v>
+        <v>351</v>
       </c>
       <c r="F396" t="s">
-        <v>58</v>
+        <v>352</v>
       </c>
       <c r="G396" s="1">
-        <v>46227</v>
+        <v>46311</v>
       </c>
       <c r="H396" s="1">
-        <v>46252</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="C397">
         <v>1</v>
       </c>
       <c r="D397" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E397" t="s">
-        <v>57</v>
+        <v>764</v>
       </c>
       <c r="F397" t="s">
-        <v>58</v>
+        <v>765</v>
       </c>
       <c r="G397" s="1">
-        <v>46227</v>
+        <v>46311</v>
       </c>
       <c r="H397" s="1">
-        <v>46252</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="C398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E398" t="s">
-        <v>57</v>
+        <v>775</v>
       </c>
       <c r="F398" t="s">
-        <v>58</v>
+        <v>776</v>
       </c>
       <c r="G398" s="1">
-        <v>46227</v>
+        <v>46311</v>
       </c>
       <c r="H398" s="1">
-        <v>46228</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B399" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="C399">
         <v>1</v>
       </c>
       <c r="D399" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E399" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="F399" t="s">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="G399" s="1">
-        <v>46230</v>
+        <v>46311</v>
       </c>
       <c r="H399" s="1">
-        <v>46252</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C400">
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E400" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F400" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="G400" s="1">
-        <v>46231</v>
+        <v>46311</v>
       </c>
       <c r="H400" s="1">
-        <v>46231</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="C401">
         <v>1</v>
       </c>
       <c r="D401" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E401" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F401" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="G401" s="1">
-        <v>46254</v>
+        <v>46311</v>
       </c>
       <c r="H401" s="1">
-        <v>46254</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="C402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E402" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F402" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="G402" s="1">
-        <v>46255</v>
+        <v>46311</v>
       </c>
       <c r="H402" s="1">
-        <v>46255</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>744</v>
+        <v>0</v>
       </c>
       <c r="B403" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="C403">
         <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E403" t="s">
-        <v>57</v>
+        <v>767</v>
       </c>
       <c r="F403" t="s">
-        <v>58</v>
+        <v>768</v>
       </c>
       <c r="G403" s="1">
-        <v>46260</v>
+        <v>46311</v>
       </c>
       <c r="H403" s="1">
-        <v>46260</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="B404" t="s">
-        <v>770</v>
+        <v>783</v>
       </c>
       <c r="C404">
         <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E404" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="F404" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="G404" s="1">
-        <v>46289</v>
+        <v>46148</v>
       </c>
       <c r="H404" s="1">
-        <v>46289</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="B405" t="s">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="C405">
         <v>1</v>
       </c>
       <c r="D405" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E405" t="s">
-        <v>57</v>
+        <v>417</v>
       </c>
       <c r="F405" t="s">
-        <v>58</v>
+        <v>418</v>
       </c>
       <c r="G405" s="1">
-        <v>46294</v>
+        <v>46268</v>
       </c>
       <c r="H405" s="1">
-        <v>46294</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="B406" t="s">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="C406">
         <v>1</v>
@@ -13417,10 +13642,10 @@
         <v>128</v>
       </c>
       <c r="E406" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F406" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G406" s="1">
         <v>46311</v>
@@ -13431,10 +13656,10 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="B407" t="s">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="C407">
         <v>1</v>
@@ -13443,10 +13668,10 @@
         <v>128</v>
       </c>
       <c r="E407" t="s">
-        <v>57</v>
+        <v>787</v>
       </c>
       <c r="F407" t="s">
-        <v>58</v>
+        <v>788</v>
       </c>
       <c r="G407" s="1">
         <v>46311</v>
@@ -13457,166 +13682,166 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="B408" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="C408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E408" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="F408" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="G408" s="1">
-        <v>46157</v>
+        <v>46308</v>
       </c>
       <c r="H408" s="1">
-        <v>46157</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B409" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="C409">
         <v>1</v>
       </c>
       <c r="D409" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E409" t="s">
-        <v>779</v>
+        <v>41</v>
       </c>
       <c r="F409" t="s">
-        <v>780</v>
+        <v>42</v>
       </c>
       <c r="G409" s="1">
-        <v>46168</v>
+        <v>46133</v>
       </c>
       <c r="H409" s="1">
-        <v>46170</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B410" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="C410">
         <v>1</v>
       </c>
       <c r="D410" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E410" t="s">
-        <v>776</v>
+        <v>41</v>
       </c>
       <c r="F410" t="s">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G410" s="1">
-        <v>46218</v>
+        <v>46134</v>
       </c>
       <c r="H410" s="1">
-        <v>46218</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B411" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="C411">
         <v>1</v>
       </c>
       <c r="D411" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E411" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="F411" t="s">
-        <v>777</v>
+        <v>20</v>
       </c>
       <c r="G411" s="1">
-        <v>46244</v>
+        <v>46156</v>
       </c>
       <c r="H411" s="1">
-        <v>46244</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B412" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="C412">
         <v>1</v>
       </c>
       <c r="D412" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E412" t="s">
-        <v>776</v>
+        <v>798</v>
       </c>
       <c r="F412" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="G412" s="1">
-        <v>46247</v>
+        <v>46213</v>
       </c>
       <c r="H412" s="1">
-        <v>46247</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B413" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="C413">
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E413" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="F413" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="G413" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="H413" s="1">
-        <v>46247</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B414" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="C414">
         <v>1</v>
@@ -13625,50 +13850,50 @@
         <v>2</v>
       </c>
       <c r="E414" t="s">
-        <v>776</v>
+        <v>172</v>
       </c>
       <c r="F414" t="s">
-        <v>777</v>
+        <v>173</v>
       </c>
       <c r="G414" s="1">
-        <v>46255</v>
+        <v>46273</v>
       </c>
       <c r="H414" s="1">
-        <v>46255</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B415" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="C415">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D415" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E415" t="s">
-        <v>776</v>
+        <v>805</v>
       </c>
       <c r="F415" t="s">
-        <v>777</v>
+        <v>806</v>
       </c>
       <c r="G415" s="1">
-        <v>46258</v>
+        <v>46300</v>
       </c>
       <c r="H415" s="1">
-        <v>46258</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B416" t="s">
-        <v>789</v>
+        <v>807</v>
       </c>
       <c r="C416">
         <v>1</v>
@@ -13677,68 +13902,1238 @@
         <v>2</v>
       </c>
       <c r="E416" t="s">
-        <v>776</v>
+        <v>182</v>
       </c>
       <c r="F416" t="s">
-        <v>777</v>
+        <v>183</v>
       </c>
       <c r="G416" s="1">
-        <v>46262</v>
+        <v>46300</v>
       </c>
       <c r="H416" s="1">
-        <v>46265</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B417" t="s">
-        <v>790</v>
+        <v>808</v>
       </c>
       <c r="C417">
         <v>1</v>
       </c>
       <c r="D417" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E417" t="s">
-        <v>13</v>
+        <v>787</v>
       </c>
       <c r="F417" t="s">
-        <v>14</v>
+        <v>788</v>
       </c>
       <c r="G417" s="1">
-        <v>46281</v>
+        <v>46300</v>
       </c>
       <c r="H417" s="1">
-        <v>46283</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B418" t="s">
-        <v>791</v>
+        <v>809</v>
       </c>
       <c r="C418">
         <v>1</v>
       </c>
       <c r="D418" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E418" t="s">
+        <v>304</v>
+      </c>
+      <c r="F418" t="s">
+        <v>305</v>
+      </c>
+      <c r="G418" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H418" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>793</v>
+      </c>
+      <c r="B419" t="s">
+        <v>810</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419" t="s">
+        <v>6</v>
+      </c>
+      <c r="E419" t="s">
+        <v>745</v>
+      </c>
+      <c r="F419" t="s">
+        <v>746</v>
+      </c>
+      <c r="G419" s="1">
+        <v>46303</v>
+      </c>
+      <c r="H419" s="1">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>793</v>
+      </c>
+      <c r="B420" t="s">
+        <v>811</v>
+      </c>
+      <c r="C420">
+        <v>2</v>
+      </c>
+      <c r="D420" t="s">
+        <v>128</v>
+      </c>
+      <c r="E420" t="s">
+        <v>149</v>
+      </c>
+      <c r="F420" t="s">
+        <v>150</v>
+      </c>
+      <c r="G420" s="1">
+        <v>46303</v>
+      </c>
+      <c r="H420" s="1">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>793</v>
+      </c>
+      <c r="B421" t="s">
+        <v>812</v>
+      </c>
+      <c r="C421">
+        <v>2</v>
+      </c>
+      <c r="D421" t="s">
+        <v>128</v>
+      </c>
+      <c r="E421" t="s">
+        <v>813</v>
+      </c>
+      <c r="F421" t="s">
+        <v>814</v>
+      </c>
+      <c r="G421" s="1">
+        <v>46308</v>
+      </c>
+      <c r="H421" s="1">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>793</v>
+      </c>
+      <c r="B422" t="s">
+        <v>815</v>
+      </c>
+      <c r="C422">
+        <v>2</v>
+      </c>
+      <c r="D422" t="s">
+        <v>6</v>
+      </c>
+      <c r="E422" t="s">
+        <v>813</v>
+      </c>
+      <c r="F422" t="s">
+        <v>814</v>
+      </c>
+      <c r="G422" s="1">
+        <v>46308</v>
+      </c>
+      <c r="H422" s="1">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>793</v>
+      </c>
+      <c r="B423" t="s">
+        <v>816</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423" t="s">
+        <v>128</v>
+      </c>
+      <c r="E423" t="s">
+        <v>509</v>
+      </c>
+      <c r="F423" t="s">
+        <v>510</v>
+      </c>
+      <c r="G423" s="1">
+        <v>46309</v>
+      </c>
+      <c r="H423" s="1">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>793</v>
+      </c>
+      <c r="B424" t="s">
+        <v>817</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424" t="s">
+        <v>2</v>
+      </c>
+      <c r="E424" t="s">
+        <v>621</v>
+      </c>
+      <c r="F424" t="s">
+        <v>622</v>
+      </c>
+      <c r="G424" s="1">
+        <v>46310</v>
+      </c>
+      <c r="H424" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>793</v>
+      </c>
+      <c r="B425" t="s">
+        <v>818</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425" t="s">
+        <v>128</v>
+      </c>
+      <c r="E425" t="s">
+        <v>149</v>
+      </c>
+      <c r="F425" t="s">
+        <v>150</v>
+      </c>
+      <c r="G425" s="1">
+        <v>46310</v>
+      </c>
+      <c r="H425" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>793</v>
+      </c>
+      <c r="B426" t="s">
+        <v>819</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+      <c r="D426" t="s">
+        <v>128</v>
+      </c>
+      <c r="E426" t="s">
+        <v>41</v>
+      </c>
+      <c r="F426" t="s">
+        <v>42</v>
+      </c>
+      <c r="G426" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H426" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>793</v>
+      </c>
+      <c r="B427" t="s">
+        <v>820</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+      <c r="D427" t="s">
+        <v>128</v>
+      </c>
+      <c r="E427" t="s">
+        <v>304</v>
+      </c>
+      <c r="F427" t="s">
+        <v>305</v>
+      </c>
+      <c r="G427" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H427" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>821</v>
+      </c>
+      <c r="B428" t="s">
+        <v>822</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428" t="s">
+        <v>2</v>
+      </c>
+      <c r="E428" t="s">
+        <v>823</v>
+      </c>
+      <c r="F428" t="s">
+        <v>824</v>
+      </c>
+      <c r="G428" s="1">
+        <v>46063</v>
+      </c>
+      <c r="H428" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>821</v>
+      </c>
+      <c r="B429" t="s">
+        <v>825</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
+      <c r="D429" t="s">
+        <v>6</v>
+      </c>
+      <c r="E429" t="s">
         <v>57</v>
       </c>
-      <c r="F418" t="s">
+      <c r="F429" t="s">
         <v>58</v>
       </c>
-      <c r="G418" s="1">
-        <v>46311</v>
-      </c>
-      <c r="H418" s="1">
-        <v>46311</v>
+      <c r="G429" s="1">
+        <v>46113</v>
+      </c>
+      <c r="H429" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>821</v>
+      </c>
+      <c r="B430" t="s">
+        <v>826</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>2</v>
+      </c>
+      <c r="E430" t="s">
+        <v>57</v>
+      </c>
+      <c r="F430" t="s">
+        <v>58</v>
+      </c>
+      <c r="G430" s="1">
+        <v>46125</v>
+      </c>
+      <c r="H430" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>821</v>
+      </c>
+      <c r="B431" t="s">
+        <v>827</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431" t="s">
+        <v>2</v>
+      </c>
+      <c r="E431" t="s">
+        <v>57</v>
+      </c>
+      <c r="F431" t="s">
+        <v>58</v>
+      </c>
+      <c r="G431" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H431" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>821</v>
+      </c>
+      <c r="B432" t="s">
+        <v>828</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+      <c r="D432" t="s">
+        <v>2</v>
+      </c>
+      <c r="E432" t="s">
+        <v>57</v>
+      </c>
+      <c r="F432" t="s">
+        <v>58</v>
+      </c>
+      <c r="G432" s="1">
+        <v>46126</v>
+      </c>
+      <c r="H432" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>821</v>
+      </c>
+      <c r="B433" t="s">
+        <v>829</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433" t="s">
+        <v>2</v>
+      </c>
+      <c r="E433" t="s">
+        <v>57</v>
+      </c>
+      <c r="F433" t="s">
+        <v>58</v>
+      </c>
+      <c r="G433" s="1">
+        <v>46128</v>
+      </c>
+      <c r="H433" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>821</v>
+      </c>
+      <c r="B434" t="s">
+        <v>830</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434" t="s">
+        <v>6</v>
+      </c>
+      <c r="E434" t="s">
+        <v>57</v>
+      </c>
+      <c r="F434" t="s">
+        <v>58</v>
+      </c>
+      <c r="G434" s="1">
+        <v>46132</v>
+      </c>
+      <c r="H434" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>821</v>
+      </c>
+      <c r="B435" t="s">
+        <v>831</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435" t="s">
+        <v>2</v>
+      </c>
+      <c r="E435" t="s">
+        <v>57</v>
+      </c>
+      <c r="F435" t="s">
+        <v>58</v>
+      </c>
+      <c r="G435" s="1">
+        <v>46161</v>
+      </c>
+      <c r="H435" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>821</v>
+      </c>
+      <c r="B436" t="s">
+        <v>832</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436" t="s">
+        <v>2</v>
+      </c>
+      <c r="E436" t="s">
+        <v>57</v>
+      </c>
+      <c r="F436" t="s">
+        <v>58</v>
+      </c>
+      <c r="G436" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H436" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>821</v>
+      </c>
+      <c r="B437" t="s">
+        <v>833</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437" t="s">
+        <v>2</v>
+      </c>
+      <c r="E437" t="s">
+        <v>57</v>
+      </c>
+      <c r="F437" t="s">
+        <v>58</v>
+      </c>
+      <c r="G437" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H437" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>821</v>
+      </c>
+      <c r="B438" t="s">
+        <v>834</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+      <c r="D438" t="s">
+        <v>6</v>
+      </c>
+      <c r="E438" t="s">
+        <v>57</v>
+      </c>
+      <c r="F438" t="s">
+        <v>58</v>
+      </c>
+      <c r="G438" s="1">
+        <v>46195</v>
+      </c>
+      <c r="H438" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>821</v>
+      </c>
+      <c r="B439" t="s">
+        <v>835</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+      <c r="D439" t="s">
+        <v>6</v>
+      </c>
+      <c r="E439" t="s">
+        <v>57</v>
+      </c>
+      <c r="F439" t="s">
+        <v>58</v>
+      </c>
+      <c r="G439" s="1">
+        <v>46210</v>
+      </c>
+      <c r="H439" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>821</v>
+      </c>
+      <c r="B440" t="s">
+        <v>836</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+      <c r="D440" t="s">
+        <v>2</v>
+      </c>
+      <c r="E440" t="s">
+        <v>57</v>
+      </c>
+      <c r="F440" t="s">
+        <v>58</v>
+      </c>
+      <c r="G440" s="1">
+        <v>46213</v>
+      </c>
+      <c r="H440" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>821</v>
+      </c>
+      <c r="B441" t="s">
+        <v>837</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+      <c r="D441" t="s">
+        <v>6</v>
+      </c>
+      <c r="E441" t="s">
+        <v>57</v>
+      </c>
+      <c r="F441" t="s">
+        <v>58</v>
+      </c>
+      <c r="G441" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H441" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>821</v>
+      </c>
+      <c r="B442" t="s">
+        <v>838</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+      <c r="D442" t="s">
+        <v>6</v>
+      </c>
+      <c r="E442" t="s">
+        <v>77</v>
+      </c>
+      <c r="F442" t="s">
+        <v>78</v>
+      </c>
+      <c r="G442" s="1">
+        <v>46226</v>
+      </c>
+      <c r="H442" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>821</v>
+      </c>
+      <c r="B443" t="s">
+        <v>839</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+      <c r="D443" t="s">
+        <v>128</v>
+      </c>
+      <c r="E443" t="s">
+        <v>57</v>
+      </c>
+      <c r="F443" t="s">
+        <v>58</v>
+      </c>
+      <c r="G443" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H443" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>821</v>
+      </c>
+      <c r="B444" t="s">
+        <v>840</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+      <c r="D444" t="s">
+        <v>6</v>
+      </c>
+      <c r="E444" t="s">
+        <v>57</v>
+      </c>
+      <c r="F444" t="s">
+        <v>58</v>
+      </c>
+      <c r="G444" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H444" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>821</v>
+      </c>
+      <c r="B445" t="s">
+        <v>841</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+      <c r="D445" t="s">
+        <v>6</v>
+      </c>
+      <c r="E445" t="s">
+        <v>57</v>
+      </c>
+      <c r="F445" t="s">
+        <v>58</v>
+      </c>
+      <c r="G445" s="1">
+        <v>46227</v>
+      </c>
+      <c r="H445" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>821</v>
+      </c>
+      <c r="B446" t="s">
+        <v>842</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446" t="s">
+        <v>6</v>
+      </c>
+      <c r="E446" t="s">
+        <v>77</v>
+      </c>
+      <c r="F446" t="s">
+        <v>78</v>
+      </c>
+      <c r="G446" s="1">
+        <v>46230</v>
+      </c>
+      <c r="H446" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>821</v>
+      </c>
+      <c r="B447" t="s">
+        <v>843</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447" t="s">
+        <v>6</v>
+      </c>
+      <c r="E447" t="s">
+        <v>57</v>
+      </c>
+      <c r="F447" t="s">
+        <v>58</v>
+      </c>
+      <c r="G447" s="1">
+        <v>46231</v>
+      </c>
+      <c r="H447" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>821</v>
+      </c>
+      <c r="B448" t="s">
+        <v>844</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+      <c r="D448" t="s">
+        <v>6</v>
+      </c>
+      <c r="E448" t="s">
+        <v>57</v>
+      </c>
+      <c r="F448" t="s">
+        <v>58</v>
+      </c>
+      <c r="G448" s="1">
+        <v>46254</v>
+      </c>
+      <c r="H448" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>821</v>
+      </c>
+      <c r="B449" t="s">
+        <v>845</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449" t="s">
+        <v>2</v>
+      </c>
+      <c r="E449" t="s">
+        <v>57</v>
+      </c>
+      <c r="F449" t="s">
+        <v>58</v>
+      </c>
+      <c r="G449" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H449" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>821</v>
+      </c>
+      <c r="B450" t="s">
+        <v>846</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+      <c r="D450" t="s">
+        <v>6</v>
+      </c>
+      <c r="E450" t="s">
+        <v>57</v>
+      </c>
+      <c r="F450" t="s">
+        <v>58</v>
+      </c>
+      <c r="G450" s="1">
+        <v>46260</v>
+      </c>
+      <c r="H450" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>821</v>
+      </c>
+      <c r="B451" t="s">
+        <v>847</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451" t="s">
+        <v>6</v>
+      </c>
+      <c r="E451" t="s">
+        <v>57</v>
+      </c>
+      <c r="F451" t="s">
+        <v>58</v>
+      </c>
+      <c r="G451" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H451" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>821</v>
+      </c>
+      <c r="B452" t="s">
+        <v>848</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+      <c r="D452" t="s">
+        <v>6</v>
+      </c>
+      <c r="E452" t="s">
+        <v>57</v>
+      </c>
+      <c r="F452" t="s">
+        <v>58</v>
+      </c>
+      <c r="G452" s="1">
+        <v>46294</v>
+      </c>
+      <c r="H452" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>821</v>
+      </c>
+      <c r="B453" t="s">
+        <v>849</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
+      </c>
+      <c r="D453" t="s">
+        <v>128</v>
+      </c>
+      <c r="E453" t="s">
+        <v>57</v>
+      </c>
+      <c r="F453" t="s">
+        <v>58</v>
+      </c>
+      <c r="G453" s="1">
+        <v>46311</v>
+      </c>
+      <c r="H453" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>850</v>
+      </c>
+      <c r="B454" t="s">
+        <v>851</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>2</v>
+      </c>
+      <c r="E454" t="s">
+        <v>852</v>
+      </c>
+      <c r="F454" t="s">
+        <v>853</v>
+      </c>
+      <c r="G454" s="1">
+        <v>46157</v>
+      </c>
+      <c r="H454" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>850</v>
+      </c>
+      <c r="B455" t="s">
+        <v>854</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+      <c r="D455" t="s">
+        <v>2</v>
+      </c>
+      <c r="E455" t="s">
+        <v>855</v>
+      </c>
+      <c r="F455" t="s">
+        <v>856</v>
+      </c>
+      <c r="G455" s="1">
+        <v>46168</v>
+      </c>
+      <c r="H455" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>850</v>
+      </c>
+      <c r="B456" t="s">
+        <v>857</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+      <c r="D456" t="s">
+        <v>2</v>
+      </c>
+      <c r="E456" t="s">
+        <v>852</v>
+      </c>
+      <c r="F456" t="s">
+        <v>853</v>
+      </c>
+      <c r="G456" s="1">
+        <v>46218</v>
+      </c>
+      <c r="H456" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>850</v>
+      </c>
+      <c r="B457" t="s">
+        <v>858</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>2</v>
+      </c>
+      <c r="E457" t="s">
+        <v>852</v>
+      </c>
+      <c r="F457" t="s">
+        <v>853</v>
+      </c>
+      <c r="G457" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H457" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>850</v>
+      </c>
+      <c r="B458" t="s">
+        <v>859</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+      <c r="D458" t="s">
+        <v>2</v>
+      </c>
+      <c r="E458" t="s">
+        <v>852</v>
+      </c>
+      <c r="F458" t="s">
+        <v>853</v>
+      </c>
+      <c r="G458" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H458" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>850</v>
+      </c>
+      <c r="B459" t="s">
+        <v>860</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+      <c r="D459" t="s">
+        <v>2</v>
+      </c>
+      <c r="E459" t="s">
+        <v>861</v>
+      </c>
+      <c r="F459" t="s">
+        <v>862</v>
+      </c>
+      <c r="G459" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H459" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>850</v>
+      </c>
+      <c r="B460" t="s">
+        <v>863</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460" t="s">
+        <v>2</v>
+      </c>
+      <c r="E460" t="s">
+        <v>852</v>
+      </c>
+      <c r="F460" t="s">
+        <v>853</v>
+      </c>
+      <c r="G460" s="1">
+        <v>46255</v>
+      </c>
+      <c r="H460" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>850</v>
+      </c>
+      <c r="B461" t="s">
+        <v>864</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="s">
+        <v>2</v>
+      </c>
+      <c r="E461" t="s">
+        <v>852</v>
+      </c>
+      <c r="F461" t="s">
+        <v>853</v>
+      </c>
+      <c r="G461" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H461" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>850</v>
+      </c>
+      <c r="B462" t="s">
+        <v>865</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462" t="s">
+        <v>2</v>
+      </c>
+      <c r="E462" t="s">
+        <v>852</v>
+      </c>
+      <c r="F462" t="s">
+        <v>853</v>
+      </c>
+      <c r="G462" s="1">
+        <v>46262</v>
+      </c>
+      <c r="H462" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>850</v>
+      </c>
+      <c r="B463" t="s">
+        <v>866</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463" t="s">
+        <v>6</v>
+      </c>
+      <c r="E463" t="s">
+        <v>13</v>
+      </c>
+      <c r="F463" t="s">
+        <v>14</v>
+      </c>
+      <c r="G463" s="1">
+        <v>46281</v>
+      </c>
+      <c r="H463" s="1">
+        <v>46283</v>
       </c>
     </row>
   </sheetData>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53CC9516-8E4E-465F-AA1C-259475813A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6C7AECD-426A-486B-9E6B-4EBF5C8A6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{22288D16-38B9-40A5-878C-524199312A9F}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{137C0C18-F7D0-4EA6-8986-AB586058BE76}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="874">
   <si>
     <t>0001</t>
   </si>
@@ -2480,9 +2480,6 @@
   </si>
   <si>
     <t xml:space="preserve">    3036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3037</t>
   </si>
   <si>
     <t>4444</t>
@@ -3094,34 +3091,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AB220E-B375-4697-AECF-D3A2A53895DE}">
-  <dimension ref="A1:H463"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD6D14C-BC21-4650-B206-D383288A53ED}">
+  <dimension ref="A1:H462"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5735,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E102" t="s">
         <v>245</v>
@@ -5891,7 +5888,7 @@
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E108" t="s">
         <v>257</v>
@@ -6827,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E144" t="s">
         <v>319</v>
@@ -8049,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E191" t="s">
         <v>319</v>
@@ -8101,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E193" t="s">
         <v>396</v>
@@ -8153,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E195" t="s">
         <v>402</v>
@@ -8439,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
         <v>402</v>
@@ -8647,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E214" t="s">
         <v>95</v>
@@ -8673,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E215" t="s">
         <v>172</v>
@@ -8855,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E222" t="s">
         <v>453</v>
@@ -9297,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E239" t="s">
         <v>86</v>
@@ -9401,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E243" t="s">
         <v>492</v>
@@ -9661,7 +9658,7 @@
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E253" t="s">
         <v>172</v>
@@ -9713,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E255" t="s">
         <v>453</v>
@@ -9791,7 +9788,7 @@
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
         <v>519</v>
@@ -10285,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E277" t="s">
         <v>453</v>
@@ -11039,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E306" t="s">
         <v>609</v>
@@ -11481,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E323" t="s">
         <v>638</v>
@@ -11559,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E326" t="s">
         <v>645</v>
@@ -11585,7 +11582,7 @@
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E327" t="s">
         <v>648</v>
@@ -11793,7 +11790,7 @@
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E335" t="s">
         <v>662</v>
@@ -11845,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E337" t="s">
         <v>662</v>
@@ -12261,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E353" t="s">
         <v>692</v>
@@ -12807,7 +12804,7 @@
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E374" t="s">
         <v>304</v>
@@ -13873,7 +13870,7 @@
         <v>2</v>
       </c>
       <c r="D415" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E415" t="s">
         <v>805</v>
@@ -14176,59 +14173,59 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="B427" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C427">
         <v>1</v>
       </c>
       <c r="D427" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E427" t="s">
-        <v>304</v>
+        <v>822</v>
       </c>
       <c r="F427" t="s">
-        <v>305</v>
+        <v>823</v>
       </c>
       <c r="G427" s="1">
-        <v>46311</v>
+        <v>46063</v>
       </c>
       <c r="H427" s="1">
-        <v>46311</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B428" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C428">
         <v>1</v>
       </c>
       <c r="D428" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E428" t="s">
-        <v>823</v>
+        <v>57</v>
       </c>
       <c r="F428" t="s">
-        <v>824</v>
+        <v>58</v>
       </c>
       <c r="G428" s="1">
-        <v>46063</v>
+        <v>46113</v>
       </c>
       <c r="H428" s="1">
-        <v>46064</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B429" t="s">
         <v>825</v>
@@ -14237,7 +14234,7 @@
         <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E429" t="s">
         <v>57</v>
@@ -14246,7 +14243,7 @@
         <v>58</v>
       </c>
       <c r="G429" s="1">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="H429" s="1">
         <v>46125</v>
@@ -14254,7 +14251,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B430" t="s">
         <v>826</v>
@@ -14272,15 +14269,15 @@
         <v>58</v>
       </c>
       <c r="G430" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="H430" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B431" t="s">
         <v>827</v>
@@ -14306,7 +14303,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B432" t="s">
         <v>828</v>
@@ -14324,15 +14321,15 @@
         <v>58</v>
       </c>
       <c r="G432" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="H432" s="1">
-        <v>46126</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B433" t="s">
         <v>829</v>
@@ -14341,7 +14338,7 @@
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E433" t="s">
         <v>57</v>
@@ -14350,15 +14347,15 @@
         <v>58</v>
       </c>
       <c r="G433" s="1">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="H433" s="1">
-        <v>46128</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B434" t="s">
         <v>830</v>
@@ -14367,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="D434" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E434" t="s">
         <v>57</v>
@@ -14376,15 +14373,15 @@
         <v>58</v>
       </c>
       <c r="G434" s="1">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="H434" s="1">
-        <v>46132</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B435" t="s">
         <v>831</v>
@@ -14402,15 +14399,15 @@
         <v>58</v>
       </c>
       <c r="G435" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="H435" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B436" t="s">
         <v>832</v>
@@ -14436,7 +14433,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B437" t="s">
         <v>833</v>
@@ -14445,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E437" t="s">
         <v>57</v>
@@ -14454,15 +14451,15 @@
         <v>58</v>
       </c>
       <c r="G437" s="1">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="H437" s="1">
-        <v>46174</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B438" t="s">
         <v>834</v>
@@ -14480,15 +14477,15 @@
         <v>58</v>
       </c>
       <c r="G438" s="1">
-        <v>46195</v>
+        <v>46210</v>
       </c>
       <c r="H438" s="1">
-        <v>46252</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B439" t="s">
         <v>835</v>
@@ -14497,7 +14494,7 @@
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E439" t="s">
         <v>57</v>
@@ -14506,15 +14503,15 @@
         <v>58</v>
       </c>
       <c r="G439" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="H439" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B440" t="s">
         <v>836</v>
@@ -14523,7 +14520,7 @@
         <v>1</v>
       </c>
       <c r="D440" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E440" t="s">
         <v>57</v>
@@ -14532,15 +14529,15 @@
         <v>58</v>
       </c>
       <c r="G440" s="1">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="H440" s="1">
-        <v>46213</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B441" t="s">
         <v>837</v>
@@ -14552,21 +14549,21 @@
         <v>6</v>
       </c>
       <c r="E441" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F441" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G441" s="1">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="H441" s="1">
-        <v>46252</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B442" t="s">
         <v>838</v>
@@ -14575,24 +14572,24 @@
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E442" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F442" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G442" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H442" s="1">
-        <v>46226</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B443" t="s">
         <v>839</v>
@@ -14601,7 +14598,7 @@
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E443" t="s">
         <v>57</v>
@@ -14618,7 +14615,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B444" t="s">
         <v>840</v>
@@ -14639,12 +14636,12 @@
         <v>46227</v>
       </c>
       <c r="H444" s="1">
-        <v>46252</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B445" t="s">
         <v>841</v>
@@ -14656,21 +14653,21 @@
         <v>6</v>
       </c>
       <c r="E445" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F445" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G445" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="H445" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B446" t="s">
         <v>842</v>
@@ -14682,21 +14679,21 @@
         <v>6</v>
       </c>
       <c r="E446" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F446" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G446" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="H446" s="1">
-        <v>46252</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B447" t="s">
         <v>843</v>
@@ -14714,15 +14711,15 @@
         <v>58</v>
       </c>
       <c r="G447" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="H447" s="1">
-        <v>46231</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B448" t="s">
         <v>844</v>
@@ -14731,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="D448" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E448" t="s">
         <v>57</v>
@@ -14740,15 +14737,15 @@
         <v>58</v>
       </c>
       <c r="G448" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H448" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B449" t="s">
         <v>845</v>
@@ -14757,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="D449" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>57</v>
@@ -14766,15 +14763,15 @@
         <v>58</v>
       </c>
       <c r="G449" s="1">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="H449" s="1">
-        <v>46255</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B450" t="s">
         <v>846</v>
@@ -14792,15 +14789,15 @@
         <v>58</v>
       </c>
       <c r="G450" s="1">
-        <v>46260</v>
+        <v>46289</v>
       </c>
       <c r="H450" s="1">
-        <v>46260</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B451" t="s">
         <v>847</v>
@@ -14818,15 +14815,15 @@
         <v>58</v>
       </c>
       <c r="G451" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="H451" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B452" t="s">
         <v>848</v>
@@ -14835,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E452" t="s">
         <v>57</v>
@@ -14844,44 +14841,44 @@
         <v>58</v>
       </c>
       <c r="G452" s="1">
-        <v>46294</v>
+        <v>46311</v>
       </c>
       <c r="H452" s="1">
-        <v>46294</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>821</v>
+        <v>849</v>
       </c>
       <c r="B453" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C453">
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E453" t="s">
-        <v>57</v>
+        <v>851</v>
       </c>
       <c r="F453" t="s">
-        <v>58</v>
+        <v>852</v>
       </c>
       <c r="G453" s="1">
-        <v>46311</v>
+        <v>46157</v>
       </c>
       <c r="H453" s="1">
-        <v>46311</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B454" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C454">
         <v>1</v>
@@ -14890,24 +14887,24 @@
         <v>2</v>
       </c>
       <c r="E454" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="F454" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="G454" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="H454" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B455" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C455">
         <v>1</v>
@@ -14916,21 +14913,21 @@
         <v>2</v>
       </c>
       <c r="E455" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F455" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G455" s="1">
-        <v>46168</v>
+        <v>46218</v>
       </c>
       <c r="H455" s="1">
-        <v>46170</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B456" t="s">
         <v>857</v>
@@ -14942,21 +14939,21 @@
         <v>2</v>
       </c>
       <c r="E456" t="s">
+        <v>851</v>
+      </c>
+      <c r="F456" t="s">
         <v>852</v>
       </c>
-      <c r="F456" t="s">
-        <v>853</v>
-      </c>
       <c r="G456" s="1">
-        <v>46218</v>
+        <v>46244</v>
       </c>
       <c r="H456" s="1">
-        <v>46218</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B457" t="s">
         <v>858</v>
@@ -14968,21 +14965,21 @@
         <v>2</v>
       </c>
       <c r="E457" t="s">
+        <v>851</v>
+      </c>
+      <c r="F457" t="s">
         <v>852</v>
       </c>
-      <c r="F457" t="s">
-        <v>853</v>
-      </c>
       <c r="G457" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="H457" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B458" t="s">
         <v>859</v>
@@ -14994,10 +14991,10 @@
         <v>2</v>
       </c>
       <c r="E458" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F458" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="G458" s="1">
         <v>46247</v>
@@ -15008,10 +15005,10 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B459" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C459">
         <v>1</v>
@@ -15020,21 +15017,21 @@
         <v>2</v>
       </c>
       <c r="E459" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="F459" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="G459" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="H459" s="1">
-        <v>46247</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B460" t="s">
         <v>863</v>
@@ -15046,21 +15043,21 @@
         <v>2</v>
       </c>
       <c r="E460" t="s">
+        <v>851</v>
+      </c>
+      <c r="F460" t="s">
         <v>852</v>
       </c>
-      <c r="F460" t="s">
-        <v>853</v>
-      </c>
       <c r="G460" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H460" s="1">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B461" t="s">
         <v>864</v>
@@ -15072,21 +15069,21 @@
         <v>2</v>
       </c>
       <c r="E461" t="s">
+        <v>851</v>
+      </c>
+      <c r="F461" t="s">
         <v>852</v>
       </c>
-      <c r="F461" t="s">
-        <v>853</v>
-      </c>
       <c r="G461" s="1">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="H461" s="1">
-        <v>46258</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B462" t="s">
         <v>865</v>
@@ -15095,44 +15092,18 @@
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E462" t="s">
-        <v>852</v>
+        <v>13</v>
       </c>
       <c r="F462" t="s">
-        <v>853</v>
+        <v>14</v>
       </c>
       <c r="G462" s="1">
-        <v>46262</v>
+        <v>46281</v>
       </c>
       <c r="H462" s="1">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A463" t="s">
-        <v>850</v>
-      </c>
-      <c r="B463" t="s">
-        <v>866</v>
-      </c>
-      <c r="C463">
-        <v>1</v>
-      </c>
-      <c r="D463" t="s">
-        <v>6</v>
-      </c>
-      <c r="E463" t="s">
-        <v>13</v>
-      </c>
-      <c r="F463" t="s">
-        <v>14</v>
-      </c>
-      <c r="G463" s="1">
-        <v>46281</v>
-      </c>
-      <c r="H463" s="1">
         <v>46283</v>
       </c>
     </row>

--- a/Data_ERP/Pedidos Transmicion.xlsx
+++ b/Data_ERP/Pedidos Transmicion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistema_Logistico_Peirano\Data_ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6C7AECD-426A-486B-9E6B-4EBF5C8A6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF65E87B-D4B3-40BB-9F21-89CDA87F12B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{137C0C18-F7D0-4EA6-8986-AB586058BE76}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D7885E72-DC02-4A0F-8FBA-BFAD3107FB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="transmicion" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="828">
   <si>
     <t>0001</t>
   </si>
@@ -790,15 +790,6 @@
     <t xml:space="preserve">  216665</t>
   </si>
   <si>
-    <t xml:space="preserve">  216673</t>
-  </si>
-  <si>
-    <t>HE15</t>
-  </si>
-  <si>
-    <t>HWANG ERIC -SANITARIOS DANIEL</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216681</t>
   </si>
   <si>
@@ -976,15 +967,6 @@
     <t>NUEVA CASA SA</t>
   </si>
   <si>
-    <t xml:space="preserve">  216937</t>
-  </si>
-  <si>
-    <t>NI04</t>
-  </si>
-  <si>
-    <t>NITUB SAIC</t>
-  </si>
-  <si>
     <t xml:space="preserve">  216954</t>
   </si>
   <si>
@@ -1201,21 +1183,9 @@
     <t>DOMINGO RESTA Y CIA. SA</t>
   </si>
   <si>
-    <t xml:space="preserve">  217329</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217330</t>
   </si>
   <si>
-    <t xml:space="preserve">  217335</t>
-  </si>
-  <si>
-    <t>AS17</t>
-  </si>
-  <si>
-    <t>AQUA SANITARIOS TANDIL S. R. L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217339</t>
   </si>
   <si>
@@ -1288,9 +1258,6 @@
     <t xml:space="preserve">  217398</t>
   </si>
   <si>
-    <t xml:space="preserve">  217399</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217401</t>
   </si>
   <si>
@@ -1321,21 +1288,6 @@
     <t>GUIDOLI FLORIO S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217422</t>
-  </si>
-  <si>
-    <t>LJ15</t>
-  </si>
-  <si>
-    <t>LEIRO JOAQUIN C. - EL GASIFICADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217429</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217452</t>
   </si>
   <si>
@@ -1378,7 +1330,160 @@
     <t>CASA BOUCIGUEZ S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217465</t>
+    <t xml:space="preserve">  217466</t>
+  </si>
+  <si>
+    <t>SY05</t>
+  </si>
+  <si>
+    <t>SANITARIOS YRIGOYEN CABRERA S. R. L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217477</t>
+  </si>
+  <si>
+    <t>GJ17</t>
+  </si>
+  <si>
+    <t>GUALTIERI JUAN A. CONSTRU-MEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217485</t>
+  </si>
+  <si>
+    <t>CI03</t>
+  </si>
+  <si>
+    <t>CARLOS ISLA Y CIA. S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217486</t>
+  </si>
+  <si>
+    <t>FP04</t>
+  </si>
+  <si>
+    <t>FLUIDOS PATAGONIA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217487</t>
+  </si>
+  <si>
+    <t>765</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ, Tiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217494</t>
+  </si>
+  <si>
+    <t>ZZ02</t>
+  </si>
+  <si>
+    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217515</t>
+  </si>
+  <si>
+    <t>CP31</t>
+  </si>
+  <si>
+    <t>CASAPAULINO SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217518</t>
+  </si>
+  <si>
+    <t>FE26</t>
+  </si>
+  <si>
+    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217524</t>
+  </si>
+  <si>
+    <t>MA31</t>
+  </si>
+  <si>
+    <t>MATRIGAS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217527</t>
+  </si>
+  <si>
+    <t>BN08</t>
+  </si>
+  <si>
+    <t>BONINO NORBERTO DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217541</t>
+  </si>
+  <si>
+    <t>SM26</t>
+  </si>
+  <si>
+    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217542</t>
   </si>
   <si>
     <t>CE23</t>
@@ -1387,177 +1492,6 @@
     <t>CEFALU S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217466</t>
-  </si>
-  <si>
-    <t>SY05</t>
-  </si>
-  <si>
-    <t>SANITARIOS YRIGOYEN CABRERA S. R. L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217477</t>
-  </si>
-  <si>
-    <t>GJ17</t>
-  </si>
-  <si>
-    <t>GUALTIERI JUAN A. CONSTRU-MEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217485</t>
-  </si>
-  <si>
-    <t>CI03</t>
-  </si>
-  <si>
-    <t>CARLOS ISLA Y CIA. S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217486</t>
-  </si>
-  <si>
-    <t>FP04</t>
-  </si>
-  <si>
-    <t>FLUIDOS PATAGONIA S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217487</t>
-  </si>
-  <si>
-    <t>765</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ, Tiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217494</t>
-  </si>
-  <si>
-    <t>ZZ02</t>
-  </si>
-  <si>
-    <t>ZINGALV GALVANIZADOS Y ZINC S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217515</t>
-  </si>
-  <si>
-    <t>CP31</t>
-  </si>
-  <si>
-    <t>CASAPAULINO SAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217518</t>
-  </si>
-  <si>
-    <t>FE26</t>
-  </si>
-  <si>
-    <t>FEMEN S.A. - CENTRO DE MATERIALES -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217523</t>
-  </si>
-  <si>
-    <t>BG15</t>
-  </si>
-  <si>
-    <t>BULFON GUILLERMO JESUS - SANIT. MATISA -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217524</t>
-  </si>
-  <si>
-    <t>MA31</t>
-  </si>
-  <si>
-    <t>MATRIGAS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217527</t>
-  </si>
-  <si>
-    <t>BN08</t>
-  </si>
-  <si>
-    <t>BONINO NORBERTO DANIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217541</t>
-  </si>
-  <si>
-    <t>SM26</t>
-  </si>
-  <si>
-    <t>SANCHEZ M. Y NUÑEZ M. S.H. - SANITARIOS NUSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217542</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217543</t>
   </si>
   <si>
@@ -1576,15 +1510,6 @@
     <t>VICTOR ALEJANDRO VEGA S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217545</t>
-  </si>
-  <si>
-    <t>DA28</t>
-  </si>
-  <si>
-    <t>DAPESOL S.A. -MATERIALES ACON</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217549</t>
   </si>
   <si>
@@ -1654,15 +1579,6 @@
     <t>SANITARIOS CAMPANA S.R.L.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217562</t>
-  </si>
-  <si>
-    <t>LP11</t>
-  </si>
-  <si>
-    <t>SANITARIOS LA PRIMERA S.R.L.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217563</t>
   </si>
   <si>
@@ -1699,9 +1615,6 @@
     <t>RAN CO MATERIALES S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217570</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217571</t>
   </si>
   <si>
@@ -1783,6 +1696,15 @@
     <t>CLACE CDC S. A.-CLACE REVESTIMIENTOS</t>
   </si>
   <si>
+    <t xml:space="preserve">  217591</t>
+  </si>
+  <si>
+    <t>HC03</t>
+  </si>
+  <si>
+    <t>HIJOS DE RAFAEL CONTI S.A. - CONTI MATERIALES</t>
+  </si>
+  <si>
     <t xml:space="preserve">  217592</t>
   </si>
   <si>
@@ -1846,15 +1768,6 @@
     <t>ALVARENGA VILLAR LUIS F.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217606</t>
-  </si>
-  <si>
-    <t>DU04</t>
-  </si>
-  <si>
-    <t>DURANTE HNOS S R L</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217607</t>
   </si>
   <si>
@@ -1921,9 +1834,6 @@
     <t>SANI 3 S.R.L</t>
   </si>
   <si>
-    <t xml:space="preserve">  217622</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217623</t>
   </si>
   <si>
@@ -1933,15 +1843,6 @@
     <t xml:space="preserve">  217626</t>
   </si>
   <si>
-    <t xml:space="preserve">  217627</t>
-  </si>
-  <si>
-    <t>NS01</t>
-  </si>
-  <si>
-    <t>NUEVO SUR S.A.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217628</t>
   </si>
   <si>
@@ -1954,16 +1855,172 @@
     <t>CRETA PORCELLANATOS S.A. -CRETA DISEGNO</t>
   </si>
   <si>
-    <t xml:space="preserve">  217630</t>
-  </si>
-  <si>
-    <t>AM04</t>
-  </si>
-  <si>
-    <t>ARDISSONE MARIO JAVIER -SANIT. ARDISSONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217632</t>
+    <t xml:space="preserve">  217633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217636</t>
+  </si>
+  <si>
+    <t>LS08</t>
+  </si>
+  <si>
+    <t>LUQUE SANITARIOS S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217639</t>
+  </si>
+  <si>
+    <t>CC63</t>
+  </si>
+  <si>
+    <t>LA CASA DE LA CONSTRUCCION S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217640</t>
+  </si>
+  <si>
+    <t>SA36</t>
+  </si>
+  <si>
+    <t>SAMOT S.A.S.  -SANIPLAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217648</t>
+  </si>
+  <si>
+    <t>PR29</t>
+  </si>
+  <si>
+    <t>PREMOLCHACO S.R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217649</t>
+  </si>
+  <si>
+    <t>KO01</t>
+  </si>
+  <si>
+    <t>KOCUDEL S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217653</t>
+  </si>
+  <si>
+    <t>RP07</t>
+  </si>
+  <si>
+    <t>RIO PLOMO S.A.S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217657</t>
+  </si>
+  <si>
+    <t>PM26</t>
+  </si>
+  <si>
+    <t>PEGORER MARTIN EDUARDO - SANITARIOS RINCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217662</t>
+  </si>
+  <si>
+    <t>SP23</t>
+  </si>
+  <si>
+    <t>SEGA PROVISIONES - SANIT CABALLITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217665</t>
+  </si>
+  <si>
+    <t>TU03</t>
+  </si>
+  <si>
+    <t>TUBONOR S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217669</t>
+  </si>
+  <si>
+    <t>VS04</t>
+  </si>
+  <si>
+    <t>V.S.MATERIALES DE J.C.MOREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217671</t>
+  </si>
+  <si>
+    <t>LG10</t>
+  </si>
+  <si>
+    <t>LOPEZ GAS ONLINE S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  217674</t>
   </si>
   <si>
     <t>PO01</t>
@@ -1972,198 +2029,6 @@
     <t>PORAL S.A.C.I.</t>
   </si>
   <si>
-    <t xml:space="preserve">  217633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217636</t>
-  </si>
-  <si>
-    <t>LS08</t>
-  </si>
-  <si>
-    <t>LUQUE SANITARIOS S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217639</t>
-  </si>
-  <si>
-    <t>CC63</t>
-  </si>
-  <si>
-    <t>LA CASA DE LA CONSTRUCCION S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217640</t>
-  </si>
-  <si>
-    <t>SA36</t>
-  </si>
-  <si>
-    <t>SAMOT S.A.S.  -SANIPLAST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217648</t>
-  </si>
-  <si>
-    <t>PR29</t>
-  </si>
-  <si>
-    <t>PREMOLCHACO S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217649</t>
-  </si>
-  <si>
-    <t>KO01</t>
-  </si>
-  <si>
-    <t>KOCUDEL S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217653</t>
-  </si>
-  <si>
-    <t>RP07</t>
-  </si>
-  <si>
-    <t>RIO PLOMO S.A.S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217657</t>
-  </si>
-  <si>
-    <t>PM26</t>
-  </si>
-  <si>
-    <t>PEGORER MARTIN EDUARDO - SANITARIOS RINCON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217658</t>
-  </si>
-  <si>
-    <t>750</t>
-  </si>
-  <si>
-    <t>SOLER, Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217661</t>
-  </si>
-  <si>
-    <t>AX01</t>
-  </si>
-  <si>
-    <t>SANITARIOS AXANTRA S.R.L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217662</t>
-  </si>
-  <si>
-    <t>SP23</t>
-  </si>
-  <si>
-    <t>SEGA PROVISIONES - SANIT CABALLITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217665</t>
-  </si>
-  <si>
-    <t>TU03</t>
-  </si>
-  <si>
-    <t>TUBONOR S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217669</t>
-  </si>
-  <si>
-    <t>VS04</t>
-  </si>
-  <si>
-    <t>V.S.MATERIALES DE J.C.MOREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217671</t>
-  </si>
-  <si>
-    <t>LG10</t>
-  </si>
-  <si>
-    <t>LOPEZ GAS ONLINE S.A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  217674</t>
-  </si>
-  <si>
     <t xml:space="preserve">  217675</t>
   </si>
   <si>
@@ -2564,9 +2429,6 @@
   </si>
   <si>
     <t xml:space="preserve">    2644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2827</t>
   </si>
   <si>
     <t>9999</t>
@@ -3091,34 +2953,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD6D14C-BC21-4650-B206-D383288A53ED}">
-  <dimension ref="A1:H462"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926156CF-C2E4-44A7-81A1-106844E77542}">
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>866</v>
+        <v>820</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>868</v>
+        <v>822</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>869</v>
+        <v>823</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>870</v>
+        <v>824</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>871</v>
+        <v>825</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>872</v>
+        <v>826</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>873</v>
+        <v>827</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5885,22 +5747,22 @@
         <v>256</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>37</v>
       </c>
       <c r="F108" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="G108" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H108" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -5908,25 +5770,25 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
+        <v>257</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E109" t="s">
+        <v>258</v>
+      </c>
+      <c r="F109" t="s">
         <v>259</v>
-      </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
-      <c r="D109" t="s">
-        <v>128</v>
-      </c>
-      <c r="E109" t="s">
-        <v>37</v>
-      </c>
-      <c r="F109" t="s">
-        <v>38</v>
       </c>
       <c r="G109" s="1">
         <v>46295</v>
       </c>
       <c r="H109" s="1">
-        <v>46309</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -5943,16 +5805,16 @@
         <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="F110" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="G110" s="1">
         <v>46295</v>
       </c>
       <c r="H110" s="1">
-        <v>46296</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -5960,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -5986,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -6012,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -6038,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -6064,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -6090,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -6116,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -6142,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -6168,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -6194,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -6220,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
         <v>2</v>
@@ -6238,7 +6100,7 @@
         <v>46295</v>
       </c>
       <c r="H121" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -6246,25 +6108,25 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
+        <v>272</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+      <c r="E122" t="s">
+        <v>273</v>
+      </c>
+      <c r="F122" t="s">
         <v>274</v>
-      </c>
-      <c r="C122">
-        <v>2</v>
-      </c>
-      <c r="D122" t="s">
-        <v>2</v>
-      </c>
-      <c r="E122" t="s">
-        <v>37</v>
-      </c>
-      <c r="F122" t="s">
-        <v>38</v>
       </c>
       <c r="G122" s="1">
         <v>46295</v>
       </c>
       <c r="H122" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -6275,10 +6137,10 @@
         <v>275</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E123" t="s">
         <v>276</v>
@@ -6287,10 +6149,10 @@
         <v>277</v>
       </c>
       <c r="G123" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H123" s="1">
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -6301,22 +6163,22 @@
         <v>278</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="F124" t="s">
-        <v>280</v>
+        <v>38</v>
       </c>
       <c r="G124" s="1">
         <v>46296</v>
       </c>
       <c r="H124" s="1">
-        <v>46303</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -6324,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -6350,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -6368,7 +6230,7 @@
         <v>46296</v>
       </c>
       <c r="H126" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -6376,25 +6238,25 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
+        <v>281</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>128</v>
+      </c>
+      <c r="E127" t="s">
+        <v>282</v>
+      </c>
+      <c r="F127" t="s">
         <v>283</v>
-      </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127" t="s">
-        <v>128</v>
-      </c>
-      <c r="E127" t="s">
-        <v>37</v>
-      </c>
-      <c r="F127" t="s">
-        <v>38</v>
       </c>
       <c r="G127" s="1">
         <v>46296</v>
       </c>
       <c r="H127" s="1">
-        <v>46302</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -6408,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E128" t="s">
         <v>285</v>
@@ -6420,7 +6282,7 @@
         <v>46296</v>
       </c>
       <c r="H128" s="1">
-        <v>46309</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -6431,10 +6293,10 @@
         <v>287</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E129" t="s">
         <v>288</v>
@@ -6446,7 +6308,7 @@
         <v>46296</v>
       </c>
       <c r="H129" s="1">
-        <v>46296</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -6457,10 +6319,10 @@
         <v>290</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
         <v>291</v>
@@ -6472,7 +6334,7 @@
         <v>46296</v>
       </c>
       <c r="H130" s="1">
-        <v>46311</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -6486,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E131" t="s">
         <v>294</v>
@@ -6495,10 +6357,10 @@
         <v>295</v>
       </c>
       <c r="G131" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="H131" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -6535,22 +6397,22 @@
         <v>299</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E133" t="s">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="F133" t="s">
-        <v>301</v>
+        <v>131</v>
       </c>
       <c r="G133" s="1">
         <v>46297</v>
       </c>
       <c r="H133" s="1">
-        <v>46297</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -6558,19 +6420,19 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
+        <v>300</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+      <c r="E134" t="s">
+        <v>301</v>
+      </c>
+      <c r="F134" t="s">
         <v>302</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>2</v>
-      </c>
-      <c r="E134" t="s">
-        <v>130</v>
-      </c>
-      <c r="F134" t="s">
-        <v>131</v>
       </c>
       <c r="G134" s="1">
         <v>46297</v>
@@ -6590,13 +6452,13 @@
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E135" t="s">
-        <v>304</v>
+        <v>37</v>
       </c>
       <c r="F135" t="s">
-        <v>305</v>
+        <v>38</v>
       </c>
       <c r="G135" s="1">
         <v>46297</v>
@@ -6610,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -6636,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -6662,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -6688,13 +6550,13 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E139" t="s">
         <v>37</v>
@@ -6714,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -6740,25 +6602,25 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
+        <v>309</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" t="s">
+        <v>310</v>
+      </c>
+      <c r="F141" t="s">
         <v>311</v>
-      </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="D141" t="s">
-        <v>128</v>
-      </c>
-      <c r="E141" t="s">
-        <v>37</v>
-      </c>
-      <c r="F141" t="s">
-        <v>38</v>
       </c>
       <c r="G141" s="1">
         <v>46297</v>
       </c>
       <c r="H141" s="1">
-        <v>46297</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -6769,10 +6631,10 @@
         <v>312</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E142" t="s">
         <v>313</v>
@@ -6781,10 +6643,10 @@
         <v>314</v>
       </c>
       <c r="G142" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="H142" s="1">
-        <v>46300</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -6795,22 +6657,22 @@
         <v>315</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" t="s">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>316</v>
+        <v>25</v>
       </c>
       <c r="F143" t="s">
-        <v>317</v>
+        <v>26</v>
       </c>
       <c r="G143" s="1">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="H143" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -6818,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6827,10 +6689,10 @@
         <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="F144" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="G144" s="1">
         <v>46300</v>
@@ -6844,25 +6706,25 @@
         <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="F145" t="s">
-        <v>26</v>
+        <v>319</v>
       </c>
       <c r="G145" s="1">
         <v>46300</v>
       </c>
       <c r="H145" s="1">
-        <v>46308</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -6870,19 +6732,19 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E146" t="s">
-        <v>276</v>
+        <v>37</v>
       </c>
       <c r="F146" t="s">
-        <v>277</v>
+        <v>38</v>
       </c>
       <c r="G146" s="1">
         <v>46300</v>
@@ -6896,19 +6758,19 @@
         <v>0</v>
       </c>
       <c r="B147" t="s">
+        <v>321</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>2</v>
+      </c>
+      <c r="E147" t="s">
+        <v>322</v>
+      </c>
+      <c r="F147" t="s">
         <v>323</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>2</v>
-      </c>
-      <c r="E147" t="s">
-        <v>324</v>
-      </c>
-      <c r="F147" t="s">
-        <v>325</v>
       </c>
       <c r="G147" s="1">
         <v>46300</v>
@@ -6922,25 +6784,25 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G148" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H148" s="1">
-        <v>46300</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -6948,25 +6810,25 @@
         <v>0</v>
       </c>
       <c r="B149" t="s">
+        <v>325</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+      <c r="D149" t="s">
+        <v>2</v>
+      </c>
+      <c r="E149" t="s">
+        <v>326</v>
+      </c>
+      <c r="F149" t="s">
         <v>327</v>
       </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-      <c r="D149" t="s">
-        <v>2</v>
-      </c>
-      <c r="E149" t="s">
-        <v>328</v>
-      </c>
-      <c r="F149" t="s">
-        <v>329</v>
-      </c>
       <c r="G149" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H149" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -6974,25 +6836,25 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
+        <v>328</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150" t="s">
+        <v>2</v>
+      </c>
+      <c r="E150" t="s">
+        <v>329</v>
+      </c>
+      <c r="F150" t="s">
         <v>330</v>
-      </c>
-      <c r="C150">
-        <v>2</v>
-      </c>
-      <c r="D150" t="s">
-        <v>6</v>
-      </c>
-      <c r="E150" t="s">
-        <v>22</v>
-      </c>
-      <c r="F150" t="s">
-        <v>23</v>
       </c>
       <c r="G150" s="1">
         <v>46301</v>
       </c>
       <c r="H150" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -7006,7 +6868,7 @@
         <v>2</v>
       </c>
       <c r="D151" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E151" t="s">
         <v>332</v>
@@ -7018,7 +6880,7 @@
         <v>46301</v>
       </c>
       <c r="H151" s="1">
-        <v>46308</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -7032,19 +6894,19 @@
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E152" t="s">
-        <v>335</v>
+        <v>22</v>
       </c>
       <c r="F152" t="s">
-        <v>336</v>
+        <v>23</v>
       </c>
       <c r="G152" s="1">
         <v>46301</v>
       </c>
       <c r="H152" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -7052,25 +6914,25 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E153" t="s">
-        <v>338</v>
+        <v>22</v>
       </c>
       <c r="F153" t="s">
-        <v>339</v>
+        <v>23</v>
       </c>
       <c r="G153" s="1">
         <v>46301</v>
       </c>
       <c r="H153" s="1">
-        <v>46301</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -7078,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7087,16 +6949,16 @@
         <v>128</v>
       </c>
       <c r="E154" t="s">
-        <v>22</v>
+        <v>337</v>
       </c>
       <c r="F154" t="s">
-        <v>23</v>
+        <v>338</v>
       </c>
       <c r="G154" s="1">
         <v>46301</v>
       </c>
       <c r="H154" s="1">
-        <v>46311</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -7104,25 +6966,25 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
+        <v>339</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>2</v>
+      </c>
+      <c r="E155" t="s">
+        <v>340</v>
+      </c>
+      <c r="F155" t="s">
         <v>341</v>
       </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155" t="s">
-        <v>128</v>
-      </c>
-      <c r="E155" t="s">
-        <v>22</v>
-      </c>
-      <c r="F155" t="s">
-        <v>23</v>
-      </c>
       <c r="G155" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H155" s="1">
-        <v>46311</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -7133,22 +6995,22 @@
         <v>342</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="s">
         <v>128</v>
       </c>
       <c r="E156" t="s">
-        <v>343</v>
+        <v>143</v>
       </c>
       <c r="F156" t="s">
-        <v>344</v>
+        <v>144</v>
       </c>
       <c r="G156" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H156" s="1">
-        <v>46309</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -7156,19 +7018,19 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="s">
         <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>346</v>
+        <v>48</v>
       </c>
       <c r="F157" t="s">
-        <v>347</v>
+        <v>49</v>
       </c>
       <c r="G157" s="1">
         <v>46302</v>
@@ -7182,25 +7044,25 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E158" t="s">
-        <v>143</v>
+        <v>345</v>
       </c>
       <c r="F158" t="s">
-        <v>144</v>
+        <v>346</v>
       </c>
       <c r="G158" s="1">
         <v>46302</v>
       </c>
       <c r="H158" s="1">
-        <v>46302</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -7208,25 +7070,25 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
+        <v>347</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>128</v>
+      </c>
+      <c r="E159" t="s">
+        <v>348</v>
+      </c>
+      <c r="F159" t="s">
         <v>349</v>
-      </c>
-      <c r="C159">
-        <v>2</v>
-      </c>
-      <c r="D159" t="s">
-        <v>2</v>
-      </c>
-      <c r="E159" t="s">
-        <v>48</v>
-      </c>
-      <c r="F159" t="s">
-        <v>49</v>
       </c>
       <c r="G159" s="1">
         <v>46302</v>
       </c>
       <c r="H159" s="1">
-        <v>46302</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -7243,10 +7105,10 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>351</v>
+        <v>37</v>
       </c>
       <c r="F160" t="s">
-        <v>352</v>
+        <v>38</v>
       </c>
       <c r="G160" s="1">
         <v>46302</v>
@@ -7260,19 +7122,19 @@
         <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E161" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="F161" t="s">
-        <v>355</v>
+        <v>38</v>
       </c>
       <c r="G161" s="1">
         <v>46302</v>
@@ -7286,25 +7148,25 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162" t="s">
         <v>128</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>353</v>
       </c>
       <c r="F162" t="s">
-        <v>38</v>
+        <v>354</v>
       </c>
       <c r="G162" s="1">
         <v>46302</v>
       </c>
       <c r="H162" s="1">
-        <v>46302</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -7312,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7338,19 +7200,19 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E164" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="F164" t="s">
-        <v>360</v>
+        <v>38</v>
       </c>
       <c r="G164" s="1">
         <v>46302</v>
@@ -7364,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7390,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7416,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7442,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7468,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7494,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7520,25 +7382,25 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" t="s">
         <v>128</v>
       </c>
       <c r="E171" t="s">
-        <v>37</v>
+        <v>364</v>
       </c>
       <c r="F171" t="s">
-        <v>38</v>
+        <v>365</v>
       </c>
       <c r="G171" s="1">
         <v>46302</v>
       </c>
       <c r="H171" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -7546,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7561,10 +7423,10 @@
         <v>38</v>
       </c>
       <c r="G172" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H172" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -7572,25 +7434,25 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="s">
         <v>128</v>
       </c>
       <c r="E173" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="F173" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="G173" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H173" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -7598,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7624,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7650,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7676,25 +7538,25 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D177" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="F177" t="s">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="G177" s="1">
         <v>46303</v>
       </c>
       <c r="H177" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -7702,25 +7564,25 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="s">
         <v>128</v>
       </c>
       <c r="E178" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="F178" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="G178" s="1">
         <v>46303</v>
       </c>
       <c r="H178" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -7728,25 +7590,25 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C179">
         <v>2</v>
       </c>
       <c r="D179" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E179" t="s">
-        <v>378</v>
+        <v>288</v>
       </c>
       <c r="F179" t="s">
-        <v>379</v>
+        <v>289</v>
       </c>
       <c r="G179" s="1">
         <v>46303</v>
       </c>
       <c r="H179" s="1">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -7754,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C180">
         <v>2</v>
@@ -7763,16 +7625,16 @@
         <v>128</v>
       </c>
       <c r="E180" t="s">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="F180" t="s">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="G180" s="1">
         <v>46303</v>
       </c>
       <c r="H180" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -7780,19 +7642,19 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D181" t="s">
         <v>128</v>
       </c>
       <c r="E181" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F181" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G181" s="1">
         <v>46303</v>
@@ -7806,19 +7668,19 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="s">
         <v>128</v>
       </c>
       <c r="E182" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F182" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G182" s="1">
         <v>46303</v>
@@ -7832,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7841,10 +7703,10 @@
         <v>128</v>
       </c>
       <c r="E183" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F183" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G183" s="1">
         <v>46303</v>
@@ -7858,25 +7720,25 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>291</v>
+        <v>372</v>
       </c>
       <c r="F184" t="s">
-        <v>292</v>
+        <v>373</v>
       </c>
       <c r="G184" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H184" s="1">
-        <v>46311</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -7884,25 +7746,25 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>291</v>
+        <v>37</v>
       </c>
       <c r="F185" t="s">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="G185" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H185" s="1">
-        <v>46311</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -7910,25 +7772,25 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E186" t="s">
-        <v>378</v>
+        <v>37</v>
       </c>
       <c r="F186" t="s">
-        <v>379</v>
+        <v>38</v>
       </c>
       <c r="G186" s="1">
         <v>46304</v>
       </c>
       <c r="H186" s="1">
-        <v>46309</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -7936,13 +7798,13 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E187" t="s">
         <v>37</v>
@@ -7962,25 +7824,25 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="s">
         <v>128</v>
       </c>
       <c r="E188" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="F188" t="s">
-        <v>38</v>
+        <v>386</v>
       </c>
       <c r="G188" s="1">
         <v>46304</v>
       </c>
       <c r="H188" s="1">
-        <v>46304</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
@@ -7988,13 +7850,13 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E189" t="s">
         <v>37</v>
@@ -8014,19 +7876,19 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
+        <v>388</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>2</v>
+      </c>
+      <c r="E190" t="s">
+        <v>389</v>
+      </c>
+      <c r="F190" t="s">
         <v>390</v>
-      </c>
-      <c r="C190">
-        <v>1</v>
-      </c>
-      <c r="D190" t="s">
-        <v>2</v>
-      </c>
-      <c r="E190" t="s">
-        <v>391</v>
-      </c>
-      <c r="F190" t="s">
-        <v>392</v>
       </c>
       <c r="G190" s="1">
         <v>46304</v>
@@ -8040,25 +7902,25 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
+        <v>391</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="s">
+        <v>2</v>
+      </c>
+      <c r="E191" t="s">
+        <v>392</v>
+      </c>
+      <c r="F191" t="s">
         <v>393</v>
       </c>
-      <c r="C191">
-        <v>1</v>
-      </c>
-      <c r="D191" t="s">
-        <v>2</v>
-      </c>
-      <c r="E191" t="s">
-        <v>319</v>
-      </c>
-      <c r="F191" t="s">
-        <v>320</v>
-      </c>
       <c r="G191" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="H191" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -8069,22 +7931,22 @@
         <v>394</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E192" t="s">
-        <v>37</v>
+        <v>395</v>
       </c>
       <c r="F192" t="s">
-        <v>38</v>
+        <v>396</v>
       </c>
       <c r="G192" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="H192" s="1">
-        <v>46304</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -8092,25 +7954,25 @@
         <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E193" t="s">
-        <v>396</v>
+        <v>332</v>
       </c>
       <c r="F193" t="s">
-        <v>397</v>
+        <v>333</v>
       </c>
       <c r="G193" s="1">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H193" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -8121,22 +7983,22 @@
         <v>398</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D194" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E194" t="s">
-        <v>399</v>
+        <v>80</v>
       </c>
       <c r="F194" t="s">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="G194" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H194" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -8144,22 +8006,22 @@
         <v>0</v>
       </c>
       <c r="B195" t="s">
+        <v>399</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="D195" t="s">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>400</v>
+      </c>
+      <c r="F195" t="s">
         <v>401</v>
       </c>
-      <c r="C195">
-        <v>1</v>
-      </c>
-      <c r="D195" t="s">
-        <v>2</v>
-      </c>
-      <c r="E195" t="s">
-        <v>402</v>
-      </c>
-      <c r="F195" t="s">
-        <v>403</v>
-      </c>
       <c r="G195" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="H195" s="1">
         <v>46308</v>
@@ -8170,25 +8032,25 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="E196" t="s">
-        <v>405</v>
+        <v>273</v>
       </c>
       <c r="F196" t="s">
-        <v>406</v>
+        <v>274</v>
       </c>
       <c r="G196" s="1">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="H196" s="1">
-        <v>46310</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -8196,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="B197" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -8205,13 +8067,13 @@
         <v>128</v>
       </c>
       <c r="E197" t="s">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="F197" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="G197" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H197" s="1">
         <v>46308</v>
@@ -8222,25 +8084,25 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
+        <v>406</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
+        <v>2</v>
+      </c>
+      <c r="E198" t="s">
+        <v>407</v>
+      </c>
+      <c r="F198" t="s">
         <v>408</v>
-      </c>
-      <c r="C198">
-        <v>2</v>
-      </c>
-      <c r="D198" t="s">
-        <v>128</v>
-      </c>
-      <c r="E198" t="s">
-        <v>80</v>
-      </c>
-      <c r="F198" t="s">
-        <v>81</v>
       </c>
       <c r="G198" s="1">
         <v>46308</v>
       </c>
       <c r="H198" s="1">
-        <v>46311</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -8257,10 +8119,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>410</v>
+        <v>212</v>
       </c>
       <c r="F199" t="s">
-        <v>411</v>
+        <v>213</v>
       </c>
       <c r="G199" s="1">
         <v>46308</v>
@@ -8274,19 +8136,19 @@
         <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>276</v>
+        <v>407</v>
       </c>
       <c r="F200" t="s">
-        <v>277</v>
+        <v>408</v>
       </c>
       <c r="G200" s="1">
         <v>46308</v>
@@ -8300,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -8309,10 +8171,10 @@
         <v>128</v>
       </c>
       <c r="E201" t="s">
-        <v>414</v>
+        <v>332</v>
       </c>
       <c r="F201" t="s">
-        <v>415</v>
+        <v>333</v>
       </c>
       <c r="G201" s="1">
         <v>46308</v>
@@ -8326,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -8335,10 +8197,10 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F202" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G202" s="1">
         <v>46308</v>
@@ -8352,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -8361,10 +8223,10 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>212</v>
+        <v>407</v>
       </c>
       <c r="F203" t="s">
-        <v>213</v>
+        <v>408</v>
       </c>
       <c r="G203" s="1">
         <v>46308</v>
@@ -8378,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -8387,10 +8249,10 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F204" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G204" s="1">
         <v>46308</v>
@@ -8404,19 +8266,19 @@
         <v>0</v>
       </c>
       <c r="B205" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="F205" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="G205" s="1">
         <v>46308</v>
@@ -8430,19 +8292,19 @@
         <v>0</v>
       </c>
       <c r="B206" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E206" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="F206" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G206" s="1">
         <v>46308</v>
@@ -8456,19 +8318,19 @@
         <v>0</v>
       </c>
       <c r="B207" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E207" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F207" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G207" s="1">
         <v>46308</v>
@@ -8482,25 +8344,25 @@
         <v>0</v>
       </c>
       <c r="B208" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E208" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F208" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="G208" s="1">
         <v>46308</v>
       </c>
       <c r="H208" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -8508,25 +8370,25 @@
         <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E209" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F209" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="G209" s="1">
         <v>46308</v>
       </c>
       <c r="H209" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -8534,25 +8396,25 @@
         <v>0</v>
       </c>
       <c r="B210" t="s">
+        <v>424</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210" t="s">
+        <v>128</v>
+      </c>
+      <c r="E210" t="s">
+        <v>425</v>
+      </c>
+      <c r="F210" t="s">
         <v>426</v>
-      </c>
-      <c r="C210">
-        <v>1</v>
-      </c>
-      <c r="D210" t="s">
-        <v>2</v>
-      </c>
-      <c r="E210" t="s">
-        <v>417</v>
-      </c>
-      <c r="F210" t="s">
-        <v>418</v>
       </c>
       <c r="G210" s="1">
         <v>46308</v>
       </c>
       <c r="H210" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -8578,7 +8440,7 @@
         <v>46308</v>
       </c>
       <c r="H211" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -8604,7 +8466,7 @@
         <v>46308</v>
       </c>
       <c r="H212" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
@@ -8618,7 +8480,7 @@
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E213" t="s">
         <v>434</v>
@@ -8630,7 +8492,7 @@
         <v>46308</v>
       </c>
       <c r="H213" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -8647,16 +8509,16 @@
         <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>95</v>
+        <v>437</v>
       </c>
       <c r="F214" t="s">
-        <v>96</v>
+        <v>438</v>
       </c>
       <c r="G214" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H214" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -8664,25 +8526,25 @@
         <v>0</v>
       </c>
       <c r="B215" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E215" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="F215" t="s">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="G215" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H215" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -8690,22 +8552,22 @@
         <v>0</v>
       </c>
       <c r="B216" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="F216" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="G216" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H216" s="1">
         <v>46309</v>
@@ -8716,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -8725,13 +8587,13 @@
         <v>128</v>
       </c>
       <c r="E217" t="s">
-        <v>391</v>
+        <v>37</v>
       </c>
       <c r="F217" t="s">
-        <v>392</v>
+        <v>38</v>
       </c>
       <c r="G217" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H217" s="1">
         <v>46309</v>
@@ -8742,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8751,13 +8613,13 @@
         <v>128</v>
       </c>
       <c r="E218" t="s">
-        <v>441</v>
+        <v>37</v>
       </c>
       <c r="F218" t="s">
-        <v>442</v>
+        <v>38</v>
       </c>
       <c r="G218" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H218" s="1">
         <v>46309</v>
@@ -8768,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="B219" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -8777,13 +8639,13 @@
         <v>128</v>
       </c>
       <c r="E219" t="s">
-        <v>444</v>
+        <v>37</v>
       </c>
       <c r="F219" t="s">
-        <v>445</v>
+        <v>38</v>
       </c>
       <c r="G219" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H219" s="1">
         <v>46309</v>
@@ -8800,16 +8662,16 @@
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>447</v>
+        <v>37</v>
       </c>
       <c r="F220" t="s">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="G220" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H220" s="1">
         <v>46309</v>
@@ -8820,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -8829,13 +8691,13 @@
         <v>128</v>
       </c>
       <c r="E221" t="s">
-        <v>450</v>
+        <v>37</v>
       </c>
       <c r="F221" t="s">
-        <v>451</v>
+        <v>38</v>
       </c>
       <c r="G221" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H221" s="1">
         <v>46309</v>
@@ -8846,25 +8708,25 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D222" t="s">
         <v>2</v>
       </c>
       <c r="E222" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F222" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G222" s="1">
         <v>46309</v>
       </c>
       <c r="H222" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -8872,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -8881,10 +8743,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F223" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G223" s="1">
         <v>46309</v>
@@ -8898,19 +8760,19 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>77</v>
+        <v>455</v>
       </c>
       <c r="F224" t="s">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="G224" s="1">
         <v>46309</v>
@@ -8924,19 +8786,19 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E225" t="s">
-        <v>396</v>
+        <v>282</v>
       </c>
       <c r="F225" t="s">
-        <v>397</v>
+        <v>283</v>
       </c>
       <c r="G225" s="1">
         <v>46309</v>
@@ -8950,19 +8812,19 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
+        <v>458</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>128</v>
+      </c>
+      <c r="E226" t="s">
+        <v>459</v>
+      </c>
+      <c r="F226" t="s">
         <v>460</v>
-      </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-      <c r="D226" t="s">
-        <v>2</v>
-      </c>
-      <c r="E226" t="s">
-        <v>461</v>
-      </c>
-      <c r="F226" t="s">
-        <v>462</v>
       </c>
       <c r="G226" s="1">
         <v>46309</v>
@@ -8976,7 +8838,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -8985,10 +8847,10 @@
         <v>128</v>
       </c>
       <c r="E227" t="s">
-        <v>37</v>
+        <v>459</v>
       </c>
       <c r="F227" t="s">
-        <v>38</v>
+        <v>460</v>
       </c>
       <c r="G227" s="1">
         <v>46309</v>
@@ -9002,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -9011,10 +8873,10 @@
         <v>128</v>
       </c>
       <c r="E228" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F228" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G228" s="1">
         <v>46309</v>
@@ -9028,19 +8890,19 @@
         <v>0</v>
       </c>
       <c r="B229" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F229" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G229" s="1">
         <v>46309</v>
@@ -9054,19 +8916,19 @@
         <v>0</v>
       </c>
       <c r="B230" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E230" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F230" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G230" s="1">
         <v>46309</v>
@@ -9080,19 +8942,19 @@
         <v>0</v>
       </c>
       <c r="B231" t="s">
+        <v>465</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231" t="s">
+        <v>128</v>
+      </c>
+      <c r="E231" t="s">
+        <v>466</v>
+      </c>
+      <c r="F231" t="s">
         <v>467</v>
-      </c>
-      <c r="C231">
-        <v>1</v>
-      </c>
-      <c r="D231" t="s">
-        <v>128</v>
-      </c>
-      <c r="E231" t="s">
-        <v>37</v>
-      </c>
-      <c r="F231" t="s">
-        <v>38</v>
       </c>
       <c r="G231" s="1">
         <v>46309</v>
@@ -9109,10 +8971,10 @@
         <v>468</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E232" t="s">
         <v>469</v>
@@ -9124,7 +8986,7 @@
         <v>46309</v>
       </c>
       <c r="H232" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -9138,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E233" t="s">
         <v>472</v>
@@ -9164,13 +9026,13 @@
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E234" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="F234" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="G234" s="1">
         <v>46309</v>
@@ -9184,19 +9046,19 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
+        <v>475</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>128</v>
+      </c>
+      <c r="E235" t="s">
+        <v>476</v>
+      </c>
+      <c r="F235" t="s">
         <v>477</v>
-      </c>
-      <c r="C235">
-        <v>1</v>
-      </c>
-      <c r="D235" t="s">
-        <v>128</v>
-      </c>
-      <c r="E235" t="s">
-        <v>285</v>
-      </c>
-      <c r="F235" t="s">
-        <v>286</v>
       </c>
       <c r="G235" s="1">
         <v>46309</v>
@@ -9219,10 +9081,10 @@
         <v>128</v>
       </c>
       <c r="E236" t="s">
-        <v>479</v>
+        <v>219</v>
       </c>
       <c r="F236" t="s">
-        <v>480</v>
+        <v>220</v>
       </c>
       <c r="G236" s="1">
         <v>46309</v>
@@ -9236,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9245,10 +9107,10 @@
         <v>128</v>
       </c>
       <c r="E237" t="s">
-        <v>479</v>
+        <v>332</v>
       </c>
       <c r="F237" t="s">
-        <v>480</v>
+        <v>333</v>
       </c>
       <c r="G237" s="1">
         <v>46309</v>
@@ -9262,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9271,10 +9133,10 @@
         <v>128</v>
       </c>
       <c r="E238" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="F238" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="G238" s="1">
         <v>46309</v>
@@ -9288,19 +9150,19 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E239" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="F239" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="G239" s="1">
         <v>46309</v>
@@ -9314,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9323,10 +9185,10 @@
         <v>128</v>
       </c>
       <c r="E240" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="F240" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="G240" s="1">
         <v>46309</v>
@@ -9340,25 +9202,25 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="E241" t="s">
-        <v>486</v>
+        <v>172</v>
       </c>
       <c r="F241" t="s">
-        <v>487</v>
+        <v>173</v>
       </c>
       <c r="G241" s="1">
         <v>46309</v>
       </c>
       <c r="H241" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -9366,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9375,10 +9237,10 @@
         <v>128</v>
       </c>
       <c r="E242" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F242" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G242" s="1">
         <v>46309</v>
@@ -9392,25 +9254,25 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E243" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F243" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G243" s="1">
         <v>46309</v>
       </c>
       <c r="H243" s="1">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -9418,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9427,10 +9289,10 @@
         <v>128</v>
       </c>
       <c r="E244" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F244" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G244" s="1">
         <v>46309</v>
@@ -9444,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9453,10 +9315,10 @@
         <v>128</v>
       </c>
       <c r="E245" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="F245" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="G245" s="1">
         <v>46309</v>
@@ -9470,25 +9332,25 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
+        <v>496</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="D246" t="s">
+        <v>128</v>
+      </c>
+      <c r="E246" t="s">
+        <v>497</v>
+      </c>
+      <c r="F246" t="s">
         <v>498</v>
-      </c>
-      <c r="C246">
-        <v>1</v>
-      </c>
-      <c r="D246" t="s">
-        <v>128</v>
-      </c>
-      <c r="E246" t="s">
-        <v>499</v>
-      </c>
-      <c r="F246" t="s">
-        <v>500</v>
       </c>
       <c r="G246" s="1">
         <v>46309</v>
       </c>
       <c r="H246" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -9496,25 +9358,25 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
+        <v>499</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247" t="s">
+        <v>128</v>
+      </c>
+      <c r="E247" t="s">
+        <v>500</v>
+      </c>
+      <c r="F247" t="s">
         <v>501</v>
-      </c>
-      <c r="C247">
-        <v>1</v>
-      </c>
-      <c r="D247" t="s">
-        <v>128</v>
-      </c>
-      <c r="E247" t="s">
-        <v>219</v>
-      </c>
-      <c r="F247" t="s">
-        <v>220</v>
       </c>
       <c r="G247" s="1">
         <v>46309</v>
       </c>
       <c r="H247" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -9531,16 +9393,16 @@
         <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>338</v>
+        <v>503</v>
       </c>
       <c r="F248" t="s">
-        <v>339</v>
+        <v>504</v>
       </c>
       <c r="G248" s="1">
         <v>46309</v>
       </c>
       <c r="H248" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -9548,7 +9410,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9557,16 +9419,16 @@
         <v>128</v>
       </c>
       <c r="E249" t="s">
-        <v>202</v>
+        <v>389</v>
       </c>
       <c r="F249" t="s">
-        <v>203</v>
+        <v>390</v>
       </c>
       <c r="G249" s="1">
         <v>46309</v>
       </c>
       <c r="H249" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -9574,7 +9436,7 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9583,16 +9445,16 @@
         <v>128</v>
       </c>
       <c r="E250" t="s">
-        <v>202</v>
+        <v>507</v>
       </c>
       <c r="F250" t="s">
-        <v>203</v>
+        <v>508</v>
       </c>
       <c r="G250" s="1">
         <v>46309</v>
       </c>
       <c r="H250" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -9600,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9609,16 +9471,16 @@
         <v>128</v>
       </c>
       <c r="E251" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="F251" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="G251" s="1">
         <v>46309</v>
       </c>
       <c r="H251" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -9626,25 +9488,25 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E252" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F252" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G252" s="1">
         <v>46309</v>
       </c>
       <c r="H252" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -9652,19 +9514,19 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E253" t="s">
-        <v>172</v>
+        <v>512</v>
       </c>
       <c r="F253" t="s">
-        <v>173</v>
+        <v>513</v>
       </c>
       <c r="G253" s="1">
         <v>46309</v>
@@ -9678,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9687,16 +9549,16 @@
         <v>128</v>
       </c>
       <c r="E254" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F254" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G254" s="1">
         <v>46309</v>
       </c>
       <c r="H254" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -9704,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9713,10 +9575,10 @@
         <v>2</v>
       </c>
       <c r="E255" t="s">
-        <v>453</v>
+        <v>13</v>
       </c>
       <c r="F255" t="s">
-        <v>454</v>
+        <v>14</v>
       </c>
       <c r="G255" s="1">
         <v>46309</v>
@@ -9730,7 +9592,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9739,16 +9601,16 @@
         <v>128</v>
       </c>
       <c r="E256" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F256" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G256" s="1">
         <v>46309</v>
       </c>
       <c r="H256" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -9756,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9765,16 +9627,16 @@
         <v>128</v>
       </c>
       <c r="E257" t="s">
-        <v>516</v>
+        <v>332</v>
       </c>
       <c r="F257" t="s">
-        <v>517</v>
+        <v>333</v>
       </c>
       <c r="G257" s="1">
         <v>46309</v>
       </c>
       <c r="H257" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -9782,25 +9644,25 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E258" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F258" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G258" s="1">
         <v>46309</v>
       </c>
       <c r="H258" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -9808,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9817,10 +9679,10 @@
         <v>128</v>
       </c>
       <c r="E259" t="s">
-        <v>522</v>
+        <v>152</v>
       </c>
       <c r="F259" t="s">
-        <v>523</v>
+        <v>153</v>
       </c>
       <c r="G259" s="1">
         <v>46309</v>
@@ -9843,10 +9705,10 @@
         <v>128</v>
       </c>
       <c r="E260" t="s">
-        <v>525</v>
+        <v>152</v>
       </c>
       <c r="F260" t="s">
-        <v>526</v>
+        <v>153</v>
       </c>
       <c r="G260" s="1">
         <v>46309</v>
@@ -9860,19 +9722,19 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
+        <v>525</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261" t="s">
+        <v>128</v>
+      </c>
+      <c r="E261" t="s">
+        <v>526</v>
+      </c>
+      <c r="F261" t="s">
         <v>527</v>
-      </c>
-      <c r="C261">
-        <v>1</v>
-      </c>
-      <c r="D261" t="s">
-        <v>128</v>
-      </c>
-      <c r="E261" t="s">
-        <v>528</v>
-      </c>
-      <c r="F261" t="s">
-        <v>529</v>
       </c>
       <c r="G261" s="1">
         <v>46309</v>
@@ -9886,19 +9748,19 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
+        <v>528</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+      <c r="D262" t="s">
+        <v>128</v>
+      </c>
+      <c r="E262" t="s">
+        <v>529</v>
+      </c>
+      <c r="F262" t="s">
         <v>530</v>
-      </c>
-      <c r="C262">
-        <v>1</v>
-      </c>
-      <c r="D262" t="s">
-        <v>128</v>
-      </c>
-      <c r="E262" t="s">
-        <v>399</v>
-      </c>
-      <c r="F262" t="s">
-        <v>400</v>
       </c>
       <c r="G262" s="1">
         <v>46309</v>
@@ -9927,7 +9789,7 @@
         <v>533</v>
       </c>
       <c r="G263" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H263" s="1">
         <v>46310</v>
@@ -9947,13 +9809,13 @@
         <v>128</v>
       </c>
       <c r="E264" t="s">
-        <v>77</v>
+        <v>535</v>
       </c>
       <c r="F264" t="s">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="G264" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H264" s="1">
         <v>46310</v>
@@ -9964,7 +9826,7 @@
         <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9973,13 +9835,13 @@
         <v>128</v>
       </c>
       <c r="E265" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F265" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G265" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H265" s="1">
         <v>46310</v>
@@ -9990,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="B266" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9999,13 +9861,13 @@
         <v>128</v>
       </c>
       <c r="E266" t="s">
-        <v>537</v>
+        <v>37</v>
       </c>
       <c r="F266" t="s">
-        <v>538</v>
+        <v>38</v>
       </c>
       <c r="G266" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H266" s="1">
         <v>46310</v>
@@ -10025,13 +9887,13 @@
         <v>128</v>
       </c>
       <c r="E267" t="s">
-        <v>537</v>
+        <v>37</v>
       </c>
       <c r="F267" t="s">
-        <v>538</v>
+        <v>38</v>
       </c>
       <c r="G267" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H267" s="1">
         <v>46310</v>
@@ -10048,16 +9910,16 @@
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E268" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F268" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G268" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H268" s="1">
         <v>46310</v>
@@ -10077,13 +9939,13 @@
         <v>128</v>
       </c>
       <c r="E269" t="s">
-        <v>542</v>
+        <v>37</v>
       </c>
       <c r="F269" t="s">
-        <v>543</v>
+        <v>38</v>
       </c>
       <c r="G269" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H269" s="1">
         <v>46310</v>
@@ -10094,22 +9956,22 @@
         <v>0</v>
       </c>
       <c r="B270" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E270" t="s">
-        <v>545</v>
+        <v>37</v>
       </c>
       <c r="F270" t="s">
-        <v>546</v>
+        <v>38</v>
       </c>
       <c r="G270" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H270" s="1">
         <v>46310</v>
@@ -10120,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -10129,13 +9991,13 @@
         <v>128</v>
       </c>
       <c r="E271" t="s">
-        <v>338</v>
+        <v>37</v>
       </c>
       <c r="F271" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="G271" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H271" s="1">
         <v>46310</v>
@@ -10146,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -10155,13 +10017,13 @@
         <v>128</v>
       </c>
       <c r="E272" t="s">
-        <v>549</v>
+        <v>37</v>
       </c>
       <c r="F272" t="s">
-        <v>550</v>
+        <v>38</v>
       </c>
       <c r="G272" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H272" s="1">
         <v>46310</v>
@@ -10172,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -10181,13 +10043,13 @@
         <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F273" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="G273" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H273" s="1">
         <v>46310</v>
@@ -10198,7 +10060,7 @@
         <v>0</v>
       </c>
       <c r="B274" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -10207,13 +10069,13 @@
         <v>128</v>
       </c>
       <c r="E274" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F274" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="G274" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H274" s="1">
         <v>46310</v>
@@ -10224,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -10233,13 +10095,13 @@
         <v>128</v>
       </c>
       <c r="E275" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F275" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G275" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H275" s="1">
         <v>46310</v>
@@ -10250,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -10259,13 +10121,13 @@
         <v>128</v>
       </c>
       <c r="E276" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="F276" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="G276" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H276" s="1">
         <v>46310</v>
@@ -10276,19 +10138,19 @@
         <v>0</v>
       </c>
       <c r="B277" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E277" t="s">
-        <v>453</v>
+        <v>252</v>
       </c>
       <c r="F277" t="s">
-        <v>454</v>
+        <v>253</v>
       </c>
       <c r="G277" s="1">
         <v>46310</v>
@@ -10302,7 +10164,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -10311,16 +10173,16 @@
         <v>128</v>
       </c>
       <c r="E278" t="s">
-        <v>561</v>
+        <v>503</v>
       </c>
       <c r="F278" t="s">
-        <v>562</v>
+        <v>504</v>
       </c>
       <c r="G278" s="1">
         <v>46310</v>
       </c>
       <c r="H278" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -10328,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -10337,10 +10199,10 @@
         <v>128</v>
       </c>
       <c r="E279" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="F279" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="G279" s="1">
         <v>46310</v>
@@ -10354,7 +10216,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -10363,16 +10225,16 @@
         <v>128</v>
       </c>
       <c r="E280" t="s">
-        <v>37</v>
+        <v>559</v>
       </c>
       <c r="F280" t="s">
-        <v>38</v>
+        <v>560</v>
       </c>
       <c r="G280" s="1">
         <v>46310</v>
       </c>
       <c r="H280" s="1">
-        <v>46310</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -10380,7 +10242,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10389,10 +10251,10 @@
         <v>128</v>
       </c>
       <c r="E281" t="s">
-        <v>37</v>
+        <v>562</v>
       </c>
       <c r="F281" t="s">
-        <v>38</v>
+        <v>563</v>
       </c>
       <c r="G281" s="1">
         <v>46310</v>
@@ -10406,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="B282" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -10415,10 +10277,10 @@
         <v>128</v>
       </c>
       <c r="E282" t="s">
-        <v>37</v>
+        <v>565</v>
       </c>
       <c r="F282" t="s">
-        <v>38</v>
+        <v>566</v>
       </c>
       <c r="G282" s="1">
         <v>46310</v>
@@ -10432,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -10441,10 +10303,10 @@
         <v>128</v>
       </c>
       <c r="E283" t="s">
-        <v>37</v>
+        <v>237</v>
       </c>
       <c r="F283" t="s">
-        <v>38</v>
+        <v>238</v>
       </c>
       <c r="G283" s="1">
         <v>46310</v>
@@ -10458,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -10467,10 +10329,10 @@
         <v>128</v>
       </c>
       <c r="E284" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="F284" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="G284" s="1">
         <v>46310</v>
@@ -10484,19 +10346,19 @@
         <v>0</v>
       </c>
       <c r="B285" t="s">
+        <v>569</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+      <c r="D285" t="s">
+        <v>128</v>
+      </c>
+      <c r="E285" t="s">
+        <v>570</v>
+      </c>
+      <c r="F285" t="s">
         <v>571</v>
-      </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="D285" t="s">
-        <v>128</v>
-      </c>
-      <c r="E285" t="s">
-        <v>37</v>
-      </c>
-      <c r="F285" t="s">
-        <v>38</v>
       </c>
       <c r="G285" s="1">
         <v>46310</v>
@@ -10519,10 +10381,10 @@
         <v>128</v>
       </c>
       <c r="E286" t="s">
-        <v>37</v>
+        <v>573</v>
       </c>
       <c r="F286" t="s">
-        <v>38</v>
+        <v>574</v>
       </c>
       <c r="G286" s="1">
         <v>46310</v>
@@ -10536,19 +10398,19 @@
         <v>0</v>
       </c>
       <c r="B287" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287" t="s">
         <v>128</v>
       </c>
       <c r="E287" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F287" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G287" s="1">
         <v>46310</v>
@@ -10562,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -10571,10 +10433,10 @@
         <v>128</v>
       </c>
       <c r="E288" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F288" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G288" s="1">
         <v>46310</v>
@@ -10588,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -10597,10 +10459,10 @@
         <v>128</v>
       </c>
       <c r="E289" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="F289" t="s">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="G289" s="1">
         <v>46310</v>
@@ -10614,7 +10476,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -10623,10 +10485,10 @@
         <v>128</v>
       </c>
       <c r="E290" t="s">
-        <v>577</v>
+        <v>517</v>
       </c>
       <c r="F290" t="s">
-        <v>578</v>
+        <v>518</v>
       </c>
       <c r="G290" s="1">
         <v>46310</v>
@@ -10675,10 +10537,10 @@
         <v>128</v>
       </c>
       <c r="E292" t="s">
-        <v>252</v>
+        <v>583</v>
       </c>
       <c r="F292" t="s">
-        <v>253</v>
+        <v>584</v>
       </c>
       <c r="G292" s="1">
         <v>46310</v>
@@ -10692,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -10701,16 +10563,16 @@
         <v>128</v>
       </c>
       <c r="E293" t="s">
-        <v>528</v>
+        <v>586</v>
       </c>
       <c r="F293" t="s">
-        <v>529</v>
+        <v>587</v>
       </c>
       <c r="G293" s="1">
         <v>46310</v>
       </c>
       <c r="H293" s="1">
-        <v>46311</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -10718,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -10727,10 +10589,10 @@
         <v>128</v>
       </c>
       <c r="E294" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F294" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G294" s="1">
         <v>46310</v>
@@ -10744,25 +10606,25 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" t="s">
         <v>128</v>
       </c>
       <c r="E295" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F295" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G295" s="1">
         <v>46310</v>
       </c>
       <c r="H295" s="1">
-        <v>46310</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -10770,7 +10632,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -10779,10 +10641,10 @@
         <v>128</v>
       </c>
       <c r="E296" t="s">
-        <v>591</v>
+        <v>16</v>
       </c>
       <c r="F296" t="s">
-        <v>592</v>
+        <v>17</v>
       </c>
       <c r="G296" s="1">
         <v>46310</v>
@@ -10796,7 +10658,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -10805,10 +10667,10 @@
         <v>128</v>
       </c>
       <c r="E297" t="s">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c r="F297" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="G297" s="1">
         <v>46310</v>
@@ -10822,7 +10684,7 @@
         <v>0</v>
       </c>
       <c r="B298" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -10831,10 +10693,10 @@
         <v>128</v>
       </c>
       <c r="E298" t="s">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="F298" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="G298" s="1">
         <v>46310</v>
@@ -10848,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -10857,10 +10719,10 @@
         <v>128</v>
       </c>
       <c r="E299" t="s">
-        <v>596</v>
+        <v>16</v>
       </c>
       <c r="F299" t="s">
-        <v>597</v>
+        <v>17</v>
       </c>
       <c r="G299" s="1">
         <v>46310</v>
@@ -10883,10 +10745,10 @@
         <v>128</v>
       </c>
       <c r="E300" t="s">
-        <v>599</v>
+        <v>494</v>
       </c>
       <c r="F300" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G300" s="1">
         <v>46310</v>
@@ -10900,19 +10762,19 @@
         <v>0</v>
       </c>
       <c r="B301" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D301" t="s">
         <v>128</v>
       </c>
       <c r="E301" t="s">
-        <v>16</v>
+        <v>488</v>
       </c>
       <c r="F301" t="s">
-        <v>17</v>
+        <v>489</v>
       </c>
       <c r="G301" s="1">
        